--- a/data/batches/2026-10-29/SwingScope_2026-10-29_tracker.xlsx
+++ b/data/batches/2026-10-29/SwingScope_2026-10-29_tracker.xlsx
@@ -1498,7 +1498,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Signal 2026-10-29  •  Day 1 of 21  •  Entry day (bought at open)  •  Exit ~2026-12-01  •  Updated 30-Oct-2026 14:55</t>
+          <t>Signal 2026-10-29  •  Day 1 of 21  •  Entry day (bought at open)  •  Exit ~2026-12-01  •  Updated 30-Oct-2026 18:08</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2385,7 +2385,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Signal 2026-10-29  •  Day 1 of 21  •  Entry day (bought at open)  •  Exit ~2026-12-01  •  Updated 30-Oct-2026 14:55</t>
+          <t>Signal 2026-10-29  •  Day 1 of 21  •  Entry day (bought at open)  •  Exit ~2026-12-01  •  Updated 30-Oct-2026 18:08</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -8125,7 +8125,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Views from auto-generated · written 2026-10-30 14:55</t>
+          <t>Views from auto-generated · written 2026-10-30 18:08</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -8271,7 +8271,7 @@
         </is>
       </c>
       <c r="E7" s="68" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="F7" s="69" t="inlineStr">
         <is>
@@ -8307,7 +8307,7 @@
         </is>
       </c>
       <c r="E8" s="68" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="F8" s="69" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
         </is>
       </c>
       <c r="E11" s="68" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.46</v>
       </c>
       <c r="F11" s="69" t="inlineStr">
         <is>
@@ -10432,7 +10432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G139"/>
+  <dimension ref="A1:G125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10460,7 +10460,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Fetched 2026-10-30 14:55</t>
+          <t>Fetched 2026-10-30 18:08</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -10510,26 +10510,26 @@
     <row r="5">
       <c r="A5" s="51" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B5" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 13:51</t>
+          <t>2026-10-30 17:26</t>
         </is>
       </c>
       <c r="C5" s="51" t="inlineStr">
         <is>
-          <t>Syrma SGS Q2 results: Profit nearly doubles to ₹117 crore, revenue jumps 74%</t>
+          <t>Markets hit 6-month high in Oct on IT rally, Jio Platforms IPO frenzy</t>
         </is>
       </c>
       <c r="D5" s="51" t="inlineStr">
         <is>
-          <t>CNBC TV18</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="E5" s="81" t="n">
-        <v>0.66</v>
+        <v>0.226</v>
       </c>
       <c r="F5" s="51" t="inlineStr">
         <is>
@@ -10545,22 +10545,22 @@
     <row r="6">
       <c r="A6" s="51" t="inlineStr">
         <is>
-          <t>AETHER</t>
+          <t>SYRMA</t>
         </is>
       </c>
       <c r="B6" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 12:34</t>
+          <t>2026-10-30 16:35</t>
         </is>
       </c>
       <c r="C6" s="51" t="inlineStr">
         <is>
-          <t>Aether Industries (NSE:AETHER): What Do Aether Industries’ September-Quarter Results Show?</t>
+          <t>Syrma SGS reports best-ever quarter; Q2 revenue up 73% to Rs 1,999.5 crore</t>
         </is>
       </c>
       <c r="D6" s="51" t="inlineStr">
         <is>
-          <t>Kalkine India</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="E6" s="81" t="n">
@@ -10580,26 +10580,26 @@
     <row r="7">
       <c r="A7" s="51" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B7" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 11:15</t>
+          <t>2026-10-30 16:07</t>
         </is>
       </c>
       <c r="C7" s="51" t="inlineStr">
         <is>
-          <t>Syrma SGS Technology Q2 results: Net profit jumps 83.1% YoY to Rs 117 crore, EBITDA rises 67.7%</t>
+          <t>Sensex Gains 308 Points, Nifty Reclaims 23,000 as IT and Pharma Stocks Lead Recovery</t>
         </is>
       </c>
       <c r="D7" s="51" t="inlineStr">
         <is>
-          <t>Business Upturn</t>
+          <t>The Indian Awaaz</t>
         </is>
       </c>
       <c r="E7" s="81" t="n">
-        <v>0.66</v>
+        <v>0.649</v>
       </c>
       <c r="F7" s="51" t="inlineStr">
         <is>
@@ -10615,26 +10615,26 @@
     <row r="8">
       <c r="A8" s="51" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B8" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 11:14</t>
+          <t>2026-10-30 16:01</t>
         </is>
       </c>
       <c r="C8" s="51" t="inlineStr">
         <is>
-          <t>Diwali 2026 Top Stocks To Buy: Apollo Hospitals, GE Vernova, TARIL, TD Power, Jindal Steel, others; top 10 picks, target</t>
+          <t>Indian Shares Snap Two-Month Losing Streak, Nifty And Sensex Gain In October</t>
         </is>
       </c>
       <c r="D8" s="51" t="inlineStr">
         <is>
-          <t>Livemint</t>
+          <t>TradingView</t>
         </is>
       </c>
       <c r="E8" s="81" t="n">
-        <v>0.66</v>
+        <v>0.361</v>
       </c>
       <c r="F8" s="51" t="inlineStr">
         <is>
@@ -10655,25 +10655,25 @@
       </c>
       <c r="B9" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 10:56</t>
+          <t>2026-10-30 15:13</t>
         </is>
       </c>
       <c r="C9" s="51" t="inlineStr">
         <is>
-          <t>Market wrap: Shriram Finance, Nestle India, Trent, InterGlobe top gainers and losers on Nifty and Sensex</t>
+          <t>Sensex Gains 308 Points, Nifty Closes Above 23,000 as IT and Pharma Stocks Lead Rally</t>
         </is>
       </c>
       <c r="D9" s="51" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>INDIA New England News</t>
         </is>
       </c>
       <c r="E9" s="81" t="n">
-        <v>0.026</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="F9" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G9" s="82" t="inlineStr">
@@ -10685,26 +10685,26 @@
     <row r="10">
       <c r="A10" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>SYRMA</t>
         </is>
       </c>
       <c r="B10" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 10:53</t>
+          <t>2026-10-30 13:51</t>
         </is>
       </c>
       <c r="C10" s="51" t="inlineStr">
         <is>
-          <t>Sensex, Nifty Rise; IT &amp; Pharma Lift Markets as Midcaps Slide</t>
+          <t>Syrma SGS Q2 results: Profit nearly doubles to ₹117 crore, revenue jumps 74%</t>
         </is>
       </c>
       <c r="D10" s="51" t="inlineStr">
         <is>
-          <t>HDFC Sky</t>
+          <t>CNBC TV18</t>
         </is>
       </c>
       <c r="E10" s="81" t="n">
-        <v>0.402</v>
+        <v>0.66</v>
       </c>
       <c r="F10" s="51" t="inlineStr">
         <is>
@@ -10720,26 +10720,26 @@
     <row r="11">
       <c r="A11" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>AETHER</t>
         </is>
       </c>
       <c r="B11" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 10:35</t>
+          <t>2026-10-30 12:34</t>
         </is>
       </c>
       <c r="C11" s="51" t="inlineStr">
         <is>
-          <t>Sensex rises 308 points, Nifty above 23,000 even as broader markets crash. Will D-Street bulls extend reco</t>
+          <t>Aether Industries (NSE:AETHER): What Do Aether Industries’ September-Quarter Results Show?</t>
         </is>
       </c>
       <c r="D11" s="51" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>Kalkine India</t>
         </is>
       </c>
       <c r="E11" s="81" t="n">
-        <v>-0.103</v>
+        <v>0</v>
       </c>
       <c r="F11" s="51" t="inlineStr">
         <is>
@@ -10760,21 +10760,21 @@
       </c>
       <c r="B12" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 10:31</t>
+          <t>2026-10-30 12:12</t>
         </is>
       </c>
       <c r="C12" s="51" t="inlineStr">
         <is>
-          <t>Sensex, Nifty extend gains for 2nd day: IT stocks lead rally, broader market underperforms</t>
+          <t>Stock markets rise for 2nd session; Sensex gains 300 points on buying in IT stocks</t>
         </is>
       </c>
       <c r="D12" s="51" t="inlineStr">
         <is>
-          <t>IndiaIPO</t>
+          <t>The Tribune</t>
         </is>
       </c>
       <c r="E12" s="81" t="n">
-        <v>0.84</v>
+        <v>0.382</v>
       </c>
       <c r="F12" s="51" t="inlineStr">
         <is>
@@ -10795,21 +10795,21 @@
       </c>
       <c r="B13" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 10:31</t>
+          <t>2026-10-30 12:05</t>
         </is>
       </c>
       <c r="C13" s="51" t="inlineStr">
         <is>
-          <t>Sensex, Nifty extend recovery; what's driving this upmove? -</t>
+          <t>Rupee gains 33 paise as dollar weakens, Sensex and Nifty end higher</t>
         </is>
       </c>
       <c r="D13" s="51" t="inlineStr">
         <is>
-          <t>IndiaIPO</t>
+          <t>The Times of India</t>
         </is>
       </c>
       <c r="E13" s="81" t="n">
-        <v>0.527</v>
+        <v>0.459</v>
       </c>
       <c r="F13" s="51" t="inlineStr">
         <is>
@@ -10830,17 +10830,17 @@
       </c>
       <c r="B14" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 10:28</t>
+          <t>2026-10-30 11:43</t>
         </is>
       </c>
       <c r="C14" s="51" t="inlineStr">
         <is>
-          <t>Sensex Today Ends 308 Points Higher | Nifty Above 22,300 | Vedanta Oil and Gas Up 8%</t>
+          <t>Sensex, Nifty End Higher as IT and Pharma Stocks Lead Gains; Broader Markets Remain Weak</t>
         </is>
       </c>
       <c r="D14" s="51" t="inlineStr">
         <is>
-          <t>Equitymaster</t>
+          <t>Business News This Week</t>
         </is>
       </c>
       <c r="E14" s="81" t="n">
@@ -10865,21 +10865,21 @@
       </c>
       <c r="B15" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 10:26</t>
+          <t>2026-10-30 11:26</t>
         </is>
       </c>
       <c r="C15" s="51" t="inlineStr">
         <is>
-          <t>Sensex, Nifty close with gain of 0.5% as IT, pharma stocks rally; weak broader market limits gains</t>
+          <t>Share Market Today: Nifty 50, Bank Nifty | Oct 30, 2026</t>
         </is>
       </c>
       <c r="D15" s="51" t="inlineStr">
         <is>
-          <t>ChiniMandi</t>
+          <t>Liquide Blog</t>
         </is>
       </c>
       <c r="E15" s="81" t="n">
-        <v>0.796</v>
+        <v>0.66</v>
       </c>
       <c r="F15" s="51" t="inlineStr">
         <is>
@@ -10900,21 +10900,21 @@
       </c>
       <c r="B16" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 10:03</t>
+          <t>2026-10-30 11:25</t>
         </is>
       </c>
       <c r="C16" s="51" t="inlineStr">
         <is>
-          <t>Sensex ends 308 points higher, Nifty above 23,000; Trent up 5%</t>
+          <t>Stock market today: Sensex, Nifty extend gains for second day as IT, pharma stocks lead rally</t>
         </is>
       </c>
       <c r="D16" s="51" t="inlineStr">
         <is>
-          <t>India Today</t>
+          <t>IBTimes India</t>
         </is>
       </c>
       <c r="E16" s="81" t="n">
-        <v>0.402</v>
+        <v>0.84</v>
       </c>
       <c r="F16" s="51" t="inlineStr">
         <is>
@@ -10935,25 +10935,25 @@
       </c>
       <c r="B17" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 09:52</t>
+          <t>2026-10-30 11:24</t>
         </is>
       </c>
       <c r="C17" s="51" t="inlineStr">
         <is>
-          <t>Market Wrap: Sensex Gains 308 Points, Nifty 50 Ends Above 23,000; Trent, IndiGo, Infosys Lead</t>
+          <t>Green Energy Stocks Decline Despite Sensex Gaining 0.4% On October 30</t>
         </is>
       </c>
       <c r="D17" s="51" t="inlineStr">
         <is>
-          <t>NDTV Profit</t>
+          <t>SolarQuarter</t>
         </is>
       </c>
       <c r="E17" s="81" t="n">
-        <v>0.649</v>
+        <v>-0.428</v>
       </c>
       <c r="F17" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G17" s="82" t="inlineStr">
@@ -10965,30 +10965,30 @@
     <row r="18">
       <c r="A18" s="51" t="inlineStr">
         <is>
-          <t>CPPLUS</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B18" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 08:44</t>
+          <t>2026-10-30 11:17</t>
         </is>
       </c>
       <c r="C18" s="51" t="inlineStr">
         <is>
-          <t>Aditya Infotech CPPLUS ESOP Allotment 48,100 Shares Oct 2026</t>
+          <t>Markets rally for 2nd day amid buying in IT firms, earnings-driven demand in Trent</t>
         </is>
       </c>
       <c r="D18" s="51" t="inlineStr">
         <is>
-          <t>Kalkine India</t>
+          <t>OrissaPOST</t>
         </is>
       </c>
       <c r="E18" s="81" t="n">
-        <v>0</v>
+        <v>0.361</v>
       </c>
       <c r="F18" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G18" s="82" t="inlineStr">
@@ -11000,26 +11000,26 @@
     <row r="19">
       <c r="A19" s="51" t="inlineStr">
         <is>
-          <t>AETHER</t>
+          <t>SYRMA</t>
         </is>
       </c>
       <c r="B19" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 08:35</t>
+          <t>2026-10-30 11:14</t>
         </is>
       </c>
       <c r="C19" s="51" t="inlineStr">
         <is>
-          <t>Aether Industries reports robust Q2 FY27 financial performance with ₹3,472M in operating revenue</t>
+          <t>Diwali 2026 Top Stocks To Buy: Apollo Hospitals, GE Vernova, TARIL, TD Power, Jindal Steel, others; top 10 picks, target</t>
         </is>
       </c>
       <c r="D19" s="51" t="inlineStr">
         <is>
-          <t>Business Upturn</t>
+          <t>Livemint</t>
         </is>
       </c>
       <c r="E19" s="81" t="n">
-        <v>0.421</v>
+        <v>0.66</v>
       </c>
       <c r="F19" s="51" t="inlineStr">
         <is>
@@ -11040,21 +11040,21 @@
       </c>
       <c r="B20" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 08:02</t>
+          <t>2026-10-30 11:07</t>
         </is>
       </c>
       <c r="C20" s="51" t="inlineStr">
         <is>
-          <t>Sensex zooms 1,200 pts in 2 days, Nifty tops 23K: Why are bulls in charge?</t>
+          <t>Indian Equities Rally on IT Sector Strength, Trent Earnings</t>
         </is>
       </c>
       <c r="D20" s="51" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>Rediff</t>
         </is>
       </c>
       <c r="E20" s="81" t="n">
-        <v>0.718</v>
+        <v>0.735</v>
       </c>
       <c r="F20" s="51" t="inlineStr">
         <is>
@@ -11075,21 +11075,21 @@
       </c>
       <c r="B21" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 06:40</t>
+          <t>2026-10-30 11:00</t>
         </is>
       </c>
       <c r="C21" s="51" t="inlineStr">
         <is>
-          <t>Passive funds could buy up to Rs 36,500 crore upon Jio Platforms' entry into Nifty, Sensex</t>
+          <t>Sensex Rises Over 300 Points, Nifty Closes Above 23,050; IT, Pharma Stocks Lead Market Gains</t>
         </is>
       </c>
       <c r="D21" s="51" t="inlineStr">
         <is>
-          <t>Moneycontrol.com</t>
+          <t>Times Now</t>
         </is>
       </c>
       <c r="E21" s="81" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.649</v>
       </c>
       <c r="F21" s="51" t="inlineStr">
         <is>
@@ -11105,30 +11105,30 @@
     <row r="22">
       <c r="A22" s="51" t="inlineStr">
         <is>
-          <t>AETHER</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B22" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 06:37</t>
+          <t>2026-10-30 10:59</t>
         </is>
       </c>
       <c r="C22" s="51" t="inlineStr">
         <is>
-          <t>AETHER Share Price Today - Aether Industries on NSE/BSE</t>
+          <t>Sensex and Nifty Gain Amid Mixed Sector Performance; Large Caps Lead Market Rally</t>
         </is>
       </c>
       <c r="D22" s="51" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>MarketsMojo</t>
         </is>
       </c>
       <c r="E22" s="81" t="n">
-        <v>0</v>
+        <v>0.796</v>
       </c>
       <c r="F22" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G22" s="82" t="inlineStr">
@@ -11140,30 +11140,30 @@
     <row r="23">
       <c r="A23" s="51" t="inlineStr">
         <is>
-          <t>AETHER</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B23" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 06:35</t>
+          <t>2026-10-30 10:56</t>
         </is>
       </c>
       <c r="C23" s="51" t="inlineStr">
         <is>
-          <t>Aether Industries Q2 FY27: Net profit rises 26% to ₹68 crore as revenue climbs 24% to ₹347 crore</t>
+          <t>Market wrap: Shriram Finance, Nestle India, Trent, InterGlobe top gainers and losers on Nifty and Sensex</t>
         </is>
       </c>
       <c r="D23" s="51" t="inlineStr">
         <is>
-          <t>Business Upturn</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="E23" s="81" t="n">
-        <v>0.612</v>
+        <v>0.026</v>
       </c>
       <c r="F23" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G23" s="82" t="inlineStr">
@@ -11175,30 +11175,30 @@
     <row r="24">
       <c r="A24" s="51" t="inlineStr">
         <is>
-          <t>AETHER</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B24" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 06:31</t>
+          <t>2026-10-30 10:53</t>
         </is>
       </c>
       <c r="C24" s="51" t="inlineStr">
         <is>
-          <t>Aether Industries Q2 FY27 Results: Revenue, EBITDA and PAT</t>
+          <t>Sensex, Nifty Rise; IT &amp; Pharma Lift Markets as Midcaps Slide</t>
         </is>
       </c>
       <c r="D24" s="51" t="inlineStr">
         <is>
-          <t>Kalkine India</t>
+          <t>HDFC Sky</t>
         </is>
       </c>
       <c r="E24" s="81" t="n">
-        <v>0</v>
+        <v>0.402</v>
       </c>
       <c r="F24" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G24" s="82" t="inlineStr">
@@ -11215,25 +11215,25 @@
       </c>
       <c r="B25" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 05:36</t>
+          <t>2026-10-30 10:36</t>
         </is>
       </c>
       <c r="C25" s="51" t="inlineStr">
         <is>
-          <t>Sensex, Nifty turn lower; broader markets crash as oil tops $116/barrel. What lies ahead?</t>
+          <t>Closing Bell: Sensex Gains 300 Points, Nifty Reclaims 23,000 Mark as IT Stocks a Lead Rally</t>
         </is>
       </c>
       <c r="D25" s="51" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>Dalal Street Investment Journal</t>
         </is>
       </c>
       <c r="E25" s="81" t="n">
-        <v>-0.34</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="F25" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G25" s="82" t="inlineStr">
@@ -11250,25 +11250,25 @@
       </c>
       <c r="B26" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 05:13</t>
+          <t>2026-10-30 10:35</t>
         </is>
       </c>
       <c r="C26" s="51" t="inlineStr">
         <is>
-          <t>Sensex, Nifty Open Volatile; India VIX Rises, Crude Above $116</t>
+          <t>Sensex rises 308 points, Nifty above 23,000 even as broader markets crash. Will D-Street bulls extend reco</t>
         </is>
       </c>
       <c r="D26" s="51" t="inlineStr">
         <is>
-          <t>HDFC Sky</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="E26" s="81" t="n">
-        <v>-0.25</v>
+        <v>-0.103</v>
       </c>
       <c r="F26" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G26" s="82" t="inlineStr">
@@ -11285,25 +11285,25 @@
       </c>
       <c r="B27" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 05:07</t>
+          <t>2026-10-30 10:31</t>
         </is>
       </c>
       <c r="C27" s="51" t="inlineStr">
         <is>
-          <t>Sensex, Nifty trade flat as IT gains counter crude oil concerns</t>
+          <t>Sensex, Nifty extend gains for 2nd day: IT stocks lead rally, broader market underperforms</t>
         </is>
       </c>
       <c r="D27" s="51" t="inlineStr">
         <is>
-          <t>India Today</t>
+          <t>IndiaIPO</t>
         </is>
       </c>
       <c r="E27" s="81" t="n">
-        <v>0.153</v>
+        <v>0.84</v>
       </c>
       <c r="F27" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G27" s="82" t="inlineStr">
@@ -11320,21 +11320,21 @@
       </c>
       <c r="B28" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 05:04</t>
+          <t>2026-10-30 10:31</t>
         </is>
       </c>
       <c r="C28" s="51" t="inlineStr">
         <is>
-          <t>Sensex, Nifty Rally in Early Trade on IT Buying, Trent Gains</t>
+          <t>Sensex, Nifty extend recovery; what's driving this upmove? -</t>
         </is>
       </c>
       <c r="D28" s="51" t="inlineStr">
         <is>
-          <t>Deccan Chronicle</t>
+          <t>IndiaIPO</t>
         </is>
       </c>
       <c r="E28" s="81" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.527</v>
       </c>
       <c r="F28" s="51" t="inlineStr">
         <is>
@@ -11355,21 +11355,21 @@
       </c>
       <c r="B29" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 05:01</t>
+          <t>2026-10-30 10:30</t>
         </is>
       </c>
       <c r="C29" s="51" t="inlineStr">
         <is>
-          <t>Sensex Today Trades Flat | Nifty Below 22,950 | BSE Telecommunication Down 1.7%</t>
+          <t>Markets reverse last week's losses; Nifty crosses 23,000, pharma jumps 7% weekly</t>
         </is>
       </c>
       <c r="D29" s="51" t="inlineStr">
         <is>
-          <t>Equitymaster</t>
+          <t>NewsDrum</t>
         </is>
       </c>
       <c r="E29" s="81" t="n">
-        <v>0.402</v>
+        <v>0.44</v>
       </c>
       <c r="F29" s="51" t="inlineStr">
         <is>
@@ -11390,21 +11390,21 @@
       </c>
       <c r="B30" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 04:57</t>
+          <t>2026-10-30 10:28</t>
         </is>
       </c>
       <c r="C30" s="51" t="inlineStr">
         <is>
-          <t>Stock Markets Today: Sensex, Nifty Up on Gains in IT Stocks</t>
+          <t>Sensex Today Ends 308 Points Higher | Nifty Above 22,300 | Vedanta Oil and Gas Up 8%</t>
         </is>
       </c>
       <c r="D30" s="51" t="inlineStr">
         <is>
-          <t>Rediff</t>
+          <t>Equitymaster</t>
         </is>
       </c>
       <c r="E30" s="81" t="n">
-        <v>0.649</v>
+        <v>0.402</v>
       </c>
       <c r="F30" s="51" t="inlineStr">
         <is>
@@ -11425,25 +11425,25 @@
       </c>
       <c r="B31" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 04:25</t>
+          <t>2026-10-30 10:26</t>
         </is>
       </c>
       <c r="C31" s="51" t="inlineStr">
         <is>
-          <t>Sensex, Nifty open marginally higher amid rising crude prices, weak global cues</t>
+          <t>Sensex, Nifty close with gain of 0.5% as IT, pharma stocks rally; weak broader market limits gains</t>
         </is>
       </c>
       <c r="D31" s="51" t="inlineStr">
         <is>
-          <t>bfsi.economictimes.indiatimes.com</t>
+          <t>ChiniMandi</t>
         </is>
       </c>
       <c r="E31" s="81" t="n">
-        <v>-0.5570000000000001</v>
+        <v>0.796</v>
       </c>
       <c r="F31" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G31" s="82" t="inlineStr">
@@ -11460,25 +11460,25 @@
       </c>
       <c r="B32" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 03:59</t>
+          <t>2026-10-30 10:21</t>
         </is>
       </c>
       <c r="C32" s="51" t="inlineStr">
         <is>
-          <t>Coal India falls 3% post Q2 results but brokerages upbeat on PSU stock</t>
+          <t>Taking Stock: Nifty reclaims 23,000, Sensex gains 308 points led by IT, pharma stocks</t>
         </is>
       </c>
       <c r="D32" s="51" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>Moneycontrol.com</t>
         </is>
       </c>
       <c r="E32" s="81" t="n">
-        <v>-0.202</v>
+        <v>0.649</v>
       </c>
       <c r="F32" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G32" s="82" t="inlineStr">
@@ -11495,21 +11495,21 @@
       </c>
       <c r="B33" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 03:34</t>
+          <t>2026-10-30 10:05</t>
         </is>
       </c>
       <c r="C33" s="51" t="inlineStr">
         <is>
-          <t>Sensex, Nifty may gain 5-8% if external headwinds recede: Baldev Prakash</t>
+          <t>Closing Bell: Sensex rises 308 points, Nifty tops 23,000; IT, pharma stocks lead recovery</t>
         </is>
       </c>
       <c r="D33" s="51" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>Zee Business</t>
         </is>
       </c>
       <c r="E33" s="81" t="n">
-        <v>0.625</v>
+        <v>0.718</v>
       </c>
       <c r="F33" s="51" t="inlineStr">
         <is>
@@ -11530,25 +11530,25 @@
       </c>
       <c r="B34" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 03:00</t>
+          <t>2026-10-30 10:03</t>
         </is>
       </c>
       <c r="C34" s="51" t="inlineStr">
         <is>
-          <t>Stock market outlook: Crude oil prices to FPI inflows - 8 triggers that could reverse trend in Sensex, Nifty 50</t>
+          <t>Sensex ends 308 points higher, Nifty above 23,000; Trent up 5%</t>
         </is>
       </c>
       <c r="D34" s="51" t="inlineStr">
         <is>
-          <t>Livemint</t>
+          <t>India Today</t>
         </is>
       </c>
       <c r="E34" s="81" t="n">
-        <v>-0.25</v>
+        <v>0.402</v>
       </c>
       <c r="F34" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G34" s="82" t="inlineStr">
@@ -11565,21 +11565,21 @@
       </c>
       <c r="B35" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 02:31</t>
+          <t>2026-10-30 09:52</t>
         </is>
       </c>
       <c r="C35" s="51" t="inlineStr">
         <is>
-          <t>Stock Market Today LIVE: GIFT Nifty signals quiet start; Brent crude at $111</t>
+          <t>Market Wrap: Sensex Gains 308 Points, Nifty 50 Ends Above 23,000; Trent, IndiGo, Infosys Lead</t>
         </is>
       </c>
       <c r="D35" s="51" t="inlineStr">
         <is>
-          <t>IndiaIPO</t>
+          <t>NDTV Profit</t>
         </is>
       </c>
       <c r="E35" s="81" t="n">
-        <v>0.389</v>
+        <v>0.649</v>
       </c>
       <c r="F35" s="51" t="inlineStr">
         <is>
@@ -11600,21 +11600,21 @@
       </c>
       <c r="B36" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 02:26</t>
+          <t>2026-10-30 08:59</t>
         </is>
       </c>
       <c r="C36" s="51" t="inlineStr">
         <is>
-          <t>Can Sensex, Nifty extend rally on Friday? Here's what market analysts say</t>
+          <t>Sensex Rises 298 Points, Nifty 50 Crosses 23,000 as IT Stocks Lead Gains</t>
         </is>
       </c>
       <c r="D36" s="51" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>Dalal Street Investment Journal</t>
         </is>
       </c>
       <c r="E36" s="81" t="n">
-        <v>0.751</v>
+        <v>0.649</v>
       </c>
       <c r="F36" s="51" t="inlineStr">
         <is>
@@ -11630,30 +11630,30 @@
     <row r="37">
       <c r="A37" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>CPPLUS</t>
         </is>
       </c>
       <c r="B37" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 01:44</t>
+          <t>2026-10-30 08:44</t>
         </is>
       </c>
       <c r="C37" s="51" t="inlineStr">
         <is>
-          <t>Stock Market Today: Gift Nifty, Tech Stocks Selloff To Binance Hack; Five Key Factors For Sensex, Nifty 50 On Oct 30</t>
+          <t>Aditya Infotech CPPLUS ESOP Allotment 48,100 Shares Oct 2026</t>
         </is>
       </c>
       <c r="D37" s="51" t="inlineStr">
         <is>
-          <t>NDTV Profit</t>
+          <t>Kalkine India</t>
         </is>
       </c>
       <c r="E37" s="81" t="n">
-        <v>0.8070000000000001</v>
+        <v>0</v>
       </c>
       <c r="F37" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G37" s="82" t="inlineStr">
@@ -11665,26 +11665,26 @@
     <row r="38">
       <c r="A38" s="51" t="inlineStr">
         <is>
-          <t>THANGAMAYL</t>
+          <t>AETHER</t>
         </is>
       </c>
       <c r="B38" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 01:17</t>
+          <t>2026-10-30 08:35</t>
         </is>
       </c>
       <c r="C38" s="51" t="inlineStr">
         <is>
-          <t>Thangamayil FY26 Net Profit Jumps 196% to ₹35,165 Lakhs</t>
+          <t>Aether Industries reports robust Q2 FY27 financial performance with ₹3,472M in operating revenue</t>
         </is>
       </c>
       <c r="D38" s="51" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>Business Upturn</t>
         </is>
       </c>
       <c r="E38" s="81" t="n">
-        <v>0.66</v>
+        <v>0.421</v>
       </c>
       <c r="F38" s="51" t="inlineStr">
         <is>
@@ -11705,21 +11705,21 @@
       </c>
       <c r="B39" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 01:14</t>
+          <t>2026-10-30 08:02</t>
         </is>
       </c>
       <c r="C39" s="51" t="inlineStr">
         <is>
-          <t>Stock market outlook today, 30 Oct: Sensex, Nifty prediction - DJIA, S&amp;P, NASDAQ, GIFT Nifty, Kospi, Nikkei, Taiwan cues</t>
+          <t>Sensex zooms 1,200 pts in 2 days, Nifty tops 23K: Why are bulls in charge?</t>
         </is>
       </c>
       <c r="D39" s="51" t="inlineStr">
         <is>
-          <t>Livemint</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="E39" s="81" t="n">
-        <v>0.842</v>
+        <v>0.718</v>
       </c>
       <c r="F39" s="51" t="inlineStr">
         <is>
@@ -11735,30 +11735,30 @@
     <row r="40">
       <c r="A40" s="51" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B40" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 00:25</t>
+          <t>2026-10-30 07:52</t>
         </is>
       </c>
       <c r="C40" s="51" t="inlineStr">
         <is>
-          <t>Jai Corp Ltd. Share Price, Stock Price - NSE/BSE Live</t>
+          <t>IndiGo, Trent, Vedanta Power among buzzing stocks as SENSEX gains over 500 pts; NIFTY trades above 23K</t>
         </is>
       </c>
       <c r="D40" s="51" t="inlineStr">
         <is>
-          <t>NDTV Profit</t>
+          <t>Upstox</t>
         </is>
       </c>
       <c r="E40" s="81" t="n">
-        <v>0</v>
+        <v>0.721</v>
       </c>
       <c r="F40" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G40" s="82" t="inlineStr">
@@ -11770,26 +11770,26 @@
     <row r="41">
       <c r="A41" s="51" t="inlineStr">
         <is>
-          <t>AETHER</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B41" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10</t>
+          <t>2026-10-30 07:31</t>
         </is>
       </c>
       <c r="C41" s="51" t="inlineStr">
         <is>
-          <t>Ather Energy Share Price Today, Ather Energy Stock Price Live NSE/BSE Updates | The Economic Times</t>
+          <t>Why Stock Market Is Rallying? Nifty Reclaims 23,100, Sensex Surges 500 Points; Three Reasons Why</t>
         </is>
       </c>
       <c r="D41" s="51" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>NDTV Profit</t>
         </is>
       </c>
       <c r="E41" s="81" t="n">
-        <v>0.494</v>
+        <v>0.71</v>
       </c>
       <c r="F41" s="51" t="inlineStr">
         <is>
@@ -11805,30 +11805,30 @@
     <row r="42">
       <c r="A42" s="51" t="inlineStr">
         <is>
-          <t>AETHER</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B42" s="51" t="inlineStr">
         <is>
-          <t>2026-10-29 18:01</t>
+          <t>2026-10-30 06:40</t>
         </is>
       </c>
       <c r="C42" s="51" t="inlineStr">
         <is>
-          <t>NAVINFLUOR Share Price Today - Navin Fluorine International on NSE/BSE</t>
+          <t>Passive funds could buy up to Rs 36,500 crore upon Jio Platforms' entry into Nifty, Sensex</t>
         </is>
       </c>
       <c r="D42" s="51" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>Moneycontrol.com</t>
         </is>
       </c>
       <c r="E42" s="81" t="n">
-        <v>0</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="F42" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G42" s="82" t="inlineStr">
@@ -11840,22 +11840,22 @@
     <row r="43">
       <c r="A43" s="51" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>AETHER</t>
         </is>
       </c>
       <c r="B43" s="51" t="inlineStr">
         <is>
-          <t>2026-10-29 17:53</t>
+          <t>2026-10-30 06:37</t>
         </is>
       </c>
       <c r="C43" s="51" t="inlineStr">
         <is>
-          <t>ZF Commercial Vehicle Control Systems India Share Price, Stock Price - NSE/BSE Live</t>
+          <t>AETHER Share Price Today - Aether Industries on NSE/BSE</t>
         </is>
       </c>
       <c r="D43" s="51" t="inlineStr">
         <is>
-          <t>NDTV Profit</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="E43" s="81" t="n">
@@ -11875,30 +11875,30 @@
     <row r="44">
       <c r="A44" s="51" t="inlineStr">
         <is>
-          <t>AEROFLEX</t>
+          <t>AETHER</t>
         </is>
       </c>
       <c r="B44" s="51" t="inlineStr">
         <is>
-          <t>2026-10-29 15:28</t>
+          <t>2026-10-30 06:35</t>
         </is>
       </c>
       <c r="C44" s="51" t="inlineStr">
         <is>
-          <t>Aeroflex Industries (NSE:AEROFLEX) Q2 FY27 Results and Hyd-Air Amalgamation</t>
+          <t>Aether Industries Q2 FY27: Net profit rises 26% to ₹68 crore as revenue climbs 24% to ₹347 crore</t>
         </is>
       </c>
       <c r="D44" s="51" t="inlineStr">
         <is>
-          <t>Kalkine India</t>
+          <t>Business Upturn</t>
         </is>
       </c>
       <c r="E44" s="81" t="n">
-        <v>0</v>
+        <v>0.612</v>
       </c>
       <c r="F44" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G44" s="82" t="inlineStr">
@@ -11910,30 +11910,30 @@
     <row r="45">
       <c r="A45" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>AETHER</t>
         </is>
       </c>
       <c r="B45" s="51" t="inlineStr">
         <is>
-          <t>2026-10-29 14:36</t>
+          <t>2026-10-30 06:31</t>
         </is>
       </c>
       <c r="C45" s="51" t="inlineStr">
         <is>
-          <t>Benchmarks rise over 1% on positive Q2 earnings, easing crude prices</t>
+          <t>Aether Industries Q2 FY27 Results: Revenue, EBITDA and PAT</t>
         </is>
       </c>
       <c r="D45" s="51" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>Kalkine India</t>
         </is>
       </c>
       <c r="E45" s="81" t="n">
-        <v>0.226</v>
+        <v>0</v>
       </c>
       <c r="F45" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G45" s="82" t="inlineStr">
@@ -11945,30 +11945,30 @@
     <row r="46">
       <c r="A46" s="51" t="inlineStr">
         <is>
-          <t>AETHER</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B46" s="51" t="inlineStr">
         <is>
-          <t>2026-10-29 14:27</t>
+          <t>2026-10-30 06:14</t>
         </is>
       </c>
       <c r="C46" s="51" t="inlineStr">
         <is>
-          <t>GUJALKALI Share Price Today - Gujarat Alkalies &amp; Chemicals on NSE/BSE</t>
+          <t>Sensex Today Live: Sensex, Nifty Trade Higher; Trent, IndiGo Gain, Coal India Shares Fall</t>
         </is>
       </c>
       <c r="D46" s="51" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>The Sunday Guardian</t>
         </is>
       </c>
       <c r="E46" s="81" t="n">
-        <v>0</v>
+        <v>0.402</v>
       </c>
       <c r="F46" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G46" s="82" t="inlineStr">
@@ -11985,25 +11985,25 @@
       </c>
       <c r="B47" s="51" t="inlineStr">
         <is>
-          <t>2026-10-29 13:03</t>
+          <t>2026-10-30 05:55</t>
         </is>
       </c>
       <c r="C47" s="51" t="inlineStr">
         <is>
-          <t>Why markets rallied: Sensex jumps over 900 points, Nifty gains 1 per cent; 5 key reasons</t>
+          <t>Sensex, Nifty open flat as crude oil prices remain elevated; IT stocks gain</t>
         </is>
       </c>
       <c r="D47" s="51" t="inlineStr">
         <is>
-          <t>The Times of India</t>
+          <t>Telangana Today</t>
         </is>
       </c>
       <c r="E47" s="81" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.103</v>
       </c>
       <c r="F47" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G47" s="82" t="inlineStr">
@@ -12015,26 +12015,26 @@
     <row r="48">
       <c r="A48" s="51" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B48" s="51" t="inlineStr">
         <is>
-          <t>2026-10-29 11:52</t>
+          <t>2026-10-30 05:50</t>
         </is>
       </c>
       <c r="C48" s="51" t="inlineStr">
         <is>
-          <t>Syrma SGS Tech - Technical picks for Diwali! 10 stocks PL Capital is bullish on this festive season. See full list</t>
+          <t>BSE IT index set to report 2nd sharpest monthly rally in over two decades</t>
         </is>
       </c>
       <c r="D48" s="51" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="E48" s="81" t="n">
-        <v>0.771</v>
+        <v>0.459</v>
       </c>
       <c r="F48" s="51" t="inlineStr">
         <is>
@@ -12055,21 +12055,21 @@
       </c>
       <c r="B49" s="51" t="inlineStr">
         <is>
-          <t>2026-10-29 11:25</t>
+          <t>2026-10-30 05:36</t>
         </is>
       </c>
       <c r="C49" s="51" t="inlineStr">
         <is>
-          <t>Stock markets rebound over 1% on Fed pause, but rupee and crude keep investors on edge</t>
+          <t>Sensex, Nifty turn lower; broader markets crash as oil tops $116/barrel. What lies ahead?</t>
         </is>
       </c>
       <c r="D49" s="51" t="inlineStr">
         <is>
-          <t>The Hindu</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="E49" s="81" t="n">
-        <v>-0.723</v>
+        <v>-0.34</v>
       </c>
       <c r="F49" s="51" t="inlineStr">
         <is>
@@ -12090,21 +12090,21 @@
       </c>
       <c r="B50" s="51" t="inlineStr">
         <is>
-          <t>2026-10-29 10:59</t>
+          <t>2026-10-30 05:14</t>
         </is>
       </c>
       <c r="C50" s="51" t="inlineStr">
         <is>
-          <t>Sensex Surges 905 Pts, Nifty Tops 22,900 on Banking, FMCG Boost</t>
+          <t>Breakout stocks: Adani Ports, Nykaa, Saregama on radar; analyst tells why</t>
         </is>
       </c>
       <c r="D50" s="51" t="inlineStr">
         <is>
-          <t>Rediff MoneyWiz</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="E50" s="81" t="n">
-        <v>0.898</v>
+        <v>0.421</v>
       </c>
       <c r="F50" s="51" t="inlineStr">
         <is>
@@ -12125,25 +12125,25 @@
       </c>
       <c r="B51" s="51" t="inlineStr">
         <is>
-          <t>2026-10-29 10:56</t>
+          <t>2026-10-30 05:13</t>
         </is>
       </c>
       <c r="C51" s="51" t="inlineStr">
         <is>
-          <t>Sensex jumps 905 points, Nifty gains 238 points as markets stage strong rebound</t>
+          <t>Sensex, Nifty Open Volatile; India VIX Rises, Crude Above $116</t>
         </is>
       </c>
       <c r="D51" s="51" t="inlineStr">
         <is>
-          <t>Telegraph India</t>
+          <t>HDFC Sky</t>
         </is>
       </c>
       <c r="E51" s="81" t="n">
-        <v>0.872</v>
+        <v>-0.25</v>
       </c>
       <c r="F51" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G51" s="82" t="inlineStr">
@@ -12160,25 +12160,25 @@
       </c>
       <c r="B52" s="51" t="inlineStr">
         <is>
-          <t>2026-10-29 10:42</t>
+          <t>2026-10-30 05:07</t>
         </is>
       </c>
       <c r="C52" s="51" t="inlineStr">
         <is>
-          <t>Indian markets stage a strong rebound, recouping yesterday’s losses as Sensex surges over 1%</t>
+          <t>Sensex, Nifty trade flat as IT gains counter crude oil concerns</t>
         </is>
       </c>
       <c r="D52" s="51" t="inlineStr">
         <is>
-          <t>The New Indian Express</t>
+          <t>India Today</t>
         </is>
       </c>
       <c r="E52" s="81" t="n">
-        <v>0.459</v>
+        <v>0.153</v>
       </c>
       <c r="F52" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G52" s="82" t="inlineStr">
@@ -12195,12 +12195,12 @@
       </c>
       <c r="B53" s="51" t="inlineStr">
         <is>
-          <t>2026-10-29 10:39</t>
+          <t>2026-10-30 05:01</t>
         </is>
       </c>
       <c r="C53" s="51" t="inlineStr">
         <is>
-          <t>Sensex Today Rallies 905 Points | Nifty Above 22,900 | 5 Reasons Why Indian Stock Markets Are Rising</t>
+          <t>Sensex Today Trades Flat | Nifty Below 22,950 | BSE Telecommunication Down 1.7%</t>
         </is>
       </c>
       <c r="D53" s="51" t="inlineStr">
@@ -12209,7 +12209,7 @@
         </is>
       </c>
       <c r="E53" s="81" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.402</v>
       </c>
       <c r="F53" s="51" t="inlineStr">
         <is>
@@ -12230,21 +12230,21 @@
       </c>
       <c r="B54" s="51" t="inlineStr">
         <is>
-          <t>2026-10-29 10:28</t>
+          <t>2026-10-30 04:58</t>
         </is>
       </c>
       <c r="C54" s="51" t="inlineStr">
         <is>
-          <t>Sensex surges 905 points, Nifty closes 1.05% higher as Fed rate pause boosts market sentiment</t>
+          <t>Sensex, Nifty Rally 2nd Day on IT Buying, Trent Earnings</t>
         </is>
       </c>
       <c r="D54" s="51" t="inlineStr">
         <is>
-          <t>ANI News</t>
+          <t>Rediff MoneyWiz</t>
         </is>
       </c>
       <c r="E54" s="81" t="n">
-        <v>0.802</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="F54" s="51" t="inlineStr">
         <is>
@@ -12265,21 +12265,21 @@
       </c>
       <c r="B55" s="51" t="inlineStr">
         <is>
-          <t>2026-10-29 08:03</t>
+          <t>2026-10-30 04:57</t>
         </is>
       </c>
       <c r="C55" s="51" t="inlineStr">
         <is>
-          <t>Stock Market Today: Why are Sensex, Nifty rising? 3 key factors</t>
+          <t>Stock Markets Today: Sensex, Nifty Up on Gains in IT Stocks</t>
         </is>
       </c>
       <c r="D55" s="51" t="inlineStr">
         <is>
-          <t>Zee Business</t>
+          <t>Rediff</t>
         </is>
       </c>
       <c r="E55" s="81" t="n">
-        <v>0.402</v>
+        <v>0.649</v>
       </c>
       <c r="F55" s="51" t="inlineStr">
         <is>
@@ -12295,30 +12295,30 @@
     <row r="56">
       <c r="A56" s="51" t="inlineStr">
         <is>
-          <t>AEROFLEX</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B56" s="51" t="inlineStr">
         <is>
-          <t>2026-10-29 07:48</t>
+          <t>2026-10-30 04:50</t>
         </is>
       </c>
       <c r="C56" s="51" t="inlineStr">
         <is>
-          <t>Aeroflex Industries shares rally over 17% on strong Q2 earnings show; material costs jump 120% YoY</t>
+          <t>Stock market today: Sensex opens higher, Trent rallies; Suzlon tumbles 8%</t>
         </is>
       </c>
       <c r="D56" s="51" t="inlineStr">
         <is>
-          <t>Upstox</t>
+          <t>NewsDrum</t>
         </is>
       </c>
       <c r="E56" s="81" t="n">
-        <v>0.8129999999999999</v>
+        <v>-0.052</v>
       </c>
       <c r="F56" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G56" s="82" t="inlineStr">
@@ -12335,21 +12335,21 @@
       </c>
       <c r="B57" s="51" t="inlineStr">
         <is>
-          <t>2026-10-29 07:15</t>
+          <t>2026-10-30 04:47</t>
         </is>
       </c>
       <c r="C57" s="51" t="inlineStr">
         <is>
-          <t>Why is market rising today? Sensex jumps 600 points, Nifty nears 22,900. 6 key factors behind Rs 3 lakh cror..</t>
+          <t>Stock Market Today: Sensex Gains in Early Trade as Investors Focus on Earnings and Global Cues</t>
         </is>
       </c>
       <c r="D57" s="51" t="inlineStr">
         <is>
-          <t>bfsi.economictimes.indiatimes.com</t>
+          <t>Business News This Week</t>
         </is>
       </c>
       <c r="E57" s="81" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.382</v>
       </c>
       <c r="F57" s="51" t="inlineStr">
         <is>
@@ -12370,25 +12370,25 @@
       </c>
       <c r="B58" s="51" t="inlineStr">
         <is>
-          <t>2026-10-29 07:09</t>
+          <t>2026-10-30 04:26</t>
         </is>
       </c>
       <c r="C58" s="51" t="inlineStr">
         <is>
-          <t>Three Reasons Why Markets Are Rising: Sensex Jumps Over 800 Points, Nifty Crosses 22,900</t>
+          <t>BLS Polymers IPO allotment today; GMP at 45% — check status on BSE, NSE and registrar</t>
         </is>
       </c>
       <c r="D58" s="51" t="inlineStr">
         <is>
-          <t>NDTV Profit</t>
+          <t>Moneycontrol.com</t>
         </is>
       </c>
       <c r="E58" s="81" t="n">
-        <v>0.6909999999999999</v>
+        <v>0</v>
       </c>
       <c r="F58" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G58" s="82" t="inlineStr">
@@ -12405,25 +12405,25 @@
       </c>
       <c r="B59" s="51" t="inlineStr">
         <is>
-          <t>2026-10-29 07:05</t>
+          <t>2026-10-30 04:19</t>
         </is>
       </c>
       <c r="C59" s="51" t="inlineStr">
         <is>
-          <t>Sensex, Nifty Rise as Reliance Industries and IT Stocks Gain; Crude Oil Limits Upside</t>
+          <t>Sensex, Nifty open marginally higher amid rising crude prices, weak global cues</t>
         </is>
       </c>
       <c r="D59" s="51" t="inlineStr">
         <is>
-          <t>India Infoline</t>
+          <t>TradingView</t>
         </is>
       </c>
       <c r="E59" s="81" t="n">
-        <v>0.494</v>
+        <v>-0.5570000000000001</v>
       </c>
       <c r="F59" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G59" s="82" t="inlineStr">
@@ -12435,30 +12435,30 @@
     <row r="60">
       <c r="A60" s="51" t="inlineStr">
         <is>
-          <t>SBC</t>
+          <t>SYRMA</t>
         </is>
       </c>
       <c r="B60" s="51" t="inlineStr">
         <is>
-          <t>2026-10-29 06:51</t>
+          <t>2026-10-30 04:16</t>
         </is>
       </c>
       <c r="C60" s="51" t="inlineStr">
         <is>
-          <t>20 Best Stocks Under 50 Rs In India October 2026 For High Returns</t>
+          <t>SYRMA Stock Price and Chart — NSE:SYRMA</t>
         </is>
       </c>
       <c r="D60" s="51" t="inlineStr">
         <is>
-          <t>Samco</t>
+          <t>TradingView</t>
         </is>
       </c>
       <c r="E60" s="81" t="n">
-        <v>0.718</v>
+        <v>0</v>
       </c>
       <c r="F60" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G60" s="82" t="inlineStr">
@@ -12470,30 +12470,30 @@
     <row r="61">
       <c r="A61" s="51" t="inlineStr">
         <is>
-          <t>AEROFLEX</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B61" s="51" t="inlineStr">
         <is>
-          <t>2026-10-29 06:44</t>
+          <t>2026-10-30 04:14</t>
         </is>
       </c>
       <c r="C61" s="51" t="inlineStr">
         <is>
-          <t>NSE: Growth levers, easing regulatory pressure underpin Jefferies' buy call</t>
+          <t>SFC Environmental Technologies IPO allotment: How to check status online on NSE, BSE, MUFG Intime India; listing date, time here</t>
         </is>
       </c>
       <c r="D61" s="51" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>Upstox</t>
         </is>
       </c>
       <c r="E61" s="81" t="n">
-        <v>0.542</v>
+        <v>0</v>
       </c>
       <c r="F61" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G61" s="82" t="inlineStr">
@@ -12505,30 +12505,30 @@
     <row r="62">
       <c r="A62" s="51" t="inlineStr">
         <is>
-          <t>AEROFLEX</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B62" s="51" t="inlineStr">
         <is>
-          <t>2026-10-29 06:42</t>
+          <t>2026-10-30 04:11</t>
         </is>
       </c>
       <c r="C62" s="51" t="inlineStr">
         <is>
-          <t>Aeroflex Industries (NSE:AEROFLEX): Did It Publish Q2 FY27 Financial Results?</t>
+          <t>Sensex, Nifty open flat amid high crude oil prices, jump in IT stocks | Business News</t>
         </is>
       </c>
       <c r="D62" s="51" t="inlineStr">
         <is>
-          <t>Kalkine India</t>
+          <t>Hindustan Times</t>
         </is>
       </c>
       <c r="E62" s="81" t="n">
-        <v>0</v>
+        <v>0.382</v>
       </c>
       <c r="F62" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G62" s="82" t="inlineStr">
@@ -12540,17 +12540,17 @@
     <row r="63">
       <c r="A63" s="51" t="inlineStr">
         <is>
-          <t>AEROFLEX</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B63" s="51" t="inlineStr">
         <is>
-          <t>2026-10-29 06:38</t>
+          <t>2026-10-30 03:59</t>
         </is>
       </c>
       <c r="C63" s="51" t="inlineStr">
         <is>
-          <t>Aeroflex zooms 18% on huge volume, over 31 mn shares change hands</t>
+          <t>Coal India falls 3% post Q2 results but brokerages upbeat on PSU stock</t>
         </is>
       </c>
       <c r="D63" s="51" t="inlineStr">
@@ -12559,11 +12559,11 @@
         </is>
       </c>
       <c r="E63" s="81" t="n">
-        <v>0.318</v>
+        <v>-0.202</v>
       </c>
       <c r="F63" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G63" s="82" t="inlineStr">
@@ -12580,25 +12580,25 @@
       </c>
       <c r="B64" s="51" t="inlineStr">
         <is>
-          <t>2026-10-29 05:31</t>
+          <t>2026-10-30 03:51</t>
         </is>
       </c>
       <c r="C64" s="51" t="inlineStr">
         <is>
-          <t>Why is market rallying today? Sensex jumps 900 points, Nifty above 22,900. 6 key factors behind Rs 5 lakh</t>
+          <t>Stock Market Today (October 30): Sensex, Nifty Open Flat; Rising Oil Prices, Geopolitical Tensions In Focus</t>
         </is>
       </c>
       <c r="D64" s="51" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>Times Now</t>
         </is>
       </c>
       <c r="E64" s="81" t="n">
-        <v>0.6909999999999999</v>
+        <v>0</v>
       </c>
       <c r="F64" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G64" s="82" t="inlineStr">
@@ -12610,26 +12610,26 @@
     <row r="65">
       <c r="A65" s="51" t="inlineStr">
         <is>
-          <t>AEROFLEX</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B65" s="51" t="inlineStr">
         <is>
-          <t>2026-10-29 05:29</t>
+          <t>2026-10-30 03:50</t>
         </is>
       </c>
       <c r="C65" s="51" t="inlineStr">
         <is>
-          <t>Aeroflex Industries Share Price Surges 14% After Q2: Profit Jumps 157%, Why the Depreciation Change Matters</t>
+          <t>Stock Market Today: Sensex edges higher, Nifty opens above 22,950</t>
         </is>
       </c>
       <c r="D65" s="51" t="inlineStr">
         <is>
-          <t>Univest</t>
+          <t>Zee Business</t>
         </is>
       </c>
       <c r="E65" s="81" t="n">
-        <v>0.827</v>
+        <v>0.402</v>
       </c>
       <c r="F65" s="51" t="inlineStr">
         <is>
@@ -12650,21 +12650,21 @@
       </c>
       <c r="B66" s="51" t="inlineStr">
         <is>
-          <t>2026-10-29 05:18</t>
+          <t>2026-10-30 03:34</t>
         </is>
       </c>
       <c r="C66" s="51" t="inlineStr">
         <is>
-          <t>Stock Markets Today: Sensex, Nifty rise in early trade on buying in RIL FII inflows</t>
+          <t>Sensex, Nifty may gain 5-8% if external headwinds recede: Baldev Prakash</t>
         </is>
       </c>
       <c r="D66" s="51" t="inlineStr">
         <is>
-          <t>Rediff</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="E66" s="81" t="n">
-        <v>0.402</v>
+        <v>0.625</v>
       </c>
       <c r="F66" s="51" t="inlineStr">
         <is>
@@ -12685,25 +12685,25 @@
       </c>
       <c r="B67" s="51" t="inlineStr">
         <is>
-          <t>2026-10-29 05:17</t>
+          <t>2026-10-30 03:00</t>
         </is>
       </c>
       <c r="C67" s="51" t="inlineStr">
         <is>
-          <t>Sensex, Nifty rise in early trade on Reliance buying, foreign inflows</t>
+          <t>Stock market outlook: Crude oil prices to FPI inflows - 8 triggers that could reverse trend in Sensex, Nifty 50</t>
         </is>
       </c>
       <c r="D67" s="51" t="inlineStr">
         <is>
-          <t>The Hindu</t>
+          <t>Livemint</t>
         </is>
       </c>
       <c r="E67" s="81" t="n">
-        <v>0.402</v>
+        <v>-0.25</v>
       </c>
       <c r="F67" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G67" s="82" t="inlineStr">
@@ -12720,21 +12720,21 @@
       </c>
       <c r="B68" s="51" t="inlineStr">
         <is>
-          <t>2026-10-29 04:44</t>
+          <t>2026-10-30 02:41</t>
         </is>
       </c>
       <c r="C68" s="51" t="inlineStr">
         <is>
-          <t>Sensex, Nifty Open Higher as Fed Holds Rates; Oil Dips Slightly</t>
+          <t>GIFT Nifty down, signals muted start for Sensex, Nifty; Asian markets plunge on AI spending worries, oil...</t>
         </is>
       </c>
       <c r="D68" s="51" t="inlineStr">
         <is>
-          <t>HDFC Sky</t>
+          <t>Moneycontrol.com</t>
         </is>
       </c>
       <c r="E68" s="81" t="n">
-        <v>0.402</v>
+        <v>0.408</v>
       </c>
       <c r="F68" s="51" t="inlineStr">
         <is>
@@ -12755,21 +12755,21 @@
       </c>
       <c r="B69" s="51" t="inlineStr">
         <is>
-          <t>2026-10-29 04:35</t>
+          <t>2026-10-30 02:35</t>
         </is>
       </c>
       <c r="C69" s="51" t="inlineStr">
         <is>
-          <t>Sensex Today Trades Higher | Nifty Above 22,700 | Jio Platforms Up 4%</t>
+          <t>Indian shares seen opening higher after earnings-led rebound; higher oil to cap gains</t>
         </is>
       </c>
       <c r="D69" s="51" t="inlineStr">
         <is>
-          <t>Equitymaster</t>
+          <t>Livemint</t>
         </is>
       </c>
       <c r="E69" s="81" t="n">
-        <v>0.402</v>
+        <v>0.382</v>
       </c>
       <c r="F69" s="51" t="inlineStr">
         <is>
@@ -12785,30 +12785,30 @@
     <row r="70">
       <c r="A70" s="51" t="inlineStr">
         <is>
-          <t>AEROFLEX</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B70" s="51" t="inlineStr">
         <is>
-          <t>2026-10-29 04:11</t>
+          <t>2026-10-30 02:21</t>
         </is>
       </c>
       <c r="C70" s="51" t="inlineStr">
         <is>
-          <t>Why are Aeroflex Industries shares rallying over 12% today? Here's what's driving the stock</t>
+          <t>Stock Market Today, October 30: RIL, Jio Q2 results, Japan rate decision, forex reserves - 10 key triggers for Sensex, Nifty</t>
         </is>
       </c>
       <c r="D70" s="51" t="inlineStr">
         <is>
-          <t>Business Upturn</t>
+          <t>ET Now</t>
         </is>
       </c>
       <c r="E70" s="81" t="n">
-        <v>0</v>
+        <v>0.402</v>
       </c>
       <c r="F70" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G70" s="82" t="inlineStr">
@@ -12825,12 +12825,12 @@
       </c>
       <c r="B71" s="51" t="inlineStr">
         <is>
-          <t>2026-10-29 03:51</t>
+          <t>2026-10-30 01:44</t>
         </is>
       </c>
       <c r="C71" s="51" t="inlineStr">
         <is>
-          <t>Stock Market Highlights: Sensex Jumps 905 Points, Nifty 50 Ends Above 22,900; Adani Stocks, Kotak Bank Lead Rally</t>
+          <t>Stock Market Today: Gift Nifty, Tech Stocks Selloff To Binance Hack; Five Key Factors For Sensex, Nifty 50 On Oct 30</t>
         </is>
       </c>
       <c r="D71" s="51" t="inlineStr">
@@ -12839,7 +12839,7 @@
         </is>
       </c>
       <c r="E71" s="81" t="n">
-        <v>0.827</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="F71" s="51" t="inlineStr">
         <is>
@@ -12855,30 +12855,30 @@
     <row r="72">
       <c r="A72" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>THANGAMAYL</t>
         </is>
       </c>
       <c r="B72" s="51" t="inlineStr">
         <is>
-          <t>2026-10-29 03:50</t>
+          <t>2026-10-30 01:17</t>
         </is>
       </c>
       <c r="C72" s="51" t="inlineStr">
         <is>
-          <t>Sensex, Nifty trade higher after US Fed holds rates; crude oil remains a concern</t>
+          <t>Thangamayil FY26 Net Profit Jumps 196% to ₹35,165 Lakhs</t>
         </is>
       </c>
       <c r="D72" s="51" t="inlineStr">
         <is>
-          <t>India Today</t>
+          <t>scanx.trade</t>
         </is>
       </c>
       <c r="E72" s="81" t="n">
-        <v>-0.25</v>
+        <v>0.66</v>
       </c>
       <c r="F72" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G72" s="82" t="inlineStr">
@@ -12895,21 +12895,21 @@
       </c>
       <c r="B73" s="51" t="inlineStr">
         <is>
-          <t>2026-10-29 01:39</t>
+          <t>2026-10-30 01:14</t>
         </is>
       </c>
       <c r="C73" s="51" t="inlineStr">
         <is>
-          <t>Stock Market Today: Gift Nifty, US Fed Policy To Oil Prices; Five Key Factors For Sensex, Nifty 50 On October 29</t>
+          <t>Stock market outlook today, 30 Oct: Sensex, Nifty prediction - DJIA, S&amp;P, NASDAQ, GIFT Nifty, Kospi, Nikkei, Taiwan cues</t>
         </is>
       </c>
       <c r="D73" s="51" t="inlineStr">
         <is>
-          <t>NDTV Profit</t>
+          <t>Livemint</t>
         </is>
       </c>
       <c r="E73" s="81" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.842</v>
       </c>
       <c r="F73" s="51" t="inlineStr">
         <is>
@@ -12930,21 +12930,21 @@
       </c>
       <c r="B74" s="51" t="inlineStr">
         <is>
-          <t>2026-10-29 01:15</t>
+          <t>2026-10-30 00:30</t>
         </is>
       </c>
       <c r="C74" s="51" t="inlineStr">
         <is>
-          <t>Stock market outlook today, 29 Oct: Sensex, Nifty prediction - DJIA, S&amp;P, NASDAQ, GIFT Nifty, Kospi, Nikkei, Taiwan cues</t>
+          <t>eClerx Services Q2 FY27 Results | Birlasoft Q2 FY27 Results | Top Buzzing Stocks Today</t>
         </is>
       </c>
       <c r="D74" s="51" t="inlineStr">
         <is>
-          <t>Livemint</t>
+          <t>Equitymaster</t>
         </is>
       </c>
       <c r="E74" s="81" t="n">
-        <v>0.842</v>
+        <v>0.202</v>
       </c>
       <c r="F74" s="51" t="inlineStr">
         <is>
@@ -12960,30 +12960,30 @@
     <row r="75">
       <c r="A75" s="51" t="inlineStr">
         <is>
-          <t>AEROFLEX</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B75" s="51" t="inlineStr">
         <is>
-          <t>2026-10-29 01:01</t>
+          <t>2026-10-30 00:23</t>
         </is>
       </c>
       <c r="C75" s="51" t="inlineStr">
         <is>
-          <t>Stocks to Watch Today: Dr Reddys Labs, Fortis Healthcare, Titagarh Rail, Hero MotoCorp, RR Kabel, Meesho,...</t>
+          <t>Advance-decline ratio hits 7-month low as market breadth weakens</t>
         </is>
       </c>
       <c r="D75" s="51" t="inlineStr">
         <is>
-          <t>Moneycontrol.com</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="E75" s="81" t="n">
-        <v>0.5570000000000001</v>
+        <v>-0.612</v>
       </c>
       <c r="F75" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G75" s="82" t="inlineStr">
@@ -12995,26 +12995,26 @@
     <row r="76">
       <c r="A76" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>AETHER</t>
         </is>
       </c>
       <c r="B76" s="51" t="inlineStr">
         <is>
-          <t>2026-10-28 18:46</t>
+          <t>2026-10-30 00:10</t>
         </is>
       </c>
       <c r="C76" s="51" t="inlineStr">
         <is>
-          <t>How can US Fed FOMC meeting outcome impact Indian stock market? Sensex, Nifty to rise? Experts decode</t>
+          <t>Ather Energy Share Price Today, Ather Energy Stock Price Live NSE/BSE Updates | The Economic Times</t>
         </is>
       </c>
       <c r="D76" s="51" t="inlineStr">
         <is>
-          <t>Livemint</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="E76" s="81" t="n">
-        <v>0.47</v>
+        <v>0.494</v>
       </c>
       <c r="F76" s="51" t="inlineStr">
         <is>
@@ -13035,17 +13035,17 @@
       </c>
       <c r="B77" s="51" t="inlineStr">
         <is>
-          <t>2026-10-28 17:25</t>
+          <t>2026-10-29 17:53</t>
         </is>
       </c>
       <c r="C77" s="51" t="inlineStr">
         <is>
-          <t>AB Cotspin India Yearly results, Financial Summary</t>
+          <t>ZF Commercial Vehicle Control Systems India Share Price, Stock Price - NSE/BSE Live</t>
         </is>
       </c>
       <c r="D77" s="51" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>NDTV Profit</t>
         </is>
       </c>
       <c r="E77" s="81" t="n">
@@ -13065,22 +13065,22 @@
     <row r="78">
       <c r="A78" s="51" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>AEROFLEX</t>
         </is>
       </c>
       <c r="B78" s="51" t="inlineStr">
         <is>
-          <t>2026-10-28 16:59</t>
+          <t>2026-10-29 15:28</t>
         </is>
       </c>
       <c r="C78" s="51" t="inlineStr">
         <is>
-          <t>Half Yearly Results, Half yearly Earnings for Shree Marutinandan</t>
+          <t>Aeroflex Industries (NSE:AEROFLEX) Q2 FY27 Results and Hyd-Air Amalgamation</t>
         </is>
       </c>
       <c r="D78" s="51" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>Kalkine India</t>
         </is>
       </c>
       <c r="E78" s="81" t="n">
@@ -13100,30 +13100,30 @@
     <row r="79">
       <c r="A79" s="51" t="inlineStr">
         <is>
-          <t>RATNAVEER</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B79" s="51" t="inlineStr">
         <is>
-          <t>2026-10-28 13:42</t>
+          <t>2026-10-29 14:36</t>
         </is>
       </c>
       <c r="C79" s="51" t="inlineStr">
         <is>
-          <t>Ratnaveer Precision Engineering Q2 FY27 Earnings Call on 3 Nov</t>
+          <t>Benchmarks rise over 1% on positive Q2 earnings, easing crude prices</t>
         </is>
       </c>
       <c r="D79" s="51" t="inlineStr">
         <is>
-          <t>Kalkine India</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="E79" s="81" t="n">
-        <v>0</v>
+        <v>0.226</v>
       </c>
       <c r="F79" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G79" s="82" t="inlineStr">
@@ -13135,30 +13135,30 @@
     <row r="80">
       <c r="A80" s="51" t="inlineStr">
         <is>
-          <t>AETHER</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B80" s="51" t="inlineStr">
         <is>
-          <t>2026-10-28 12:26</t>
+          <t>2026-10-29 12:44</t>
         </is>
       </c>
       <c r="C80" s="51" t="inlineStr">
         <is>
-          <t>SRF Share Price Today - SRF on NSE/BSE</t>
+          <t>Indian Equities Rally: Sensex Jumps 905 Pts, Nifty Tops 22,900</t>
         </is>
       </c>
       <c r="D80" s="51" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
+          <t>Rediff</t>
         </is>
       </c>
       <c r="E80" s="81" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="F80" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G80" s="82" t="inlineStr">
@@ -13170,30 +13170,30 @@
     <row r="81">
       <c r="A81" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>SYRMA</t>
         </is>
       </c>
       <c r="B81" s="51" t="inlineStr">
         <is>
-          <t>2026-10-28 12:18</t>
+          <t>2026-10-29 11:52</t>
         </is>
       </c>
       <c r="C81" s="51" t="inlineStr">
         <is>
-          <t>Indian markets end lower as IT weakness and crude oil concerns weigh on sentiment</t>
+          <t>Syrma SGS Tech - Technical picks for Diwali! 10 stocks PL Capital is bullish on this festive season. See full list</t>
         </is>
       </c>
       <c r="D81" s="51" t="inlineStr">
         <is>
-          <t>The New Indian Express</t>
+          <t>The Economic Times</t>
         </is>
       </c>
       <c r="E81" s="81" t="n">
-        <v>-0.8070000000000001</v>
+        <v>0.771</v>
       </c>
       <c r="F81" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G81" s="82" t="inlineStr">
@@ -13210,25 +13210,25 @@
       </c>
       <c r="B82" s="51" t="inlineStr">
         <is>
-          <t>2026-10-28 12:04</t>
+          <t>2026-10-29 11:41</t>
         </is>
       </c>
       <c r="C82" s="51" t="inlineStr">
         <is>
-          <t>Sensex, Nifty Slip as Crude Near $115; IT, O&amp;G Drag Markets</t>
+          <t>Share Market Today: Nifty 50, Bank Nifty | Oct 29, 2026</t>
         </is>
       </c>
       <c r="D82" s="51" t="inlineStr">
         <is>
-          <t>HDFC Sky</t>
+          <t>Liquide Blog</t>
         </is>
       </c>
       <c r="E82" s="81" t="n">
-        <v>-0.649</v>
+        <v>0.66</v>
       </c>
       <c r="F82" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G82" s="82" t="inlineStr">
@@ -13245,25 +13245,25 @@
       </c>
       <c r="B83" s="51" t="inlineStr">
         <is>
-          <t>2026-10-28 11:30</t>
+          <t>2026-10-29 10:56</t>
         </is>
       </c>
       <c r="C83" s="51" t="inlineStr">
         <is>
-          <t>Sensex ends in red on selling in IT stocks, rising crude oil prices</t>
+          <t>Sensex jumps 905 points, Nifty gains 238 points as markets stage strong rebound</t>
         </is>
       </c>
       <c r="D83" s="51" t="inlineStr">
         <is>
-          <t>DD India</t>
+          <t>Telegraph India</t>
         </is>
       </c>
       <c r="E83" s="81" t="n">
-        <v>-0.572</v>
+        <v>0.872</v>
       </c>
       <c r="F83" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G83" s="82" t="inlineStr">
@@ -13280,21 +13280,21 @@
       </c>
       <c r="B84" s="51" t="inlineStr">
         <is>
-          <t>2026-10-28 11:06</t>
+          <t>2026-10-29 10:50</t>
         </is>
       </c>
       <c r="C84" s="51" t="inlineStr">
         <is>
-          <t>Sensex, Nifty decline amid rising crude, US Fed caution</t>
+          <t>Sensex, Nifty see sharp recovery; is the worst finally over?</t>
         </is>
       </c>
       <c r="D84" s="51" t="inlineStr">
         <is>
-          <t>Rediff</t>
+          <t>Business Today</t>
         </is>
       </c>
       <c r="E84" s="81" t="n">
-        <v>-0.5570000000000001</v>
+        <v>-0.34</v>
       </c>
       <c r="F84" s="51" t="inlineStr">
         <is>
@@ -13315,21 +13315,21 @@
       </c>
       <c r="B85" s="51" t="inlineStr">
         <is>
-          <t>2026-10-28 10:43</t>
+          <t>2026-10-29 10:46</t>
         </is>
       </c>
       <c r="C85" s="51" t="inlineStr">
         <is>
-          <t>Sensex Today Ends 353 Points Lower | Nifty Below 22,700 | AWL Agri Business Down 6%</t>
+          <t>Sensex Soars 905 Points; Nifty Near 22,940 as Markets Rebound</t>
         </is>
       </c>
       <c r="D85" s="51" t="inlineStr">
         <is>
-          <t>Equitymaster</t>
+          <t>HDFC Sky</t>
         </is>
       </c>
       <c r="E85" s="81" t="n">
-        <v>0.226</v>
+        <v>0.727</v>
       </c>
       <c r="F85" s="51" t="inlineStr">
         <is>
@@ -13350,25 +13350,25 @@
       </c>
       <c r="B86" s="51" t="inlineStr">
         <is>
-          <t>2026-10-28 10:40</t>
+          <t>2026-10-29 10:42</t>
         </is>
       </c>
       <c r="C86" s="51" t="inlineStr">
         <is>
-          <t>Sensex falls 353 points, Nifty below 22,700 as IT and oil stocks drag</t>
+          <t>Indian markets stage a strong rebound, recouping yesterday’s losses as Sensex surges over 1%</t>
         </is>
       </c>
       <c r="D86" s="51" t="inlineStr">
         <is>
-          <t>India Today</t>
+          <t>The New Indian Express</t>
         </is>
       </c>
       <c r="E86" s="81" t="n">
-        <v>-0.202</v>
+        <v>0.459</v>
       </c>
       <c r="F86" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G86" s="82" t="inlineStr">
@@ -13380,30 +13380,30 @@
     <row r="87">
       <c r="A87" s="51" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B87" s="51" t="inlineStr">
         <is>
-          <t>2026-10-28 07:00</t>
+          <t>2026-10-29 10:39</t>
         </is>
       </c>
       <c r="C87" s="51" t="inlineStr">
         <is>
-          <t>Syrma SGS Technology (NSEI:SYRMA) Stock Forecast &amp; Analyst Predictions</t>
+          <t>Sensex Today Rallies 905 Points | Nifty Above 22,900 | 5 Reasons Why Indian Stock Markets Are Rising</t>
         </is>
       </c>
       <c r="D87" s="51" t="inlineStr">
         <is>
-          <t>Simply Wall St</t>
+          <t>Equitymaster</t>
         </is>
       </c>
       <c r="E87" s="81" t="n">
-        <v>0</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="F87" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G87" s="82" t="inlineStr">
@@ -13415,30 +13415,30 @@
     <row r="88">
       <c r="A88" s="51" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B88" s="51" t="inlineStr">
         <is>
-          <t>2026-10-28 06:20</t>
+          <t>2026-10-29 10:11</t>
         </is>
       </c>
       <c r="C88" s="51" t="inlineStr">
         <is>
-          <t>NSE adds six stocks to F&amp;O segment from today, October 28: Check full list</t>
+          <t>Taking Stock: Markets rebound sharply; Nifty above 22,900, Sensex jumps 905 pts as IT, FMCG, banking...</t>
         </is>
       </c>
       <c r="D88" s="51" t="inlineStr">
         <is>
-          <t>Zee Business</t>
+          <t>Moneycontrol.com</t>
         </is>
       </c>
       <c r="E88" s="81" t="n">
-        <v>0</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="F88" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G88" s="82" t="inlineStr">
@@ -13455,25 +13455,25 @@
       </c>
       <c r="B89" s="51" t="inlineStr">
         <is>
-          <t>2026-10-28 05:37</t>
+          <t>2026-10-29 08:33</t>
         </is>
       </c>
       <c r="C89" s="51" t="inlineStr">
         <is>
-          <t>Stock market crash today: Sensex plunges 995 points, Nifty sheds 1% ahead of Fed decision: Here's what spooked D-Street</t>
+          <t>Sensex jumps over 900 points, Nifty inches above 22,950; Reliance, Jio, Adani stocks lead gains</t>
         </is>
       </c>
       <c r="D89" s="51" t="inlineStr">
         <is>
-          <t>Livemint</t>
+          <t>Fortune India</t>
         </is>
       </c>
       <c r="E89" s="81" t="n">
-        <v>-0.802</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="F89" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G89" s="82" t="inlineStr">
@@ -13485,30 +13485,30 @@
     <row r="90">
       <c r="A90" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>AEROFLEX</t>
         </is>
       </c>
       <c r="B90" s="51" t="inlineStr">
         <is>
-          <t>2026-10-28 05:36</t>
+          <t>2026-10-29 08:32</t>
         </is>
       </c>
       <c r="C90" s="51" t="inlineStr">
         <is>
-          <t>Sensex falls 500 points: 3 reasons why the stock market is down today</t>
+          <t>OnEMI Technology rises 5% after Q2FY27 profit doubles to ₹125 crore</t>
         </is>
       </c>
       <c r="D90" s="51" t="inlineStr">
         <is>
-          <t>India Today</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="E90" s="81" t="n">
-        <v>-0.382</v>
+        <v>0.34</v>
       </c>
       <c r="F90" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G90" s="82" t="inlineStr">
@@ -13520,26 +13520,26 @@
     <row r="91">
       <c r="A91" s="51" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B91" s="51" t="inlineStr">
         <is>
-          <t>2026-10-28 05:30</t>
+          <t>2026-10-29 08:03</t>
         </is>
       </c>
       <c r="C91" s="51" t="inlineStr">
         <is>
-          <t>Syrma SGS Technology (SYRMA.NS) Jumps 3.67% to ₹1575.3, Approaches ₹1654.07 Resistance Zone - Time Weighted Price</t>
+          <t>Stock Market Today: Why are Sensex, Nifty rising? 3 key factors</t>
         </is>
       </c>
       <c r="D91" s="51" t="inlineStr">
         <is>
-          <t>https://www.siam.in/</t>
+          <t>Zee Business</t>
         </is>
       </c>
       <c r="E91" s="81" t="n">
-        <v>0.459</v>
+        <v>0.402</v>
       </c>
       <c r="F91" s="51" t="inlineStr">
         <is>
@@ -13560,25 +13560,25 @@
       </c>
       <c r="B92" s="51" t="inlineStr">
         <is>
-          <t>2026-10-28 05:26</t>
+          <t>2026-10-29 07:59</t>
         </is>
       </c>
       <c r="C92" s="51" t="inlineStr">
         <is>
-          <t>Why Is Stock Market Falling Today? 4 Key Reasons Behind Sensex, Nifty Crash</t>
+          <t>SENSEX jumps over 500 pts, NIFTY above 22,800 in noon deals; Power Grid, Hyundai Motor, Jupiter Wagon among buzzing stocks</t>
         </is>
       </c>
       <c r="D92" s="51" t="inlineStr">
         <is>
-          <t>NDTV</t>
+          <t>Upstox</t>
         </is>
       </c>
       <c r="E92" s="81" t="n">
-        <v>-0.402</v>
+        <v>0.753</v>
       </c>
       <c r="F92" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G92" s="82" t="inlineStr">
@@ -13590,30 +13590,30 @@
     <row r="93">
       <c r="A93" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>AEROFLEX</t>
         </is>
       </c>
       <c r="B93" s="51" t="inlineStr">
         <is>
-          <t>2026-10-28 05:26</t>
+          <t>2026-10-29 07:48</t>
         </is>
       </c>
       <c r="C93" s="51" t="inlineStr">
         <is>
-          <t>Market fall explained: Sensex dives 995 points intraday, Nifty at 22,500</t>
+          <t>Aeroflex Industries shares rally over 17% on strong Q2 earnings show; material costs jump 120% YoY</t>
         </is>
       </c>
       <c r="D93" s="51" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>Upstox</t>
         </is>
       </c>
       <c r="E93" s="81" t="n">
-        <v>0.077</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="F93" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G93" s="82" t="inlineStr">
@@ -13630,21 +13630,21 @@
       </c>
       <c r="B94" s="51" t="inlineStr">
         <is>
-          <t>2026-10-28 04:56</t>
+          <t>2026-10-29 07:05</t>
         </is>
       </c>
       <c r="C94" s="51" t="inlineStr">
         <is>
-          <t>Sensex Today Tanks 793 Points | Nifty Below 22,550 | Nifty IT Index Down 3.1%</t>
+          <t>Sensex, Nifty Rise as Reliance Industries and IT Stocks Gain; Crude Oil Limits Upside</t>
         </is>
       </c>
       <c r="D94" s="51" t="inlineStr">
         <is>
-          <t>Equitymaster</t>
+          <t>India Infoline</t>
         </is>
       </c>
       <c r="E94" s="81" t="n">
-        <v>0.296</v>
+        <v>0.494</v>
       </c>
       <c r="F94" s="51" t="inlineStr">
         <is>
@@ -13660,30 +13660,30 @@
     <row r="95">
       <c r="A95" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>SBC</t>
         </is>
       </c>
       <c r="B95" s="51" t="inlineStr">
         <is>
-          <t>2026-10-28 04:46</t>
+          <t>2026-10-29 06:51</t>
         </is>
       </c>
       <c r="C95" s="51" t="inlineStr">
         <is>
-          <t>Sensex falls nearly 700 points as rising crude prices, FPI outflows weigh on markets</t>
+          <t>20 Best Stocks Under 50 Rs In India October 2026 For High Returns</t>
         </is>
       </c>
       <c r="D95" s="51" t="inlineStr">
         <is>
-          <t>DD India</t>
+          <t>Samco</t>
         </is>
       </c>
       <c r="E95" s="81" t="n">
-        <v>-0.743</v>
+        <v>0.718</v>
       </c>
       <c r="F95" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G95" s="82" t="inlineStr">
@@ -13695,30 +13695,30 @@
     <row r="96">
       <c r="A96" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>AEROFLEX</t>
         </is>
       </c>
       <c r="B96" s="51" t="inlineStr">
         <is>
-          <t>2026-10-28 04:35</t>
+          <t>2026-10-29 06:44</t>
         </is>
       </c>
       <c r="C96" s="51" t="inlineStr">
         <is>
-          <t>Sensex sheds 691 points, Nifty falls below 22,600 on rising crude prices, FPI concerns</t>
+          <t>NSE: Growth levers, easing regulatory pressure underpin Jefferies' buy call</t>
         </is>
       </c>
       <c r="D96" s="51" t="inlineStr">
         <is>
-          <t>ChiniMandi</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="E96" s="81" t="n">
-        <v>-0.735</v>
+        <v>0.542</v>
       </c>
       <c r="F96" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G96" s="82" t="inlineStr">
@@ -13730,26 +13730,26 @@
     <row r="97">
       <c r="A97" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>AEROFLEX</t>
         </is>
       </c>
       <c r="B97" s="51" t="inlineStr">
         <is>
-          <t>2026-10-28 04:35</t>
+          <t>2026-10-29 06:42</t>
         </is>
       </c>
       <c r="C97" s="51" t="inlineStr">
         <is>
-          <t>Sensex falls 684 points, Nifty drops below 22,600 in early trade</t>
+          <t>Aeroflex Industries (NSE:AEROFLEX): Did It Publish Q2 FY27 Financial Results?</t>
         </is>
       </c>
       <c r="D97" s="51" t="inlineStr">
         <is>
-          <t>Telangana Today</t>
+          <t>Kalkine India</t>
         </is>
       </c>
       <c r="E97" s="81" t="n">
-        <v>0.026</v>
+        <v>0</v>
       </c>
       <c r="F97" s="51" t="inlineStr">
         <is>
@@ -13765,30 +13765,30 @@
     <row r="98">
       <c r="A98" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>AEROFLEX</t>
         </is>
       </c>
       <c r="B98" s="51" t="inlineStr">
         <is>
-          <t>2026-10-28 04:32</t>
+          <t>2026-10-29 06:38</t>
         </is>
       </c>
       <c r="C98" s="51" t="inlineStr">
         <is>
-          <t>Stock Markets Today: Sensex, Nifty Tumble as IT Stocks, Crude Prices Weigh</t>
+          <t>Aeroflex zooms 18% on huge volume, over 31 mn shares change hands</t>
         </is>
       </c>
       <c r="D98" s="51" t="inlineStr">
         <is>
-          <t>Rediff</t>
+          <t>Business Standard</t>
         </is>
       </c>
       <c r="E98" s="81" t="n">
-        <v>-0.25</v>
+        <v>0.318</v>
       </c>
       <c r="F98" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G98" s="82" t="inlineStr">
@@ -13800,30 +13800,30 @@
     <row r="99">
       <c r="A99" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>AEROFLEX</t>
         </is>
       </c>
       <c r="B99" s="51" t="inlineStr">
         <is>
-          <t>2026-10-28 04:32</t>
+          <t>2026-10-29 05:29</t>
         </is>
       </c>
       <c r="C99" s="51" t="inlineStr">
         <is>
-          <t>Sensex, Nifty Slide as Crude Near $116 and IT Stocks Tumble</t>
+          <t>Aeroflex Industries Share Price Surges 14% After Q2: Profit Jumps 157%, Why the Depreciation Change Matters</t>
         </is>
       </c>
       <c r="D99" s="51" t="inlineStr">
         <is>
-          <t>HDFC Sky</t>
+          <t>Univest</t>
         </is>
       </c>
       <c r="E99" s="81" t="n">
-        <v>-0.25</v>
+        <v>0.827</v>
       </c>
       <c r="F99" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G99" s="82" t="inlineStr">
@@ -13840,25 +13840,25 @@
       </c>
       <c r="B100" s="51" t="inlineStr">
         <is>
-          <t>2026-10-28 04:25</t>
+          <t>2026-10-29 05:25</t>
         </is>
       </c>
       <c r="C100" s="51" t="inlineStr">
         <is>
-          <t>Why Is Stock Market Falling Today? Sensex Drops Over 800 Points, Nifty Slips Below 22,600; Key Reasons Explained</t>
+          <t>Why Is Share Market Rising Today? Know Key Reasons Behind Sensex, Nifty Rally On October 29</t>
         </is>
       </c>
       <c r="D100" s="51" t="inlineStr">
         <is>
-          <t>NDTV Profit</t>
+          <t>News18</t>
         </is>
       </c>
       <c r="E100" s="81" t="n">
-        <v>-0.077</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="F100" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G100" s="82" t="inlineStr">
@@ -13875,25 +13875,25 @@
       </c>
       <c r="B101" s="51" t="inlineStr">
         <is>
-          <t>2026-10-28 04:06</t>
+          <t>2026-10-29 05:17</t>
         </is>
       </c>
       <c r="C101" s="51" t="inlineStr">
         <is>
-          <t>Why did market fall today? Sensex falls 353 points, Nifty closes below 22,700 despite Jio’s solid debut; 4</t>
+          <t>Sensex, Nifty rise in early trade on Reliance buying, foreign inflows</t>
         </is>
       </c>
       <c r="D101" s="51" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>The Hindu</t>
         </is>
       </c>
       <c r="E101" s="81" t="n">
-        <v>-0.411</v>
+        <v>0.402</v>
       </c>
       <c r="F101" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G101" s="82" t="inlineStr">
@@ -13910,25 +13910,25 @@
       </c>
       <c r="B102" s="51" t="inlineStr">
         <is>
-          <t>2026-10-28 03:49</t>
+          <t>2026-10-29 04:58</t>
         </is>
       </c>
       <c r="C102" s="51" t="inlineStr">
         <is>
-          <t>Sensex, Nifty open in red dragged by fall in IT stocks; Infosys down 5%</t>
+          <t>Sensex, Nifty Rise on Reliance Buying, Foreign Inflows</t>
         </is>
       </c>
       <c r="D102" s="51" t="inlineStr">
         <is>
-          <t>India Today</t>
+          <t>Rediff MoneyWiz</t>
         </is>
       </c>
       <c r="E102" s="81" t="n">
-        <v>0.026</v>
+        <v>0.402</v>
       </c>
       <c r="F102" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G102" s="82" t="inlineStr">
@@ -13945,21 +13945,21 @@
       </c>
       <c r="B103" s="51" t="inlineStr">
         <is>
-          <t>2026-10-28 02:47</t>
+          <t>2026-10-29 04:44</t>
         </is>
       </c>
       <c r="C103" s="51" t="inlineStr">
         <is>
-          <t>GIFT Nifty crashes over 220 pts, signals weak start for Sensex and Nifty despite global rally; US Fed in...</t>
+          <t>Sensex, Nifty Open Higher as Fed Holds Rates; Oil Dips Slightly</t>
         </is>
       </c>
       <c r="D103" s="51" t="inlineStr">
         <is>
-          <t>Moneycontrol.com</t>
+          <t>HDFC Sky</t>
         </is>
       </c>
       <c r="E103" s="81" t="n">
-        <v>0.606</v>
+        <v>0.402</v>
       </c>
       <c r="F103" s="51" t="inlineStr">
         <is>
@@ -13980,21 +13980,21 @@
       </c>
       <c r="B104" s="51" t="inlineStr">
         <is>
-          <t>2026-10-28 01:54</t>
+          <t>2026-10-29 04:35</t>
         </is>
       </c>
       <c r="C104" s="51" t="inlineStr">
         <is>
-          <t>Stock Market Today: Gift Nifty, Jio IPO Listing To Nasdaq, Kospi Rally; Five Factors For Sensex, Nifty 50 On Oct 28</t>
+          <t>Sensex Today Trades Higher | Nifty Above 22,700 | Jio Platforms Up 4%</t>
         </is>
       </c>
       <c r="D104" s="51" t="inlineStr">
         <is>
-          <t>NDTV Profit</t>
+          <t>Equitymaster</t>
         </is>
       </c>
       <c r="E104" s="81" t="n">
-        <v>0.883</v>
+        <v>0.402</v>
       </c>
       <c r="F104" s="51" t="inlineStr">
         <is>
@@ -14015,21 +14015,21 @@
       </c>
       <c r="B105" s="51" t="inlineStr">
         <is>
-          <t>2026-10-28 01:45</t>
+          <t>2026-10-29 03:51</t>
         </is>
       </c>
       <c r="C105" s="51" t="inlineStr">
         <is>
-          <t>Stock market outlook for 28 Oct: Sensex, Nifty prediction - Jio Platforms IPO listing, GIFT Nifty, US and Asian markets</t>
+          <t>Stock Market Highlights: Sensex Jumps 905 Points, Nifty 50 Ends Above 22,900; Adani Stocks, Kotak Bank Lead Rally</t>
         </is>
       </c>
       <c r="D105" s="51" t="inlineStr">
         <is>
-          <t>Livemint</t>
+          <t>NDTV Profit</t>
         </is>
       </c>
       <c r="E105" s="81" t="n">
-        <v>0.842</v>
+        <v>0.827</v>
       </c>
       <c r="F105" s="51" t="inlineStr">
         <is>
@@ -14050,25 +14050,25 @@
       </c>
       <c r="B106" s="51" t="inlineStr">
         <is>
-          <t>2026-10-28 00:40</t>
+          <t>2026-10-29 03:50</t>
         </is>
       </c>
       <c r="C106" s="51" t="inlineStr">
         <is>
-          <t>Reading the Nifty 50 and Sensex: What the Two Headline Indices Tell You</t>
+          <t>Sensex, Nifty trade higher after US Fed holds rates; crude oil remains a concern</t>
         </is>
       </c>
       <c r="D106" s="51" t="inlineStr">
         <is>
-          <t>www.tmgm.com</t>
+          <t>India Today</t>
         </is>
       </c>
       <c r="E106" s="81" t="n">
-        <v>0.402</v>
+        <v>-0.25</v>
       </c>
       <c r="F106" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G106" s="82" t="inlineStr">
@@ -14085,21 +14085,21 @@
       </c>
       <c r="B107" s="51" t="inlineStr">
         <is>
-          <t>2026-10-27 18:08</t>
+          <t>2026-10-29 01:15</t>
         </is>
       </c>
       <c r="C107" s="51" t="inlineStr">
         <is>
-          <t>Markets end flat ahead of Fed decision; FPIs buy shares worth ₹4,240 crore</t>
+          <t>Stock market outlook today, 29 Oct: Sensex, Nifty prediction - DJIA, S&amp;P, NASDAQ, GIFT Nifty, Kospi, Nikkei, Taiwan cues</t>
         </is>
       </c>
       <c r="D107" s="51" t="inlineStr">
         <is>
-          <t>Business Standard</t>
+          <t>Livemint</t>
         </is>
       </c>
       <c r="E107" s="81" t="n">
-        <v>0.477</v>
+        <v>0.842</v>
       </c>
       <c r="F107" s="51" t="inlineStr">
         <is>
@@ -14115,26 +14115,26 @@
     <row r="108">
       <c r="A108" s="51" t="inlineStr">
         <is>
-          <t>AETHER</t>
+          <t>AEROFLEX</t>
         </is>
       </c>
       <c r="B108" s="51" t="inlineStr">
         <is>
-          <t>2026-10-27 12:08</t>
+          <t>2026-10-29 01:01</t>
         </is>
       </c>
       <c r="C108" s="51" t="inlineStr">
         <is>
-          <t>Ather Energy shares: 125% YTD returns! Experts give 'portfolio stock' tag after Q2 results 2026 | Target, stop-loss</t>
+          <t>Stocks to Watch Today: Dr Reddys Labs, Fortis Healthcare, Titagarh Rail, Hero MotoCorp, RR Kabel, Meesho,...</t>
         </is>
       </c>
       <c r="D108" s="51" t="inlineStr">
         <is>
-          <t>TradingView</t>
+          <t>Moneycontrol.com</t>
         </is>
       </c>
       <c r="E108" s="81" t="n">
-        <v>0.457</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="F108" s="51" t="inlineStr">
         <is>
@@ -14155,21 +14155,21 @@
       </c>
       <c r="B109" s="51" t="inlineStr">
         <is>
-          <t>2026-10-27 12:05</t>
+          <t>2026-10-28 18:46</t>
         </is>
       </c>
       <c r="C109" s="51" t="inlineStr">
         <is>
-          <t>Stock market today: Sensex, Nifty flat as smallcaps rally and IT stocks fall</t>
+          <t>How can US Fed FOMC meeting outcome impact Indian stock market? Sensex, Nifty to rise? Experts decode</t>
         </is>
       </c>
       <c r="D109" s="51" t="inlineStr">
         <is>
-          <t>BusinessLine</t>
+          <t>Livemint</t>
         </is>
       </c>
       <c r="E109" s="81" t="n">
-        <v>0.511</v>
+        <v>0.47</v>
       </c>
       <c r="F109" s="51" t="inlineStr">
         <is>
@@ -14185,30 +14185,30 @@
     <row r="110">
       <c r="A110" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>RATNAVEER</t>
         </is>
       </c>
       <c r="B110" s="51" t="inlineStr">
         <is>
-          <t>2026-10-27 11:36</t>
+          <t>2026-10-28 13:42</t>
         </is>
       </c>
       <c r="C110" s="51" t="inlineStr">
         <is>
-          <t>Stock Market Highlights: Sensex, Nifty 50 End Flat On F&amp;O Expiry Day; Asian Paints, Coal India, Grasim Top Drags</t>
+          <t>Ratnaveer Precision Engineering Q2 FY27 Earnings Call on 3 Nov</t>
         </is>
       </c>
       <c r="D110" s="51" t="inlineStr">
         <is>
-          <t>NDTV Profit</t>
+          <t>Kalkine India</t>
         </is>
       </c>
       <c r="E110" s="81" t="n">
-        <v>0.273</v>
+        <v>0</v>
       </c>
       <c r="F110" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G110" s="82" t="inlineStr">
@@ -14220,30 +14220,30 @@
     <row r="111">
       <c r="A111" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>AEROFLEX</t>
         </is>
       </c>
       <c r="B111" s="51" t="inlineStr">
         <is>
-          <t>2026-10-27 11:30</t>
+          <t>2026-10-28 12:25</t>
         </is>
       </c>
       <c r="C111" s="51" t="inlineStr">
         <is>
-          <t>Sensex, Nifty End Flat as Oil, Fed Jitters Cap Upside</t>
+          <t>Aeroflex Industries Q2 FY27 Results and CFO Change Announced</t>
         </is>
       </c>
       <c r="D111" s="51" t="inlineStr">
         <is>
-          <t>HDFC Sky</t>
+          <t>Kalkine India</t>
         </is>
       </c>
       <c r="E111" s="81" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="F111" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G111" s="82" t="inlineStr">
@@ -14255,30 +14255,30 @@
     <row r="112">
       <c r="A112" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>SYRMA</t>
         </is>
       </c>
       <c r="B112" s="51" t="inlineStr">
         <is>
-          <t>2026-10-27 11:27</t>
+          <t>2026-10-28 07:00</t>
         </is>
       </c>
       <c r="C112" s="51" t="inlineStr">
         <is>
-          <t>Gift Nifty Signals Flat Start as Fed Decision Looms</t>
+          <t>Syrma SGS Technology (NSEI:SYRMA) Stock Forecast &amp; Analyst Predictions</t>
         </is>
       </c>
       <c r="D112" s="51" t="inlineStr">
         <is>
-          <t>HDFC Sky</t>
+          <t>Simply Wall St</t>
         </is>
       </c>
       <c r="E112" s="81" t="n">
-        <v>0.612</v>
+        <v>0</v>
       </c>
       <c r="F112" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G112" s="82" t="inlineStr">
@@ -14295,21 +14295,21 @@
       </c>
       <c r="B113" s="51" t="inlineStr">
         <is>
-          <t>2026-10-27 10:50</t>
+          <t>2026-10-28 07:00</t>
         </is>
       </c>
       <c r="C113" s="51" t="inlineStr">
         <is>
-          <t>Sensex, Nifty end flat; Sona BLW jumps 9%, Mazagon Dock falls 6%</t>
+          <t>Market News: Share Market Today, NIFTY, BSE/NSE LIVE, Sensex Today, Latest Share Market News Live Updates</t>
         </is>
       </c>
       <c r="D113" s="51" t="inlineStr">
         <is>
-          <t>Fortune India</t>
+          <t>Livemint</t>
         </is>
       </c>
       <c r="E113" s="81" t="n">
-        <v>0.477</v>
+        <v>0.532</v>
       </c>
       <c r="F113" s="51" t="inlineStr">
         <is>
@@ -14325,22 +14325,22 @@
     <row r="114">
       <c r="A114" s="51" t="inlineStr">
         <is>
-          <t>CPPLUS</t>
+          <t>SYRMA</t>
         </is>
       </c>
       <c r="B114" s="51" t="inlineStr">
         <is>
-          <t>2026-10-27 10:46</t>
+          <t>2026-10-28 06:20</t>
         </is>
       </c>
       <c r="C114" s="51" t="inlineStr">
         <is>
-          <t>Aditya Infotech partners with Ranveer Singh as brand ambassador for CP PLUS</t>
+          <t>NSE adds six stocks to F&amp;O segment from today, October 28: Check full list</t>
         </is>
       </c>
       <c r="D114" s="51" t="inlineStr">
         <is>
-          <t>Business Upturn</t>
+          <t>Zee Business</t>
         </is>
       </c>
       <c r="E114" s="81" t="n">
@@ -14360,30 +14360,30 @@
     <row r="115">
       <c r="A115" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>SYRMA</t>
         </is>
       </c>
       <c r="B115" s="51" t="inlineStr">
         <is>
-          <t>2026-10-27 10:44</t>
+          <t>2026-10-28 05:30</t>
         </is>
       </c>
       <c r="C115" s="51" t="inlineStr">
         <is>
-          <t>Sensex Today Ends Flat | Nifty Below 22,750 | Axis Bank &amp; Asian Paints Top Losers</t>
+          <t>Syrma SGS Technology (SYRMA.NS) Jumps 3.67% to ₹1575.3, Approaches ₹1654.07 Resistance Zone - Time Weighted Price</t>
         </is>
       </c>
       <c r="D115" s="51" t="inlineStr">
         <is>
-          <t>Equitymaster</t>
+          <t>https://www.siam.in/</t>
         </is>
       </c>
       <c r="E115" s="81" t="n">
-        <v>0.026</v>
+        <v>0.459</v>
       </c>
       <c r="F115" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G115" s="82" t="inlineStr">
@@ -14400,21 +14400,21 @@
       </c>
       <c r="B116" s="51" t="inlineStr">
         <is>
-          <t>2026-10-27 10:43</t>
+          <t>2026-10-28 05:26</t>
         </is>
       </c>
       <c r="C116" s="51" t="inlineStr">
         <is>
-          <t>Sensex, Nifty Flat Amid Bank/IT Selling, Crude, US Fed Caution</t>
+          <t>Why Is Stock Market Falling Today? 4 Key Reasons Behind Sensex, Nifty Crash</t>
         </is>
       </c>
       <c r="D116" s="51" t="inlineStr">
         <is>
-          <t>Rediff MoneyWiz</t>
+          <t>NDTV</t>
         </is>
       </c>
       <c r="E116" s="81" t="n">
-        <v>-0.25</v>
+        <v>-0.402</v>
       </c>
       <c r="F116" s="51" t="inlineStr">
         <is>
@@ -14435,25 +14435,25 @@
       </c>
       <c r="B117" s="51" t="inlineStr">
         <is>
-          <t>2026-10-27 10:37</t>
+          <t>2026-10-28 04:15</t>
         </is>
       </c>
       <c r="C117" s="51" t="inlineStr">
         <is>
-          <t>Sensex, Nifty end flat as high crude and Fed caution offset sectoral gains</t>
+          <t>Jio Platforms becomes 12th Reliance Group company to list on NSE, says CEO Ashishkumar Chauhan</t>
         </is>
       </c>
       <c r="D117" s="51" t="inlineStr">
         <is>
-          <t>India Today</t>
+          <t>Moneycontrol.com</t>
         </is>
       </c>
       <c r="E117" s="81" t="n">
-        <v>0.34</v>
+        <v>0</v>
       </c>
       <c r="F117" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G117" s="82" t="inlineStr">
@@ -14470,21 +14470,21 @@
       </c>
       <c r="B118" s="51" t="inlineStr">
         <is>
-          <t>2026-10-27 10:35</t>
+          <t>2026-10-28 01:13</t>
         </is>
       </c>
       <c r="C118" s="51" t="inlineStr">
         <is>
-          <t>Why stock market ended mixed today: Sensex, Nifty flat as Midcap Index gains 565 points</t>
+          <t>Stock Market Today Highlights , Oct 6: Sensex settles 685 pts higher; Nifty 50 rises 220 pts; IT, Realty, PSU Banks end in red</t>
         </is>
       </c>
       <c r="D118" s="51" t="inlineStr">
         <is>
-          <t>IndiaIPO</t>
+          <t>BusinessLine</t>
         </is>
       </c>
       <c r="E118" s="81" t="n">
-        <v>0.649</v>
+        <v>0.402</v>
       </c>
       <c r="F118" s="51" t="inlineStr">
         <is>
@@ -14500,30 +14500,30 @@
     <row r="119">
       <c r="A119" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>AETHER</t>
         </is>
       </c>
       <c r="B119" s="51" t="inlineStr">
         <is>
-          <t>2026-10-27 10:22</t>
+          <t>2026-10-27 12:08</t>
         </is>
       </c>
       <c r="C119" s="51" t="inlineStr">
         <is>
-          <t>Nifty, Sensex close flat amid pressure from high crude prices and caution ahead of US Fed policy</t>
+          <t>Ather Energy shares: 125% YTD returns! Experts give 'portfolio stock' tag after Q2 results 2026 | Target, stop-loss</t>
         </is>
       </c>
       <c r="D119" s="51" t="inlineStr">
         <is>
-          <t>ANI News</t>
+          <t>TradingView</t>
         </is>
       </c>
       <c r="E119" s="81" t="n">
-        <v>-0.34</v>
+        <v>0.457</v>
       </c>
       <c r="F119" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="G119" s="82" t="inlineStr">
@@ -14535,30 +14535,30 @@
     <row r="120">
       <c r="A120" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>CPPLUS</t>
         </is>
       </c>
       <c r="B120" s="51" t="inlineStr">
         <is>
-          <t>2026-10-27 08:56</t>
+          <t>2026-10-27 10:46</t>
         </is>
       </c>
       <c r="C120" s="51" t="inlineStr">
         <is>
-          <t>Is India's Stock Market Heading For Its Worst Year Since 2008 Crisis?</t>
+          <t>Aditya Infotech partners with Ranveer Singh as brand ambassador for CP PLUS</t>
         </is>
       </c>
       <c r="D120" s="51" t="inlineStr">
         <is>
-          <t>NDTV</t>
+          <t>Business Upturn</t>
         </is>
       </c>
       <c r="E120" s="81" t="n">
-        <v>-0.848</v>
+        <v>0</v>
       </c>
       <c r="F120" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G120" s="82" t="inlineStr">
@@ -14570,7 +14570,7 @@
     <row r="121">
       <c r="A121" s="51" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B121" s="51" t="inlineStr">
@@ -14580,16 +14580,16 @@
       </c>
       <c r="C121" s="51" t="inlineStr">
         <is>
-          <t>Aptus Value Housing Nine Monthly results</t>
+          <t>Sensex Today | Stock Market Live: Sensex, Nifty trade flat; smallcaps jump 2.5%, IT slides 1.5%</t>
         </is>
       </c>
       <c r="D121" s="51" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
+          <t>IndiaIPO</t>
         </is>
       </c>
       <c r="E121" s="81" t="n">
-        <v>0.34</v>
+        <v>0.67</v>
       </c>
       <c r="F121" s="51" t="inlineStr">
         <is>
@@ -14605,30 +14605,30 @@
     <row r="122">
       <c r="A122" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>CPPLUS</t>
         </is>
       </c>
       <c r="B122" s="51" t="inlineStr">
         <is>
-          <t>2026-10-27 07:00</t>
+          <t>2026-10-27 02:09</t>
         </is>
       </c>
       <c r="C122" s="51" t="inlineStr">
         <is>
-          <t>Sensex Today | Stock Market Live: Sensex, Nifty trade flat; smallcaps jump 2.5%, IT slides 1.5%</t>
+          <t>Do Aditya Infotech's (NSE:CPPLUS) Earnings Warrant Your Attention?</t>
         </is>
       </c>
       <c r="D122" s="51" t="inlineStr">
         <is>
-          <t>IndiaIPO</t>
+          <t>Simply Wall St</t>
         </is>
       </c>
       <c r="E122" s="81" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="F122" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="G122" s="82" t="inlineStr">
@@ -14645,25 +14645,25 @@
       </c>
       <c r="B123" s="51" t="inlineStr">
         <is>
-          <t>2026-10-27 07:00</t>
+          <t>2026-10-26 21:36</t>
         </is>
       </c>
       <c r="C123" s="51" t="inlineStr">
         <is>
-          <t>Closing Bell: Sensex, Nifty end flat on expiry day; pharma, realty shine, IT drags</t>
+          <t>Indian Stock Market Crash: Sensex Falls 5,035 Pts, Nifty Drops 1,453 Pts From Peak; Can Budget Revive Bulls?</t>
         </is>
       </c>
       <c r="D123" s="51" t="inlineStr">
         <is>
-          <t>IndiaIPO</t>
+          <t>Goodreturns</t>
         </is>
       </c>
       <c r="E123" s="81" t="n">
-        <v>0.077</v>
+        <v>-0.318</v>
       </c>
       <c r="F123" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G123" s="82" t="inlineStr">
@@ -14675,30 +14675,30 @@
     <row r="124">
       <c r="A124" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>SMLMAH</t>
         </is>
       </c>
       <c r="B124" s="51" t="inlineStr">
         <is>
-          <t>2026-10-27 06:58</t>
+          <t>2026-10-26 05:47</t>
         </is>
       </c>
       <c r="C124" s="51" t="inlineStr">
         <is>
-          <t>Indian Stock Market: Sensex and Nifty Trade Flat Amid IT Sell-Off, Broader Markets Outperform</t>
+          <t>SML Mahindra Limited (SMLMAH.NS) Slips 2.83% to ₹4,706.5 as Stock Tests Lower End of ₹4,471–₹4,942 Range - Hedge Fund Favorites</t>
         </is>
       </c>
       <c r="D124" s="51" t="inlineStr">
         <is>
-          <t>Pragativadi</t>
+          <t>https://www.siam.in/</t>
         </is>
       </c>
       <c r="E124" s="81" t="n">
-        <v>0.6909999999999999</v>
+        <v>-0.318</v>
       </c>
       <c r="F124" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="G124" s="82" t="inlineStr">
@@ -14715,21 +14715,21 @@
       </c>
       <c r="B125" s="51" t="inlineStr">
         <is>
-          <t>2026-10-27 06:02</t>
+          <t>2026-10-25 14:34</t>
         </is>
       </c>
       <c r="C125" s="51" t="inlineStr">
         <is>
-          <t>Sensex Jumps 483 Points, Nifty Recovers After 4-Day Slump</t>
+          <t>Stock market prediction for Monday Oct 26: Sensex, Nifty levels, top stocks to watch - Will bulls dance again?</t>
         </is>
       </c>
       <c r="D125" s="51" t="inlineStr">
         <is>
-          <t>Rediff MoneyWiz</t>
+          <t>IndiaIPO</t>
         </is>
       </c>
       <c r="E125" s="81" t="n">
-        <v>0.361</v>
+        <v>0.542</v>
       </c>
       <c r="F125" s="51" t="inlineStr">
         <is>
@@ -14737,496 +14737,6 @@
         </is>
       </c>
       <c r="G125" s="82" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B126" s="51" t="inlineStr">
-        <is>
-          <t>2026-10-27 05:17</t>
-        </is>
-      </c>
-      <c r="C126" s="51" t="inlineStr">
-        <is>
-          <t>Stock Markets Today: Sensex, Nifty Dip on High Crude Prices, IT Sector Woes</t>
-        </is>
-      </c>
-      <c r="D126" s="51" t="inlineStr">
-        <is>
-          <t>Rediff</t>
-        </is>
-      </c>
-      <c r="E126" s="81" t="n">
-        <v>-0.477</v>
-      </c>
-      <c r="F126" s="51" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G126" s="82" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B127" s="51" t="inlineStr">
-        <is>
-          <t>2026-10-27 05:10</t>
-        </is>
-      </c>
-      <c r="C127" s="51" t="inlineStr">
-        <is>
-          <t>Stock markets fall in early trade amid persistently elevated crude oil prices, IT selling</t>
-        </is>
-      </c>
-      <c r="D127" s="51" t="inlineStr">
-        <is>
-          <t>bfsi.economictimes.indiatimes.com</t>
-        </is>
-      </c>
-      <c r="E127" s="81" t="n">
-        <v>-0.727</v>
-      </c>
-      <c r="F127" s="51" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G127" s="82" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="51" t="inlineStr">
-        <is>
-          <t>CPPLUS</t>
-        </is>
-      </c>
-      <c r="B128" s="51" t="inlineStr">
-        <is>
-          <t>2026-10-27 02:09</t>
-        </is>
-      </c>
-      <c r="C128" s="51" t="inlineStr">
-        <is>
-          <t>Do Aditya Infotech's (NSE:CPPLUS) Earnings Warrant Your Attention?</t>
-        </is>
-      </c>
-      <c r="D128" s="51" t="inlineStr">
-        <is>
-          <t>Simply Wall St</t>
-        </is>
-      </c>
-      <c r="E128" s="81" t="n">
-        <v>0</v>
-      </c>
-      <c r="F128" s="51" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G128" s="82" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B129" s="51" t="inlineStr">
-        <is>
-          <t>2026-10-27 01:30</t>
-        </is>
-      </c>
-      <c r="C129" s="51" t="inlineStr">
-        <is>
-          <t>Stock market outlook today, 27 Oct: Sensex, Nifty prediction - DJIA, S&amp;P, NASDAQ, GIFT Nifty, Kospi, Nikkei, Taiwan cues</t>
-        </is>
-      </c>
-      <c r="D129" s="51" t="inlineStr">
-        <is>
-          <t>Livemint</t>
-        </is>
-      </c>
-      <c r="E129" s="81" t="n">
-        <v>0.842</v>
-      </c>
-      <c r="F129" s="51" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G129" s="82" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B130" s="51" t="inlineStr">
-        <is>
-          <t>2026-10-26 10:28</t>
-        </is>
-      </c>
-      <c r="C130" s="51" t="inlineStr">
-        <is>
-          <t>Sensex Today Ends 483 Points Higher | Nifty Above 22,750 | Apollo Micro Systems Up 10%</t>
-        </is>
-      </c>
-      <c r="D130" s="51" t="inlineStr">
-        <is>
-          <t>Equitymaster</t>
-        </is>
-      </c>
-      <c r="E130" s="81" t="n">
-        <v>0.402</v>
-      </c>
-      <c r="F130" s="51" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G130" s="82" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B131" s="51" t="inlineStr">
-        <is>
-          <t>2026-10-26 10:18</t>
-        </is>
-      </c>
-      <c r="C131" s="51" t="inlineStr">
-        <is>
-          <t>Taking Stock: Market snaps 4-day losing streak; Nifty reclaims 22,700, Sensex gains 483 pts</t>
-        </is>
-      </c>
-      <c r="D131" s="51" t="inlineStr">
-        <is>
-          <t>Moneycontrol.com</t>
-        </is>
-      </c>
-      <c r="E131" s="81" t="n">
-        <v>0.402</v>
-      </c>
-      <c r="F131" s="51" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G131" s="82" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="51" t="inlineStr">
-        <is>
-          <t>SMLMAH</t>
-        </is>
-      </c>
-      <c r="B132" s="51" t="inlineStr">
-        <is>
-          <t>2026-10-26 05:47</t>
-        </is>
-      </c>
-      <c r="C132" s="51" t="inlineStr">
-        <is>
-          <t>SML Mahindra Limited (SMLMAH.NS) Slips 2.83% to ₹4,706.5 as Stock Tests Lower End of ₹4,471–₹4,942 Range - Hedge Fund Favorites</t>
-        </is>
-      </c>
-      <c r="D132" s="51" t="inlineStr">
-        <is>
-          <t>https://www.siam.in/</t>
-        </is>
-      </c>
-      <c r="E132" s="81" t="n">
-        <v>-0.318</v>
-      </c>
-      <c r="F132" s="51" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G132" s="82" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B133" s="51" t="inlineStr">
-        <is>
-          <t>2026-10-26 04:52</t>
-        </is>
-      </c>
-      <c r="C133" s="51" t="inlineStr">
-        <is>
-          <t>Sensex jumps 1,100 pts from day’s low, Nifty closes above 22,750 as D-St rebounds after 4-day losses. Is t</t>
-        </is>
-      </c>
-      <c r="D133" s="51" t="inlineStr">
-        <is>
-          <t>The Economic Times</t>
-        </is>
-      </c>
-      <c r="E133" s="81" t="n">
-        <v>0.202</v>
-      </c>
-      <c r="F133" s="51" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G133" s="82" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B134" s="51" t="inlineStr">
-        <is>
-          <t>2026-10-26 04:32</t>
-        </is>
-      </c>
-      <c r="C134" s="51" t="inlineStr">
-        <is>
-          <t>Sensex settles 500 pts higher, Nifty ends above 22,750: Key factors behind markets snapping 4-day fall</t>
-        </is>
-      </c>
-      <c r="D134" s="51" t="inlineStr">
-        <is>
-          <t>Moneycontrol.com</t>
-        </is>
-      </c>
-      <c r="E134" s="81" t="n">
-        <v>0.077</v>
-      </c>
-      <c r="F134" s="51" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G134" s="82" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B135" s="51" t="inlineStr">
-        <is>
-          <t>2026-10-26 04:05</t>
-        </is>
-      </c>
-      <c r="C135" s="51" t="inlineStr">
-        <is>
-          <t>Why is the stock market down today? Sensex drops over 600 points, Nifty drops below 22,400 - Top 3 reasons explained</t>
-        </is>
-      </c>
-      <c r="D135" s="51" t="inlineStr">
-        <is>
-          <t>Livemint</t>
-        </is>
-      </c>
-      <c r="E135" s="81" t="n">
-        <v>0.542</v>
-      </c>
-      <c r="F135" s="51" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G135" s="82" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B136" s="51" t="inlineStr">
-        <is>
-          <t>2026-10-26 01:27</t>
-        </is>
-      </c>
-      <c r="C136" s="51" t="inlineStr">
-        <is>
-          <t>Stock Market Today: Gift Nifty, FPI Outflows To Oil Prices; Five Key Factors For Sensex, Nifty 50 On October 26</t>
-        </is>
-      </c>
-      <c r="D136" s="51" t="inlineStr">
-        <is>
-          <t>NDTV Profit</t>
-        </is>
-      </c>
-      <c r="E136" s="81" t="n">
-        <v>0.8070000000000001</v>
-      </c>
-      <c r="F136" s="51" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G136" s="82" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B137" s="51" t="inlineStr">
-        <is>
-          <t>2026-10-26 01:22</t>
-        </is>
-      </c>
-      <c r="C137" s="51" t="inlineStr">
-        <is>
-          <t>Stock market outlook today, 26 Oct: Sensex, Nifty prediction - DJIA, S&amp;P, NASDAQ, GIFT Nifty, Kospi, Nikkei cues</t>
-        </is>
-      </c>
-      <c r="D137" s="51" t="inlineStr">
-        <is>
-          <t>Livemint</t>
-        </is>
-      </c>
-      <c r="E137" s="81" t="n">
-        <v>0.842</v>
-      </c>
-      <c r="F137" s="51" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G137" s="82" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="51" t="inlineStr">
-        <is>
-          <t>MARKET</t>
-        </is>
-      </c>
-      <c r="B138" s="51" t="inlineStr">
-        <is>
-          <t>2026-10-25 07:03</t>
-        </is>
-      </c>
-      <c r="C138" s="51" t="inlineStr">
-        <is>
-          <t>Trump hints at an Iran attack or deal! Impact on India stock market, Sensex, Nifty, gold decoded; top 10 stocks to watch</t>
-        </is>
-      </c>
-      <c r="D138" s="51" t="inlineStr">
-        <is>
-          <t>Livemint</t>
-        </is>
-      </c>
-      <c r="E138" s="81" t="n">
-        <v>0.176</v>
-      </c>
-      <c r="F138" s="51" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G138" s="82" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="51" t="inlineStr">
-        <is>
-          <t>SYRMA</t>
-        </is>
-      </c>
-      <c r="B139" s="51" t="inlineStr">
-        <is>
-          <t>2026-10-23 22:40</t>
-        </is>
-      </c>
-      <c r="C139" s="51" t="inlineStr">
-        <is>
-          <t>ELECON Share Price Today - Elecon Engineering Company on NSE/BSE</t>
-        </is>
-      </c>
-      <c r="D139" s="51" t="inlineStr">
-        <is>
-          <t>scanx.trade</t>
-        </is>
-      </c>
-      <c r="E139" s="81" t="n">
-        <v>0</v>
-      </c>
-      <c r="F139" s="51" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G139" s="82" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -15237,7 +14747,7 @@
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <conditionalFormatting sqref="E5:E139">
+  <conditionalFormatting sqref="E5:E125">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-1"/>
@@ -15371,20 +14881,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G123" r:id="rId119"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G124" r:id="rId120"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G125" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G126" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G127" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G128" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G129" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G130" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G131" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G132" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G133" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G134" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G135" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G136" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G137" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G138" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G139" r:id="rId135"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
@@ -15411,28 +14907,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>"src": "bhavcopy"}}, "CPPLUS": {"2026-10-29": {"open": 3985.0, "close": 3951.7, "src": "yahoo"}, "2026-10-30": {"open": 3932.1, "close": 3811.5, "src": "bhavcopy"}}, "THANGAMAYL": {"2026-10-29": {"open": 4681.0, "close": 4630.5, "src": "yahoo"}, "2026-10-30": {"open": 4620.0, "close": 4455.0, "src": "bhavcopy"}}, "KIRLOSENG": {"2026-10-29": {"open": 1907.3, "close": 1890.3, "src": "yahoo"}, "2026-10-30": {"open": 1884.0, "close": 1796.1, "src": "bhavcopy"}}, "SMLMAH": {"2026-10-29": {"open": 4770.5, "close": 4848.0, "src": "yahoo"}, "2026-10-30": {"open": 4918.0, "close": 4724.5, "src": "bhavcopy"}}, "AETHER": {"2026-10-29": {"open": 1590.0, "close": 1581.0, "src": "yahoo"}, "2026-10-30": {"open": 1597.4, "close": 1616.2, "src": "bhavcopy"}}, "SBC": {"2026-10-29": {"open": 65.39, "close": 66.52, "src": "yahoo"}, "2026-10-30": {"open": 67.05, "close": 66.15, "src": "bhavcopy"}}, "SYRMA": {"2026-10-29": {"open": 1563.0, "close": 1669.0, "src": "yahoo"}, "2026-10-30": {"open": 1675.0, "close": 1625.3, "src": "bhavcopy"}}, "TDPOWERSYS": {"2026-10-29": {"open": 719.8, "close": 719.45, "src": "yahoo"}, "2026-10-30": {"open": 705.0, "close": 713.9, "src": "bhavcopy"}}, "RATNAVEER": {"2026-10-29": {"open": 345.0, "close": 352.85, "src": "yahoo"}, "2026-10-30": {"open": 354.2, "close": 360.25, "src": "bhavcopy"}}, "NIFTY50": {"2026-10-29": {"open": 22690.65, "close": 22936.75, "src": "yahoo"}, "2026-10-30": {"open": 22964.5, "close": 23053.1, "src": "bhavcopy"}}}, "entry_override": {}, "news": {"fetched": "2026-10-30 14:55", "days": 7, "items": [{"symbol": "SYRMA", "title": "Syrma SGS Q2 results: Profit nearly doubles to \u20b9117 crore, revenue jumps 74%", "link": "https://news.google.com/rss/articles/CBMipwFBVV95cUxQa0tHRVBlU0NteTRiWnRVeHdHSzBkUXdLd2tRWTJPYThtVXJUT0V4Z09aVVpUaWE4TUVQQVNvVXVzYVFsRmZlT1VFVFE4NWI3bFRScmJmZTdsa3FrTmtvNmdEeXF5WnlsdWFDZ3pOdUJnUmpsYUdVTDRHWDVJS0RRMTlrWFNQR3Zib1cybjlXZUQ1WXRNVGxlZWlnblZLQll3czJQelAzUdIBrAFBVV95cUxQWWVNajdfcWthd1FGS3dENzdIeWltVzdfWTRueHBPYlFWSEs4MHNnOW9HQnVWODIxTENyb21PblA5Y3d2Ym4zeVkza29VZ0VQSENCb3dhUVQyN1N4WFlGWnNTaUt1czBRWl9NTy01UmU0bExnQXZKMUhpeW8yUU9GT0tPbDFpeHh6em5GZzNZNzZTYUFuSkR6RlFwS0Fwcy1SQjZLSHdDdTRFaTZm?oc=5", "source": "CNBC TV18", "published": "2026-10-30 13:51", "score": 0.66, "label": "Positive"}, {"symbol": "AETHER", "title": "Aether Industries (NSE:AETHER): What Do Aether Industries\u2019 September-Quarter Results Show?", "link": "https://news.google.com/rss/articles/CBMixgFBVV95cUxNb3lGcXBYMGhGTkhHcVNBUFRETjZsYWl5eDRicWZEU0hTLVo1bHB1UDFFNHRPa3NsaGM1MzlmU0ptWnUtNzJwTWVCTDB2RXU3cWVvblI1UjZhVkZEb3pxVXJnUVlvamRDaTRUcVh5S05ubGhydDhkU1hNR2hOLVZldzhfbktjM0VJU3V4TTBKaS1ycUtvX2pQem4ycUNuN1NmUHU5cTlwLTctT3RQR0ZmZlVaSTNKcW9veHUyQVh2Nmx1dlFPRWc?oc=5", "source": "Kalkine India", "published": "2026-10-30 12:34", "score": 0.0, "label": "Neutral"}, {"symbol": "SYRMA", "title": "Syrma SGS Technology Q2 results: Net profit jumps 83.1% YoY to Rs 117 crore, EBITDA rises 67.7%", "link": "https://news.google.com/rss/articles/CBMi7wFBVV95cUxQbTJaR3NseUh5UWNIZnFRcVFwYllEQUdwNTNKVVZNUFR3RFJFanNMSktJV3NsS25XVDBDeGFfRUFXNUxtQmZYajVOQ29DaFRaYk9RTTlDMGFQM0NjT1o1ZWJtS2VuN2JCT1VEU2ZyWHVINGgwc0lVa0liODhpZEVDTEhSTTczQ3hxMEFLUnMyZ192MThYT1JwRk5aYUZJd3ZuWU5qSS1lRzJ5Yjh6SGpESnBrX2hFT2RtVTVuNG5jZ1Rnb2Y1bEtpUU1YM241ZGJBMmJHWFI5blJHaVZKTXJ2ZTZFcC1UX2NvUlZOZkhqSQ?oc=5", "source": "Business Upturn", "published": "2026-10-30 11:15", "score": 0.66, "label": "Positive"}, {"symbol": "SYRMA", "title": "Diwali 2026 Top Stocks To Buy: Apollo Hospitals, GE Vernova, TARIL, TD Power, Jindal Steel, others; top 10 picks, target", "link": "https://news.google.com/rss/articles/CBMikwJBVV95cUxOejZuNVZHYUg3QlloRzQzYXBzbjR3OFdESEFXaU1ZaGg4ZU1YMkExbUpVNHZ0S1JCUEZQNmRKVXVraTVxNjAxcnc2MWhPamFkclpDVGNEZDlILWhBdmtzQy16RHVJaW1wQjdtbmN1TUVUZDBudlMtNnNfcXdWMEV1ZWphaElvTUdTeTBsNDFYbEs3UEFHMVMySzZCVEIzeUYwR3Y3bWdPQmVfcHBlOG84Zkg0aGxLMmtLVDhzQms1MUNnWDRXYmFjbnZWQzU0SC1Oci1JXzBjbnQ0UTBJU1l1MWJ4MTd4TV9NM0FVSC1LRV80c1Q4QllyS01NOWFHVUZpMXdkdEpSNmt0aEg4WVl4V2Fwc9IBmAJBVV95cUxPQjJxY1ZBR21RVFNpWE1vR0pkOVA5Z0RUUmFZRDZ4dS16TWpjdzFzcjM0QmQ3bVkxWV9fWmdIdXIzdzA3MFZHUXNIZm9sdjUtd3cyUl82V1RKRTlZVHBMQjVNeFdXWmp6U293TS1WYnpiVzJhZlV0UVZGbTJ6WldTVC03bmhmYlhobTJJNlRUd2VucW1vRlpPRElMelZneGJGdzZLWmRVMWxSd3MwbXpKVXBEQkdMVEdsNWR5c0NXT3dGRVlUSEFGZ3licnVTbllGbnZ6VFBCNGxmZk01cWJjcVpqQW1TZGlmNkE4RUlwdDVyRDhoZUJmaTNLNVpBQ3JRTklFX2dkM2lIcnUxNXlxZnBCemtMMThQ?oc=5", "source": "Livemint", "published": "2026-10-30 11:14", "score": 0.66, "label": "Positive"}, {"symbol": "MARKET", "title": "Market wrap: Shriram Finance, Nestle India, Trent, InterGlobe top gainers and losers on Nifty and Sensex", "link": "https://news.google.com/rss/articles/CBMingJBVV95cUxQNWQ5WS1pSUV0c0k1UDRCeWxBMjNfVDZWWXg2UUJXLWJIUjUxQ2pwb0NBUk1sRDh3MkJRSVZpZnBzOWJ5c3k1Vlh4RW9DUmpROUdjQUpGMm1oSDMycTlMOU1RU1ZjSTA4REhOb0o3c0FqYTFuc29VaTRBMkd1Mms1aVF4NW95dHVaME8ydXp6VDVVU1BTeWFFanRSR2dhOE9PdWU1MWY3dW1QSi1aN21UemxxdXptbHE3Q0FNWVZqN1JXTnBEVzJXTV9jdXFId04ta0ZvTGdCOFRZcnU0WjlGYkdQQlpISlNxQi1XY09zYTBaNVZLcEVfVVpWdUJaYzNBd3l1alEtYjFXZzVETzFodUk3Wk93a3lVX0I2R1ZB0gGXAkFVX3lxTE96bkJGNFNzdEVsbWxGQzJDYjkwbkRtNjVjZnR5MV9TQlB5cHR4a2o2eVBhVW83T09YTUZ3dkdYTnVRVmlPaG9aNXVCbE9tZ0hFalhVamZoN2VGc3VNU01FZGVxSWtELWZhaXEwYTRjdUlhQzR5OGw5WW9ZWjhzNXVRYzViYV9oZ3NuUVlGbFNfQ3lHQkE1ci10OTBjRkNqR1hhZXk0WVAxZUVYSGhwUFpIcDhiQmZxYWZuODM2eEhFUXQ3ZEFsME8wdVZ0OVB3NVJoWU1iV25tVWdJT1FINklXT2JhTXM2NDFsT1JFVXphUUZLOTZ2OHVLejdOTzRsdkc0TkxVeGctbkwtVVlxUDRhb1pJVDJWMA?oc=5", "source": "The Economic Times", "published": "2026-10-30 10:56", "score": 0.026, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex, Nifty Rise; IT &amp; Pharma Lift Markets as Midcaps Slide", "link": "https://news.google.com/rss/articles/CBMisgFBVV95cUxOajFHdFZlZGo5cUk0dWJ3V1E4c2dCUFlBVFVMZV8wYklSQzVtUEJKRDZVSFhIdHRIUDUyZGlHc1ZWVC12bGwzMTFtSEpqdWdpYmowZmRqQ2ttVWVuaDRVOTh4b05lUVBQR2JYeUNjWDRjcjRMWExJSEFhV2lKRFRoUUVmaWFtSDBYdjBldjI2NWdYUlBHZXpUX1FRVXpwaXZucGpuQWlRLWxrdkJoWmRRblNR?oc=5", "source": "HDFC Sky", "published": "2026-10-30 10:53", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex rises 308 points, Nifty above 23,000 even as broader markets crash. Will D-Street bulls extend reco", "link": "https://news.google.com/rss/articles/CBMipwJBVV95cUxPTXhsRWN1cm45ckpDbWUxY21qclNKLTVCeDlaUlJweGFFUS1qSG40b09sNVlzTFBKQVNPZzU4R3VSSGZuNF96dHFPVVFDQmFOTy1YZU43YjJaRWpCczlrZkViZ0tTSS1lN1VzSUdrbHFoS01uMW9vRjl3MWRzSnZiSkd2T3REMjBBUTYwY29vOS1xSDNndVhFT0RNdjVtN1lFUkljSlE0cjR3ZjJqRDZodXBuMlpmSGJhYklpRnAxYktzS0hhYWJoRUJUWWUyeWlScXlTVk05VkMtazRESVQ1STE0TU1Cd0Q5Z2NHcXdZWm5XeFpaMHFJUm9CalNmMGdYZEpTS2ttUnFvaDFjVEc1YzhEb3NLSWlMRHYxUXVwaUFWQTZXZ0lR0gGgAkFVX3lxTE55RHpQVXVLRUxDYkNVYmFlZ2FlbU9vdnZVNTBvUXhZSFJBaHpKOXJ6dnE1aVpGSXlZeGdGaUtmMGN5TVdHX21JYkhuVXgyWmE5eW9UcEhMdmg0cGlJaGFRdEttaktQTlphMEs3Vml4cW1MMXY1eTU5S1dtbDRfRXREd2hmM3FRMGdBMVFjUmpqSlJZMUtOVjUzbTdaVTVUT3I1NDE5cWljc0NGaHFnZ1RVM0RWQUxBU0swOE1Ydk1HVDlvRU9GM0htOVdxeWZRRXRNWjVRbF96MVVZQzBsX2JfNlNLTDlaYk5HWm9fS2xQeExiWFNBMmh5UHlBdGUwYlozX0ZCU2ZxUzBjcmNQUG5PSzdkQW91cEppOWNsM1ZIWQ?oc=5", "source": "The Economic Times", "published": "2026-10-30 10:35", "score": -0.103, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex, Nifty extend gains for 2nd day: IT stocks lead rally, broader market underperforms", "link": "https://news.google.com/rss/articles/CBMiwAFBVV95cUxNUzFDYmRlTTRKR1BhNDQxb3lJc1ZER3FjUXB6ZFVQV1o5MHZVVk12ZS01ME1iVHZ1NkNWOGNHS2N2YTBWZzFRS0luNkRwUllwcDNYNktWWXNwaTFQdWk0aDlsQmUyQzNhMXowZnFkbzg1UGI2NHlkc2tldzhPYy0zc2tIVmw3VUhXMVRtbUxnd2pTdEdsME12eDM5VlBGWEZXNzFHY08zTl81am9jQkJTZFVzSVdMX0IzaTVZcUNGb1Q?oc=5", "source": "IndiaIPO", "published": "2026-10-30 10:31", "score": 0.84, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty extend recovery; what's driving this upmove? -", "link": "https://news.google.com/rss/articles/CBMilAFBVV95cUxORUxpb0U0WlRwTF81LXhEQklDb1lULTAyRHhKbzE2MDkyblBpNzg3QVJ3YlVTTG5zZ1RMSjlpaG1TUk1JUXhhZUVKTTE5bHJqMm1KRmpLUm91SGtibV81VURxNXZnd3c5YmRNcnpVWDFqNGJvaXBYXzdKd0NWSVlzMTMzVnV2Q1lIQWFPRTM0OEgxTDFl?oc=5", "source": "IndiaIPO", "published": "2026-10-30 10:31", "score": 0.527, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex Today Ends 308 Points Higher | Nifty Above 22,300 | Vedanta Oil and Gas Up 8%", "link": "https://news.google.com/rss/articles/CBMi2AFBVV95cUxPa0xfS0R1dFFiRTdEaW5zbFpJQVdYNC1yNzlKN0xUU1NSaGJ5LUJKa3M1Z2lZWHlrVm5GR3F0WG4tQzh1OEhHZHNxYlU5ekRTODFKVU4wUDltbkdFd2NVOThobHFPVHVPdTNXc1BndmNxY3RwTXRwNEpPcUhPNjJ0MlBDalpJYm53MUctVjIyWWowdEFEY3JucEo2bU01RzdVVzZmMWk3MVRJYTRZMjBCZjN0NGx1WnRTUDE0OThSZWtMT0x5NExVS21OVnh6YmJ6aUJ6WW1RbjE?oc=5", "source": "Equitymaster", "published": "2026-10-30 10:28", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty close with gain of 0.5% as IT, pharma stocks rally; weak broader market limits gains", "link": "https://news.google.com/rss/articles/CBMivwFBVV95cUxPZW9rV0NJRXU2T002TkpGY3BBMWpjYWJMLXNYOUZ4bUQwZkw4UU1ZMmJLblFRZWhpdmZUc0VPYVp5WHVDMTRFZnRsNkZzQjFlMUdlMGgyQy05bVpVa0lhaU9PSTlXU2ZTYWdIUVF3ZEV2MFB1SGVtbk9LUWhPWWRQbVlCbHNTbVRZZW40QW45R1hVVkcwc3VWemxkRUdieTA1YmhHZVMybTBWNW5OTnJzcTgzOHVkbVlGbzBxSlpxUQ?oc=5", "source": "ChiniMandi", "published": "2026-10-30 10:26", "score": 0.796, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex ends 308 points higher, Nifty above 23,000; Trent up 5%", "link": "https://news.google.com/rss/articles/CBMi1wFBVV95cUxQMlVJODZONnhDZU1vT2d0Wl9ZMEFmZkN6RGFrVU95R2RqanBoZEpCSTRZckxNcjVOTDFoY1FyaGE0RF9hS3UwVlptODRfMHFoY0Rvd0l0R3JJTUUzTExBeVc0RVFNUElyaGkybHdwZHByWjF6Nld4VWVCRHFEQ3l1UkQtSHB0M1VrZXB4MTBEWENzUnowS1I2c1BOeGIycEJWSmRScUlFQnc2N1VwVmlGd3BSX19iNEp4SWxNMWJiV0hXZHZ3NDIyQlg2NnQ0N09XWWZTdHU1UdIB3AFBVV95cUxQSTJkN2R1WXNmVVFmNE5GX1M4RHhod3daU2k0emQ5N0lWdmZxcXI1VDFCWDBkcDg2eGZ0TWV4R2ZCOVdtTC1leTBaOGRnaFd6UHRhbWhUNVBpRzhib0F4RWNybFlUTlBMamtLUXN4VXlOcUZTT0FBZ21Wa1hUZ2FYZUgwSDVPVGFjQ2R5ZXh6OGtMWGlzMUI1SjJQR2NaelFXTm5nZU9jVnBSLUtjTzhqZVlMWHNTc3FjSm1pekpVRFd2TTdLci03cGozMjhoczAtQ3pENXNoZ056d3dM?oc=5", "source": "India Today", "published": "2026-10-30 10:03", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Market Wrap: Sensex Gains 308 Points, Nifty 50 Ends Above 23,000; Trent, IndiGo, Infosys Lead", "link": "https://news.google.com/rss/articles/CBMiiAJBVV95cUxQZTFyMk9sdFl3QmJnUDd2OGhhdDNIZ3FwcDQwclFmNE1Ba3ZsakV0RzN0RHlKUkRYZnJST19SVDlqZmp5UGV0OGdOYzlLTkNNMTFqaEhNZGQ5cmctT2JzTEtZNzk4N1lfb2lyc2NuVU1ETHNWU0ZBZWpxX29hVWxxNUp4VE5pNndCVFVDeWtmZWNPQkh4U2xFeFp6NEd0am1jV2FBSWZIb215bUxTVnc2LTdhQ0lmM21KSHUtQjVSVlVpajhPdkZYdHQwTEgyc01tMFdxLXZBZkUwSUdGdXNkUjl4NGVMeHNWNzVROXhhSDUxT1BJSXo1enlzR3VVNXpyeWRaeTc4YmLSAZACQVVfeXFMTUltcFpOMzllTWlGSzAweENGY0Nob0tmTk96eV9wOVB1cGlDeTRuN1hRRFI4RS1KTVoyUW5xdWxpU24ySVIzWk9JV2F6bks2bVJ4TlZidVFqQk1LU3pOYlNEV2Qyc1JVSGlhVDhyb19xQlpQbWFmUmdXakhsUDZtSUEzSXlnQVA1SEhXV1BzZURDVnJablhfSk1FUzVCSmEwQmpZczltQVRON3otMzV4MnUzVGxsTlNJMGt3ZU5fWlhrcU53YzdHTE92UGx0QjdBTkdfOUVobGVib3VCcDR2MGZ4Ulk4R1haZkJZdEQxalExRDZqT01DMjlQbEE4RVJ4b0Z0UGh1c05kX1A3bnNOWFQ?oc=5", "source": "NDTV Profit", "published": "2026-10-30 09:52", "score": 0.649, "label": "Positive"}, {"symbol": "CPPLUS", "title": "Aditya Infotech CPPLUS ESOP Allotment 48,100 Shares Oct 2026", "link": "https://news.google.com/rss/articles/CBMiwAFBVV95cUxOUHlaMl84Z2E4T0RVUE5PMW5FZjVuQW1RcjFVTXd2ZUdMdmE3dXpNTURraTVmWHJYd2lQbG5fQVh2ZE1WVDlob2NDR2I2YWRQMVRLR0t2YVRaSVlYWXBsVXJoS2YwUENlLXducG1jaUtKbXNlUEVHQy1RT0JXdXhLZV81UklYZzFuMmFMUFFuRS1sMkRaZGgzRHNyMk9Yek5sdi1oNVZXbmdxTDhyZzlhODVKX1pmS1pYODc3MHBBT3Y?oc=5", "source": "Kalkine India", "published": "2026-10-30 08:44", "score": 0.0, "label": "Neutral"}, {"symbol": "AETHER", "title": "Aether Industries reports robust Q2 FY27 financial performance with \u20b93,472M in operating revenue", "link": "https://news.google.com/rss/articles/CBMizwFBVV95cUxQaXBiV3ZRODczRjJseWRyYjk2WlFLdHd1ek5tSHNjR0NGRGVIV09hM29yRHZLUjRxaTMxeU9fMmN0bFE4d3k5a0hMWk42TXVVR0NZMV90Zmcyc1p2NHJNRzRnT2NMN0szWFRTcm80TU96MTlGdXZ4UEs2U2VYaGZmUUdGdGdtNE5YVVRTdVNOSXpsYUpQTEdVMXU2NVNBbHR4RUNNQ09WaHIwSVdtRjM2Qm5RNjV0cGk0ZThLblZOLW1UbGwxYjg4RFN3QW1kOE0?oc=5", "source": "Business Upturn", "published": "2026-10-30 08:35", "score": 0.421, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex zooms 1,200 pts in 2 days, Nifty tops 23K: Why are bulls in charge?", "link": "https://news.google.com/rss/articles/CBMi1AFBVV95cUxOTDJ1dFlKVkRQMEhPdHhUbGlyTHk4ams1Y0EySG9zRlhkcWpORm1FUzdwWDdtVmZRT2s1YWJJYUpDU3h6UUt6Y29DaFJsMFpmZkwxMnk1dnNGQ3kzSlNfNlZoOTVURThySncwaUZ1cDJzeGU5NlN2NV9aeWROd3RuWTItcmtlNUE5WkZVbi1wUUtobnJzRGp4SE1PcUtPaTQxbnVDRUdTWFpQTGZjMzh6dTJ0TzJtRVNMbUJMVmlBTlFPTXQxX19QWktWUEhWM3ZkNm51VtIB2gFBVV95cUxQcjQ4VkQzSUZjUnlJeGk3b3ZFQk5QYVM1ejM2X3dZanFHNFhOWTFJME0teEVXZFRQZDgzMzktem9uMWc3ZXphVVJJUGwzUG1KVnpKVi1Xamd4cy1qM0hTYUR6OTVSa2ZUQ1E2S3dwWHV3MTByUGtFQS1seXl0SWNUXzhxeFZ3UEZIQVd2V0w5NlNNeHgzeUVHYTV4ak1iYW5IY0IycU4xYnJ5dGxxMm1QSFdQTGpQYWE3Y2dUekVadEVSeHZYc3c1UDdmMDVJd3hXbjlMRjItUlhBUQ?oc=5", "source": "Business Standard", "published": "2026-10-30 08:02", "score": 0.718, "label": "Positive"}, {"symbol": "MARKET", "title": "Passive funds could buy up to Rs 36,500 crore upon Jio Platforms' entry into Nifty, Sensex", "link": "https://news.google.com/rss/articles/CBMi6AFBVV95cUxPQml6RHdZS2FTeE1nN05IMHpUTVYwR3BxdXhNRVViWjlzSExMb2ZsRFBGZmc3bXZRbDR0Z2ZZVkNhclFpRS1tYWtfN3RpM18waHFDdkRzR3FWeDllUFhvb2JlaVQ0RkozVWt6b0dwS1VWRk5zcjVaM09RUjE4ME1rNmZ1WkxqVl9FVm40ZmVoeEp0X25uTWN0Vm5PLVV2OGpLaTF6X1VuNW5kNUVwU1FtclNGdU94LXQxdUozUTNwQnVDQzR1OEhCcVhpNWpOakxseUIySzRrdWMycFR2TWRRSUtjQWdCZUxh0gHuAUFVX3lxTFBvVWFETnc5Y1BDWk1YWmhPdFNTbTZESnpWaHNVSTRoTWJHVlBONW1yVldTVThqckJyTURkTXotaVRCX3lOZ3o0QlRINTZJcnY2SmI0R0JuMkdjV21jVVJrcG55Y1lrM0F5N0NUS1pnODZNTmRIbVRLYU5nbXE3UmZyb0hERFNBdTJ1SEdTLUluV3FldFF2VVd1d2lucXpUcUlxNVlnODdqdkN2UjE1WmNfWlU2NWJLelpwSXptX3hKMGpjQ2xaOVFDdW5hd21UMktsODRIaVdmY0ZoZkdhQnZvaC1Ha01SN1JlVV9TR2c?oc=5", "source": "Moneycontrol.com", "published": "2026-10-30 06:40", "score": 0.691, "label": "Positive"}, {"symbol": "AETHER", "title": "AETHER Share Price Today - Aether Industries on NSE/BSE", "link": "https://news.google.com/rss/articles/CBMiXkFVX3lxTE5YVWFUSmNPUGtKRF9jY2EtNTNkS1lUVHJYOFgzZWJkY3NrY1lucDJqajdnSjhJTFZuSkZMSjhwSUp3UEs2cDZtNTYzd0YzbEs5NE9IRy1VQzgyWm5YTVE?oc=5", "source": "scanx.trade", "published": "2026-10-30 06:37", "score": 0.0, "label": "Neutral"}, {"symbol": "AETHER", "title": "Aether Industries Q2 FY27: Net profit rises 26% to \u20b968 crore as revenue climbs 24% to \u20b9347 crore", "link": "https://news.google.com/rss/articles/CBMi2wFBVV95cUxNbVVVa0lsV1JvNU1BWnlRVFJSNDQ2Y3l5Z0xwZWdFS2JSTkJPbkxlN2ZfNE1ZZ2hVa0EwMVZ3enhwOGNTQ2VFRC0waFdOckhEaGJ5RDctUGg4UUEyNE9La1BweFVkeWNya2h0SFZ4WVZhZlVLTjl2cXhLaURoTkxSMXd6MHVVTmtYZk90SUx1NmsycU1KMHZKZVItNWRuR29pYy1KWTVEMWdPdGVQcHRQMXFadHJ2TFc0UEFjVGpKM2s1WTJER1RJV3Y4eU1GMmItSDNpR2hBZlRNdkk?oc=5", "source": "Business Upturn", "published": "2026-10-30 06:35", "score": 0.612, "label": "Positive"}, {"symbol": "AETHER", "title": "Aether Industries Q2 FY27 Results: Revenue, EBITDA and PAT", "link": "https://news.google.com/rss/articles/CBMiwwFBVV95cUxNLTdIWDMtbG5YaEVpMVZSemJTMzFndWU5OVVkcDJXdHpCeU9ON2JtcGRmNmJESXByQ3ZWYlh0bDZuWExfOXhtQXVhc2U2eThtZ2psXzFKS2NKS1VXU3lPNG1uNmlfWUE0aUlWVERSdS1RTXpGZkVzZlRfWXhhcDN3dGktb2JwdjJHQUM5YTdTZU43RkZGM3Q4RTZKc09HTzFHTlNmNlZpcWtKSi1Ia0hyMWNUZEUtUy1GWXdFMlVPRWNVQ1E?oc=5", "source": "Kalkine India", "published": "2026-10-30 06:31", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex, Nifty turn lower; broader markets crash as oil tops $116/barrel. What lies ahead?", "link": "https://news.google.com/rss/articles/CBMi2AJBVV95cUxOZEZkOUo3elRXQW41eS1KOUQ0S3NvWFE1OTNHVy04WW1BeHhDV3djcGFrem5PMS10dEVmamxsYjEwYnNJZ1BVbTNwVnQySHpKZ2RPd1NzempiTGp3UTMySEc5d011SkdOYzFXUzlPd0hRLTREMGRmQVZLS0FyNWUwaDNnUm1nSjhISzYtNGNsZEF6VWZVOEc0bjJ5azRJODFKWVZyZldCeUJtbUg4Z19GWEUtWFNQLVA4azNtVkZ6UWNMcDk0ZWdEYmdVS05WQ0RLZElsQ2I1RjVXbUZZaHBaSF9lay1BQzNuMlc5b2o5Uk1oWmNMLU84dmQzRnZub2RXbjVYVlZ4bjVKTVpkaHZLeDRZcjZVNnpocnRTMU00eGQxZHZUbGNGemN3SFl1T1NzbXBCTmdMU3BuYWZMc0pJbmVnOTFCb0dUeXFhRXU3bGNqUjNzamVGQ9IB9AFBVV95cUxOamxtQkl4aWpPQXZ3RXdZblRPa085YklxbVh2ZXczb1BhNGdoLWpOSWF6OEdHTjcydlA4eXlUOHpZMUdNMk45VDNGNXJacFBra25ycnNGQlFJT090el9yc3ZjZ3NYRmhZa0VHX1JEOER2RHQyV3RXRURtUnZrQk5Xci04Wk41X1RTSXhJN0haNmtVNUFpbmVMR0F6VzFPZHliV0dHMU9iR05WTWFPb29QazVvRXk0eVNLb1hfNXlIclJ6YWhfa0ZUc25Xdm5fLWZhWEhHUGk3SHZHNkxKUUpqRm9KdjdyREFhdV8xeXpkMll4aEZk?oc=5", "source": "The Economic Times", "published": "2026-10-30 05:36", "score": -0.34, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex, Nifty Open Volatile; India VIX Rises, Crude Above $116", "link": "https://news.google.com/rss/articles/CBMixgFBVV95cUxQY2daQnV3TThDSXViZGppTlJha2tMZVU4ZEV6Smw5ai13RUxwa3ZoODdGYTYwLS16eW1UdlY3SHVyQjVSLVAxUlVXNmhiTVNSdTFHVXNNYk94VXY2a1Q4V2c0cjluWDNBbkxwZDVfLXdxUTk3aV9xM0hnVElQcERGaDAwaVBRU2JZam8wTVM5WlhsSXJGMXBkWWlIdUZXWEZITzlJRk9LM1pEOE8yYVdETHp4WjRzWklrV0dvak5Pc0ZiaFdlMVE?oc=5", "source": "HDFC Sky", "published": "2026-10-30 05:13", "score": -0.25, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex, Nifty trade flat as IT gains counter crude oil concerns", "link": "https://news.google.com/rss/articles/CBMi1gFBVV95cUxOMUFDOGdnZDc3VlZTRnBlVi1TNmpxRmRKTUtJaVVaYXFIOWJYRklfam54WG1OWkU2MEphUEhmbjlEVHBWUEp4TVhNSFZQN256ZGxjcjdaRUxsd1ZsNjYyc192SnlCNnVBdjJXU3gwdEVBX3AxMllFTXlLbFJOUGlkWnNRRjE2RXJRUUhUMVFraGpnZEFRQlFLUTVnY3lDREJkWXdsZ2l4MVhxNXZxSlUzMllBQy1IRm9ja1lYTUdzRXBqdHhvTkFOVlRJTVR1VFRFMjFEUzVR0gHbAUFVX3lxTFAwZDI2NmhfbDE1RmRhTlk3a0NVMGpWakRNLXpfMVdYQmJGcDRjYWpOTkVNTS0xaWc3MVRCRXVrV0g4YlNIY080RmtqN1QwUEdwRzlXOGdESzFXOUZxalN2RmJRZGh5MGdOUUFEQlQ1XzZOSFUtb2dEemREUFJXTUZYSTJ0eWwtRUpMWTBBa2ZBanpkV19PYkpUNFJFVDk0OWN4cnJTeUw1MjdVTjBDNF9Mamdzc3BrTHM3dXFWZWs3Ujh4ZWREQTZQVlRWYU1raXJpMmpOVDFpUC1vbw?oc=5", "source": "India Today", "published": "2026-10-30 05:07", "score": 0.153, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex, Nifty Rally in Early Trade on IT Buying, Trent Gains", "link": "https://news.google.com/rss/articles/CBMiuAFBVV95cUxOb3NZczFpdm9QMlJjMVdqbW5UTkhINFlJRGNma2FGZE1yQ2p5ODEyRnVab2UydWJ4b3lVV2VPaXlobFFzeEg0Y05YSDdYTXVtYzBDOHdGeXBTX1RKcU9hNENLU19fRmlTRERxN3h0allCVVpuSndxdmJhQXpmWm5obzhGXzNFVTRGNkFDcnFYVVpWQlFqcDVZUk1uX1JzczZYUHpHZkxhUnB6N29YWi1jaVJFZW40aDJu0gG-AUFVX3lxTE1KNVRRdzFtcGR2NzVVTDBWVmI3eWN6TXE1Y0NEeVFEYWp4NUY2SjFETS04X3VfVG5aaWdDN3UzcUpkTElkemk0Vi1aZi1jQ2MyeTZMdnoxb0EwYkhnR2pGc1JGeUFuTDhGY01SbHRHOVg5TjV3YmlEdHRCMm1NaEo1dGE4MUxfRlJhazZpd05KZ25VWjc5RTNoX2VjVEwtZDN4NEJPLUcxVmNFMHpfMzUtMmNDa0JHbHNEZmNGZEE?oc=5", "source": "Deccan Chronicle", "published": "2026-10-30 05:04", "score": 0.807, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex Today Trades Flat | Nifty Below 22,950 | BSE Telecommunication Down 1.7%", "link": "https://news.google.com/rss/articles/CBMi0AFBVV95cUxOcUo1LU9Dd3BjaFU1bVBLSXhidmJfcFJmeDBUWFBaRUFJRF9FVlk0ckhLWTR2ZzJWQ0NIRkhXZUZOQzVHR0VDQjI2NE5IUl9PS0I3UmFSbVVnRVI2V2NoeDdOVGdPYXM2UDdkQTVIa2RMOTAzUzRKRExNTERWbk84eDVsN0RPM3gtcmhENlBhNEcyZEo5UFdoQWZKSkFiUTR1eDltLXpoTFF4VTM4UXUzLVFBSGIwMlVzV0lyTDRrSEFZaGNjTTlLRkp0N1ltbXln?oc=5", "source": "Equitymaster", "published": "2026-10-30 05:01", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock Markets Today: Sensex, Nifty Up on Gains in IT Stocks", "link": "https://news.google.com/rss/articles/CBMiwgFBVV95cUxNRm9wczhmdDJsYW0tSUc3Q3VzRGVzTzZSMzdpR2o2MmJHX21lYTJHQmNUU2w3dElpcEpyUXFBbHZaZHlqRXNidXdpWVZEaWhXWlNaZlM2TTM1RXpWb1BwTUFNOWU4YjNsSnZzazJWbkdwNE5XTDdueHgzWWdwdWlCZkdUekVNdEhDaDhKRzZuUnFiWlNtaDIxd3RwNHFkWXB2andGM0ZwMUJLUHpOSDExLXZndGtjSmdCYzl1UXNLRWZWUdIBxAFBVV95cUxPTmdzMG1GRF93RmdyMFR4SUYzWFFxSUhLei1zLXZSZXZIaXdFY29CWU5zcVFLNHAxMzBJUGhfUWhEMW9STlRBME9aUUstYzZvMV9TaXFUOF9DWk1mM1BOOUVuUXVPMjJTUTI0Y1BRMkN4MDE0cENsV05mbEEteHAtMmR1WWM2TjVGbHNnWmdoTFVNR1Q3OER3WDFjUU1oMkt1VXJfRmt3bTEwWGM5ZmE0bDZRbDVUUUYzYmVEdl9QS04xNUxY?oc=5", "source": "Rediff", "published": "2026-10-30 04:57", "score": 0.649, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty open marginally higher amid rising crude prices, weak global cues", "link": "https://news.google.com/rss/articles/CBMi6AFBVV95cUxQVVdQbFd1TGh2Y1ZldUp4b21nR3VzUFZHSHZUQUw4NlY0M1hBZ2g2NGZDa2RZcmFYNktpeWpMWVpkaExBZVloVUgxaFFXOS1mTkJZcmxsNHVjNGgxWTR6dDNvR0c2UzlnaTM3VGVmakt6OTlzZndtSG5HV2pkc0R4azlLOWVjVm5xLWtFblFSZU44RFEzajdNT2JDbjNvdFFvYlNSV2ppVGQ1Y0VyYmtNNlg1U2IxdlR0Z1ROZmh0OTNmNkVnUlpmSzNDMEp1YmRzRlV4LV8xb3d5anFyRHNVSXoyOFhBNVBE0gHuAUFVX3lxTE9CSG94UGNLcE8yWWR0RzBacVdib2ZORzVDZlhRUkg2V1dkTGROQzFuTTlFRlM0SmRfcjVZRklIRHZ4NDlyNTh3d2NGZEQwSG83RUl6c3pmX2FvdWx4S0RLbWRpT05iN0JFTW5xUnh0Yk1UWUhfMnRBOTBGODJOelRlTUZBU0hJaHlfYUJId1lvSkE0UktENUVjXzY3cnNsbUU0WXoyTzktSHh6REhHZHJwS2NqalVoTGlDZElCSXlSR0tLaDhURXFORE5RRGhMOEIxbFhDaXJBWFNxWWc5dDRWY01VT205MzA0QV9wbVE?oc=5", "source": "bfsi.economictimes.indiatimes.com", "published": "2026-10-30 04:25", "score": -0.557, "label": "Negative"}, {"symbol": "MARKET", "title": "Coal India falls 3% post Q2 results but brokerages upbeat on PSU stock", "link": "https://news.google.com/rss/articles/CBMi0gFBVV95cUxNRWNKZDdGNHlETVRZR2VZMEZOdWJVUXZLbzd1RVRqazNuN0NrV2NUMWJDREZxanNlWElPSHRyRUFsY1lMZVRCTWtIMEZNSDBnd0xxREJtVG9FSFU1NUd4WDd4aGN1X2phV2lIY1pjTDRNMlNHYWxYNUZ5NjdnTVp2YndLa3ZDRjFiaGNvTkdQbm5fVTRvX09IakEzMm1CU0VFSjh6UmI1TjdybFJwc19mNjlwM09wU2RrSmRuTDBjOGhlalItM28wa2trQU5fZFpvOEHSAdcBQVVfeXFMTkVnMXZSY1FaMDlfNURXUTctY2NnMml1SExJZHV6SFNSYlhTVTBmckc5YVhrRTJHYndWMlg2YWo5OXRUUV9yNzgyWk9VVnVpU252WENCLXFQNnlTMEdVeHoxb293N1czYnE4WmwwV1lCZE9zS2VOYm9YSEZ2ZDE3RFlDeFMwRTJMZFFSNFh1X3B5RjZ6ek5fbVdqSHd4S3JOMEkwLUdBRkRMSEJ6SFE2eHFmZFJKejdGZ3Y1aGZHdnBHUjN3UUoyY0RYbmJoZnladHV6RS1xQTQ?oc=5", "source": "Business Standard", "published": "2026-10-30 03:59", "score": -0.202, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex, Nifty may gain 5-8% if external headwinds recede: Baldev Prakash", "link": "https://news.google.com/rss/articles/CBMi2gFBVV95cUxPcTJTc3Vndll3czhydnJSQk8xRzVicWRTQXIxdWVxb1diVGt1R2IxMEEzWkF6d2stU2F0U2o4SlZQSkVUMUJlSEdzMVdCQ05Da2pNaC1TaUJaYW9Za1Jfd2hFNmJpdTNXQ2NXbXR4SXJ2RU1na183RnUtSk5IYmJ2V0lfVWhTMkx5VXFULUNqY2dUVUVqY1BVbXZvRHpmeS01d0lQbWgyUFBqUURPV2tFTG00eWZQNmFxckRYUkxZVF81TGNEaDRMdkRNZ2txWDBYS2taNnJvTEJ5Z9IB3wFBVV95cUxNeVpabmdOVGR1X3M1R21QQlZJbGZ1MzJmdU81a3lGTTdlaVhGLVNwUUUtMF9QRlFJdXlkNG9UMVdiNjhhUmE4bGV6b2tGREdROGV4MXFGVk43NS1faWNZT3dpcUUwR1FXU19uZW5rUHhZUUFzcjdTVzkzTWlWTWZ0eGxYclR0S2t0VWlHcVpacFVjYlFPazNpYVY4TWxkeGQ4U2JTZTFNd0dDTXBiMS1kY0otbXZjbUpONDBhcnFwMFhqdEhfZW1oWDFvdkZRNkxfUktFaW85RjRXQWhSR2ZZ?oc=5", "source": "Business Standard", "published": "2026-10-30 03:34", "score": 0.625, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock market outlook: Crude oil prices to FPI inflows - 8 triggers that could reverse trend in Sensex, Nifty 50", "link": "https://news.google.com/rss/articles/CBMihgJBVV95cUxNOEZaNmc4dnEtRC16Vm5IVHhCd1Y2S19zcjRpVDdSWVZZajg4NjNGMGtyWnE0U2tPbjJUMXVkOFFlT1RERHZWQlBEOHJxWmdITmJPREVXZ1JIaUd3aWNQUTcyMUlqZnpFQWRiZHJLcE5YWmlZOUdlamlzX1NtYUdqczBmamh5Q044dnNPVHZsdEdfTWRmR2pxLUlXeXduUU1laHVpVHhfVmE3OThMWmdwMHdBa2RmbDdVZW82VUc3TGV4TVM1cG85anM5TUpROGVZZlR6MkYzczB4d2YwcU42YWlPeEtmUUw3Tk4wbFBZTDMwUGlSUWtDeHFmRjQyejJLaXhiVmxn0gGLAkFVX3lxTFBIdUVWNXVfYV8zN0tXeE1oZmNpZS1LTk1GNGxzUXRINHQxcWQ3Zy1SOTN1NWRta2tjeG1uQ2NJaE5nTGpzVUlHeXBtaHlaNTM5NWVGUmM4cm10M25WTGplanFSd0F5OUtYWXFGWklQYkpudlIzakczNDNjQi1HNmJYUnRxSTlsVi1xelhNd2h3MU9wSmpyNjcyMTRoLXNpcXBLc1VreklSaS1DNktabHpISXdSSmhpWXRGRm1wQlgzSUk2RVJOZDJTY21vMFdwS0FNZ2psM1NZT0FpbmZsZGQ5VnRlQmx0Q0RWM0FudEk4SEFqRldYOGpsNktPdGxPdU1DZ2hldlRMaEZFOA?oc=5", "source": "Livemint", "published": "2026-10-30 03:00", "score": -0.25, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock Market Today LIVE: GIFT Nifty signals quiet start; Brent crude at $111", "link": "https://news.google.com/rss/articles/CBMirgFBVV95cUxQVkZ2QnRqNU0xM0Y0anVKUjZmQzR4VHE5enhQc0N6WjgxMmhya3pGSzJmUEY5cHgyV09BRm5xUU9vMlU0RW9oM1BxeHBoalg3ZzhldWFJZUgyRlhkWXE5WjZnQzJfU05lSnhRU21jVEhMZ0dhcDNPZk5GWDd6aDNLVFhzNDVXSWJjQWpxTTA0YlZMdU5QcFpfNDVTUWVPVlR3YVB0Ti1pTW5MX19GWlE?oc=5", "source": "IndiaIPO", "published": "2026-10-30 02:31", "score": 0.389, "label": "Positive"}, {"symbol": "MARKET", "title": "Can Sensex, Nifty extend rally on Friday? Here's what market analysts say", "link": "https://news.google.com/rss/articles/CBMi1AFBVV95cUxPWGxjWEFLUmtMVFF2bVBLY0d2a0dvWV95My1ZU25MbTFtS0tIb2czMm5CdV9IV0o0WGMxalUtWGM1RUJkNlBybVcwa2hIZ0pydGJKN3Uxc1BzUDExNklVR1lsTk5jVnVDZ2VZR0pVbElVcFpmRVJfa09nVWhUMXVWWEtDaTFjeE9OQ2lnYTcwQnlLcnVZSlA0MHZud3VQNUthYmlDZzFtNFd6RldnRnhMTVlZREZCWlJuOGtNVE9OYTV6WllHcXBiUTFsVzJPazM5c2ZjWtIB2gFBVV95cUxOM3BKenNkenFoUnlraTJ0WHpzeTdKbWhQako4dWNmMjVva05Qd0tzc2Zyc3J1YTZEN1JSRjA0dS1Yb0p0bXJlVTU1N0tCN3dNTFVXVFFwcFNnOVdGUUZCQ3NoTFk5ODZ6UkJTRHdkOFppdWtiUU9YSmlMMTZpVmdULUYxRnVXdkxmeXNmTFN4d2EyR0JnVGVVNnFvbmJRZ1pmVWhiYTlaYXRnZk1FM0Q5ZXVyWTgtWGozSUpsQmJWZkJCY0JxODV5WXRaZGNDZ2I4X2s2MjU1Nmk3dw?oc=5", "source": "Business Standard", "published": "2026-10-30 02:26", "score": 0.751, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock Market Today: Gift Nifty, Tech Stocks Selloff To Binance Hack; Five Key Factors For Sensex, Nifty 50 On Oct 30", "link": "https://news.google.com/rss/articles/CBMigAJBVV95cUxNdkc2UTMzMXp6a3dsbm55eXlZMzFHdzJ2S2UtYWkzcVdJekZDOHh1RVJaOXFMMlFwdXdWd0lMajR2TUItTTl3cF84b2R2R1NXVmd1dVlta0VpcTFhYWkxUlhnZDYxTHhoeEtYM0JGeDAzQkRlc0FNR1dCNWV1RUw1VUdYa1FkQ09FMWZmM21mN2pwQTVfUVU5ejlScGhzY3F0MjVHY1lTNmZkdHNJRTk5dG0zODcwOTVHRzRqYi1OVE1BUVQwbWdQWkQzWE13ZWZlTmJYUGlHRnhGTWJhWGtQTkJmMExFa0ZURmJzcGtOeWVwWHg4SlNfUnc5TC15eUxT0gGIAkFVX3lxTE5kMVJROUdWQWIwcWlxNGduSHdncXluWWduV1l3a3MtMzRMcXdsUmdzekdkVkVPR1JRNUp3bVVhb19WREFhTzUyYU5BVzRpUDNEZTduODNsb1ZyMDR1OGRybGRhWlRGbzB1Q25iTTRLZGtYMlpBT050bTM0TXBDX1BfN1JOLUttSkd2N0dYT2RGX1dUOTE5Tk1aOVVSRXlmd2tmaUVTUTczcTlrVTU0QnEtSHhJdjhDa1Y5R2R0aHlJQVhpNkg5bC1FcWtOU09KN0FuY3pmZW1RcWplZ0toNUZWYXdMZGx4aGJBZXpidlF6MXhnWGpmaHEwUTZVYVVlUE1VM3FBanFvZg?oc=5", "source": "NDTV Profit", "published": "2026-10-30 01:44", "score": 0.807, "label": "Positive"}, {"symbol": "THANGAMAYL", "title": "Thangamayil FY26 Net Profit Jumps 196% to \u20b935,165 Lakhs", "link": "https://news.google.com/rss/articles/CBMi8AFBVV95cUxNZWQxVFZva3o0cms1Y2N2ZmRJMnk0TmZzTTdLUWVuZE8taXVteEgyeDhHQi1wYUIyU0RGb3J5QWFxd2pLSTJILUVSOEZVZTBDbExkVkMtT0tiNjhGOGpubU1KQ25LQ1ZFUXkyUDZmY0FIdWZBSm96cm1vZ3R3VEtQUHFKLTBZM18tZmx4NDhNRWM2OURvX2xQQXJncWtod1ZoR3ZoV3A4bldUSkxXMU8xNlEzU2tMeWYxeHMwYk5LeVlYQ3hJeGVqMkdNYlRIQTZnUXpxTk5xZzA0aGZqNGVId0pnbTRLd3RJNWZZcWQ3azQ?oc=5", "source": "scanx.trade", "published": "2026-10-30 01:17", "score": 0.66, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock market outlook today, 30 Oct: Sensex, Nifty prediction - DJIA, S&amp;P, NASDAQ, GIFT Nifty, Kospi, Nikkei, Taiwan cues", "link": "https://news.google.com/rss/articles/CBMihAJBVV95cUxNU0lLTXdXRXlnWnktM1lpdVdQMEZ1Q0ltbHlFQlZOa1pRM09LcGlnYTRubzNDcks4N21ZaGdEV3ZpRFV0N1FhT3htZkM5djl3WngtREVSVkdhbWkzWFQzNjJQN2MwZDVYaXQ3Q3pPOUxLaDlVUFF5aEFzWkY2TU1jRjloa19jNTBBMHZMYkZGVExUMlV5aXlXaVV6M3Z4QV9WaDF2ekFRMlg4dXV1aE1TMWR5bHlUUi1XODB1MHFraXVKLXZGOXJvNTdmRnJNNmY5WU1JSXJ1dXpVTjdXR2NyVUpVSUdYbFFqS0gybXp5MG5tSDdhWEpTb1RVMkJlZ29ZN09WNdIBigJBVV95cUxQQ3pIRzJQZmY1VXpnc0Nra014TklOZ0lvNkhtZUJ0UFJiQmtZQ090aUpZTlFfTWdMMW9HT1U1UVJEU2NUcVFUUmtyb0E2emhPa1hmMGd6eDYyMWk4R3JURTFVYThqZzNBS3lyNC1zcTRyajNKcWF0d213aWd2Y1J3aGRNMVlqRDhOaUZpNktDcmNSRFlpMnVVU1NOTlV3TTMtX2tLSkNyMWNrVWtwd29sQkxxTkUxYll2X1FoOWJVY2ZTcUVBUXRMVGVTNnY5UGZlNVZpRTQ1bnhUdzBkM1BPTjl4dUxfS2FRd3NzZUpJMF9CWW44QXRWaVFuaW02M29sZlBCMThPRWlfUQ?oc=5", "source": "Livemint", "published": "2026-10-30 01:14", "score": 0.842, "label": "Positive"}, {"symbol": "SYRMA", "title": "Jai Corp Ltd. Share Price, Stock Price - NSE/BSE Live", "link": "https://news.google.com/rss/articles/CBMiekFVX3lxTE16eHJNMjhIb2ZJcnJieF9VVVVlZUhCZUNhTVF2OGdyazlxR3FwNVBPN2pJR0ZVcC0yUWZsS2k1TXdndkhMbDUwem5XdzdIYzdvMkpHVXRfellWeUxPeGFzbjNvY1l6ZkFfbkhmcWdfX0w4UnRyZmVlX0RR?oc=5", "source": "NDTV Profit", "published": "2026-10-30 00:25", "score": 0.0, "label": "Neutral"}, {"symbol": "AETHER", "title": "Ather Energy Share Price Today, Ather Energy Stock Price Live NSE/BSE Updates | The Economic Times", "link": "https://news.google.com/rss/articles/CBMiigFBVV95cUxNMmpPVXcxeVFIRHF1aHV6dFRLVnhXV3djOWRQN2tuMmxVTnhDeVNJSnFoV2ZscmFoaEtaWXhCT0tabGNHdVhlOV8zcG45eTJrYS04ek9hSlNlMEZPYlpyeS1pbXNqbjlVVklKeEFrX1R6OUEzXzhRdjNneFZzbEFFMjc4MmZ4T3dSMnc?oc=5", "source": "The Economic Times", "published": "2026-10-30 00:10", "score": 0.494, "label": "Positive"}, {"symbol": "AETHER", "title": "NAVINFLUOR Share Price Today - Navin Fluorine International on NSE/BSE", "link": "https://news.google.com/rss/articles/CBMibEFVX3lxTE5KVkRzcU5uaGJqRnktQVNCenZKQ1NlZERDM2duMTh3ZVBRWGRheFQxdkdZdzJoZHozc2dpcFhmUUl3Mmg1M1IwY3diN3hNMjBnVTVyRG1VOVdzOEdlVzlaY2taamYyRnYtNTJoQQ?oc=5", "source": "scanx.trade", "published": "2026-10-29 18:01", "score": 0.0, "label": "Neutral"}, {"symbol": "SYRMA", "title": "ZF Commercial Vehicle Control Systems India Share Price, Stock Price - NSE/BSE Live", "link": "https://news.google.com/rss/articles/CBMipAFBVV95cUxQaGJ5UUduMmFWUzQxODJRNUFmT0hGMWE5Ykx6RXRJRFRRMGowSGJ2eE5INlhVYVU2OENDblNfcUFlRUlHNzZBRlFyQlZ6dmxtX1NXUjE4dUxEOHpkM1U2NXM3dl9jdzZsU2FUTnQ3SFRqWUNxOXl4cUV1NzllM296YVBMQlktaHQ3V21QQktRWEp4Vm9xbkhjZ0Y2TEY1SzVDVTVkZw?oc=5", "source": "NDTV Profit", "published": "2026-10-29 17:53", "score": 0.0, "label": "Neutral"}, {"symbol": "AEROFLEX", "title": "Aeroflex Industries (NSE:AEROFLEX) Q2 FY27 Results and Hyd-Air Amalgamation", "link": "https://news.google.com/rss/articles/CBMi8AFBVV95cUxNVzBvb2wxcTMxV1h4Y0l6T01NR1p3blBHcUxEN1pKQVNxVTZXQWFmWmdyMDFMaHRxRERqNkJLMjQ4WGJzNENnUklwaUJBMHVLMmFodmdmWXlPLTdhOEpZSGJwLU9ON1NmUks1VUE5cnNYUHYzQ0hrb1pveURwTU9yd0J3WUMwSmJkWmEyMEZrMUhNcVBCZWRpMV9HSFpPdVFKV0xXOU9BTFB5cWVVbTlFdGU3YmY3cHQtX3M1UTVFYVMwZHg5a3djc09lY09PTWt5UzdRMnJEUF94U0N6ZlZ3X2doc3hmSXFMRGxiZjA5SDQ?oc=5", "source": "Kalkine India", "published": "2026-10-29 15:28", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Benchmarks rise over 1% on positive Q2 earnings, easing crude prices", "link": "https://news.google.com/rss/articles/CBMi0AFBVV95cUxQN2x1Nk5sek1aeDluWGNMSnEwREx2</t>
+          <t>"src": "bhavcopy"}}, "CPPLUS": {"2026-10-29": {"open": 3985.0, "close": 3951.7, "src": "yahoo"}, "2026-10-30": {"open": 3932.1, "close": 3811.5, "src": "bhavcopy"}}, "THANGAMAYL": {"2026-10-29": {"open": 4681.0, "close": 4630.5, "src": "yahoo"}, "2026-10-30": {"open": 4620.0, "close": 4455.0, "src": "bhavcopy"}}, "KIRLOSENG": {"2026-10-29": {"open": 1907.3, "close": 1890.3, "src": "yahoo"}, "2026-10-30": {"open": 1884.0, "close": 1796.1, "src": "bhavcopy"}}, "SMLMAH": {"2026-10-29": {"open": 4770.5, "close": 4848.0, "src": "yahoo"}, "2026-10-30": {"open": 4918.0, "close": 4724.5, "src": "bhavcopy"}}, "AETHER": {"2026-10-29": {"open": 1590.0, "close": 1581.0, "src": "yahoo"}, "2026-10-30": {"open": 1597.4, "close": 1616.2, "src": "bhavcopy"}}, "SBC": {"2026-10-29": {"open": 65.39, "close": 66.52, "src": "yahoo"}, "2026-10-30": {"open": 67.05, "close": 66.15, "src": "bhavcopy"}}, "SYRMA": {"2026-10-29": {"open": 1563.0, "close": 1669.0, "src": "yahoo"}, "2026-10-30": {"open": 1675.0, "close": 1625.3, "src": "bhavcopy"}}, "TDPOWERSYS": {"2026-10-29": {"open": 719.8, "close": 719.45, "src": "yahoo"}, "2026-10-30": {"open": 705.0, "close": 713.9, "src": "bhavcopy"}}, "RATNAVEER": {"2026-10-29": {"open": 345.0, "close": 352.85, "src": "yahoo"}, "2026-10-30": {"open": 354.2, "close": 360.25, "src": "bhavcopy"}}, "NIFTY50": {"2026-10-29": {"open": 22690.65, "close": 22936.75, "src": "yahoo"}, "2026-10-30": {"open": 22964.5, "close": 23053.1, "src": "bhavcopy"}}}, "entry_override": {}, "news": {"fetched": "2026-10-30 18:08", "days": 7, "items": [{"symbol": "MARKET", "title": "Markets hit 6-month high in Oct on IT rally, Jio Platforms IPO frenzy", "link": "https://news.google.com/rss/articles/CBMi0AFBVV95cUxOdXZHZEdOTVJWWHBOLXZXb2NuTDlvY1RUMk5Ld2ozdTZ5UnRubVkyTk11YlQ2WkVZMmhncnBsQ0prdHlQbHUtQjlDMlNlVGdwSmVyMFdjWWNqc3lLalpvek9Bd2d5MnFHZTJRM0p5TlMwdmRicFVmMzcwb2NYZkpFRXM5czY3S2hMSnhyb2lMX2hQeFZ3ODNZckk3Nkk0MlM4d2s1U1hBVGxhOVdHYS1oamhGMFVCYWtuUm95WjM1M2N4MG92M3lhcXBJYjVlM0920gHWAUFVX3lxTE03MVNYWWtyQjllRDNNR2VtWHZrNVl3aHYyTnBWeS1tc1Y4Z2pzRWU2c0EyNUprd3ZVM0tEalJnUi15SUVsYm5kNzNOZzloRlZ5Mld6NWwzNVhObUR5WC1GUnFZTmdoWjlTY2M3M3J0YXhDR1hfbXFMM3UtRVZVcWtad1RxaWlEY0FWVFRLTVdXZlduWkNzN3lVMTU3akYyZUlUUmduVEZHU2NROGg1TFBLYlkycVY1M01iSG1qR3ZOaWZMR2ZDdlBFdWNETWVfU19jNTY2TWc?oc=5", "source": "Business Standard", "published": "2026-10-30 17:26", "score": 0.226, "label": "Positive"}, {"symbol": "SYRMA", "title": "Syrma SGS reports best-ever quarter; Q2 revenue up 73% to Rs 1,999.5 crore", "link": "https://news.google.com/rss/articles/CBMi4wFBVV95cUxOX1lzeEswS005dk5yZEl6Z0pvX1VQbnp2RzBnR3JvdFVwanI5V2lFdHlTcE02Tm14Mzg5MFN0blpUcm54YnNjY3dsSVJSSEpLaXQ3ZHlocnpLYVpIVVo2NkNxRVVEZTFmT29UOHFIbmNxS1VlUnN0SW1oMXl3NzZyUGpBU29HVWd3c2dNVGFhNWtxNjMyeHlsTEc3NmxmY3Q5LUF3TE9GRkpoZFByd2ZEeG1fb2liWkJaRUMwUTFiZWptOWFXZXJIeUxKQzg1ckpoY0NIUzhtVXNqMHZvS1VJRWtnUdIB6AFBVV95cUxQNWpYOU5EY3MweXZaRE53azhMcEpJRG8wNzlVcm1DY0xiZjhNa2JQaGF5bFlad19ZNGpQcGZiR3RQSk1hNnZkdEllZWdKRVdJZnZhb3dwZzgtY1dfVklxc0k3NzVPQ1h1VElTQkxSbGNMZThoNDJaNG5DQV9kbGY2U0ctaTVBZXc1cTM2dkVzaWc1NzVLYXo5WWJVcWhVdUpXS2pzRS1LT3VDT3B5Ym5SNjNlbk5CcHJaaWdiOUNZWGxNOHExX0lLLWo4S2c0eF9DOGotTkZPdzR4R1lYN0otRURMdXBRRi1N?oc=5", "source": "The Economic Times", "published": "2026-10-30 16:35", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex Gains 308 Points, Nifty Reclaims 23,000 as IT and Pharma Stocks Lead Recovery", "link": "https://news.google.com/rss/articles/CBMirwFBVV95cUxPNlo0QnpXclVoY0VJMFg4c2FMUlRzOGpTcElSVzNscEh2Q18zdXpwZXIyVjh3bzAzZVNoNk1pSlNweFJ3TW1BMDVidmJLZzV0cU9KQnZYcjhjZ2VHQmtjUGlnRllmT3QydWdneklFSVQzdWlVdG5leVZCdEZ4NHdMOTZUX0ZCQ3daaXhSQWV4RGphRnJKMkJ2X0VSNlB2XzJIaTk5TE1PejdrOTZzX2N3?oc=5", "source": "The Indian Awaaz", "published": "2026-10-30 16:07", "score": 0.649, "label": "Positive"}, {"symbol": "MARKET", "title": "Indian Shares Snap Two-Month Losing Streak, Nifty And Sensex Gain In October", "link": "https://news.google.com/rss/articles/CBMizAFBVV95cUxOWWxJcWJZM0t1RFdIV0ZTRkVWZzVHZkluTlB1aFZmVC1KeUhaSS15eDN6QnFHb2hBYy1HdHRQV3Rjb0xOOUpPMlBZRUpEcGtUaFA4YjNISVpLN0NHZVVqNElaXzFvTV9KUTJWVHJiaFlkbXpLTEpiNDdLd2VkNEU5bWQxdnVZUThmVkNseGVEa1VpQnhhUEN4X1hYY2ZGcGNWb25LdzFOVzhNU0xvVWNITjNnRHJYekQxNm10ODVTTFVtRVhGSEFxdEluLWQ?oc=5", "source": "TradingView", "published": "2026-10-30 16:01", "score": 0.361, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex Gains 308 Points, Nifty Closes Above 23,000 as IT and Pharma Stocks Lead Rally", "link": "https://news.google.com/rss/articles/CBMisgFBVV95cUxPWndrT0xmdkJxeDluWUM1cjJYX2Z2VUZyQXlqMVZzZkMyUzFXQTJsQ2JlMzU2MUJzejJfLU0yZzNlRUFELTN2dWozZGRJcXVlUzlyZ3RwSlctcUJGSkpmcGRxUDhWRGxuRUt1V1cyY1A5SG1GWnBHb0s0VDE5Vk1FcGtDczFsSDNqR29vTENzTjRkemV6M1AtcnY3aXdGdW9qUGZBb2NSd2dZTTh2UW1VcFdn?oc=5", "source": "INDIA New England News", "published": "2026-10-30 15:13", "score": 0.807, "label": "Positive"}, {"symbol": "SYRMA", "title": "Syrma SGS Q2 results: Profit nearly doubles to \u20b9117 crore, revenue jumps 74%", "link": "https://news.google.com/rss/articles/CBMirAFBVV95cUxQWWVNajdfcWthd1FGS3dENzdIeWltVzdfWTRueHBPYlFWSEs4MHNnOW9HQnVWODIxTENyb21PblA5Y3d2Ym4zeVkza29VZ0VQSENCb3dhUVQyN1N4WFlGWnNTaUt1czBRWl9NTy01UmU0bExnQXZKMUhpeW8yUU9GT0tPbDFpeHh6em5GZzNZNzZTYUFuSkR6RlFwS0Fwcy1SQjZLSHdDdTRFaTZm0gGsAUFVX3lxTFBZZU1qN19xa2F3UUZLd0Q3N0h5aW1XN19ZNG54cE9iUVZISzgwc2c5b0dCdVY4MjFMQ3JvbU9uUDljd3ZibjN5WTNrb1VnRVBIQ0Jvd2FRVDI3U3hYWUZac1NpS3VzMFFaX01PLTVSZTRsTGdBdkoxSGl5bzJRT0ZPS09sMWl4eHp6bkZnM1k3NlNhQW5KRHpGUXBLQXBzLVJCNktId0N1NEVpNmY?oc=5", "source": "CNBC TV18", "published": "2026-10-30 13:51", "score": 0.66, "label": "Positive"}, {"symbol": "AETHER", "title": "Aether Industries (NSE:AETHER): What Do Aether Industries\u2019 September-Quarter Results Show?", "link": "https://news.google.com/rss/articles/CBMixgFBVV95cUxNb3lGcXBYMGhGTkhHcVNBUFRETjZsYWl5eDRicWZEU0hTLVo1bHB1UDFFNHRPa3NsaGM1MzlmU0ptWnUtNzJwTWVCTDB2RXU3cWVvblI1UjZhVkZEb3pxVXJnUVlvamRDaTRUcVh5S05ubGhydDhkU1hNR2hOLVZldzhfbktjM0VJU3V4TTBKaS1ycUtvX2pQem4ycUNuN1NmUHU5cTlwLTctT3RQR0ZmZlVaSTNKcW9veHUyQVh2Nmx1dlFPRWc?oc=5", "source": "Kalkine India", "published": "2026-10-30 12:34", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Stock markets rise for 2nd session; Sensex gains 300 points on buying in IT stocks", "link": "https://news.google.com/rss/articles/CBMiwwFBVV95cUxNNHNJTGVrRmdOU1FVSGlwTFhRazBPeXZpUW1pc0MxOWxtc0FHT1pLZ2NiUF9XdTRnOV9vQlE1bGttMll3cndvLUVVTU5keHBhd09TNDJRSTRFNnBOUXVmaHFMYlhKZDUxYVpyanlsRDJWM2Jnc1EybzhJUU4xOV9LbWRPRHF4M2N0clRqeTY3dVQzMXdtcFQydkVyYjR5RkJYUEN6Z3lGLVNKSURzSmkxXzNrSjRXLThsSTNWQjE2aVY1R0HSAccBQVVfeXFMUEhJTURkQzA5dm1saFZIZjBlOTFFRUQ3dXZuaFd5MndSSUhNUGc2R2VBXzJHRWVObnBJdDVlY3FKVmRnbGlla25hSFhjb09fYktLRWY1Vm83TExtQkJlLVNvTkRzM0xfR1NxdTZUMUpMNHdCakZoX29GZ2hiUk1VNE9vMEdtTzZNXzU5ZWltdDZnSFFVY0R1aHRFeDRxR3Q1bEJhcEFTX2VSOFE1TzZiOVNpRjZyODdQMUN3aV9NSkxocDlWbU1zQQ?oc=5", "source": "The Tribune", "published": "2026-10-30 12:12", "score": 0.382, "label": "Positive"}, {"symbol": "MARKET", "title": "Rupee gains 33 paise as dollar weakens, Sensex and Nifty end higher", "link": "https://news.google.com/rss/articles/CBMi5wFBVV95cUxPbU9TVlhwU0RfZ2RaSWlHVzZ6aGIwa2RlSjR3OWpJOV9hNUdpQzh2R05ueGxaVVBMR1RtTlVqMU1Cd0Vwd0FJOVpDRGVZOWRlQzRtWEM5NUVOX2J6MjdlNTNfSUtzSnlQek1VQjRQZm1ocVVZVzdpTmJTb2tKajBzeWlSbjF1dzBwN0xMT2swckJfUlAwM3NqM21uN2ZSTU01bUl4S0M1YjZ6RFNTY0xPZDB5ZmxhRzVVTURZV1dmLWg1S1d4ZGRCQVF6RWV3MUh1a0lFd1VaMjdBMlk1aFdva1NnWHFLNE3SAewBQVVfeXFMUFpQa1Boc2xFMXp6VExQenhIdVBMb2poRHpCTk0xbWRuSmJxQWJIb0VGcFd4cHJuUDRUY0pTZTk0ZnBSOG1uNEhHRWM1a0lQek5RQ0RYVzR1WURocFg0eHJRQTdXOGpEWjJaSWczYnNVTlljUDZTYzVPakppc1g5azNhVmtRaGRrT29hcHFmczBVVE1BSzZiaVpocUppYmgyenJ5UnEyclBMN045ajFDQ1lkZ0dyNlRlLUo1UklSVHJIdEF6Qzg5Z21uS05DdVRIUmtFSFB1ajJkMHVaeWxMdUVCakdQTEFSU0toeUg?oc=5", "source": "The Times of India", "published": "2026-10-30 12:05", "score": 0.459, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty End Higher as IT and Pharma Stocks Lead Gains; Broader Markets Remain Weak", "link": "https://news.google.com/rss/articles/CBMiyAFBVV95cUxQOXFXLU9kY2FWQXc3dUJDdmZmZk9MYm9LNzFrclM5QWZNdklOSW42ZmwxMl9CVkdWYmJSZ3liYktscXZWeE8tc2NGNVVVSjNKdTVZRXkzSWlRWXpkcGhSQnlsRTYtZnI1Q2tvZkk5a1dxV0J2WmdwLVIybDg3MndlOFlwcmpXQzF1YjlCTHdWRnRBTktCbzVNMUFVODk4VFRRWmZYUGNOWE1QZmRGakZYUVFMaUJ4Zmxjc2pMM3JONDJKeDIyVHNUVg?oc=5", "source": "Business News This Week", "published": "2026-10-30 11:43", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Share Market Today: Nifty 50, Bank Nifty | Oct 30, 2026", "link": "https://news.google.com/rss/articles/CBMivgFBVV95cUxPY25ELUgtdk81RlJKeUYxeUE5TGpwQnVBcFJzVHZydWE4UmN2cmhTMDVONnhUeEg5ejBNd21IcU5nTWxtRmstMjl6Yks2TE1ZcHhMQVo0NVMwUGZrbkd0UFltSkE0bWdxMzlnV3NCZkhrelhfbTlVT0NadjJOZjYxejFobXhuT0dnNHlFYTduRXZNSlRJRFRrRVR3N0pBRFRaMlIxYVRZUmdIZDJHUmhFbjBScGdwMG5GNEdaS093?oc=5", "source": "Liquide Blog", "published": "2026-10-30 11:26", "score": 0.66, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock market today: Sensex, Nifty extend gains for second day as IT, pharma stocks lead rally", "link": "https://news.google.com/rss/articles/CBMitwFBVV95cUxNR3JxNnMzYkh6T2dLQjV3cEN0VzV3NGxfS3F6a0FWOTlFd0RYOS1Da200aWNibW1hbnFWTG0yOVBjMEZfSWU0bDZlUldYZEl5YW5pZFdoVi03U1Z0VUdQajh1eHhQcTlMV0FzVzBzNjg5Z3BvOUhKcG1nZ2FkeXVKbEZWVk5oa2U2bmhSUjZsOHVacGJxejlYdmtEOGhNbi1fT2pKeWZtaEttVkltR0lfYVZjeDc1N0E?oc=5", "source": "IBTimes India", "published": "2026-10-30 11:25", "score": 0.84, "label": "Positive"}, {"symbol": "MARKET", "title": "Green Energy Stocks Decline Despite Sensex Gaining 0.4% On October 30", "link": "https://news.google.com/rss/articles/CBMiqAFBVV95cUxQRmduc0NPQlNZdUdVRXMzR1R0WV91RjJCTzZvSTRWMHRxcW1MdXc2UF9nZnlSbnhkOTg4NXljdkNrYXE3UDV2WldYQ3lkS1pzV1duNVBkMm80SE5BRVh1MkdabzhfQ1lDZlROc3EzRHdEeV9GdG1UWkFEUGdTOXFsTklGLXFOTmlwSExzMnZSM3NxUVdydzg5Q2w3U29DUHNjRHNCRVRBNTc?oc=5", "source": "SolarQuarter", "published": "2026-10-30 11:24", "score": -0.428, "label": "Negative"}, {"symbol": "MARKET", "title": "Markets rally for 2nd day amid buying in IT firms, earnings-driven demand in Trent", "link": "https://news.google.com/rss/articles/CBMirgFBVV95cUxQMXVXZngtY2JfMzFTOVlMdVdLMmIyckJEZ28xbGI3djF0cXE3YVItSDk3WFRFRWx1QnJCRjR2NGdWLTAwNlJYZ0kyaFZ1VGd6STA2bVFRRVRWRjRla0VTZk1uR21XdlVLYUltMW1tSEV3TUdiR0dheXh4clR1a0Rhd25UbFlrNV9DVVdIc1QyRVJIVlR0OXdOaW0wUHNVOEFyOG1Vd1BNVUdVZ1NBM0HSAa4BQVVfeXFMUDF1V2Z4LWNiXzMxUzlZTHVXSzJiMnJCRGdvMWxiN3YxdHFxN2FSLUg5N1hURUVsdUJyQkY0djRnVi0wMDZSWGdJMmhWdVRnekkwNm1RUUVUVkY0ZWtFU2ZNbkdtV3ZVS2FJbTFtbUhFd01HYkdHYXl4eHJUdWtEYXduVGxZazVfQ1VXSHNUMkVSSFZUdDl3TmltMFBzVThBcjhtVXdQTVVHVWdTQTNB?oc=5", "source": "OrissaPOST", "published": "2026-10-30 11:17", "score": 0.361, "label": "Positive"}, {"symbol": "SYRMA", "title": "Diwali 2026 Top Stocks To Buy: Apollo Hospitals, GE Vernova, TARIL, TD Power, Jindal Steel, others; top 10 picks, target", "link": "https://news.google.com/rss/articles/CBMikwJBVV95cUxOejZuNVZHYUg3QlloRzQzYXBzbjR3OFdESEFXaU1ZaGg4ZU1YMkExbUpVNHZ0S1JCUEZQNmRKVXVraTVxNjAxcnc2MWhPamFkclpDVGNEZDlILWhBdmtzQy16RHVJaW1wQjdtbmN1TUVUZDBudlMtNnNfcXdWMEV1ZWphaElvTUdTeTBsNDFYbEs3UEFHMVMySzZCVEIzeUYwR3Y3bWdPQmVfcHBlOG84Zkg0aGxLMmtLVDhzQms1MUNnWDRXYmFjbnZWQzU0SC1Oci1JXzBjbnQ0UTBJU1l1MWJ4MTd4TV9NM0FVSC1LRV80c1Q4QllyS01NOWFHVUZpMXdkdEpSNmt0aEg4WVl4V2Fwc9IBmAJBVV95cUxPQjJxY1ZBR21RVFNpWE1vR0pkOVA5Z0RUUmFZRDZ4dS16TWpjdzFzcjM0QmQ3bVkxWV9fWmdIdXIzdzA3MFZHUXNIZm9sdjUtd3cyUl82V1RKRTlZVHBMQjVNeFdXWmp6U293TS1WYnpiVzJhZlV0UVZGbTJ6WldTVC03bmhmYlhobTJJNlRUd2VucW1vRlpPRElMelZneGJGdzZLWmRVMWxSd3MwbXpKVXBEQkdMVEdsNWR5c0NXT3dGRVlUSEFGZ3licnVTbllGbnZ6VFBCNGxmZk01cWJjcVpqQW1TZGlmNkE4RUlwdDVyRDhoZUJmaTNLNVpBQ3JRTklFX2dkM2lIcnUxNXlxZnBCemtMMThQ?oc=5", "source": "Livemint", "published": "2026-10-30 11:14", "score": 0.66, "label": "Positive"}, {"symbol": "MARKET", "title": "Indian Equities Rally on IT Sector Strength, Trent Earnings", "link": "https://news.google.com/rss/articles/CBMivgFBVV95cUxNUjdNY3FGSXVhZWNuMFI2cTU0Tk1HbjdRNHZ0NEJoOFBQTWNCNFU5S3ZfZzlKYlJYOHpid0twc3ZkUzRyMmE4VnJjUGJybldSTWlYRUl0QkNJRVVGSFdNNWRYWWtjYVVyNG94cVc0bGJhVGo0bmhqbFd3MklsSEh1b3h3YzhQY05QLWhzUTlzaUpsSUZyRFZiUG1KNVBIVEI0SUhneTZDRTJ2Nm5pUGJGR2J1cC1VRWhmVlEtQUx30gHAAUFVX3lxTFB3aVc1Wlo2ZUlnQkk5akNVSHU4ZmNjTlFEdEtOekpRYzFTZnFKZVlNRHAxSm5WUGlWMmhySGs4bzRnbGRpempPWU9WdG1FbXpKUlpzajNIVV9xYlZSYURwcFEtYS1yVWMzRkxOdmZnRTJjNU43ZnJNZFZpR0hMenJTU3hPZDVCa19FbGxaWUU5Z01kbklXaGZDSHVyYjVKQzRyamxydExyM1RkN0kwR2NRVnFIdFJOSkZ3ek1pZElYcA?oc=5", "source": "Rediff", "published": "2026-10-30 11:07", "score": 0.735, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex Rises Over 300 Points, Nifty Closes Above 23,050; IT, Pharma Stocks Lead Market Gains", "link": "https://news.google.com/rss/articles/CBMi8wFBVV95cUxNMFMwbG5wbEljemRIR3lwN192YnVpZm5OZkdZSV9ORzV1S014VXNwZ05lV2hEY0tlUXhfUW9mbmVxeWpsNU9ia2UyMlJRaGJkM2NrQ0pxYzVSbjQwLThkME5jRG5rb1FHTXQ5ZVNKUTB3Tnk4eTdYVXFiS2J3NENxM0lDTEhTZXNPSnlHVzBrLWhXUnh1MVROWkpXMFpSLUpBNkx4djUtck1RYk5PSER3cGR3UTd0d0lhWmNxRk40c1l0TGs1ckVsSGZTRHdjRVFCa0FIM1hlaVVuV1FzV1lhRHJHYVB4N3BQRmZ3T1JTbndoRjjSAfgBQVVfeXFMT0R4SzdXUXU1WldnR2dzSVpmTGdKdG9aNkhhemNHRTA1MVVfMmM0SVJoU3V0VWFIamw5ZDFibG5UR01RNlFjMHVvVXdjNUxwOGlGOUNXXy1tUmhSUjl5aFc1VmN5Mm8wRUlhNnBVTzhHbjZWUFA1QkJKX2xPV0pwV0NYRmVuNVM2Um1tSW9sSl8tVHZBZTI3WXNvNFlzT2M3dzRUTjE4d2F3RmhLUlZlZV9PenZFYW9kOW9xbjFJa0N5UkgzQ1pLRUk0bkR6dXA2UEFVS21mcFRWeWpVVGtwT01xYjVRd1duOGhHbW0ycm0yVXB4R0hHVWk?oc=5", "source": "Times Now", "published": "2026-10-30 11:00", "score": 0.649, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex and Nifty Gain Amid Mixed Sector Performance; Large Caps Lead Market Rally", "link": "https://news.google.com/rss/articles/CBMi1gFBVV95cUxNN0pVM1RiS0dxNkFVVTdVaUQxbTFOaHp2Z2x0N014TTRPcFpjZWs4YzhLb0RENWZ0RkcySVFza3JZU2hlWDRSNzhlajBLUlQzZVJQUWxpUy03RzkxSGFCZHZqMU0zaG1vOWVTYTdfNlNDaGpQR0VHemlDd2EzbFNQclNneTZUTjhpcC1JQXJJN0tNYzl0WjNHUC1SeHN3Vk4yOHJXSWVRaFdYVDZRWGRrU3hkX05LQUlha0p0RnlrblpfRjZ4Z0ZlMjR4VHB3ZmY4U1QwUnJR?oc=5", "source": "MarketsMojo", "published": "2026-10-30 10:59", "score": 0.796, "label": "Positive"}, {"symbol": "MARKET", "title": "Market wrap: Shriram Finance, Nestle India, Trent, InterGlobe top gainers and losers on Nifty and Sensex", "link": "https://news.google.com/rss/articles/CBMikgJBVV95cUxPOWtiUzAzVWw5Mk40VlV4WkZoSUJoOW5NNmZndTFSOEVMdHFkaGk3WHNRTFFlSzl1OHJ0VmVyalI5YkxsTGRWRVNoc0JPSXZ6RnpSMGxWcFhFNHFPdG9RWUJYYk1ULWlTV282cE5ES0YxWmVqNmUyaXE0d3RjQVA4UVFySzNreEZ3WWNmS0Nldi1RUDFSNDBMNWhYWE8zbW9uUEFaYTZlZTVUTHpwSVBWeTRpQjRBUmRmdjVSMXFCbE9kVy1tU3FtazFJaE0wUVJYVlNVYVJHSDEzTGpqU2FxZFdOQjY5ZFlxOHNEUnFKNnd5SC03ZDE2ZmR3YjdkS2U2cEFMSEw0dVkteHo2N29PMHZB0gGXAkFVX3lxTE96bkJGNFNzdEVsbWxGQzJDYjkwbkRtNjVjZnR5MV9TQlB5cHR4a2o2eVBhVW83T09YTUZ3dkdYTnVRVmlPaG9aNXVCbE9tZ0hFalhVamZoN2VGc3VNU01FZGVxSWtELWZhaXEwYTRjdUlhQzR5OGw5WW9ZWjhzNXVRYzViYV9oZ3NuUVlGbFNfQ3lHQkE1ci10OTBjRkNqR1hhZXk0WVAxZUVYSGhwUFpIcDhiQmZxYWZuODM2eEhFUXQ3ZEFsME8wdVZ0OVB3NVJoWU1iV25tVWdJT1FINklXT2JhTXM2NDFsT1JFVXphUUZLOTZ2OHVLejdOTzRsdkc0TkxVeGctbkwtVVlxUDRhb1pJVDJWMA?oc=5", "source": "The Economic Times", "published": "2026-10-30 10:56", "score": 0.026, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex, Nifty Rise; IT &amp; Pharma Lift Markets as Midcaps Slide", "link": "https://news.google.com/rss/articles/CBMisgFBVV95cUxOajFHdFZlZGo5cUk0dWJ3V1E4c2dCUFlBVFVMZV8wYklSQzVtUEJKRDZVSFhIdHRIUDUyZGlHc1ZWVC12bGwzMTFtSEpqdWdpYmowZmRqQ2ttVWVuaDRVOTh4b05lUVBQR2JYeUNjWDRjcjRMWExJSEFhV2lKRFRoUUVmaWFtSDBYdjBldjI2NWdYUlBHZXpUX1FRVXpwaXZucGpuQWlRLWxrdkJoWmRRblNR?oc=5", "source": "HDFC Sky", "published": "2026-10-30 10:53", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Closing Bell: Sensex Gains 300 Points, Nifty Reclaims 23,000 Mark as IT Stocks a Lead Rally", "link": "https://news.google.com/rss/articles/CBMi0wFBVV95cUxNWmRkUkxrWFBGcW9fcUVPUnhZSWpZNUhEUXI2ZXljYkVWSTM3ZWJmdl9EeTZwOEktUlF1a0tod0VsR1pLOUlrODNydzdCTXhxU3ZsNzBXTUkydlkteG9uQVp5dmxNM2lfcG04ZUREZV9GQTg3NWxKd0F5cUFxX0Vzd2hZV2RqSnA2VndFWnV2NUEzSGxwdVZVVS00YjVGQmlVVzRnZDgtRTVUTXBNRG9zano2dTFvWkpSRVY3OFRkVVplbjRmTXQtZ01SeXZhWHh6ZW5B?oc=5", "source": "Dalal Street Investment Journal", "published": "2026-10-30 10:36", "score": 0.807, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex rises 308 points, Nifty above 23,000 even as broader markets crash. Will D-Street bulls extend reco", "link": "https://news.google.com/rss/articles/CBMipwJBVV95cUxPTXhsRWN1cm45ckpDbWUxY21qclNKLTVCeDlaUlJweGFFUS1qSG40b09sNVlzTFBKQVNPZzU4R3VSSGZuNF96dHFPVVFDQmFOTy1YZU43YjJaRWpCczlrZkViZ0tTSS1lN1VzSUdrbHFoS01uMW9vRjl3MWRzSnZiSkd2T3REMjBBUTYwY29vOS1xSDNndVhFT0RNdjVtN1lFUkljSlE0cjR3ZjJqRDZodXBuMlpmSGJhYklpRnAxYktzS0hhYWJoRUJUWWUyeWlScXlTVk05VkMtazRESVQ1STE0TU1Cd0Q5Z2NHcXdZWm5XeFpaMHFJUm9CalNmMGdYZEpTS2ttUnFvaDFjVEc1YzhEb3NLSWlMRHYxUXVwaUFWQTZXZ0lR0gGgAkFVX3lxTE55RHpQVXVLRUxDYkNVYmFlZ2FlbU9vdnZVNTBvUXhZSFJBaHpKOXJ6dnE1aVpGSXlZeGdGaUtmMGN5TVdHX21JYkhuVXgyWmE5eW9UcEhMdmg0cGlJaGFRdEttaktQTlphMEs3Vml4cW1MMXY1eTU5S1dtbDRfRXREd2hmM3FRMGdBMVFjUmpqSlJZMUtOVjUzbTdaVTVUT3I1NDE5cWljc0NGaHFnZ1RVM0RWQUxBU0swOE1Ydk1HVDlvRU9GM0htOVdxeWZRRXRNWjVRbF96MVVZQzBsX2JfNlNLTDlaYk5HWm9fS2xQeExiWFNBMmh5UHlBdGUwYlozX0ZCU2ZxUzBjcmNQUG5PSzdkQW91cEppOWNsM1ZIWQ?oc=5", "source": "The Economic Times", "published": "2026-10-30 10:35", "score": -0.103, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex, Nifty extend gains for 2nd day: IT stocks lead rally, broader market underperforms", "link": "https://news.google.com/rss/articles/CBMiwAFBVV95cUxNUzFDYmRlTTRKR1BhNDQxb3lJc1ZER3FjUXB6ZFVQV1o5MHZVVk12ZS01ME1iVHZ1NkNWOGNHS2N2YTBWZzFRS0luNkRwUllwcDNYNktWWXNwaTFQdWk0aDlsQmUyQzNhMXowZnFkbzg1UGI2NHlkc2tldzhPYy0zc2tIVmw3VUhXMVRtbUxnd2pTdEdsME12eDM5VlBGWEZXNzFHY08zTl81am9jQkJTZFVzSVdMX0IzaTVZcUNGb1Q?oc=5", "source": "IndiaIPO", "published": "2026-10-30 10:31", "score": 0.84, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty extend recovery; what's driving this upmove? -", "link": "https://news.google.com/rss/articles/CBMilAFBVV95cUxORUxpb0U0WlRwTF81LXhEQklDb1lULTAyRHhKbzE2MDkyblBpNzg3QVJ3YlVTTG5zZ1RMSjlpaG1TUk1JUXhhZUVKTTE5bHJqMm1KRmpLUm91SGtibV81VURxNXZnd3c5YmRNcnpVWDFqNGJvaXBYXzdKd0NWSVlzMTMzVnV2Q1lIQWFPRTM0OEgxTDFl?oc=5", "source": "IndiaIPO", "published": "2026-10-30 10:31", "score": 0.527, "label": "Positive"}, {"symbol": "MARKET", "title": "Markets reverse last week's losses; Nifty crosses 23,000, pharma jumps 7% weekly", "link": "https://news.google.com/rss/articles/CBMiuAFBVV95cUxNdW5ud3NiVkJObS1vS3V4YWtacEFfYjNtX05KeWhyb2VacUlHZFc0UmF1Z0pBalhfRVNwampJb0VodkJ1czJJaV9INE8xUWVVRlkydGdDYS1zUU1lRWFmRjFUUktwa0U0a2d3VVU4VmJTaDBFRnVhUFZBSG9vVnpYV2NaSGRJZUFva1B6U296UzREYmlqcDF3RjhTU0lzLWh0cXFSazdFX3hHY040aXNjd2E5cTJZSWVk0gG4AUFVX3lxTE11bm53c2JWQk5tLW9LdXhha1pwQV9iM21fTkp5aHJvZVpxSUdkVzRSYXVnSkFqWF9FU3BqaklvRWh2QnVzMklpX0g0TzFRZVVGWTJ0Z0NhLXNRTWVFYWZGMVRSS3BrRTRrZ3dVVThWYlNoMEVGdWFQVkFIb29WelhXY1pIZEllQW9rUHpTb3pTNERiaWpwMXdGOFNTSXMtaHRxcVJrN0VfeEdjTjRpc2N3YTlxMllJZWQ?oc=5", "source": "NewsDrum", "published": "2026-10-30 10:30", "score": 0.44, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex Today Ends 308 Points Higher | Nifty Above 22,300 | Vedanta Oil and Gas Up 8%", "link": "https://news.google.com/rss/articles/CBMi2AFBVV95cUxOaVVsSnlXUHFmTWxXVlZSNnRHcy1zRW1wbUdOZmZRWG1DQmlBbVVSWmJIdF83V0VObkV0NVh0T3kwQ0Z3U2VuV01NSUxTU1drMldDTnpjVXF5a0d1ZldaU2liWHNaRlMzazdiOHpiaDdFeVBrbGJORWN5MmtUTk44UVVGZVFmaDJZNXdmekEwS05XQzNDbGxPeDZsWFd1amQ1YUxQd2w3VGVZUGtaTHdGUGdoemFLVUlqcU1aZkhJMUFKQmlqU1pmcXdfMEc4ZHM5U25iX3NjOVY?oc=5", "source": "Equitymaster", "published": "2026-10-30 10:28", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty close with gain of 0.5% as IT, pharma stocks rally; weak broader market limits gains", "link": "https://news.google.com/rss/articles/CBMivwFBVV95cUxPZW9rV0NJRXU2T002TkpGY3BBMWpjYWJMLXNYOUZ4bUQwZkw4UU1ZMmJLblFRZWhpdmZUc0VPYVp5WHVDMTRFZnRsNkZzQjFlMUdlMGgyQy05bVpVa0lhaU9PSTlXU2ZTYWdIUVF3ZEV2MFB1SGVtbk9LUWhPWWRQbVlCbHNTbVRZZW40QW45R1hVVkcwc3VWemxkRUdieTA1YmhHZVMybTBWNW5OTnJzcTgzOHVkbVlGbzBxSlpxUQ?oc=5", "source": "ChiniMandi", "published": "2026-10-30 10:26", "score": 0.796, "label": "Positive"}, {"symbol": "MARKET", "title": "Taking Stock: Nifty reclaims 23,000, Sensex gains 308 points led by IT, pharma stocks", "link": "https://news.google.com/rss/articles/CBMi4AFBVV95cUxOOVBXVDRvbFRPVGZUMlYxdWZuVVJKMUxjOWw1blFmUW5JQWFvYzFmd1pGVldOaWhSd2NySVF0NUs3V25BNlFKMnhrM0dRVmtRMU1IYmhtbVlPamRBejdHYXZ5XzFnd1JJdkk0Z0dGV2NYZ1JmNkhBVTNvV2xnc3BSb2FFaFdNUXdCWkJQU2V4V2JDMG8weXVyYmJBUHZZdndmVE5lNXNGdmtxeTlGVXl3ek1BN1k1bzJ0WGV2VmFYQ2h6SjVLUEQyT2JUeV9PZWRaUGFBTFNmSnUwSEZCOWFIV9IB5gFBVV95cUxPSU5LVTJRUC1YUEVNeHNUemEyUmRkd0JaT1hqbFlvZVBCWk8yMWtZY19sR3dnekgxT2FCT3pKaUZfWkMwZjdKYWtCUUlSZm1GaUcxbzdUSmN2M0RudFF1dHJHVFQ4UlVldnc3UE5JWFJ6T19OU0E0X2JvZXF5NTM3RGFmYWlTam1xTnE1bTYtMlFtcmdTYVBlOWtFbGxvQ2xNUThNTzZMei1obURvZ0s4VGFnazd5WUVHRXZFR0pERExITkhhc0VFM0VVbG9sWEtPb0xrd1F4TlUtYkc5bTY2M2M5ZVZ4Zw?oc=5", "source": "Moneycontrol.com", "published": "2026-10-30 10:21", "score": 0.649, "label": "Positive"}, {"symbol": "MARKET", "title": "Closing Bell: Sensex rises 308 points, Nifty tops 23,000; IT, pharma stocks lead recovery", "link": "https://news.google.com/rss/articles/CBMi9wFBVV95cUxQc3JkY25Iamc5akJlYWgxSHNJMGJqQm9iSWtwWThPZWhnczU4YnJJOC1sdGZMOERMeWluV0FkVmV0QlNxQy1mVG5xMkRWSUVEdE0xYk81QjcxdXdra1kyTk1lZlc5MFV2RnQ5d0hOUGdXQWNBSUIxUWRTc1pMcmNfakNUOG5HcTVaNlBFblI3R1FUX21PbDNJY3I2Q2o3Rnc1OTZDVzI1TG10VUpUS0pLdWJMS2dLY1ZSSzVTdU80MTZlUFFPSEdKN3V1VklZZm93RmtzcF9nNTBsM0FFdVhfY01UamRYRkpWVlYxcDJmVkxMUEpJdmkw?oc=5", "source": "Zee Business", "published": "2026-10-30 10:05", "score": 0.718, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex ends 308 points higher, Nifty above 23,000; Trent up 5%", "link": "https://news.google.com/rss/articles/CBMi1wFBVV95cUxQMlVJODZONnhDZU1vT2d0Wl9ZMEFmZkN6RGFrVU95R2RqanBoZEpCSTRZckxNcjVOTDFoY1FyaGE0RF9hS3UwVlptODRfMHFoY0Rvd0l0R3JJTUUzTExBeVc0RVFNUElyaGkybHdwZHByWjF6Nld4VWVCRHFEQ3l1UkQtSHB0M1VrZXB4MTBEWENzUnowS1I2c1BOeGIycEJWSmRScUlFQnc2N1VwVmlGd3BSX19iNEp4SWxNMWJiV0hXZHZ3NDIyQlg2NnQ0N09XWWZTdHU1UdIB3AFBVV95cUxQSTJkN2R1WXNmVVFmNE5GX1M4RHhod3daU2k0emQ5N0lWdmZxcXI1VDFCWDBkcDg2eGZ0TWV4R2ZCOVdtTC1leTBaOGRnaFd6UHRhbWhUNVBpRzhib0F4RWNybFlUTlBMamtLUXN4VXlOcUZTT0FBZ21Wa1hUZ2FYZUgwSDVPVGFjQ2R5ZXh6OGtMWGlzMUI1SjJQR2NaelFXTm5nZU9jVnBSLUtjTzhqZVlMWHNTc3FjSm1pekpVRFd2TTdLci03cGozMjhoczAtQ3pENXNoZ056d3dM?oc=5", "source": "India Today", "published": "2026-10-30 10:03", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Market Wrap: Sensex Gains 308 Points, Nifty 50 Ends Above 23,000; Trent, IndiGo, Infosys Lead", "link": "https://news.google.com/rss/articles/CBMiiAJBVV95cUxQZTFyMk9sdFl3QmJnUDd2OGhhdDNIZ3FwcDQwclFmNE1Ba3ZsakV0RzN0RHlKUkRYZnJST19SVDlqZmp5UGV0OGdOYzlLTkNNMTFqaEhNZGQ5cmctT2JzTEtZNzk4N1lfb2lyc2NuVU1ETHNWU0ZBZWpxX29hVWxxNUp4VE5pNndCVFVDeWtmZWNPQkh4U2xFeFp6NEd0am1jV2FBSWZIb215bUxTVnc2LTdhQ0lmM21KSHUtQjVSVlVpajhPdkZYdHQwTEgyc01tMFdxLXZBZkUwSUdGdXNkUjl4NGVMeHNWNzVROXhhSDUxT1BJSXo1enlzR3VVNXpyeWRaeTc4YmLSAZACQVVfeXFMTUltcFpOMzllTWlGSzAweENGY0Nob0tmTk96eV9wOVB1cGlDeTRuN1hRRFI4RS1KTVoyUW5xdWxpU24ySVIzWk9JV2F6bks2bVJ4TlZidVFqQk1LU3pOYlNEV2Qyc1JVSGlhVDhyb19xQlpQbWFmUmdXakhsUDZtSUEzSXlnQVA1SEhXV1BzZURDVnJablhfSk1FUzVCSmEwQmpZczltQVRON3otMzV4MnUzVGxsTlNJMGt3ZU5fWlhrcU53YzdHTE92UGx0QjdBTkdfOUVobGVib3VCcDR2MGZ4Ulk4R1haZkJZdEQxalExRDZqT01DMjlQbEE4RVJ4b0Z0UGh1c05kX1A3bnNOWFQ?oc=5", "source": "NDTV Profit", "published": "2026-10-30 09:52", "score": 0.649, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex Rises 298 Points, Nifty 50 Crosses 23,000 as IT Stocks Lead Gains", "link": "https://news.google.com/rss/articles/CBMiuwFBVV95cUxNTkdfNHBGVl9UeTFzNGUtdzRHMk5xb3Y4N0VvTGkxWUZ1WGJuNm9FLUtBRWxuZUE4QUVQT2VYOFpSTXpDOHJ6b1VrUXZia3E5TzdCdTlOUnhXVkNVMW5GVEJmQmZuWDlieDl2VndJTWYzRF9rZ3I5LVVfb0ZpbDBya2JrdHBIdFQzZUROemVYUU5LSjAwMFVaellUbWVnMkYyMUFTam9WY25YUWd3NFNRUHE5MkRGTW82TTJN?oc=5", "source": "Dalal Street Investment Journal", "published": "2026-10-30 08:59", "score": 0.649, "label": "Positive"}, {"symbol": "CPPLUS", "title": "Aditya Infotech CPPLUS ESOP Allotment 48,100 Shares Oct 2026", "link": "https://news.google.com/rss/articles/CBMiwAFBVV95cUxOUHlaMl84Z2E4T0RVUE5PMW5FZjVuQW1RcjFVTXd2ZUdMdmE3dXpNTURraTVmWHJYd2lQbG5fQVh2ZE1WVDlob2NDR2I2YWRQMVRLR0t2YVRaSVlYWXBsVXJoS2YwUENlLXducG1jaUtKbXNlUEVHQy1RT0JXdXhLZV81UklYZzFuMmFMUFFuRS1sMkRaZGgzRHNyMk9Yek5sdi1oNVZXbmdxTDhyZzlhODVKX1pmS1pYODc3MHBBT3Y?oc=5", "source": "Kalkine India", "published": "2026-10-30 08:44", "score": 0.0, "label": "Neutral"}, {"symbol": "AETHER", "title": "Aether Industries reports robust Q2 FY27 financial performance with \u20b93,472M in operating revenue", "link": "https://news.google.com/rss/articles/CBMizwFBVV95cUxQaXBiV3ZRODczRjJseWRyYjk2WlFLdHd1ek5tSHNjR0NGRGVIV09hM29yRHZLUjRxaTMxeU9fMmN0bFE4d3k5a0hMWk42TXVVR0NZMV90Zmcyc1p2NHJNRzRnT2NMN0szWFRTcm80TU96MTlGdXZ4UEs2U2VYaGZmUUdGdGdtNE5YVVRTdVNOSXpsYUpQTEdVMXU2NVNBbHR4RUNNQ09WaHIwSVdtRjM2Qm5RNjV0cGk0ZThLblZOLW1UbGwxYjg4RFN3QW1kOE0?oc=5", "source": "Business Upturn", "published": "2026-10-30 08:35", "score": 0.421, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex zooms 1,200 pts in 2 days, Nifty tops 23K: Why are bulls in charge?", "link": "https://news.google.com/rss/articles/CBMi1AFBVV95cUxOTDJ1dFlKVkRQMEhPdHhUbGlyTHk4ams1Y0EySG9zRlhkcWpORm1FUzdwWDdtVmZRT2s1YWJJYUpDU3h6UUt6Y29DaFJsMFpmZkwxMnk1dnNGQ3kzSlNfNlZoOTVURThySncwaUZ1cDJzeGU5NlN2NV9aeWROd3RuWTItcmtlNUE5WkZVbi1wUUtobnJzRGp4SE1PcUtPaTQxbnVDRUdTWFpQTGZjMzh6dTJ0TzJtRVNMbUJMVmlBTlFPTXQxX19QWktWUEhWM3ZkNm51VtIB2gFBVV95cUxQcjQ4VkQzSUZjUnlJeGk3b3ZFQk5QYVM1ejM2X3dZanFHNFhOWTFJME0teEVXZFRQZDgzMzktem9uMWc3ZXphVVJJUGwzUG1KVnpKVi1Xamd4cy1qM0hTYUR6OTVSa2ZUQ1E2S3dwWHV3MTByUGtFQS1seXl0SWNUXzhxeFZ3UEZIQVd2V0w5NlNNeHgzeUVHYTV4ak1iYW5IY0IycU4xYnJ5dGxxMm1QSFdQTGpQYWE3Y2dUekVadEVSeHZYc3c1UDdmMDVJd3hXbjlMRjItUlhBUQ?oc=5", "source": "Business Standard", "published": "2026-10-30 08:02", "score": 0.718, "label": "Positive"}, {"symbol": "MARKET", "title": "IndiGo, Trent, Vedanta Power among buzzing stocks as SENSEX gains over 500 pts; NIFTY trades above 23K", "link": "https://news.google.com/rss/articles/CBMi8gFBVV95cUxQVWhkWWtVc0VYNGNZNEZwLWxOVklBeHdGYnpsM3NiVnRtUlYtNGlwWHVzNWpZUkdnRjJmUVhiT2g2MFEwN2o4SXNwM1ZSOGV4cnEzb3lOUHJDbVdYcnJiMDBVbFB4cHo4Und1XzdMRF9uWEo4ZDRpSks0SE1GUTlFX251ZGNfWVZ2dEw0QklyVmZZR3g4X2dSNWRNOFcxXzJUbnY4WXFqeXVSRUdfVFBNUm9ZVVp5UGRCNG1PaHFsUW5BOVJsTHFPSHJvTlBxd0VIZW9NWkhfUkJGbEFKOXRER0ZBdkE1VDdoNWhyVlloQWlOZw?oc=5", "source": "Upstox", "published": "2026-10-30 07:52", "score": 0.721, "label": "Positive"}, {"symbol": "MARKET", "title": "Why Stock Market Is Rallying? Nifty Reclaims 23,100, Sensex Surges 500 Points; Three Reasons Why", "link": "https://news.google.com/rss/articles/CBMi1gFBVV95cUxNT3ppT2hyUUlUTExXYmkwSWM5TTRRSGd3d1ZzTk5rU1kxU2pRQkZQX2RybGhkWE80aUFRc2gwZ3MyczV4Mzh1emRfd0h5QjlOOWN3S21ZbFkwODVqOUs0b0tnbzNNd2Y2ZENQXzM0WFNxUTZLS3VMUFFidXR1SjdFb19hLVZIY2JxVHZPVW9CMVc1S0cyb0FCOW5ydENoQ1ZSYUVuaGJBY1l6U1RjQXF0c3FYU0VXbGpnLVhkTEtyc01yM1hZTjRvbnpPMEpVNE9JMkRqaVRn0gHeAUFVX3lxTE1JUmRUNjZycl9ZN1RHazZuU2VHLUxzRzMtZWF6Mzg0X2dvOHNhMXYzeUpzc212SU5wdEN6SGhLd1g5ZTNER3pCalNkWnp1NnN4MnNYNi00cVdwZUdyUFRrZnFDdHllaUxYVGFnZy12WEJtMHNGSUxrbkJ2YTZ4djlYWFZ5czdKUW80aFV0YXVjTThZc0tFNmJ1MENSRzZkV1FyMTZQMTc4LXZSWHYyNC1UeFhHWTJaUFM3U2RuZ29HUWVLa3JudW9rb1EyQU9iS3dKN0dxSnNTR1ZHNVRqdw?oc=5", "source": "NDTV Profit", "published": "2026-10-30 07:31", "score": 0.71, "label": "Positive"}, {"symbol": "MARKET", "title": "Passive funds could buy up to Rs 36,500 crore upon Jio Platforms' entry into Nifty, Sensex", "link": "https://news.google.com/rss/articles/CBMi6AFBVV95cUxPQml6RHdZS2FTeE1nN05IMHpUTVYwR3BxdXhNRVViWjlzSExMb2ZsRFBGZmc3bXZRbDR0Z2ZZVkNhclFpRS1tYWtfN3RpM18waHFDdkRzR3FWeDllUFhvb2JlaVQ0RkozVWt6b0dwS1VWRk5zcjVaM09RUjE4ME1rNmZ1WkxqVl9FVm40ZmVoeEp0X25uTWN0Vm5PLVV2OGpLaTF6X1VuNW5kNUVwU1FtclNGdU94LXQxdUozUTNwQnVDQzR1OEhCcVhpNWpOakxseUIySzRrdWMycFR2TWRRSUtjQWdCZUxh0gHuAUFVX3lxTFBvVWFETnc5Y1BDWk1YWmhPdFNTbTZESnpWaHNVSTRoTWJHVlBONW1yVldTVThqckJyTURkTXotaVRCX3lOZ3o0QlRINTZJcnY2SmI0R0JuMkdjV21jVVJrcG55Y1lrM0F5N0NUS1pnODZNTmRIbVRLYU5nbXE3UmZyb0hERFNBdTJ1SEdTLUluV3FldFF2VVd1d2lucXpUcUlxNVlnODdqdkN2UjE1WmNfWlU2NWJLelpwSXptX3hKMGpjQ2xaOVFDdW5hd21UMktsODRIaVdmY0ZoZkdhQnZvaC1Ha01SN1JlVV9TR2c?oc=5", "source": "Moneycontrol.com", "published": "2026-10-30 06:40", "score": 0.691, "label": "Positive"}, {"symbol": "AETHER", "title": "AETHER Share Price Today - Aether Industries on NSE/BSE", "link": "https://news.google.com/rss/articles/CBMiXkFVX3lxTE5YVWFUSmNPUGtKRF9jY2EtNTNkS1lUVHJYOFgzZWJkY3NrY1lucDJqajdnSjhJTFZuSkZMSjhwSUp3UEs2cDZtNTYzd0YzbEs5NE9IRy1VQzgyWm5YTVE?oc=5", "source": "scanx.trade", "published": "2026-10-30 06:37", "score": 0.0, "label": "Neutral"}, {"symbol": "AETHER", "title": "Aether Industries Q2 FY27: Net profit rises 26% to \u20b968 crore as revenue climbs 24% to \u20b9347 crore", "link": "https://news.google.com/rss/articles/CBMi2wFBVV95cUxNbVVVa0lsV1JvNU1BWnlRVFJSNDQ2Y3l5Z0xwZWdFS2JSTkJPbkxlN2ZfNE1ZZ2hVa0EwMVZ3enhwOGNTQ2VFRC0waFdOckhEaGJ5RDctUGg4UUEyNE9La1BweFVkeWNya2h0SFZ4WVZhZlVLTjl2cXhLaURoTkxSMXd6MHVVTmtYZk90SUx1NmsycU1KMHZKZVItNWRuR29pYy1KWTVEMWdPdGVQcHRQMXFadHJ2TFc0UEFjVGpKM2s1WTJER1RJV3Y4eU1GMmItSDNpR2hBZlRNdkk?oc=5", "source": "Business Upturn", "published": "2026-10-30 06:35", "score": 0.612, "label": "Positive"}, {"symbol": "AETHER", "title": "Aether Industries Q2 FY27 Results: Revenue, EBITDA and PAT", "link": "https://news.google.com/rss/articles/CBMiwwFBVV95cUxNLTdIWDMtbG5YaEVpMVZSemJTMzFndWU5OVVkcDJXdHpCeU9ON2JtcGRmNmJESXByQ3ZWYlh0bDZuWExfOXhtQXVhc2U2eThtZ2psXzFKS2NKS1VXU3lPNG1uNmlfWUE0aUlWVERSdS1RTXpGZkVzZlRfWXhhcDN3dGktb2JwdjJHQUM5YTdTZU43RkZGM3Q4RTZKc09HTzFHTlNmNlZpcWtKSi1Ia0hyMWNUZEUtUy1GWXdFMlVPRWNVQ1E?oc=5", "source": "Kalkine India", "published": "2026-10-30 06:31", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex Today Live: Sensex, Nifty Trade Higher; Trent, IndiGo Gain, Coal India Shares Fall", "link": "https://news.google.com/rss/articles/CBMizAFBVV95cUxOcXdkRkl0dlpWcXlSb1U1T3BxdXhIb0x3Mi1PUUE4QXh6WWNkREVUTWV0djV4MFBUSVlLZk54SDlsbnFsNGg2b0dnZjh4b193bXpzRndMZHZpUjAxb3VTam5mc0J2dEdWOVNNLUt</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SGR5ZjRTd0tzT1NiQ3hoY3htWkJtSW1nYWlrOWRNeS1LVlNMYU5sRVF3eWRzQTVzallfc1JEMVhkSWc3TV9IM21vWG1vTmZRUmVEUmllVVhNdU13YUVVS01LUFNzTHVRRE80bDdaVW5XWXFUTm1oVjZNN2dQaExRMmpMNEdiSzdGMlhuTVBvZ2ZVTTZ1aUdYSTRhek9HbXFMZDNyTEdFSF9GLUZkRGZPOVlTU2JsNTF4WWtw0gHWAUFVX3lxTFB2LU9UckFtY0YwdFAtQ080T2I5a0NJZFowOEJ5bGJsRUR0M1E4WU5jR1d1X2ViencxOWR1dUVlYlVBdS1XRDhBWmpHVUhDNWhxbTdIWkdtdDBLY1hSN2hOclNhcG9HYlRITk81azlSZzFIY0lWZ0RrREg3THYxQWw0ZzIwUnFfUVFpbDQtQ3JESmpTMTZ2U1NFRHk5YjJRekdGWmlUaUhPR0I1UnYxc2dMSmRTdV9yc3hVM1VFc3lXWjZPRTB2UzZzT2kwVE9zMlhkZUQ0NFE?oc=5", "source": "Business Standard", "published": "2026-10-29 14:36", "score": 0.226, "label": "Positive"}, {"symbol": "AETHER", "title": "GUJALKALI Share Price Today - Gujarat Alkalies &amp; Chemicals on NSE/BSE", "link": "https://news.google.com/rss/articles/CBMiakFVX3lxTE1jSVBOQjUwbHMxcUhlTUlVcWJmVjlNbWhoMEZXTWZvRUVVMnJZdWlDV0xWcVZKaURzT1o1UG1xaENWRkNkX1BDVzNZUHBLa0dJNWlsaWRUSi0wNGZqRExjZTU5T3dNTmViSXc?oc=5", "source": "scanx.trade", "published": "2026-10-29 14:27", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Why markets rallied: Sensex jumps over 900 points, Nifty gains 1 per cent; 5 key reasons", "link": "https://news.google.com/rss/articles/CBMi9AFBVV95cUxOV2JFLS1oXzVnM3R0aFVjdkpzTDM0cVh6cWRtUnBmOVpqbGpGU19iWjAyS2NTdEhpMHZITGZwNm1kbFg5YVVpWUkzOEpaWHNvVGRCYTRyOUM0RWtsTkJIWFpYSjYwTXdfTjFVTXNEVmpROHBfblVxdTVTRlI5NmVpYlUwX3JXT2J6M0dWVmNRWjZwSDZSMlpaTHhxdUFRRGVNZDh1VV9mS2I3Wkp1UUx2SnVOaVMtTEtGZFhDcW53V0ZWWUFMdWJqU3dzeE1DV1dVMkR3THhJeHg2blJmVXU0SEtQbHdFSDN2Q0cyU0RMMGVPM0xM0gH6AUFVX3lxTE1CQWRvOTFHOU9DMTAtMjUyTWEyem5lQVRyYzNQMzd1OWxPRHEyVUx3OEtsUUc0Uy16Q0lkTTE2X0FBQ1VyaTFwUnFNMnc2b0pIM1N1SUdKcnhuWG1YbDNGZUE0RE5uSzBqdDcyRWEwN3lLR3htVTBfLTNSclZTeW84ajcwQ05tWS1pczQtN0dJdEtKdXA4d0N3UTlrdDFOWXVVdG8xMDVpQ2JkaGI3Nnlic1RHaUtEMWlQS0VrajR3RGc5SWo0aWNrSEloNzczZ3lMQ01LZ2hkWXIxSFBCanJHSUpwUWxsVGt3S2J5MVNvTFI2aFZYWXFPbmc?oc=5", "source": "The Times of India", "published": "2026-10-29 13:03", "score": 0.807, "label": "Positive"}, {"symbol": "SYRMA", "title": "Syrma SGS Tech - Technical picks for Diwali! 10 stocks PL Capital is bullish on this festive season. See full list", "link": "https://news.google.com/rss/articles/CBMijwJBVV95cUxPY0dYWGhsUHRsOC1HMHVFeFR6YlBhcENObTZlV3lXZkJyUVFLMU50T2pfT3k1Qk5aWkJBUWJOZDE4TTNrSDlUd1dCbTJ0NjlYal9SUmFjSTg0LWt5RldXS3YwRzVOZjBGbk96OF9IQnRETU9VcXFXM2tVMHJWb2R4Szk5MU5YNlpsa05xMldaajYxaUtXc3JmWnJZREZpdHlkM2dsS2Z5VDE2bjRZdmZidE1fR3NXTXRGdFdMVTh4czJOVDBxZFB0MDk4bEN4RmZpN2dJT2JyeFMyYVlYbXdxVE13dmxSWEtTa0NnWDM3eGJIaDA2ejJpdkZHcVFLUTJGZEhJVFduNEh0aGNGY3Q0?oc=5", "source": "The Economic Times", "published": "2026-10-29 11:52", "score": 0.771, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock markets rebound over 1% on Fed pause, but rupee and crude keep investors on edge", "link": "https://news.google.com/rss/articles/CBMi1gFBVV95cUxQdDlZWEp6Z0c1WkJRSHdmUnl2OUY3cUpKak5iNWJEUVllLTNmelJRalJlTUJRcHFaOWtUcXpXeXFkOGZTaGw3U3E4ZUt6NjcxM1hDem1TaWN0NlBxaTZiMkN4aC1hc1pRRGpxdDNpRGUzRzJRMnZ0bTc4ZTlXQWNLbk9SbWNuTDlrMlhfempqX2VZQUpmdkF3NkxobmJ3VUpCbllSWDJVY0hSZDJ5Q0tPUVJyRHFRemxYTGJQeW1tb0I5a0d3YjNGMVF0dV9iUGxKMjVoRFh30gHcAUFVX3lxTFB1RlBYcHZYODl1ck96MG16Vm54Y2tTZFhoVFI0YXpLRDhNLTVMbUlVaWFtZUZ1UHJpSGcwcUw5WTd1WGRlSHBoRWdXUHoxaUFLOTlCVENUblpoaFJVU1RxOVR3Y1Z4M3NzTDIxa09vT1ZnVFFWVlUxX1QtRTVxUGNMcmx2Vy0xV3pKVDlfdDBtZDAwUkJqd2xxTWo2Z3RBUHQwamlfN2hObzRKbHhIT05GSDloNTMzR3FyV0FGV1lYZ2hlSDI2Q09NdXJIM210dHFad1hYVFU5SjA1M0I?oc=5", "source": "The Hindu", "published": "2026-10-29 11:25", "score": -0.723, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex Surges 905 Pts, Nifty Tops 22,900 on Banking, FMCG Boost", "link": "https://news.google.com/rss/articles/CBMiqwFBVV95cUxQYldTSk5iZ1RLbnd3cU05cDdfbVVwaFJnZVNSTjlPX3B4MW9uZlNlUkhyN05LQVJlTGVYQjN5eXM0aGR6MFZ5U2FPcjE1U2Zoa2tzbm15X1VrVm9JTnFiUjBvOWRybElwcldLbGlCNk5ackFCQnFNeWo3ejdRcFktdHprRGRha3FmN2tzVm83VDVyX21TZkFSdTE0WnlMQjBRSWtMN3BzcGlOdlXSAbABQVVfeXFMTnZxRzZteVlmN3gzSEpRUEJ6ZXJZM0VDMjV5LVA2b3FicTBLYUpmNG5DdXdkbDJIdllXU0llTjREQXN3YmJIZU1OcEVJVkczSk54TzZod0d5azRlM19GbDhoZ1U5UkNtTktoTzhmLXRaQjhFYkEtbzNEZkw0eURSbWRVNy1lV1JZSUNLaGlhX08yQzJTYzJjYkwzbUVZdVVUYXN6eGRxZnNmS1pBZno0Z1o?oc=5", "source": "Rediff MoneyWiz", "published": "2026-10-29 10:59", "score": 0.898, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex jumps 905 points, Nifty gains 238 points as markets stage strong rebound", "link": "https://news.google.com/rss/articles/CBMiygFBVV95cUxNQkR0eEdvajJ2ZVB6SjltUGY0ODdUZ1BYZGxjb3Nfdjd4Y3hYMVZ3MlNqU1BBSmsyQ05fWDVFZ0s1SEd5dmg3ay1OdnNrT0ZINnVfVnU0dzJodXg5ZzBvejZRY2pMb3RBREYwMGNIaTdwXzZsZXJkOEIxUFJxVFRvdjgzVnhfMGdOTVNUVDFmOE4tVDVvM1lZNHlHNlZ6cTNYa000YTVTM19qV1VFek40RVUxVUU4WXhWZjQtV3Y5REdrN1V0VllxMU930gHPAUFVX3lxTE5pbk1LaDNBZDF1WGstdlROOUVfSXBQX2FuaE5FTzVQOEhCNHh1UTdEdmtua3JzLUY2RDRBYkJ5Z0xLRVdRMFkxZEZlcTl3cFZLSXZuM0VBOUw3SDYyazBGcVVyZWFOTVhqRDhteTBnTVc4UzBENXk1YXZwcVY1V19LZ0JVSWV0aGpfbDY0YWwxN1ZOVUlQeVlaTUNhY0NuZVVkTmNvZ2Z3VG1QUk5yd2p5VzdyRTRYUFN0Q2lYejd6cVF1YVBGQko1TzhuOGJxbw?oc=5", "source": "Telegraph India", "published": "2026-10-29 10:56", "score": 0.872, "label": "Positive"}, {"symbol": "MARKET", "title": "Indian markets stage a strong rebound, recouping yesterday\u2019s losses as Sensex surges over 1%", "link": "https://news.google.com/rss/articles/CBMi2wFBVV95cUxPNjhqLWVyaGVfUDI5aXNGT3VhMUNQc2wwQVQtVnA3S29YWVc3ZlpRVmQ4WG9JUHBZVjhpOVpIYi04YVBlMmVuMF9ZOXdHM3pfUGNSS1Fzcm05dnQ4Z1ZPN3l4WUVTMlRZdlVRcUQxUDVVdmE2RXg4aF9wcGpYZmlnQTNOVG5zUmJ2OVh6a0dOTjFKY3h1WC0xOU1qd0dZUndxc2NjRUxGNE13cVd5dUJGTTZhUUh4Vnlrc29vRHZmTW4xQmhwM1FpWVJTQVlNYldZRENhTDZWcW5oYm_SAegBQVVfeXFMTUlaeTNneHFjNHF0a2Y0cWpyeXF4QzNSdDBRWFlKTmptOTN6VVJ5MDR3X0pjajQydzZRQWcwNmhKRmhuUXA3T3U1TUo5WDQwT2l0OVV5ZVZ4UGJlVVNtT1luR0plcTBaU1p6dDdqYm1oSS11NEJ1bWR2eGFlcno3eF94U0xOV2Z3WjFVTk9jMmJOUUhlNkZzUjlYekp0VkVaWW12M2pDUlZKbGJUaWtiZFdYVmxPV0x2ekZoX2ZpbU5RMFhZXzNzbnZlcjVLOGFrMTVjMU92VzNZQTFUNDhzSGRpWlQ5cnMybQ?oc=5", "source": "The New Indian Express", "published": "2026-10-29 10:42", "score": 0.459, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex Today Rallies 905 Points | Nifty Above 22,900 | 5 Reasons Why Indian Stock Markets Are Rising", "link": "https://news.google.com/rss/articles/CBMi7wFBVV95cUxPdmVRUFJReXJwV3FPNWs0U21MRjBvOHE4eGxuMGpOWHpFWlVSSU90WHFITUwtQUM5VjJXQzRGY1RLb3A1UFEzS1l2blhJTUlnaEhxS2ROOVQtNDNNUUl2TGZSajc3ZHh5MG9VdERpbWF4LTRfSFdvS1JxVU1BYmZFdHo0WW5hZkdkam1sbzNDUE51Nmp5NnU2QWlZUFFzYWt3SUR2SW5xTGtFRDdkSklUaHVNSFh5bG9STDd2Q0lRamxfMDlEc2ktX295clRDZVRvN3kwdTBmMVgxV1FKSTh3bW1MLUNVanV3ZXBYQWd1QQ?oc=5", "source": "Equitymaster", "published": "2026-10-29 10:39", "score": 0.691, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex surges 905 points, Nifty closes 1.05% higher as Fed rate pause boosts market sentiment", "link": "https://news.google.com/rss/articles/CBMi2AFBVV95cUxNS3Mtb1dXbVlRd2pURnEwd3FDWEZTWHJiZUxPVzYzczFBbHBxSmlRYnVVTVlsMWdsRGx5UXFXMVVteDJUZVhZV2FIQWNiQ3pvMHlTSlJiVXEydFhaaEZ1eUp3M3VhZmVoZW9SYzhqVFZmMVM0R2hoQ0pmR1FlQ1Q4NFBEbmt4TU8wWU9aNXpTa2Q0NkVJOGY4WVRFVFpxd19vU2NBZE5OMXg3Q09UeTdyWVVWNVNaSHVFenh1X2J4T2lpV21MazFKNS14eXBvVGRUQ3FrNWwwWDE?oc=5", "source": "ANI News", "published": "2026-10-29 10:28", "score": 0.802, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock Market Today: Why are Sensex, Nifty rising? 3 key factors", "link": "https://news.google.com/rss/articles/CBMiqwFBVV95cUxQd2ZpdWNMN2xVa3NjdUc0WDFvUGNhdDZkVUhOZGQ0dm04T0s5R1Q1cHJyVE9CVDF5RXk0V3UzT1lTSFRCYTJfTXNEd3NyRVRrVU5UNUEtbnpPaE1Ycm45MjVmWERFMnR5X05pQldUUlIwVlA3QjQ1Qmh6ZG1Ua3JQVUxRSDBKbjhIYlc4cjVJNmxsS3ZsQV8xZ1VoOF9Ed2NlR01LWU0zcDhtaWc?oc=5", "source": "Zee Business", "published": "2026-10-29 08:03", "score": 0.402, "label": "Positive"}, {"symbol": "AEROFLEX", "title": "Aeroflex Industries shares rally over 17% on strong Q2 earnings show; material costs jump 120% YoY", "link": "https://news.google.com/rss/articles/CBMi7AFBVV95cUxQQWlWYm1LaHBiMlF4V1d2VEg1UW1NY1FUWHlOWDFRTjBlMVVZNFlNSzBsWjB0MC1TeVRnbS1OZ2tvUjJUWkY1ejlnQXd6Nm44U21MZ0JmOXdsb3hhc19felBvbVJBZW1XMkFNeU1QSU50ZFZPUGs5N0Y5MlR0cVJDNjd3S2wyaF84MG4wQ3g1ajFSOWxTc2pqeGZOWmRoQmE2cHhOeFVodGdGOHBkLXRfNmhkNE1hdFNjcVlkVlJxX19JeGo1V1FJMjFZZUFJOENNMDh0U0pnaW1uQnNoLWJ1SnF4c1FiWENYQldTRg?oc=5", "source": "Upstox", "published": "2026-10-29 07:48", "score": 0.813, "label": "Positive"}, {"symbol": "MARKET", "title": "Why is market rising today? Sensex jumps 600 points, Nifty nears 22,900. 6 key factors behind Rs 3 lakh cror..", "link": "https://news.google.com/rss/articles/CBMiggJBVV95cUxOOU5QYXJBaTVGLXRqR056UExJZDVTYlpyUWR6VmhxUDAtbUFicGlSd3FlNWV2MURhX1FtTVRwUVgzTFMyOVlvdUN5SjhZX2FZMmxoRUptdnBsNzU1bzdiRF8tVFdxRTZSQWpzZ1VYQThLMjdWZlU0QnNPVnhUYlB6LWc2dlhZczd2bTZqX3dFanBncmF4ejhOWTJYOUJpdGNTbDFwSFBnZUQ4VnE5ckt4RXBkOVNfR3U1ZTBHek5xbFRwYk9JN1VCclZHMl95NFFuLUdCTUlHZ0hQMFhRNFBTOHVoNVB3Z3VSazREeW1EaW4xM3NiUEdVUGZyVEFmVEZ4dHfSAYcCQVVfeXFMTWN5c2ZBRlMwR2dWWlh6cHl0UXdHWnEyUmVKbGFjM3JGcldOdndhU3FsX3gtS1YwemdJZm5YbFEta1h4dHlzU2ZVXzJHNUNRck4wU21WYVVxUHFJY2YyUndiMmJSRVFrbnpRa0NMN0JMaXJyd1B1bkdwRHh2TDQ0cG4xWWhRVnZkNUR4T0FOOWtvRERPQ1VQQmhQdGl3R0NMSk5fNFN5NUVZT3JNVmtYQkgtUTNUQUhSaUhZS0lDcm9Gckl4VTlLMDVFX1VDT3ltTVJ4LXU2dlFIUnpTVGRpV0VxVjZGWkVZa3dBeE1kc25sMTZSa0VkbG5vVkR6NTJTXzdMVDJUU1U?oc=5", "source": "bfsi.economictimes.indiatimes.com", "published": "2026-10-29 07:15", "score": 0.691, "label": "Positive"}, {"symbol": "MARKET", "title": "Three Reasons Why Markets Are Rising: Sensex Jumps Over 800 Points, Nifty Crosses 22,900", "link": "https://news.google.com/rss/articles/CBMiywFBVV95cUxOc1l6QlN6SUJqM0FLV0M4MnlVWU9IYndGOG03emVPN0ZJXzRMTnI0SGg4Ymh4UHhpcnRyWmpDanp5VUIwSzhwSnhrYUtvYnlVYjk1czBqeFkzT2hEMVBZMllqcGxMWlUtQmFpQ3p4SGRMaW5WejN3MWNqRC1GaEpidUFKc3FiVU5TMXlhYlFqR3ZBaXBMYXRFVUNZMUdweUh0ZjNpcGV4N2ZoYVNMcU93LXdoQkVTOXdZLWpaWW5QSi1aMFQzRF84S2RWSdIB0wFBVV95cUxPcElqNUotVFRQdmJJMk9VeW1SaWVBaUU0UjVSeldWTS1RVjZISjF0NmFiVTR2a28zbmFSb1U5NDYzaDdaX3ducV90NkNRaFJHVmZ5dWlzU0dJNUx4WHdaeVN2Nk5TU3V5aDViNDIxYXVSQlhyOGk4b3F0OUhrSEp2V2lKNEJ1eHlCY3V6RFY3bUpQQnlOYXFrSUdyTEJzM1c0UlJIbjl6azFYREU4MHdyTWtwLVM1dVlweG50enNCVDJxQjJLcm1fcGtoV21RbFhVbG9z?oc=5", "source": "NDTV Profit", "published": "2026-10-29 07:09", "score": 0.691, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty Rise as Reliance Industries and IT Stocks Gain; Crude Oil Limits Upside", "link": "https://news.google.com/rss/articles/CBMixAFBVV95cUxNRXNQN3ZYVmxrczhYNV9wVHBZTVJ6bjFaY29LT1kyS08yQmd2MXlweEVaQUduNmhhWDBqTVlhZVpKb3dZdHdkdHlvOVRhY2toLTFRajBQMW1lMS1rZGpUaEp5WDJuaTJ1X2M5UW5LM3k0bFp5SkM0TkVwWTViYS1RMlFNcWk5SkVHbnVLbGtxYVNuNl9OanU4Mk5Ja2tUNTVBUDFSVVZ5cFBsQ3pncVZneVBQS3hTV3N3TEhzVm1hYldRLXc3?oc=5", "source": "India Infoline", "published": "2026-10-29 07:05", "score": 0.494, "label": "Positive"}, {"symbol": "SBC", "title": "20 Best Stocks Under 50 Rs In India October 2026 For High Returns", "link": "https://news.google.com/rss/articles/CBMidEFVX3lxTE92U3Fjd2lHOGFGOGZCWE1YTDJpVmo0TktIVk5LUkx5NkE2R3B5M0Y5VjBmZWRYS25aNjB3SlhWMVFVUVNrRVZQX3YzM2FiOHg4b0FhN3kwY1dkejdFWWtFd0dNNlEtRVh4TjNLQnVzRFJWa1ZO?oc=5", "source": "Samco", "published": "2026-10-29 06:51", "score": 0.718, "label": "Positive"}, {"symbol": "AEROFLEX", "title": "NSE: Growth levers, easing regulatory pressure underpin Jefferies' buy call", "link": "https://news.google.com/rss/articles/CBMi1gFBVV95cUxOWDh2RDkydGlLckd3VlBaTWo1NzZfQ1UwRUZzaDlleFQwQTR3MmdmQTlxWkIwTnpFblRKSnVLaHpxSUNVcnpkTmVxZFhuTWdQc1pKTEJJUGZqYnBOWjNVcVNzT2VTa1NLY3VmYXhpQU55Qkd5eTJjMmFWZ2JXM1dmTk1LeEZPQndQdjZadnRmS2pkbV81V3htOXVwUXFXcnVDNkM2VU9PNzR3VzhLUUpyWmw1dUtmWlVPN09BYzlJSEIzZ0RGc2hEemJNcUlPa1hnZFRMaG9B0gHbAUFVX3lxTE53SVEzdlA1N2syc1RkZHBqMW9qcng5UmpVZ1lMczg5VkI3VmFTTzFZckxIVzhScTZZUDRGc1Q3UnlwYkUzcmQ5ZmlaSGJ3NmJBanZxUExPSzdLVlJ2UUJtYUhZNGVOZ0x3c0cxcFhkcVBuOVRjSnJkTS1feGRqN2ZQMU1MaGtJUy15dlRwdnhmT0lSalh2YVN0WDFXWkhIMlJQZVh4RUFja0pDNzVxRHV0eWhTeXFWMTBBcGhTbnZUMG55aEpST2dhZFlocWUxdGl2RVJjMHVEYzJHUQ?oc=5", "source": "Business Standard", "published": "2026-10-29 06:44", "score": 0.542, "label": "Positive"}, {"symbol": "AEROFLEX", "title": "Aeroflex Industries (NSE:AEROFLEX): Did It Publish Q2 FY27 Financial Results?", "link": "https://news.google.com/rss/articles/CBMivAFBVV95cUxOUDdIXzZMbXllYVcydHVDazlNYnJkSm05eGt5eFBtTzEzWDBsOWpiUG1IdjFPaHVwQjNRZm11Zl93S211VmhlaWUxaDNMTmVhaGV3RkhkRnFFYU9rb0pCcWlFRDJHVmtLNXhmVGV0R0ZXbUNLajlVZlZsZGhMZkZqWjA5NEFlbVplSjF0cGwxTE1ob2FzQjFkem9nNkRhdEtzX2tqOUY2SXU2dEhaWVViTDB0QjVwWWw5UmRBdg?oc=5", "source": "Kalkine India", "published": "2026-10-29 06:42", "score": 0.0, "label": "Neutral"}, {"symbol": "AEROFLEX", "title": "Aeroflex zooms 18% on huge volume, over 31 mn shares change hands", "link": "https://news.google.com/rss/articles/CBMiygFBVV95cUxPM0hjTzhyVzdyUnJfQnc5eFZFNlRQbVREa2s0S1VnRFc0UlUtVzRrT1NCa3hHaC0wVXM3RjVRNE5wczd1Tk9idzk2OTY2MGQwUDJCNHFlVDQ1el9RWGl4Zm9sd1pJOU00T2t1RU1ZMzRHeXZ3YzNEWFlFV1RmTUFsakMxY1ZINVFONGxJb091cFhtbjV5QVJfSDVjODZHeWhxT0piOW9EaE9SZlVIcXNMS1JRcFNLbkxxOURKUUxKRmo1N0hPek1TNGNn0gHPAUFVX3lxTE50REw5VnZCd1NnOE1DMUVBeXJuQnpKOWlsNkZnMVNhTmlkZjY0OTY3bEhMaDBnNmdNRkNHdDVEdzhua0NCRW9sdGhoVnE2LUpuYVpJY2Ywbk1vTnlBY3REVHJoT2hIOU1yWTVrdVlDZ0pLZnVTNldwcDZ6dUNYRW5yblpqS3o5NWpDVlByeW5xS3o4ME02NTBZb1Y5VzdTZEloOXR1T3VzaTZxU2cwYVlGMGJIcEhsdVNrUmREYXdDQjRkOUJRV0hPTnMydVF5cw?oc=5", "source": "Business Standard", "published": "2026-10-29 06:38", "score": 0.318, "label": "Positive"}, {"symbol": "MARKET", "title": "Why is market rallying today? Sensex jumps 900 points, Nifty above 22,900. 6 key factors behind Rs 5 lakh", "link": "https://news.google.com/rss/articles/CBMikwJBVV95cUxPdk9rN2FKLVE5VTg4S2phUUhUUjlCTjhVTjEtZVJqbmhiUkx6aVlfc2o2ZzNOVDVOVEltQm14TlRFYU5tTVZja0pnRC0xbC13aEZzeVYtUGRCTGEwVDA3ZEI4SzZybkpmNW9QNFBJTmkzZ2FEN25CQk5yT3h5ZXZHdUlLUGo3blE1TlAyQVJBTllJdl8tQkF6TGlEYkJ6YURwd05EMFlWUXNIT1NZRnE4WmZQTXBKX1h2LXJHT0dSZ1V0S1RKbFNDZkZXQTNmY2xObEoyTGpaSmNPaG9zR19zLUlld3pBR0dYajN4NW45Ui14TlV2dGNwX2FSXzNHNlh4Vy1CZmpaUkJpQ244ODJUY1d5MNIBmAJBVV95cUxPYWJWLV9VVHRFQjZwWFhwRnFQRlBJTjRGSzA2R0ZWUnhsMUlDSjBMMlZpaTVNZVA5Z0h0Z0dmdzZsVHpvRkJlalNpMTBUeWxJWXV4VWJ6Y0pyTVE5WHlfczZ1RkdEaWlzcDlKWjdoS3d6aWF5S2hGeThzTkd0dHdLTDQxMkVQZ25feFhxUFlub3NueHJJVHQ0TEttTzRhOWpKSWkwcWZWbmJhTW16RUFWa2V4bmc5SjE0eHlVVVVvbDRlMWtXV3d6MG43UmlBMnkxTlJCWDJQUGY0YUpSRGFmd01EenBnZ0VQREE5ZGliZTZiaDBnNEhlcUFSN0IzV3Izdlk5NGdqb2VkSnVUNDlZQ3ZROTA5QUc4?oc=5", "source": "The Economic Times", "published": "2026-10-29 05:31", "score": 0.691, "label": "Positive"}, {"symbol": "AEROFLEX", "title": "Aeroflex Industries Share Price Surges 14% After Q2: Profit Jumps 157%, Why the Depreciation Change Matters", "link": "https://news.google.com/rss/articles/CBMi3AFBVV95cUxNanpjQUFtMlRJTE9VYkRiZHVsdDd4bzhuRTd4MlpDd2RvRzZYTDN0UzdQaDJwcEQwaWc4cktjUzRPVUFBN2RRY2czNlhDRVJ5WnlDMHdyTmpUb2J1ekgtZ3RwcHVJYnptZVV2dWJxX0xuRWU1UkVVVjBmOU5Pd2FBMWl2ZkV6TFlodUt1MUNwb2dRNG9aaTRrenRrU3g3ZnE2TXFWU2NHUjYxUVJVOWpYRG5RdUNRMUdvSC16ZGtQb25uZnVNd1BPZHBpOE80MFNMYy04SS1TaGVSNWtl?oc=5", "source": "Univest", "published": "2026-10-29 05:29", "score": 0.827, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock Markets Today: Sensex, Nifty rise in early trade on buying in RIL FII inflows", "link": "https://news.google.com/rss/articles/CBMiwAFBVV95cUxPbTVraU16TkYwWTUwVXpUbzRPV2FHUzNLQk5KVk4zS2RWdzhZLXdTTFVnaV9EcnZwR0ozcHQ2VzFYTDZTeUJ3MzFKM3ZNbEhPM2c4UmZySndFcHFKeG1oQnhwZ3Rpb0lJQk5obzhrWHNreTUwbGUwY3IydU5EMGNPTHppNy1XM1ZiWUFJY2ZKSkRGZjdzN2ZUaHMwbVdtbXo4WnhBVVA5NW1BYnVFMVF1eWhDZnBVYTRpZ1NaOGdNQjLSAcMBQVVfeXFMUE14LWs0aDE1M29hdE1ZemNOTkdVbXNoS1ZKQzc4N29zdkx1MGtYY29TZXRWSWdxdzAyX1ZtMHYyeVhZRG1hbFZlWGduaXhJRWgyUnl6QUljNUZMUmU2X0xLUWZpTnpNMFZuRW1zU3FjeF82eDVTZDRpYzJuTzZhMHlQTW5YNC1HX1BBXzRyWkxwVkNCYXpQeldNR1puMDdIaWtKeURJdXNWTHVENWxPRnBuVEkwdDI5ZDB1OTBnTEstUDNF?oc=5", "source": "Rediff", "published": "2026-10-29 05:18", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty rise in early trade on Reliance buying, foreign inflows", "link": "https://news.google.com/rss/articles/CBMiyAFBVV95cUxNbm9FWDJhbHFCMEpNTC1uZ1dtTWhHd09pYzd6N0s5aTJfclVMU3hmTmVoQVQ4UUxiWXQ2THJ6SkxJSDFIVGRfT3VHZFktS0d1M09BQzIxc1Y3OHE4Vjg5TjYwYjJ6UWpSRk9heE0xdWtSTThObUczdk51dEJmMUlZeXI5eExPQnF6OHp5Z3lna2RhVG9LemNROEkyVFBYUGVwZS04MWxzZkZqbjlpRGd2ekFXZzJ3VHB1YkpOeTBpQ3dabmtjOUFXdtIBzwFBVV95cUxNUm83blpBb3pITXIyTnhpekdUM19lZkFHR3pwOVlxaGRZbHhZeVJ0akN1MW4zSk9EdjgzRl9sUnZUMy1aWkVDQTJJaVJYeVI5SHdnYUVwM3VseEdjNkU2aDU5MlZrdkw3alBCMFlROTRBWVlGMnBHeGFhZXhxSFFRdzU3MjZzSS13djBVcXNpSDVvSlNtSVNkT0JPTmg3SkZ4amFZMFhYTG5uVjN0ZlNmSy02VnUzWlBEaWhZUFlhQmJYakZJQVUxZFJMWnRDZDg?oc=5", "source": "The Hindu", "published": "2026-10-29 05:17", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty Open Higher as Fed Holds Rates; Oil Dips Slightly", "link": "https://news.google.com/rss/articles/CBMi2AFBVV95cUxOWmtQMEZ5NFEwOHMtVlFJWGFKY005a2RTMWF4NlNNcXFQN1RYMmNHeDVVbmx2YlA0Z0xSUGs3aWZlUUJqVmpDMjhOU1M4enFVbFhTOTZEWmZVUFFUZ2JHSzNmRU5GaDhlQjRNUEpuTUd3aFI4MjJYa0tXamJUU3RXQmlJYXFRc2ZVU2UwSkIyNXF4SU5HRjhlZ1UwUktObGJjU29FRlBTSDJva29XUlVudGd5NldOcmxaTU14OFhsTi05Q2V5NEtFQXY5T0MzQnF2Smo5SWdTV1o?oc=5", "source": "HDFC Sky", "published": "2026-10-29 04:44", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex Today Trades Higher | Nifty Above 22,700 | Jio Platforms Up 4%", "link": "https://news.google.com/rss/articles/CBMixAFBVV95cUxPdHRLMXRySU0yU0lBdUJDU1RzcEpvM01WZjNEOXlaTlJGd2FnZk1fNUxTY2p0Q2lrNUpNOFN6UkNpc2xKNVBTYVJmRkJXaEJyX0Z0eUoxOG9kZmlic1hQaE84eWR4TU9JNDhVa243amFRMC11bjRzN3pwZHpiV2N6VlVMTEJqR2gtYmk5WExRek40TWtvOGtvcHRhTU14MGhaYWtsZHBianlEajd0dnFGdElaR0FIbmQyTkxMSHhjZG1nUTBL?oc=5", "source": "Equitymaster", "published": "2026-10-29 04:35", "score": 0.402, "label": "Positive"}, {"symbol": "AEROFLEX", "title": "Why are Aeroflex Industries shares rallying over 12% today? Here's what's driving the stock", "link": "https://news.google.com/rss/articles/CBMi0gFBVV95cUxQY2xISHBTaDU1UWd6TWtwbHpNS3NmbFNCcHZYWU1VUWdjNVAyM2phUmZUVTJkZWowcjZ6VzhreGN0dFBWQkIxaTFyX19aeC0xTFgzSF90eldySGttWEdkQjRRLU02eEdZVk1wd0RsT2xhX2pBaDhIdWc2d3pKMl9XbDBTb1Q1LW1OWl9UYThkRThlYno2TjBhakJXSlZYemhHSFRVdUNBU1lLc0h5OFBRdFZRMXBPZTNWeGpyNUJRTEc3Vm9tVTRhR0dlOTBuQ2ZoWmc?oc=5", "source": "Business Upturn", "published": "2026-10-29 04:11", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Stock Market Highlights: Sensex Jumps 905 Points, Nifty 50 Ends Above 22,900; Adani Stocks, Kotak Bank Lead Rally", "link": "https://news.google.com/rss/articles/CBMi5gFBVV95cUxNd2cxcjN4THQ4TFZtR2FweWRJR1BWYmpUcDJTZlRBVWZEeGZYR3R5RFNsYmFzM1ppNlN0Ykw4ZDdZR3l1Y05qZWdjZGpHOEt0QWZHcWFEQmVEc2RkMzl2cFZGbzV6eWFsZU42Nm1YUWZ1QTM4QVZIWmttM056VDhidk1sNmQ0Z3FDU3V1T3c3THFrTGloTjVUU2FHN3pKRUlfXzk1NkhzWTBmTWxWdGk2OVRwTWlLNmpLb1ZDamdaYVFwNHBtdzJObklHbXVEYzhCZHowY0o0OGs4WC1OTDl4WnVtUS1ld9IB7gFBVV95cUxObXhwRThRVnFsTlU0c3E5ejlpZEV1TTJ1QzBWd1JraWdFVWdaMjgwV2p6UUZGSGx6U0Rrajd6cjRlQUdocWczWDUzcGhpSE9YQ2g0RlN2eGg4M01aUHM2TzdPMm1Id1BqVS1pTnQ5eEl5MEZIaGQ2YVBRYlZ2ZU9hdVVkeGJ3NVVVQUpuRlVKQy1MdDl5SHdQUzFhM1A1eFdOcWVKN0k0cmlJOHN2NlNoamZaNlZIWF9GQ1JMWHRFM2drU3FTVERXX2ZYYlFUOGo3dmpVN3N3YUFNV1pTbzJwQUJkUnRLSFV3SXBFZkFn?oc=5", "source": "NDTV Profit", "published": "2026-10-29 03:51", "score": 0.827, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty trade higher after US Fed holds rates; crude oil remains a concern", "link": "https://news.google.com/rss/articles/CBMiwgFBVV95cUxNQXViREYtTGFhN2E1dTNudm5xR0VHZU1kakd2WHZiNDZXV3VvWFRhVXVvUlAxU3FEVTlmeHdWbjc3VFRvVmNvczJwTkVPbldUejYza0FYcFBDVTFrWHVtS2xLYXhPNjNkLWRmbE5wMDNTbWY2Mm92UGNhZDhaNUdZSF9GODkyMjhselJ0eDVQbGpscENobHRpWkxBU1F3R2cwWVR4cDNDVkd4dWZ1dS1nRkhEQTA4WlBnZGZERndyM1M2UdIBxwFBVV95cUxQV2VVVC1qZXc5RGl2TGRPd0Y5YTFKQV9GWFVLV3o1WHpDVldxaDdWVEljWGxsTVViS2R6Q1BXNTNJYXVMX1g5NDZ5cUFiOUNjMnlUZ1NHYWlqUUhRUWl3S29FR3haNFl5OGZnakRVbmVNWjdnclA1anlWbDZ2aGFXZ29KQnJncXcyWGZjd3pCYVBmZjJDbDJ5UXFxanBlcm1kNXRBRlo0UmlQaVBxWkF6eEV5T3ZjamRZY0dpc2dHS04xWjI0NFhv?oc=5", "source": "India Today", "published": "2026-10-29 03:50", "score": -0.25, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock Market Today: Gift Nifty, US Fed Policy To Oil Prices; Five Key Factors For Sensex, Nifty 50 On October 29", "link": "https://news.google.com/rss/articles/CBMi9gFBVV95cUxQTkdjeEhGQ0k3SHlKU0xzYmpBYVV2MWlyVl9laFRPY2N3WXRFWFEtdDQ3ZUU2YWdhaGpab1FKRXZMTlVHYmRHODQtZEUyVk5aVVc2c0hnV2FsYndnQ0FsaGMtTnhzcWhTMGZNeHBNbWxITEN3Y1ZjSTZMZ1Q1UjZjX1E5elRJdXZFd1dPeEx0ZzBfai1qQjA4TDZyRUZHY3V2Uk9mMW9qYWtrXzg4ZVEzU0IxSUlkTlZzM2VVcUpyU2lDN1lRSThQZFExVTNBVVdHOTUzem5qTXBreHJYV0g4c1ktRG0wYVpLSGJDcnA1ODZNbWtRa0HSAf4BQVVfeXFMT1NWT0FQYUNvd1FuaW1kcGpueVB0TmQ0THlZckR5aUlqaVViM0xYY2NTb0szRzVpa1hPRUk4MVo2WmNzc0gtTFF6Y2paZUs3VzZRRW5YZHJaanNDenJObUpxSW1BVHhkNWhBNV9teHVUTm5ERkx0V0tRQnVYNW1GUGY0VFp2RnFUc1BaRHlyeVpYYUMtbkpmanpoVk9aQ21wMzQwbnhqT2FiM1o2ZF9xemRBbzZiYWJwOWFZcTNtVHRMUDZvYkZKbk1EVXFRQ1ZSLWJYMXVJMUtzVVVyRDB5Q0ViNV9wTFdxdnFxWlFmN1RMZ2FDbHJlSFB3UVNDNEE?oc=5", "source": "NDTV Profit", "published": "2026-10-29 01:39", "score": 0.807, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock market outlook today, 29 Oct: Sensex, Nifty prediction - DJIA, S&amp;P, NASDAQ, GIFT Nifty, Kospi, Nikkei, Taiwan cues", "link": "https://news.google.com/rss/articles/CBMihAJBVV95cUxPbGZqMHp2VC02aEFPMWpFUDdkcGlUbGVqSHFVUTdtem9scXhMSTdwRHlQNWxyeGFjd19oVUJBLWtEWXA4bGVSVFlHY3BMTzdhc2RlekgyWmpWVFBYdThfNGJqT05SREFmb2NVT3hsZ0IxSWlVSXVWXzhyeUVQYWlWQWV5OUlmdDA1dldGM1JQdjBSZEtackdibmVLVEFwdWo3M0lha3hvdTNaNEZYTzhXQ01ic3lPMlFjSWFIRHJDeGlTTVR5dUc5S0RvaW85aG82T2xwdnFoSy1yTDRWNnloQ2UxaUpWbW9xYTFHNGw4dDJZMWoxVEUtZER0NlFQa2p2NHZQddIBigJBVV95cUxOYWFiZ291M3RVdE1Oc3JKM05Nd0d0LTM3dWFHS2laLXF6M1ltczBYWlh0SUFtejJZVU9lZlM1R0FWcldBZGRvT2hyWjlBZkl0QV8wUTFqN2J3THNzUGtYekI3MU5oRUVTbklKMXp4Q3NZQUJUaE4zaUJvVXFCRDZiXzN2NTZUWlRQdkRpNWFFdDdpTi0wSTR6ejhNMXBVQWNoMFI0MzVCckFaeklBMUZINEZ6czM0YjdpRjBId1lfVXFqYWszN0tvRy1leWhDZEJZSDBQa2lzdUtIZjNqVHpFcTBJZFZRbzJTMVZkS3BKVUVERWdhWUhlQkdUWGlKOHhuWXpqRDFTbnFHUQ?oc=5", "source": "Livemint", "published": "2026-10-29 01:15", "score": 0.842, "label": "Positive"}, {"symbol": "AEROFLEX", "title": "Stocks to Watch Today: Dr Reddys Labs, Fortis Healthcare, Titagarh Rail, Hero MotoCorp, RR Kabel, Meesho,...", "link": "https://news.google.com/rss/articles/CBMivwJBVV95cUxOckZvTEdLSXpNR2ZfZFZRSlBSb251aFdLSERNTF9tTEVuOWt2a3JoVG9GWEZZa1B5VTVCZDc3Sm40VWlpZGJ0TWQzcWJNbmJjenNTcVpBUW83Mm1ySWpaYUVabmpaUHhGTmxWMjNqWWdmcHJtWWJvS3haYzEzY1J5MHg1YmVlV2FiTkZRTGNyQ1Yxb05WUFNiaDJNVjRjRHBjZHR6SmYyakpkNXFRWm1rcnpxaDlUVktBTWUtaTVoNjRjejJJUUVDeEl0ak5qWjBBb291eERuUHp2dkNNTXJCczFSaE9ycUpic0hZY2llYTFSdmNUMS1pQ3ZwRDczNkZ2UU9xMFNTLV9XMVF5Y1dCcTRfeE1aR2FqMW85ekJCMGhUWTY5ejhEd0NLT0tDTTdKR3pOVklydkxjX0pSb0R30gHEAkFVX3lxTE4zbTVMdTBDbDhuSFZpOUNZQWlQc000SVprR1hFRHIzajZFVkhEUGFRRjhXaDVwai15X2VfQUxVYnVnRW00QmxzZktoRms4UjB5N3Q0U2ZSNElMWktubjhxcVdBY0tlSldIMkI5czlWZU1QNkF5dlRINHBOa2VKakp0RnFMbUhiMzFNSHEtOHN6QnZxUEM3aHhHSF94cC1kMEtFck5QM3A4RzBydk83dHFETWxkOWFhYzltM0RPTkdMMTl2NXp0RUtsTFJrRjU4dlNWcjFTXzBYTEdQSFB3STBXY2YyR2tGNnFTTlBTRGhJODdpbDdPRVJBUlFzN0FxWnpQN05vVzVWSDN4R2ZzWlJ0bFN5dlloOVh5QWlWZWJHTGtWRmtXOG85djNCdlhNM3V4bTNSSl91QlZoOFVKSzBENVVEaw?oc=5", "source": "Moneycontrol.com", "published": "2026-10-29 01:01", "score": 0.557, "label": "Positive"}, {"symbol": "MARKET", "title": "How can US Fed FOMC meeting outcome impact Indian stock market? Sensex, Nifty to rise? Experts decode", "link": "https://news.google.com/rss/articles/CBMi_AFBVV95cUxOZFZvM3NMeWFaZWdDOXJWX3Y3dnA3RjJmMUlZNjZUU3I4RlRwemFzWjNLc2VGSXIxOThvYXJmekVZMkJDNjkxbkV0SVNRWjI2ZGdsOFctY2Z3TExhbFFKUXlfUHZXUG5RNmVtVktMLUtLVjN1WmdmM2RvQUs5b0gwVlBhbkEwdlFkN1duNURLcGJ2Ni1fSVpCdXpORXlFR1JudmYyZHM4U3RsRFpuMUxtakh2MjFMLUJKMkRoSmZmU3lSRmxhWHpNLUlDS2E2c2VGbU5fV0d1dW5jc2tpb1VQWjQzYV9sRmh4Ykk5Vk5rLWR4UkZZZFdJNW1yNzDSAYICQVVfeXFMTXhyQlhLeEtxLW9oR0lQcHoxNTBaaTdqaDgyMWVYVXhJZXlteDZGUEcwUjlZd05rUXdSRC1yMmFZWkl6ZEZZRmFiZ0dBSFBMcTVzU3ZORG82VzZ6VGVseW0yZGZxR1M4V1VLTjI0aDJfU29EZ0NqT1VsaktXNTVoeXdPNlNxYlNpSWZpOXpTQzB4c1lrb2Y3T1F1MVp2T08xaW4zNTVobVpQTmlfdlRITThka2hhc1U5WTF5cXgtXzBZdXlYbGVPT0t5OTd1MXZnTUtMWUxVRUFwbWlPWmxTeFRKV0VvNkh6U3pEUVdBZ04wSzJaN0dEWUFsWnMteWpuZzB3?oc=5", "source": "Livemint", "published": "2026-10-28 18:46", "score": 0.47, "label": "Positive"}, {"symbol": "SYRMA", "title": "AB Cotspin India Yearly results, Financial Summary", "link": "https://news.google.com/rss/articles/CBMihgFBVV95cUxNV3ctWkhyVUNIVThaZG1RLXlxV0I5N1BtamJzcGtCYlU5R1Y3ajF6M2ltLVhYQkxWTl8zYjh5Uk5tTkUwSkRoa1hBRDhjZVlmRVVaRWhkTkhESjBVVUpoZml3d09VRkgxTlhZd1R5SWF3YXR5M1lGZEZEbkRURkktNFZlNzdQZw?oc=5", "source": "The Economic Times", "published": "2026-10-28 17:25", "score": 0.0, "label": "Neutral"}, {"symbol": "SYRMA", "title": "Half Yearly Results, Half yearly Earnings for Shree Marutinandan", "link": "https://news.google.com/rss/articles/CBMimgFBVV95cUxOdFhDTHdVdVNpekFDUUlFSHM5Y1dBVmFHXzlpMEU1UXFzR2VtNlM0aVZEdkhDMGdLRGlLVWFxUFlvSE1jb0xCMUxwbm9RWmp2VGh3SkxwdXdJY1JucnFpcm9wT3JmcFM3cmNuRmhNOTVmcGxvQ21CMXdWT0lkZG5sMHdkWUY0V25YNGhqVVpYbERybUpPVXFfMThR?oc=5", "source": "The Economic Times", "published": "2026-10-28 16:59", "score": 0.0, "label": "Neutral"}, {"symbol": "RATNAVEER", "title": "Ratnaveer Precision Engineering Q2 FY27 Earnings Call on 3 Nov", "link": "https://news.google.com/rss/articles/CBMi1gFBVV95cUxOT0FlR3g5MTluX3phZ0tWLW1iVHAzbUh0dGFBRjcyLTBFQTl5bXkweTNIYlAtYjFSYlhBUFJYQ05VOVUzUFRLaDhwcmg0b2xZSE1JMV9rNlpuMFFDYTljQnpjdE5rMDJ2YWxGaDJZMFpCWFd5RDBuYjFvbE8xS085dmc0aktudXE5MDc5UlhCUVlQSVBtRnFwbUtwNG1lNkFVM2tWYzNLeDdHTGlhUjBXNEVMZ011Q0RJVkVoM24tWTNHWERXbHZ5U1hhOTRDQ0RmSlBFWDdn?oc=5", "source": "Kalkine India", "published": "2026-10-28 13:42", "score": 0.0, "label": "Neutral"}, {"symbol": "AETHER", "title": "SRF Share Price Today - SRF on NSE/BSE", "link": "https://news.google.com/rss/articles/CBMiS0FVX3lxTE92aVdVcHo2Sk5FU3FpVjJraHRrdzkzcHk3cWNySWN5NTF4T3dqOTRLMXNoOU1XVnRaNzZpY0FYTHpPcXZreE1VTWZFSQ?oc=5", "source": "scanx.trade", "published": "2026-10-28 12:26", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Indian markets end lower as IT weakness and crude oil concerns weigh on sentiment", "link": "https://news.google.com/rss/articles/CBMi0AFBVV95cUxQOWZoUXlONnJ6X2V1bFJOclpWWVlXcGVzWmtNYzdlbHJoZThoMEJ3RnZoUlJsOTkzal9jZWtyY3hPTnU4R3dwZ0JpdDcwT0RvNXlhZ2M5TUJ1QzljYktmNmpYbkxfREVHVklXbkpFc2dfb3cyRTdYX1VvYnFRbkczSEZuY0cweG0yRVdsVUluVHRBbE1IZGZjMXAxU1FBRUhPaXZvNkhmdHFKLU0tVTlvc3JMSldjTGRsY1JSTzVtMk1vNTRzR2NZbjZObG5jUG8z0gHeAUFVX3lxTE5zYWI2anl3OExsVTF0RFVuM0FnbzdYQXNQaDNoME8tQ1c4ejE2NWFpVG5aa1BaeXpIc2drSUFIcjB4NkFzUkpydmFxODJnaEp2VnNsMEthLTN3TS1PaXM5b05LQUxIWkdLdVVQMXBmcF9LUTlkUThjVzFoMG1URjhHemxxX090TDBSS3lqOXNWT0lGVmdxQy0welU4RDZySjV6TGhrcXFDSVBJNW1xTmg4RUlCY05EcnY0cTBpVU5vYURybm1hM2l5V0ZZWm00cTNZdEZtQkUzaUVNdXJKUQ?oc=5", "source": "The New Indian Express", "published": "2026-10-28 12:18", "score": -0.807, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex, Nifty Slip as Crude Near $115; IT, O&amp;G Drag Markets", "link": "https://news.google.com/rss/articles/CBMiywFBVV95cUxPWW9WemFsdTYxd0YtRXFGNGktZFJxM2lCV0ozWnFvRElEdWExdDdDSmRGVU5Gb3RBanh0Qld6OUNyVnJjR2JGSnFEMUttV3Bjazc0eWM3V0FEcm5feE5aV0t2Z2FlT0NiMUkyX1c5UlAtZmxRQkNwX1IzMmRib2NWaWs2V1ZsSUVsRUR4S29FdmV1dkdzaGJaRWdtelhacGRjcmFITlU5RndRMWxUcy1wTkxReDNCci1TeDhvenZhZXhsUG4tVjhFQTF0dw?oc=5", "source": "HDFC Sky", "published": "2026-10-28 12:04", "score": -0.649, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex ends in red on selling in IT stocks, rising crude oil prices", "link": "https://news.google.com/rss/articles/CBMingFBVV95cUxPWHdjeTlxY29wcTBTRVJKZlg0eklLVDZXX005c3AxOG1ueDdXV0NmcWJHNVFIaXBlX2FUaVI3SUhqaUY2RG9rc2JqWmppVnhPQzlPdjY5ODFFajZ2X0xLMnNwYWNIZXlXX205aTBRTm40WnJncDNOeFRPdWU4ZzhjNlVQSUNoWkxaSEZNU0E0aXAzZzlNalhkRWc1M1NXUQ?oc=5", "source": "DD India", "published": "2026-10-28 11:30", "score": -0.572, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex, Nifty decline amid rising crude, US Fed caution", "link": "https://news.google.com/rss/articles/CBMixAFBVV95cUxQMWFfb0lXdlExR0JWV3kxcmhLZlZERWJiWUFmTjhBb21lRExvaGJrNWJPWnUxMTlsQkNMMUxzY2xHMFZPTXFsczZnZWo4cWNpaTNxWVNyWXNCWEsxdnpWd2NmZkxBU3ltMUE4T29wYWRkN2ZXLUdIX3JkMUtVZGFUUTNQQnoxMVZkUVZrOEVINEdkNmotNFg3S051T1VRSVVnU3g4MVVEeVc4Z2pNcXFnY3FwMXdKUHQxWVhoTDdtZUhNMUNK0gHHAUFVX3lxTFAwOFVDVDNYOTFkT1Q4dmtzeTd5NEdfcmE2Vmd6VGhicmY4ZS1hY1VfZTgwdFNBZmtTRVA3bjNCTVotbi1vN1RzUkJ1aEJ1elhETF9GOUFxZGZFZGV5ZzAxaXVoT1U0MG1hTm9EdUtVRmxpZnQ0Mi1jeTZFdnFleWZTQjltQ3lVeDJvLWNIQUJrN2lNdzdiVXpXUUFpbW9WN2M0cGQ2X1FrSXhuVEFtNGNqV29lTGt6clI4M05jRVppenJnM0dGalE?oc=5", "source": "Rediff", "published": "2026-10-28 11:06", "score": -0.557, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex Today Ends 353 Points Lower | Nifty Below 22,700 | AWL Agri Business Down 6%", "link": "https://news.google.com/rss/articles/CBMi1wFBVV95cUxQMzRmeU5idFdCSUtXRDhnSndONWszVVlrLWVlbUxpSERVY3pFLVdZSjdBZmoxY2o2bGdnQU1rNDhXcGk0WTlUeHRoT0syaG4tdzJ6d0E1TTZUWlVJX2g3YzcweXNYZnZzNmR1TkdQazRvQk1Md2VDd1hnT3VKQnZHSnZQWlprVUY0N0dxUXVFck5ETXRZN2w0TjRqSEYwMkNPSjZWa29MaGpyOHNMRFBBLUI1Y2Qzc2NYU1RvaE9FQVROTzFwNEdJWkx5NXlTSDU2X2tLQWJaaw?oc=5", "source": "Equitymaster", "published": "2026-10-28 10:43", "score": 0.226, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex falls 353 points, Nifty below 22,700 as IT and oil stocks drag", "link": "https://news.google.com/rss/articles/CBMizAFBVV95cUxNZTliNHpyYmJJOEJwOHk5MWkyOHFFTnlnN2EzUXdBR2pHVl9ZZHlZM0pTLTZGb0lhSXdaOGhfakNheE9OLW93WHd2S2o5TEJRdHBDR2lSdkxJeTR6TGVzSk5uZy1zWVBCVWl1R2NDdmZiT0RpN295T3BDWGxNcy1GcDFTUWpSZXBQbVVOc0luTm1Za2dUYkNCYVRtLXVNeHdLTUhzWXhrbUxKTmJWbDI3QkN2UjljV1l4bUdoUjRiX1VUTHpKUHZvbmtXR03SAdIBQVVfeXFMUHFvV2hZS2dRVGRqRGtEMWVxQVhaalp6cVBGbVVUZzZTNWIzS19Zbkk2SVR1Z0syU1diTmlQRXNVYzEzUUNRdzdtelp4ZEpTazJTV2JFX2ZhMnNBQkFpQ1p2MFlBZlg4SkxBT0s4Q2R4UXBxTk9KdlpQd1g2ZUh0djZTRTdTQ1RnUXdNQnR0RWZIMG03dWd3Z1JmTEQ0TkNmamdFQTZGbTJCX1ZSUTZKRFZlZS1wRzU5VFZ0VEJiNnYxM25TNjNYY1VScTBBVnJMczdB?oc=5", "source": "India Today", "published": "2026-10-28 10:40", "score": -0.202, "label": "Negative"}, {"symbol": "SYRMA", "title": "Syrma SGS Technology (NSEI:SYRMA) Stock Forecast &amp; Analyst Predictions", "link": "https://news.google.com/rss/articles/CBMiiAFBVV95cUxOdkctWjFPZDVydlFqbGVBQmtXM184Ny1vUmw1dnFzSGNyTmNRRzd4dWVLTFZEeXNRbjRYdng5eXhaaGE4cDV3RHNBd21HeGJZYVhDbFU5anp4LURYeUFpeVV0bUk3e</t>
+          <t>CR2VuX2lDWlF4NDhWSTFNVVVyVE9VbHJrSUwzZnJPdG9FVE1NNHVIcWlnMEpiWWZfVjJrZ1hmbE5zTXJXdVptRS05V1ZqM0VpVENxV1gyaDZCT2t4c1Y3d1lQTk5zUEHSAdIBQVVfeXFMTVNfZHAtb3RQNmU4T09SV0dBZFdLSkZJUUdRV2VZSjRUaUtVR05CRVNpR2EwVy1GR3NtdHlrYndwZmZ0T2d5NkNCeDAyS0M2Y1ZkX0oyUks1LXpkTkFqUnNvWHYwYWw1MTJDQno1NWZxT3pDS3F4Z1B2a3ZKTTlkNFM4ZGZicWlSYVV3WTFqbHBWNW05ZmpZZXk1akFpQTl0YWJ3V1FIdGFKOHB4VXVNdkgyanNmdTFYRUczZ2NleW5xaVNiRkNmXzh4dXQ1b2YtM3hB?oc=5", "source": "The Sunday Guardian", "published": "2026-10-30 06:14", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty open flat as crude oil prices remain elevated; IT stocks gain", "link": "https://news.google.com/rss/articles/CBMiogFBVV95cUxNMzlJdG1RZmREVmFLalpRMGpfR2k0a010SjVMTk0za3NnazZxdlE1MlZ6TTczdW9aM2s0ZGZsVmlBcTJvSnJ4ZlhTZ0JubW5kTDR6aE9FR0p3ekxHeU9fOHptZVRBNVdHd3lNSVJVZ1F1NzNFcURBRTQ4WjRBNEFqZE1Gamx2VFY2NHJaZkxYRHdiNUhzcDdCck5lZk1WTlhnQWc?oc=5", "source": "Telangana Today", "published": "2026-10-30 05:55", "score": 0.103, "label": "Neutral"}, {"symbol": "MARKET", "title": "BSE IT index set to report 2nd sharpest monthly rally in over two decades", "link": "https://news.google.com/rss/articles/CBMi1wFBVV95cUxNNlZWX3NYV0RDNkQxcXNfZ3Z3VEZwVDY3ejdUOElORUN2YXd3eFNBODctaDV5a3ZrT29fNnY3VzRtTjJOSVdwVVNCRW9LZU5kOWhJZFE1UHlLaGk2VHcyVGZMWGhJUE1KNlR0SkdRN1hpVkhvOG16Y1dSZm5oWEpNYU9oeW11QjEzV3FzbVVDcldGTXJWNng1bHdNbHQtaFlRUGpqWHpUbTVESzVBQnBrT3NoYWVpdS0tYlQzaVRveWhLZG8tN2NQSy00V29SWWdJUEJBTTBHY9IB3AFBVV95cUxQNzFWYUNDdTRJdVR5ZEw4N0RDYXdwaEFTM21GTTZoQ3hLbjNQOGZHTTFjSWk1VXpuY0lmMGZJZlk5ZFdCZkhoX3U2ek5wZU5LbDBnczctRmJxaWFxNVl2TjZWaktwTDBSWjVMTEhBZGh0ZGNoSXN5TEdvYzVqaUtHQ2pCQmZYTXppVmJrdzN0N0hCVTZSRzc2cGdtVTJpREFoUGxQclFpWmdIWUZQVkViaFNwd293dEp3a3BpbW5nZVRCdkZvd2czWXFhLWFlbGlMN3ZYQjJ6b2t3cWlf?oc=5", "source": "Business Standard", "published": "2026-10-30 05:50", "score": 0.459, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty turn lower; broader markets crash as oil tops $116/barrel. What lies ahead?", "link": "https://news.google.com/rss/articles/CBMi2AJBVV95cUxOZEZkOUo3elRXQW41eS1KOUQ0S3NvWFE1OTNHVy04WW1BeHhDV3djcGFrem5PMS10dEVmamxsYjEwYnNJZ1BVbTNwVnQySHpKZ2RPd1NzempiTGp3UTMySEc5d011SkdOYzFXUzlPd0hRLTREMGRmQVZLS0FyNWUwaDNnUm1nSjhISzYtNGNsZEF6VWZVOEc0bjJ5azRJODFKWVZyZldCeUJtbUg4Z19GWEUtWFNQLVA4azNtVkZ6UWNMcDk0ZWdEYmdVS05WQ0RLZElsQ2I1RjVXbUZZaHBaSF9lay1BQzNuMlc5b2o5Uk1oWmNMLU84dmQzRnZub2RXbjVYVlZ4bjVKTVpkaHZLeDRZcjZVNnpocnRTMU00eGQxZHZUbGNGemN3SFl1T1NzbXBCTmdMU3BuYWZMc0pJbmVnOTFCb0dUeXFhRXU3bGNqUjNzamVGQ9IB9AFBVV95cUxOamxtQkl4aWpPQXZ3RXdZblRPa085YklxbVh2ZXczb1BhNGdoLWpOSWF6OEdHTjcydlA4eXlUOHpZMUdNMk45VDNGNXJacFBra25ycnNGQlFJT090el9yc3ZjZ3NYRmhZa0VHX1JEOER2RHQyV3RXRURtUnZrQk5Xci04Wk41X1RTSXhJN0haNmtVNUFpbmVMR0F6VzFPZHliV0dHMU9iR05WTWFPb29QazVvRXk0eVNLb1hfNXlIclJ6YWhfa0ZUc25Xdm5fLWZhWEhHUGk3SHZHNkxKUUpqRm9KdjdyREFhdV8xeXpkMll4aEZk?oc=5", "source": "The Economic Times", "published": "2026-10-30 05:36", "score": -0.34, "label": "Negative"}, {"symbol": "MARKET", "title": "Breakout stocks: Adani Ports, Nykaa, Saregama on radar; analyst tells why", "link": "https://news.google.com/rss/articles/CBMi0gFBVV95cUxOTW50Tkl2NDNWMDEzblZlNmpXRTdHSDNFVkpwNGZIQjJDVTJ0OGJWeVFPWjIwclB4TU9meUs5d25nZUYxU0VYWlRZQjRGSV9PdERaTVRWY1VOcWxXX1pJY0p6WDJ2LWN5N0ZqYXBRSnE0Vzd6Y2MtTWduaTBURU04SXJCVVRBN0RNOVRqcmJDb1hRWW1hdFkzZ2NNM0hGU2RNLVMzVG9taU5XNFBFdkpzNlQ5WDJVckRFTmNKMDFTckRsblJoX2Y0S1czWlc2dDhBMmfSAdcBQVVfeXFMTmQ5Rm4yV2dIQS1VOFR0clFWLUdUTlZUR1A5VVYzV2NhVzdhZXJCMGhKMlNxMElXT3F1UFdTbWl2bWs2N0Iya0U0WHhxZld1U29mRWlwYU1RWnlNOEZmQ3QzQnlIQkFsRjRnMFl3QlZ0c3lfT1NFQk5GVWV0cmQtT093RWE4UTNXMGx5dWZBenZCMmYxak41TkFYNXJEUWFTSlkxWEpsNGFsTl80SE85NVVWYTBiSk9wcG9BVF9jLWpiaVltQWpVVEsyTk9KX2luU1ZsUTA3aHc?oc=5", "source": "Business Standard", "published": "2026-10-30 05:14", "score": 0.421, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty Open Volatile; India VIX Rises, Crude Above $116", "link": "https://news.google.com/rss/articles/CBMixgFBVV95cUxQY2daQnV3TThDSXViZGppTlJha2tMZVU4ZEV6Smw5ai13RUxwa3ZoODdGYTYwLS16eW1UdlY3SHVyQjVSLVAxUlVXNmhiTVNSdTFHVXNNYk94VXY2a1Q4V2c0cjluWDNBbkxwZDVfLXdxUTk3aV9xM0hnVElQcERGaDAwaVBRU2JZam8wTVM5WlhsSXJGMXBkWWlIdUZXWEZITzlJRk9LM1pEOE8yYVdETHp4WjRzWklrV0dvak5Pc0ZiaFdlMVE?oc=5", "source": "HDFC Sky", "published": "2026-10-30 05:13", "score": -0.25, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex, Nifty trade flat as IT gains counter crude oil concerns", "link": "https://news.google.com/rss/articles/CBMi1gFBVV95cUxOMUFDOGdnZDc3VlZTRnBlVi1TNmpxRmRKTUtJaVVaYXFIOWJYRklfam54WG1OWkU2MEphUEhmbjlEVHBWUEp4TVhNSFZQN256ZGxjcjdaRUxsd1ZsNjYyc192SnlCNnVBdjJXU3gwdEVBX3AxMllFTXlLbFJOUGlkWnNRRjE2RXJRUUhUMVFraGpnZEFRQlFLUTVnY3lDREJkWXdsZ2l4MVhxNXZxSlUzMllBQy1IRm9ja1lYTUdzRXBqdHhvTkFOVlRJTVR1VFRFMjFEUzVR0gHbAUFVX3lxTFAwZDI2NmhfbDE1RmRhTlk3a0NVMGpWakRNLXpfMVdYQmJGcDRjYWpOTkVNTS0xaWc3MVRCRXVrV0g4YlNIY080RmtqN1QwUEdwRzlXOGdESzFXOUZxalN2RmJRZGh5MGdOUUFEQlQ1XzZOSFUtb2dEemREUFJXTUZYSTJ0eWwtRUpMWTBBa2ZBanpkV19PYkpUNFJFVDk0OWN4cnJTeUw1MjdVTjBDNF9Mamdzc3BrTHM3dXFWZWs3Ujh4ZWREQTZQVlRWYU1raXJpMmpOVDFpUC1vbw?oc=5", "source": "India Today", "published": "2026-10-30 05:07", "score": 0.153, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex Today Trades Flat | Nifty Below 22,950 | BSE Telecommunication Down 1.7%", "link": "https://news.google.com/rss/articles/CBMi0AFBVV95cUxOcUo1LU9Dd3BjaFU1bVBLSXhidmJfcFJmeDBUWFBaRUFJRF9FVlk0ckhLWTR2ZzJWQ0NIRkhXZUZOQzVHR0VDQjI2NE5IUl9PS0I3UmFSbVVnRVI2V2NoeDdOVGdPYXM2UDdkQTVIa2RMOTAzUzRKRExNTERWbk84eDVsN0RPM3gtcmhENlBhNEcyZEo5UFdoQWZKSkFiUTR1eDltLXpoTFF4VTM4UXUzLVFBSGIwMlVzV0lyTDRrSEFZaGNjTTlLRkp0N1ltbXln?oc=5", "source": "Equitymaster", "published": "2026-10-30 05:01", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty Rally 2nd Day on IT Buying, Trent Earnings", "link": "https://news.google.com/rss/articles/CBMipAFBVV95cUxPSHQwT25wUDBQTGJydm9RS2lOZkl5b1Bod190aV94bE5lRVZsNUVYX1ppMHQxRWc3bGZCNTRyeThwbE01bG11OUdmYUtnMEE1VkduNVZUTTBMRkZST2JDM05qaDVnUnY0LWlHV0cya1d6SEh5MnNhUjB1VUtIc2pPVmk5N245MDJ5VVNuR0I3b1VKRlFYcE1YM002b0RRb3IzY0ZMMdIBqgFBVV95cUxPQ2N4c1RBUjFWOGVlVUE2NzFITzlDOVJ3Rm83dXJhX2F4UmF0cE9RLXhOTTFIQzdmYVoyM1ZCamdabGlUTU9tVklfUm4xTVlPZTgyaUNTM1FnRnlUTzdiOVBFeURwTUhWd05qdUxiNjktVmlyQTZyeWZBa1VaWS1UanR2d0dLbEJyQm9YN2hBeXJ6d3hJdlVDR2Q4dmloMG5tbC1YOFR5TUdBUQ?oc=5", "source": "Rediff MoneyWiz", "published": "2026-10-30 04:58", "score": 0.691, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock Markets Today: Sensex, Nifty Up on Gains in IT Stocks", "link": "https://news.google.com/rss/articles/CBMiwgFBVV95cUxNRm9wczhmdDJsYW0tSUc3Q3VzRGVzTzZSMzdpR2o2MmJHX21lYTJHQmNUU2w3dElpcEpyUXFBbHZaZHlqRXNidXdpWVZEaWhXWlNaZlM2TTM1RXpWb1BwTUFNOWU4YjNsSnZzazJWbkdwNE5XTDdueHgzWWdwdWlCZkdUekVNdEhDaDhKRzZuUnFiWlNtaDIxd3RwNHFkWXB2andGM0ZwMUJLUHpOSDExLXZndGtjSmdCYzl1UXNLRWZWUdIBxAFBVV95cUxPTmdzMG1GRF93RmdyMFR4SUYzWFFxSUhLei1zLXZSZXZIaXdFY29CWU5zcVFLNHAxMzBJUGhfUWhEMW9STlRBME9aUUstYzZvMV9TaXFUOF9DWk1mM1BOOUVuUXVPMjJTUTI0Y1BRMkN4MDE0cENsV05mbEEteHAtMmR1WWM2TjVGbHNnWmdoTFVNR1Q3OER3WDFjUU1oMkt1VXJfRmt3bTEwWGM5ZmE0bDZRbDVUUUYzYmVEdl9QS04xNUxY?oc=5", "source": "Rediff", "published": "2026-10-30 04:57", "score": 0.649, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock market today: Sensex opens higher, Trent rallies; Suzlon tumbles 8%", "link": "https://news.google.com/rss/articles/CBMisAFBVV95cUxQd0tQR0Y5aWc2NjdaVlF0a0RFLTFKM0kwclM2WXFsQmJrTGtEbkFSYmRKSk95b3F5LVVYcXVTVTBJNWxBM2xqSzVKOGJGVllrMURVZmhRcmYxa0QyRVRqZW8xYS1kQjdneVktNHRLaUx6ZHlrY3F4ekk0RkktSkVWRl9rME9PNUFsbC1fcDQ5VTR2UDBwVUJGV1AwcXJQQk1pQlBleXF2WVVTWVhuNjZ1SNIBsAFBVV95cUxQd0tQR0Y5aWc2NjdaVlF0a0RFLTFKM0kwclM2WXFsQmJrTGtEbkFSYmRKSk95b3F5LVVYcXVTVTBJNWxBM2xqSzVKOGJGVllrMURVZmhRcmYxa0QyRVRqZW8xYS1kQjdneVktNHRLaUx6ZHlrY3F4ekk0RkktSkVWRl9rME9PNUFsbC1fcDQ5VTR2UDBwVUJGV1AwcXJQQk1pQlBleXF2WVVTWVhuNjZ1SA?oc=5", "source": "NewsDrum", "published": "2026-10-30 04:50", "score": -0.052, "label": "Neutral"}, {"symbol": "MARKET", "title": "Stock Market Today: Sensex Gains in Early Trade as Investors Focus on Earnings and Global Cues", "link": "https://news.google.com/rss/articles/CBMi0gFBVV95cUxPYjRWVkJta0FLZGc0VW1vVWVpMnZxckxFNll3RkVpdGZsbGJrWVJKZk85Y1ZWODY2ZUs3V3pBRnFYSHpCR0VrdXpEX09DTHJwTkgybTdvLTFzZnNCQ1NocmNyMXpyQjBfX29GeWZMdHY3M0g3T0NVeERRT3g0UUN2Vlg3eTNzRlhRaklnalQ2VlF5aWZDcGxZb1puYXNaX1NvUk9yLUZhUklaV0N0ZmhyeW9ROERDbGRtOF92V1pvU2l6NGJwMHNPZk5xWkdWcDhXX0E?oc=5", "source": "Business News This Week", "published": "2026-10-30 04:47", "score": 0.382, "label": "Positive"}, {"symbol": "MARKET", "title": "BLS Polymers IPO allotment today; GMP at 45% \u2014 check status on BSE, NSE and registrar", "link": "https://news.google.com/rss/articles/CBMi4AFBVV95cUxNYWZNdk04SlliSDd0WXdTVm9EYVFNc2lFcXJfbTdXN3BMLTVoeEM1UUh2eVl0WWJTSGpHNnY4aUEySTMxblYtblFzNHplTS1qRE14VXFkQ0lJcHpBa3FZMlphZk5LSEkxTGtFMWlSVm9HMnVieXRJbWc2bmlHdWJxZ1JkNF9IYnpOazNpWjVvcWttbThpdHFJNkJzT3Rrd3I2Q2hPUmduaExHZFA2WWZiaG1BOHVVdGdWRVUxenAtWjJxbU1Ga1lVT1VCcXY4RmlaUjFWWWQwUEg3UFJtcGVVdNIB5gFBVV95cUxNS1JhWVlMbVdvTTVwdFFuaTNRNnZDemVETm8wdjRKRk1LTWRJb3hpWUNWOVY0WUdDRU1iNThsMzFQbnZGQnVRWnBsYnFXVkNTLUh4M1BDZERhdVRXY056NGRuemN3NTZKTFNYUFp5TFlvSWJIdFhFX3RfeEdvcHlVQTA3TnFZNURBclJrR0d5YjN5V2xrbHlkaDM5a1NRVzI1WHUtT3ZoNm0wS3BqQ1BlZEtrSnR4SzNCbjducnpFRHZEMGxlX0sxMEE5NHdPMkM1bGJWN2Jnei1Za3dhMENZbGN0SmhSZw?oc=5", "source": "Moneycontrol.com", "published": "2026-10-30 04:26", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex, Nifty open marginally higher amid rising crude prices, weak global cues", "link": "https://news.google.com/rss/articles/CBMizwFBVV95cUxQZEVUOGVMeklfRE9LWkxXTEw2eHBrUG9qTkZjSkt1ZFpvZ0laVlpMS2FhN0ZTWnh5RnJjNFZsb1BTcjJreS0xS1pUT29lQVl0UXNUT1dlemdUZEFLVlhjQUQ2QXVCdnZYazJ4bnhnZERxWU9FMGg1WG9vM2pBZEFNV1ZycE55QTdvLXJscl9faTZfSGNWc2VYUTF3R3NUMXZfVWtDak5UNjFjQVJvZVpqTEFWRmhKQnozcjFQdjVKVWV3Z3lxVTA3QkNUU2F3Zjg?oc=5", "source": "TradingView", "published": "2026-10-30 04:19", "score": -0.557, "label": "Negative"}, {"symbol": "SYRMA", "title": "SYRMA Stock Price and Chart \u2014 NSE:SYRMA", "link": "https://news.google.com/rss/articles/CBMiWkFVX3lxTE1ud0tHczZETmVYWGR6VkdGWkdsc1M4N2pKRFM1UXdpNGlyWTVHbGVHS25tOUdlZjBPRExoWlZLcVQ3ckFPU21KdFQ5dHBqc09VdjJZeV9JMjVzUQ?oc=5", "source": "TradingView", "published": "2026-10-30 04:16", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "SFC Environmental Technologies IPO allotment: How to check status online on NSE, BSE, MUFG Intime India; listing date, time here", "link": "https://news.google.com/rss/articles/CBMiiwJBVV95cUxPQnU3M05KNTNXQ1M1NEp0YkxucF9JdkpfYjdVU242WjVTcmI1eFlCWk5odktUV1k2MDJlcUwwTEZzTEFtLU1YMnUtaFdwSk4zZFZScnJ5Uk1IbHpySnYzWmxwYlVBaTdxZ1p0M0NmSGpBMl82blNZSEw0RnNzVHBMbzFJZkV4VDNhUVQ5MWJzT21yelpGMlZ6RHp0Qk1lZzBkSl9GTDJRQk5ZR1FzeTE5OVF1a3VjWlc5eWlkT0M5R2ZsaDFuVWdWRzdEcTREVnVRVnBNUE0tN3JNUGtoY1g2bkVpWmd1OWV3Umc2T2JhekhDOXlRSVMtNDNXRjdBbXg4Qm5rZW8ycVAyRUk?oc=5", "source": "Upstox", "published": "2026-10-30 04:14", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex, Nifty open flat amid high crude oil prices, jump in IT stocks | Business News", "link": "https://news.google.com/rss/articles/CBMiiwJBVV95cUxQZzBDN3QzQVZXQWpWLTRSUV9kckdKZThxT2F4amxOS2JlZjRYc0puWVUzX3NoTVVxa0V0djNvd2ZNUjhZNEFjTU1DdGxIaGpacXVwb2o5bG9HNnIyRmNTSDZpLU5xSU9vR0RZYU10QUlBQnZPaTlQNDVvZGtaY0h2RnJvN1RXbGhDdG5Mek5UeUNjNXBNd201ekJBSksxTVY2YkhiUzRjaWlQYk9mV2s4Q1Y4RjBSSnd2d2hDcm15TEk2dm5UcHd2UG1IV0lSVVJnR2lYUVk0UHZCZFV2ZnVWZVR0dG5UcVhPSG5nQ2lZT3FpZi1VSjM5SkVrd1Q3R2FGYmhHY1ZERUptajTSAZACQVVfeXFMTVgza0lkcW9ucm1sWEE1YkQteVVCQXpfbE9SWU1FUWxpUHhtcG5pWlpkaVBKNmlka3JaN1N5MW02QTlZUmYwTFdYMUtObGhIQi11dkM0NG9zOHhVZVMzSVYwQU9KQ0l1bGFucktxZ21UcjV3TFd5Q2Q2dzJfUnYwZndLZlUwYkVVRTdhUUNTYkJvZm45Vm5MVUxQT3VyMWxDNDUySi0yNzVKN3hIRG9PZjJEMXpiSE40UWZqem5BU09fVjNSNWZxYzZzZTd1THFCSXRDS2NUV2RmY2RMa1R2bV9mN0pOUzJZaTFGSVlsMG83WTlFNjdSdkswa3NES2lLUW15SENIWWR5blNHWEJaa1Y?oc=5", "source": "Hindustan Times", "published": "2026-10-30 04:11", "score": 0.382, "label": "Positive"}, {"symbol": "MARKET", "title": "Coal India falls 3% post Q2 results but brokerages upbeat on PSU stock", "link": "https://news.google.com/rss/articles/CBMi0gFBVV95cUxNRWNKZDdGNHlETVRZR2VZMEZOdWJVUXZLbzd1RVRqazNuN0NrV2NUMWJDREZxanNlWElPSHRyRUFsY1lMZVRCTWtIMEZNSDBnd0xxREJtVG9FSFU1NUd4WDd4aGN1X2phV2lIY1pjTDRNMlNHYWxYNUZ5NjdnTVp2YndLa3ZDRjFiaGNvTkdQbm5fVTRvX09IakEzMm1CU0VFSjh6UmI1TjdybFJwc19mNjlwM09wU2RrSmRuTDBjOGhlalItM28wa2trQU5fZFpvOEHSAdcBQVVfeXFMTkVnMXZSY1FaMDlfNURXUTctY2NnMml1SExJZHV6SFNSYlhTVTBmckc5YVhrRTJHYndWMlg2YWo5OXRUUV9yNzgyWk9VVnVpU252WENCLXFQNnlTMEdVeHoxb293N1czYnE4WmwwV1lCZE9zS2VOYm9YSEZ2ZDE3RFlDeFMwRTJMZFFSNFh1X3B5RjZ6ek5fbVdqSHd4S3JOMEkwLUdBRkRMSEJ6SFE2eHFmZFJKejdGZ3Y1aGZHdnBHUjN3UUoyY0RYbmJoZnladHV6RS1xQTQ?oc=5", "source": "Business Standard", "published": "2026-10-30 03:59", "score": -0.202, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock Market Today (October 30): Sensex, Nifty Open Flat; Rising Oil Prices, Geopolitical Tensions In Focus", "link": "https://news.google.com/rss/articles/CBMigwJBVV95cUxPSkcyQktHdUYwRC1IRHJsakZFTVhZUHRvX2FiZDRnZmdVdy1jWkd3bkFRQWhkLWlQZHp2aE42MTYxU3ZvOURHQUFUdV9YTGdWb292M0xDWV9TekpLU0pNaEp5MnJDMXRDRFdnZHJDdi13VVM2Tzk0d3FyZmpfVHEtVEpaV29SN25RYS10SjV2SzRTV25uNmZRMjRvR2tXV0w5M1FqcUZVNEVXbFo1aHpyNm42VWQzbnVFY1Q3ZkhpRzF5YkIyWnBqM1JoNkZ2Q2tfc00wNnNKOEJlSW54LXFjSmVZNGlnTkRWS2Q0d2s2RlBQMUJwMnRSazdlaVhRak81d3NR0gGIAkFVX3lxTFBrc1lJc1k2dWYtM3dmcTRSNGZyS0htWEg4akV0MjhNU2dvRkMwTlg2a1poMk5sR0NCLURBNDBBMUwzZEJqa0ZPR1N5dWI1OHBWT3FYV2Itczh6Z2w1SEN0QjFHYTdNUlVEVmZza3F6aGtvSEhPZ19tZkNrQVVtcEFHdGFVNXhiQlJZR0RoTDBkdHBPTXE0WktPT21CQnFPWGQzUmM2b3I4bXBwbWQwX29QWEI2aVpyWk5fSmpYNHVtSWtRSkhmbU9ONHVrNThqQXVNT2dCUXY1R2NxaGQ1dkNTaHVqN1RmcHRTLXdOOEhTbkVncHVpYzNiSVVNY0dtUnhHOGthZF9YVQ?oc=5", "source": "Times Now", "published": "2026-10-30 03:51", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Stock Market Today: Sensex edges higher, Nifty opens above 22,950", "link": "https://news.google.com/rss/articles/CBMirgFBVV95cUxQNHhZR2hsX1hjcDRiWWxSc1V4QVNpNDFad3g3STVkMGdrTG9vaU5ObV9ZYUNIN3dpUlFUUmhsTHVHWmpHRVRMVVlfUHVFSURqZHJQaksycmc5Y2NVZEt1OVlyWFJOWEVsWDB6Tm1nOVFLOWJ0YjZ1UnJKMXJwcEJGdXljWlJUcmdhWTdkS1A4NFlpeXRDekdoN3l6SEQxSEhSQnhjcURURkkyajlGVHc?oc=5", "source": "Zee Business", "published": "2026-10-30 03:50", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty may gain 5-8% if external headwinds recede: Baldev Prakash", "link": "https://news.google.com/rss/articles/CBMi2gFBVV95cUxPcTJTc3Vndll3czhydnJSQk8xRzVicWRTQXIxdWVxb1diVGt1R2IxMEEzWkF6d2stU2F0U2o4SlZQSkVUMUJlSEdzMVdCQ05Da2pNaC1TaUJaYW9Za1Jfd2hFNmJpdTNXQ2NXbXR4SXJ2RU1na183RnUtSk5IYmJ2V0lfVWhTMkx5VXFULUNqY2dUVUVqY1BVbXZvRHpmeS01d0lQbWgyUFBqUURPV2tFTG00eWZQNmFxckRYUkxZVF81TGNEaDRMdkRNZ2txWDBYS2taNnJvTEJ5Z9IB3wFBVV95cUxNeVpabmdOVGR1X3M1R21QQlZJbGZ1MzJmdU81a3lGTTdlaVhGLVNwUUUtMF9QRlFJdXlkNG9UMVdiNjhhUmE4bGV6b2tGREdROGV4MXFGVk43NS1faWNZT3dpcUUwR1FXU19uZW5rUHhZUUFzcjdTVzkzTWlWTWZ0eGxYclR0S2t0VWlHcVpacFVjYlFPazNpYVY4TWxkeGQ4U2JTZTFNd0dDTXBiMS1kY0otbXZjbUpONDBhcnFwMFhqdEhfZW1oWDFvdkZRNkxfUktFaW85RjRXQWhSR2ZZ?oc=5", "source": "Business Standard", "published": "2026-10-30 03:34", "score": 0.625, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock market outlook: Crude oil prices to FPI inflows - 8 triggers that could reverse trend in Sensex, Nifty 50", "link": "https://news.google.com/rss/articles/CBMihgJBVV95cUxNOEZaNmc4dnEtRC16Vm5IVHhCd1Y2S19zcjRpVDdSWVZZajg4NjNGMGtyWnE0U2tPbjJUMXVkOFFlT1RERHZWQlBEOHJxWmdITmJPREVXZ1JIaUd3aWNQUTcyMUlqZnpFQWRiZHJLcE5YWmlZOUdlamlzX1NtYUdqczBmamh5Q044dnNPVHZsdEdfTWRmR2pxLUlXeXduUU1laHVpVHhfVmE3OThMWmdwMHdBa2RmbDdVZW82VUc3TGV4TVM1cG85anM5TUpROGVZZlR6MkYzczB4d2YwcU42YWlPeEtmUUw3Tk4wbFBZTDMwUGlSUWtDeHFmRjQyejJLaXhiVmxn0gGLAkFVX3lxTFBIdUVWNXVfYV8zN0tXeE1oZmNpZS1LTk1GNGxzUXRINHQxcWQ3Zy1SOTN1NWRta2tjeG1uQ2NJaE5nTGpzVUlHeXBtaHlaNTM5NWVGUmM4cm10M25WTGplanFSd0F5OUtYWXFGWklQYkpudlIzakczNDNjQi1HNmJYUnRxSTlsVi1xelhNd2h3MU9wSmpyNjcyMTRoLXNpcXBLc1VreklSaS1DNktabHpISXdSSmhpWXRGRm1wQlgzSUk2RVJOZDJTY21vMFdwS0FNZ2psM1NZT0FpbmZsZGQ5VnRlQmx0Q0RWM0FudEk4SEFqRldYOGpsNktPdGxPdU1DZ2hldlRMaEZFOA?oc=5", "source": "Livemint", "published": "2026-10-30 03:00", "score": -0.25, "label": "Negative"}, {"symbol": "MARKET", "title": "GIFT Nifty down, signals muted start for Sensex, Nifty; Asian markets plunge on AI spending worries, oil...", "link": "https://news.google.com/rss/articles/CBMigAJBVV95cUxOQkZmUHBNNXpGaGxiR2gxMnp3Ry1tVjBlTWlHMUZHUWc0SnJLbk5vU3kteU1zMVFkZDd6RGUwQ0RmZV9OUUtITUgtSU8tMURBT0ExV3dWaDF4MzFKZDhGcTJoeXVzUkg0QzRKcHJiSUZjV29XeGJhVDNIMXE5YzEyNEFiSTJ0cnYyUndHbXY1UTFtUzhZT1l0Q21YYi1Ycy0xekxBR0cxdkxFUmZuMEN1eklZd1c5ekNWV2JtbXEzV1F1emd2eXlhOWtXR3k5VTBaNGd4Z3M0U0ZTdUZ6a0tHakV1WktJd1YwMHh2M3pQUjkwSHRwcE93c0R1bzBhVTdD0gGGAkFVX3lxTE1SNmF2clJMZV9kSHRkZUpwZ0FjcUhOS0NEQVZ1S0NzYzBXaE5jMXQ0Y3NuYUR0VEVFZE94OFpRbGtiYUgxbVc3TzRad3JGb2t6ZDJZQVVzMnd6QXpMeGFMd3RHWTF2QmNGUjlMT0NnTDQ4SURVZ2UtcnJLUjRncVptM1BGMnhtdWRCM1N2STRsUnpSWDhYbnlwcTF1UHhNOUpadWpzaDJTOFZJUzVoN0w2Q3dRNG0tdFpUbDdrVm9XWk5lRUF5bUk3X3BmVTVBZ0E5dzIxMzJDeHdhbWVxVFRtcFNfWkVyV0QtN1BzbFFkRkJiLVVlMVAzMENGMlVYUU43ZGdvUnc?oc=5", "source": "Moneycontrol.com", "published": "2026-10-30 02:41", "score": 0.408, "label": "Positive"}, {"symbol": "MARKET", "title": "Indian shares seen opening higher after earnings-led rebound; higher oil to cap gains", "link": "https://news.google.com/rss/articles/CBMi6gFBVV95cUxORkRQbWxVNzVaYjNjN2d0aXNjQURWdFEyOXVPY2hENENXdU42M2t6M3dWM1Z4M1A1dVBPQ1RoTW8zZF85eXhQZE9Yb1ZORE1sdTcyWmlHem04YXBxWHFPYlFnenYyY0FDMENWdGh2OWd4VERuMERHOFVDTHFPU0FuM2FYOWZ6a0dKUUdJZnh2SlJZUC1aZkNCU0JFSFFqNTROYzRIcEVPek9QejlIZTBlUXVhbHJheTl5YnZXX09MYVpUSmZaV3VaYWE0WkZhYzdwUUo4bU1pS0hKSWNTblg5MnBFX1ZpbW9SZ1HSAe8BQVVfeXFMTlV4SnU3cWpJSUQ0U0ZPdEg3Q016RmVCSmUtb09pY1hsZjBweEZvSDM3d3dlQUwzRy1WX0RISm5naDZCQ1VIWFNTYzdiMm84cW5UZjgzQ2ljOVJFVEctUnFzR0pKZ3R2RE5qVFZvdURFNldfT183VktEcUd2bjgtWGxoSjVsdTFvMjhiXzAyMVBjb0czNjNQRkJmN1Fjb19rUzlFVDNmT3F0MnBCNFAzUnVaTHdXdDBGTl9IQ3RIM3Z3VTR2VHVrTDg4cWR1a25GY1BaUVVaN2RtYVRULTVCN1UtaGJQTlJXcUtTRXBoUk0?oc=5", "source": "Livemint", "published": "2026-10-30 02:35", "score": 0.382, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock Market Today, October 30: RIL, Jio Q2 results, Japan rate decision, forex reserves - 10 key triggers for Sensex, Nifty", "link": "https://news.google.com/rss/articles/CBMi_AFBVV95cUxNamZ1UG1fNEpHV0dYVE1zb1lmLWJxUk5rSEx0M2hsV0NGRXdSaElkZTBNUjZXbU5pZW5STUpUbEkzTFg2OEhGWlk4Q2hkeXZxdHAzMG1vZFZVT2VoTkdweEt4Z0ppU3BscGlFMjN5ell5NE5wNHJ4NWpkV05PMkVENUVHVHR1bjAzQWtNTW8yelVwWjN3SldlUkxpaEIwdHlQdXFRVXh3dUZYR1JMZUVwY3Y3S09GdXBpTVFVVGFxaWdYcXRzR0NYVlBFMVR2NmJYVUNJcmZmVlhXQnJiRG9pZzBiUlJuMnpJVlBpWjBzTjh3bkhEeHpRRWJRdU7SAYICQVVfeXFMTVlBRG51UDZtVlB0OENLRUZvdlJTOXUzNU44SndaYUoxVXplVS1GZFpTMXF4WVUwTUp5bHotM0N6SXJtZlJmdzE3ZjFUaDcwUlBpWmR2c2ZpTUJNSUREOTV5cUN3eUFsTWZ0dmt3UVhEYzFaYTJaaWRFV284OGlZeGVoLUJfTElLZVVqUTVudUR4aGR4aHVEb3lYXzg2WUpIbjR5OVJ0NVdUUE1HWGdfSHoxckxvM09YdVBGRnNLV3laOXNNckVRWXEyd1pvelRCelluV1RNT1Zxb25reU42ODN6SlhBVWdLV0lXd2tXMGx0QVBXM2Y4WVNzZ3Y3c2lTV2Rn?oc=5", "source": "ET Now", "published": "2026-10-30 02:21", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock Market Today: Gift Nifty, Tech Stocks Selloff To Binance Hack; Five Key Factors For Sensex, Nifty 50 On Oct 30", "link": "https://news.google.com/rss/articles/CBMigAJBVV95cUxNdkc2UTMzMXp6a3dsbm55eXlZMzFHdzJ2S2UtYWkzcVdJekZDOHh1RVJaOXFMMlFwdXdWd0lMajR2TUItTTl3cF84b2R2R1NXVmd1dVlta0VpcTFhYWkxUlhnZDYxTHhoeEtYM0JGeDAzQkRlc0FNR1dCNWV1RUw1VUdYa1FkQ09FMWZmM21mN2pwQTVfUVU5ejlScGhzY3F0MjVHY1lTNmZkdHNJRTk5dG0zODcwOTVHRzRqYi1OVE1BUVQwbWdQWkQzWE13ZWZlTmJYUGlHRnhGTWJhWGtQTkJmMExFa0ZURmJzcGtOeWVwWHg4SlNfUnc5TC15eUxT0gGIAkFVX3lxTE5kMVJROUdWQWIwcWlxNGduSHdncXluWWduV1l3a3MtMzRMcXdsUmdzekdkVkVPR1JRNUp3bVVhb19WREFhTzUyYU5BVzRpUDNEZTduODNsb1ZyMDR1OGRybGRhWlRGbzB1Q25iTTRLZGtYMlpBT050bTM0TXBDX1BfN1JOLUttSkd2N0dYT2RGX1dUOTE5Tk1aOVVSRXlmd2tmaUVTUTczcTlrVTU0QnEtSHhJdjhDa1Y5R2R0aHlJQVhpNkg5bC1FcWtOU09KN0FuY3pmZW1RcWplZ0toNUZWYXdMZGx4aGJBZXpidlF6MXhnWGpmaHEwUTZVYVVlUE1VM3FBanFvZg?oc=5", "source": "NDTV Profit", "published": "2026-10-30 01:44", "score": 0.807, "label": "Positive"}, {"symbol": "THANGAMAYL", "title": "Thangamayil FY26 Net Profit Jumps 196% to \u20b935,165 Lakhs", "link": "https://news.google.com/rss/articles/CBMi8AFBVV95cUxNZWQxVFZva3o0cms1Y2N2ZmRJMnk0TmZzTTdLUWVuZE8taXVteEgyeDhHQi1wYUIyU0RGb3J5QWFxd2pLSTJILUVSOEZVZTBDbExkVkMtT0tiNjhGOGpubU1KQ25LQ1ZFUXkyUDZmY0FIdWZBSm96cm1vZ3R3VEtQUHFKLTBZM18tZmx4NDhNRWM2OURvX2xQQXJncWtod1ZoR3ZoV3A4bldUSkxXMU8xNlEzU2tMeWYxeHMwYk5LeVlYQ3hJeGVqMkdNYlRIQTZnUXpxTk5xZzA0aGZqNGVId0pnbTRLd3RJNWZZcWQ3azQ?oc=5", "source": "scanx.trade", "published": "2026-10-30 01:17", "score": 0.66, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock market outlook today, 30 Oct: Sensex, Nifty prediction - DJIA, S&amp;P, NASDAQ, GIFT Nifty, Kospi, Nikkei, Taiwan cues", "link": "https://news.google.com/rss/articles/CBMihAJBVV95cUxNU0lLTXdXRXlnWnktM1lpdVdQMEZ1Q0ltbHlFQlZOa1pRM09LcGlnYTRubzNDcks4N21ZaGdEV3ZpRFV0N1FhT3htZkM5djl3WngtREVSVkdhbWkzWFQzNjJQN2MwZDVYaXQ3Q3pPOUxLaDlVUFF5aEFzWkY2TU1jRjloa19jNTBBMHZMYkZGVExUMlV5aXlXaVV6M3Z4QV9WaDF2ekFRMlg4dXV1aE1TMWR5bHlUUi1XODB1MHFraXVKLXZGOXJvNTdmRnJNNmY5WU1JSXJ1dXpVTjdXR2NyVUpVSUdYbFFqS0gybXp5MG5tSDdhWEpTb1RVMkJlZ29ZN09WNdIBigJBVV95cUxQQ3pIRzJQZmY1VXpnc0Nra014TklOZ0lvNkhtZUJ0UFJiQmtZQ090aUpZTlFfTWdMMW9HT1U1UVJEU2NUcVFUUmtyb0E2emhPa1hmMGd6eDYyMWk4R3JURTFVYThqZzNBS3lyNC1zcTRyajNKcWF0d213aWd2Y1J3aGRNMVlqRDhOaUZpNktDcmNSRFlpMnVVU1NOTlV3TTMtX2tLSkNyMWNrVWtwd29sQkxxTkUxYll2X1FoOWJVY2ZTcUVBUXRMVGVTNnY5UGZlNVZpRTQ1bnhUdzBkM1BPTjl4dUxfS2FRd3NzZUpJMF9CWW44QXRWaVFuaW02M29sZlBCMThPRWlfUQ?oc=5", "source": "Livemint", "published": "2026-10-30 01:14", "score": 0.842, "label": "Positive"}, {"symbol": "MARKET", "title": "eClerx Services Q2 FY27 Results | Birlasoft Q2 FY27 Results | Top Buzzing Stocks Today", "link": "https://news.google.com/rss/articles/CBMi3gFBVV95cUxOS0Fuc0x6cVdyNW5qTUFaU2FrZU8wRzZaeXA3ZV9rZ3FtTE9jeml2NzVaOWhaV2stVzl0VnJDRERDNXlnX1dnSUI5M3dROEpacDFlTDF3QldiVTBaVGhvVmR5ZnoySE9zUlVIN0RyeVItTGpiVkFXSjV3TW9hdXF6X1AyWFdyeVNNaGQ3VEh0cWphT3dnTmlBWHBYZmwtazZ4REVpSHJtWC05cUpRc3VCZmVKYkpCbnRvLVl5VXBYVTk5ZTZWZ1FNZVY4V1JNVFV4U2FwNDhuNkZHRjJ6NGc?oc=5", "source": "Equitymaster", "published": "2026-10-30 00:30", "score": 0.202, "label": "Positive"}, {"symbol": "MARKET", "title": "Advance-decline ratio hits 7-month low as market breadth weakens", "link": "https://news.google.com/rss/articles/CBMi0gFBVV95cUxNSXRYTnJUbnhsTDFmcG5lMlVpT3lvVjNCUDR5NmJQTHU2UmdnZ21RZ25XOWRFdmF5X2prVU5nYVMyb0pZMXBZRkZ0SmZmaTczMVVEUlRXblVOUS1aMlg5V2lrMzlHQVJmU285blJNM0Y4T3UtNVlQd184cmlNcTZRUkVJNmc5Qjdva1VVUlJ2RU1taWlqNk1lWVpVOEtFZkNaMTdwRF9rUEZNQVdCUGQyTFBwWFJOVkl5RGx0a0RYVWtQS2pNYWhUY20xWHRJV2pkeFHSAdcBQVVfeXFMTUVCeWwyaTY1Um55NjExa2t4WXR1b09RSHlvRDlPYlA4M3Z4aTVCX05lQ1FpNTlsM3I2dUVRR0FSWk9hNmdYSFdkeWxCM3hDaUZMMVlockdfSnV2bUEtSlBEaHVCdW5NRGw1YjdTaGRjWDlMaDMzMy14Q1RyaHA5UVVxVE1RYXNBTnFQNU9aeVE4amd1UmNFWG5PdlVMMzhvQTlQZGxNeTJVb0ptUUZyNlFjY0tHX0EzQU5PYzVCSXZjdWVpaWRBRnlDRE1oQWNFOWJFRHZQdWM?oc=5", "source": "The Economic Times", "published": "2026-10-30 00:23", "score": -0.612, "label": "Negative"}, {"symbol": "AETHER", "title": "Ather Energy Share Price Today, Ather Energy Stock Price Live NSE/BSE Updates | The Economic Times", "link": "https://news.google.com/rss/articles/CBMiigFBVV95cUxNMmpPVXcxeVFIRHF1aHV6dFRLVnhXV3djOWRQN2tuMmxVTnhDeVNJSnFoV2ZscmFoaEtaWXhCT0tabGNHdVhlOV8zcG45eTJrYS04ek9hSlNlMEZPYlpyeS1pbXNqbjlVVklKeEFrX1R6OUEzXzhRdjNneFZzbEFFMjc4MmZ4T3dSMnc?oc=5", "source": "The Economic Times", "published": "2026-10-30 00:10", "score": 0.494, "label": "Positive"}, {"symbol": "SYRMA", "title": "ZF Commercial Vehicle Control Systems India Share Price, Stock Price - NSE/BSE Live", "link": "https://news.google.com/rss/articles/CBMipAFBVV95cUxQaGJ5UUduMmFWUzQxODJRNUFmT0hGMWE5Ykx6RXRJRFRRMGowSGJ2eE5INlhVYVU2OENDblNfcUFlRUlHNzZBRlFyQlZ6dmxtX1NXUjE4dUxEOHpkM1U2NXM3dl9jdzZsU2FUTnQ3SFRqWUNxOXl4cUV1NzllM296YVBMQlktaHQ3V21QQktRWEp4Vm9xbkhjZ0Y2TEY1SzVDVTVkZw?oc=5", "source": "NDTV Profit", "published": "2026-10-29 17:53", "score": 0.0, "label": "Neutral"}, {"symbol": "AEROFLEX", "title": "Aeroflex Industries (NSE:AEROFLEX) Q2 FY27 Results and Hyd-Air Amalgamation", "link": "https://news.google.com/rss/articles/CBMi8AFBVV95cUxNVzBvb2wxcTMxV1h4Y0l6T01NR1p3blBHcUxEN1pKQVNxVTZXQWFmWmdyMDFMaHRxRERqNkJLMjQ4WGJzNENnUklwaUJBMHVLMmFodmdmWXlPLTdhOEpZSGJwLU9ON1NmUks1VUE5cnNYUHYzQ0hrb1pveURwTU9yd0J3WUMwSmJkWmEyMEZrMUhNcVBCZWRpMV9HSFpPdVFKV0xXOU9BTFB5cWVVbTlFdGU3YmY3cHQtX3M1UTVFYVMwZHg5a3djc09lY09PTWt5UzdRMnJEUF94U0N6ZlZ3X2doc3hmSXFMRGxiZjA5SDQ?oc=5", "source": "Kalkine India", "published": "2026-10-29 15:28", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Benchmarks rise over 1% on positive Q2 earnings, easing crude prices", "link": "https://news.google.com/rss/articles/CBMi0AFBVV95cUxQN2x1Nk5sek1aeDluWGNMSnEwREx2SGR5ZjRTd0tzT1NiQ3hoY3htWkJtSW1nYWlrOWRNeS1LVlNMYU5sRVF3eWRzQTVzallfc1JEMVhkSWc3TV9IM21vWG1vTmZRUmVEUmllVVhNdU13YUVVS01LUFNzTHVRRE80bDdaVW5XWXFUTm1oVjZNN2dQaExRMmpMNEdiSzdGMlhuTVBvZ2ZVTTZ1aUdYSTRhek9HbXFMZDNyTEdFSF9GLUZkRGZPOVlTU2JsNTF4WWtw0gHWAUFVX3lxTFB2LU9UckFtY0YwdFAtQ080T2I5a0NJZFowOEJ5bGJsRUR0M1E4WU5jR1d1X2ViencxOWR1dUVlYlVBdS1XRDhBWmpHVUhDNWhxbTdIWkdtdDBLY1hSN2hOclNhcG9HYlRITk81azlSZzFIY0lWZ0RrREg3THYxQWw0ZzIwUnFfUVFpbDQtQ3JESmpTMTZ2U1NFRHk5YjJRekdGWmlUaUhPR0I1UnYxc2dMSmRTdV9yc3hVM1VFc3lXWjZPRTB2UzZzT2kwVE9zMlhkZUQ0NFE?oc=5", "source": "Business Standard", "published": "2026-10-29 14:36", "score": 0.226, "label": "Positive"}, {"symbol": "MARKET", "title": "Indian Equities Rally: Sensex Jumps 905 Pts, Nifty Tops 22,900", "link": "https://news.google.com/rss/articles/CBMixgFBVV95cUxNYUVZT0t1WTRFOVoyX2FhRnJvNFl6cWcwVFhIS3llaUlxMzVHQmpoUXhYVHdQM002TFNvdXA2VktDUk5DczlZQ2ZOUkM4X2lyQXhOMkNqcDk3M1BnUkZYLVpPdVNjeGlaaDNrWGZEdXBncTUyMl9lZDVpTTZrclU5eXpaLWdELV8ybmo4cVgxZTRQRkZneC1nSDVESGNzZUhPRnkxMHNaUC1JRlRaQUx0d180VHN2bmZXX1pGM0FzMm0ydmJoZlHSAcgBQVVfeXFMUGFhZ2k5dzdoSnBTZGxVNlpZdVNMYzBwdnJlUmh0NU1Xa2FGOTBSMFV6STJFdzRSQUFWOE1udE1abXdWUklOdVJlN2lFSk1DVlVRbTdNRDlsZFZ6STd2ZE5UYU8zZElhRGR5U1M5NDZFaDROZjNXRS1leXdtNDJsT3JjUDQ3Z1dkd1B3Zjl0Y0RVRWhVRS04b2RxWkZvRUJPY0pBM21IZUY1TDdPNXNwUmlTdEk3WGViTWtQYjltQ3pOb2NvVV9SVHU?oc=5", "source": "Rediff", "published": "2026-10-29 12:44", "score": 0.9, "label": "Positive"}, {"symbol": "SYRMA", "title": "Syrma SGS Tech - Technical picks for Diwali! 10 stocks PL Capital is bullish on this festive season. See full list", "link": "https://news.google.com/rss/articles/CBMijwJBVV95cUxPY0dYWGhsUHRsOC1HMHVFeFR6YlBhcENObTZlV3lXZkJyUVFLMU50T2pfT3k1Qk5aWkJBUWJOZDE4TTNrSDlUd1dCbTJ0NjlYal9SUmFjSTg0LWt5RldXS3YwRzVOZjBGbk96OF9IQnRETU9VcXFXM2tVMHJWb2R4Szk5MU5YNlpsa05xMldaajYxaUtXc3JmWnJZREZpdHlkM2dsS2Z5VDE2bjRZdmZidE1fR3NXTXRGdFdMVTh4czJOVDBxZFB0MDk4bEN4RmZpN2dJT2JyeFMyYVlYbXdxVE13dmxSWEtTa0NnWDM3eGJIaDA2ejJpdkZHcVFLUTJGZEhJVFduNEh0aGNGY3Q0?oc=5", "source": "The Economic Times", "published": "2026-10-29 11:52", "score": 0.771, "label": "Positive"}, {"symbol": "MARKET", "title": "Share Market Today: Nifty 50, Bank Nifty | Oct 29, 2026", "link": "https://news.google.com/rss/articles/CBMizAFBVV95cUxOTzVHQkVNVVJvd3ItZVNfcUVReFBxSXIzdVNXdnpxUF9iYUg5eURJTmlFbHN4M2hqd014d1BKOV9RdUxtTm5XQjd2TmNGU1piWU9uZUZ2S0c3WWFTcnpoRTFQYmN4T2ZLNWNadndEY0h2OFMzXzdoUDU3dXB6cEhhcG45dEdVLVdvanplODBFTnJod2JiWi0zaml0S1Q5MEF1LVFfajRXS1hoakRDZk5jZ3N3akYteTB1RUloODg4UU9aRDZvRUg4bW9TMDA?oc=5", "source": "Liquide Blog", "published": "2026-10-29 11:41", "score": 0.66, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex jumps 905 points, Nifty gains 238 points as markets stage strong rebound", "link": "https://news.google.com/rss/articles/CBMiygFBVV95cUxNQkR0eEdvajJ2ZVB6SjltUGY0ODdUZ1BYZGxjb3Nfdjd4Y3hYMVZ3MlNqU1BBSmsyQ05fWDVFZ0s1SEd5dmg3ay1OdnNrT0ZINnVfVnU0dzJodXg5ZzBvejZRY2pMb3RBREYwMGNIaTdwXzZsZXJkOEIxUFJxVFRvdjgzVnhfMGdOTVNUVDFmOE4tVDVvM1lZNHlHNlZ6cTNYa000YTVTM19qV1VFek40RVUxVUU4WXhWZjQtV3Y5REdrN1V0VllxMU930gHPAUFVX3lxTE5pbk1LaDNBZDF1WGstdlROOUVfSXBQX2FuaE5FTzVQOEhCNHh1UTdEdmtua3JzLUY2RDRBYkJ5Z0xLRVdRMFkxZEZlcTl3cFZLSXZuM0VBOUw3SDYyazBGcVVyZWFOTVhqRDhteTBnTVc4UzBENXk1YXZwcVY1V19LZ0JVSWV0aGpfbDY0YWwxN1ZOVUlQeVlaTUNhY0NuZVVkTmNvZ2Z3VG1QUk5yd2p5VzdyRTRYUFN0Q2lYejd6cVF1YVBGQko1TzhuOGJxbw?oc=5", "source": "Telegraph India", "published": "2026-10-29 10:56", "score": 0.872, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty see sharp recovery; is the worst finally over?", "link": "https://news.google.com/rss/articles/CBMiwwFBVV95cUxOOEJuMmFvQ1BDSEJEeUIzWTZSdDJ1cGtQZW0ySm4tM2xhM2xIQlhIUHVJUXNFM1pyMGpUMlhQeXIyZXhDT2VLcVRFc3ZfOGVIUTVQMEwwenIxLVF5eDZfRk01VkdBYWN6cmh6Z0dJYmtxNV8wRDdOM0FBOV9QbHluRWFhUkRwalVsM3ZyX19fajBId2tiUmFRUEY0VUkxaVpyOE00cXhXTS1ueFRCRlpacUZYWnNJcFRSMmtQX2ptTXVfT1HSAcgBQVVfeXFMTkhyMVUwVHBnRTl3RUY4U1RJSHNacGtrVEhNbnR5bjFVak9yeTBfWHlqMXZjaTFLUFlFNUtQM1FjY2ZJdW13WFdYR2M2WmppQnBiOTZ2WTRJUG9mNGExOFVxVXJ2OEg3aHpBRmM5eUJoUHBxT2VrUGcyekRPVm9VZFlfX0JuWTFydFlPYnR6OEpscUdPNHcydU9KejNORW5Jd1N5UGh6TGxidWgwb2R2Q01ydWVJVF9Dckd1X2FETVdtVmUxdVd2Tks?oc=5", "source": "Business Today", "published": "2026-10-29 10:50", "score": -0.34, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex Soars 905 Points; Nifty Near 22,940 as Markets Rebound", "link": "https://news.google.com/rss/articles/CBMiyAFBVV95cUxNTEctOW5hZk9uc1ItTjBmOVl2NmRMZlViRF9VWG5fZEdSMnQ1YU5OSEhTcXZ4RU0yMF9XSDZZeDJQbHprOS0zYkxOSW9scjBCeDlJTTF3Wmo0TDJNWXFTMzNWVUJhZFIxQmFMSmo3Tjk2Sk95RFNzVS0tbDdQWnM0RjlhdnliUldJWGh3c29mTUk3Y04zbExYVno2TDBVdTdka3VvcktuTXlYeWFBNDhDbGlWT1VqVTJuUVQ3YWVoZmRBa3dZb2V2Sg?oc=5", "source": "HDFC Sky", "published": "2026-10-29 10:46", "score": 0.727, "label": "Positive"}, {"symbol": "MARKET", "title": "Indian markets stage a strong rebound, recouping yesterday\u2019s losses as Sensex surges over 1%", "link": "https://news.google.com/rss/articles/CBMi2wFBVV95cUxPNjhqLWVyaGVfUDI5aXNGT3VhMUNQc2wwQVQtVnA3S29YWVc3ZlpRVmQ4WG9JUHBZVjhpOVpIYi04YVBlMmVuMF9ZOXdHM3pfUGNSS1Fzcm05dnQ4Z1ZPN3l4WUVTMlRZdlVRcUQxUDVVdmE2RXg4aF9wcGpYZmlnQTNOVG5zUmJ2OVh6a0dOTjFKY3h1WC0xOU1qd0dZUndxc2NjRUxGNE13cVd5dUJGTTZhUUh4Vnlrc29vRHZmTW4xQmhwM1FpWVJTQVlNYldZRENhTDZWcW5oYm_SAeg</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>kF2NEtWN0NTTFRDekFwTUY5MEpoeGlobnNOWWxWMFVPVTdt?oc=5", "source": "Simply Wall St", "published": "2026-10-28 07:00", "score": 0.0, "label": "Neutral"}, {"symbol": "SYRMA", "title": "NSE adds six stocks to F&amp;O segment from today, October 28: Check full list", "link": "https://news.google.com/rss/articles/CBMiugFBVV95cUxQcXRqZ2VkU1BlRnY3clZsRkEweDlZOXdLYUFpMmM5QUc2eVhULTBmaXZNOTJaM1ltRkMwY1g5NUFSSUJibzdac2JSeV9pLWlzblJuMmdwTVlRSktfNlJ4YkxfYWpVd1VMd3JLel9hcGNrcmZJQUJsYlplNVMtQXNROC1CZTBvOE55eXpUSnhIaXNPeGt5V09rdjVEQlhJaTJDbmJlRTMxeGtONVhJbGNJb3FuSHRaWXFPMlE?oc=5", "source": "Zee Business", "published": "2026-10-28 06:20", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Stock market crash today: Sensex plunges 995 points, Nifty sheds 1% ahead of Fed decision: Here's what spooked D-Street", "link": "https://news.google.com/rss/articles/CBMikAJBVV95cUxOMFlUOGxPbER6VGFzUWlYX1hkbGdNNlpHb2lIU1VlNTNhQ3Jvdm9TZ2Z6NHdhUzVhV25aNXBpT2hrUmt0SW9SVjJPZUJPOEtlVnJaVWtfUWdMWE9QdkJQV0E1ZVlDSzV4alhSOTZtR05SWEd0TEZfbFdWZnV2VGp0VFcyMmZnQVh6ZlhCbmpDTmY5NXNxZWwxWnZhV0xMUXJxdFNQbHNwWHB2LXc4cnJiVnFXeXJNX2lYc0lQZUd6MHRuOTM1TXlCek4td1JveFNnZU8wYnQxZVFaRWIxWWtOdUNCUTRHLW5hLWNueEUzcGJ5Tzc4NXpseUw3TFViZHJwZ0k2OGFEWGt0RnJ6V0RjaNIBlgJBVV95cUxNQXlWaURfa2owSFdwNGtDa2JvalN2M3RKYmlaYVl2d1M2QVV2TURNemU1dmlOMnVqa29EX0tqYm44OTNDUnc3NVpoSlU5Z2YtYU16T3AzNHlaWGFyMWkwNUJ6SDFHM1o0b3hla25rQkNvZ2t2cGo4c21oM0txVUdzeDhPTFRYOUVUN1BHSEt1ajROcTU4UFpJc3I4WmxIMnVCbGZKeGpYZXFMYnRRSXZqUjNVUHNNaWRaN2U3THZqWEtHYVEtS3FMVnRiRmNNR3p4UkpSekF5ZnJtM2wtUDEtNER2eGhhdl8ta3dBeE1EbS0wMlktSnhjaFhRUHQxalFncHk3WThfeEZrWVNPN1lzbm50dHVTQQ?oc=5", "source": "Livemint", "published": "2026-10-28 05:37", "score": -0.802, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex falls 500 points: 3 reasons why the stock market is down today", "link": "https://news.google.com/rss/articles/CBMi6gFBVV95cUxOQUdsVkg4RjMtMFpldFBOTi1NSFVMZFZaR0dXeXFrT29uRUluZzlOUVJGaEh5aUZ5WmFBY050eUFHdTRDZ3pVOS1yZDVZMjRwa2tvX2h4OW1MejktVHFqZHk1VWxTMU1EV1VjcUhkSnBjS1k4elhQZkpzazNzUEJXLUpjcUsyVklKeEJ3N1oybTNqXzVvU3RhaVBPVE1peS1XR2JSVk8tT1l5YldGNV80S2dDd2l0VE9yXzNIUFVQbGNRSnByN0RZWE9XX25pam54ZFNBa3hqcHJubzJ6SHhGYl9lZFdMaGFpU3fSAe8BQVVfeXFMUEpDRGJmdmlHNkU3Um5xRDBRSWhFZWFIeUVwUWtGOXdZZ19jMzRhajNOdTdfRUhhU3NQTVJzdVQ3YWpNNWdSVC1DcmdaQ19fUzR2UmN4a2Z3NWV0TVVZN21jOWFNbkhwbUtjQnBsZlRQTnYyMDhKei1KNE1XZFFlTHJjM1Fmbl9wLWFHTzFTZXkxUzd4TUhYUnpRSy0tTWVyM1ltTW1pZ1Q0Rkt0eEItNVFiX3VwYnNuWTJNYXlINGl4UUZHeG1YVlZhc05QNG5rQzRmX2xnMTNCWkpKcTQtVFk4bGNqOFZEVXBKalJJUGc?oc=5", "source": "India Today", "published": "2026-10-28 05:36", "score": -0.382, "label": "Negative"}, {"symbol": "SYRMA", "title": "Syrma SGS Technology (SYRMA.NS) Jumps 3.67% to \u20b91575.3, Approaches \u20b91654.07 Resistance Zone - Time Weighted Price", "link": "https://news.google.com/rss/articles/CBMiwgFBVV95cUxNeXpfQm9hem5Ed2xQdUZyMjYxaWUwd0pFME01Rmoza0E3VjctMWFyUHlBNEpNVWNaTkdyc1dBelRsbmZaWVRObEx2eXFsS2hxWVpsRGVDeEEtYmtjcG1rVHNzNllEbTVFVks2YklNTFJiUjU1Qld0bUZjVUhxN0NzYmp2dmFOc05wcmFHOFV5aVBhRHdBb2dmcERPZ2RhMEZ2UGpfeVpxZTJJV2hnZlZFOGdJcXJZN3N6X21uVDY4TngwZw?oc=5", "source": "https://www.siam.in/", "published": "2026-10-28 05:30", "score": 0.459, "label": "Positive"}, {"symbol": "MARKET", "title": "Why Is Stock Market Falling Today? 4 Key Reasons Behind Sensex, Nifty Crash", "link": "https://news.google.com/rss/articles/CBMiuAFBVV95cUxObWxhVDV4ZlIydzBlUDdmdzFaMGRMcWw5N3RjWHRSWnZKOU85V1BaM1pOVDJBU0NjcUcycEZ0a1lGdTFjT2JBU3hGRl8xV0tmRmN6Rk9pSmo2MTJXLW1sRTFEZXROZ2NyaWlOc25CajVNNlBBTWN1aTNrWk9rTDU0QlhJaUt4MHV0cDdwSUs4M1M0WEZGYUJxTWtUUDhJeUNRc1Z1NXhlZTRPZHFzZmgwQzlWQWNxeldN0gHAAUFVX3lxTE5jb2ZQVkFqMmdkV1pQR3ZUaFBnRnNEODlSbFdlOWpxNGUxVnlRTlZjX1JraXlkVlZhNjc0ektuZ0VpaVFfbkhwRFI2N3JaSEtKc0pkZ1RQRjFVS3hhQlFVSUJHdE0yODNqS1NJRXc5LU9mM19GMWc4ZjdfbXd5WnRZTWpqTDJ3eGs3NnUxNmdhOWg2S2YxS2FnUUdPOFZoQ1JBdElkQWZJaVBNVXNuRDB2c1dpSEpxaDVwWWdKOFo4LQ?oc=5", "source": "NDTV", "published": "2026-10-28 05:26", "score": -0.402, "label": "Negative"}, {"symbol": "MARKET", "title": "Market fall explained: Sensex dives 995 points intraday, Nifty at 22,500", "link": "https://news.google.com/rss/articles/CBMi0wFBVV95cUxOajRZeW5FeTk4NGJnOHFzaHlmWjd0WDk4NU9fWTVlLXJqWjhpUjVSaUR0UHZpOW9jN010OWhpQU1TakwyMlhSWlM4dFdYZnlXbnRsUzlQeW5FZnN2MThOLUNacHZCQ2RzNlkzaFZONzZTVXNPNlk2QmVZcnFJOGdRM3hPMDFGd1JiSEViZE1KN3pZRF9MN2NXcWo4amV4R1VMVmxkMmFxSDJXNXhSTDZXWHRaakpIdkIxR2VUVmVqLVdVWGkxN1ZtRnRTUmlQS1E1T1800gHYAUFVX3lxTE5tUW5DWXVQQzNNazEyRy1Jci1SeUNrSkNCOEc4OXBJZVR2NTluNUxidGtDNFZBSEttQkhHNEhOSE51ZE5taEZaa1JyX1NEZlZTRDZHWUtOdm5KdVR5d09wMmdsWDVCMlY1SlZhdGxFd09oWXpmUkc1YmRIdUVTa3duUWpLbkF4R09WdURRSER3WC1BYndqYno3cV9Fd2RJNXB6cjk1eUxTMTFISFhHOGcyRmpuaGNJUHlMU2tINDE5UjRHOTNualZLMFlITjA3Tk03RmV3a1owVA?oc=5", "source": "Business Standard", "published": "2026-10-28 05:26", "score": 0.077, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex Today Tanks 793 Points | Nifty Below 22,550 | Nifty IT Index Down 3.1%", "link": "https://news.google.com/rss/articles/CBMisgJBVV95cUxNNTE5SXk2WlQ0bDBjSGZrYVBzRWtub2dySmF0Ym9rV1hFYTJ4aHdrUU02UFF5dzFQN3o0X2VhMDAxRTFJX1ptLXRsSGZOTTUxbzNIcGRISTN4X1JWSkZRa0RiS1Ytamh3Vmh6Q0huNnh6WnNQbFI2S0pKSWNQYXM0RG0xM3RvUVhIT0VRYjhQMHJrMFNTd1R3N0FHcmNfWnM2RDh5SndjdVVmQTBNdlUtdlplM1FsYnRoeVc3SHhDUE5nMmdLX3Z1Y29VLUpuN1JGS0hvMXh4ZlVKV3BycHNRU0NZMlFLY0ppcUpHNDQwVWtLRzRFRmVEam5CazVycGszeWlJTU1CRkxCY1A4VkUzTXpWWEZoN1FlRGR6MC03ZHdfbUdtdG5wZXJHdzVZUWpodmc?oc=5", "source": "Equitymaster", "published": "2026-10-28 04:56", "score": 0.296, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex falls nearly 700 points as rising crude prices, FPI outflows weigh on markets", "link": "https://news.google.com/rss/articles/CBMitAFBVV95cUxQN25aS1ZxTW1tUkNIMkpGYTRyUDdKWVA5aGF1ZnRDY3dpZkRrbjBjWUtjRjVXbXhLRndScEdobk4yUW1mSi1mN1hzQ2poVDBlYWJvanJDVFFNNEl6c2k0aHVIWFJ5bHMzNG93c1JTQ0YyczFtTlMtR3NKMGhBT2pRVk1xSXNkYjJCMFhaTnB5Rk8tMDNCdzlVcjViZkR6azItdWt3MTE3S2VKcWZTb0RrSkdiUXc?oc=5", "source": "DD India", "published": "2026-10-28 04:46", "score": -0.743, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex sheds 691 points, Nifty falls below 22,600 on rising crude prices, FPI concerns", "link": "https://news.google.com/rss/articles/CBMisAFBVV95cUxNTVhwVWxMZ0EteGF2NHZ5ekpSamxCN24wVklBaFljblVtcWhNY1FLN0tpcjRuWWFIQmlRcEIycmY0eUthaVZLOUVOcjBuU21XR3pXdVphanhwdnp2a2dtY0tQSTllbll6dUpOOG1PcEducmhrSzR6blhxTlNHTnFRT0hETUdZcWhWM0xXTEJuMzE4Y01UYTM2alpOVnBEdW5ZaGUtZV9LQTJEeV9mM3gyaw?oc=5", "source": "ChiniMandi", "published": "2026-10-28 04:35", "score": -0.735, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex falls 684 points, Nifty drops below 22,600 in early trade", "link": "https://news.google.com/rss/articles/CBMikwFBVV95cUxPWmExdDBRYTNiejJZeGhPbEhsUElycDA1N2JLWUNSb0xKWFpGSi1vaEJSZURnemxYbjZwNkMxRm44M1d2cG9wTVhhLW1CYlowSm4xanZ5OV9tQzdIVFhrVTJ2RWpzLXlHUU1GSHJWYnh4QUtsV054dm1oYXRSd1QxTmQyR0pPX2N2b1hDSmg0WGxXS3M?oc=5", "source": "Telangana Today", "published": "2026-10-28 04:35", "score": 0.026, "label": "Neutral"}, {"symbol": "MARKET", "title": "Stock Markets Today: Sensex, Nifty Tumble as IT Stocks, Crude Prices Weigh", "link": "https://news.google.com/rss/articles/CBMixwFBVV95cUxPUjYzTTdhbkI4NlczWmJKbWxMblNncjdaQnpoRzVQbTBjdEc2YW9hZk5rclZ6RXVIU2hJOGdpTkttMUE2cTFieVZ2ekg5QVJQbU1vWkg1cHFIMFRzYlVjM043SS02aUozQ2xQenQ3alZMZzJ6U1c5VmJJejk1NS1RdWhBcTNyeHBZaWhadi1UdlpJQ05rUWxBTkJaOEJtejBvNThXSXlnTVdSWWxhSXVVdG1vcGJpQkZFZmNSM1h3T2NuSDg1NEsw0gHKAUFVX3lxTE83QUF3N2RZejc1a2dBQVZQb1pmczFoWUpSeVYxNVhBRjFqRDlYMTdJTEZUdEhuQlpyUTJMUUI1T3JYaVlqQVlaN191YXRpNXRxb0FDNVROdnEyZlk5MWVFM0tvSUlLLVo4X3dJYzhsTjlUTkdWdDdUSncxdm1TQm5FbFgyWUwxSE9BSXRtb2ZtN04tNmJlQ01qWHNHWkF0TkNtZ3FhdkhyejRqVVhzSHBWQ2l1Y1d4cWlOQ3FYdm9IMC1iRWdqSVJGa1E?oc=5", "source": "Rediff", "published": "2026-10-28 04:32", "score": -0.25, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex, Nifty Slide as Crude Near $116 and IT Stocks Tumble", "link": "https://news.google.com/rss/articles/CBMi0AFBVV95cUxOUVVIU2hUd1lTbTJOQWNJeUdXeENUbC02SEJ3M1JPTU1acnU2d2NHWmxucTB3Nk9MNVZjc29BUGprR2VSZzhZN2UyX01KdEdBWDBFQ3h6UVhVQlRtYnJaTE1TX0FGSTFvMGo5SlQ2RnVfNnM0TDJLTV9lVXFRRzhGMUQ4OTN6bXh3M0tPaGdLNmgxUVNFZzlxVjg3Uzg0enFlUE8welpMT1E3Z2NnWUhkcmxhZkNXUFg2R3FnajhTaFlKV3I3bmVqWG8wMHFmSHZq?oc=5", "source": "HDFC Sky", "published": "2026-10-28 04:32", "score": -0.25, "label": "Negative"}, {"symbol": "MARKET", "title": "Why Is Stock Market Falling Today? Sensex Drops Over 800 Points, Nifty Slips Below 22,600; Key Reasons Explained", "link": "https://news.google.com/rss/articles/CBMiigJBVV95cUxPWWg0dDRpcmtjNklEc0lVSG5lZWxUR2JXMF9EaDR5YWozMk1rMjZhU0hOQjhaR0lLMDZFYWNuNUxPV1NmdkdLTGRwMnRMVDVDNFlaSmpONU5qellPa0lVTjRfZ2FxWERCbVptWWc3WFlZazJTUlp0bW53U3QySDBHMW9Ic2g3djNHbS1oWV82NHVmWTQwaDNOU3UtWDFqRmtjSi1jZUgwczZ3dW16SHFYbXhieUZQWlZRV3ZnbVY0bjFyZXdyS1N6eG81QnU2c2l0dFNSdlRCVXFhdTdnSmN5WEdkQ1dGTXZiblVMUVRpX2NCLXA1bWxadmMySVFaZDcwY25EQVRyY3BHd9IBkgJBVV95cUxONzVPaXVRSE1WNE8teUkxaWRiR3JXMklmNk55OUx4YnlTX3lDLXQyaUx3ZXRtekFFcm9XbDlNMmt6NEJYeVpzNlJPRF9DQUVzSS0wbDZSTHE4QjJ4UDhCRTJNLVMxY1hRV3FoZFhpeGVqQkpFWHdqYzVQZHpIb24tckxGWWpMTHVtN0pQbXBfXzczMG1kRFVnN0ctWXdCbmhKNzV6YlV0dnNyQlFrX1hjZzd2bHhfa0tIZ3l3TDhqMnExTFVlcnIzci10cG1YSURiWUpvMEs5S2JNV3hZdmYydmRETGlKMGE3WGVrTC1YLWtGbFVfcG82MmNtZjZ1X0tGZEN2U1pyUkFVQWpPVEJ5d013?oc=5", "source": "NDTV Profit", "published": "2026-10-28 04:25", "score": -0.077, "label": "Neutral"}, {"symbol": "MARKET", "title": "Why did market fall today? Sensex falls 353 points, Nifty closes below 22,700 despite Jio\u2019s solid debut; 4", "link": "https://news.google.com/rss/articles/CBMimgJBVV95cUxPN3hVTktXNUNKT25YaFFQM052YXZtRFJhT2x1cmVuUlZ0SmZqWEM5VHlmcjJrcG03cFRiZHlmZzdKMjRiT1VOLUdBWFc1Y3V1REpYdzd0N2NXTFBMM0hVRExkZ3JjS2NZX3hObU5PTERMZmJ6VGVKSERCeEl2bmp4aFFYcXZINEplX3FCNGwtMzZxamJ2bzAwcTF4ZmVHa19UeUJPS1NfUW5FWHp6cGM5c2tjRGFoT2NMNXJQQmpHWk1VaUNqZkY3S2R1dlZLbVhpQXgzZUJlc05zdHpHQU85Mm13a1ZQMzZtUHc3WDNBS0tReWtVQmFiVHdWemtzLVFuM1JUN05wbm5fYlNpVjNDNEV0WVdMMGFOV1HSAZ8CQVVfeXFMTlgyVjJwSnZEQURZMTMxWFdXdGdJUHdhVXdxaUR3Q2g0RjVBaG1PazdmQmlfNU13NUVNUEQ4UVoyaWcxX015ZGFiUGdyc29LQzRXanMtODBZbGlVQVFTTV9sRmEzdHA4NFdOUENlU1F2WjkyMloyTWxyNzJvMkZRZU5HZ0xxTVpsOHowaVVYT2RqdGNGeHBMb2xkWUpaM0g4Tm5YaW5qcmRQRHpta0FUVlRvVVJhaEJvcHc3Qnl1WWhxMlQyaEFUTzVFZ3d1cDRBUm02VFpvUzNuWXFQQ3RPdTRVTzVOME5TeFZiUHYtcGFUQ2RPTklPbG9iZXVfek1PcHk4bVNsWmdtXzNIWGtuREtWZF9OLXRpSE1Ra0RLU1k?oc=5", "source": "The Economic Times", "published": "2026-10-28 04:06", "score": -0.411, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex, Nifty open in red dragged by fall in IT stocks; Infosys down 5%", "link": "https://news.google.com/rss/articles/CBMi7AFBVV95cUxOZ0VWVnNwckNzWGp4dnIwU1kxY09iakhsLW5TMnBWRmkwQTlKc0JvZF9BZ3VmTFJKb010SGVSM1NMUmhwak5QUVNOQTZ1Vm1uZFA4Z25LSkNGaEVLcjZyRF9JeWwwbHBUa3U4Q0VoYks3b21GT1c4YW9SQ2FEQWM1QWNsSHVYMVIteDc2NHY1SElEVFpFTVRhOTFhVnR3NjhFZHhpWnVHRmpTbnVqaDdabWpsNEVVem5vVlprX09wbTgwZWRCVXEyNFgxTEJobXFzOTJsdU5sZk85NXRtLW4wMEVEUHVGNnFsZ0w3Z9IB8gFBVV95cUxNNXJvUWlJOHllZ0ZpbkZsNzJ2am1zR1J6MnVNOWV6RUZXbG1fSGxjODRvdGlsRnJMTkxVQVM4eXg5eE0tb29oTzNpLWUwTUpYdmJST0E4MVF3Vks2OU9kVU9LZzV1dG8tY2hiclVLTHUxS1FxR2ZxTGNQc2pQNVoxVHJuZnFhandSd0RqWmxacUloUEpaV3NuZDZoR2JiUGhPSjZPaHdMT3ZxX2pYcFRYQ0pjcnhOVUROdjFMNUxRNWpjdl81enNHY1JnN1lRaHFnYzdMcERoWUNOTkJjUVFZRGp2bE1fR0Fhd1R0c3EzY0JsZw?oc=5", "source": "India Today", "published": "2026-10-28 03:49", "score": 0.026, "label": "Neutral"}, {"symbol": "MARKET", "title": "GIFT Nifty crashes over 220 pts, signals weak start for Sensex and Nifty despite global rally; US Fed in...", "link": "https://news.google.com/rss/articles/CBMigwJBVV95cUxQODRoS2dkTW5ybk9WdnFlU216MXdvdFdkWXZ1YVlWbFRvcjYyZDFYZG9KanZueFFXazEzQ1ljRURydm9MbWlMNmM1dmY2dHpucnlXOEIzNXdWRVNBc3JCR2FnZkhZMEMwLXlpVS16UmtvNWlKR3BDRFIxb1pIY0NQN3EzNXRlNGc2Vk5yV3EtX01JOG5lUXFmM3doeS15Ml85WWMtZmtlTkFCRjdmU0licG9DUDIyZjFqMzNUUTBjRG9MQV9FVGhlYjZJV0lYQnE1elJCb1RJZFhCN2VUWEpmeURfYTYtdmM3YlVpckdORG13VHMwXzVvUWh5OURiRkFkZWh30gGIAkFVX3lxTE1yUWV2R29fUFY5TGFZWUZLRTRlX3RTQ3R3cHN5dFpxRUVqVFllUDVZMFlQZkd3cXN5MUlCWlpNMl9ZQXJEdFNuRFBfZ0E4OFBSVGtWdGE1VWo2LUNyYVg0ZEN1Y2xZRnBEQnZ4QTNFOGhjVXNCSWlhdUJfc3IwNjR3N1dDdENxbGFMelRSTEJnM1paN1RRY1dMTDBQUEg3XzhXWVU5aFQxemRXZ3ZvZUhjbWg1Q3ZzWkEzZzJkeG9NZTUzWkRVa0FNVlRQX0lIT1ZZQmZtdkItczRDME9tUnlCUU84cnU5QmNVQy1nRi1LeXI5YTVwVDFxZENUYlkzUnI1YmJKRWRXWg?oc=5", "source": "Moneycontrol.com", "published": "2026-10-28 02:47", "score": 0.606, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock Market Today: Gift Nifty, Jio IPO Listing To Nasdaq, Kospi Rally; Five Factors For Sensex, Nifty 50 On Oct 28", "link": "https://news.google.com/rss/articles/CBMigwJBVV95cUxOV0NNUHlXN193VWhlcWJONTl4M0taMm1wN0ZUcmRoOXZNZ1dhWkdjWjY5a3U3ZXJzNTlHRlM3NjZuY095QVZITERNU091VFVud1FYQmM1aXRVc1BnQ1NKSzlMNDJtMzFwdUpUenRjLThPZWJIRGxvWnRiYkdxSnlwYUIxS0NRWU9ERnJ4N1FhRGIxSUxWRm5USjRGdGtnWjRTOUtTUzJFVUoxNF9vS0ZtNVdSbm9icFZJRWM5UWp1MndBcmotY3FvNHlxeklhOElDaU5ZWUR0VG96MjVKZUpkSC1ZWW94NWU5d2czcW15OU1sXzljN0UxSTFIeUwxLVp4ZXVV0gGLAkFVX3lxTE1CaEZOVXM2WVpwS2RtSGNma1A2M1ExMklaUXR2eFZnU1RDVmZLV1hjTnFUQkJxNmJiamJPdU96a21udE13bm8xZ3g1LWdIRXhaekJITWJPMlJ4b0ZwM2hCSENsRV9QNjFWUTU5X1RDcjV1aXZHdkNBVkg4em1YalJPSV92SGJNUDdJWFNLWnZfSUNXTDhWSDBMX3FtbXd0aGlzVWVPMlpVbnV4VkJYY0U2RHRSU0doa3l2TktzZWRKdFBoMUtjUU9rWHl1UVlBZ1lyc2VCS2hGdkwxcXFFbERVQndQS2JTOHgtMmJuUEhVYlZSUXRTZGN0bW5NMzFmdVIwMlNzUlcyMkpjaw?oc=5", "source": "NDTV Profit", "published": "2026-10-28 01:54", "score": 0.883, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock market outlook for 28 Oct: Sensex, Nifty prediction - Jio Platforms IPO listing, GIFT Nifty, US and Asian markets", "link": "https://news.google.com/rss/articles/CBMikAJBVV95cUxQbGQxcFFLUDN1THJXOVNaMEsydnpFQWJjQVZRWW9jNGJXczJxZDNpdElrOGx3bFluNFFCWVgyM1RQR0RUWFgwTGFCc3FaLTlBcTVGQ2JDRUNCVll4cFJ0V2pxVGw1TkJaTjZqSjE2VGZHZXdqR19talF2N085OGJBYjF3M1lCaWNlZjFLRGtaNUVBVHpIWi1mNXJaTE9iZVREdTkyQ0djMWNGdGNaZkV0WGlqOS1HTUJUcWRpSDZYTkc0VUVya1JBSEVzLUlibDhZUjJfS0JrdVdWTGJTYWJpTXVWeWRNdU8tSXZHQ25ybmtZQzlhR21mNzl5TlBtbzhNRnJmTFcxN2VWLUdJNEp4Q9IBlgJBVV95cUxONVlXWWJCbVhCZDBjM0ZhUDlEcnBWNVJUdTNGNjJXeXV4NlRpY2lwQlNmVFM5dDlwdVVEejdRX2MyZWFvbG1LLUJ1VGc1Zy1KamlfWHk3SHRiMlAtM0VBUjY2MHIwVzZyR3Jyc3ZMNnkxSTlLTUNHQ3hRNHdJRi00UEZ5TDNrS2p4UGVxUFhyX19RLUZSOXd1c2NzSm5LczdpRkY1UnFzRks3cjdBX2NWVXhVSkZoaXNfOGxvMXQwX3p3VVN2M2tVZTZmRDIyZ1FvN0tfTWF4LUt1ZXI2RTZkTGY1Zndpdkw2Y3djeUdNT2pwOU44Q1JXWHM0UkV0bEdTVWpaVTZ3SXA0SzZSTnYtWjBLMUxldw?oc=5", "source": "Livemint", "published": "2026-10-28 01:45", "score": 0.842, "label": "Positive"}, {"symbol": "MARKET", "title": "Reading the Nifty 50 and Sensex: What the Two Headline Indices Tell You", "link": "https://news.google.com/rss/articles/CBMiqgFBVV95cUxPNnFuYVBDbWNVdXpPblY4eC05ZTlEWk51T3dWSEVPLUJaRzN4SUJLWkRfa3VfbGN4dFJqeVY4WV81V3VPb18tUmlqS20zM1lIZ0dwRmVzMGxPUE1oWmdFdnVtd3gyOC1OYkdsRXVjZGd2R3BVV2YyQVMxalFfd1ZZMDFtNENrWXNtM2hjMGdXbVFPclhXeUE2N2RRU3Jfc1Jrd2pGRXd6WE0tQQ?oc=5", "source": "www.tmgm.com", "published": "2026-10-28 00:40", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Markets end flat ahead of Fed decision; FPIs buy shares worth \u20b94,240 crore", "link": "https://news.google.com/rss/articles/CBMi8gFBVV95cUxOeGdEaVY2NjFmaFl5cU1MSmM2SmRFWEQycFhUMjNlbkRkY3I1SUpfOG10X2oyLW1jd0dCb2wzNkZ6dWZjcGV5ajJJWmMwVnNKRVJwcDJ3SlY5NU5rSEpCUVh3bFE4cDhkeHZFY01GS2pIYlU3ejVPY2VpRVUwS2dkQ1dXZzNVRWtsUkJxSXA4NTVobHFpcHFYU0lGMHdlc2hBSUI5eUQ5RldFUDRzMXZzTHJVVzBnMFBJM0xGc0l4Y1kyaTJCbnZMMnc5ampMbk1QOHF0a3oySjJJNG0ybXNOel9sdjVPZE41RVEtWkpKUU1OZ9IB9wFBVV95cUxNTHFKcFdlVGVRcWtEMWlTWUl3XzFDdGJ0RGJRWXBnLWFBdzQtZ1B4UW9mMWEzbEhoVkxRZXZXMWVoN2VXeUlWS2VfS1Z2WVpWZmhacDlZRjVDSFhUbFl2Qm5GeGRXNmRHaURwNjAydk9aSmJxSTFPclc4UTVydmN2X3dxdmNNVllMZmJReWlqUHFwSEZnckphOTRwUEpCRHFnV0lOM19MMUZKWGZqOUZ3YUlMTEw1OGhIUVlRTTFsSnZTWXUzYmZhVXRGZDRwN0liZHIxcTU4NG50X2NiRXBRdHdaelEzc05oaExtbFpYSnJuSnRrMDRR?oc=5", "source": "Business Standard", "published": "2026-10-27 18:08", "score": 0.477, "label": "Positive"}, {"symbol": "AETHER", "title": "Ather Energy shares: 125% YTD returns! Experts give 'portfolio stock' tag after Q2 results 2026 | Target, stop-loss", "link": "https://news.google.com/rss/articles/CBMi9wFBVV95cUxPYmlLLVpwT1RwQ2tYR1F6WlNVTWJ3N3h6R3MyX2ZvVlhHUjlDZVdHTHhGeVF1dnBQOEdjb21UQUFuclpzTVh6a283ZF9EWWJqb1lreEp1dzZFMEx0eVJLQmlUcXc2elo2SEE2c3ZiVEZLYk1sLVJkZ191cnZOb0QyT1pBSUxfR1o2UkRoMlN5dnlnWklGMC1OTVp0bmlNaFJwdW1JOUhFdkg1TWlIZl9xUUwweTlfUThhaE9oeGstZ1ZnaUZGckh0b2xsSldWb3B1Um9MUWtCUDJzTmQycFVUTExRUFdGSkx1a0hubHVjYmtLZEo1ZGRr?oc=5", "source": "TradingView", "published": "2026-10-27 12:08", "score": 0.457, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock market today: Sensex, Nifty flat as smallcaps rally and IT stocks fall", "link": "https://news.google.com/rss/articles/CBMi0AFBVV95cUxPWGZBRmlDeUJ2YWlaNjVHQXo2RnRkS2R3VlRrdEVNd0t2Ymg0Ri1qQi15dEI2NFdhYkRKSkVBejd6SzJZSS1FejBQcWNaNmY5UC1ZcUVqZ0U4djcxNk9BWHZmeEFQRjNrT2dmZEI5bkUxUlNMbk9HTk9Uam9zRGlDclI4bmNVOFNYMS0xQ2tQUm5SYjdvb2Vmb3NsaDFzcExOeWlRT3p0M05jbnk3VDlqQ0ZKaExWN09RdGp0ZVZUQVc2X0VxYVlKNjVZZDRlbWVv0gHXAUFVX3lxTE5GZHRLX2Y0cVZ4eUM3TUUtZ0dEMTd3Ml9senV2YWFkTmVXX3RndG5vZzRFN2xJNmZidi16ZHhVTllyLTJzcUExcWp5SDJJVXJnRUtpOF92WWNXMkNnN0ljVURlbVhwcENBZmFhYXBGNTRyazhwZ09FMURzd2dRSDI5dXZyTW1PYWlfa0FZV1RTRkRQQ3lfSFVFT3ZGSTZvMnVtS2VQck9yYTFxbmlfX2pOeUtEN0xybDBKeE9CU3A2T1RzVFNVNUM0dk8wanVnZHUwWGEwMTRV?oc=5", "source": "BusinessLine", "published": "2026-10-27 12:05", "score": 0.511, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock Market Highlights: Sensex, Nifty 50 End Flat On F&amp;O Expiry Day; Asian Paints, Coal India, Grasim Top Drags", "link": "https://news.google.com/rss/articles/CBMi0gFBVV95cUxOTkxWdW4yQXdPNm12MEU0dmYwN29LYl9tMjV3Zml3WmhvNXdpU3doc2h2bWEwcEE3cElFRkVIZUJjeTdTdXl3OWxZZ1luUG84LU9vbGRsVWNldnhPNWFWT2RTRUJMNUxaV3ZmWmxXQ2tHelJHMm5UdjFCSFpRNzlVYjcyR19ZZ3ZicVhrZVFITzAtQUZXaFRpZlBaOUpHOXhhelhURW1qUmhhbEJfREFOQ0hnSUJ4V3RHVHlTMHZwV1c0d2dHSm5UV0pseFJCMkJjaVHSAdoBQVVfeXFMTmx6S1hjeHJac2pGQjRHc0ZwMWw3c0R1Z3o0Sm5paS1VMG1ILW5ieWNnN3dXVUhwZFFVSm1YUmdTYURLdDdVUEpTSm1vaFJVSGQ3MEdqb3VOVUdVVHJGNGhSb3JRM2pwWm02aUEtd3oyN1ZUVG1XVC1iam1zTjlLY3VJa1BHeUNYc3V5NXFTOW5aVmRSOGI4WUNQdmxpT1hzcUFjMk5lQWlrd2lyZmZxLVNDMUtHbFVqNjEzR2Z0V3VRREJFcm9uRzl1WHB2cklZeXN1VU5FY29tUXc?oc=5", "source": "NDTV Profit", "published": "2026-10-27 11:36", "score": 0.273, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty End Flat as Oil, Fed Jitters Cap Upside", "link": "https://news.google.com/rss/articles/CBMiuAFBVV95cUxQNmV5cmNlY2hydnc0SVZGcWdIVGZxWEhyUWU3QlE1M05YNUpMeWw3R0Q3Z2JWdUo3d2tSZHdjR1RRV1FQVlZOLURJTzBEOVJydkFXREtsUmpkeHFIemJOMW96Z3c1MElNVzlLdzVlcVEzX1N1OEhvTW10NFdOZkJUUm14RzU4Y2ZEOXAwWHZzY0lGbEpsY2FDWFZKZUZlZ0JDamZKRzJYcld5ejdHU0RDS2VnaS1iTmR2?oc=5", "source": "HDFC Sky", "published": "2026-10-27 11:30", "score": 0.67, "label": "Positive"}, {"symbol": "MARKET", "title": "Gift Nifty Signals Flat Start as Fed Decision Looms", "link": "https://news.google.com/rss/articles/CBMiiwFBVV95cUxNZ3FjZTljMEVjbVliUVRyeW16RzNKZkNYaHJtdkRWZFQ5ZUkwdUNwbGpEdGVYSl9HWXoyc1NHazVObXZEVUZBcFlxTnZkZmNnRFpZUk1JcFBhdGQxTTk1YXdneU92ZjFDcTVHWlYxTS02RWpDNnF4bk9IOFVXTk9KU2JFZDl0WE9DNmw4?oc=5", "source": "HDFC Sky", "published": "2026-10-27 11:27", "score": 0.612, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty end flat; Sona BLW jumps 9%, Mazagon Dock falls 6%", "link": "https://news.google.com/rss/articles/CBMipgFBVV95cUxNM3hGaVpJZlFtTVRTRktjY2JJbm1IRGNub2t5RGF6RjZpSkE1Vnh5ck1JNlpIc1JFMmhwVkJVWkR1ZXRUcXZxX1RFYmtsNkRyaFl4c25HdkJBTEJ4ZzQ2OWZaRk9DTDBZY1FudjQzRUpOTEhUazBuSEl0anE0ajBzT19hS1kwcWd5eWFRV0gzdmJid2hGY2FtOFN0ZW00ci14aTVxQTNn0gGzAUFVX3lxTE1lalJJTGtYZDlNU3JHQzFtUGdrdUdkOFlRTTVMY0hub0JkQzB2UFplTGRYX1ZXanhTR203bnRBUy1rc1BFM3FYMmRHN09iYWFWajBZZUsxVzJncmdlOUxtRW51NEpwUFFIWkx5cGtpYll6dGMxSW52SFJvYlpST2dUSXZpSUdXdVdZeEdGSmxyb0VsRTBYNC1nQnh6blNPSUx1VG9rVTVjT2prT0ZmeUNvM18w?oc=5", "source": "Fortune India", "published": "2026-10-27 10:50", "score": 0.477, "label": "Positive"}, {"symbol": "CPPLUS", "title": "Aditya Infotech partners with Ranveer Singh as brand ambassador for CP PLUS", "link": "https://news.google.com/rss/articles/CBMitwFBVV95cUxOYV92ZHBGUmxnOU0ydGQwSjdwUnBLNFBuMHdjbGhLSWpRYzI4ajM2dEFIVW9lQkV5NFZOdzNYeFJtS3pISkZXMVZET1p3aWZXQ1N1cU92OUNMa19wNGEycXF6Ykw5SlJ0eGVreTZZdW9UTktVbTFGeU5HRHpuVWpLOTQ5SWo1bTJKU0tJNUlVVzhqYnBoMEpuVGFWelJ1U09EclhrM19FeVNCbVFOUENnZ2xraFNiZVE?oc=5", "source": "Business Upturn", "published": "2026-10-27 10:46", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex Today Ends Flat | Nifty Below 22,750 | Axis Bank &amp; Asian Paints Top Losers", "link": "https://news.google.com/rss/articles/CBMi1AFBVV95cUxOZnZSRWJxOEQyWXg1YVB1VXlXeUFVbTVicHBxMkxUbnJxbnhhTlZKU3p4V0c0dk1vbjY3NVBpOFNmRVUwNWVCSC00ZkNkTDNHRHUyOVFpWVZzMXVRQzNzbWtLMGEwQ3ZRaEZCVnl4MVN1WXQtTmNVa1Z3ZVFDTTJxeHZYQzJwQlpmQU9FTjRtRldzUXhGSkJFQ2tpRURXVnJ0UTNXUmE4SE5lLUdXSmNlYkVpRGpnVzI4akcxcENlcG83QWJTNE1RZEdDOGVNVncxTnM2Nw?oc=5", "source": "Equitymaster", "published": "2026-10-27 10:44", "score": 0.026, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex, Nifty Flat Amid Bank/IT Selling, Crude, US Fed Caution", "link": "https://news.google.com/rss/articles/CBMirwFBVV95cUxPaE94ZzJ5dnQxdWVKWG1pRDVyUGRja0JfdEdSdXBnMzNLTjl1Q0ZhRUNfMDNmTWhRamdJQTJUZzNBdWNSWG5TYVp4OUQ3Z0p2bEpTTk9kZUVJY0thSk9IM19qSy1DVkNxOFR6SFphTEkxWHRuLVl1T1hVd1BDUnB1MFpaZ056anFvZDZhSWFDMUJ1V2czT3dNbnp0eU56MkMyYUtBMnZFQkxyVVN5OTBj0gG0AUFVX3lxTE9sdGR4dWFjdV8xTHpMMTFyeERSZEVjNWNBOFpNWW9DNkN2M0pnYkc0T08tVlFIQ1V2cnlrbmF6OGZwSnp2TDdsZmY5dTVadTNHdFRHdEs2cUpBQlRieFFud1hRS0daLUNzMTRrRUFfLVhXT2tFV1JVQ2t0VDJXQm1QZmFsWWZZMko5eHpBODE1V3dZVENIb3ZYMWk5aHU1b1QyUkd1ek13VkNOSS0zbHRzcmpycQ?oc=5", "source": "Rediff MoneyWiz", "published": "2026-10-27 10:43", "score": -0.25, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex, Nifty end flat as high crude and Fed caution offset sectoral gains", "link": "https://news.google.com/rss/articles/CBMi0AFBVV95cUxNSE5fd2R2dlZMSHNPUEg2cnQ3WktSX1BzbUVuWnE5aVNkdlZjSzN5NkVXZzZHUE1MUldtRFdCRXYyX2l2WFo3allFekdTSW91VEl4RFVoWG1mZ2wxOHk0YmhNRXo0dmZfNkdUZUt0VGVGNmhsMkN1d0lCaGxDS2VSTFh0WGpmS2dHSVpfMWUycTZTVTZ4bjktU05VQ0FDOFZHVlBoNzhzUFYyNU9YSFZVUUM1WFg2VC1yMHFCZmJyMEZwWW9pNzNDWlZjSHNjQTRS0gHWAUFVX3lxTE44RkJWdG9HajgtbVZVSjlnQ1hPdF85akRSWF9BZTBpeGMzeXlNTDMwRXFpYk9QLVdfRlFMZ0xPYUI0MGpHZnVfWmZLdTJrNlVzeGpLOWdSOVNjV25EVVRBLTdqNTl4NXlGQzlucThWbWVyU1hxVGFNQ3M3bkthSnJYSTIwVW9TcEJsanhyV0lDNldtd3NmbE8wU0taeHpVUkM3RVBLQTZkYzkzMXB3dVdaSS1oMF9ndE1ZcUhXMHBiT2JjbkhyckJwQzdjZnIzLTJSelB4cUE?oc=5", "source": "India Today", "published": "2026-10-27 10:37", "score": 0.34, "label": "Positive"}, {"symbol": "MARKET", "title": "Why stock market ended mixed today: Sensex, Nifty flat as Midcap Index gains 565 points", "link": "https://news.google.com/rss/articles/CBMivgFBVV95cUxPWXUzSV8xY1IwQmZCLVJRSWl5b29heE8zSWE0dUExaUFsR1pBaGNacFVaZVc5OXUzbFdwajRYMVBFZ2tad0IwWDVrMnEzeExrWktpMHRvWFlENnFybERmSlhLVzZsa1laa3k1Yll2aUVXbC13THhFOUhIV0NIX2pwcTVOSml5ckZJRjhIY3JlTVgxenlXR1owRmdGdDZkSnZSM0w1SDY0dGVGTHRzUDRjYTRfbjhqT2Zrek1HOEdB?oc=5", "source": "IndiaIPO", "published": "2026-10-27 10:35", "score": 0.649, "label": "Positive"}, {"symbol": "MARKET", "title": "Nifty, Sensex close flat amid pressure from high crude prices and caution ahead of US Fed policy", "link": "https://news.google.com/rss/articles/CBMi4wFBVV95cUxPSFBtUFJmM3hPblNvT1VQemlJRFl5WDV1Y0NuREtvVk1abHQxWkROczktb09iMXAzd2xMRi1yUGxyNHVxdkdVbnlBbkRLaXAzS1VMRWVMSm4tckVTUUF1aEpvb2tWem55TUd4Smx5S2IzMUl1RTZlR3lhYjJQM0xfTU9Ya2FRRmxRWWRWSnpzYVlNaWxTbk9MYlFPRm5sT1FRTTBWWVhSa0h6MlNzSVM5WFhrN29JUTRkeGdRX01UeksxWlk2cllkek9GSEtCZ1NkZ0E3MHVVMndTczVRUFBkamtVOA?oc=5", "source": "ANI News", "published": "2026-10-27 10:22", "score": -0.34, "label": "Negative"}, {"symbol": "MARKET", "title": "Is India's Stock Market Heading For Its Worst Year Since 2008 Crisis?", "link": "https://news.google.com/rss/articles/CBMivwFBVV95cUxQaUVuSEo2MFlJdEl2TzJpb0FDR3QxUzQ2TnJaWVk3V09oMW8zV0w0S0NtZDRzUnZiN2RIRGQ3aElmeG5YelB5MVF3MElkYmFJQV9RX0ZMR2FsSUJzdDcydkVZeS1zZUJTSDZtYTdfTGI4cm1ES0JRTjFkd080YS1JbHNzOUFYQ2pwYjE1SEE5MkY3TXBLSE04d1BnOFZ0S3dnR1I0cjI3Yi0wUWxzSWxfZ19ydnNESlJIS0s1NFpVUdIBxwFBVV95cUxNOHRRcjNnTjFKcHlkWFI0eXBXZ2R3QmhQcGZzRXQ2OTVqdE1ZWlZrdGNBTEFlMzJtdlpJMTVPdFJpZ3pDaVRYd0Myd1FraUwtV1d5X29zM1pGNGJ1dVZ5OF82US1rRGRyMGR0UEFrb0RBQVFRRHNUR054UVdKYUJBTHhmYjhjWkVXZ1l3LWRtaWRPNTRDNXJacHpoNTYxN0Fxb3NnNHR0MzkxMmpibGdKY0hkeWh1UHNRUmZNUXdtWFdMT2hJVGhr?oc=5", "source": "NDTV", "published": "2026-10-27 08:56", "score": -0.848, "label": "Negative"}, {"symbol": "SYRMA", "title": "Aptus Value Housing Nine Monthly results", "link": "https://news.google.com/rss/articles/CBMirAFBVV95cUxPM0VaaU1ZREplWC1xY055eXdIT2RJaEFDTXFPY3pFWFFxSW1uQXYzRUFjRENYZjBIRWduanFXck84NUJobjhEMGFEMW9yV0hRd2ZvX1RJT0hvaVdsMFdMbTBWSHZiRmlpQ04wZ2IzOUN2bXNLc2drVjVucG0weWN6V0NBRDFmTVJXV0lacmF4N0RGVzhrVzRVUzQ0QzhwUFFDbFFvTEg1WjBBWEZk?oc=5", "source": "The Economic Times", "published": "2026-10-27 07:00", "score": 0.34, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex Today | Stock Market Live: Sensex, Nifty trade flat; smallcaps jump 2.5%, IT slides 1.5%", "link": "https://news.google.com/rss/articles/CBMivgFBVV95cUxNeXFmTEJhQTB3U2FSNW5IN0lub2hFVk1aSGlmU1RUUE1ITjFDcmpDTVdFQ1VJOHFzYWpqZXpoNEVUbE9pVjh3ZWE2VEcybVI0VEdLNDV2WF9jbHdIX1llcklPcjFXMDM4QzZ0MXptcGtVTjdLTjlUN0pPeFhjOS1vel9YcERQWWFibVdYdzAwTkdtak9UNV9ObGlfdmVXU2RhZGNvaW9XV2o4VFlvOXFUQmd6OU9PaW5GbEhkdDBn?oc=5", "source": "IndiaIPO", "published": "2026-10-27 07:00", "score": 0.67, "label": "Positive"}, {"symbol": "MARKET", "title": "Closing Bell: Sensex, Nifty end flat on expiry day; pharma, realty shine, IT drags", "link": "https://news.google.com/rss/articles/CBMiswFBVV95cUxQVVRna1NhS1lyLXVCZmlaaDhCQWJJc0hnN2NJVlNxS3U5SUE5WlBSSXFZV0xoaUFPd0FTS1M1aWJzcy0yTWxBa1B3QlRaT0RidFB6Um5OdGZEdUg5cEVKaTZUc2FpUFphNzBDdzZIRVM2c3N2T1R1RnRXUFJUNXdYVGJaLWVtN2Zhd1NBdUNTX3NwcmplTGRxNFBFM09XYUNGUXNGODhKTXJIRGZ2ZVI2QVo3TQ?oc=5", "source": "IndiaIPO", "published": "2026-10-27 07:00", "score": 0.077, "label": "Neutral"}, {"symbol": "MARKET", "title": "Indian Stock Market: Sensex and Nifty Trade Flat Amid IT Sell-Off, Broader Markets Outperform", "link": "https://news.google.com/rss/articles/CBMitwFBVV95cUxPd2pWd3Q1X1Ywa1lMdUZQcm9ibFNSUkJmc2U5VGVYbkQzWGkzX213ZFRwa3JTVGp4Ui16VEMxVDhLNUE5SVBCb0VnaG9CazdWYTZDajBVTmhmc2tpbjJtR3F4b1FBem9LSUdjejRLRkdrcjFrR3h0akpLRU44SXdoZWc0bXdaMXJHdnRUcGkyV1F6aGFsMEtMT2phNVZVQ0xPb0lELTZIaU1GaTYxVk5oNDdHdjdNMzQ?oc=5", "source": "Pragativadi", "published": "2026-10-27 06:58", "score": 0.691, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex Jumps 483 Points, Nifty Recovers After 4-Day Slump", "link": "https://news.google.com/rss/articles/CBMirgFBVV95cUxQZnNvcWk2MGZvU2hxU2lOaVh0ZjJtdTQ2ZEIxeU5ZVmNfTHotQ1FPQUk2RzE4SlY3Wm12UUhGdHlGOFlPSEh4dVQzX1VBOW14NE5IVnRLdzJtUDZQY05uN1V3aGtUcUJsTndEMVFPcmZOUFVKZlgxTXFucGdKX2E3a2h1UmlWMEVmdmZWQmRvcXVzTDdCalk0MWtSVnRqVTN3Y2cxWVBVYXNGek1PR0HSAbMBQVVfeXFMT1F0SHhMdjdDNXJOWFFKek9TX0FwV2lkTS1Gal9RMkV5eXZmSUlhbmNJZllTZVFaYnRWVTBYcXBlWno2U1ZDXzBYRHpMdXNLZEhBU3NvcUVxaExhNGRHNmZVLUJKTi1vcTI2REl0dnpJVnZ4VXRES2l3MkpmRExaYlZ3d09MNWVoN1JuclpsTmV1VXVGdmRnSjB0ZEllT2RCUDgtdmh0X1JQSU8tbktsV2trTmM?oc=5", "source": "Rediff MoneyWiz", "published": "2026-10-27 06:02", "score": 0.361, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock Markets Today: Sensex, Nifty Dip on High Crude Prices, IT Sector Woes", "link": "https://news.google.com/rss/articles/CBMi2wFBVV95cUxNeHFLVTdjZ2hPazYwSXhYRjQzaFZhV3VGeWx5QzQ4cEw3VHBnN3FGRGNYUnAtckZseEI3SDNrRnlZRHZPcVdoZmdKemtVTnBKX2Zza3VuYUpIZWxiS043OUcwWEhmaTVRcHJkb3FfQTB1QUZrXy1CSml3MkFfVUE3VmpOMmlvaEJJVTlsaUpjMjJFeFBLZ2pPbUN6YlAtX2JfVEtHMnY1VUdmYVRPSnZyQU5mUlNVVzVjOHFsbGRVMHdGUnk5Z0Z2SkNoUkpNSXIzbkVCS2U3R2J6dmvSAd4BQVVfeXFMTVhJay1WR0kwZzBCZzRreEl3Q3I2VXFiTE5sVjcySno3MC0tRVBPVUNsQWpJaFp1VUp0SlJJUG1oQnNDRWZ0YnFSMEZGQXdFUUMxOG42dTdGM2ZwYlYwcnlmLVFIbERLVlkydGx4RGp6THEwakstdnhObVB3Ymxta0dfYVlsNlFwVHJLWENoSXpzeFFZSkxWZnR5TFpER1Vsc1NPS2dndW04c040NGlmeElJRjU0TVZ0eVdjazZ3N1FSSkdkUEJnVFlWOW1ITWFIY0xWUU1PUi1tYlQxVlp3?oc=5", "source": "Rediff", "published": "2026-10-27 05:17", "score": -0.477, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock markets fall in early trade amid persistently elevated crude oil prices, IT selling", "link": "https://news.google.com/rss/articles/CBMi9wFBVV95cUxQX1hLOFBnck1zNGxNSl9SQVlEb3B5QnE4YW9veWRZdmdFd3MxelJFRDRKVXVBVERQX3c1SHdDeDZPZFlpMGZ6NW9lLVAyMWJRRTlSREJMRm9QVUIyZkRVNFA4OThZOGJiQ1F4ZC1LYnRRMHRTNEFMejZabElmbmQ0ZDI1aWU0R2pCUjdRX0F3ejByeWJMQXc3S05uYV9GNWRYM1BFd2ViUWpsOU5oRlhkOVdxUEx6NVdlZUx0elQwdHVXUjVkd2VtSWlkcnl0QzRpVi13VlpXM1NwdzhIR3dPTlY5YmwxUUNtZXhjcXIteExzbE03TUhZ0gH8AUFVX3lxTE5Ba0ZTXy1wcDBKSm1fUFFtRTVFT010TG50Q29IcUJhRnZCc1VpMjItdkQ5LTBsd2ZEaEJPR05LUVlHeDM1MWotdVdSNUpYRVFhYjJidHU0QXhjNkV0akt6V0xkZlNPZ0ZkMGRBd241cERHLV83N1pvc0UzclRYazlBcWpTR3JzVjRDbElMX0dhRnMtSG9MYTloSkloVTlKTkhYanVfV3htNEwwUjlXeEh5OWZ4WEUtLVVIZS1RZTRJMUh2Z29sZ1g5UlI5TzVHeUk2a1M0ZlBldUhNSnlOWDlfS2VuY2NzOGo2SkNJUXlJM0RqdUNFYjlTVWYxNA?oc=5", "source": "bfsi.economictimes.indiatimes.com", "published": "2026-10-27 05:10", "score": -0.727, "label": "Negative"}, {"symbol": "CPPLUS", "title": "Do Aditya Infotech's (NSE:CPPLUS) Earnings Warrant Your Attention?", "link": "https://news.google.com/rss/articles/CBMi0gFBVV95cUxPWm03Y2s2TzZiU2ZxV1l5QTBwZTlLVXkzOFd2WlYyZ1ZiU2dEWUFneElwRG1HMUNaNTFCX1p2V3otUVhCZU5SOTlyRUNIdjZaTTh4cUVmWDRHMlg3ZDNCX0VQaEtITUpRNVBvbHRFMnJ0NjV4YjhOUHZNUFJhZ1IwRGt3UXJDeE16ck5zb3ZSN0ozNVVMc2xjM05NRGVrUjVfWlVEZGJpWGNicFNnb0NvSDYxMFZyS0FoRkFhZTU2T2lienVEZzV5WWxkeFF4bjFsMHfSAdcBQVVfeXFMTkpxQ2JGc2tYb1NXcGpqQzBib1gxRXpKNUpTcmZ0a3lkcm1oMVpBcTN5M3piTUludmVTZWN2ekRHUnpDTThqRVd5TFloZ0h2UkpScFBiWkJ1ZlhxMUtqaXdNaTU0bGhlZVFPX2wyOG9fRDhZYWRPVWxkUzRTTmZabnFpSnA4b0FnM0VDbTY1R3U0ZmJueThIU180bWtiSTV6NHhzbzd4blZsVDdSaHQwWlo3RTdDSk9iTFdqSkZKbEJhSHhzWFJhR3NkVnVzdUVXbTNUTXM5c00?oc=5", "source": "Simply Wall St", "published": "2026-10-27 02:09", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Stock market outlook today, 27 Oct: Sensex, Nifty prediction - DJIA, S&amp;P, NASDAQ, GIFT Nifty, Kospi, Nikkei, Taiwan cues", "link": "https://news.google.com/rss/articles/CBMiggJBVV95cUxQUVVnVFprN1pwVWtldGFwam9RN2lqcVZPdDRPb3R0Tk84UmlicnBGWHlqanhVZ3JRRTFPcTliOE8xTkg0Sk</t>
+          <t>BQVVfeXFMTUlaeTNneHFjNHF0a2Y0cWpyeXF4QzNSdDBRWFlKTmptOTN6VVJ5MDR3X0pjajQydzZRQWcwNmhKRmhuUXA3T3U1TUo5WDQwT2l0OVV5ZVZ4UGJlVVNtT1luR0plcTBaU1p6dDdqYm1oSS11NEJ1bWR2eGFlcno3eF94U0xOV2Z3WjFVTk9jMmJOUUhlNkZzUjlYekp0VkVaWW12M2pDUlZKbGJUaWtiZFdYVmxPV0x2ekZoX2ZpbU5RMFhZXzNzbnZlcjVLOGFrMTVjMU92VzNZQTFUNDhzSGRpWlQ5cnMybQ?oc=5", "source": "The New Indian Express", "published": "2026-10-29 10:42", "score": 0.459, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex Today Rallies 905 Points | Nifty Above 22,900 | 5 Reasons Why Indian Stock Markets Are Rising", "link": "https://news.google.com/rss/articles/CBMi7wFBVV95cUxPdmVRUFJReXJwV3FPNWs0U21MRjBvOHE4eGxuMGpOWHpFWlVSSU90WHFITUwtQUM5VjJXQzRGY1RLb3A1UFEzS1l2blhJTUlnaEhxS2ROOVQtNDNNUUl2TGZSajc3ZHh5MG9VdERpbWF4LTRfSFdvS1JxVU1BYmZFdHo0WW5hZkdkam1sbzNDUE51Nmp5NnU2QWlZUFFzYWt3SUR2SW5xTGtFRDdkSklUaHVNSFh5bG9STDd2Q0lRamxfMDlEc2ktX295clRDZVRvN3kwdTBmMVgxV1FKSTh3bW1MLUNVanV3ZXBYQWd1QQ?oc=5", "source": "Equitymaster", "published": "2026-10-29 10:39", "score": 0.691, "label": "Positive"}, {"symbol": "MARKET", "title": "Taking Stock: Markets rebound sharply; Nifty above 22,900, Sensex jumps 905 pts as IT, FMCG, banking...", "link": "https://news.google.com/rss/articles/CBMigwJBVV95cUxOXzFMWXRnalBiNzZsclZWenNqSHowWVV6S2FERmkzNVNwLXBmNzF1c2d6ckVTbkktVlRjUks2VEJFdm5jLU1NXy04MUNaLVE3X0NzU3ZIc2hJOTUxekM2a1llTTZBd3BiNFFFRndOZ0NEZzg0dzcyam96LUpsUnB0dndBa3VndXFvajl1R2JrSl83TWdxVzJITkwwY2UyQjdib2stWUVwSF9FMmc5eG9vZGRtNFdwejNZUmVTeEdsb0lyVVlXOFVRYmZlLTFkLTVyTThFekVvcHgyZXFYOWZCNDdhdzJpVi1YVUFWMnNlMUM5UFV3SzlGMHZFbWVFZF9CQzNR0gGIAkFVX3lxTE1xMWNrVTUzbjlORGN3R2hOcU1qYjFIeW9UMGR3a0FSQUFLTFpnUzBWb0w0UHVxU0tVenQ5V1ZEMTNIb1Z6bGhSenNLblBleUpQckp0SXBuTFpIX1FSNWZhelZxNWtZRVZrMVJ6MTcxbkZ3b3B4MThKdHZXY1M0bGVrcENTd0RrUkMzQWlPemQza0N4bENUZWtOaWl4U0g1Y0JZc0lWRHJJVkpXYmxYal9TRnkxU3FxYnFIdS1WTmlWdzZjWWlVNGJuVjJtOTgxY2x1RURxVXUwTWQ5d1VFXzF1VEhJMlg2NWZkVEl0d1pab3JmMDNxRjFXSlRFSkQwUmVEbGpvQ3d6VA?oc=5", "source": "Moneycontrol.com", "published": "2026-10-29 10:11", "score": 0.691, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex jumps over 900 points, Nifty inches above 22,950; Reliance, Jio, Adani stocks lead gains", "link": "https://news.google.com/rss/articles/CBMixgFBVV95cUxPQVZrakE3dkhQQVJoLWlTOFk3NUkzSkVhaUJQSkNIR0RVTkpyU1k0ekpCc21oSXhSc2J4MS1ZbHNBSWQtbVhuNGw4WGw0S1RHaTZsU2dqUDQ4ZzVzUHJFSVRpWFdRRzg4ZTFIOVV5VmxfVmY0cXBjV09JWlRLYXhBbEMtSEhQcGlGQzZvdFMzWEllQ0RGTXVlYXZVMml5cnVGbVVIdXNudHNTVlN3ZnVoMlljTXN0TVJ1N2VQa01xUHVRNkZCVlHSAdMBQVVfeXFMTk4xOG9rOGlGVEZVWjhhUEx4X1llNENQeEZHUy13eC1XWjlvY21zZGRWNTdmZTJHTFU1STlpUXZHTFJVOWt2R3FsbTk0cmM1MDFYV2tzdDUyUUVZUTZJVDdqeWNfbFZwZTI0V1RqT3lGT1RkaDFlUFhDd3NTNzdKaUtZVU5OZHpEWC1GU3hxckNJWWI3c3ZDWmM2b2g1cVpaWTBsRTJQVUE2NXlZQzh2QVRQdlZ1RmJKcG9SM3FhZ0hiVGxPbFYwT2tCczd6YVpUTUlqWQ?oc=5", "source": "Fortune India", "published": "2026-10-29 08:33", "score": 0.807, "label": "Positive"}, {"symbol": "AEROFLEX", "title": "OnEMI Technology rises 5% after Q2FY27 profit doubles to \u20b9125 crore", "link": "https://news.google.com/rss/articles/CBMi3AFBVV95cUxNbGlvX0FHQ1JfUEFBa3FfTlJHN01rRC1VSUpYYlN4TFpGVGZMb1d0akNDNFBWNWVQVFBCOXpqQ0FoUm9uNExvd1UtMkxiRVNGNnc3Z0N4Ymk2a3FkR1N3bTNtYkxxVlkwNHdRbEFfTTQ3NXA4VWlCcE01RTZFZTBTbGVsd0dfRmllMDdnbHh1RXpIY0cwSDFVaXVKX0R3dG5kRzdxbVFtZlgwZ3NfMWdpS3RBa3gzREJwTWdyNEIycXFBbzk1YjQ1VS15SE5zemRNYjBjZE5kTXlNWVM50gHiAUFVX3lxTFBrdXI4MnRhaDVEVV9JaW5ibHQtN0Nnc3M0RHd5OFQ4RVp5VGJ1QjRIZXBnejB1ODZFZndtNU1RM1lqUW1FYVhXVGJsc09pT3JpZjhOaDBoX3VMU19LYXdaS1J2TjNVN1FvczdDNUdTaFVjTDZCVDUwNEp5RVoyeElWRWJFdFdLN0RrRFR3ODlXUm91TVYyR3ZWaGRKWTVraWFacDFOOTZaa0xndEtZM1lsaXVTSG9GUkg5SWwyVjB6eXBvdnh3ZmpzUTJ2ZzdQVUlNbnFhTGVhOU5aczdqU1l0QkE?oc=5", "source": "Business Standard", "published": "2026-10-29 08:32", "score": 0.34, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock Market Today: Why are Sensex, Nifty rising? 3 key factors", "link": "https://news.google.com/rss/articles/CBMiqwFBVV95cUxQd2ZpdWNMN2xVa3NjdUc0WDFvUGNhdDZkVUhOZGQ0dm04T0s5R1Q1cHJyVE9CVDF5RXk0V3UzT1lTSFRCYTJfTXNEd3NyRVRrVU5UNUEtbnpPaE1Ycm45MjVmWERFMnR5X05pQldUUlIwVlA3QjQ1Qmh6ZG1Ua3JQVUxRSDBKbjhIYlc4cjVJNmxsS3ZsQV8xZ1VoOF9Ed2NlR01LWU0zcDhtaWc?oc=5", "source": "Zee Business", "published": "2026-10-29 08:03", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "SENSEX jumps over 500 pts, NIFTY above 22,800 in noon deals; Power Grid, Hyundai Motor, Jupiter Wagon among buzzing stocks", "link": "https://news.google.com/rss/articles/CBMiiAJBVV95cUxPdnJnbmdzc1NmZ0hiWGxTdWRUQWlaNmdGS0l1U2NrbktXbjBfMldGNmREeVlrakdOOTJQUHN5b0JLUmVYbzgxcWZZcGRmZER3OHkwVS05bGE2YTdkaHFjdDEtYVRaTFFaczBuZ2tPRjd2TlI3b0F6OEZFMDlqT0JDd041b0Z5SUlVOG5hYjVWVk5nd3EyZ1d2UWxORlZnSUtPdllmbU1TcDIxWWVsTnI5Mjlrd0RxRE0ydkNNTUVuZHRJZk9pWXNQSDIwUnlKQnhnNkxRbFhsRHM2TXZNcHk5U1h5UkpwaHZNZFlwWUg1SDhkcWJtR0JnNTkwSFFpRENHcko3VFduRHY?oc=5", "source": "Upstox", "published": "2026-10-29 07:59", "score": 0.753, "label": "Positive"}, {"symbol": "AEROFLEX", "title": "Aeroflex Industries shares rally over 17% on strong Q2 earnings show; material costs jump 120% YoY", "link": "https://news.google.com/rss/articles/CBMi7AFBVV95cUxQQWlWYm1LaHBiMlF4V1d2VEg1UW1NY1FUWHlOWDFRTjBlMVVZNFlNSzBsWjB0MC1TeVRnbS1OZ2tvUjJUWkY1ejlnQXd6Nm44U21MZ0JmOXdsb3hhc19felBvbVJBZW1XMkFNeU1QSU50ZFZPUGs5N0Y5MlR0cVJDNjd3S2wyaF84MG4wQ3g1ajFSOWxTc2pqeGZOWmRoQmE2cHhOeFVodGdGOHBkLXRfNmhkNE1hdFNjcVlkVlJxX19JeGo1V1FJMjFZZUFJOENNMDh0U0pnaW1uQnNoLWJ1SnF4c1FiWENYQldTRg?oc=5", "source": "Upstox", "published": "2026-10-29 07:48", "score": 0.813, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty Rise as Reliance Industries and IT Stocks Gain; Crude Oil Limits Upside", "link": "https://news.google.com/rss/articles/CBMixAFBVV95cUxNRXNQN3ZYVmxrczhYNV9wVHBZTVJ6bjFaY29LT1kyS08yQmd2MXlweEVaQUduNmhhWDBqTVlhZVpKb3dZdHdkdHlvOVRhY2toLTFRajBQMW1lMS1rZGpUaEp5WDJuaTJ1X2M5UW5LM3k0bFp5SkM0TkVwWTViYS1RMlFNcWk5SkVHbnVLbGtxYVNuNl9OanU4Mk5Ja2tUNTVBUDFSVVZ5cFBsQ3pncVZneVBQS3hTV3N3TEhzVm1hYldRLXc3?oc=5", "source": "India Infoline", "published": "2026-10-29 07:05", "score": 0.494, "label": "Positive"}, {"symbol": "SBC", "title": "20 Best Stocks Under 50 Rs In India October 2026 For High Returns", "link": "https://news.google.com/rss/articles/CBMidEFVX3lxTE92U3Fjd2lHOGFGOGZCWE1YTDJpVmo0TktIVk5LUkx5NkE2R3B5M0Y5VjBmZWRYS25aNjB3SlhWMVFVUVNrRVZQX3YzM2FiOHg4b0FhN3kwY1dkejdFWWtFd0dNNlEtRVh4TjNLQnVzRFJWa1ZO?oc=5", "source": "Samco", "published": "2026-10-29 06:51", "score": 0.718, "label": "Positive"}, {"symbol": "AEROFLEX", "title": "NSE: Growth levers, easing regulatory pressure underpin Jefferies' buy call", "link": "https://news.google.com/rss/articles/CBMi1gFBVV95cUxOWDh2RDkydGlLckd3VlBaTWo1NzZfQ1UwRUZzaDlleFQwQTR3MmdmQTlxWkIwTnpFblRKSnVLaHpxSUNVcnpkTmVxZFhuTWdQc1pKTEJJUGZqYnBOWjNVcVNzT2VTa1NLY3VmYXhpQU55Qkd5eTJjMmFWZ2JXM1dmTk1LeEZPQndQdjZadnRmS2pkbV81V3htOXVwUXFXcnVDNkM2VU9PNzR3VzhLUUpyWmw1dUtmWlVPN09BYzlJSEIzZ0RGc2hEemJNcUlPa1hnZFRMaG9B0gHbAUFVX3lxTE53SVEzdlA1N2syc1RkZHBqMW9qcng5UmpVZ1lMczg5VkI3VmFTTzFZckxIVzhScTZZUDRGc1Q3UnlwYkUzcmQ5ZmlaSGJ3NmJBanZxUExPSzdLVlJ2UUJtYUhZNGVOZ0x3c0cxcFhkcVBuOVRjSnJkTS1feGRqN2ZQMU1MaGtJUy15dlRwdnhmT0lSalh2YVN0WDFXWkhIMlJQZVh4RUFja0pDNzVxRHV0eWhTeXFWMTBBcGhTbnZUMG55aEpST2dhZFlocWUxdGl2RVJjMHVEYzJHUQ?oc=5", "source": "Business Standard", "published": "2026-10-29 06:44", "score": 0.542, "label": "Positive"}, {"symbol": "AEROFLEX", "title": "Aeroflex Industries (NSE:AEROFLEX): Did It Publish Q2 FY27 Financial Results?", "link": "https://news.google.com/rss/articles/CBMivAFBVV95cUxOUDdIXzZMbXllYVcydHVDazlNYnJkSm05eGt5eFBtTzEzWDBsOWpiUG1IdjFPaHVwQjNRZm11Zl93S211VmhlaWUxaDNMTmVhaGV3RkhkRnFFYU9rb0pCcWlFRDJHVmtLNXhmVGV0R0ZXbUNLajlVZlZsZGhMZkZqWjA5NEFlbVplSjF0cGwxTE1ob2FzQjFkem9nNkRhdEtzX2tqOUY2SXU2dEhaWVViTDB0QjVwWWw5UmRBdg?oc=5", "source": "Kalkine India", "published": "2026-10-29 06:42", "score": 0.0, "label": "Neutral"}, {"symbol": "AEROFLEX", "title": "Aeroflex zooms 18% on huge volume, over 31 mn shares change hands", "link": "https://news.google.com/rss/articles/CBMiygFBVV95cUxPM0hjTzhyVzdyUnJfQnc5eFZFNlRQbVREa2s0S1VnRFc0UlUtVzRrT1NCa3hHaC0wVXM3RjVRNE5wczd1Tk9idzk2OTY2MGQwUDJCNHFlVDQ1el9RWGl4Zm9sd1pJOU00T2t1RU1ZMzRHeXZ3YzNEWFlFV1RmTUFsakMxY1ZINVFONGxJb091cFhtbjV5QVJfSDVjODZHeWhxT0piOW9EaE9SZlVIcXNMS1JRcFNLbkxxOURKUUxKRmo1N0hPek1TNGNn0gHPAUFVX3lxTE50REw5VnZCd1NnOE1DMUVBeXJuQnpKOWlsNkZnMVNhTmlkZjY0OTY3bEhMaDBnNmdNRkNHdDVEdzhua0NCRW9sdGhoVnE2LUpuYVpJY2Ywbk1vTnlBY3REVHJoT2hIOU1yWTVrdVlDZ0pLZnVTNldwcDZ6dUNYRW5yblpqS3o5NWpDVlByeW5xS3o4ME02NTBZb1Y5VzdTZEloOXR1T3VzaTZxU2cwYVlGMGJIcEhsdVNrUmREYXdDQjRkOUJRV0hPTnMydVF5cw?oc=5", "source": "Business Standard", "published": "2026-10-29 06:38", "score": 0.318, "label": "Positive"}, {"symbol": "AEROFLEX", "title": "Aeroflex Industries Share Price Surges 14% After Q2: Profit Jumps 157%, Why the Depreciation Change Matters", "link": "https://news.google.com/rss/articles/CBMi3AFBVV95cUxNanpjQUFtMlRJTE9VYkRiZHVsdDd4bzhuRTd4MlpDd2RvRzZYTDN0UzdQaDJwcEQwaWc4cktjUzRPVUFBN2RRY2czNlhDRVJ5WnlDMHdyTmpUb2J1ekgtZ3RwcHVJYnptZVV2dWJxX0xuRWU1UkVVVjBmOU5Pd2FBMWl2ZkV6TFlodUt1MUNwb2dRNG9aaTRrenRrU3g3ZnE2TXFWU2NHUjYxUVJVOWpYRG5RdUNRMUdvSC16ZGtQb25uZnVNd1BPZHBpOE80MFNMYy04SS1TaGVSNWtl?oc=5", "source": "Univest", "published": "2026-10-29 05:29", "score": 0.827, "label": "Positive"}, {"symbol": "MARKET", "title": "Why Is Share Market Rising Today? Know Key Reasons Behind Sensex, Nifty Rally On October 29", "link": "https://news.google.com/rss/articles/CBMi2wFBVV95cUxOeE9MZkVEWTFFS1VsUjNNTFU5ZlRHVFdZaWpNSnYxd0Z3RVUxVU44d0VYai1fVWVjQUZOb1RaaTNfVHFSSTNvUFdUNzdwbXI3NWVIYk1SaDRkcGJTdjQxWEdvcVZnZTk2c2psZFRQUmhvVHlpM1ZmVHFvMUpRT2VSZHFnaF9BT2VSc1EtNUxNWVNNekg4ZUVqendFR3NwTDJVSENkaDhncHNmdlYtSGRtWXY3bUxCbDZMVG9yNmh3QlNMSVphWG5iOTF0N240Q0JiVGg3Nzh3eXZJeU3SAeABQVVfeXFMT0RuVlF2YUh6LUZlVTVLRUxEbGVrZHJNV2NLRGdEdVktSWx1UjdYSkpfU1doZFlrZnNCYmRrMmhyWmRlVlhOZ1N3YVdHZlBIelhzbFhuVEJOYkFsQ1g0cHhWOF9sWGlCUDVlY0g0Tm50eUxmWDdtTUpGbllCeUl1anJiWmI1UFJtcURLaXhiNWIwUTFwdFVDM1RMVk9CLXMxOUNIYnpMSi1QNEtzRHRnN1VzVHVzdG96VVktOWdNaGR4Yzl6UUVZdDBzeGVxVVd4dmwxV1I5Z2FvVThNQXJhb0I?oc=5", "source": "News18", "published": "2026-10-29 05:25", "score": 0.691, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty rise in early trade on Reliance buying, foreign inflows", "link": "https://news.google.com/rss/articles/CBMiyAFBVV95cUxNbm9FWDJhbHFCMEpNTC1uZ1dtTWhHd09pYzd6N0s5aTJfclVMU3hmTmVoQVQ4UUxiWXQ2THJ6SkxJSDFIVGRfT3VHZFktS0d1M09BQzIxc1Y3OHE4Vjg5TjYwYjJ6UWpSRk9heE0xdWtSTThObUczdk51dEJmMUlZeXI5eExPQnF6OHp5Z3lna2RhVG9LemNROEkyVFBYUGVwZS04MWxzZkZqbjlpRGd2ekFXZzJ3VHB1YkpOeTBpQ3dabmtjOUFXdtIBzwFBVV95cUxNUm83blpBb3pITXIyTnhpekdUM19lZkFHR3pwOVlxaGRZbHhZeVJ0akN1MW4zSk9EdjgzRl9sUnZUMy1aWkVDQTJJaVJYeVI5SHdnYUVwM3VseEdjNkU2aDU5MlZrdkw3alBCMFlROTRBWVlGMnBHeGFhZXhxSFFRdzU3MjZzSS13djBVcXNpSDVvSlNtSVNkT0JPTmg3SkZ4amFZMFhYTG5uVjN0ZlNmSy02VnUzWlBEaWhZUFlhQmJYakZJQVUxZFJMWnRDZDg?oc=5", "source": "The Hindu", "published": "2026-10-29 05:17", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty Rise on Reliance Buying, Foreign Inflows", "link": "https://news.google.com/rss/articles/CBMipwFBVV95cUxPRVNVU1ZRN1V1UUVLcGhjaHU0VFhyOWtyM3liZjJRMktZZ1dyVnk2cVphWFNPUnZLMDlBLW1kLUtid2RoMnpfTUdUZnNid002YVNDWkRqYWFPMHJDVkNzNHlZZGVPOFh6Tm4wRjI1UWtDMFV4cmI3b0l4WHVGRVliMkc2NUVGNHFqOUtKQV84UFgtVTlSa2gwanZxM2k2d0M3RkZQamhoWdIBrAFBVV95cUxOcFR0UC0yTjN5THRxNGk0cXRiaURuZXZhanBvUFNiMW5mOS1TSS1WbTc2TXcweE5IMFd3U01BeTg5R1FKelY0eUhIYVJibUxZNmE5WUtPeWlwQ2ZmUFVEMnNmUUZGT0luS0d5YkNydTcwMFNvOTBHdzctWkl5MzRuNElfU0M4QkVabGtEYlR0U294NFBxNFpRWGs5blc3elZFa3QySy1SdkN4VGNu?oc=5", "source": "Rediff MoneyWiz", "published": "2026-10-29 04:58", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty Open Higher as Fed Holds Rates; Oil Dips Slightly", "link": "https://news.google.com/rss/articles/CBMi2AFBVV95cUxOWmtQMEZ5NFEwOHMtVlFJWGFKY005a2RTMWF4NlNNcXFQN1RYMmNHeDVVbmx2YlA0Z0xSUGs3aWZlUUJqVmpDMjhOU1M4enFVbFhTOTZEWmZVUFFUZ2JHSzNmRU5GaDhlQjRNUEpuTUd3aFI4MjJYa0tXamJUU3RXQmlJYXFRc2ZVU2UwSkIyNXF4SU5HRjhlZ1UwUktObGJjU29FRlBTSDJva29XUlVudGd5NldOcmxaTU14OFhsTi05Q2V5NEtFQXY5T0MzQnF2Smo5SWdTV1o?oc=5", "source": "HDFC Sky", "published": "2026-10-29 04:44", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex Today Trades Higher | Nifty Above 22,700 | Jio Platforms Up 4%", "link": "https://news.google.com/rss/articles/CBMixAFBVV95cUxPdHRLMXRySU0yU0lBdUJDU1RzcEpvM01WZjNEOXlaTlJGd2FnZk1fNUxTY2p0Q2lrNUpNOFN6UkNpc2xKNVBTYVJmRkJXaEJyX0Z0eUoxOG9kZmlic1hQaE84eWR4TU9JNDhVa243amFRMC11bjRzN3pwZHpiV2N6VlVMTEJqR2gtYmk5WExRek40TWtvOGtvcHRhTU14MGhaYWtsZHBianlEajd0dnFGdElaR0FIbmQyTkxMSHhjZG1nUTBL?oc=5", "source": "Equitymaster", "published": "2026-10-29 04:35", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock Market Highlights: Sensex Jumps 905 Points, Nifty 50 Ends Above 22,900; Adani Stocks, Kotak Bank Lead Rally", "link": "https://news.google.com/rss/articles/CBMi5gFBVV95cUxNd2cxcjN4THQ4TFZtR2FweWRJR1BWYmpUcDJTZlRBVWZEeGZYR3R5RFNsYmFzM1ppNlN0Ykw4ZDdZR3l1Y05qZWdjZGpHOEt0QWZHcWFEQmVEc2RkMzl2cFZGbzV6eWFsZU42Nm1YUWZ1QTM4QVZIWmttM056VDhidk1sNmQ0Z3FDU3V1T3c3THFrTGloTjVUU2FHN3pKRUlfXzk1NkhzWTBmTWxWdGk2OVRwTWlLNmpLb1ZDamdaYVFwNHBtdzJObklHbXVEYzhCZHowY0o0OGs4WC1OTDl4WnVtUS1ld9IB7gFBVV95cUxObXhwRThRVnFsTlU0c3E5ejlpZEV1TTJ1QzBWd1JraWdFVWdaMjgwV2p6UUZGSGx6U0Rrajd6cjRlQUdocWczWDUzcGhpSE9YQ2g0RlN2eGg4M01aUHM2TzdPMm1Id1BqVS1pTnQ5eEl5MEZIaGQ2YVBRYlZ2ZU9hdVVkeGJ3NVVVQUpuRlVKQy1MdDl5SHdQUzFhM1A1eFdOcWVKN0k0cmlJOHN2NlNoamZaNlZIWF9GQ1JMWHRFM2drU3FTVERXX2ZYYlFUOGo3dmpVN3N3YUFNV1pTbzJwQUJkUnRLSFV3SXBFZkFn?oc=5", "source": "NDTV Profit", "published": "2026-10-29 03:51", "score": 0.827, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty trade higher after US Fed holds rates; crude oil remains a concern", "link": "https://news.google.com/rss/articles/CBMiwgFBVV95cUxNQXViREYtTGFhN2E1dTNudm5xR0VHZU1kakd2WHZiNDZXV3VvWFRhVXVvUlAxU3FEVTlmeHdWbjc3VFRvVmNvczJwTkVPbldUejYza0FYcFBDVTFrWHVtS2xLYXhPNjNkLWRmbE5wMDNTbWY2Mm92UGNhZDhaNUdZSF9GODkyMjhselJ0eDVQbGpscENobHRpWkxBU1F3R2cwWVR4cDNDVkd4dWZ1dS1nRkhEQTA4WlBnZGZERndyM1M2UdIBxwFBVV95cUxQV2VVVC1qZXc5RGl2TGRPd0Y5YTFKQV9GWFVLV3o1WHpDVldxaDdWVEljWGxsTVViS2R6Q1BXNTNJYXVMX1g5NDZ5cUFiOUNjMnlUZ1NHYWlqUUhRUWl3S29FR3haNFl5OGZnakRVbmVNWjdnclA1anlWbDZ2aGFXZ29KQnJncXcyWGZjd3pCYVBmZjJDbDJ5UXFxanBlcm1kNXRBRlo0UmlQaVBxWkF6eEV5T3ZjamRZY0dpc2dHS04xWjI0NFhv?oc=5", "source": "India Today", "published": "2026-10-29 03:50", "score": -0.25, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock market outlook today, 29 Oct: Sensex, Nifty prediction - DJIA, S&amp;P, NASDAQ, GIFT Nifty, Kospi, Nikkei, Taiwan cues", "link": "https://news.google.com/rss/articles/CBMihAJBVV95cUxPbGZqMHp2VC02aEFPMWpFUDdkcGlUbGVqSHFVUTdtem9scXhMSTdwRHlQNWxyeGFjd19oVUJBLWtEWXA4bGVSVFlHY3BMTzdhc2RlekgyWmpWVFBYdThfNGJqT05SREFmb2NVT3hsZ0IxSWlVSXVWXzhyeUVQYWlWQWV5OUlmdDA1dldGM1JQdjBSZEtackdibmVLVEFwdWo3M0lha3hvdTNaNEZYTzhXQ01ic3lPMlFjSWFIRHJDeGlTTVR5dUc5S0RvaW85aG82T2xwdnFoSy1yTDRWNnloQ2UxaUpWbW9xYTFHNGw4dDJZMWoxVEUtZER0NlFQa2p2NHZQddIBigJBVV95cUxOYWFiZ291M3RVdE1Oc3JKM05Nd0d0LTM3dWFHS2laLXF6M1ltczBYWlh0SUFtejJZVU9lZlM1R0FWcldBZGRvT2hyWjlBZkl0QV8wUTFqN2J3THNzUGtYekI3MU5oRUVTbklKMXp4Q3NZQUJUaE4zaUJvVXFCRDZiXzN2NTZUWlRQdkRpNWFFdDdpTi0wSTR6ejhNMXBVQWNoMFI0MzVCckFaeklBMUZINEZ6czM0YjdpRjBId1lfVXFqYWszN0tvRy1leWhDZEJZSDBQa2lzdUtIZjNqVHpFcTBJZFZRbzJTMVZkS3BKVUVERWdhWUhlQkdUWGlKOHhuWXpqRDFTbnFHUQ?oc=5", "source": "Livemint", "published": "2026-10-29 01:15", "score": 0.842, "label": "Positive"}, {"symbol": "AEROFLEX", "title": "Stocks to Watch Today: Dr Reddys Labs, Fortis Healthcare, Titagarh Rail, Hero MotoCorp, RR Kabel, Meesho,...", "link": "https://news.google.com/rss/articles/CBMivwJBVV95cUxOckZvTEdLSXpNR2ZfZFZRSlBSb251aFdLSERNTF9tTEVuOWt2a3JoVG9GWEZZa1B5VTVCZDc3Sm40VWlpZGJ0TWQzcWJNbmJjenNTcVpBUW83Mm1ySWpaYUVabmpaUHhGTmxWMjNqWWdmcHJtWWJvS3haYzEzY1J5MHg1YmVlV2FiTkZRTGNyQ1Yxb05WUFNiaDJNVjRjRHBjZHR6SmYyakpkNXFRWm1rcnpxaDlUVktBTWUtaTVoNjRjejJJUUVDeEl0ak5qWjBBb291eERuUHp2dkNNTXJCczFSaE9ycUpic0hZY2llYTFSdmNUMS1pQ3ZwRDczNkZ2UU9xMFNTLV9XMVF5Y1dCcTRfeE1aR2FqMW85ekJCMGhUWTY5ejhEd0NLT0tDTTdKR3pOVklydkxjX0pSb0R30gHEAkFVX3lxTE4zbTVMdTBDbDhuSFZpOUNZQWlQc000SVprR1hFRHIzajZFVkhEUGFRRjhXaDVwai15X2VfQUxVYnVnRW00QmxzZktoRms4UjB5N3Q0U2ZSNElMWktubjhxcVdBY0tlSldIMkI5czlWZU1QNkF5dlRINHBOa2VKakp0RnFMbUhiMzFNSHEtOHN6QnZxUEM3aHhHSF94cC1kMEtFck5QM3A4RzBydk83dHFETWxkOWFhYzltM0RPTkdMMTl2NXp0RUtsTFJrRjU4dlNWcjFTXzBYTEdQSFB3STBXY2YyR2tGNnFTTlBTRGhJODdpbDdPRVJBUlFzN0FxWnpQN05vVzVWSDN4R2ZzWlJ0bFN5dlloOVh5QWlWZWJHTGtWRmtXOG85djNCdlhNM3V4bTNSSl91QlZoOFVKSzBENVVEaw?oc=5", "source": "Moneycontrol.com", "published": "2026-10-29 01:01", "score": 0.557, "label": "Positive"}, {"symbol": "MARKET", "title": "How can US Fed FOMC meeting outcome impact Indian stock market? Sensex, Nifty to rise? Experts decode", "link": "https://news.google.com/rss/articles/CBMi_AFBVV95cUxOZFZvM3NMeWFaZWdDOXJWX3Y3dnA3RjJmMUlZNjZUU3I4RlRwemFzWjNLc2VGSXIxOThvYXJmekVZMkJDNjkxbkV0SVNRWjI2ZGdsOFctY2Z3TExhbFFKUXlfUHZXUG5RNmVtVktMLUtLVjN1WmdmM2RvQUs5b0gwVlBhbkEwdlFkN1duNURLcGJ2Ni1fSVpCdXpORXlFR1JudmYyZHM4U3RsRFpuMUxtakh2MjFMLUJKMkRoSmZmU3lSRmxhWHpNLUlDS2E2c2VGbU5fV0d1dW5jc2tpb1VQWjQzYV9sRmh4Ykk5Vk5rLWR4UkZZZFdJNW1yNzDSAYICQVVfeXFMTXhyQlhLeEtxLW9oR0lQcHoxNTBaaTdqaDgyMWVYVXhJZXlteDZGUEcwUjlZd05rUXdSRC1yMmFZWkl6ZEZZRmFiZ0dBSFBMcTVzU3ZORG82VzZ6VGVseW0yZGZxR1M4V1VLTjI0aDJfU29EZ0NqT1VsaktXNTVoeXdPNlNxYlNpSWZpOXpTQzB4c1lrb2Y3T1F1MVp2T08xaW4zNTVobVpQTmlfdlRITThka2hhc1U5WTF5cXgtXzBZdXlYbGVPT0t5OTd1MXZnTUtMWUxVRUFwbWlPWmxTeFRKV0VvNkh6U3pEUVdBZ04wSzJaN0dEWUFsWnMteWpuZzB3?oc=5", "source": "Livemint", "published": "2026-10-28 18:46", "score": 0.47, "label": "Positive"}, {"symbol": "RATNAVEER", "title": "Ratnaveer Precision Engineering Q2 FY27 Earnings Call on 3 Nov", "link": "https://news.google.com/rss/articles/CBMi1gFBVV95cUxOT0FlR3g5MTluX3phZ0tWLW1iVHAzbUh0dGFBRjcyLTBFQTl5bXkweTNIYlAtYjFSYlhBUFJYQ05VOVUzUFRLaDhwcmg0b2xZSE1JMV9rNlpuMFFDYTljQnpjdE5rMDJ2YWxGaDJZMFpCWFd5RDBuYjFvbE8xS085dmc0aktudXE5MDc5UlhCUVlQSVBtRnFwbUtwNG1lNkFVM2tWYzNLeDdHTGlhUjBXNEVMZ011Q0RJVkVoM24tWTNHWERXbHZ5U1hhOTRDQ0RmSlBFWDdn?oc=5", "source": "Kalkine India", "published": "2026-10-28 13:42", "score": 0.0, "label": "Neutral"}, {"symbol": "AEROFLEX", "title": "Aeroflex Industries Q2 FY27 Results and CFO Change Announced", "link": "https://news.google.com/rss/articles/CBMiwgFBVV95cUxNUnE1em5WY3o4a3A5REpCZ2hBWEVjVmh0SHZrdTlNcFpIaWs4cGZvWVBSeXZ5QU5vQkJHX25UMk9CVVQ0VVFfRXNuMnJWcDhrOWczYko2Q2FmYk90LWRadHFfbFRwM1hrQ2lBYmNaX3psWFp1MTg2dGdyTmtCTWt4OF9hQkdmaG1JVU13TFVaNVVrLURGOVVDckl5Z1pMenBsc3Axdmswam1ET0NLMk1MNzVubVFTTkVVR0dsbUhxMU1UZw?oc=5", "source": "Kalkine India", "published": "2026-10-28 12:25", "score": 0.0, "label": "Neutral"}, {"symbol": "SYRMA", "title": "Syrma SGS Technology (NSEI:SYRMA) Stock Forecast &amp; Analyst Predictions", "link": "https://news.google.com/rss/articles/CBMiiAFBVV95cUxOdkctWjFPZDVydlFqbGVBQmtXM184Ny1vUmw1dnFzSGNyTmNRRzd4dWVLTFZEeXNRbjRYdng5eXhaaGE4cDV3RHNBd21HeGJZYVhDbFU5anp4LURYeUFpeVV0bUk3ekF2NEtWN0NTTFRDekFwTUY5MEpoeGlobnNOWWxWMFVPVTdt?oc=5", "source": "Simply Wall St", "published": "2026-10-28 07:00", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Market News: Share Market Today, NIFTY, BSE/NSE LIVE, Sensex Today, Latest Share Market News Live Updates", "link": "https://news.google.com/rss/articles/CBMiRkFVX3lxTFA2eURra0RNN0hZR0ZxYmMxV00ycGZkVS14M1JaTGFnc2lGeVdLS3NUaDQ0Q0pKSkpLbDcwMUhQN1lwcHJNbmc?oc=5", "source": "Livemint", "published": "2026-10-28 07:00", "score": 0.532, "label": "Positive"}, {"symbol": "SYRMA", "title": "NSE adds six stocks to F&amp;O segment from today, October 28: Check full list", "link": "https://news.google.com/rss/articles/CBMiugFBVV95cUxQcXRqZ2VkU1BlRnY3clZsRkEweDlZOXdLYUFpMmM5QUc2eVhULTBmaXZNOTJaM1ltRkMwY1g5NUFSSUJibzdac2JSeV9pLWlzblJuMmdwTVlRSktfNlJ4YkxfYWpVd1VMd3JLel9hcGNrcmZJQUJsYlplNVMtQXNROC1CZTBvOE55eXpUSnhIaXNPeGt5V09rdjVEQlhJaTJDbmJlRTMxeGtONVhJbGNJb3FuSHRaWXFPMlE?oc=5", "source": "Zee Business", "published": "2026-10-28 06:20", "score": 0.0, "label": "Neutral"}, {"symbol": "SYRMA", "title": "Syrma SGS Technology (SYRMA.NS) Jumps 3.67% to \u20b91575.3, Approaches \u20b91654.07 Resistance Zone - Time Weighted Price", "link": "https://news.google.com/rss/articles/CBMiwgFBVV95cUxNeXpfQm9hem5Ed2xQdUZyMjYxaWUwd0pFME01Rmoza0E3VjctMWFyUHlBNEpNVWNaTkdyc1dBelRsbmZaWVRObEx2eXFsS2hxWVpsRGVDeEEtYmtjcG1rVHNzNllEbTVFVks2YklNTFJiUjU1Qld0bUZjVUhxN0NzYmp2dmFOc05wcmFHOFV5aVBhRHdBb2dmcERPZ2RhMEZ2UGpfeVpxZTJJV2hnZlZFOGdJcXJZN3N6X21uVDY4TngwZw?oc=5", "source": "https://www.siam.in/", "published": "2026-10-28 05:30", "score": 0.459, "label": "Positive"}, {"symbol": "MARKET", "title": "Why Is Stock Market Falling Today? 4 Key Reasons Behind Sensex, Nifty Crash", "link": "https://news.google.com/rss/articles/CBMiuAFBVV95cUxObWxhVDV4ZlIydzBlUDdmdzFaMGRMcWw5N3RjWHRSWnZKOU85V1BaM1pOVDJBU0NjcUcycEZ0a1lGdTFjT2JBU3hGRl8xV0tmRmN6Rk9pSmo2MTJXLW1sRTFEZXROZ2NyaWlOc25CajVNNlBBTWN1aTNrWk9rTDU0QlhJaUt4MHV0cDdwSUs4M1M0WEZGYUJxTWtUUDhJeUNRc1Z1NXhlZTRPZHFzZmgwQzlWQWNxeldN0gHAAUFVX3lxTE5jb2ZQVkFqMmdkV1pQR3ZUaFBnRnNEODlSbFdlOWpxNGUxVnlRTlZjX1JraXlkVlZhNjc0ektuZ0VpaVFfbkhwRFI2N3JaSEtKc0pkZ1RQRjFVS3hhQlFVSUJHdE0yODNqS1NJRXc5LU9mM19GMWc4ZjdfbXd5WnRZTWpqTDJ3eGs3NnUxNmdhOWg2S2YxS2FnUUdPOFZoQ1JBdElkQWZJaVBNVXNuRDB2c1dpSEpxaDVwWWdKOFo4LQ?oc=5", "source": "NDTV", "published": "2026-10-28 05:26", "score": -0.402, "label": "Negative"}, {"symbol": "MARKET", "title": "Jio Platforms becomes 12th Reliance Group company to list on NSE, says CEO Ashishkumar Chauhan", "link": "https://news.google.com/rss/articles/CBMi6gFBVV95cUxQVmpfeVpRbWpoMXJWS3BUZUQtMXRSUXgweXpYTEdsTERjUVNUdWNtbWJTZHFzeDBhNTdvUVpDUVA4b19UMXVjYVpNZ09HbVd1VmhqRlRfeTNrYVp4LXR1YXRGaTI0V1pOdnYyVk0wWmlrd01PazZzQzIxQndjcGdDZlBmYUdfQ3BXSEdzMF9sZExrcXRNV1NFRGFfMGo1MVZ3S0JpU1lXbmNadFc2S0RWV3JOSzVxc1Q3MzAzV25jMTc2WDY0SU5jRkthRy1JVGQwQUNDZWRSWXVMVFBKaVRINXdsUnRKdHVHX2fSAe8BQVVfeXFMT054SUVmc0J6eEdQOWs4NzBLcGRoOExnZkEzTWpwMVFYeDBHZjBnYkJkTDF4WTI1d1UwMWFheFgwQWRJTHJCb3A0dGF0b3l5R01USkMwUmtiUktQWE4wWlluU1dhRDBvbVBfTHpUNFhzZ0gzTEN4WmtXOGVzRlo5U0RBb3g3aGRwNzRQdkdqcEhyOXlYYTc1eWJKQ3d0MS1FbkJxT1FmbUc0NXlId1Q3ZmRKYWtORWRmUlQ4eEpTQjhlbkVhQ2lqRWNQdUhwaHo1UHU4UEd0c0p0bU13aEprR2ZqUEFLdE5takk0RU5fWTQ?oc=5", "source": "Moneycontrol.com", "published": "2026-10-28 04:15", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Stock Market Today Highlights , Oct 6: Sensex settles 685 pts higher; Nifty 50 rises 220 pts; IT, Realty, PSU Banks end in red", "link": "https://news.google.com/rss/articles/CBMixwFBVV95cUxPNjdLa1Q4STc5UFU5VzcxNWpmcHBDaXd3U1ktUkJhTUk0ZjlJRHZ6YWtzTkRhNDg0WFlELXdwLUlkMkVCYm1GUHhQNUlwazJHWlZIaVlhZmVBcGdOVHZsNFd2QUg5VXJkNjRKSzlvMnc3dWN0SjVFTnlidVVZMzctRjdEVzF4X3B0TEpUNURhcHFRV2ZMb3VDUGtnNDZhNXdIQWNlTTBHRGZPXzNkLUVXY1ZONFNHYjhqbFQwS0JqMGROVjE2bmZJ0gHOAUFVX3lxTE8wN3RPazNfT2JQaWdsVUpBb01Jd1FBTU9qYkZrNnZ2eENBY1UwSTBwOU1FWEcteXJ3RDNBME40TTRJTGdWOGxRVGl6TC1FTTkzenVWTFczZ2Q4c19jSXcyU3VfdFVwdzVZaktpa0hsRWIyZWtRbkVYcWdtWHpUTWd2MWFlTG4xVWhTY1o3czQ0RmF6NU5xTXNTRUdPZXhTNGVlT1Z6TXZHUHN0aVlmeTVBalhXdVBYdl96OGxaSksyQ19wMks2em5jNDZOdDFn?oc=5", "source": "BusinessLine", "published": "2026-10-28 01:13", "score": 0.402, "label": "Positive"}, {"symbol": "AETHER", "title": "Ather Energy shares: 125% YTD returns! Experts give 'portfolio stock' tag after Q2 results 2026 | Target, stop-loss", "link": "https://news.google.com/rss/articles/CBMi9wFBVV95cUxPYmlLLVpwT1RwQ2tYR1F6WlNVTWJ3N3h6R3MyX2ZvVlhHUjlDZVdHTHhGeVF1dnBQOEdjb21UQUFuclpzTVh6a283ZF9EWWJqb1lreEp1dzZFMEx0eVJLQmlUcXc2elo2SEE2c3ZiVEZLYk1sLVJkZ191cnZOb0QyT1pBSUxfR1o2UkRoMlN5dnlnWklGMC1OTVp0bmlNaFJwdW1JOUhFdkg1TWlIZl9xUUwweTlfUThhaE9oeGstZ1ZnaUZGckh0b2xsSldWb3B1Um9MUWtCUDJzTmQycFVUTExRUFdGSkx1a0hubHVjYmtLZEo1ZGRr?oc=5", "source": "TradingView", "published": "2026-10-27 12:08", "score": 0.457, "label": "Positive"}, {"symbol": "CPPLUS", "title": "Aditya Infotech partners with Ranveer Singh as brand ambassador for CP PLUS", "link": "https://news.google.com/rss/articles/CBMitwFBVV95cUxOYV92ZHBGUmxnOU0ydGQwSjdwUnBLNFBuMHdjbGhLSWpRYzI4ajM2dEFIVW9lQkV5NFZOdzNYeFJtS3pISkZXMVZET1p3aWZXQ1N1cU92OUNMa19wNGEycXF6Ykw5SlJ0eGVreTZZdW9UTktVbTFGeU5HRHpuVWpLOTQ5SWo1bTJKU0tJNUlVVzhqYnBoMEpuVGFWelJ1U09EclhrM19FeVNCbVFOUENnZ2xraFNiZVE?oc=5", "source": "Business Upturn", "published": "2026-10-27 10:46", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex Today | Stock Market Live: Sensex, Nifty trade flat; smallcaps jump 2.5%, IT slides 1.5%", "link": "https://news.google.com/rss/articles/CBMivgFBVV95cUxNeXFmTEJhQTB3U2FSNW5IN0lub2hFVk1aSGlmU1RUUE1ITjFDcmpDTVdFQ1VJOHFzYWpqZXpoNEVUbE9pVjh3ZWE2VEcybVI0VEdLNDV2WF9jbHdIX1llcklPcjFXMDM4QzZ0MXptcGtVTjdLTjlUN0pPeFhjOS1vel9YcERQWWFibVdYdzAwTkdtak9UNV9ObGlfdmVXU2RhZGNvaW9XV2o4VFlvOXFUQmd6OU9PaW5GbEhkdDBn?oc=5", "source": "IndiaIPO", "published": "2026-10-27 07:00", "score": 0.67, "label": "Positive"}, {"symbol": "CPPLUS", "title": "Do Aditya Infotech's (NSE:CPPLUS) Earnings Warrant Your Attention?", "link": "https://news.google.com/rss/articles/CBMi0gFBVV95cUxPWm03Y2s2TzZiU2ZxV1l5QTBwZTlLVXkzOFd2WlYyZ1ZiU2dEWUFneElwRG1HMUNaNTFCX1p2V3otUVhCZU5SOTlyRUNIdjZaTTh4cUVmWDRHMlg3ZDNCX0VQaEtITUpRNVBvbHRFMnJ0NjV4YjhOUHZNUFJhZ1IwRGt3UXJDeE16ck5zb3ZSN0ozNVVMc2xjM05NRGVrUjVfWlVEZGJpWGNicFNnb0NvSDYxMFZyS0FoRkFhZTU2T2lienVEZzV5WWxkeFF4bjFsMHfSAdcBQVVfeXFMTkpxQ2JGc2tYb1NXcGpqQzBib1gxRXpKNUpTcmZ0a3lkcm1oMVpBcTN5M3piTUludmVTZWN2ekRHUnpDTThqRVd5TFloZ0h2UkpScFBiWkJ1ZlhxMUtqaXdNaTU0bGhlZVFPX2wyOG9fRDhZYWRPVWxkUzRTTmZabnFpSnA4b0FnM0VDbTY1R3U0ZmJueThIU180bWtiSTV6NHhzbzd4blZsVDdSaHQwWlo3RTdDSk9iTFdqSkZKbEJhSHhzWFJhR3NkVnVzdUVXbTNUTXM5c00?oc=5", "source": "Simply Wall St", "published": "2026-10-27 02:09", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Indian Stock Market Crash: Sensex Falls 5,035 Pts, Nifty Drops 1,453 Pts From Peak; Can Budget Revive Bulls?", "link": "https://news.google.com/rss/articles/CBMi3gFBVV95cUxNaTRicEdpc2xjWnRrZGlDQmVHYUhyYlk5bE5VeU9FSWtwWEQ2MzFWMGtmeDJ3NFo2R0dEX3cwblVQemxEWFp0U3dwalVQTnFWOGlWb08zbGNVSlYyQzUtM244eWJPeGFXTHZMMm9RdVlHaTJqb0NJeFNiekM0TmxJbnhRSl82YWFUNlpyaWR0Q0NsMEVkb05jQXVOQTI1Vlpmb1FCZzVrcjcybUpJX1NON3dMRUVDbE9jV2FHQXd1OU1FRll5Rm40NVpkYmdlZTVpUFZ1b2dEb1VXU3FKaWc?oc=5", "source": "Goodreturns", "published": "2026-10-26 21:36", "score": -0.318, "label": "Negative"}, {"symbol": "SMLMAH", "title": "SML Mahindra Limited (SMLMAH.NS) Slips 2.83% to \u20b94,706.5 as Stock Tests Lower End of \u20b94,471\u2013\u20b94,942 Range - Hedge Fund Favorites", "link": "https://news.google.com/rss/articles/CBMizwFBVV95cUxNbV9TQktMZzVLS2k1YWJHSlJsamJtNXBFOHJwZHEtX2ZCZ2Y2azU5blNvbVpLQngxeF94SEVkb3phRXVpOUFVb2tBdFJCUkczMENNTU92Ry12WE5idExOVjFVOXZNdndUNEVIdVpFZlpvczFiT3ZtRlVDeE9ibkhleVc0dEJNWFF1ZmJpMTdMa3V2a1ZaNzBGenpNTXRxTEdERXNVb3dQbXBPMWdWMURzeXNkZHVfRnFnTkxvclhiVk1FcVBJQUlDUDNzcFNtTUU?oc=5", "source": "https://www.siam.in/", "published": "2026-10-26 05:47", "score": -0.318, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock market prediction for Monday Oct 26: Sensex, Nifty levels, top stocks to watch - Will bulls dance again?", "link": "https://news.google.com/rss/articles/CBMi1wFBVV95cUxQaHNMNE94WElpelJxRFNZMmFoS1p0a2lrZUFFa2Vla0JFb2psbEVOSW5HY2pCNjZ5VzBfa1lyem8zRktLVVduZ1hlc1E0aW0yQ0Fxb0ZSUFJZLWlMd3hKZjFqY1VaOTRSNGxpN3QzbVNvaFhoX2Zyc2JueHVtRWRyTkhkalBPZ2M1dWdwU2NFWURyTmFLUjFvV3NybkJiTVpQYy1Fd1dLMlRxRHFZWGNobWpUclFZQ184OGk2eFRqUFBaWF9sT1FiUlJ2SjdpWTZCT1ktVzhNdw?oc=5", "source": "IndiaIPO", "published": "2026-10-25 14:34", "score": 0.542, "label": "Positive"}], "errors": []}, "created": "2026-10-30T14:55:17", "last_updated": "2026-10-30T18:08:40", "corp_actions": [], "fundamentals": {"AEROFLEX": {"name": "AEROFLEX INDUSTRIES LTD", "pe": 78.65103, "fwd_pe": 54.181824, "sector": "Industrials", "industry": "Metal Fabrication", "mcap_cr": 7098.2230016, "pb": 14.2838125, "rev_growth": 0.873, "earn_growth": 1.509}, "CPPLUS": {"name": "ADITYA INFOTECH LIMITED", "pe": 93.28194, "fwd_pe": 50.383343, "sector": "Industrials", "industry": "Building Products &amp; Equipment", "mcap_cr": 46739.259392, "pb": 23.922348, "rev_growth": 0.895, "earn_growth": 3.037}, "THANGAMAYL": {"name": "THANGAMAYIL JEWELLERY LTD", "pe": 35.413353, "fwd_pe": 24.44221, "sector": "Consumer Cyclical", "industry": "Luxury Goods", "mcap_cr": 13847.0391808, "pb": 9.778979, "rev_growth": 0.712, "earn_growth": 0.861}, "KIRLOSENG": {"name": "KIRLOSKAR OIL ENG LTD", "pe": 47.92156, "fwd_pe": 31.48291, "sector": "Industrials", "industry": "Specialty Industrial Machinery", "mcap_cr": 26136.82176, "pb": 7.2113123, "rev_growth": 0.134, "earn_growth": -0.199}, "SMLMAH": {"name": "SML MAHINDRA LIMITED", "pe": 46.491833, "fwd_pe": null, "sector": "Consumer Cyclical", "industry": "Auto Manufacturers", "mcap_cr": 6837.129216, "pb": 12.203249, "rev_growth": 0.207, "earn_growth": -0.444}, "AETHER": {"name": "AETHER INDUSTRIES LIMITED", "pe": 91.00225, "fwd_pe": 54.33023, "sector": "Basic Materials", "industry": "Specialty Chemicals", "mcap_cr": 21451.4745344, "pb": 8.731544, "rev_growth": 0.275, "earn_growth": 0.341}, "SBC": {"name": "SBC EXPORTS LIMITED", "pe": 77.82353, "fwd_pe": null, "sector": "Consumer Cyclical", "industry": "Apparel Manufacturing", "mcap_cr": 3149.997056, "pb": 31.276596, "rev_growth": 0.855, "earn_growth": 0.0}, "SYRMA": {"name": "SYRMA SGS TECHNOLOGY LTD", "pe": 84.51898, "fwd_pe": 50.154373, "sector": "Technology", "industry": "Electronic Components", "mcap_cr": 31307.3369088, "pb": 10.862635, "rev_growth": 0.683, "earn_growth": 0.86}, "TDPOWERSYS": {"name": "TD POWER SYSTEMS LTD.", "pe": 81.125, "fwd_pe": 47.99328, "sector": "Industrials", "industry": "Specialty Industrial Machinery", "mcap_cr": 22948.2299392, "pb": 20.810984, "rev_growth": 0.721, "earn_growth": 0.72}, "RATNAVEER": {"name": "RATNAVEER PRECISION ENG L", "pe": 18.569588, "fwd_pe": 22.657234, "sector": "Basic Materials", "industry": "Steel", "mcap_cr": 3023.4468352, "pb": 3.659887, "rev_growth": 0.189, "earn_growth": -0.097}}, "research": {"method": "auto", "generated": "2026-10-30 18:08", "title": "Stock by stock (auto-generated)", "stocks": {"AEROFLEX": {"symbol": "AEROFLEX", "name": "AEROF</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VqRFplanRfTHdDUXdpa3o3NGt3TmRIRHZ2NzZlU20zWHpTY1gtdGVuU1JEeXNvSU91M2QxUTJNMXNUVTczZWdKN0ZkSDBvUG9nOUE0X01GV3FjYU1ocDJuS1FzVW5lZ29DTG5wWEZPUS0yTWJyZGt4UVBLckowTTdtMXd5OGZFN2YwMGotelU3X0ZFRXNkalpydUtzN3lMamN2eWxoN2JYelhLY0V5dG1GeWppeFRNWjVzaTlMUlFsOGNqY1HSAYcCQVVfeXFMTnQ1TGxaT2xKNGpmMUw4dVpEeV84S19hclJFOGpRT1Q5V3BFSXFYZXR5YWZjYTdZSndVbFFZRUdSVldRekxQcVIwV3MyN1pxb24wTnFPZXQ1UmltTF8xSm9NeVhuc3JfTXZQeEpCVy1GbUNRbWI3M2NHTkhqYk03bXVLOGpVZ3g1Y3pMeE9oUkREWEhlZzNVZ3pNOVNlcGtfeG85UUk5M3A2SEVpR0Y1VWdlX2hreTlRV1p6VnVXSjNMUnZWYVhmSnh6T20tdDNKbUUyaHNhWS1tQVU2YXpBOGlTN3Y1QkVhRVQzWFJ4VU0tUHdfaWI5ekE1UnBZU09HdEs0bW1CTFE?oc=5", "source": "Livemint", "published": "2026-10-27 01:30", "score": 0.842, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex Today Ends 483 Points Higher | Nifty Above 22,750 | Apollo Micro Systems Up 10%", "link": "https://news.google.com/rss/articles/CBMi2wFBVV95cUxPNVY4djR0M0xNQWI4dUltb0hiY0pBV0RERmduWkxPd05zT0xvWDR6TkI4UnFlWEpXQ2RoeUdzTmVCYTltSlBNWU1uelg5ZmhDLW9YaGNPLTJxeWNOUUk2QWhrd3VOZ2tkZWRtZTI1c3lHUW1qQXlRWUI5QzJ4bDg5a29rSnJ5R2tlbnJvQ3NRR2JNMzVEeG5ERmtNSmcwclc5TmdKVFZsVDlKQnM3QzN2c054Q1M2V2U3MmRKTmFOS2oySGh0dXJQRXpZQXoyaGJfdTVURHFDSW55QlE?oc=5", "source": "Equitymaster", "published": "2026-10-26 10:28", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Taking Stock: Market snaps 4-day losing streak; Nifty reclaims 22,700, Sensex gains 483 pts", "link": "https://news.google.com/rss/articles/CBMi6AFBVV95cUxOVWJueUF1ZWF1TG4wWWNaNDZuZTBmVExLdzJIbm5IMEtxZ2xSRXFZSll3ZGJRTnNHTU9yVUZJa24xR0NJUUMySENtQU9pRTlGaWNRMXluNl9La1M0U1VnanlmN09OQmV2N3hRbE1uTWhJamNUMldPVF9HWUV3SC12MmxqS002SFF0X2JHTUl3ZkMtUldyTWlXX092YjZJdUt6OHVVMXZIR1NUamZ5RGVJM3BqVnFFQ0JIbmhHNjlFLUhreVVKRk9DVG1vR3JtSWN4V1V5X3JvUDhPMERoeERIUjBsM2kzWExz0gHuAUFVX3lxTE9SUjdSaUNmT294eG1rSTRKdWhFSEtzMDlHQ29odFVmckFhMzI2UUFSZDVicHdoMDdNZ3QwTHlkMV9oYU41Mk1pMERicWcxdk9OX1hkLUdpN3VCa1ZfV1NVWHo3Ukc0QXJLMWxnR2xmaGQxQWtMOGZIcFpBXzMxSF9PTzBkS2pVOU1zZTFLNGpEMFpxQ24zNWZlZ0QwSWdaanpqZHNUa2x4V3BVWm9xa3phdFlkQnE2TWVndWZRWkw2OFBpemV4ZUJPV2JYbEItYVRqZFl1TDF4ZlVZU3RoNGNqVzVaUnJPMGNMMllyR0E?oc=5", "source": "Moneycontrol.com", "published": "2026-10-26 10:18", "score": 0.402, "label": "Positive"}, {"symbol": "SMLMAH", "title": "SML Mahindra Limited (SMLMAH.NS) Slips 2.83% to \u20b94,706.5 as Stock Tests Lower End of \u20b94,471\u2013\u20b94,942 Range - Hedge Fund Favorites", "link": "https://news.google.com/rss/articles/CBMizwFBVV95cUxNbV9TQktMZzVLS2k1YWJHSlJsamJtNXBFOHJwZHEtX2ZCZ2Y2azU5blNvbVpLQngxeF94SEVkb3phRXVpOUFVb2tBdFJCUkczMENNTU92Ry12WE5idExOVjFVOXZNdndUNEVIdVpFZlpvczFiT3ZtRlVDeE9ibkhleVc0dEJNWFF1ZmJpMTdMa3V2a1ZaNzBGenpNTXRxTEdERXNVb3dQbXBPMWdWMURzeXNkZHVfRnFnTkxvclhiVk1FcVBJQUlDUDNzcFNtTUU?oc=5", "source": "https://www.siam.in/", "published": "2026-10-26 05:47", "score": -0.318, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex jumps 1,100 pts from day\u2019s low, Nifty closes above 22,750 as D-St rebounds after 4-day losses. Is t", "link": "https://news.google.com/rss/articles/CBMijAJBVV95cUxNdHlGVlhDbi04WWhPOU5Qdzcyc2FGWnBNLVVEbUU3SzRnVm5IQ1RXMWc1RUFpNUIxOC0yVkxtYTJsSWNWYjB3cVhFWVFGUU9SSHhtX1JsdFp3djJqbFRDdURTY2VJYVoxQVRjS2VYZXNJem9MVzVHZWhxWmgybEl1TE1OdFI4bHRwTXZyMENjWTUwWGhXQkNmNUlPd3pjS3VpbF82SG5zb1V3YldiNl93STI3RVZIVXhKNWltdHZFUkxNMFNER0Y2cmYyRnV2b29VYUoxcmtNV2lJWkdWQTFnaGxDXzNuREpPSmlOSFliaC05Mzl6bE80YkxOOTltWmxMd2xIaDRuN2ZCSEF60gGSAkFVX3lxTE5iU183QzBCMXA1cUJUUS1UWDZORmpLdHZrLWxzRExLdUViWUdtdnJqM1JkRV9Hc1kzMHA4VUhDc1I5clMwN2pTWHJDZnRpaTlVSmh6bzEzU28xMkxSd0pvV2RjdExaVFFBY0F2TXhtZ0JXRkF5RWlqbng4V2E2MHZwTXp5OE9icHFJSlBIUERNREtoZDdJZ3JLNml6NWRaZTFBZnBVSVJLXzF3Wk5Wd0hvVkN2Mkl2U3NkVks4N3FXb3NmUFpHYkpIWHJkdFhJSG1FckdnN2ZmbGdOSHRkN3Y1VFFkRENaZ09ESUdLU1F2MGVmck8xYjRQRzJNZkFkeGY5cTE2RDB3a2JIQ1JEV3FHVUE?oc=5", "source": "The Economic Times", "published": "2026-10-26 04:52", "score": 0.202, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex settles 500 pts higher, Nifty ends above 22,750: Key factors behind markets snapping 4-day fall", "link": "https://news.google.com/rss/articles/CBMi8gFBVV95cUxObWtEb2xmNG1MT1gtZGl5QmxBd0FnOUsyTG9KRC1fZGp4TVB2bXU5dy1DbXVFT0lpMHJsdjhJUG8xUGNOUTRCazQ0eGdNNm1aRmp5STQ5WVVfVk11QmlNaW5sRVFzMGFneGd0WFR1TV9SMzRYWlR6M2JxR3FPMmFXVjctVlRQS0Fkb0dLUGN0QzdHUlV3YjBJWUhLYnppS0xrY3ljU1pScG1ZYlhYOUQ4bGJCQXRkRDNMS0h6cExQOWRkWkJhbm5UMEt6clUxbjhNamRwNnBMUF9GZXlhc29ZOEhwN0ZFdEc0OHdNM21pOXcwQdIB9wFBVV95cUxPYm5CY2tLWFh0dHNHTDhZVU5ZUU9jTzZqUmZkMUxHX09CT1JXVW9yNDJralc1a0I3MkY5ajNSVlNlZEtOOVJhajV2SERSbDRveW5CZVRyaWl1QmxmMF9zR0M1a2hwUEtibHRnYzhrc2xreUpKNVJLbkdCdnBnelpMejYxeDFhVmc0czFLQXd2dmd1cFBHTmVES1VabGxha25OTnFIZ2RTUlU4b3BXWmxuVVZidVJpcEhxdU5VaHBGT0JYd2JUaUlKa2lJdl9TV29tTHQ0NWJJZUpZM2l6eUZIT1lVTGQxQ3d6SF9SMloxMUZTODFYR01v?oc=5", "source": "Moneycontrol.com", "published": "2026-10-26 04:32", "score": 0.077, "label": "Neutral"}, {"symbol": "MARKET", "title": "Why is the stock market down today? Sensex drops over 600 points, Nifty drops below 22,400 - Top 3 reasons explained", "link": "https://news.google.com/rss/articles/CBMijwJBVV95cUxOb1ltRTY1OWNHNTZkX01xdG94Sno3YzJaVXpTRGVHRm5oeHVsbmtxX2lLN1VYbDhkaV91TUdPRG1vYk5ISlp6Y2xzVkZXdkNtQ1FCY2h0WFRSck9fZG5idm9STGFzWjQ2RXN0THlLcWZITV9QRy1yVGFyTnRvNTFHQ2sxRkloT190WWlFRTlJWUJCV3Vhcmg2YUZtVEJOaVRTR3FyclhwSlF0OGhHM3AyZVhPbmhQa2lpalR1QTRabi1pRDdYWHVSSUNINzRIWUd5TDJtUm9ieklsb3hzZ2tqdWp6ZHdGWVZFLTFDVVJWem1XVHJtRFhQd2J6Vy1DWjFyV0JOMGxtaUw2QzhTX2Iw0gGUAkFVX3lxTE43aTVQOGpOSnN6Q1RIY0hHMUZoa1lWQ3VWYjBCVzdxSmZJM2VxRlkzdngteEhxTzRWOFY5UVE3Rk1NX0J0a281VDdaTTVCakxnX0pWTTJNT09QNzRLcjRmdGhNNlBJczlFUzNIOEY0Qm1UNUpPVzhqbFduWmg2azBPTlY2WW5KZ1BPYmZBQ0t0a3NYem0zc3h4cXBjVXhRWkdxZXFqR3pyS2JjX2pycmVGc0ZtblJRa0F5WVU0bDlFMlNlV2hUeFo2c0c3X2JydnBRNjlGMEkxb3RUcVdNMThtRVNiVG05RlBhX3FkRXdGc2NZN1V4cW9MQTZ4MkRkNU9YNkc1Njg1QklKVXM2SGx2dVZmQQ?oc=5", "source": "Livemint", "published": "2026-10-26 04:05", "score": 0.542, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock Market Today: Gift Nifty, FPI Outflows To Oil Prices; Five Key Factors For Sensex, Nifty 50 On October 26", "link": "https://news.google.com/rss/articles/CBMi9AFBVV95cUxPSHRyNnRKa2l4REEydXQ2Q2k3TGFibXlGTHYxMXZYNWVfT0wwREEwV1JCbDMtZjZPa2c3SGMtcVVXdTVONDFuQ19MRmdxNkYxNVRMOHRJTEVyX2Jwd3h4UVVZcGhSZExmLXNUc0ZpS3dPX0V5eEVVTmtWMVlaNXNwTkFxaVFZTnVxNjNuaWkwbWZGb0toQkVkcUZvVG1oWi1VdzFPZHVQSzFFdFVfcHRIMVAtV1lycE9OaVJzdDRGWE5uamNsdEhCWmt2TEZpZ1plUE1uS3V5ZlViQWVmMzljSURGeTZBWkdJM1R4NWlnQWpTX3BO0gH8AUFVX3lxTE9JSmRUODFyV0xUUE16TFZoTkxKOXFjOTVRSUxzenEwRmt6LUUtWXlUZlNBekdRWFhUM3kwUjV2d2JWMExZWEUxNkt2d0JET2RMdkw0WGNpakMyMm9yX3NhLW5PVVdNTlVaNVdSUDRELUZOUXJsZndCTXU4TE9wcFVySTk3LW5qQzRJMUR1aWhsLW15VUJDbVhHNlg4QWpkTFdaODItQzVEMUs2Ukd3ci1LaHV4Y1lqS1VadWRVcmxYM1JRRl9qZTNQRUZSM0NsRDVFOWUxT1ZiVUU4eWVaT3hQUWJjMnFwb0JlcG1BMmc1TldxdVJNRzhHN3BDMQ?oc=5", "source": "NDTV Profit", "published": "2026-10-26 01:27", "score": 0.807, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock market outlook today, 26 Oct: Sensex, Nifty prediction - DJIA, S&amp;P, NASDAQ, GIFT Nifty, Kospi, Nikkei cues", "link": "https://news.google.com/rss/articles/CBMiggJBVV95cUxPQ1VteDhIb2FLNjlYTDNFYnpHMkZnUUhzdWp1OXhZVmFEakEwUkRhaFRQWkw1NTFmT3pNWjdtWV9sRG44T2t3ZWJKY2hfZ2JnTVBHMkZaVDFFdWpseUQ2Q1BrMG9UTzUtWmJjaDlEQkJzWkczZ096NWNyekZwODNmTi1vaFRaRHJ5WHVoRnJ0anZ3RnRYVTB0UVJtaWU3VHotWHkyN253b1N2U3FBakhfcFBMcVotUXJEZVB3bV9VN0NpWnJIT2dQQ1lhNm9TNTJ0TnhSOHctb3FKeldmVmtzN0Y1UXBNWXkwckpSdU5LM2FpSDNrNGdkQmhOY3RzVThScmfSAYcCQVVfeXFMTVhYNU56cEdVekczaDV0QXFhMWhxYk1ScXYxVGpyZURHTDQyYmJYdTAtdEt3S0NPaDVxaXpodmMwNko5bzJtcnZjSlV5Xy1WS3ViVDFDWk9TUUdjclpRMnpGMWsweklyTk5SenllRUR4QnF0N1pMU0NaTXNHTWw1NmljUE1FX2FSOUtaZGc3SldjMVBjNzZsV2EyUEVTdlZ4STlGY0JTRlNOUGFxUVN3bC1kVWlTSHNUb0NlQUhSZmw1UlZxWkJHQjNMYlI2V01JZ2ZCcldqemg2Qk81NFZESE1yVjZORUxBSnlYY1FYaGtSeXowOEUwYVVSXzRuRWs2UjFhNmkzdlU?oc=5", "source": "Livemint", "published": "2026-10-26 01:22", "score": 0.842, "label": "Positive"}, {"symbol": "MARKET", "title": "Trump hints at an Iran attack or deal! Impact on India stock market, Sensex, Nifty, gold decoded; top 10 stocks to watch", "link": "https://news.google.com/rss/articles/CBMikwJBVV95cUxNa3ozTnRCMGwyY1N4ZU44amNGNmtOQU95T0dPWG1JV0lLOHI3TEdzU0pJYXR1S3VPODFBZktza2RBYTRnQmdiSFROTE9fNkkwNTJsNnVMZDBwR3NQMTlxUEVudmRpMjM2Wmh1bjBsdjBfZmtHM3RwWUc2Tk5sc2JhVjQ1dElaS3hJdl9HOHNucGhHZ1lNQTMycHVSTmxZZFY2RHpobzZjNmNSNTBrb1lTeE14WkdYcWNnU29PWU1BRW5RVTY4QkJNbUM2dlhZRU9aYnRJUDNvaHI0TDg5N0ZEakVndlh4Z1k0cV90ZTRGeW9RNW9tWjhUakR0cGtzanJ1OHVFR0lzRFdaOTdMUmRybUdlONIBmAJBVV95cUxQaUpwaTBtTU0wdTdWbUllRWhlMmR4eGRwY055bVE5VVUxNGEyY3h2Y09XaXN5SjJ2a2FGc3ZrT2VTNFRtTEZJTjdlQkR4eGFqSDgzMzlSZFJJYUxjYmNmZTdoMUhneS1CZm0wZ3RnS3JNcnJkSUJPMS1pRW81aDA5UHNBbXZVYThRY19BSFNRZno2Sm5GeXpSMDFPUG1sRjZxMTFTWGZOMU4yakNFNmRaeW03NEJGLVA3aElDWThicGZNb2ZzdzE2eHN3bk1WUWxyQ0x6dDBULTg4T1hFNGFjTDFQOWF3Y1VRdWtqdEFJS2dDYW54LWZtaERRNGZKMHdIOUZCbWMxQWpiTV9VV2w3ekNRQnF0Q1Nx?oc=5", "source": "Livemint", "published": "2026-10-25 07:03", "score": 0.176, "label": "Neutral"}, {"symbol": "SYRMA", "title": "ELECON Share Price Today - Elecon Engineering Company on NSE/BSE", "link": "https://news.google.com/rss/articles/CBMiakFVX3lxTFBXWW9pdkRraEFFc1FVaFlDY0tuU1JSc0dHSUtZbERXa0t5czV0a0JBRWJXaFNRTzFVWXlMZXdaeGVoSENlQkp2czQ3aDVWZ2JFb2lYRkZlQ0lQeFlRdUNmMDVLcU96aV9QOVE?oc=5", "source": "scanx.trade", "published": "2026-10-23 22:40", "score": 0.0, "label": "Neutral"}], "errors": []}, "created": "2026-10-30T14:55:17", "last_updated": "2026-10-30T14:55:20", "corp_actions": [], "fundamentals": {"AEROFLEX": {"name": "AEROFLEX INDUSTRIES LTD", "pe": 78.65103, "fwd_pe": 54.181824, "sector": "Industrials", "industry": "Metal Fabrication", "mcap_cr": 7098.2230016, "pb": 14.2838125, "rev_growth": 0.873, "earn_growth": 1.509}, "CPPLUS": {"name": "ADITYA INFOTECH LIMITED", "pe": 93.28194, "fwd_pe": 50.383343, "sector": "Industrials", "industry": "Building Products &amp; Equipment", "mcap_cr": 46739.259392, "pb": 23.922348, "rev_growth": 0.895, "earn_growth": 3.037}, "THANGAMAYL": {"name": "THANGAMAYIL JEWELLERY LTD", "pe": 35.413353, "fwd_pe": 24.44221, "sector": "Consumer Cyclical", "industry": "Luxury Goods", "mcap_cr": 13847.0391808, "pb": 9.778979, "rev_growth": 0.712, "earn_growth": 0.861}, "KIRLOSENG": {"name": "KIRLOSKAR OIL ENG LTD", "pe": 47.92156, "fwd_pe": 31.48291, "sector": "Industrials", "industry": "Specialty Industrial Machinery", "mcap_cr": 26136.82176, "pb": 7.2113123, "rev_growth": 0.134, "earn_growth": -0.199}, "SMLMAH": {"name": "SML MAHINDRA LIMITED", "pe": 46.491833, "fwd_pe": null, "sector": "Consumer Cyclical", "industry": "Auto Manufacturers", "mcap_cr": 6837.129216, "pb": 12.203249, "rev_growth": 0.207, "earn_growth": -0.444}, "AETHER": {"name": "AETHER INDUSTRIES LIMITED", "pe": 91.00225, "fwd_pe": 54.33023, "sector": "Basic Materials", "industry": "Specialty Chemicals", "mcap_cr": 21451.4745344, "pb": 8.731544, "rev_growth": 0.275, "earn_growth": 0.341}, "SBC": {"name": "SBC EXPORTS LIMITED", "pe": 77.82353, "fwd_pe": null, "sector": "Consumer Cyclical", "industry": "Apparel Manufacturing", "mcap_cr": 3149.997056, "pb": 31.276596, "rev_growth": 0.855, "earn_growth": 0.0}, "SYRMA": {"name": "SYRMA SGS TECHNOLOGY LTD", "pe": 84.51898, "fwd_pe": 50.154373, "sector": "Technology", "industry": "Electronic Components", "mcap_cr": 31307.3369088, "pb": 10.862635, "rev_growth": 0.683, "earn_growth": 0.86}, "TDPOWERSYS": {"name": "TD POWER SYSTEMS LTD.", "pe": 81.125, "fwd_pe": 47.99328, "sector": "Industrials", "industry": "Specialty Industrial Machinery", "mcap_cr": 22948.2299392, "pb": 20.810984, "rev_growth": 0.721, "earn_growth": 0.72}, "RATNAVEER": {"name": "RATNAVEER PRECISION ENG L", "pe": 18.569588, "fwd_pe": 22.657234, "sector": "Basic Materials", "industry": "Steel", "mcap_cr": 3023.4468352, "pb": 3.659887, "rev_growth": 0.189, "earn_growth": -0.097}}, "research": {"method": "auto", "generated": "2026-10-30 14:55", "title": "Stock by stock (auto-generated)", "stocks": {"AEROFLEX": {"symbol": "AEROFLEX", "name": "AEROFLEX INDUSTRIES LTD", "view": "Moderately bullish", "view_score": 0.86, "tone": "mod-bull", "summary": "6.1% below its 12-month high: a shallow pullback inside the uptrend.", "why": "Shallow pullback, strong earnings growth, highest volatility", "points": [{"text": "6.1% below its 12-month high: a shallow pullback inside the uptrend.", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "Highest volatility of the batch (70%) \u2014 expect big swings.", "kind": "risk", "source": "SwingScope data", "url": ""}, {"text": "Premium valuation (P/E \u2248 79).", "kind": "context", "source": "SwingScope data", "url": ""}, {"text": "Earnings growth \u2248 151% YoY (latest quarter).", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "[Results] Aeroflex Industries Share Price Surges 14% After Q2: Profit Jumps 157%, Why the Depreciation Change Matters", "kind": "catalyst", "source": "Univest", "url": "https://news.google.com/rss/articles/CBMi3AFBVV95cUxNanpjQUFtMlRJTE9VYkRiZHVsdDd4bzhuRTd4MlpDd2RvRzZYTDN0UzdQaDJwcEQwaWc4cktjUzRPVUFBN2RRY2czNlhDRVJ5WnlDMHdyTmpUb2J1ekgtZ3RwcHVJYnptZVV2dWJxX0xuRWU1UkVVVjBmOU5Pd2FBMWl2ZkV6TFlodUt1MUNwb2dRNG9aaTRrenRrU3g3ZnE2TXFWU2NHUjYxUVJVOWpYRG5RdUNRMUdvSC16ZGtQb25uZnVNd1BPZHBpOE80MFNMYy04SS1TaGVSNWtl?oc=5"}, {"text": "Since entry: -0.36% (Day 1).", "kind": "risk", "source": "SwingScope data", "url": ""}]}, "CPPLUS": {"symbol": "CPPLUS", "name": "ADITYA INFOTECH LIMITED", "view": "Neutral to bullish", "view_score": 0.4, "tone": "spec", "summary": "11.0% below its 12-month high: a shallow pullback inside the uptrend.", "why": "Shallow pullback, strong earnings growth, stretched valuation", "points": [{"text": "11.0% below its 12-month high: a shallow pullback inside the uptrend.", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "Valuation is stretched (P/E \u2248 93).", "kind": "risk", "source": "SwingScope data", "url": ""}, {"text": "Earnings growth \u2248 304% YoY (latest quarter).", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "[Results] Do Aditya Infotech's (NSE:CPPLUS) Earnings Warrant Your Attention?", "kind": "context", "source": "Simply Wall St", "url": "https://news.google.com/rss/articles/CBMi0gFBVV95cUxPWm03Y2s2TzZiU2ZxV1l5QTBwZTlLVXkzOFd2WlYyZ1ZiU2dEWUFneElwRG1HMUNaNTFCX1p2V3otUVhCZU5SOTlyRUNIdjZaTTh4cUVmWDRHMlg3ZDNCX0VQaEtITUpRNVBvbHRFMnJ0NjV4YjhOUHZNUFJhZ1IwRGt3UXJDeE16ck5zb3ZSN0ozNVVMc2xjM05NRGVrUjVfWlVEZGJpWGNicFNnb0NvSDYxMFZyS0FoRkFhZTU2T2lienVEZzV5WWxkeFF4bjFsMHfSAdcBQVVfeXFMTkpxQ2JGc2tYb1NXcGpqQzBib1gxRXpKNUpTcmZ0a3lkcm1oMVpBcTN5M3piTUludmVTZWN2ekRHUnpDTThqRVd5TFloZ0h2UkpScFBiWkJ1ZlhxMUtqaXdNaTU0bGhlZVFPX2wyOG9fRDhZYWRPVWxkUzRTTmZabnFpSnA4b0FnM0VDbTY1R3U0ZmJueThIU180bWtiSTV6NHhzbzd4blZsVDdSaHQwWlo3RTdDSk9iTFdqSkZKbEJhSHhzWFJhR3NkVnVzdUVXbTNUTXM5c00?oc=5"}, {"text": "Since entry: -3.07% (Day 1).", "kind": "risk", "source": "SwingScope data", "url": ""}]}, "THANGAMAYL": {"symbol": "THANGAMAYL", "name": "THANGAMAYIL JEWELLERY LTD", "view": "Neutral to bearish", "view_score": -0.91, "tone": "mod-bear", "summary": "36.7% below its 12-month high \u2014 a deep drawdown; the trend is weakening.", "why": "Strong earnings growth, results, deep drawdown, negative recent leg", "points": [{"text": "36.7% below its 12-month high \u2014 a deep drawdown; the trend is weakening.", "kind": "risk", "source": "SwingScope data", "url": ""}, {"text": "3-1 month return -22.3% \u2014 the recent leg is negative.", "kind": "risk", "source": "SwingScope data", "url": ""}, {"text": "High volatility (58%).", "kind": "risk", "source": "SwingScope data", "url": ""}, {"text": "Thin liquidity (\u20b937 cr/day) \u2014 gap risk in a falling market.", "kind": "risk", "source": "SwingScope data", "url": ""}, {"text": "Earnings growth \u2248 86% YoY (latest quarter).", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "[Results] Thangamayil FY26 Net Profit Jumps 196% to \u20b935,165 Lakhs", "kind": "catalyst", "source": "scanx.trade", "url": "https://news.google.com/rss/articles/CBMi8AFBVV95cUxNZWQxVFZva3o0cms1Y2N2ZmRJMnk0TmZzTTdLUWVuZE8taXVteEgyeDhHQi1wYUIyU0RGb3J5QWFxd2pLSTJILUVSOEZVZTBDbExkVkMtT0tiNjhGOGpubU1KQ25LQ1ZFUXkyUDZmY0FIdWZBSm96cm1vZ3R3VEtQUHFKLTBZM18tZmx4NDhNRWM2OURvX2xQQXJncWtod1ZoR3ZoV3A4bldUSkxXMU8xNlEzU2tMeWYxeHMwYk5LeVlYQ3hJeGVqMkdNYlRIQTZnUXpxTk5xZzA0aGZqNGVId0pnbTRLd3RJNWZZcWQ3azQ?oc=5"}, {"text": "Since entry: -3.79% (Day 1).", "kind": "risk", "source": "SwingScope data", "url": ""}]}, "KIRLOSENG": {"symbol": "KIRLOSENG", "name": "KIRLOSKAR OIL ENG LTD", "view": "Neutral to bearish", "view_score": -1.2, "tone": "mod-bear", "summary": "26.3% below its 12-month high \u2014 a deep drawdown; the trend is weakening.", "why": "Deep drawdown", "points": [{"text": "26.3% below its 12-month high \u2014 a deep drawdown; the trend is weakening.", "kind": "risk", "source": "SwingScope data", "url": ""}, {"text": "Since entry: -4.98% (Day 1).", "kind": "risk", "source": "SwingScope data", "url": ""}]}, "SMLMAH": {"symbol": "SMLMAH", "name": "SML MAHINDRA LIMITED", "view": "Bearish", "view_score": -1.78, "tone": "bear", "summary": "29.0% below its 12-month high \u2014 a deep drawdown; the trend is weakening.", "why": "Accelerating momentum, deep drawdown, high volatility", "points": [{"text": "29.0% below its 12-month high \u2014 a deep drawdown; the trend is weakening.", "kind": "risk", "source": "SwingScope data", "url": ""}, {"text": "3-1 month return +42.7% \u2014 recent momentum is accelerating.", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "High volatility (62%).", "kind": "risk", "source": "SwingScope data", "url": ""}, {"text": "Thin liquidity (\u20b938 cr/day) \u2014 gap risk in a falling market.", "kind": "risk", "source": "SwingScope data", "url": ""}, {"text": "Since entry: -3.93% (Day 1).", "kind": "risk", "source": "SwingScope data", "url": ""}]}, "AETHER": {"symbol": "AETHER", "name": "AETHER INDUSTRIES LIMITED", "view": "Neutral", "view_score": -0.56, "tone": "neutral", "summary": "12.2% below its 12-month high \u2014 consolidating after a big run.", "why": "Results, thin liquidity, stretched valuation", "points": [{"text": "12.2% below its 12-month high \u2014 consolidating after a big run.", "kind": "context", "source": "SwingScope data", "url": ""}, {"text": "Thin liquidity (\u20b939 cr/day) \u2014 gap risk in a falling market.", "kind": "risk", "source": "SwingScope data", "url": ""}, {"text": "Valuation is stretched (P/E \u2248 91).", "kind": "risk", "source": "SwingScope data", "url": ""}, {"text": "[Results] Aether Industries Q2 FY27: Net profit rises 26% to \u20b968 crore as revenue climbs 24% to \u20b9347 crore", "kind": "catalyst", "source": "Business Upturn", "url": "https://news.google.com/rss/articles/CBMi2wFBVV95cUxNbVVVa0lsV1JvNU1BWnlRVFJSNDQ2Y3l5Z0xwZWdFS2JSTkJPbkxlN2ZfNE1ZZ2hVa0EwMVZ3enhwOGNTQ2VFRC0waFdOckhEaGJ5RDctUGg4UUEyNE9La1BweFVkeWNya2h0SFZ4WVZhZlVLTjl2cXhLaURoTkxSMXd6MHVVTmtYZk90SUx1NmsycU1KMHZKZVItNWRuR29pYy1KWTVEMWdPdGVQcHRQMXFadHJ2TFc0UEFjVGpKM2s1WTJER1RJV3Y4eU1GMmItSDNpR2hBZlRNdkk?oc=5"}, {"text": "Since entry: +1.18% (Day 1).", "kind": "catalyst", "source": "SwingScope data", "url": ""}]}, "SBC": {"symbol": "SBC", "name": "SBC EXPORTS LIMITED", "view": "Strongest, bullish", "view_score": 2.0, "tone": "strong-bull", "summary": "Close is only -0.0% below its 12-month high \u2014 relative strength near highs.", "why": "Near highs, accelerating momentum, thin liquidity", "points": [{"text": "Close is only -0.0% below its 12-month high \u2014 relative strength near highs.", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "3-1 month return +27.2% \u2014 recent momentum is accelerating.", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "Lowest volatility of the batch (36%).", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "Thin liquidity (\u20b948 cr/day) \u2014 gap risk in a falling market.", "kind": "risk", "source": "SwingScope data", "url": ""}, {"text": "Premium valuation (P/E \u2248 78).", "kind": "context", "source": "SwingScope data", "url": ""}, {"text": "Since entry: -1.34% (Day 1).", "kind": "risk", "source": "SwingScope data", "url": ""}]}, "SYRMA": {"symbol": "SYRMA", "name": "SYRMA SGS TECHNOLOGY LTD", "view": "Bullish", "view_score": 1.53, "tone": "bull", "summary": "6.4% below its 12-month high: a shallow pullback inside the uptrend.", "why": "Shallow pullback, accelerating momentum", "points": [{"text": "6.4% below its 12-month high: a shallow pullback inside the uptrend.", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "3-1 month return +30.0% \u2014 recent momentum is accelerating.", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "Premium valuation (P/E \u2248 85).", "kind": "context", "source": "SwingScope data", "url": ""}, {"text": "Earnings growth \u2248 86% YoY (latest quarter).", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "[Results] Syrma SGS Q2 results: Profit nearly doubles to \u20b9117 crore, revenue jumps 74%", "kind": "catalyst", "source": "CNBC TV18", "url": "https://news.google.com/rss/articles/CBMipwFBVV95cUxQa0tHRVBlU0NteTRiWnRVeHdHSzBkUXdLd2tRWTJPYThtVXJUT0V4Z09aVVpUaWE4TUVQQVNvVXVzYVFsRmZlT1VFVFE4NWI3bFRScmJmZTdsa3FrTmtvNmdEeXF5WnlsdWFDZ3pOdUJnUmpsYUdVTDRHWDVJS0RRMTlrWFNQR3Zib1cybjlXZUQ1WXRNVGxlZWlnblZLQll3czJQelAzUdIBrAFBVV95cUxQWWVNajdfcWthd1FGS3dENzdIeWltVzdfWTRueHBPYlFWSEs4MHNnOW9HQnVWODIxTENyb21PblA5Y3d2Ym4zeVkza29VZ0VQSENCb3dhUVQyN1N4WFlGWnNTaUt1czBRWl9NTy01UmU0bExnQXZKMUhpeW8yUU9GT0tPbDFpeHh6em5GZzNZNzZTYUFuSkR6RlFwS0Fwcy1SQjZLSHdDdTRFaTZm?oc=5"}, {"text": "Since entry: -2.97% (Day 1).", "kind": "risk", "source": "SwingScope data", "url": ""}]}, "TDPOWERSYS": {"symbol": "TDPOWERSYS", "name": "TD POWER SYSTEMS LTD.", "view": "Neutral to bullish", "view_score": 0.5, "tone": "spec", "summary": "12.9% below its 12-month high \u2014 consolidating after a big run.", "why": "Accelerating momentum, strong earnings growth, high volatility", "points": [{"text": "12.9% below its 12-month high \u2014 consolidating after a big run.", "kind": "context", "source": "SwingScope data", "url": ""}, {"text": "3-1 month return +39.4% \u2014 recent momentum is accelerating.", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "High volatility (63%).", "kind": "risk", "source": "SwingScope data", "url": ""}, {"text": "Premium valuation (P/E \u2248 81).", "kind": "context", "source": "SwingScope data", "url": ""}, {"text": "Earnings growth \u2248 72% YoY (latest quarter).", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "Since entry: -0.77% (Day 1).", "kind": "risk", "source": "SwingScope data", "url": ""}]}, "RATNAVEER": {"symbol": "RATNAVEER", "name": "RATNAVEER PRECISION ENG L", "view": "Strongest, bullish", "view_score": 1.8, "tone": "strong-bull", "summary": "Close is only -0.0% below its 12-month high \u2014 relative strength near highs.", "why": "Near highs, very strong 6-1", "points": [{"text": "Close is only -0.0% below its 12-month high \u2014 relative strength near highs.", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "6-1 month return +106% \u2014 very strong medium-term momentum.", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "3-1 month return +77.9% \u2014 recent momentum is accelerating.", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "Most liquid name in the batch (\u20b9178 cr/day).", "kind": "context", "source": "SwingScope data", "url": ""}, {"text": "[Results] Ratnaveer Precision Engineering Q2 FY27 Earnings Call on 3 Nov", "kind": "context", "source": "Kalkine India", "url": "https://news.google.com/rss/articles/CBMi1gFBVV95cUxOT0FlR3g5MTluX3phZ0tWLW1iVHAzbUh0dGFBRjcyLTBFQTl5bXkweTNIYlAtYjFSYlhBUFJYQ05VOVUzUFRLaDhwcmg0b2xZSE1JMV9rNlpuMFFDYTljQnpjdE5rMDJ2YWxGaDJZMFpCWFd5RDBuYjFvbE8xS085dmc0aktudXE5MDc5UlhCUVlQSVBtRnFwbUtwNG1lNkFVM2tWYzNLeDdHTGlhUjBXNEVMZ011Q0RJVkVoM24tWTNHWERXbHZ5U1hhOTRDQ0RmSlBFWDdn?oc=5"}, {"text": "Since entry: +1.71% (Day 1).", "kind": "catalyst", "source": "SwingScope data", "url": ""}]}}, "shortlist": ["SBC", "RATNAVEER", "SYRMA", "AEROFLEX", "TDPOWERSYS", "CPPLUS", "AETHER", "THANGAMAYL", "KIRLOSENG", "SMLMAH"], "missing": []}}</t>
+          <t>LEX INDUSTRIES LTD", "view": "Moderately bullish", "view_score": 0.85, "tone": "mod-bull", "summary": "6.1% below its 12-month high: a shallow pullback inside the uptrend.", "why": "Shallow pullback, strong earnings growth, highest volatility", "points": [{"text": "6.1% below its 12-month high: a shallow pullback inside the uptrend.", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "Highest volatility of the batch (70%) \u2014 expect big swings.", "kind": "risk", "source": "SwingScope data", "url": ""}, {"text": "Premium valuation (P/E \u2248 79).", "kind": "context", "source": "SwingScope data", "url": ""}, {"text": "Earnings growth \u2248 151% YoY (latest quarter).", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "[Results] Aeroflex Industries Share Price Surges 14% After Q2: Profit Jumps 157%, Why the Depreciation Change Matters", "kind": "catalyst", "source": "Univest", "url": "https://news.google.com/rss/articles/CBMi3AFBVV95cUxNanpjQUFtMlRJTE9VYkRiZHVsdDd4bzhuRTd4MlpDd2RvRzZYTDN0UzdQaDJwcEQwaWc4cktjUzRPVUFBN2RRY2czNlhDRVJ5WnlDMHdyTmpUb2J1ekgtZ3RwcHVJYnptZVV2dWJxX0xuRWU1UkVVVjBmOU5Pd2FBMWl2ZkV6TFlodUt1MUNwb2dRNG9aaTRrenRrU3g3ZnE2TXFWU2NHUjYxUVJVOWpYRG5RdUNRMUdvSC16ZGtQb25uZnVNd1BPZHBpOE80MFNMYy04SS1TaGVSNWtl?oc=5"}, {"text": "Since entry: -0.36% (Day 1).", "kind": "risk", "source": "SwingScope data", "url": ""}]}, "CPPLUS": {"symbol": "CPPLUS", "name": "ADITYA INFOTECH LIMITED", "view": "Neutral to bullish", "view_score": 0.4, "tone": "spec", "summary": "11.0% below its 12-month high: a shallow pullback inside the uptrend.", "why": "Shallow pullback, strong earnings growth, stretched valuation", "points": [{"text": "11.0% below its 12-month high: a shallow pullback inside the uptrend.", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "Valuation is stretched (P/E \u2248 93).", "kind": "risk", "source": "SwingScope data", "url": ""}, {"text": "Earnings growth \u2248 304% YoY (latest quarter).", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "[Results] Do Aditya Infotech's (NSE:CPPLUS) Earnings Warrant Your Attention?", "kind": "context", "source": "Simply Wall St", "url": "https://news.google.com/rss/articles/CBMi0gFBVV95cUxPWm03Y2s2TzZiU2ZxV1l5QTBwZTlLVXkzOFd2WlYyZ1ZiU2dEWUFneElwRG1HMUNaNTFCX1p2V3otUVhCZU5SOTlyRUNIdjZaTTh4cUVmWDRHMlg3ZDNCX0VQaEtITUpRNVBvbHRFMnJ0NjV4YjhOUHZNUFJhZ1IwRGt3UXJDeE16ck5zb3ZSN0ozNVVMc2xjM05NRGVrUjVfWlVEZGJpWGNicFNnb0NvSDYxMFZyS0FoRkFhZTU2T2lienVEZzV5WWxkeFF4bjFsMHfSAdcBQVVfeXFMTkpxQ2JGc2tYb1NXcGpqQzBib1gxRXpKNUpTcmZ0a3lkcm1oMVpBcTN5M3piTUludmVTZWN2ekRHUnpDTThqRVd5TFloZ0h2UkpScFBiWkJ1ZlhxMUtqaXdNaTU0bGhlZVFPX2wyOG9fRDhZYWRPVWxkUzRTTmZabnFpSnA4b0FnM0VDbTY1R3U0ZmJueThIU180bWtiSTV6NHhzbzd4blZsVDdSaHQwWlo3RTdDSk9iTFdqSkZKbEJhSHhzWFJhR3NkVnVzdUVXbTNUTXM5c00?oc=5"}, {"text": "Since entry: -3.07% (Day 1).", "kind": "risk", "source": "SwingScope data", "url": ""}]}, "THANGAMAYL": {"symbol": "THANGAMAYL", "name": "THANGAMAYIL JEWELLERY LTD", "view": "Neutral to bearish", "view_score": -0.91, "tone": "mod-bear", "summary": "36.7% below its 12-month high \u2014 a deep drawdown; the trend is weakening.", "why": "Strong earnings growth, results, deep drawdown, negative recent leg", "points": [{"text": "36.7% below its 12-month high \u2014 a deep drawdown; the trend is weakening.", "kind": "risk", "source": "SwingScope data", "url": ""}, {"text": "3-1 month return -22.3% \u2014 the recent leg is negative.", "kind": "risk", "source": "SwingScope data", "url": ""}, {"text": "High volatility (58%).", "kind": "risk", "source": "SwingScope data", "url": ""}, {"text": "Thin liquidity (\u20b937 cr/day) \u2014 gap risk in a falling market.", "kind": "risk", "source": "SwingScope data", "url": ""}, {"text": "Earnings growth \u2248 86% YoY (latest quarter).", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "[Results] Thangamayil FY26 Net Profit Jumps 196% to \u20b935,165 Lakhs", "kind": "catalyst", "source": "scanx.trade", "url": "https://news.google.com/rss/articles/CBMi8AFBVV95cUxNZWQxVFZva3o0cms1Y2N2ZmRJMnk0TmZzTTdLUWVuZE8taXVteEgyeDhHQi1wYUIyU0RGb3J5QWFxd2pLSTJILUVSOEZVZTBDbExkVkMtT0tiNjhGOGpubU1KQ25LQ1ZFUXkyUDZmY0FIdWZBSm96cm1vZ3R3VEtQUHFKLTBZM18tZmx4NDhNRWM2OURvX2xQQXJncWtod1ZoR3ZoV3A4bldUSkxXMU8xNlEzU2tMeWYxeHMwYk5LeVlYQ3hJeGVqMkdNYlRIQTZnUXpxTk5xZzA0aGZqNGVId0pnbTRLd3RJNWZZcWQ3azQ?oc=5"}, {"text": "Since entry: -3.79% (Day 1).", "kind": "risk", "source": "SwingScope data", "url": ""}]}, "KIRLOSENG": {"symbol": "KIRLOSENG", "name": "KIRLOSKAR OIL ENG LTD", "view": "Neutral to bearish", "view_score": -1.2, "tone": "mod-bear", "summary": "26.3% below its 12-month high \u2014 a deep drawdown; the trend is weakening.", "why": "Deep drawdown", "points": [{"text": "26.3% below its 12-month high \u2014 a deep drawdown; the trend is weakening.", "kind": "risk", "source": "SwingScope data", "url": ""}, {"text": "Since entry: -4.98% (Day 1).", "kind": "risk", "source": "SwingScope data", "url": ""}]}, "SMLMAH": {"symbol": "SMLMAH", "name": "SML MAHINDRA LIMITED", "view": "Bearish", "view_score": -1.78, "tone": "bear", "summary": "29.0% below its 12-month high \u2014 a deep drawdown; the trend is weakening.", "why": "Accelerating momentum, deep drawdown, high volatility", "points": [{"text": "29.0% below its 12-month high \u2014 a deep drawdown; the trend is weakening.", "kind": "risk", "source": "SwingScope data", "url": ""}, {"text": "3-1 month return +42.7% \u2014 recent momentum is accelerating.", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "High volatility (62%).", "kind": "risk", "source": "SwingScope data", "url": ""}, {"text": "Thin liquidity (\u20b938 cr/day) \u2014 gap risk in a falling market.", "kind": "risk", "source": "SwingScope data", "url": ""}, {"text": "Since entry: -3.93% (Day 1).", "kind": "risk", "source": "SwingScope data", "url": ""}]}, "AETHER": {"symbol": "AETHER", "name": "AETHER INDUSTRIES LIMITED", "view": "Neutral", "view_score": -0.46, "tone": "neutral", "summary": "12.2% below its 12-month high \u2014 consolidating after a big run.", "why": "Results, thin liquidity, stretched valuation", "points": [{"text": "12.2% below its 12-month high \u2014 consolidating after a big run.", "kind": "context", "source": "SwingScope data", "url": ""}, {"text": "Thin liquidity (\u20b939 cr/day) \u2014 gap risk in a falling market.", "kind": "risk", "source": "SwingScope data", "url": ""}, {"text": "Valuation is stretched (P/E \u2248 91).", "kind": "risk", "source": "SwingScope data", "url": ""}, {"text": "[Results] Aether Industries Q2 FY27: Net profit rises 26% to \u20b968 crore as revenue climbs 24% to \u20b9347 crore", "kind": "catalyst", "source": "Business Upturn", "url": "https://news.google.com/rss/articles/CBMi2wFBVV95cUxNbVVVa0lsV1JvNU1BWnlRVFJSNDQ2Y3l5Z0xwZWdFS2JSTkJPbkxlN2ZfNE1ZZ2hVa0EwMVZ3enhwOGNTQ2VFRC0waFdOckhEaGJ5RDctUGg4UUEyNE9La1BweFVkeWNya2h0SFZ4WVZhZlVLTjl2cXhLaURoTkxSMXd6MHVVTmtYZk90SUx1NmsycU1KMHZKZVItNWRuR29pYy1KWTVEMWdPdGVQcHRQMXFadHJ2TFc0UEFjVGpKM2s1WTJER1RJV3Y4eU1GMmItSDNpR2hBZlRNdkk?oc=5"}, {"text": "Since entry: +1.18% (Day 1).", "kind": "catalyst", "source": "SwingScope data", "url": ""}]}, "SBC": {"symbol": "SBC", "name": "SBC EXPORTS LIMITED", "view": "Strongest, bullish", "view_score": 2.0, "tone": "strong-bull", "summary": "Close is only -0.0% below its 12-month high \u2014 relative strength near highs.", "why": "Near highs, accelerating momentum, thin liquidity", "points": [{"text": "Close is only -0.0% below its 12-month high \u2014 relative strength near highs.", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "3-1 month return +27.2% \u2014 recent momentum is accelerating.", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "Lowest volatility of the batch (36%).", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "Thin liquidity (\u20b948 cr/day) \u2014 gap risk in a falling market.", "kind": "risk", "source": "SwingScope data", "url": ""}, {"text": "Premium valuation (P/E \u2248 78).", "kind": "context", "source": "SwingScope data", "url": ""}, {"text": "Since entry: -1.34% (Day 1).", "kind": "risk", "source": "SwingScope data", "url": ""}]}, "SYRMA": {"symbol": "SYRMA", "name": "SYRMA SGS TECHNOLOGY LTD", "view": "Bullish", "view_score": 1.54, "tone": "bull", "summary": "6.4% below its 12-month high: a shallow pullback inside the uptrend.", "why": "Shallow pullback, accelerating momentum", "points": [{"text": "6.4% below its 12-month high: a shallow pullback inside the uptrend.", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "3-1 month return +30.0% \u2014 recent momentum is accelerating.", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "Premium valuation (P/E \u2248 85).", "kind": "context", "source": "SwingScope data", "url": ""}, {"text": "Earnings growth \u2248 86% YoY (latest quarter).", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "[Results] Syrma SGS Q2 results: Profit nearly doubles to \u20b9117 crore, revenue jumps 74%", "kind": "catalyst", "source": "CNBC TV18", "url": "https://news.google.com/rss/articles/CBMirAFBVV95cUxQWWVNajdfcWthd1FGS3dENzdIeWltVzdfWTRueHBPYlFWSEs4MHNnOW9HQnVWODIxTENyb21PblA5Y3d2Ym4zeVkza29VZ0VQSENCb3dhUVQyN1N4WFlGWnNTaUt1czBRWl9NTy01UmU0bExnQXZKMUhpeW8yUU9GT0tPbDFpeHh6em5GZzNZNzZTYUFuSkR6RlFwS0Fwcy1SQjZLSHdDdTRFaTZm0gGsAUFVX3lxTFBZZU1qN19xa2F3UUZLd0Q3N0h5aW1XN19ZNG54cE9iUVZISzgwc2c5b0dCdVY4MjFMQ3JvbU9uUDljd3ZibjN5WTNrb1VnRVBIQ0Jvd2FRVDI3U3hYWUZac1NpS3VzMFFaX01PLTVSZTRsTGdBdkoxSGl5bzJRT0ZPS09sMWl4eHp6bkZnM1k3NlNhQW5KRHpGUXBLQXBzLVJCNktId0N1NEVpNmY?oc=5"}, {"text": "Since entry: -2.97% (Day 1).", "kind": "risk", "source": "SwingScope data", "url": ""}]}, "TDPOWERSYS": {"symbol": "TDPOWERSYS", "name": "TD POWER SYSTEMS LTD.", "view": "Neutral to bullish", "view_score": 0.5, "tone": "spec", "summary": "12.9% below its 12-month high \u2014 consolidating after a big run.", "why": "Accelerating momentum, strong earnings growth, high volatility", "points": [{"text": "12.9% below its 12-month high \u2014 consolidating after a big run.", "kind": "context", "source": "SwingScope data", "url": ""}, {"text": "3-1 month return +39.4% \u2014 recent momentum is accelerating.", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "High volatility (63%).", "kind": "risk", "source": "SwingScope data", "url": ""}, {"text": "Premium valuation (P/E \u2248 81).", "kind": "context", "source": "SwingScope data", "url": ""}, {"text": "Earnings growth \u2248 72% YoY (latest quarter).", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "Since entry: -0.77% (Day 1).", "kind": "risk", "source": "SwingScope data", "url": ""}]}, "RATNAVEER": {"symbol": "RATNAVEER", "name": "RATNAVEER PRECISION ENG L", "view": "Strongest, bullish", "view_score": 1.8, "tone": "strong-bull", "summary": "Close is only -0.0% below its 12-month high \u2014 relative strength near highs.", "why": "Near highs, very strong 6-1", "points": [{"text": "Close is only -0.0% below its 12-month high \u2014 relative strength near highs.", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "6-1 month return +106% \u2014 very strong medium-term momentum.", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "3-1 month return +77.9% \u2014 recent momentum is accelerating.", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "Most liquid name in the batch (\u20b9178 cr/day).", "kind": "context", "source": "SwingScope data", "url": ""}, {"text": "[Results] Ratnaveer Precision Engineering Q2 FY27 Earnings Call on 3 Nov", "kind": "context", "source": "Kalkine India", "url": "https://news.google.com/rss/articles/CBMi1gFBVV95cUxOT0FlR3g5MTluX3phZ0tWLW1iVHAzbUh0dGFBRjcyLTBFQTl5bXkweTNIYlAtYjFSYlhBUFJYQ05VOVUzUFRLaDhwcmg0b2xZSE1JMV9rNlpuMFFDYTljQnpjdE5rMDJ2YWxGaDJZMFpCWFd5RDBuYjFvbE8xS085dmc0aktudXE5MDc5UlhCUVlQSVBtRnFwbUtwNG1lNkFVM2tWYzNLeDdHTGlhUjBXNEVMZ011Q0RJVkVoM24tWTNHWERXbHZ5U1hhOTRDQ0RmSlBFWDdn?oc=5"}, {"text": "Since entry: +1.71% (Day 1).", "kind": "catalyst", "source": "SwingScope data", "url": ""}]}}, "shortlist": ["SBC", "RATNAVEER", "SYRMA", "AEROFLEX", "TDPOWERSYS", "CPPLUS", "AETHER", "THANGAMAYL", "KIRLOSENG", "SMLMAH"], "missing": []}, "telegram_sent": "2026-10-30", "pending_alerts": []}</t>
         </is>
       </c>
     </row>

--- a/data/batches/2026-10-29/SwingScope_2026-10-29_tracker.xlsx
+++ b/data/batches/2026-10-29/SwingScope_2026-10-29_tracker.xlsx
@@ -31,7 +31,7 @@
     <numFmt numFmtId="167" formatCode="+0.00;-0.00;0.00"/>
     <numFmt numFmtId="168" formatCode="+0.00;-0.00"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="24">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -134,12 +134,6 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00374151"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
       <color rgb="009b1c1c"/>
       <sz val="10"/>
     </font>
@@ -179,7 +173,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="17">
     <fill>
       <patternFill/>
     </fill>
@@ -249,11 +243,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00fdecc8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00e5e7eb"/>
       </patternFill>
     </fill>
     <fill>
@@ -383,7 +372,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -588,13 +577,13 @@
     <xf numFmtId="0" fontId="17" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -604,13 +593,10 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="168" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1498,7 +1484,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Signal 2026-10-29  •  Day 1 of 21  •  Entry day (bought at open)  •  Exit ~2026-12-01  •  Updated 30-Oct-2026 18:08</t>
+          <t>Signal 2026-10-29  •  Day 1 of 21  •  Entry day (bought at open)  •  Exit ~2026-12-01  •  Updated 30-Oct-2026 19:42</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2385,7 +2371,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Signal 2026-10-29  •  Day 1 of 21  •  Entry day (bought at open)  •  Exit ~2026-12-01  •  Updated 30-Oct-2026 18:08</t>
+          <t>Signal 2026-10-29  •  Day 1 of 21  •  Entry day (bought at open)  •  Exit ~2026-12-01  •  Updated 30-Oct-2026 19:42</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -8094,7 +8080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I71"/>
+  <dimension ref="A1:I70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8125,7 +8111,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Views from auto-generated · written 2026-10-30 18:08</t>
+          <t>Views from auto-generated · written 2026-10-30 19:42</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -8271,7 +8257,7 @@
         </is>
       </c>
       <c r="E7" s="68" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="F7" s="69" t="inlineStr">
         <is>
@@ -8411,11 +8397,11 @@
       </c>
       <c r="D11" s="73" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Neutral to bearish</t>
         </is>
       </c>
       <c r="E11" s="68" t="n">
-        <v>-0.46</v>
+        <v>-0.62</v>
       </c>
       <c r="F11" s="69" t="inlineStr">
         <is>
@@ -8427,7 +8413,7 @@
       </c>
       <c r="H11" s="51" t="inlineStr">
         <is>
-          <t>• Neutral call</t>
+          <t>✗ Off track</t>
         </is>
       </c>
     </row>
@@ -8437,29 +8423,29 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>THANGAMAYL</t>
+          <t>KIRLOSENG</t>
         </is>
       </c>
       <c r="C12" s="51" t="inlineStr">
         <is>
-          <t>THANGAMAYIL JEWELLERY LTD</t>
-        </is>
-      </c>
-      <c r="D12" s="74" t="inlineStr">
+          <t>KIRLOSKAR OIL ENG LTD</t>
+        </is>
+      </c>
+      <c r="D12" s="73" t="inlineStr">
         <is>
           <t>Neutral to bearish</t>
         </is>
       </c>
       <c r="E12" s="68" t="n">
-        <v>-0.91</v>
+        <v>-1.2</v>
       </c>
       <c r="F12" s="69" t="inlineStr">
         <is>
-          <t>Strong earnings growth, results, deep drawdown, negative recent leg</t>
+          <t>Deep drawdown</t>
         </is>
       </c>
       <c r="G12" s="18" t="n">
-        <v>-0.03790087463556846</v>
+        <v>-0.04983335978416125</v>
       </c>
       <c r="H12" s="51" t="inlineStr">
         <is>
@@ -8473,29 +8459,29 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>KIRLOSENG</t>
+          <t>THANGAMAYL</t>
         </is>
       </c>
       <c r="C13" s="51" t="inlineStr">
         <is>
-          <t>KIRLOSKAR OIL ENG LTD</t>
+          <t>THANGAMAYIL JEWELLERY LTD</t>
         </is>
       </c>
       <c r="D13" s="74" t="inlineStr">
         <is>
-          <t>Neutral to bearish</t>
+          <t>Bearish</t>
         </is>
       </c>
       <c r="E13" s="68" t="n">
-        <v>-1.2</v>
+        <v>-1.7</v>
       </c>
       <c r="F13" s="69" t="inlineStr">
         <is>
-          <t>Deep drawdown</t>
+          <t>Strong earnings growth, deep drawdown, negative recent leg</t>
         </is>
       </c>
       <c r="G13" s="18" t="n">
-        <v>-0.04983335978416125</v>
+        <v>-0.03790087463556846</v>
       </c>
       <c r="H13" s="51" t="inlineStr">
         <is>
@@ -8517,7 +8503,7 @@
           <t>SML MAHINDRA LIMITED</t>
         </is>
       </c>
-      <c r="D14" s="75" t="inlineStr">
+      <c r="D14" s="74" t="inlineStr">
         <is>
           <t>Bearish</t>
         </is>
@@ -8540,7 +8526,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="76" t="inlineStr">
+      <c r="A16" s="75" t="inlineStr">
         <is>
           <t>STOCK BY STOCK — catalysts, risks and sources</t>
         </is>
@@ -8598,7 +8584,7 @@
           <t>SBC EXPORTS LIMITED</t>
         </is>
       </c>
-      <c r="D18" s="77" t="inlineStr">
+      <c r="D18" s="76" t="inlineStr">
         <is>
           <t>Catalyst</t>
         </is>
@@ -8630,7 +8616,7 @@
           <t>SBC EXPORTS LIMITED</t>
         </is>
       </c>
-      <c r="D19" s="77" t="inlineStr">
+      <c r="D19" s="76" t="inlineStr">
         <is>
           <t>Catalyst</t>
         </is>
@@ -8662,7 +8648,7 @@
           <t>SBC EXPORTS LIMITED</t>
         </is>
       </c>
-      <c r="D20" s="77" t="inlineStr">
+      <c r="D20" s="76" t="inlineStr">
         <is>
           <t>Catalyst</t>
         </is>
@@ -8694,7 +8680,7 @@
           <t>SBC EXPORTS LIMITED</t>
         </is>
       </c>
-      <c r="D21" s="78" t="inlineStr">
+      <c r="D21" s="77" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
@@ -8726,7 +8712,7 @@
           <t>SBC EXPORTS LIMITED</t>
         </is>
       </c>
-      <c r="D22" s="79" t="inlineStr">
+      <c r="D22" s="78" t="inlineStr">
         <is>
           <t>Context</t>
         </is>
@@ -8758,7 +8744,7 @@
           <t>SBC EXPORTS LIMITED</t>
         </is>
       </c>
-      <c r="D23" s="78" t="inlineStr">
+      <c r="D23" s="77" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
@@ -8790,7 +8776,7 @@
           <t>RATNAVEER PRECISION ENG L</t>
         </is>
       </c>
-      <c r="D24" s="77" t="inlineStr">
+      <c r="D24" s="76" t="inlineStr">
         <is>
           <t>Catalyst</t>
         </is>
@@ -8822,7 +8808,7 @@
           <t>RATNAVEER PRECISION ENG L</t>
         </is>
       </c>
-      <c r="D25" s="77" t="inlineStr">
+      <c r="D25" s="76" t="inlineStr">
         <is>
           <t>Catalyst</t>
         </is>
@@ -8854,7 +8840,7 @@
           <t>RATNAVEER PRECISION ENG L</t>
         </is>
       </c>
-      <c r="D26" s="77" t="inlineStr">
+      <c r="D26" s="76" t="inlineStr">
         <is>
           <t>Catalyst</t>
         </is>
@@ -8886,7 +8872,7 @@
           <t>RATNAVEER PRECISION ENG L</t>
         </is>
       </c>
-      <c r="D27" s="79" t="inlineStr">
+      <c r="D27" s="78" t="inlineStr">
         <is>
           <t>Context</t>
         </is>
@@ -8918,7 +8904,7 @@
           <t>RATNAVEER PRECISION ENG L</t>
         </is>
       </c>
-      <c r="D28" s="79" t="inlineStr">
+      <c r="D28" s="78" t="inlineStr">
         <is>
           <t>Context</t>
         </is>
@@ -8934,7 +8920,7 @@
           <t>Kalkine India</t>
         </is>
       </c>
-      <c r="H28" s="80" t="inlineStr">
+      <c r="H28" s="79" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -8954,7 +8940,7 @@
           <t>RATNAVEER PRECISION ENG L</t>
         </is>
       </c>
-      <c r="D29" s="77" t="inlineStr">
+      <c r="D29" s="76" t="inlineStr">
         <is>
           <t>Catalyst</t>
         </is>
@@ -8986,7 +8972,7 @@
           <t>SYRMA SGS TECHNOLOGY LTD</t>
         </is>
       </c>
-      <c r="D30" s="77" t="inlineStr">
+      <c r="D30" s="76" t="inlineStr">
         <is>
           <t>Catalyst</t>
         </is>
@@ -9018,7 +9004,7 @@
           <t>SYRMA SGS TECHNOLOGY LTD</t>
         </is>
       </c>
-      <c r="D31" s="77" t="inlineStr">
+      <c r="D31" s="76" t="inlineStr">
         <is>
           <t>Catalyst</t>
         </is>
@@ -9050,7 +9036,7 @@
           <t>SYRMA SGS TECHNOLOGY LTD</t>
         </is>
       </c>
-      <c r="D32" s="79" t="inlineStr">
+      <c r="D32" s="78" t="inlineStr">
         <is>
           <t>Context</t>
         </is>
@@ -9082,7 +9068,7 @@
           <t>SYRMA SGS TECHNOLOGY LTD</t>
         </is>
       </c>
-      <c r="D33" s="77" t="inlineStr">
+      <c r="D33" s="76" t="inlineStr">
         <is>
           <t>Catalyst</t>
         </is>
@@ -9114,7 +9100,7 @@
           <t>SYRMA SGS TECHNOLOGY LTD</t>
         </is>
       </c>
-      <c r="D34" s="77" t="inlineStr">
+      <c r="D34" s="76" t="inlineStr">
         <is>
           <t>Catalyst</t>
         </is>
@@ -9130,7 +9116,7 @@
           <t>CNBC TV18</t>
         </is>
       </c>
-      <c r="H34" s="80" t="inlineStr">
+      <c r="H34" s="79" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -9150,7 +9136,7 @@
           <t>SYRMA SGS TECHNOLOGY LTD</t>
         </is>
       </c>
-      <c r="D35" s="78" t="inlineStr">
+      <c r="D35" s="77" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
@@ -9182,7 +9168,7 @@
           <t>AEROFLEX INDUSTRIES LTD</t>
         </is>
       </c>
-      <c r="D36" s="77" t="inlineStr">
+      <c r="D36" s="76" t="inlineStr">
         <is>
           <t>Catalyst</t>
         </is>
@@ -9214,7 +9200,7 @@
           <t>AEROFLEX INDUSTRIES LTD</t>
         </is>
       </c>
-      <c r="D37" s="78" t="inlineStr">
+      <c r="D37" s="77" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
@@ -9246,7 +9232,7 @@
           <t>AEROFLEX INDUSTRIES LTD</t>
         </is>
       </c>
-      <c r="D38" s="79" t="inlineStr">
+      <c r="D38" s="78" t="inlineStr">
         <is>
           <t>Context</t>
         </is>
@@ -9278,7 +9264,7 @@
           <t>AEROFLEX INDUSTRIES LTD</t>
         </is>
       </c>
-      <c r="D39" s="77" t="inlineStr">
+      <c r="D39" s="76" t="inlineStr">
         <is>
           <t>Catalyst</t>
         </is>
@@ -9310,7 +9296,7 @@
           <t>AEROFLEX INDUSTRIES LTD</t>
         </is>
       </c>
-      <c r="D40" s="77" t="inlineStr">
+      <c r="D40" s="76" t="inlineStr">
         <is>
           <t>Catalyst</t>
         </is>
@@ -9326,7 +9312,7 @@
           <t>Univest</t>
         </is>
       </c>
-      <c r="H40" s="80" t="inlineStr">
+      <c r="H40" s="79" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -9346,7 +9332,7 @@
           <t>AEROFLEX INDUSTRIES LTD</t>
         </is>
       </c>
-      <c r="D41" s="78" t="inlineStr">
+      <c r="D41" s="77" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
@@ -9378,7 +9364,7 @@
           <t>TD POWER SYSTEMS LTD.</t>
         </is>
       </c>
-      <c r="D42" s="79" t="inlineStr">
+      <c r="D42" s="78" t="inlineStr">
         <is>
           <t>Context</t>
         </is>
@@ -9410,7 +9396,7 @@
           <t>TD POWER SYSTEMS LTD.</t>
         </is>
       </c>
-      <c r="D43" s="77" t="inlineStr">
+      <c r="D43" s="76" t="inlineStr">
         <is>
           <t>Catalyst</t>
         </is>
@@ -9442,7 +9428,7 @@
           <t>TD POWER SYSTEMS LTD.</t>
         </is>
       </c>
-      <c r="D44" s="78" t="inlineStr">
+      <c r="D44" s="77" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
@@ -9474,7 +9460,7 @@
           <t>TD POWER SYSTEMS LTD.</t>
         </is>
       </c>
-      <c r="D45" s="79" t="inlineStr">
+      <c r="D45" s="78" t="inlineStr">
         <is>
           <t>Context</t>
         </is>
@@ -9506,7 +9492,7 @@
           <t>TD POWER SYSTEMS LTD.</t>
         </is>
       </c>
-      <c r="D46" s="77" t="inlineStr">
+      <c r="D46" s="76" t="inlineStr">
         <is>
           <t>Catalyst</t>
         </is>
@@ -9538,7 +9524,7 @@
           <t>TD POWER SYSTEMS LTD.</t>
         </is>
       </c>
-      <c r="D47" s="78" t="inlineStr">
+      <c r="D47" s="77" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
@@ -9570,7 +9556,7 @@
           <t>ADITYA INFOTECH LIMITED</t>
         </is>
       </c>
-      <c r="D48" s="77" t="inlineStr">
+      <c r="D48" s="76" t="inlineStr">
         <is>
           <t>Catalyst</t>
         </is>
@@ -9602,7 +9588,7 @@
           <t>ADITYA INFOTECH LIMITED</t>
         </is>
       </c>
-      <c r="D49" s="78" t="inlineStr">
+      <c r="D49" s="77" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
@@ -9634,7 +9620,7 @@
           <t>ADITYA INFOTECH LIMITED</t>
         </is>
       </c>
-      <c r="D50" s="77" t="inlineStr">
+      <c r="D50" s="76" t="inlineStr">
         <is>
           <t>Catalyst</t>
         </is>
@@ -9666,7 +9652,7 @@
           <t>ADITYA INFOTECH LIMITED</t>
         </is>
       </c>
-      <c r="D51" s="79" t="inlineStr">
+      <c r="D51" s="78" t="inlineStr">
         <is>
           <t>Context</t>
         </is>
@@ -9682,7 +9668,7 @@
           <t>Simply Wall St</t>
         </is>
       </c>
-      <c r="H51" s="80" t="inlineStr">
+      <c r="H51" s="79" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -9702,7 +9688,7 @@
           <t>ADITYA INFOTECH LIMITED</t>
         </is>
       </c>
-      <c r="D52" s="78" t="inlineStr">
+      <c r="D52" s="77" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
@@ -9734,7 +9720,7 @@
           <t>AETHER INDUSTRIES LIMITED</t>
         </is>
       </c>
-      <c r="D53" s="79" t="inlineStr">
+      <c r="D53" s="78" t="inlineStr">
         <is>
           <t>Context</t>
         </is>
@@ -9766,7 +9752,7 @@
           <t>AETHER INDUSTRIES LIMITED</t>
         </is>
       </c>
-      <c r="D54" s="78" t="inlineStr">
+      <c r="D54" s="77" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
@@ -9798,7 +9784,7 @@
           <t>AETHER INDUSTRIES LIMITED</t>
         </is>
       </c>
-      <c r="D55" s="78" t="inlineStr">
+      <c r="D55" s="77" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
@@ -9830,23 +9816,23 @@
           <t>AETHER INDUSTRIES LIMITED</t>
         </is>
       </c>
-      <c r="D56" s="77" t="inlineStr">
+      <c r="D56" s="76" t="inlineStr">
         <is>
           <t>Catalyst</t>
         </is>
       </c>
       <c r="E56" s="69" t="inlineStr">
         <is>
-          <t>[Results] Aether Industries Q2 FY27: Net profit rises 26% to ₹68 crore as revenue climbs 24% to ₹347 crore</t>
+          <t>[Results] Ather Energy shares: 125% YTD returns! Experts give 'portfolio stock' tag after Q2 results 2026 | Target, stop-loss</t>
         </is>
       </c>
       <c r="F56" s="64" t="n"/>
       <c r="G56" s="51" t="inlineStr">
         <is>
-          <t>Business Upturn</t>
-        </is>
-      </c>
-      <c r="H56" s="80" t="inlineStr">
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="H56" s="79" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -9866,7 +9852,7 @@
           <t>AETHER INDUSTRIES LIMITED</t>
         </is>
       </c>
-      <c r="D57" s="77" t="inlineStr">
+      <c r="D57" s="76" t="inlineStr">
         <is>
           <t>Catalyst</t>
         </is>
@@ -9890,22 +9876,22 @@
       </c>
       <c r="B58" s="51" t="inlineStr">
         <is>
-          <t>THANGAMAYL</t>
+          <t>KIRLOSENG</t>
         </is>
       </c>
       <c r="C58" s="51" t="inlineStr">
         <is>
-          <t>THANGAMAYIL JEWELLERY LTD</t>
-        </is>
-      </c>
-      <c r="D58" s="78" t="inlineStr">
+          <t>KIRLOSKAR OIL ENG LTD</t>
+        </is>
+      </c>
+      <c r="D58" s="77" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
       </c>
       <c r="E58" s="69" t="inlineStr">
         <is>
-          <t>36.7% below its 12-month high — a deep drawdown; the trend is weakening.</t>
+          <t>26.3% below its 12-month high — a deep drawdown; the trend is weakening.</t>
         </is>
       </c>
       <c r="F58" s="64" t="n"/>
@@ -9922,22 +9908,22 @@
       </c>
       <c r="B59" s="51" t="inlineStr">
         <is>
-          <t>THANGAMAYL</t>
+          <t>KIRLOSENG</t>
         </is>
       </c>
       <c r="C59" s="51" t="inlineStr">
         <is>
-          <t>THANGAMAYIL JEWELLERY LTD</t>
-        </is>
-      </c>
-      <c r="D59" s="78" t="inlineStr">
+          <t>KIRLOSKAR OIL ENG LTD</t>
+        </is>
+      </c>
+      <c r="D59" s="77" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
       </c>
       <c r="E59" s="69" t="inlineStr">
         <is>
-          <t>3-1 month return -22.3% — the recent leg is negative.</t>
+          <t>Since entry: -4.98% (Day 1).</t>
         </is>
       </c>
       <c r="F59" s="64" t="n"/>
@@ -9950,7 +9936,7 @@
     </row>
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="50" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B60" s="51" t="inlineStr">
         <is>
@@ -9962,14 +9948,14 @@
           <t>THANGAMAYIL JEWELLERY LTD</t>
         </is>
       </c>
-      <c r="D60" s="78" t="inlineStr">
+      <c r="D60" s="77" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
       </c>
       <c r="E60" s="69" t="inlineStr">
         <is>
-          <t>High volatility (58%).</t>
+          <t>36.7% below its 12-month high — a deep drawdown; the trend is weakening.</t>
         </is>
       </c>
       <c r="F60" s="64" t="n"/>
@@ -9982,7 +9968,7 @@
     </row>
     <row r="61" ht="30" customHeight="1">
       <c r="A61" s="50" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B61" s="51" t="inlineStr">
         <is>
@@ -9994,14 +9980,14 @@
           <t>THANGAMAYIL JEWELLERY LTD</t>
         </is>
       </c>
-      <c r="D61" s="78" t="inlineStr">
+      <c r="D61" s="77" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
       </c>
       <c r="E61" s="69" t="inlineStr">
         <is>
-          <t>Thin liquidity (₹37 cr/day) — gap risk in a falling market.</t>
+          <t>3-1 month return -22.3% — the recent leg is negative.</t>
         </is>
       </c>
       <c r="F61" s="64" t="n"/>
@@ -10014,7 +10000,7 @@
     </row>
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="50" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B62" s="51" t="inlineStr">
         <is>
@@ -10028,12 +10014,12 @@
       </c>
       <c r="D62" s="77" t="inlineStr">
         <is>
-          <t>Catalyst</t>
+          <t>Risk</t>
         </is>
       </c>
       <c r="E62" s="69" t="inlineStr">
         <is>
-          <t>Earnings growth ≈ 86% YoY (latest quarter).</t>
+          <t>High volatility (58%).</t>
         </is>
       </c>
       <c r="F62" s="64" t="n"/>
@@ -10046,7 +10032,7 @@
     </row>
     <row r="63" ht="30" customHeight="1">
       <c r="A63" s="50" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B63" s="51" t="inlineStr">
         <is>
@@ -10060,29 +10046,25 @@
       </c>
       <c r="D63" s="77" t="inlineStr">
         <is>
-          <t>Catalyst</t>
+          <t>Risk</t>
         </is>
       </c>
       <c r="E63" s="69" t="inlineStr">
         <is>
-          <t>[Results] Thangamayil FY26 Net Profit Jumps 196% to ₹35,165 Lakhs</t>
+          <t>Thin liquidity (₹37 cr/day) — gap risk in a falling market.</t>
         </is>
       </c>
       <c r="F63" s="64" t="n"/>
       <c r="G63" s="51" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
-        </is>
-      </c>
-      <c r="H63" s="80" t="inlineStr">
-        <is>
-          <t>open ↗</t>
-        </is>
-      </c>
+          <t>SwingScope data</t>
+        </is>
+      </c>
+      <c r="H63" s="51" t="n"/>
     </row>
     <row r="64" ht="30" customHeight="1">
       <c r="A64" s="50" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B64" s="51" t="inlineStr">
         <is>
@@ -10094,14 +10076,14 @@
           <t>THANGAMAYIL JEWELLERY LTD</t>
         </is>
       </c>
-      <c r="D64" s="78" t="inlineStr">
-        <is>
-          <t>Risk</t>
+      <c r="D64" s="76" t="inlineStr">
+        <is>
+          <t>Catalyst</t>
         </is>
       </c>
       <c r="E64" s="69" t="inlineStr">
         <is>
-          <t>Since entry: -3.79% (Day 1).</t>
+          <t>Earnings growth ≈ 86% YoY (latest quarter).</t>
         </is>
       </c>
       <c r="F64" s="64" t="n"/>
@@ -10118,22 +10100,22 @@
       </c>
       <c r="B65" s="51" t="inlineStr">
         <is>
-          <t>KIRLOSENG</t>
+          <t>THANGAMAYL</t>
         </is>
       </c>
       <c r="C65" s="51" t="inlineStr">
         <is>
-          <t>KIRLOSKAR OIL ENG LTD</t>
-        </is>
-      </c>
-      <c r="D65" s="78" t="inlineStr">
+          <t>THANGAMAYIL JEWELLERY LTD</t>
+        </is>
+      </c>
+      <c r="D65" s="77" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
       </c>
       <c r="E65" s="69" t="inlineStr">
         <is>
-          <t>26.3% below its 12-month high — a deep drawdown; the trend is weakening.</t>
+          <t>Since entry: -3.79% (Day 1).</t>
         </is>
       </c>
       <c r="F65" s="64" t="n"/>
@@ -10146,26 +10128,26 @@
     </row>
     <row r="66" ht="30" customHeight="1">
       <c r="A66" s="50" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B66" s="51" t="inlineStr">
         <is>
-          <t>KIRLOSENG</t>
+          <t>SMLMAH</t>
         </is>
       </c>
       <c r="C66" s="51" t="inlineStr">
         <is>
-          <t>KIRLOSKAR OIL ENG LTD</t>
-        </is>
-      </c>
-      <c r="D66" s="78" t="inlineStr">
+          <t>SML MAHINDRA LIMITED</t>
+        </is>
+      </c>
+      <c r="D66" s="77" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
       </c>
       <c r="E66" s="69" t="inlineStr">
         <is>
-          <t>Since entry: -4.98% (Day 1).</t>
+          <t>29.0% below its 12-month high — a deep drawdown; the trend is weakening.</t>
         </is>
       </c>
       <c r="F66" s="64" t="n"/>
@@ -10190,14 +10172,14 @@
           <t>SML MAHINDRA LIMITED</t>
         </is>
       </c>
-      <c r="D67" s="78" t="inlineStr">
-        <is>
-          <t>Risk</t>
+      <c r="D67" s="76" t="inlineStr">
+        <is>
+          <t>Catalyst</t>
         </is>
       </c>
       <c r="E67" s="69" t="inlineStr">
         <is>
-          <t>29.0% below its 12-month high — a deep drawdown; the trend is weakening.</t>
+          <t>3-1 month return +42.7% — recent momentum is accelerating.</t>
         </is>
       </c>
       <c r="F67" s="64" t="n"/>
@@ -10224,12 +10206,12 @@
       </c>
       <c r="D68" s="77" t="inlineStr">
         <is>
-          <t>Catalyst</t>
+          <t>Risk</t>
         </is>
       </c>
       <c r="E68" s="69" t="inlineStr">
         <is>
-          <t>3-1 month return +42.7% — recent momentum is accelerating.</t>
+          <t>High volatility (62%).</t>
         </is>
       </c>
       <c r="F68" s="64" t="n"/>
@@ -10254,14 +10236,14 @@
           <t>SML MAHINDRA LIMITED</t>
         </is>
       </c>
-      <c r="D69" s="78" t="inlineStr">
+      <c r="D69" s="77" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
       </c>
       <c r="E69" s="69" t="inlineStr">
         <is>
-          <t>High volatility (62%).</t>
+          <t>Thin liquidity (₹38 cr/day) — gap risk in a falling market.</t>
         </is>
       </c>
       <c r="F69" s="64" t="n"/>
@@ -10286,14 +10268,14 @@
           <t>SML MAHINDRA LIMITED</t>
         </is>
       </c>
-      <c r="D70" s="78" t="inlineStr">
+      <c r="D70" s="77" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
       </c>
       <c r="E70" s="69" t="inlineStr">
         <is>
-          <t>Thin liquidity (₹38 cr/day) — gap risk in a falling market.</t>
+          <t>Since entry: -3.93% (Day 1).</t>
         </is>
       </c>
       <c r="F70" s="64" t="n"/>
@@ -10304,40 +10286,8 @@
       </c>
       <c r="H70" s="51" t="n"/>
     </row>
-    <row r="71" ht="30" customHeight="1">
-      <c r="A71" s="50" t="n">
-        <v>10</v>
-      </c>
-      <c r="B71" s="51" t="inlineStr">
-        <is>
-          <t>SMLMAH</t>
-        </is>
-      </c>
-      <c r="C71" s="51" t="inlineStr">
-        <is>
-          <t>SML MAHINDRA LIMITED</t>
-        </is>
-      </c>
-      <c r="D71" s="78" t="inlineStr">
-        <is>
-          <t>Risk</t>
-        </is>
-      </c>
-      <c r="E71" s="69" t="inlineStr">
-        <is>
-          <t>Since entry: -3.93% (Day 1).</t>
-        </is>
-      </c>
-      <c r="F71" s="64" t="n"/>
-      <c r="G71" s="51" t="inlineStr">
-        <is>
-          <t>SwingScope data</t>
-        </is>
-      </c>
-      <c r="H71" s="51" t="n"/>
-    </row>
   </sheetData>
-  <mergeCells count="56">
+  <mergeCells count="55">
     <mergeCell ref="E43:F43"/>
     <mergeCell ref="E50:F50"/>
     <mergeCell ref="E55:F55"/>
@@ -10345,7 +10295,6 @@
     <mergeCell ref="E62:F62"/>
     <mergeCell ref="E68:F68"/>
     <mergeCell ref="E33:F33"/>
-    <mergeCell ref="E71:F71"/>
     <mergeCell ref="E67:F67"/>
     <mergeCell ref="E42:F42"/>
     <mergeCell ref="E23:F23"/>
@@ -10418,7 +10367,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H51" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H56" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
@@ -10432,7 +10380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G125"/>
+  <dimension ref="A1:G134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10460,7 +10408,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Fetched 2026-10-30 18:08</t>
+          <t>Fetched 2026-10-30 19:42</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -10510,33 +10458,33 @@
     <row r="5">
       <c r="A5" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>SYRMA</t>
         </is>
       </c>
       <c r="B5" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 17:26</t>
+          <t>2026-10-30 18:13</t>
         </is>
       </c>
       <c r="C5" s="51" t="inlineStr">
         <is>
-          <t>Markets hit 6-month high in Oct on IT rally, Jio Platforms IPO frenzy</t>
+          <t>JSW Dulux Share Price, Stock Price - NSE/BSE Live</t>
         </is>
       </c>
       <c r="D5" s="51" t="inlineStr">
         <is>
-          <t>Business Standard</t>
-        </is>
-      </c>
-      <c r="E5" s="81" t="n">
-        <v>0.226</v>
+          <t>NDTV Profit</t>
+        </is>
+      </c>
+      <c r="E5" s="80" t="n">
+        <v>0</v>
       </c>
       <c r="F5" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G5" s="82" t="inlineStr">
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G5" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -10563,7 +10511,7 @@
           <t>The Economic Times</t>
         </is>
       </c>
-      <c r="E6" s="81" t="n">
+      <c r="E6" s="80" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="51" t="inlineStr">
@@ -10571,7 +10519,7 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="G6" s="82" t="inlineStr">
+      <c r="G6" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -10585,28 +10533,28 @@
       </c>
       <c r="B7" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 16:07</t>
+          <t>2026-10-30 16:01</t>
         </is>
       </c>
       <c r="C7" s="51" t="inlineStr">
         <is>
-          <t>Sensex Gains 308 Points, Nifty Reclaims 23,000 as IT and Pharma Stocks Lead Recovery</t>
+          <t>Indian Shares Snap Two-Month Losing Streak, Nifty And Sensex Gain In October</t>
         </is>
       </c>
       <c r="D7" s="51" t="inlineStr">
         <is>
-          <t>The Indian Awaaz</t>
-        </is>
-      </c>
-      <c r="E7" s="81" t="n">
-        <v>0.649</v>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="E7" s="80" t="n">
+        <v>0.361</v>
       </c>
       <c r="F7" s="51" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G7" s="82" t="inlineStr">
+      <c r="G7" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -10615,33 +10563,33 @@
     <row r="8">
       <c r="A8" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>SYRMA</t>
         </is>
       </c>
       <c r="B8" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 16:01</t>
+          <t>2026-10-30 13:51</t>
         </is>
       </c>
       <c r="C8" s="51" t="inlineStr">
         <is>
-          <t>Indian Shares Snap Two-Month Losing Streak, Nifty And Sensex Gain In October</t>
+          <t>Syrma SGS Q2 results: Profit nearly doubles to ₹117 crore, revenue jumps 74%</t>
         </is>
       </c>
       <c r="D8" s="51" t="inlineStr">
         <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="E8" s="81" t="n">
-        <v>0.361</v>
+          <t>CNBC TV18</t>
+        </is>
+      </c>
+      <c r="E8" s="80" t="n">
+        <v>0.66</v>
       </c>
       <c r="F8" s="51" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G8" s="82" t="inlineStr">
+      <c r="G8" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -10650,33 +10598,33 @@
     <row r="9">
       <c r="A9" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>AETHER</t>
         </is>
       </c>
       <c r="B9" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 15:13</t>
+          <t>2026-10-30 12:34</t>
         </is>
       </c>
       <c r="C9" s="51" t="inlineStr">
         <is>
-          <t>Sensex Gains 308 Points, Nifty Closes Above 23,000 as IT and Pharma Stocks Lead Rally</t>
+          <t>Aether Industries (NSE:AETHER): What Do Aether Industries’ September-Quarter Results Show?</t>
         </is>
       </c>
       <c r="D9" s="51" t="inlineStr">
         <is>
-          <t>INDIA New England News</t>
-        </is>
-      </c>
-      <c r="E9" s="81" t="n">
-        <v>0.8070000000000001</v>
+          <t>Kalkine India</t>
+        </is>
+      </c>
+      <c r="E9" s="80" t="n">
+        <v>0</v>
       </c>
       <c r="F9" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G9" s="82" t="inlineStr">
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G9" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -10690,20 +10638,20 @@
       </c>
       <c r="B10" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 13:51</t>
+          <t>2026-10-30 11:14</t>
         </is>
       </c>
       <c r="C10" s="51" t="inlineStr">
         <is>
-          <t>Syrma SGS Q2 results: Profit nearly doubles to ₹117 crore, revenue jumps 74%</t>
+          <t>Diwali 2026 Top Stocks To Buy: Apollo Hospitals, GE Vernova, TARIL, TD Power, Jindal Steel, others; top 10 picks, target</t>
         </is>
       </c>
       <c r="D10" s="51" t="inlineStr">
         <is>
-          <t>CNBC TV18</t>
-        </is>
-      </c>
-      <c r="E10" s="81" t="n">
+          <t>Livemint</t>
+        </is>
+      </c>
+      <c r="E10" s="80" t="n">
         <v>0.66</v>
       </c>
       <c r="F10" s="51" t="inlineStr">
@@ -10711,7 +10659,7 @@
           <t>Positive</t>
         </is>
       </c>
-      <c r="G10" s="82" t="inlineStr">
+      <c r="G10" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -10720,33 +10668,33 @@
     <row r="11">
       <c r="A11" s="51" t="inlineStr">
         <is>
-          <t>AETHER</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B11" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 12:34</t>
+          <t>2026-10-30 10:56</t>
         </is>
       </c>
       <c r="C11" s="51" t="inlineStr">
         <is>
-          <t>Aether Industries (NSE:AETHER): What Do Aether Industries’ September-Quarter Results Show?</t>
+          <t>Market wrap: Shriram Finance, Nestle India, Trent, InterGlobe top gainers and losers on Nifty and Sensex</t>
         </is>
       </c>
       <c r="D11" s="51" t="inlineStr">
         <is>
-          <t>Kalkine India</t>
-        </is>
-      </c>
-      <c r="E11" s="81" t="n">
-        <v>0</v>
+          <t>The Economic Times</t>
+        </is>
+      </c>
+      <c r="E11" s="80" t="n">
+        <v>0.026</v>
       </c>
       <c r="F11" s="51" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="G11" s="82" t="inlineStr">
+      <c r="G11" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -10760,28 +10708,28 @@
       </c>
       <c r="B12" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 12:12</t>
+          <t>2026-10-30 10:53</t>
         </is>
       </c>
       <c r="C12" s="51" t="inlineStr">
         <is>
-          <t>Stock markets rise for 2nd session; Sensex gains 300 points on buying in IT stocks</t>
+          <t>Sensex, Nifty Rise; IT &amp; Pharma Lift Markets as Midcaps Slide</t>
         </is>
       </c>
       <c r="D12" s="51" t="inlineStr">
         <is>
-          <t>The Tribune</t>
-        </is>
-      </c>
-      <c r="E12" s="81" t="n">
-        <v>0.382</v>
+          <t>HDFC Sky</t>
+        </is>
+      </c>
+      <c r="E12" s="80" t="n">
+        <v>0.402</v>
       </c>
       <c r="F12" s="51" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G12" s="82" t="inlineStr">
+      <c r="G12" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -10795,28 +10743,28 @@
       </c>
       <c r="B13" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 12:05</t>
+          <t>2026-10-30 10:35</t>
         </is>
       </c>
       <c r="C13" s="51" t="inlineStr">
         <is>
-          <t>Rupee gains 33 paise as dollar weakens, Sensex and Nifty end higher</t>
+          <t>Sensex rises 308 points, Nifty above 23,000 even as broader markets crash. Will D-Street bulls extend reco</t>
         </is>
       </c>
       <c r="D13" s="51" t="inlineStr">
         <is>
-          <t>The Times of India</t>
-        </is>
-      </c>
-      <c r="E13" s="81" t="n">
-        <v>0.459</v>
+          <t>The Economic Times</t>
+        </is>
+      </c>
+      <c r="E13" s="80" t="n">
+        <v>-0.103</v>
       </c>
       <c r="F13" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G13" s="82" t="inlineStr">
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G13" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -10830,28 +10778,28 @@
       </c>
       <c r="B14" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 11:43</t>
+          <t>2026-10-30 10:31</t>
         </is>
       </c>
       <c r="C14" s="51" t="inlineStr">
         <is>
-          <t>Sensex, Nifty End Higher as IT and Pharma Stocks Lead Gains; Broader Markets Remain Weak</t>
+          <t>Sensex, Nifty extend gains for 2nd day: IT stocks lead rally, broader market underperforms</t>
         </is>
       </c>
       <c r="D14" s="51" t="inlineStr">
         <is>
-          <t>Business News This Week</t>
-        </is>
-      </c>
-      <c r="E14" s="81" t="n">
-        <v>0.402</v>
+          <t>IndiaIPO</t>
+        </is>
+      </c>
+      <c r="E14" s="80" t="n">
+        <v>0.84</v>
       </c>
       <c r="F14" s="51" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G14" s="82" t="inlineStr">
+      <c r="G14" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -10865,28 +10813,28 @@
       </c>
       <c r="B15" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 11:26</t>
+          <t>2026-10-30 10:28</t>
         </is>
       </c>
       <c r="C15" s="51" t="inlineStr">
         <is>
-          <t>Share Market Today: Nifty 50, Bank Nifty | Oct 30, 2026</t>
+          <t>Sensex Today Ends 308 Points Higher | Nifty Above 22,300 | Vedanta Oil and Gas Up 8%</t>
         </is>
       </c>
       <c r="D15" s="51" t="inlineStr">
         <is>
-          <t>Liquide Blog</t>
-        </is>
-      </c>
-      <c r="E15" s="81" t="n">
-        <v>0.66</v>
+          <t>Equitymaster</t>
+        </is>
+      </c>
+      <c r="E15" s="80" t="n">
+        <v>0.402</v>
       </c>
       <c r="F15" s="51" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G15" s="82" t="inlineStr">
+      <c r="G15" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -10900,28 +10848,28 @@
       </c>
       <c r="B16" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 11:25</t>
+          <t>2026-10-30 10:26</t>
         </is>
       </c>
       <c r="C16" s="51" t="inlineStr">
         <is>
-          <t>Stock market today: Sensex, Nifty extend gains for second day as IT, pharma stocks lead rally</t>
+          <t>Sensex, Nifty close with gain of 0.5% as IT, pharma stocks rally; weak broader market limits gains</t>
         </is>
       </c>
       <c r="D16" s="51" t="inlineStr">
         <is>
-          <t>IBTimes India</t>
-        </is>
-      </c>
-      <c r="E16" s="81" t="n">
-        <v>0.84</v>
+          <t>ChiniMandi</t>
+        </is>
+      </c>
+      <c r="E16" s="80" t="n">
+        <v>0.796</v>
       </c>
       <c r="F16" s="51" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G16" s="82" t="inlineStr">
+      <c r="G16" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -10935,28 +10883,28 @@
       </c>
       <c r="B17" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 11:24</t>
+          <t>2026-10-30 10:03</t>
         </is>
       </c>
       <c r="C17" s="51" t="inlineStr">
         <is>
-          <t>Green Energy Stocks Decline Despite Sensex Gaining 0.4% On October 30</t>
+          <t>Sensex ends 308 points higher, Nifty above 23,000; Trent up 5%</t>
         </is>
       </c>
       <c r="D17" s="51" t="inlineStr">
         <is>
-          <t>SolarQuarter</t>
-        </is>
-      </c>
-      <c r="E17" s="81" t="n">
-        <v>-0.428</v>
+          <t>India Today</t>
+        </is>
+      </c>
+      <c r="E17" s="80" t="n">
+        <v>0.402</v>
       </c>
       <c r="F17" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G17" s="82" t="inlineStr">
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G17" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -10970,28 +10918,28 @@
       </c>
       <c r="B18" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 11:17</t>
+          <t>2026-10-30 09:52</t>
         </is>
       </c>
       <c r="C18" s="51" t="inlineStr">
         <is>
-          <t>Markets rally for 2nd day amid buying in IT firms, earnings-driven demand in Trent</t>
+          <t>Market Wrap: Sensex Gains 308 Points, Nifty 50 Ends Above 23,000; Trent, IndiGo, Infosys Lead</t>
         </is>
       </c>
       <c r="D18" s="51" t="inlineStr">
         <is>
-          <t>OrissaPOST</t>
-        </is>
-      </c>
-      <c r="E18" s="81" t="n">
-        <v>0.361</v>
+          <t>NDTV Profit</t>
+        </is>
+      </c>
+      <c r="E18" s="80" t="n">
+        <v>0.649</v>
       </c>
       <c r="F18" s="51" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G18" s="82" t="inlineStr">
+      <c r="G18" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -11000,33 +10948,33 @@
     <row r="19">
       <c r="A19" s="51" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>CPPLUS</t>
         </is>
       </c>
       <c r="B19" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 11:14</t>
+          <t>2026-10-30 08:44</t>
         </is>
       </c>
       <c r="C19" s="51" t="inlineStr">
         <is>
-          <t>Diwali 2026 Top Stocks To Buy: Apollo Hospitals, GE Vernova, TARIL, TD Power, Jindal Steel, others; top 10 picks, target</t>
+          <t>Aditya Infotech CPPLUS ESOP Allotment 48,100 Shares Oct 2026</t>
         </is>
       </c>
       <c r="D19" s="51" t="inlineStr">
         <is>
-          <t>Livemint</t>
-        </is>
-      </c>
-      <c r="E19" s="81" t="n">
-        <v>0.66</v>
+          <t>Kalkine India</t>
+        </is>
+      </c>
+      <c r="E19" s="80" t="n">
+        <v>0</v>
       </c>
       <c r="F19" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G19" s="82" t="inlineStr">
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G19" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -11035,33 +10983,33 @@
     <row r="20">
       <c r="A20" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>AETHER</t>
         </is>
       </c>
       <c r="B20" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 11:07</t>
+          <t>2026-10-30 08:35</t>
         </is>
       </c>
       <c r="C20" s="51" t="inlineStr">
         <is>
-          <t>Indian Equities Rally on IT Sector Strength, Trent Earnings</t>
+          <t>Aether Industries reports robust Q2 FY27 financial performance with ₹3,472M in operating revenue</t>
         </is>
       </c>
       <c r="D20" s="51" t="inlineStr">
         <is>
-          <t>Rediff</t>
-        </is>
-      </c>
-      <c r="E20" s="81" t="n">
-        <v>0.735</v>
+          <t>Business Upturn</t>
+        </is>
+      </c>
+      <c r="E20" s="80" t="n">
+        <v>0.421</v>
       </c>
       <c r="F20" s="51" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G20" s="82" t="inlineStr">
+      <c r="G20" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -11075,28 +11023,28 @@
       </c>
       <c r="B21" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 11:00</t>
+          <t>2026-10-30 08:02</t>
         </is>
       </c>
       <c r="C21" s="51" t="inlineStr">
         <is>
-          <t>Sensex Rises Over 300 Points, Nifty Closes Above 23,050; IT, Pharma Stocks Lead Market Gains</t>
+          <t>Sensex zooms 1,200 pts in 2 days, Nifty tops 23K: Why are bulls in charge?</t>
         </is>
       </c>
       <c r="D21" s="51" t="inlineStr">
         <is>
-          <t>Times Now</t>
-        </is>
-      </c>
-      <c r="E21" s="81" t="n">
-        <v>0.649</v>
+          <t>Business Standard</t>
+        </is>
+      </c>
+      <c r="E21" s="80" t="n">
+        <v>0.718</v>
       </c>
       <c r="F21" s="51" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G21" s="82" t="inlineStr">
+      <c r="G21" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -11110,28 +11058,28 @@
       </c>
       <c r="B22" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 10:59</t>
+          <t>2026-10-30 06:40</t>
         </is>
       </c>
       <c r="C22" s="51" t="inlineStr">
         <is>
-          <t>Sensex and Nifty Gain Amid Mixed Sector Performance; Large Caps Lead Market Rally</t>
+          <t>Passive funds could buy up to Rs 36,500 crore upon Jio Platforms' entry into Nifty, Sensex</t>
         </is>
       </c>
       <c r="D22" s="51" t="inlineStr">
         <is>
-          <t>MarketsMojo</t>
-        </is>
-      </c>
-      <c r="E22" s="81" t="n">
-        <v>0.796</v>
+          <t>Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="E22" s="80" t="n">
+        <v>0.6909999999999999</v>
       </c>
       <c r="F22" s="51" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G22" s="82" t="inlineStr">
+      <c r="G22" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -11140,33 +11088,33 @@
     <row r="23">
       <c r="A23" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>AETHER</t>
         </is>
       </c>
       <c r="B23" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 10:56</t>
+          <t>2026-10-30 06:37</t>
         </is>
       </c>
       <c r="C23" s="51" t="inlineStr">
         <is>
-          <t>Market wrap: Shriram Finance, Nestle India, Trent, InterGlobe top gainers and losers on Nifty and Sensex</t>
+          <t>AETHER Share Price Today - Aether Industries on NSE/BSE</t>
         </is>
       </c>
       <c r="D23" s="51" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
-        </is>
-      </c>
-      <c r="E23" s="81" t="n">
-        <v>0.026</v>
+          <t>scanx.trade</t>
+        </is>
+      </c>
+      <c r="E23" s="80" t="n">
+        <v>0</v>
       </c>
       <c r="F23" s="51" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="G23" s="82" t="inlineStr">
+      <c r="G23" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -11175,33 +11123,33 @@
     <row r="24">
       <c r="A24" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>AETHER</t>
         </is>
       </c>
       <c r="B24" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 10:53</t>
+          <t>2026-10-30 06:31</t>
         </is>
       </c>
       <c r="C24" s="51" t="inlineStr">
         <is>
-          <t>Sensex, Nifty Rise; IT &amp; Pharma Lift Markets as Midcaps Slide</t>
+          <t>Aether Industries Q2 FY27 Results: Revenue, EBITDA and PAT</t>
         </is>
       </c>
       <c r="D24" s="51" t="inlineStr">
         <is>
-          <t>HDFC Sky</t>
-        </is>
-      </c>
-      <c r="E24" s="81" t="n">
-        <v>0.402</v>
+          <t>Kalkine India</t>
+        </is>
+      </c>
+      <c r="E24" s="80" t="n">
+        <v>0</v>
       </c>
       <c r="F24" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G24" s="82" t="inlineStr">
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G24" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -11215,28 +11163,28 @@
       </c>
       <c r="B25" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 10:36</t>
+          <t>2026-10-30 05:36</t>
         </is>
       </c>
       <c r="C25" s="51" t="inlineStr">
         <is>
-          <t>Closing Bell: Sensex Gains 300 Points, Nifty Reclaims 23,000 Mark as IT Stocks a Lead Rally</t>
+          <t>Sensex, Nifty turn lower; broader markets crash as oil tops $116/barrel. What lies ahead?</t>
         </is>
       </c>
       <c r="D25" s="51" t="inlineStr">
         <is>
-          <t>Dalal Street Investment Journal</t>
-        </is>
-      </c>
-      <c r="E25" s="81" t="n">
-        <v>0.8070000000000001</v>
+          <t>The Economic Times</t>
+        </is>
+      </c>
+      <c r="E25" s="80" t="n">
+        <v>-0.34</v>
       </c>
       <c r="F25" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G25" s="82" t="inlineStr">
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G25" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -11250,28 +11198,28 @@
       </c>
       <c r="B26" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 10:35</t>
+          <t>2026-10-30 05:13</t>
         </is>
       </c>
       <c r="C26" s="51" t="inlineStr">
         <is>
-          <t>Sensex rises 308 points, Nifty above 23,000 even as broader markets crash. Will D-Street bulls extend reco</t>
+          <t>Sensex, Nifty Open Volatile; India VIX Rises, Crude Above $116</t>
         </is>
       </c>
       <c r="D26" s="51" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
-        </is>
-      </c>
-      <c r="E26" s="81" t="n">
-        <v>-0.103</v>
+          <t>HDFC Sky</t>
+        </is>
+      </c>
+      <c r="E26" s="80" t="n">
+        <v>-0.25</v>
       </c>
       <c r="F26" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G26" s="82" t="inlineStr">
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G26" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -11285,28 +11233,28 @@
       </c>
       <c r="B27" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 10:31</t>
+          <t>2026-10-30 05:07</t>
         </is>
       </c>
       <c r="C27" s="51" t="inlineStr">
         <is>
-          <t>Sensex, Nifty extend gains for 2nd day: IT stocks lead rally, broader market underperforms</t>
+          <t>Sensex, Nifty trade flat as IT gains counter crude oil concerns</t>
         </is>
       </c>
       <c r="D27" s="51" t="inlineStr">
         <is>
-          <t>IndiaIPO</t>
-        </is>
-      </c>
-      <c r="E27" s="81" t="n">
-        <v>0.84</v>
+          <t>India Today</t>
+        </is>
+      </c>
+      <c r="E27" s="80" t="n">
+        <v>0.153</v>
       </c>
       <c r="F27" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G27" s="82" t="inlineStr">
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G27" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -11320,28 +11268,28 @@
       </c>
       <c r="B28" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 10:31</t>
+          <t>2026-10-30 05:01</t>
         </is>
       </c>
       <c r="C28" s="51" t="inlineStr">
         <is>
-          <t>Sensex, Nifty extend recovery; what's driving this upmove? -</t>
+          <t>Sensex Today Trades Flat | Nifty Below 22,950 | BSE Telecommunication Down 1.7%</t>
         </is>
       </c>
       <c r="D28" s="51" t="inlineStr">
         <is>
-          <t>IndiaIPO</t>
-        </is>
-      </c>
-      <c r="E28" s="81" t="n">
-        <v>0.527</v>
+          <t>Equitymaster</t>
+        </is>
+      </c>
+      <c r="E28" s="80" t="n">
+        <v>0.402</v>
       </c>
       <c r="F28" s="51" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G28" s="82" t="inlineStr">
+      <c r="G28" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -11355,28 +11303,28 @@
       </c>
       <c r="B29" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 10:30</t>
+          <t>2026-10-30 04:58</t>
         </is>
       </c>
       <c r="C29" s="51" t="inlineStr">
         <is>
-          <t>Markets reverse last week's losses; Nifty crosses 23,000, pharma jumps 7% weekly</t>
+          <t>Sensex, Nifty Rally 2nd Day on IT Buying, Trent Earnings</t>
         </is>
       </c>
       <c r="D29" s="51" t="inlineStr">
         <is>
-          <t>NewsDrum</t>
-        </is>
-      </c>
-      <c r="E29" s="81" t="n">
-        <v>0.44</v>
+          <t>Rediff MoneyWiz</t>
+        </is>
+      </c>
+      <c r="E29" s="80" t="n">
+        <v>0.6909999999999999</v>
       </c>
       <c r="F29" s="51" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G29" s="82" t="inlineStr">
+      <c r="G29" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -11390,28 +11338,28 @@
       </c>
       <c r="B30" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 10:28</t>
+          <t>2026-10-30 04:57</t>
         </is>
       </c>
       <c r="C30" s="51" t="inlineStr">
         <is>
-          <t>Sensex Today Ends 308 Points Higher | Nifty Above 22,300 | Vedanta Oil and Gas Up 8%</t>
+          <t>Stock Markets Today: Sensex, Nifty Up on Gains in IT Stocks</t>
         </is>
       </c>
       <c r="D30" s="51" t="inlineStr">
         <is>
-          <t>Equitymaster</t>
-        </is>
-      </c>
-      <c r="E30" s="81" t="n">
-        <v>0.402</v>
+          <t>Rediff</t>
+        </is>
+      </c>
+      <c r="E30" s="80" t="n">
+        <v>0.649</v>
       </c>
       <c r="F30" s="51" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G30" s="82" t="inlineStr">
+      <c r="G30" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -11425,28 +11373,28 @@
       </c>
       <c r="B31" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 10:26</t>
+          <t>2026-10-30 04:25</t>
         </is>
       </c>
       <c r="C31" s="51" t="inlineStr">
         <is>
-          <t>Sensex, Nifty close with gain of 0.5% as IT, pharma stocks rally; weak broader market limits gains</t>
+          <t>Sensex, Nifty open marginally higher amid rising crude prices, weak global cues</t>
         </is>
       </c>
       <c r="D31" s="51" t="inlineStr">
         <is>
-          <t>ChiniMandi</t>
-        </is>
-      </c>
-      <c r="E31" s="81" t="n">
-        <v>0.796</v>
+          <t>bfsi.economictimes.indiatimes.com</t>
+        </is>
+      </c>
+      <c r="E31" s="80" t="n">
+        <v>-0.5570000000000001</v>
       </c>
       <c r="F31" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G31" s="82" t="inlineStr">
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G31" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -11455,33 +11403,33 @@
     <row r="32">
       <c r="A32" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>SYRMA</t>
         </is>
       </c>
       <c r="B32" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 10:21</t>
+          <t>2026-10-30 04:16</t>
         </is>
       </c>
       <c r="C32" s="51" t="inlineStr">
         <is>
-          <t>Taking Stock: Nifty reclaims 23,000, Sensex gains 308 points led by IT, pharma stocks</t>
+          <t>SYRMA Stock Price and Chart — NSE:SYRMA</t>
         </is>
       </c>
       <c r="D32" s="51" t="inlineStr">
         <is>
-          <t>Moneycontrol.com</t>
-        </is>
-      </c>
-      <c r="E32" s="81" t="n">
-        <v>0.649</v>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="E32" s="80" t="n">
+        <v>0</v>
       </c>
       <c r="F32" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G32" s="82" t="inlineStr">
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G32" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -11495,28 +11443,28 @@
       </c>
       <c r="B33" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 10:05</t>
+          <t>2026-10-30 03:59</t>
         </is>
       </c>
       <c r="C33" s="51" t="inlineStr">
         <is>
-          <t>Closing Bell: Sensex rises 308 points, Nifty tops 23,000; IT, pharma stocks lead recovery</t>
+          <t>Coal India falls 3% post Q2 results but brokerages upbeat on PSU stock</t>
         </is>
       </c>
       <c r="D33" s="51" t="inlineStr">
         <is>
-          <t>Zee Business</t>
-        </is>
-      </c>
-      <c r="E33" s="81" t="n">
-        <v>0.718</v>
+          <t>Business Standard</t>
+        </is>
+      </c>
+      <c r="E33" s="80" t="n">
+        <v>-0.202</v>
       </c>
       <c r="F33" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G33" s="82" t="inlineStr">
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G33" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -11530,20 +11478,20 @@
       </c>
       <c r="B34" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 10:03</t>
+          <t>2026-10-30 03:50</t>
         </is>
       </c>
       <c r="C34" s="51" t="inlineStr">
         <is>
-          <t>Sensex ends 308 points higher, Nifty above 23,000; Trent up 5%</t>
+          <t>Stock Market Today: Sensex edges higher, Nifty opens above 22,950</t>
         </is>
       </c>
       <c r="D34" s="51" t="inlineStr">
         <is>
-          <t>India Today</t>
-        </is>
-      </c>
-      <c r="E34" s="81" t="n">
+          <t>Zee Business</t>
+        </is>
+      </c>
+      <c r="E34" s="80" t="n">
         <v>0.402</v>
       </c>
       <c r="F34" s="51" t="inlineStr">
@@ -11551,7 +11499,7 @@
           <t>Positive</t>
         </is>
       </c>
-      <c r="G34" s="82" t="inlineStr">
+      <c r="G34" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -11565,28 +11513,28 @@
       </c>
       <c r="B35" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 09:52</t>
+          <t>2026-10-30 03:34</t>
         </is>
       </c>
       <c r="C35" s="51" t="inlineStr">
         <is>
-          <t>Market Wrap: Sensex Gains 308 Points, Nifty 50 Ends Above 23,000; Trent, IndiGo, Infosys Lead</t>
+          <t>Sensex, Nifty may gain 5-8% if external headwinds recede: Baldev Prakash</t>
         </is>
       </c>
       <c r="D35" s="51" t="inlineStr">
         <is>
-          <t>NDTV Profit</t>
-        </is>
-      </c>
-      <c r="E35" s="81" t="n">
-        <v>0.649</v>
+          <t>Business Standard</t>
+        </is>
+      </c>
+      <c r="E35" s="80" t="n">
+        <v>0.625</v>
       </c>
       <c r="F35" s="51" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G35" s="82" t="inlineStr">
+      <c r="G35" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -11600,28 +11548,28 @@
       </c>
       <c r="B36" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 08:59</t>
+          <t>2026-10-30 03:00</t>
         </is>
       </c>
       <c r="C36" s="51" t="inlineStr">
         <is>
-          <t>Sensex Rises 298 Points, Nifty 50 Crosses 23,000 as IT Stocks Lead Gains</t>
+          <t>Stock market outlook: Crude oil prices to FPI inflows - 8 triggers that could reverse trend in Sensex, Nifty 50</t>
         </is>
       </c>
       <c r="D36" s="51" t="inlineStr">
         <is>
-          <t>Dalal Street Investment Journal</t>
-        </is>
-      </c>
-      <c r="E36" s="81" t="n">
-        <v>0.649</v>
+          <t>Livemint</t>
+        </is>
+      </c>
+      <c r="E36" s="80" t="n">
+        <v>-0.25</v>
       </c>
       <c r="F36" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G36" s="82" t="inlineStr">
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G36" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -11630,33 +11578,33 @@
     <row r="37">
       <c r="A37" s="51" t="inlineStr">
         <is>
-          <t>CPPLUS</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B37" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 08:44</t>
+          <t>2026-10-30 02:41</t>
         </is>
       </c>
       <c r="C37" s="51" t="inlineStr">
         <is>
-          <t>Aditya Infotech CPPLUS ESOP Allotment 48,100 Shares Oct 2026</t>
+          <t>GIFT Nifty down, signals muted start for Sensex, Nifty; Asian markets plunge on AI spending worries, oil...</t>
         </is>
       </c>
       <c r="D37" s="51" t="inlineStr">
         <is>
-          <t>Kalkine India</t>
-        </is>
-      </c>
-      <c r="E37" s="81" t="n">
-        <v>0</v>
+          <t>Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="E37" s="80" t="n">
+        <v>0.408</v>
       </c>
       <c r="F37" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G37" s="82" t="inlineStr">
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G37" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -11665,33 +11613,33 @@
     <row r="38">
       <c r="A38" s="51" t="inlineStr">
         <is>
-          <t>AETHER</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B38" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 08:35</t>
+          <t>2026-10-30 02:31</t>
         </is>
       </c>
       <c r="C38" s="51" t="inlineStr">
         <is>
-          <t>Aether Industries reports robust Q2 FY27 financial performance with ₹3,472M in operating revenue</t>
+          <t>Stock Market Today LIVE: GIFT Nifty signals quiet start; Brent crude at $111</t>
         </is>
       </c>
       <c r="D38" s="51" t="inlineStr">
         <is>
-          <t>Business Upturn</t>
-        </is>
-      </c>
-      <c r="E38" s="81" t="n">
-        <v>0.421</v>
+          <t>IndiaIPO</t>
+        </is>
+      </c>
+      <c r="E38" s="80" t="n">
+        <v>0.389</v>
       </c>
       <c r="F38" s="51" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G38" s="82" t="inlineStr">
+      <c r="G38" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -11705,12 +11653,12 @@
       </c>
       <c r="B39" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 08:02</t>
+          <t>2026-10-30 02:26</t>
         </is>
       </c>
       <c r="C39" s="51" t="inlineStr">
         <is>
-          <t>Sensex zooms 1,200 pts in 2 days, Nifty tops 23K: Why are bulls in charge?</t>
+          <t>Can Sensex, Nifty extend rally on Friday? Here's what market analysts say</t>
         </is>
       </c>
       <c r="D39" s="51" t="inlineStr">
@@ -11718,15 +11666,15 @@
           <t>Business Standard</t>
         </is>
       </c>
-      <c r="E39" s="81" t="n">
-        <v>0.718</v>
+      <c r="E39" s="80" t="n">
+        <v>0.751</v>
       </c>
       <c r="F39" s="51" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G39" s="82" t="inlineStr">
+      <c r="G39" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -11740,28 +11688,28 @@
       </c>
       <c r="B40" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 07:52</t>
+          <t>2026-10-30 01:44</t>
         </is>
       </c>
       <c r="C40" s="51" t="inlineStr">
         <is>
-          <t>IndiGo, Trent, Vedanta Power among buzzing stocks as SENSEX gains over 500 pts; NIFTY trades above 23K</t>
+          <t>Stock Market Today: Gift Nifty, Tech Stocks Selloff To Binance Hack; Five Key Factors For Sensex, Nifty 50 On Oct 30</t>
         </is>
       </c>
       <c r="D40" s="51" t="inlineStr">
         <is>
-          <t>Upstox</t>
-        </is>
-      </c>
-      <c r="E40" s="81" t="n">
-        <v>0.721</v>
+          <t>NDTV Profit</t>
+        </is>
+      </c>
+      <c r="E40" s="80" t="n">
+        <v>0.8070000000000001</v>
       </c>
       <c r="F40" s="51" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G40" s="82" t="inlineStr">
+      <c r="G40" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -11775,28 +11723,28 @@
       </c>
       <c r="B41" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 07:31</t>
+          <t>2026-10-30 01:14</t>
         </is>
       </c>
       <c r="C41" s="51" t="inlineStr">
         <is>
-          <t>Why Stock Market Is Rallying? Nifty Reclaims 23,100, Sensex Surges 500 Points; Three Reasons Why</t>
+          <t>Stock market outlook today, 30 Oct: Sensex, Nifty prediction - DJIA, S&amp;P, NASDAQ, GIFT Nifty, Kospi, Nikkei, Taiwan cues</t>
         </is>
       </c>
       <c r="D41" s="51" t="inlineStr">
         <is>
-          <t>NDTV Profit</t>
-        </is>
-      </c>
-      <c r="E41" s="81" t="n">
-        <v>0.71</v>
+          <t>Livemint</t>
+        </is>
+      </c>
+      <c r="E41" s="80" t="n">
+        <v>0.842</v>
       </c>
       <c r="F41" s="51" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G41" s="82" t="inlineStr">
+      <c r="G41" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -11805,33 +11753,33 @@
     <row r="42">
       <c r="A42" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>AETHER</t>
         </is>
       </c>
       <c r="B42" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 06:40</t>
+          <t>2026-10-30 00:10</t>
         </is>
       </c>
       <c r="C42" s="51" t="inlineStr">
         <is>
-          <t>Passive funds could buy up to Rs 36,500 crore upon Jio Platforms' entry into Nifty, Sensex</t>
+          <t>Ather Energy Share Price Today, Ather Energy Stock Price Live NSE/BSE Updates | The Economic Times</t>
         </is>
       </c>
       <c r="D42" s="51" t="inlineStr">
         <is>
-          <t>Moneycontrol.com</t>
-        </is>
-      </c>
-      <c r="E42" s="81" t="n">
-        <v>0.6909999999999999</v>
+          <t>The Economic Times</t>
+        </is>
+      </c>
+      <c r="E42" s="80" t="n">
+        <v>0.494</v>
       </c>
       <c r="F42" s="51" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G42" s="82" t="inlineStr">
+      <c r="G42" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -11845,12 +11793,12 @@
       </c>
       <c r="B43" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 06:37</t>
+          <t>2026-10-29 18:01</t>
         </is>
       </c>
       <c r="C43" s="51" t="inlineStr">
         <is>
-          <t>AETHER Share Price Today - Aether Industries on NSE/BSE</t>
+          <t>NAVINFLUOR Share Price Today - Navin Fluorine International on NSE/BSE</t>
         </is>
       </c>
       <c r="D43" s="51" t="inlineStr">
@@ -11858,7 +11806,7 @@
           <t>scanx.trade</t>
         </is>
       </c>
-      <c r="E43" s="81" t="n">
+      <c r="E43" s="80" t="n">
         <v>0</v>
       </c>
       <c r="F43" s="51" t="inlineStr">
@@ -11866,7 +11814,7 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="G43" s="82" t="inlineStr">
+      <c r="G43" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -11875,33 +11823,33 @@
     <row r="44">
       <c r="A44" s="51" t="inlineStr">
         <is>
-          <t>AETHER</t>
+          <t>SYRMA</t>
         </is>
       </c>
       <c r="B44" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 06:35</t>
+          <t>2026-10-29 17:53</t>
         </is>
       </c>
       <c r="C44" s="51" t="inlineStr">
         <is>
-          <t>Aether Industries Q2 FY27: Net profit rises 26% to ₹68 crore as revenue climbs 24% to ₹347 crore</t>
+          <t>ZF Commercial Vehicle Control Systems India Share Price, Stock Price - NSE/BSE Live</t>
         </is>
       </c>
       <c r="D44" s="51" t="inlineStr">
         <is>
-          <t>Business Upturn</t>
-        </is>
-      </c>
-      <c r="E44" s="81" t="n">
-        <v>0.612</v>
+          <t>NDTV Profit</t>
+        </is>
+      </c>
+      <c r="E44" s="80" t="n">
+        <v>0</v>
       </c>
       <c r="F44" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G44" s="82" t="inlineStr">
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G44" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -11910,17 +11858,17 @@
     <row r="45">
       <c r="A45" s="51" t="inlineStr">
         <is>
-          <t>AETHER</t>
+          <t>AEROFLEX</t>
         </is>
       </c>
       <c r="B45" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 06:31</t>
+          <t>2026-10-29 15:28</t>
         </is>
       </c>
       <c r="C45" s="51" t="inlineStr">
         <is>
-          <t>Aether Industries Q2 FY27 Results: Revenue, EBITDA and PAT</t>
+          <t>Aeroflex Industries (NSE:AEROFLEX) Q2 FY27 Results and Hyd-Air Amalgamation</t>
         </is>
       </c>
       <c r="D45" s="51" t="inlineStr">
@@ -11928,7 +11876,7 @@
           <t>Kalkine India</t>
         </is>
       </c>
-      <c r="E45" s="81" t="n">
+      <c r="E45" s="80" t="n">
         <v>0</v>
       </c>
       <c r="F45" s="51" t="inlineStr">
@@ -11936,7 +11884,7 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="G45" s="82" t="inlineStr">
+      <c r="G45" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -11950,28 +11898,28 @@
       </c>
       <c r="B46" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 06:14</t>
+          <t>2026-10-29 14:36</t>
         </is>
       </c>
       <c r="C46" s="51" t="inlineStr">
         <is>
-          <t>Sensex Today Live: Sensex, Nifty Trade Higher; Trent, IndiGo Gain, Coal India Shares Fall</t>
+          <t>Benchmarks rise over 1% on positive Q2 earnings, easing crude prices</t>
         </is>
       </c>
       <c r="D46" s="51" t="inlineStr">
         <is>
-          <t>The Sunday Guardian</t>
-        </is>
-      </c>
-      <c r="E46" s="81" t="n">
-        <v>0.402</v>
+          <t>Business Standard</t>
+        </is>
+      </c>
+      <c r="E46" s="80" t="n">
+        <v>0.226</v>
       </c>
       <c r="F46" s="51" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G46" s="82" t="inlineStr">
+      <c r="G46" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -11980,33 +11928,33 @@
     <row r="47">
       <c r="A47" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>AETHER</t>
         </is>
       </c>
       <c r="B47" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 05:55</t>
+          <t>2026-10-29 14:27</t>
         </is>
       </c>
       <c r="C47" s="51" t="inlineStr">
         <is>
-          <t>Sensex, Nifty open flat as crude oil prices remain elevated; IT stocks gain</t>
+          <t>GUJALKALI Share Price Today - Gujarat Alkalies &amp; Chemicals on NSE/BSE</t>
         </is>
       </c>
       <c r="D47" s="51" t="inlineStr">
         <is>
-          <t>Telangana Today</t>
-        </is>
-      </c>
-      <c r="E47" s="81" t="n">
-        <v>0.103</v>
+          <t>scanx.trade</t>
+        </is>
+      </c>
+      <c r="E47" s="80" t="n">
+        <v>0</v>
       </c>
       <c r="F47" s="51" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="G47" s="82" t="inlineStr">
+      <c r="G47" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -12020,28 +11968,28 @@
       </c>
       <c r="B48" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 05:50</t>
+          <t>2026-10-29 13:03</t>
         </is>
       </c>
       <c r="C48" s="51" t="inlineStr">
         <is>
-          <t>BSE IT index set to report 2nd sharpest monthly rally in over two decades</t>
+          <t>Why markets rallied: Sensex jumps over 900 points, Nifty gains 1 per cent; 5 key reasons</t>
         </is>
       </c>
       <c r="D48" s="51" t="inlineStr">
         <is>
-          <t>Business Standard</t>
-        </is>
-      </c>
-      <c r="E48" s="81" t="n">
-        <v>0.459</v>
+          <t>The Times of India</t>
+        </is>
+      </c>
+      <c r="E48" s="80" t="n">
+        <v>0.8070000000000001</v>
       </c>
       <c r="F48" s="51" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G48" s="82" t="inlineStr">
+      <c r="G48" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -12055,28 +12003,28 @@
       </c>
       <c r="B49" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 05:36</t>
+          <t>2026-10-29 12:44</t>
         </is>
       </c>
       <c r="C49" s="51" t="inlineStr">
         <is>
-          <t>Sensex, Nifty turn lower; broader markets crash as oil tops $116/barrel. What lies ahead?</t>
+          <t>Indian Equities Rally: Sensex Jumps 905 Pts, Nifty Tops 22,900</t>
         </is>
       </c>
       <c r="D49" s="51" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
-        </is>
-      </c>
-      <c r="E49" s="81" t="n">
-        <v>-0.34</v>
+          <t>Rediff</t>
+        </is>
+      </c>
+      <c r="E49" s="80" t="n">
+        <v>0.9</v>
       </c>
       <c r="F49" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G49" s="82" t="inlineStr">
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G49" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -12085,33 +12033,33 @@
     <row r="50">
       <c r="A50" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>SYRMA</t>
         </is>
       </c>
       <c r="B50" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 05:14</t>
+          <t>2026-10-29 11:52</t>
         </is>
       </c>
       <c r="C50" s="51" t="inlineStr">
         <is>
-          <t>Breakout stocks: Adani Ports, Nykaa, Saregama on radar; analyst tells why</t>
+          <t>Syrma SGS Tech - Technical picks for Diwali! 10 stocks PL Capital is bullish on this festive season. See full list</t>
         </is>
       </c>
       <c r="D50" s="51" t="inlineStr">
         <is>
-          <t>Business Standard</t>
-        </is>
-      </c>
-      <c r="E50" s="81" t="n">
-        <v>0.421</v>
+          <t>The Economic Times</t>
+        </is>
+      </c>
+      <c r="E50" s="80" t="n">
+        <v>0.771</v>
       </c>
       <c r="F50" s="51" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G50" s="82" t="inlineStr">
+      <c r="G50" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -12125,28 +12073,28 @@
       </c>
       <c r="B51" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 05:13</t>
+          <t>2026-10-29 10:59</t>
         </is>
       </c>
       <c r="C51" s="51" t="inlineStr">
         <is>
-          <t>Sensex, Nifty Open Volatile; India VIX Rises, Crude Above $116</t>
+          <t>Sensex Surges 905 Pts, Nifty Tops 22,900 on Banking, FMCG Boost</t>
         </is>
       </c>
       <c r="D51" s="51" t="inlineStr">
         <is>
-          <t>HDFC Sky</t>
-        </is>
-      </c>
-      <c r="E51" s="81" t="n">
-        <v>-0.25</v>
+          <t>Rediff MoneyWiz</t>
+        </is>
+      </c>
+      <c r="E51" s="80" t="n">
+        <v>0.898</v>
       </c>
       <c r="F51" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G51" s="82" t="inlineStr">
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G51" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -12160,28 +12108,28 @@
       </c>
       <c r="B52" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 05:07</t>
+          <t>2026-10-29 10:56</t>
         </is>
       </c>
       <c r="C52" s="51" t="inlineStr">
         <is>
-          <t>Sensex, Nifty trade flat as IT gains counter crude oil concerns</t>
+          <t>Sensex jumps 905 points, Nifty gains 238 points as markets stage strong rebound</t>
         </is>
       </c>
       <c r="D52" s="51" t="inlineStr">
         <is>
-          <t>India Today</t>
-        </is>
-      </c>
-      <c r="E52" s="81" t="n">
-        <v>0.153</v>
+          <t>Telegraph India</t>
+        </is>
+      </c>
+      <c r="E52" s="80" t="n">
+        <v>0.872</v>
       </c>
       <c r="F52" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G52" s="82" t="inlineStr">
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G52" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -12195,28 +12143,28 @@
       </c>
       <c r="B53" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 05:01</t>
+          <t>2026-10-29 10:42</t>
         </is>
       </c>
       <c r="C53" s="51" t="inlineStr">
         <is>
-          <t>Sensex Today Trades Flat | Nifty Below 22,950 | BSE Telecommunication Down 1.7%</t>
+          <t>Indian markets stage a strong rebound, recouping yesterday’s losses as Sensex surges over 1%</t>
         </is>
       </c>
       <c r="D53" s="51" t="inlineStr">
         <is>
-          <t>Equitymaster</t>
-        </is>
-      </c>
-      <c r="E53" s="81" t="n">
-        <v>0.402</v>
+          <t>The New Indian Express</t>
+        </is>
+      </c>
+      <c r="E53" s="80" t="n">
+        <v>0.459</v>
       </c>
       <c r="F53" s="51" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G53" s="82" t="inlineStr">
+      <c r="G53" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -12230,20 +12178,20 @@
       </c>
       <c r="B54" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 04:58</t>
+          <t>2026-10-29 10:39</t>
         </is>
       </c>
       <c r="C54" s="51" t="inlineStr">
         <is>
-          <t>Sensex, Nifty Rally 2nd Day on IT Buying, Trent Earnings</t>
+          <t>Sensex Today Rallies 905 Points | Nifty Above 22,900 | 5 Reasons Why Indian Stock Markets Are Rising</t>
         </is>
       </c>
       <c r="D54" s="51" t="inlineStr">
         <is>
-          <t>Rediff MoneyWiz</t>
-        </is>
-      </c>
-      <c r="E54" s="81" t="n">
+          <t>Equitymaster</t>
+        </is>
+      </c>
+      <c r="E54" s="80" t="n">
         <v>0.6909999999999999</v>
       </c>
       <c r="F54" s="51" t="inlineStr">
@@ -12251,7 +12199,7 @@
           <t>Positive</t>
         </is>
       </c>
-      <c r="G54" s="82" t="inlineStr">
+      <c r="G54" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -12260,33 +12208,33 @@
     <row r="55">
       <c r="A55" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>AEROFLEX</t>
         </is>
       </c>
       <c r="B55" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 04:57</t>
+          <t>2026-10-29 08:32</t>
         </is>
       </c>
       <c r="C55" s="51" t="inlineStr">
         <is>
-          <t>Stock Markets Today: Sensex, Nifty Up on Gains in IT Stocks</t>
+          <t>OnEMI Technology rises 5% after Q2FY27 profit doubles to ₹125 crore</t>
         </is>
       </c>
       <c r="D55" s="51" t="inlineStr">
         <is>
-          <t>Rediff</t>
-        </is>
-      </c>
-      <c r="E55" s="81" t="n">
-        <v>0.649</v>
+          <t>Business Standard</t>
+        </is>
+      </c>
+      <c r="E55" s="80" t="n">
+        <v>0.34</v>
       </c>
       <c r="F55" s="51" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G55" s="82" t="inlineStr">
+      <c r="G55" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -12300,28 +12248,28 @@
       </c>
       <c r="B56" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 04:50</t>
+          <t>2026-10-29 08:03</t>
         </is>
       </c>
       <c r="C56" s="51" t="inlineStr">
         <is>
-          <t>Stock market today: Sensex opens higher, Trent rallies; Suzlon tumbles 8%</t>
+          <t>Stock Market Today: Why are Sensex, Nifty rising? 3 key factors</t>
         </is>
       </c>
       <c r="D56" s="51" t="inlineStr">
         <is>
-          <t>NewsDrum</t>
-        </is>
-      </c>
-      <c r="E56" s="81" t="n">
-        <v>-0.052</v>
+          <t>Zee Business</t>
+        </is>
+      </c>
+      <c r="E56" s="80" t="n">
+        <v>0.402</v>
       </c>
       <c r="F56" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G56" s="82" t="inlineStr">
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G56" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -12330,33 +12278,33 @@
     <row r="57">
       <c r="A57" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>AEROFLEX</t>
         </is>
       </c>
       <c r="B57" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 04:47</t>
+          <t>2026-10-29 07:48</t>
         </is>
       </c>
       <c r="C57" s="51" t="inlineStr">
         <is>
-          <t>Stock Market Today: Sensex Gains in Early Trade as Investors Focus on Earnings and Global Cues</t>
+          <t>Aeroflex Industries shares rally over 17% on strong Q2 earnings show; material costs jump 120% YoY</t>
         </is>
       </c>
       <c r="D57" s="51" t="inlineStr">
         <is>
-          <t>Business News This Week</t>
-        </is>
-      </c>
-      <c r="E57" s="81" t="n">
-        <v>0.382</v>
+          <t>Upstox</t>
+        </is>
+      </c>
+      <c r="E57" s="80" t="n">
+        <v>0.8129999999999999</v>
       </c>
       <c r="F57" s="51" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G57" s="82" t="inlineStr">
+      <c r="G57" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -12370,28 +12318,28 @@
       </c>
       <c r="B58" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 04:26</t>
+          <t>2026-10-29 07:09</t>
         </is>
       </c>
       <c r="C58" s="51" t="inlineStr">
         <is>
-          <t>BLS Polymers IPO allotment today; GMP at 45% — check status on BSE, NSE and registrar</t>
+          <t>Three Reasons Why Markets Are Rising: Sensex Jumps Over 800 Points, Nifty Crosses 22,900</t>
         </is>
       </c>
       <c r="D58" s="51" t="inlineStr">
         <is>
-          <t>Moneycontrol.com</t>
-        </is>
-      </c>
-      <c r="E58" s="81" t="n">
-        <v>0</v>
+          <t>NDTV Profit</t>
+        </is>
+      </c>
+      <c r="E58" s="80" t="n">
+        <v>0.6909999999999999</v>
       </c>
       <c r="F58" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G58" s="82" t="inlineStr">
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G58" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -12405,28 +12353,28 @@
       </c>
       <c r="B59" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 04:19</t>
+          <t>2026-10-29 07:05</t>
         </is>
       </c>
       <c r="C59" s="51" t="inlineStr">
         <is>
-          <t>Sensex, Nifty open marginally higher amid rising crude prices, weak global cues</t>
+          <t>Sensex, Nifty Rise as Reliance Industries and IT Stocks Gain; Crude Oil Limits Upside</t>
         </is>
       </c>
       <c r="D59" s="51" t="inlineStr">
         <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="E59" s="81" t="n">
-        <v>-0.5570000000000001</v>
+          <t>India Infoline</t>
+        </is>
+      </c>
+      <c r="E59" s="80" t="n">
+        <v>0.494</v>
       </c>
       <c r="F59" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G59" s="82" t="inlineStr">
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G59" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -12435,33 +12383,33 @@
     <row r="60">
       <c r="A60" s="51" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B60" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 04:16</t>
+          <t>2026-10-29 07:00</t>
         </is>
       </c>
       <c r="C60" s="51" t="inlineStr">
         <is>
-          <t>SYRMA Stock Price and Chart — NSE:SYRMA</t>
+          <t>Sensex Today | Stock Market Live: Sensex jumps 600 pts, Nifty at 22,850; Adani Ports surges 4%, FMCG</t>
         </is>
       </c>
       <c r="D60" s="51" t="inlineStr">
         <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="E60" s="81" t="n">
-        <v>0</v>
+          <t>IndiaIPO</t>
+        </is>
+      </c>
+      <c r="E60" s="80" t="n">
+        <v>0.836</v>
       </c>
       <c r="F60" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G60" s="82" t="inlineStr">
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G60" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -12470,33 +12418,33 @@
     <row r="61">
       <c r="A61" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>SBC</t>
         </is>
       </c>
       <c r="B61" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 04:14</t>
+          <t>2026-10-29 06:51</t>
         </is>
       </c>
       <c r="C61" s="51" t="inlineStr">
         <is>
-          <t>SFC Environmental Technologies IPO allotment: How to check status online on NSE, BSE, MUFG Intime India; listing date, time here</t>
+          <t>20 Best Stocks Under 50 Rs In India October 2026 For High Returns</t>
         </is>
       </c>
       <c r="D61" s="51" t="inlineStr">
         <is>
-          <t>Upstox</t>
-        </is>
-      </c>
-      <c r="E61" s="81" t="n">
-        <v>0</v>
+          <t>Samco</t>
+        </is>
+      </c>
+      <c r="E61" s="80" t="n">
+        <v>0.718</v>
       </c>
       <c r="F61" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G61" s="82" t="inlineStr">
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G61" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -12505,33 +12453,33 @@
     <row r="62">
       <c r="A62" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>AEROFLEX</t>
         </is>
       </c>
       <c r="B62" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 04:11</t>
+          <t>2026-10-29 06:44</t>
         </is>
       </c>
       <c r="C62" s="51" t="inlineStr">
         <is>
-          <t>Sensex, Nifty open flat amid high crude oil prices, jump in IT stocks | Business News</t>
+          <t>NSE: Growth levers, easing regulatory pressure underpin Jefferies' buy call</t>
         </is>
       </c>
       <c r="D62" s="51" t="inlineStr">
         <is>
-          <t>Hindustan Times</t>
-        </is>
-      </c>
-      <c r="E62" s="81" t="n">
-        <v>0.382</v>
+          <t>Business Standard</t>
+        </is>
+      </c>
+      <c r="E62" s="80" t="n">
+        <v>0.542</v>
       </c>
       <c r="F62" s="51" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G62" s="82" t="inlineStr">
+      <c r="G62" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -12540,33 +12488,33 @@
     <row r="63">
       <c r="A63" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>AEROFLEX</t>
         </is>
       </c>
       <c r="B63" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 03:59</t>
+          <t>2026-10-29 06:42</t>
         </is>
       </c>
       <c r="C63" s="51" t="inlineStr">
         <is>
-          <t>Coal India falls 3% post Q2 results but brokerages upbeat on PSU stock</t>
+          <t>Aeroflex Industries (NSE:AEROFLEX): Did It Publish Q2 FY27 Financial Results?</t>
         </is>
       </c>
       <c r="D63" s="51" t="inlineStr">
         <is>
-          <t>Business Standard</t>
-        </is>
-      </c>
-      <c r="E63" s="81" t="n">
-        <v>-0.202</v>
+          <t>Kalkine India</t>
+        </is>
+      </c>
+      <c r="E63" s="80" t="n">
+        <v>0</v>
       </c>
       <c r="F63" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G63" s="82" t="inlineStr">
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G63" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -12575,33 +12523,33 @@
     <row r="64">
       <c r="A64" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>AEROFLEX</t>
         </is>
       </c>
       <c r="B64" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 03:51</t>
+          <t>2026-10-29 06:38</t>
         </is>
       </c>
       <c r="C64" s="51" t="inlineStr">
         <is>
-          <t>Stock Market Today (October 30): Sensex, Nifty Open Flat; Rising Oil Prices, Geopolitical Tensions In Focus</t>
+          <t>Aeroflex zooms 18% on huge volume, over 31 mn shares change hands</t>
         </is>
       </c>
       <c r="D64" s="51" t="inlineStr">
         <is>
-          <t>Times Now</t>
-        </is>
-      </c>
-      <c r="E64" s="81" t="n">
-        <v>0</v>
+          <t>Business Standard</t>
+        </is>
+      </c>
+      <c r="E64" s="80" t="n">
+        <v>0.318</v>
       </c>
       <c r="F64" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G64" s="82" t="inlineStr">
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G64" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -12615,28 +12563,28 @@
       </c>
       <c r="B65" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 03:50</t>
+          <t>2026-10-29 05:31</t>
         </is>
       </c>
       <c r="C65" s="51" t="inlineStr">
         <is>
-          <t>Stock Market Today: Sensex edges higher, Nifty opens above 22,950</t>
+          <t>Why is market rallying today? Sensex jumps 900 points, Nifty above 22,900. 6 key factors behind Rs 5 lakh</t>
         </is>
       </c>
       <c r="D65" s="51" t="inlineStr">
         <is>
-          <t>Zee Business</t>
-        </is>
-      </c>
-      <c r="E65" s="81" t="n">
-        <v>0.402</v>
+          <t>The Economic Times</t>
+        </is>
+      </c>
+      <c r="E65" s="80" t="n">
+        <v>0.6909999999999999</v>
       </c>
       <c r="F65" s="51" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G65" s="82" t="inlineStr">
+      <c r="G65" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -12645,33 +12593,33 @@
     <row r="66">
       <c r="A66" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>AEROFLEX</t>
         </is>
       </c>
       <c r="B66" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 03:34</t>
+          <t>2026-10-29 05:29</t>
         </is>
       </c>
       <c r="C66" s="51" t="inlineStr">
         <is>
-          <t>Sensex, Nifty may gain 5-8% if external headwinds recede: Baldev Prakash</t>
+          <t>Aeroflex Industries Share Price Surges 14% After Q2: Profit Jumps 157%, Why the Depreciation Change Matters</t>
         </is>
       </c>
       <c r="D66" s="51" t="inlineStr">
         <is>
-          <t>Business Standard</t>
-        </is>
-      </c>
-      <c r="E66" s="81" t="n">
-        <v>0.625</v>
+          <t>Univest</t>
+        </is>
+      </c>
+      <c r="E66" s="80" t="n">
+        <v>0.827</v>
       </c>
       <c r="F66" s="51" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G66" s="82" t="inlineStr">
+      <c r="G66" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -12685,28 +12633,28 @@
       </c>
       <c r="B67" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 03:00</t>
+          <t>2026-10-29 05:18</t>
         </is>
       </c>
       <c r="C67" s="51" t="inlineStr">
         <is>
-          <t>Stock market outlook: Crude oil prices to FPI inflows - 8 triggers that could reverse trend in Sensex, Nifty 50</t>
+          <t>Stock Markets Today: Sensex, Nifty rise in early trade on buying in RIL FII inflows</t>
         </is>
       </c>
       <c r="D67" s="51" t="inlineStr">
         <is>
-          <t>Livemint</t>
-        </is>
-      </c>
-      <c r="E67" s="81" t="n">
-        <v>-0.25</v>
+          <t>Rediff</t>
+        </is>
+      </c>
+      <c r="E67" s="80" t="n">
+        <v>0.402</v>
       </c>
       <c r="F67" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G67" s="82" t="inlineStr">
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G67" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -12720,28 +12668,28 @@
       </c>
       <c r="B68" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 02:41</t>
+          <t>2026-10-29 05:17</t>
         </is>
       </c>
       <c r="C68" s="51" t="inlineStr">
         <is>
-          <t>GIFT Nifty down, signals muted start for Sensex, Nifty; Asian markets plunge on AI spending worries, oil...</t>
+          <t>Sensex, Nifty rise in early trade on Reliance buying, foreign inflows</t>
         </is>
       </c>
       <c r="D68" s="51" t="inlineStr">
         <is>
-          <t>Moneycontrol.com</t>
-        </is>
-      </c>
-      <c r="E68" s="81" t="n">
-        <v>0.408</v>
+          <t>The Hindu</t>
+        </is>
+      </c>
+      <c r="E68" s="80" t="n">
+        <v>0.402</v>
       </c>
       <c r="F68" s="51" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G68" s="82" t="inlineStr">
+      <c r="G68" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -12755,28 +12703,28 @@
       </c>
       <c r="B69" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 02:35</t>
+          <t>2026-10-29 04:44</t>
         </is>
       </c>
       <c r="C69" s="51" t="inlineStr">
         <is>
-          <t>Indian shares seen opening higher after earnings-led rebound; higher oil to cap gains</t>
+          <t>Sensex, Nifty Open Higher as Fed Holds Rates; Oil Dips Slightly</t>
         </is>
       </c>
       <c r="D69" s="51" t="inlineStr">
         <is>
-          <t>Livemint</t>
-        </is>
-      </c>
-      <c r="E69" s="81" t="n">
-        <v>0.382</v>
+          <t>HDFC Sky</t>
+        </is>
+      </c>
+      <c r="E69" s="80" t="n">
+        <v>0.402</v>
       </c>
       <c r="F69" s="51" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G69" s="82" t="inlineStr">
+      <c r="G69" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -12790,20 +12738,20 @@
       </c>
       <c r="B70" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 02:21</t>
+          <t>2026-10-29 04:35</t>
         </is>
       </c>
       <c r="C70" s="51" t="inlineStr">
         <is>
-          <t>Stock Market Today, October 30: RIL, Jio Q2 results, Japan rate decision, forex reserves - 10 key triggers for Sensex, Nifty</t>
+          <t>Sensex Today Trades Higher | Nifty Above 22,700 | Jio Platforms Up 4%</t>
         </is>
       </c>
       <c r="D70" s="51" t="inlineStr">
         <is>
-          <t>ET Now</t>
-        </is>
-      </c>
-      <c r="E70" s="81" t="n">
+          <t>Equitymaster</t>
+        </is>
+      </c>
+      <c r="E70" s="80" t="n">
         <v>0.402</v>
       </c>
       <c r="F70" s="51" t="inlineStr">
@@ -12811,7 +12759,7 @@
           <t>Positive</t>
         </is>
       </c>
-      <c r="G70" s="82" t="inlineStr">
+      <c r="G70" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -12820,33 +12768,33 @@
     <row r="71">
       <c r="A71" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>AEROFLEX</t>
         </is>
       </c>
       <c r="B71" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 01:44</t>
+          <t>2026-10-29 04:11</t>
         </is>
       </c>
       <c r="C71" s="51" t="inlineStr">
         <is>
-          <t>Stock Market Today: Gift Nifty, Tech Stocks Selloff To Binance Hack; Five Key Factors For Sensex, Nifty 50 On Oct 30</t>
+          <t>Why are Aeroflex Industries shares rallying over 12% today? Here's what's driving the stock</t>
         </is>
       </c>
       <c r="D71" s="51" t="inlineStr">
         <is>
-          <t>NDTV Profit</t>
-        </is>
-      </c>
-      <c r="E71" s="81" t="n">
-        <v>0.8070000000000001</v>
+          <t>Business Upturn</t>
+        </is>
+      </c>
+      <c r="E71" s="80" t="n">
+        <v>0</v>
       </c>
       <c r="F71" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G71" s="82" t="inlineStr">
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G71" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -12855,33 +12803,33 @@
     <row r="72">
       <c r="A72" s="51" t="inlineStr">
         <is>
-          <t>THANGAMAYL</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B72" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 01:17</t>
+          <t>2026-10-29 03:51</t>
         </is>
       </c>
       <c r="C72" s="51" t="inlineStr">
         <is>
-          <t>Thangamayil FY26 Net Profit Jumps 196% to ₹35,165 Lakhs</t>
+          <t>Stock Market Highlights: Sensex Jumps 905 Points, Nifty 50 Ends Above 22,900; Adani Stocks, Kotak Bank Lead Rally</t>
         </is>
       </c>
       <c r="D72" s="51" t="inlineStr">
         <is>
-          <t>scanx.trade</t>
-        </is>
-      </c>
-      <c r="E72" s="81" t="n">
-        <v>0.66</v>
+          <t>NDTV Profit</t>
+        </is>
+      </c>
+      <c r="E72" s="80" t="n">
+        <v>0.827</v>
       </c>
       <c r="F72" s="51" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G72" s="82" t="inlineStr">
+      <c r="G72" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -12895,28 +12843,28 @@
       </c>
       <c r="B73" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 01:14</t>
+          <t>2026-10-29 03:50</t>
         </is>
       </c>
       <c r="C73" s="51" t="inlineStr">
         <is>
-          <t>Stock market outlook today, 30 Oct: Sensex, Nifty prediction - DJIA, S&amp;P, NASDAQ, GIFT Nifty, Kospi, Nikkei, Taiwan cues</t>
+          <t>Sensex, Nifty trade higher after US Fed holds rates; crude oil remains a concern</t>
         </is>
       </c>
       <c r="D73" s="51" t="inlineStr">
         <is>
-          <t>Livemint</t>
-        </is>
-      </c>
-      <c r="E73" s="81" t="n">
-        <v>0.842</v>
+          <t>India Today</t>
+        </is>
+      </c>
+      <c r="E73" s="80" t="n">
+        <v>-0.25</v>
       </c>
       <c r="F73" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G73" s="82" t="inlineStr">
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G73" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -12930,28 +12878,28 @@
       </c>
       <c r="B74" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 00:30</t>
+          <t>2026-10-29 02:36</t>
         </is>
       </c>
       <c r="C74" s="51" t="inlineStr">
         <is>
-          <t>eClerx Services Q2 FY27 Results | Birlasoft Q2 FY27 Results | Top Buzzing Stocks Today</t>
+          <t>Share Market Today LIVE, 29th Oct: GIFT Nifty signals gains; Fed holds rates, Brent at $114</t>
         </is>
       </c>
       <c r="D74" s="51" t="inlineStr">
         <is>
-          <t>Equitymaster</t>
-        </is>
-      </c>
-      <c r="E74" s="81" t="n">
-        <v>0.202</v>
+          <t>IndiaIPO</t>
+        </is>
+      </c>
+      <c r="E74" s="80" t="n">
+        <v>0.837</v>
       </c>
       <c r="F74" s="51" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G74" s="82" t="inlineStr">
+      <c r="G74" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -12965,28 +12913,28 @@
       </c>
       <c r="B75" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 00:23</t>
+          <t>2026-10-29 01:50</t>
         </is>
       </c>
       <c r="C75" s="51" t="inlineStr">
         <is>
-          <t>Advance-decline ratio hits 7-month low as market breadth weakens</t>
+          <t>US Fed Holds Rates, But Another Hike Looms: What It Means For Indian Stock Market</t>
         </is>
       </c>
       <c r="D75" s="51" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
-        </is>
-      </c>
-      <c r="E75" s="81" t="n">
-        <v>-0.612</v>
+          <t>NDTV Profit</t>
+        </is>
+      </c>
+      <c r="E75" s="80" t="n">
+        <v>-0.226</v>
       </c>
       <c r="F75" s="51" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G75" s="82" t="inlineStr">
+      <c r="G75" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -12995,33 +12943,33 @@
     <row r="76">
       <c r="A76" s="51" t="inlineStr">
         <is>
-          <t>AETHER</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B76" s="51" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10</t>
+          <t>2026-10-29 01:39</t>
         </is>
       </c>
       <c r="C76" s="51" t="inlineStr">
         <is>
-          <t>Ather Energy Share Price Today, Ather Energy Stock Price Live NSE/BSE Updates | The Economic Times</t>
+          <t>Stock Market Today: Gift Nifty, US Fed Policy To Oil Prices; Five Key Factors For Sensex, Nifty 50 On October 29</t>
         </is>
       </c>
       <c r="D76" s="51" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
-        </is>
-      </c>
-      <c r="E76" s="81" t="n">
-        <v>0.494</v>
+          <t>NDTV Profit</t>
+        </is>
+      </c>
+      <c r="E76" s="80" t="n">
+        <v>0.8070000000000001</v>
       </c>
       <c r="F76" s="51" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G76" s="82" t="inlineStr">
+      <c r="G76" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -13030,33 +12978,33 @@
     <row r="77">
       <c r="A77" s="51" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B77" s="51" t="inlineStr">
         <is>
-          <t>2026-10-29 17:53</t>
+          <t>2026-10-29 01:15</t>
         </is>
       </c>
       <c r="C77" s="51" t="inlineStr">
         <is>
-          <t>ZF Commercial Vehicle Control Systems India Share Price, Stock Price - NSE/BSE Live</t>
+          <t>Stock market outlook today, 29 Oct: Sensex, Nifty prediction - DJIA, S&amp;P, NASDAQ, GIFT Nifty, Kospi, Nikkei, Taiwan cues</t>
         </is>
       </c>
       <c r="D77" s="51" t="inlineStr">
         <is>
-          <t>NDTV Profit</t>
-        </is>
-      </c>
-      <c r="E77" s="81" t="n">
-        <v>0</v>
+          <t>Livemint</t>
+        </is>
+      </c>
+      <c r="E77" s="80" t="n">
+        <v>0.842</v>
       </c>
       <c r="F77" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G77" s="82" t="inlineStr">
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G77" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -13070,28 +13018,28 @@
       </c>
       <c r="B78" s="51" t="inlineStr">
         <is>
-          <t>2026-10-29 15:28</t>
+          <t>2026-10-29 01:01</t>
         </is>
       </c>
       <c r="C78" s="51" t="inlineStr">
         <is>
-          <t>Aeroflex Industries (NSE:AEROFLEX) Q2 FY27 Results and Hyd-Air Amalgamation</t>
+          <t>Stocks to Watch Today: Dr Reddys Labs, Fortis Healthcare, Titagarh Rail, Hero MotoCorp, RR Kabel, Meesho,...</t>
         </is>
       </c>
       <c r="D78" s="51" t="inlineStr">
         <is>
-          <t>Kalkine India</t>
-        </is>
-      </c>
-      <c r="E78" s="81" t="n">
-        <v>0</v>
+          <t>Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="E78" s="80" t="n">
+        <v>0.5570000000000001</v>
       </c>
       <c r="F78" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G78" s="82" t="inlineStr">
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G78" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -13105,28 +13053,28 @@
       </c>
       <c r="B79" s="51" t="inlineStr">
         <is>
-          <t>2026-10-29 14:36</t>
+          <t>2026-10-28 18:46</t>
         </is>
       </c>
       <c r="C79" s="51" t="inlineStr">
         <is>
-          <t>Benchmarks rise over 1% on positive Q2 earnings, easing crude prices</t>
+          <t>How can US Fed FOMC meeting outcome impact Indian stock market? Sensex, Nifty to rise? Experts decode</t>
         </is>
       </c>
       <c r="D79" s="51" t="inlineStr">
         <is>
-          <t>Business Standard</t>
-        </is>
-      </c>
-      <c r="E79" s="81" t="n">
-        <v>0.226</v>
+          <t>Livemint</t>
+        </is>
+      </c>
+      <c r="E79" s="80" t="n">
+        <v>0.47</v>
       </c>
       <c r="F79" s="51" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G79" s="82" t="inlineStr">
+      <c r="G79" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -13135,33 +13083,33 @@
     <row r="80">
       <c r="A80" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>RATNAVEER</t>
         </is>
       </c>
       <c r="B80" s="51" t="inlineStr">
         <is>
-          <t>2026-10-29 12:44</t>
+          <t>2026-10-28 13:42</t>
         </is>
       </c>
       <c r="C80" s="51" t="inlineStr">
         <is>
-          <t>Indian Equities Rally: Sensex Jumps 905 Pts, Nifty Tops 22,900</t>
+          <t>Ratnaveer Precision Engineering Q2 FY27 Earnings Call on 3 Nov</t>
         </is>
       </c>
       <c r="D80" s="51" t="inlineStr">
         <is>
-          <t>Rediff</t>
-        </is>
-      </c>
-      <c r="E80" s="81" t="n">
-        <v>0.9</v>
+          <t>Kalkine India</t>
+        </is>
+      </c>
+      <c r="E80" s="80" t="n">
+        <v>0</v>
       </c>
       <c r="F80" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G80" s="82" t="inlineStr">
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G80" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -13170,33 +13118,33 @@
     <row r="81">
       <c r="A81" s="51" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>AETHER</t>
         </is>
       </c>
       <c r="B81" s="51" t="inlineStr">
         <is>
-          <t>2026-10-29 11:52</t>
+          <t>2026-10-28 12:26</t>
         </is>
       </c>
       <c r="C81" s="51" t="inlineStr">
         <is>
-          <t>Syrma SGS Tech - Technical picks for Diwali! 10 stocks PL Capital is bullish on this festive season. See full list</t>
+          <t>SRF Share Price Today - SRF on NSE/BSE</t>
         </is>
       </c>
       <c r="D81" s="51" t="inlineStr">
         <is>
-          <t>The Economic Times</t>
-        </is>
-      </c>
-      <c r="E81" s="81" t="n">
-        <v>0.771</v>
+          <t>scanx.trade</t>
+        </is>
+      </c>
+      <c r="E81" s="80" t="n">
+        <v>0</v>
       </c>
       <c r="F81" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G81" s="82" t="inlineStr">
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G81" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -13210,28 +13158,28 @@
       </c>
       <c r="B82" s="51" t="inlineStr">
         <is>
-          <t>2026-10-29 11:41</t>
+          <t>2026-10-28 12:18</t>
         </is>
       </c>
       <c r="C82" s="51" t="inlineStr">
         <is>
-          <t>Share Market Today: Nifty 50, Bank Nifty | Oct 29, 2026</t>
+          <t>Indian markets end lower as IT weakness and crude oil concerns weigh on sentiment</t>
         </is>
       </c>
       <c r="D82" s="51" t="inlineStr">
         <is>
-          <t>Liquide Blog</t>
-        </is>
-      </c>
-      <c r="E82" s="81" t="n">
-        <v>0.66</v>
+          <t>The New Indian Express</t>
+        </is>
+      </c>
+      <c r="E82" s="80" t="n">
+        <v>-0.8070000000000001</v>
       </c>
       <c r="F82" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G82" s="82" t="inlineStr">
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G82" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -13245,28 +13193,28 @@
       </c>
       <c r="B83" s="51" t="inlineStr">
         <is>
-          <t>2026-10-29 10:56</t>
+          <t>2026-10-28 12:04</t>
         </is>
       </c>
       <c r="C83" s="51" t="inlineStr">
         <is>
-          <t>Sensex jumps 905 points, Nifty gains 238 points as markets stage strong rebound</t>
+          <t>Sensex, Nifty Slip as Crude Near $115; IT, O&amp;G Drag Markets</t>
         </is>
       </c>
       <c r="D83" s="51" t="inlineStr">
         <is>
-          <t>Telegraph India</t>
-        </is>
-      </c>
-      <c r="E83" s="81" t="n">
-        <v>0.872</v>
+          <t>HDFC Sky</t>
+        </is>
+      </c>
+      <c r="E83" s="80" t="n">
+        <v>-0.649</v>
       </c>
       <c r="F83" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G83" s="82" t="inlineStr">
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G83" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -13280,28 +13228,28 @@
       </c>
       <c r="B84" s="51" t="inlineStr">
         <is>
-          <t>2026-10-29 10:50</t>
+          <t>2026-10-28 11:30</t>
         </is>
       </c>
       <c r="C84" s="51" t="inlineStr">
         <is>
-          <t>Sensex, Nifty see sharp recovery; is the worst finally over?</t>
+          <t>Sensex ends in red on selling in IT stocks, rising crude oil prices</t>
         </is>
       </c>
       <c r="D84" s="51" t="inlineStr">
         <is>
-          <t>Business Today</t>
-        </is>
-      </c>
-      <c r="E84" s="81" t="n">
-        <v>-0.34</v>
+          <t>DD India</t>
+        </is>
+      </c>
+      <c r="E84" s="80" t="n">
+        <v>-0.572</v>
       </c>
       <c r="F84" s="51" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G84" s="82" t="inlineStr">
+      <c r="G84" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -13315,28 +13263,28 @@
       </c>
       <c r="B85" s="51" t="inlineStr">
         <is>
-          <t>2026-10-29 10:46</t>
+          <t>2026-10-28 10:43</t>
         </is>
       </c>
       <c r="C85" s="51" t="inlineStr">
         <is>
-          <t>Sensex Soars 905 Points; Nifty Near 22,940 as Markets Rebound</t>
+          <t>Sensex Today Ends 353 Points Lower | Nifty Below 22,700 | AWL Agri Business Down 6%</t>
         </is>
       </c>
       <c r="D85" s="51" t="inlineStr">
         <is>
-          <t>HDFC Sky</t>
-        </is>
-      </c>
-      <c r="E85" s="81" t="n">
-        <v>0.727</v>
+          <t>Equitymaster</t>
+        </is>
+      </c>
+      <c r="E85" s="80" t="n">
+        <v>0.226</v>
       </c>
       <c r="F85" s="51" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G85" s="82" t="inlineStr">
+      <c r="G85" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -13350,28 +13298,28 @@
       </c>
       <c r="B86" s="51" t="inlineStr">
         <is>
-          <t>2026-10-29 10:42</t>
+          <t>2026-10-28 10:40</t>
         </is>
       </c>
       <c r="C86" s="51" t="inlineStr">
         <is>
-          <t>Indian markets stage a strong rebound, recouping yesterday’s losses as Sensex surges over 1%</t>
+          <t>Sensex falls 353 points, Nifty below 22,700 as IT and oil stocks drag</t>
         </is>
       </c>
       <c r="D86" s="51" t="inlineStr">
         <is>
-          <t>The New Indian Express</t>
-        </is>
-      </c>
-      <c r="E86" s="81" t="n">
-        <v>0.459</v>
+          <t>India Today</t>
+        </is>
+      </c>
+      <c r="E86" s="80" t="n">
+        <v>-0.202</v>
       </c>
       <c r="F86" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G86" s="82" t="inlineStr">
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G86" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -13380,33 +13328,33 @@
     <row r="87">
       <c r="A87" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>SYRMA</t>
         </is>
       </c>
       <c r="B87" s="51" t="inlineStr">
         <is>
-          <t>2026-10-29 10:39</t>
+          <t>2026-10-28 07:00</t>
         </is>
       </c>
       <c r="C87" s="51" t="inlineStr">
         <is>
-          <t>Sensex Today Rallies 905 Points | Nifty Above 22,900 | 5 Reasons Why Indian Stock Markets Are Rising</t>
+          <t>Syrma SGS Technology (NSEI:SYRMA) Stock Forecast &amp; Analyst Predictions</t>
         </is>
       </c>
       <c r="D87" s="51" t="inlineStr">
         <is>
-          <t>Equitymaster</t>
-        </is>
-      </c>
-      <c r="E87" s="81" t="n">
-        <v>0.6909999999999999</v>
+          <t>Simply Wall St</t>
+        </is>
+      </c>
+      <c r="E87" s="80" t="n">
+        <v>0</v>
       </c>
       <c r="F87" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G87" s="82" t="inlineStr">
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G87" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -13415,33 +13363,33 @@
     <row r="88">
       <c r="A88" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>SYRMA</t>
         </is>
       </c>
       <c r="B88" s="51" t="inlineStr">
         <is>
-          <t>2026-10-29 10:11</t>
+          <t>2026-10-28 06:20</t>
         </is>
       </c>
       <c r="C88" s="51" t="inlineStr">
         <is>
-          <t>Taking Stock: Markets rebound sharply; Nifty above 22,900, Sensex jumps 905 pts as IT, FMCG, banking...</t>
+          <t>NSE adds six stocks to F&amp;O segment from today, October 28: Check full list</t>
         </is>
       </c>
       <c r="D88" s="51" t="inlineStr">
         <is>
-          <t>Moneycontrol.com</t>
-        </is>
-      </c>
-      <c r="E88" s="81" t="n">
-        <v>0.6909999999999999</v>
+          <t>Zee Business</t>
+        </is>
+      </c>
+      <c r="E88" s="80" t="n">
+        <v>0</v>
       </c>
       <c r="F88" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G88" s="82" t="inlineStr">
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G88" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -13455,28 +13403,28 @@
       </c>
       <c r="B89" s="51" t="inlineStr">
         <is>
-          <t>2026-10-29 08:33</t>
+          <t>2026-10-28 05:37</t>
         </is>
       </c>
       <c r="C89" s="51" t="inlineStr">
         <is>
-          <t>Sensex jumps over 900 points, Nifty inches above 22,950; Reliance, Jio, Adani stocks lead gains</t>
+          <t>Stock market crash today: Sensex plunges 995 points, Nifty sheds 1% ahead of Fed decision: Here's what spooked D-Street</t>
         </is>
       </c>
       <c r="D89" s="51" t="inlineStr">
         <is>
-          <t>Fortune India</t>
-        </is>
-      </c>
-      <c r="E89" s="81" t="n">
-        <v>0.8070000000000001</v>
+          <t>Livemint</t>
+        </is>
+      </c>
+      <c r="E89" s="80" t="n">
+        <v>-0.802</v>
       </c>
       <c r="F89" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G89" s="82" t="inlineStr">
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G89" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -13485,33 +13433,33 @@
     <row r="90">
       <c r="A90" s="51" t="inlineStr">
         <is>
-          <t>AEROFLEX</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B90" s="51" t="inlineStr">
         <is>
-          <t>2026-10-29 08:32</t>
+          <t>2026-10-28 05:36</t>
         </is>
       </c>
       <c r="C90" s="51" t="inlineStr">
         <is>
-          <t>OnEMI Technology rises 5% after Q2FY27 profit doubles to ₹125 crore</t>
+          <t>Sensex falls 500 points: 3 reasons why the stock market is down today</t>
         </is>
       </c>
       <c r="D90" s="51" t="inlineStr">
         <is>
-          <t>Business Standard</t>
-        </is>
-      </c>
-      <c r="E90" s="81" t="n">
-        <v>0.34</v>
+          <t>India Today</t>
+        </is>
+      </c>
+      <c r="E90" s="80" t="n">
+        <v>-0.382</v>
       </c>
       <c r="F90" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G90" s="82" t="inlineStr">
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G90" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -13520,33 +13468,33 @@
     <row r="91">
       <c r="A91" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>SYRMA</t>
         </is>
       </c>
       <c r="B91" s="51" t="inlineStr">
         <is>
-          <t>2026-10-29 08:03</t>
+          <t>2026-10-28 05:30</t>
         </is>
       </c>
       <c r="C91" s="51" t="inlineStr">
         <is>
-          <t>Stock Market Today: Why are Sensex, Nifty rising? 3 key factors</t>
+          <t>Syrma SGS Technology (SYRMA.NS) Jumps 3.67% to ₹1575.3, Approaches ₹1654.07 Resistance Zone - Time Weighted Price</t>
         </is>
       </c>
       <c r="D91" s="51" t="inlineStr">
         <is>
-          <t>Zee Business</t>
-        </is>
-      </c>
-      <c r="E91" s="81" t="n">
-        <v>0.402</v>
+          <t>https://www.siam.in/</t>
+        </is>
+      </c>
+      <c r="E91" s="80" t="n">
+        <v>0.459</v>
       </c>
       <c r="F91" s="51" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G91" s="82" t="inlineStr">
+      <c r="G91" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -13560,28 +13508,28 @@
       </c>
       <c r="B92" s="51" t="inlineStr">
         <is>
-          <t>2026-10-29 07:59</t>
+          <t>2026-10-28 05:26</t>
         </is>
       </c>
       <c r="C92" s="51" t="inlineStr">
         <is>
-          <t>SENSEX jumps over 500 pts, NIFTY above 22,800 in noon deals; Power Grid, Hyundai Motor, Jupiter Wagon among buzzing stocks</t>
+          <t>Why Is Stock Market Falling Today? 4 Key Reasons Behind Sensex, Nifty Crash</t>
         </is>
       </c>
       <c r="D92" s="51" t="inlineStr">
         <is>
-          <t>Upstox</t>
-        </is>
-      </c>
-      <c r="E92" s="81" t="n">
-        <v>0.753</v>
+          <t>NDTV</t>
+        </is>
+      </c>
+      <c r="E92" s="80" t="n">
+        <v>-0.402</v>
       </c>
       <c r="F92" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G92" s="82" t="inlineStr">
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G92" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -13590,33 +13538,33 @@
     <row r="93">
       <c r="A93" s="51" t="inlineStr">
         <is>
-          <t>AEROFLEX</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B93" s="51" t="inlineStr">
         <is>
-          <t>2026-10-29 07:48</t>
+          <t>2026-10-28 05:26</t>
         </is>
       </c>
       <c r="C93" s="51" t="inlineStr">
         <is>
-          <t>Aeroflex Industries shares rally over 17% on strong Q2 earnings show; material costs jump 120% YoY</t>
+          <t>Market fall explained: Sensex dives 995 points intraday, Nifty at 22,500</t>
         </is>
       </c>
       <c r="D93" s="51" t="inlineStr">
         <is>
-          <t>Upstox</t>
-        </is>
-      </c>
-      <c r="E93" s="81" t="n">
-        <v>0.8129999999999999</v>
+          <t>Business Standard</t>
+        </is>
+      </c>
+      <c r="E93" s="80" t="n">
+        <v>0.077</v>
       </c>
       <c r="F93" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G93" s="82" t="inlineStr">
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G93" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -13630,28 +13578,28 @@
       </c>
       <c r="B94" s="51" t="inlineStr">
         <is>
-          <t>2026-10-29 07:05</t>
+          <t>2026-10-28 04:56</t>
         </is>
       </c>
       <c r="C94" s="51" t="inlineStr">
         <is>
-          <t>Sensex, Nifty Rise as Reliance Industries and IT Stocks Gain; Crude Oil Limits Upside</t>
+          <t>Sensex Today Tanks 793 Points | Nifty Below 22,550 | Nifty IT Index Down 3.1%</t>
         </is>
       </c>
       <c r="D94" s="51" t="inlineStr">
         <is>
-          <t>India Infoline</t>
-        </is>
-      </c>
-      <c r="E94" s="81" t="n">
-        <v>0.494</v>
+          <t>Equitymaster</t>
+        </is>
+      </c>
+      <c r="E94" s="80" t="n">
+        <v>0.296</v>
       </c>
       <c r="F94" s="51" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G94" s="82" t="inlineStr">
+      <c r="G94" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -13660,33 +13608,33 @@
     <row r="95">
       <c r="A95" s="51" t="inlineStr">
         <is>
-          <t>SBC</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B95" s="51" t="inlineStr">
         <is>
-          <t>2026-10-29 06:51</t>
+          <t>2026-10-28 04:46</t>
         </is>
       </c>
       <c r="C95" s="51" t="inlineStr">
         <is>
-          <t>20 Best Stocks Under 50 Rs In India October 2026 For High Returns</t>
+          <t>Sensex falls nearly 700 points as rising crude prices, FPI outflows weigh on markets</t>
         </is>
       </c>
       <c r="D95" s="51" t="inlineStr">
         <is>
-          <t>Samco</t>
-        </is>
-      </c>
-      <c r="E95" s="81" t="n">
-        <v>0.718</v>
+          <t>DD India</t>
+        </is>
+      </c>
+      <c r="E95" s="80" t="n">
+        <v>-0.743</v>
       </c>
       <c r="F95" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G95" s="82" t="inlineStr">
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G95" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -13695,33 +13643,33 @@
     <row r="96">
       <c r="A96" s="51" t="inlineStr">
         <is>
-          <t>AEROFLEX</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B96" s="51" t="inlineStr">
         <is>
-          <t>2026-10-29 06:44</t>
+          <t>2026-10-28 04:35</t>
         </is>
       </c>
       <c r="C96" s="51" t="inlineStr">
         <is>
-          <t>NSE: Growth levers, easing regulatory pressure underpin Jefferies' buy call</t>
+          <t>Sensex sheds 691 points, Nifty falls below 22,600 on rising crude prices, FPI concerns</t>
         </is>
       </c>
       <c r="D96" s="51" t="inlineStr">
         <is>
-          <t>Business Standard</t>
-        </is>
-      </c>
-      <c r="E96" s="81" t="n">
-        <v>0.542</v>
+          <t>ChiniMandi</t>
+        </is>
+      </c>
+      <c r="E96" s="80" t="n">
+        <v>-0.735</v>
       </c>
       <c r="F96" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G96" s="82" t="inlineStr">
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G96" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -13730,33 +13678,33 @@
     <row r="97">
       <c r="A97" s="51" t="inlineStr">
         <is>
-          <t>AEROFLEX</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B97" s="51" t="inlineStr">
         <is>
-          <t>2026-10-29 06:42</t>
+          <t>2026-10-28 04:32</t>
         </is>
       </c>
       <c r="C97" s="51" t="inlineStr">
         <is>
-          <t>Aeroflex Industries (NSE:AEROFLEX): Did It Publish Q2 FY27 Financial Results?</t>
+          <t>Stock Markets Today: Sensex, Nifty Tumble as IT Stocks, Crude Prices Weigh</t>
         </is>
       </c>
       <c r="D97" s="51" t="inlineStr">
         <is>
-          <t>Kalkine India</t>
-        </is>
-      </c>
-      <c r="E97" s="81" t="n">
-        <v>0</v>
+          <t>Rediff</t>
+        </is>
+      </c>
+      <c r="E97" s="80" t="n">
+        <v>-0.25</v>
       </c>
       <c r="F97" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G97" s="82" t="inlineStr">
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G97" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -13765,33 +13713,33 @@
     <row r="98">
       <c r="A98" s="51" t="inlineStr">
         <is>
-          <t>AEROFLEX</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B98" s="51" t="inlineStr">
         <is>
-          <t>2026-10-29 06:38</t>
+          <t>2026-10-28 04:32</t>
         </is>
       </c>
       <c r="C98" s="51" t="inlineStr">
         <is>
-          <t>Aeroflex zooms 18% on huge volume, over 31 mn shares change hands</t>
+          <t>Sensex, Nifty Slide as Crude Near $116 and IT Stocks Tumble</t>
         </is>
       </c>
       <c r="D98" s="51" t="inlineStr">
         <is>
-          <t>Business Standard</t>
-        </is>
-      </c>
-      <c r="E98" s="81" t="n">
-        <v>0.318</v>
+          <t>HDFC Sky</t>
+        </is>
+      </c>
+      <c r="E98" s="80" t="n">
+        <v>-0.25</v>
       </c>
       <c r="F98" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G98" s="82" t="inlineStr">
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G98" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -13800,33 +13748,33 @@
     <row r="99">
       <c r="A99" s="51" t="inlineStr">
         <is>
-          <t>AEROFLEX</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B99" s="51" t="inlineStr">
         <is>
-          <t>2026-10-29 05:29</t>
+          <t>2026-10-28 04:25</t>
         </is>
       </c>
       <c r="C99" s="51" t="inlineStr">
         <is>
-          <t>Aeroflex Industries Share Price Surges 14% After Q2: Profit Jumps 157%, Why the Depreciation Change Matters</t>
+          <t>Why Is Stock Market Falling Today? Sensex Drops Over 800 Points, Nifty Slips Below 22,600; Key Reasons Explained</t>
         </is>
       </c>
       <c r="D99" s="51" t="inlineStr">
         <is>
-          <t>Univest</t>
-        </is>
-      </c>
-      <c r="E99" s="81" t="n">
-        <v>0.827</v>
+          <t>NDTV Profit</t>
+        </is>
+      </c>
+      <c r="E99" s="80" t="n">
+        <v>-0.077</v>
       </c>
       <c r="F99" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G99" s="82" t="inlineStr">
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G99" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -13840,28 +13788,28 @@
       </c>
       <c r="B100" s="51" t="inlineStr">
         <is>
-          <t>2026-10-29 05:25</t>
+          <t>2026-10-28 04:06</t>
         </is>
       </c>
       <c r="C100" s="51" t="inlineStr">
         <is>
-          <t>Why Is Share Market Rising Today? Know Key Reasons Behind Sensex, Nifty Rally On October 29</t>
+          <t>Why did market fall today? Sensex falls 353 points, Nifty closes below 22,700 despite Jio’s solid debut; 4</t>
         </is>
       </c>
       <c r="D100" s="51" t="inlineStr">
         <is>
-          <t>News18</t>
-        </is>
-      </c>
-      <c r="E100" s="81" t="n">
-        <v>0.6909999999999999</v>
+          <t>The Economic Times</t>
+        </is>
+      </c>
+      <c r="E100" s="80" t="n">
+        <v>-0.411</v>
       </c>
       <c r="F100" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G100" s="82" t="inlineStr">
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G100" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -13875,28 +13823,28 @@
       </c>
       <c r="B101" s="51" t="inlineStr">
         <is>
-          <t>2026-10-29 05:17</t>
+          <t>2026-10-28 03:49</t>
         </is>
       </c>
       <c r="C101" s="51" t="inlineStr">
         <is>
-          <t>Sensex, Nifty rise in early trade on Reliance buying, foreign inflows</t>
+          <t>Sensex, Nifty open in red dragged by fall in IT stocks; Infosys down 5%</t>
         </is>
       </c>
       <c r="D101" s="51" t="inlineStr">
         <is>
-          <t>The Hindu</t>
-        </is>
-      </c>
-      <c r="E101" s="81" t="n">
-        <v>0.402</v>
+          <t>India Today</t>
+        </is>
+      </c>
+      <c r="E101" s="80" t="n">
+        <v>0.026</v>
       </c>
       <c r="F101" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G101" s="82" t="inlineStr">
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G101" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -13910,28 +13858,28 @@
       </c>
       <c r="B102" s="51" t="inlineStr">
         <is>
-          <t>2026-10-29 04:58</t>
+          <t>2026-10-28 02:47</t>
         </is>
       </c>
       <c r="C102" s="51" t="inlineStr">
         <is>
-          <t>Sensex, Nifty Rise on Reliance Buying, Foreign Inflows</t>
+          <t>GIFT Nifty crashes over 220 pts, signals weak start for Sensex and Nifty despite global rally; US Fed in...</t>
         </is>
       </c>
       <c r="D102" s="51" t="inlineStr">
         <is>
-          <t>Rediff MoneyWiz</t>
-        </is>
-      </c>
-      <c r="E102" s="81" t="n">
-        <v>0.402</v>
+          <t>Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="E102" s="80" t="n">
+        <v>0.606</v>
       </c>
       <c r="F102" s="51" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G102" s="82" t="inlineStr">
+      <c r="G102" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -13945,28 +13893,28 @@
       </c>
       <c r="B103" s="51" t="inlineStr">
         <is>
-          <t>2026-10-29 04:44</t>
+          <t>2026-10-28 01:54</t>
         </is>
       </c>
       <c r="C103" s="51" t="inlineStr">
         <is>
-          <t>Sensex, Nifty Open Higher as Fed Holds Rates; Oil Dips Slightly</t>
+          <t>Stock Market Today: Gift Nifty, Jio IPO Listing To Nasdaq, Kospi Rally; Five Factors For Sensex, Nifty 50 On Oct 28</t>
         </is>
       </c>
       <c r="D103" s="51" t="inlineStr">
         <is>
-          <t>HDFC Sky</t>
-        </is>
-      </c>
-      <c r="E103" s="81" t="n">
-        <v>0.402</v>
+          <t>NDTV Profit</t>
+        </is>
+      </c>
+      <c r="E103" s="80" t="n">
+        <v>0.883</v>
       </c>
       <c r="F103" s="51" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G103" s="82" t="inlineStr">
+      <c r="G103" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -13980,28 +13928,28 @@
       </c>
       <c r="B104" s="51" t="inlineStr">
         <is>
-          <t>2026-10-29 04:35</t>
+          <t>2026-10-28 01:45</t>
         </is>
       </c>
       <c r="C104" s="51" t="inlineStr">
         <is>
-          <t>Sensex Today Trades Higher | Nifty Above 22,700 | Jio Platforms Up 4%</t>
+          <t>Stock market outlook for 28 Oct: Sensex, Nifty prediction - Jio Platforms IPO listing, GIFT Nifty, US and Asian markets</t>
         </is>
       </c>
       <c r="D104" s="51" t="inlineStr">
         <is>
-          <t>Equitymaster</t>
-        </is>
-      </c>
-      <c r="E104" s="81" t="n">
-        <v>0.402</v>
+          <t>Livemint</t>
+        </is>
+      </c>
+      <c r="E104" s="80" t="n">
+        <v>0.842</v>
       </c>
       <c r="F104" s="51" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G104" s="82" t="inlineStr">
+      <c r="G104" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -14015,28 +13963,28 @@
       </c>
       <c r="B105" s="51" t="inlineStr">
         <is>
-          <t>2026-10-29 03:51</t>
+          <t>2026-10-28 00:44</t>
         </is>
       </c>
       <c r="C105" s="51" t="inlineStr">
         <is>
-          <t>Stock Market Highlights: Sensex Jumps 905 Points, Nifty 50 Ends Above 22,900; Adani Stocks, Kotak Bank Lead Rally</t>
+          <t>Indian Stock Market News, Equity Market and Sensex Today in India</t>
         </is>
       </c>
       <c r="D105" s="51" t="inlineStr">
         <is>
-          <t>NDTV Profit</t>
-        </is>
-      </c>
-      <c r="E105" s="81" t="n">
-        <v>0.827</v>
+          <t>Equitymaster</t>
+        </is>
+      </c>
+      <c r="E105" s="80" t="n">
+        <v>0</v>
       </c>
       <c r="F105" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G105" s="82" t="inlineStr">
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G105" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -14050,28 +13998,28 @@
       </c>
       <c r="B106" s="51" t="inlineStr">
         <is>
-          <t>2026-10-29 03:50</t>
+          <t>2026-10-28 00:40</t>
         </is>
       </c>
       <c r="C106" s="51" t="inlineStr">
         <is>
-          <t>Sensex, Nifty trade higher after US Fed holds rates; crude oil remains a concern</t>
+          <t>Reading the Nifty 50 and Sensex: What the Two Headline Indices Tell You</t>
         </is>
       </c>
       <c r="D106" s="51" t="inlineStr">
         <is>
-          <t>India Today</t>
-        </is>
-      </c>
-      <c r="E106" s="81" t="n">
-        <v>-0.25</v>
+          <t>www.tmgm.com</t>
+        </is>
+      </c>
+      <c r="E106" s="80" t="n">
+        <v>0.402</v>
       </c>
       <c r="F106" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G106" s="82" t="inlineStr">
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G106" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -14085,28 +14033,28 @@
       </c>
       <c r="B107" s="51" t="inlineStr">
         <is>
-          <t>2026-10-29 01:15</t>
+          <t>2026-10-27 18:08</t>
         </is>
       </c>
       <c r="C107" s="51" t="inlineStr">
         <is>
-          <t>Stock market outlook today, 29 Oct: Sensex, Nifty prediction - DJIA, S&amp;P, NASDAQ, GIFT Nifty, Kospi, Nikkei, Taiwan cues</t>
+          <t>Markets end flat ahead of Fed decision; FPIs buy shares worth ₹4,240 crore</t>
         </is>
       </c>
       <c r="D107" s="51" t="inlineStr">
         <is>
-          <t>Livemint</t>
-        </is>
-      </c>
-      <c r="E107" s="81" t="n">
-        <v>0.842</v>
+          <t>Business Standard</t>
+        </is>
+      </c>
+      <c r="E107" s="80" t="n">
+        <v>0.477</v>
       </c>
       <c r="F107" s="51" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G107" s="82" t="inlineStr">
+      <c r="G107" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -14115,33 +14063,33 @@
     <row r="108">
       <c r="A108" s="51" t="inlineStr">
         <is>
-          <t>AEROFLEX</t>
+          <t>AETHER</t>
         </is>
       </c>
       <c r="B108" s="51" t="inlineStr">
         <is>
-          <t>2026-10-29 01:01</t>
+          <t>2026-10-27 12:08</t>
         </is>
       </c>
       <c r="C108" s="51" t="inlineStr">
         <is>
-          <t>Stocks to Watch Today: Dr Reddys Labs, Fortis Healthcare, Titagarh Rail, Hero MotoCorp, RR Kabel, Meesho,...</t>
+          <t>Ather Energy shares: 125% YTD returns! Experts give 'portfolio stock' tag after Q2 results 2026 | Target, stop-loss</t>
         </is>
       </c>
       <c r="D108" s="51" t="inlineStr">
         <is>
-          <t>Moneycontrol.com</t>
-        </is>
-      </c>
-      <c r="E108" s="81" t="n">
-        <v>0.5570000000000001</v>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="E108" s="80" t="n">
+        <v>0.457</v>
       </c>
       <c r="F108" s="51" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G108" s="82" t="inlineStr">
+      <c r="G108" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -14155,28 +14103,28 @@
       </c>
       <c r="B109" s="51" t="inlineStr">
         <is>
-          <t>2026-10-28 18:46</t>
+          <t>2026-10-27 12:05</t>
         </is>
       </c>
       <c r="C109" s="51" t="inlineStr">
         <is>
-          <t>How can US Fed FOMC meeting outcome impact Indian stock market? Sensex, Nifty to rise? Experts decode</t>
+          <t>Stock market today: Sensex, Nifty flat as smallcaps rally and IT stocks fall</t>
         </is>
       </c>
       <c r="D109" s="51" t="inlineStr">
         <is>
-          <t>Livemint</t>
-        </is>
-      </c>
-      <c r="E109" s="81" t="n">
-        <v>0.47</v>
+          <t>BusinessLine</t>
+        </is>
+      </c>
+      <c r="E109" s="80" t="n">
+        <v>0.511</v>
       </c>
       <c r="F109" s="51" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G109" s="82" t="inlineStr">
+      <c r="G109" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -14185,33 +14133,33 @@
     <row r="110">
       <c r="A110" s="51" t="inlineStr">
         <is>
-          <t>RATNAVEER</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B110" s="51" t="inlineStr">
         <is>
-          <t>2026-10-28 13:42</t>
+          <t>2026-10-27 11:36</t>
         </is>
       </c>
       <c r="C110" s="51" t="inlineStr">
         <is>
-          <t>Ratnaveer Precision Engineering Q2 FY27 Earnings Call on 3 Nov</t>
+          <t>Stock Market Highlights: Sensex, Nifty 50 End Flat On F&amp;O Expiry Day; Asian Paints, Coal India, Grasim Top Drags</t>
         </is>
       </c>
       <c r="D110" s="51" t="inlineStr">
         <is>
-          <t>Kalkine India</t>
-        </is>
-      </c>
-      <c r="E110" s="81" t="n">
-        <v>0</v>
+          <t>NDTV Profit</t>
+        </is>
+      </c>
+      <c r="E110" s="80" t="n">
+        <v>0.273</v>
       </c>
       <c r="F110" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G110" s="82" t="inlineStr">
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G110" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -14220,33 +14168,33 @@
     <row r="111">
       <c r="A111" s="51" t="inlineStr">
         <is>
-          <t>AEROFLEX</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B111" s="51" t="inlineStr">
         <is>
-          <t>2026-10-28 12:25</t>
+          <t>2026-10-27 11:30</t>
         </is>
       </c>
       <c r="C111" s="51" t="inlineStr">
         <is>
-          <t>Aeroflex Industries Q2 FY27 Results and CFO Change Announced</t>
+          <t>Sensex, Nifty End Flat as Oil, Fed Jitters Cap Upside</t>
         </is>
       </c>
       <c r="D111" s="51" t="inlineStr">
         <is>
-          <t>Kalkine India</t>
-        </is>
-      </c>
-      <c r="E111" s="81" t="n">
-        <v>0</v>
+          <t>HDFC Sky</t>
+        </is>
+      </c>
+      <c r="E111" s="80" t="n">
+        <v>0.67</v>
       </c>
       <c r="F111" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G111" s="82" t="inlineStr">
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G111" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -14255,33 +14203,33 @@
     <row r="112">
       <c r="A112" s="51" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B112" s="51" t="inlineStr">
         <is>
-          <t>2026-10-28 07:00</t>
+          <t>2026-10-27 11:27</t>
         </is>
       </c>
       <c r="C112" s="51" t="inlineStr">
         <is>
-          <t>Syrma SGS Technology (NSEI:SYRMA) Stock Forecast &amp; Analyst Predictions</t>
+          <t>Gift Nifty Signals Flat Start as Fed Decision Looms</t>
         </is>
       </c>
       <c r="D112" s="51" t="inlineStr">
         <is>
-          <t>Simply Wall St</t>
-        </is>
-      </c>
-      <c r="E112" s="81" t="n">
-        <v>0</v>
+          <t>HDFC Sky</t>
+        </is>
+      </c>
+      <c r="E112" s="80" t="n">
+        <v>0.612</v>
       </c>
       <c r="F112" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G112" s="82" t="inlineStr">
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G112" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -14290,33 +14238,33 @@
     <row r="113">
       <c r="A113" s="51" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>CPPLUS</t>
         </is>
       </c>
       <c r="B113" s="51" t="inlineStr">
         <is>
-          <t>2026-10-28 07:00</t>
+          <t>2026-10-27 10:46</t>
         </is>
       </c>
       <c r="C113" s="51" t="inlineStr">
         <is>
-          <t>Market News: Share Market Today, NIFTY, BSE/NSE LIVE, Sensex Today, Latest Share Market News Live Updates</t>
+          <t>Aditya Infotech partners with Ranveer Singh as brand ambassador for CP PLUS</t>
         </is>
       </c>
       <c r="D113" s="51" t="inlineStr">
         <is>
-          <t>Livemint</t>
-        </is>
-      </c>
-      <c r="E113" s="81" t="n">
-        <v>0.532</v>
+          <t>Business Upturn</t>
+        </is>
+      </c>
+      <c r="E113" s="80" t="n">
+        <v>0</v>
       </c>
       <c r="F113" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G113" s="82" t="inlineStr">
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G113" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -14325,33 +14273,33 @@
     <row r="114">
       <c r="A114" s="51" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B114" s="51" t="inlineStr">
         <is>
-          <t>2026-10-28 06:20</t>
+          <t>2026-10-27 10:44</t>
         </is>
       </c>
       <c r="C114" s="51" t="inlineStr">
         <is>
-          <t>NSE adds six stocks to F&amp;O segment from today, October 28: Check full list</t>
+          <t>Sensex Today Ends Flat | Nifty Below 22,750 | Axis Bank &amp; Asian Paints Top Losers</t>
         </is>
       </c>
       <c r="D114" s="51" t="inlineStr">
         <is>
-          <t>Zee Business</t>
-        </is>
-      </c>
-      <c r="E114" s="81" t="n">
-        <v>0</v>
+          <t>Equitymaster</t>
+        </is>
+      </c>
+      <c r="E114" s="80" t="n">
+        <v>0.026</v>
       </c>
       <c r="F114" s="51" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="G114" s="82" t="inlineStr">
+      <c r="G114" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -14360,33 +14308,33 @@
     <row r="115">
       <c r="A115" s="51" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B115" s="51" t="inlineStr">
         <is>
-          <t>2026-10-28 05:30</t>
+          <t>2026-10-27 10:43</t>
         </is>
       </c>
       <c r="C115" s="51" t="inlineStr">
         <is>
-          <t>Syrma SGS Technology (SYRMA.NS) Jumps 3.67% to ₹1575.3, Approaches ₹1654.07 Resistance Zone - Time Weighted Price</t>
+          <t>Sensex, Nifty Flat Amid Bank/IT Selling, Crude, US Fed Caution</t>
         </is>
       </c>
       <c r="D115" s="51" t="inlineStr">
         <is>
-          <t>https://www.siam.in/</t>
-        </is>
-      </c>
-      <c r="E115" s="81" t="n">
-        <v>0.459</v>
+          <t>Rediff MoneyWiz</t>
+        </is>
+      </c>
+      <c r="E115" s="80" t="n">
+        <v>-0.25</v>
       </c>
       <c r="F115" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G115" s="82" t="inlineStr">
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G115" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -14400,28 +14348,28 @@
       </c>
       <c r="B116" s="51" t="inlineStr">
         <is>
-          <t>2026-10-28 05:26</t>
+          <t>2026-10-27 10:37</t>
         </is>
       </c>
       <c r="C116" s="51" t="inlineStr">
         <is>
-          <t>Why Is Stock Market Falling Today? 4 Key Reasons Behind Sensex, Nifty Crash</t>
+          <t>Sensex, Nifty end flat as high crude and Fed caution offset sectoral gains</t>
         </is>
       </c>
       <c r="D116" s="51" t="inlineStr">
         <is>
-          <t>NDTV</t>
-        </is>
-      </c>
-      <c r="E116" s="81" t="n">
-        <v>-0.402</v>
+          <t>India Today</t>
+        </is>
+      </c>
+      <c r="E116" s="80" t="n">
+        <v>0.34</v>
       </c>
       <c r="F116" s="51" t="inlineStr">
         <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="G116" s="82" t="inlineStr">
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G116" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -14435,28 +14383,28 @@
       </c>
       <c r="B117" s="51" t="inlineStr">
         <is>
-          <t>2026-10-28 04:15</t>
+          <t>2026-10-27 10:35</t>
         </is>
       </c>
       <c r="C117" s="51" t="inlineStr">
         <is>
-          <t>Jio Platforms becomes 12th Reliance Group company to list on NSE, says CEO Ashishkumar Chauhan</t>
+          <t>Why stock market ended mixed today: Sensex, Nifty flat as Midcap Index gains 565 points</t>
         </is>
       </c>
       <c r="D117" s="51" t="inlineStr">
         <is>
-          <t>Moneycontrol.com</t>
-        </is>
-      </c>
-      <c r="E117" s="81" t="n">
-        <v>0</v>
+          <t>IndiaIPO</t>
+        </is>
+      </c>
+      <c r="E117" s="80" t="n">
+        <v>0.649</v>
       </c>
       <c r="F117" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G117" s="82" t="inlineStr">
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G117" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -14470,28 +14418,28 @@
       </c>
       <c r="B118" s="51" t="inlineStr">
         <is>
-          <t>2026-10-28 01:13</t>
+          <t>2026-10-27 10:22</t>
         </is>
       </c>
       <c r="C118" s="51" t="inlineStr">
         <is>
-          <t>Stock Market Today Highlights , Oct 6: Sensex settles 685 pts higher; Nifty 50 rises 220 pts; IT, Realty, PSU Banks end in red</t>
+          <t>Nifty, Sensex close flat amid pressure from high crude prices and caution ahead of US Fed policy</t>
         </is>
       </c>
       <c r="D118" s="51" t="inlineStr">
         <is>
-          <t>BusinessLine</t>
-        </is>
-      </c>
-      <c r="E118" s="81" t="n">
-        <v>0.402</v>
+          <t>ANI News</t>
+        </is>
+      </c>
+      <c r="E118" s="80" t="n">
+        <v>-0.34</v>
       </c>
       <c r="F118" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G118" s="82" t="inlineStr">
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G118" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -14500,33 +14448,33 @@
     <row r="119">
       <c r="A119" s="51" t="inlineStr">
         <is>
-          <t>AETHER</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B119" s="51" t="inlineStr">
         <is>
-          <t>2026-10-27 12:08</t>
+          <t>2026-10-27 08:56</t>
         </is>
       </c>
       <c r="C119" s="51" t="inlineStr">
         <is>
-          <t>Ather Energy shares: 125% YTD returns! Experts give 'portfolio stock' tag after Q2 results 2026 | Target, stop-loss</t>
+          <t>Is India's Stock Market Heading For Its Worst Year Since 2008 Crisis?</t>
         </is>
       </c>
       <c r="D119" s="51" t="inlineStr">
         <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="E119" s="81" t="n">
-        <v>0.457</v>
+          <t>NDTV</t>
+        </is>
+      </c>
+      <c r="E119" s="80" t="n">
+        <v>-0.848</v>
       </c>
       <c r="F119" s="51" t="inlineStr">
         <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="G119" s="82" t="inlineStr">
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G119" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -14535,33 +14483,33 @@
     <row r="120">
       <c r="A120" s="51" t="inlineStr">
         <is>
-          <t>CPPLUS</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B120" s="51" t="inlineStr">
         <is>
-          <t>2026-10-27 10:46</t>
+          <t>2026-10-27 07:00</t>
         </is>
       </c>
       <c r="C120" s="51" t="inlineStr">
         <is>
-          <t>Aditya Infotech partners with Ranveer Singh as brand ambassador for CP PLUS</t>
+          <t>Sensex Today | Stock Market Live: Sensex, Nifty trade flat; smallcaps jump 2.5%, IT slides 1.5%</t>
         </is>
       </c>
       <c r="D120" s="51" t="inlineStr">
         <is>
-          <t>Business Upturn</t>
-        </is>
-      </c>
-      <c r="E120" s="81" t="n">
-        <v>0</v>
+          <t>IndiaIPO</t>
+        </is>
+      </c>
+      <c r="E120" s="80" t="n">
+        <v>0.67</v>
       </c>
       <c r="F120" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G120" s="82" t="inlineStr">
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G120" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -14575,28 +14523,28 @@
       </c>
       <c r="B121" s="51" t="inlineStr">
         <is>
-          <t>2026-10-27 07:00</t>
+          <t>2026-10-27 06:58</t>
         </is>
       </c>
       <c r="C121" s="51" t="inlineStr">
         <is>
-          <t>Sensex Today | Stock Market Live: Sensex, Nifty trade flat; smallcaps jump 2.5%, IT slides 1.5%</t>
+          <t>Indian Stock Market: Sensex and Nifty Trade Flat Amid IT Sell-Off, Broader Markets Outperform</t>
         </is>
       </c>
       <c r="D121" s="51" t="inlineStr">
         <is>
-          <t>IndiaIPO</t>
-        </is>
-      </c>
-      <c r="E121" s="81" t="n">
-        <v>0.67</v>
+          <t>Pragativadi</t>
+        </is>
+      </c>
+      <c r="E121" s="80" t="n">
+        <v>0.6909999999999999</v>
       </c>
       <c r="F121" s="51" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G121" s="82" t="inlineStr">
+      <c r="G121" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -14605,33 +14553,33 @@
     <row r="122">
       <c r="A122" s="51" t="inlineStr">
         <is>
-          <t>CPPLUS</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B122" s="51" t="inlineStr">
         <is>
-          <t>2026-10-27 02:09</t>
+          <t>2026-10-27 06:02</t>
         </is>
       </c>
       <c r="C122" s="51" t="inlineStr">
         <is>
-          <t>Do Aditya Infotech's (NSE:CPPLUS) Earnings Warrant Your Attention?</t>
+          <t>Sensex Jumps 483 Points, Nifty Recovers After 4-Day Slump</t>
         </is>
       </c>
       <c r="D122" s="51" t="inlineStr">
         <is>
-          <t>Simply Wall St</t>
-        </is>
-      </c>
-      <c r="E122" s="81" t="n">
-        <v>0</v>
+          <t>Rediff MoneyWiz</t>
+        </is>
+      </c>
+      <c r="E122" s="80" t="n">
+        <v>0.361</v>
       </c>
       <c r="F122" s="51" t="inlineStr">
         <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="G122" s="82" t="inlineStr">
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G122" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -14645,28 +14593,28 @@
       </c>
       <c r="B123" s="51" t="inlineStr">
         <is>
-          <t>2026-10-26 21:36</t>
+          <t>2026-10-27 05:17</t>
         </is>
       </c>
       <c r="C123" s="51" t="inlineStr">
         <is>
-          <t>Indian Stock Market Crash: Sensex Falls 5,035 Pts, Nifty Drops 1,453 Pts From Peak; Can Budget Revive Bulls?</t>
+          <t>Stock Markets Today: Sensex, Nifty Dip on High Crude Prices, IT Sector Woes</t>
         </is>
       </c>
       <c r="D123" s="51" t="inlineStr">
         <is>
-          <t>Goodreturns</t>
-        </is>
-      </c>
-      <c r="E123" s="81" t="n">
-        <v>-0.318</v>
+          <t>Rediff</t>
+        </is>
+      </c>
+      <c r="E123" s="80" t="n">
+        <v>-0.477</v>
       </c>
       <c r="F123" s="51" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G123" s="82" t="inlineStr">
+      <c r="G123" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -14675,33 +14623,33 @@
     <row r="124">
       <c r="A124" s="51" t="inlineStr">
         <is>
-          <t>SMLMAH</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="B124" s="51" t="inlineStr">
         <is>
-          <t>2026-10-26 05:47</t>
+          <t>2026-10-27 05:10</t>
         </is>
       </c>
       <c r="C124" s="51" t="inlineStr">
         <is>
-          <t>SML Mahindra Limited (SMLMAH.NS) Slips 2.83% to ₹4,706.5 as Stock Tests Lower End of ₹4,471–₹4,942 Range - Hedge Fund Favorites</t>
+          <t>Stock markets fall in early trade amid persistently elevated crude oil prices, IT selling</t>
         </is>
       </c>
       <c r="D124" s="51" t="inlineStr">
         <is>
-          <t>https://www.siam.in/</t>
-        </is>
-      </c>
-      <c r="E124" s="81" t="n">
-        <v>-0.318</v>
+          <t>bfsi.economictimes.indiatimes.com</t>
+        </is>
+      </c>
+      <c r="E124" s="80" t="n">
+        <v>-0.727</v>
       </c>
       <c r="F124" s="51" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G124" s="82" t="inlineStr">
+      <c r="G124" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -14710,33 +14658,348 @@
     <row r="125">
       <c r="A125" s="51" t="inlineStr">
         <is>
+          <t>CPPLUS</t>
+        </is>
+      </c>
+      <c r="B125" s="51" t="inlineStr">
+        <is>
+          <t>2026-10-27 02:09</t>
+        </is>
+      </c>
+      <c r="C125" s="51" t="inlineStr">
+        <is>
+          <t>Do Aditya Infotech's (NSE:CPPLUS) Earnings Warrant Your Attention?</t>
+        </is>
+      </c>
+      <c r="D125" s="51" t="inlineStr">
+        <is>
+          <t>Simply Wall St</t>
+        </is>
+      </c>
+      <c r="E125" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G125" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="51" t="inlineStr">
+        <is>
           <t>MARKET</t>
         </is>
       </c>
-      <c r="B125" s="51" t="inlineStr">
-        <is>
-          <t>2026-10-25 14:34</t>
-        </is>
-      </c>
-      <c r="C125" s="51" t="inlineStr">
-        <is>
-          <t>Stock market prediction for Monday Oct 26: Sensex, Nifty levels, top stocks to watch - Will bulls dance again?</t>
-        </is>
-      </c>
-      <c r="D125" s="51" t="inlineStr">
-        <is>
-          <t>IndiaIPO</t>
-        </is>
-      </c>
-      <c r="E125" s="81" t="n">
+      <c r="B126" s="51" t="inlineStr">
+        <is>
+          <t>2026-10-27 01:30</t>
+        </is>
+      </c>
+      <c r="C126" s="51" t="inlineStr">
+        <is>
+          <t>Stock market outlook today, 27 Oct: Sensex, Nifty prediction - DJIA, S&amp;P, NASDAQ, GIFT Nifty, Kospi, Nikkei, Taiwan cues</t>
+        </is>
+      </c>
+      <c r="D126" s="51" t="inlineStr">
+        <is>
+          <t>Livemint</t>
+        </is>
+      </c>
+      <c r="E126" s="80" t="n">
+        <v>0.842</v>
+      </c>
+      <c r="F126" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G126" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B127" s="51" t="inlineStr">
+        <is>
+          <t>2026-10-26 10:28</t>
+        </is>
+      </c>
+      <c r="C127" s="51" t="inlineStr">
+        <is>
+          <t>Sensex Today Ends 483 Points Higher | Nifty Above 22,750 | Apollo Micro Systems Up 10%</t>
+        </is>
+      </c>
+      <c r="D127" s="51" t="inlineStr">
+        <is>
+          <t>Equitymaster</t>
+        </is>
+      </c>
+      <c r="E127" s="80" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="F127" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G127" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B128" s="51" t="inlineStr">
+        <is>
+          <t>2026-10-26 10:18</t>
+        </is>
+      </c>
+      <c r="C128" s="51" t="inlineStr">
+        <is>
+          <t>Taking Stock: Market snaps 4-day losing streak; Nifty reclaims 22,700, Sensex gains 483 pts</t>
+        </is>
+      </c>
+      <c r="D128" s="51" t="inlineStr">
+        <is>
+          <t>Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="E128" s="80" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="F128" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G128" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="51" t="inlineStr">
+        <is>
+          <t>SMLMAH</t>
+        </is>
+      </c>
+      <c r="B129" s="51" t="inlineStr">
+        <is>
+          <t>2026-10-26 05:47</t>
+        </is>
+      </c>
+      <c r="C129" s="51" t="inlineStr">
+        <is>
+          <t>SML Mahindra Limited (SMLMAH.NS) Slips 2.83% to ₹4,706.5 as Stock Tests Lower End of ₹4,471–₹4,942 Range - Hedge Fund Favorites</t>
+        </is>
+      </c>
+      <c r="D129" s="51" t="inlineStr">
+        <is>
+          <t>https://www.siam.in/</t>
+        </is>
+      </c>
+      <c r="E129" s="80" t="n">
+        <v>-0.318</v>
+      </c>
+      <c r="F129" s="51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G129" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B130" s="51" t="inlineStr">
+        <is>
+          <t>2026-10-26 04:32</t>
+        </is>
+      </c>
+      <c r="C130" s="51" t="inlineStr">
+        <is>
+          <t>Sensex settles 500 pts higher, Nifty ends above 22,750: Key factors behind markets snapping 4-day fall</t>
+        </is>
+      </c>
+      <c r="D130" s="51" t="inlineStr">
+        <is>
+          <t>Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="E130" s="80" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="F130" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G130" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B131" s="51" t="inlineStr">
+        <is>
+          <t>2026-10-26 04:05</t>
+        </is>
+      </c>
+      <c r="C131" s="51" t="inlineStr">
+        <is>
+          <t>Why is the stock market down today? Sensex drops over 600 points, Nifty drops below 22,400 - Top 3 reasons explained</t>
+        </is>
+      </c>
+      <c r="D131" s="51" t="inlineStr">
+        <is>
+          <t>Livemint</t>
+        </is>
+      </c>
+      <c r="E131" s="80" t="n">
         <v>0.542</v>
       </c>
-      <c r="F125" s="51" t="inlineStr">
+      <c r="F131" s="51" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G125" s="82" t="inlineStr">
+      <c r="G131" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B132" s="51" t="inlineStr">
+        <is>
+          <t>2026-10-26 01:27</t>
+        </is>
+      </c>
+      <c r="C132" s="51" t="inlineStr">
+        <is>
+          <t>Stock Market Today: Gift Nifty, FPI Outflows To Oil Prices; Five Key Factors For Sensex, Nifty 50 On October 26</t>
+        </is>
+      </c>
+      <c r="D132" s="51" t="inlineStr">
+        <is>
+          <t>NDTV Profit</t>
+        </is>
+      </c>
+      <c r="E132" s="80" t="n">
+        <v>0.8070000000000001</v>
+      </c>
+      <c r="F132" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G132" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B133" s="51" t="inlineStr">
+        <is>
+          <t>2026-10-26 01:22</t>
+        </is>
+      </c>
+      <c r="C133" s="51" t="inlineStr">
+        <is>
+          <t>Stock market outlook today, 26 Oct: Sensex, Nifty prediction - DJIA, S&amp;P, NASDAQ, GIFT Nifty, Kospi, Nikkei cues</t>
+        </is>
+      </c>
+      <c r="D133" s="51" t="inlineStr">
+        <is>
+          <t>Livemint</t>
+        </is>
+      </c>
+      <c r="E133" s="80" t="n">
+        <v>0.842</v>
+      </c>
+      <c r="F133" s="51" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G133" s="81" t="inlineStr">
+        <is>
+          <t>open ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="51" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="B134" s="51" t="inlineStr">
+        <is>
+          <t>2026-10-25 07:03</t>
+        </is>
+      </c>
+      <c r="C134" s="51" t="inlineStr">
+        <is>
+          <t>Trump hints at an Iran attack or deal! Impact on India stock market, Sensex, Nifty, gold decoded; top 10 stocks to watch</t>
+        </is>
+      </c>
+      <c r="D134" s="51" t="inlineStr">
+        <is>
+          <t>Livemint</t>
+        </is>
+      </c>
+      <c r="E134" s="80" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="F134" s="51" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="G134" s="81" t="inlineStr">
         <is>
           <t>open ↗</t>
         </is>
@@ -14747,7 +15010,7 @@
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <conditionalFormatting sqref="E5:E125">
+  <conditionalFormatting sqref="E5:E134">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-1"/>
@@ -14881,6 +15144,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G123" r:id="rId119"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G124" r:id="rId120"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G125" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G126" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G127" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G128" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G129" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G130" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G131" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G132" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G133" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G134" r:id="rId130"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
@@ -14907,28 +15179,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>"src": "bhavcopy"}}, "CPPLUS": {"2026-10-29": {"open": 3985.0, "close": 3951.7, "src": "yahoo"}, "2026-10-30": {"open": 3932.1, "close": 3811.5, "src": "bhavcopy"}}, "THANGAMAYL": {"2026-10-29": {"open": 4681.0, "close": 4630.5, "src": "yahoo"}, "2026-10-30": {"open": 4620.0, "close": 4455.0, "src": "bhavcopy"}}, "KIRLOSENG": {"2026-10-29": {"open": 1907.3, "close": 1890.3, "src": "yahoo"}, "2026-10-30": {"open": 1884.0, "close": 1796.1, "src": "bhavcopy"}}, "SMLMAH": {"2026-10-29": {"open": 4770.5, "close": 4848.0, "src": "yahoo"}, "2026-10-30": {"open": 4918.0, "close": 4724.5, "src": "bhavcopy"}}, "AETHER": {"2026-10-29": {"open": 1590.0, "close": 1581.0, "src": "yahoo"}, "2026-10-30": {"open": 1597.4, "close": 1616.2, "src": "bhavcopy"}}, "SBC": {"2026-10-29": {"open": 65.39, "close": 66.52, "src": "yahoo"}, "2026-10-30": {"open": 67.05, "close": 66.15, "src": "bhavcopy"}}, "SYRMA": {"2026-10-29": {"open": 1563.0, "close": 1669.0, "src": "yahoo"}, "2026-10-30": {"open": 1675.0, "close": 1625.3, "src": "bhavcopy"}}, "TDPOWERSYS": {"2026-10-29": {"open": 719.8, "close": 719.45, "src": "yahoo"}, "2026-10-30": {"open": 705.0, "close": 713.9, "src": "bhavcopy"}}, "RATNAVEER": {"2026-10-29": {"open": 345.0, "close": 352.85, "src": "yahoo"}, "2026-10-30": {"open": 354.2, "close": 360.25, "src": "bhavcopy"}}, "NIFTY50": {"2026-10-29": {"open": 22690.65, "close": 22936.75, "src": "yahoo"}, "2026-10-30": {"open": 22964.5, "close": 23053.1, "src": "bhavcopy"}}}, "entry_override": {}, "news": {"fetched": "2026-10-30 18:08", "days": 7, "items": [{"symbol": "MARKET", "title": "Markets hit 6-month high in Oct on IT rally, Jio Platforms IPO frenzy", "link": "https://news.google.com/rss/articles/CBMi0AFBVV95cUxOdXZHZEdOTVJWWHBOLXZXb2NuTDlvY1RUMk5Ld2ozdTZ5UnRubVkyTk11YlQ2WkVZMmhncnBsQ0prdHlQbHUtQjlDMlNlVGdwSmVyMFdjWWNqc3lLalpvek9Bd2d5MnFHZTJRM0p5TlMwdmRicFVmMzcwb2NYZkpFRXM5czY3S2hMSnhyb2lMX2hQeFZ3ODNZckk3Nkk0MlM4d2s1U1hBVGxhOVdHYS1oamhGMFVCYWtuUm95WjM1M2N4MG92M3lhcXBJYjVlM0920gHWAUFVX3lxTE03MVNYWWtyQjllRDNNR2VtWHZrNVl3aHYyTnBWeS1tc1Y4Z2pzRWU2c0EyNUprd3ZVM0tEalJnUi15SUVsYm5kNzNOZzloRlZ5Mld6NWwzNVhObUR5WC1GUnFZTmdoWjlTY2M3M3J0YXhDR1hfbXFMM3UtRVZVcWtad1RxaWlEY0FWVFRLTVdXZlduWkNzN3lVMTU3akYyZUlUUmduVEZHU2NROGg1TFBLYlkycVY1M01iSG1qR3ZOaWZMR2ZDdlBFdWNETWVfU19jNTY2TWc?oc=5", "source": "Business Standard", "published": "2026-10-30 17:26", "score": 0.226, "label": "Positive"}, {"symbol": "SYRMA", "title": "Syrma SGS reports best-ever quarter; Q2 revenue up 73% to Rs 1,999.5 crore", "link": "https://news.google.com/rss/articles/CBMi4wFBVV95cUxOX1lzeEswS005dk5yZEl6Z0pvX1VQbnp2RzBnR3JvdFVwanI5V2lFdHlTcE02Tm14Mzg5MFN0blpUcm54YnNjY3dsSVJSSEpLaXQ3ZHlocnpLYVpIVVo2NkNxRVVEZTFmT29UOHFIbmNxS1VlUnN0SW1oMXl3NzZyUGpBU29HVWd3c2dNVGFhNWtxNjMyeHlsTEc3NmxmY3Q5LUF3TE9GRkpoZFByd2ZEeG1fb2liWkJaRUMwUTFiZWptOWFXZXJIeUxKQzg1ckpoY0NIUzhtVXNqMHZvS1VJRWtnUdIB6AFBVV95cUxQNWpYOU5EY3MweXZaRE53azhMcEpJRG8wNzlVcm1DY0xiZjhNa2JQaGF5bFlad19ZNGpQcGZiR3RQSk1hNnZkdEllZWdKRVdJZnZhb3dwZzgtY1dfVklxc0k3NzVPQ1h1VElTQkxSbGNMZThoNDJaNG5DQV9kbGY2U0ctaTVBZXc1cTM2dkVzaWc1NzVLYXo5WWJVcWhVdUpXS2pzRS1LT3VDT3B5Ym5SNjNlbk5CcHJaaWdiOUNZWGxNOHExX0lLLWo4S2c0eF9DOGotTkZPdzR4R1lYN0otRURMdXBRRi1N?oc=5", "source": "The Economic Times", "published": "2026-10-30 16:35", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex Gains 308 Points, Nifty Reclaims 23,000 as IT and Pharma Stocks Lead Recovery", "link": "https://news.google.com/rss/articles/CBMirwFBVV95cUxPNlo0QnpXclVoY0VJMFg4c2FMUlRzOGpTcElSVzNscEh2Q18zdXpwZXIyVjh3bzAzZVNoNk1pSlNweFJ3TW1BMDVidmJLZzV0cU9KQnZYcjhjZ2VHQmtjUGlnRllmT3QydWdneklFSVQzdWlVdG5leVZCdEZ4NHdMOTZUX0ZCQ3daaXhSQWV4RGphRnJKMkJ2X0VSNlB2XzJIaTk5TE1PejdrOTZzX2N3?oc=5", "source": "The Indian Awaaz", "published": "2026-10-30 16:07", "score": 0.649, "label": "Positive"}, {"symbol": "MARKET", "title": "Indian Shares Snap Two-Month Losing Streak, Nifty And Sensex Gain In October", "link": "https://news.google.com/rss/articles/CBMizAFBVV95cUxOWWxJcWJZM0t1RFdIV0ZTRkVWZzVHZkluTlB1aFZmVC1KeUhaSS15eDN6QnFHb2hBYy1HdHRQV3Rjb0xOOUpPMlBZRUpEcGtUaFA4YjNISVpLN0NHZVVqNElaXzFvTV9KUTJWVHJiaFlkbXpLTEpiNDdLd2VkNEU5bWQxdnVZUThmVkNseGVEa1VpQnhhUEN4X1hYY2ZGcGNWb25LdzFOVzhNU0xvVWNITjNnRHJYekQxNm10ODVTTFVtRVhGSEFxdEluLWQ?oc=5", "source": "TradingView", "published": "2026-10-30 16:01", "score": 0.361, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex Gains 308 Points, Nifty Closes Above 23,000 as IT and Pharma Stocks Lead Rally", "link": "https://news.google.com/rss/articles/CBMisgFBVV95cUxPWndrT0xmdkJxeDluWUM1cjJYX2Z2VUZyQXlqMVZzZkMyUzFXQTJsQ2JlMzU2MUJzejJfLU0yZzNlRUFELTN2dWozZGRJcXVlUzlyZ3RwSlctcUJGSkpmcGRxUDhWRGxuRUt1V1cyY1A5SG1GWnBHb0s0VDE5Vk1FcGtDczFsSDNqR29vTENzTjRkemV6M1AtcnY3aXdGdW9qUGZBb2NSd2dZTTh2UW1VcFdn?oc=5", "source": "INDIA New England News", "published": "2026-10-30 15:13", "score": 0.807, "label": "Positive"}, {"symbol": "SYRMA", "title": "Syrma SGS Q2 results: Profit nearly doubles to \u20b9117 crore, revenue jumps 74%", "link": "https://news.google.com/rss/articles/CBMirAFBVV95cUxQWWVNajdfcWthd1FGS3dENzdIeWltVzdfWTRueHBPYlFWSEs4MHNnOW9HQnVWODIxTENyb21PblA5Y3d2Ym4zeVkza29VZ0VQSENCb3dhUVQyN1N4WFlGWnNTaUt1czBRWl9NTy01UmU0bExnQXZKMUhpeW8yUU9GT0tPbDFpeHh6em5GZzNZNzZTYUFuSkR6RlFwS0Fwcy1SQjZLSHdDdTRFaTZm0gGsAUFVX3lxTFBZZU1qN19xa2F3UUZLd0Q3N0h5aW1XN19ZNG54cE9iUVZISzgwc2c5b0dCdVY4MjFMQ3JvbU9uUDljd3ZibjN5WTNrb1VnRVBIQ0Jvd2FRVDI3U3hYWUZac1NpS3VzMFFaX01PLTVSZTRsTGdBdkoxSGl5bzJRT0ZPS09sMWl4eHp6bkZnM1k3NlNhQW5KRHpGUXBLQXBzLVJCNktId0N1NEVpNmY?oc=5", "source": "CNBC TV18", "published": "2026-10-30 13:51", "score": 0.66, "label": "Positive"}, {"symbol": "AETHER", "title": "Aether Industries (NSE:AETHER): What Do Aether Industries\u2019 September-Quarter Results Show?", "link": "https://news.google.com/rss/articles/CBMixgFBVV95cUxNb3lGcXBYMGhGTkhHcVNBUFRETjZsYWl5eDRicWZEU0hTLVo1bHB1UDFFNHRPa3NsaGM1MzlmU0ptWnUtNzJwTWVCTDB2RXU3cWVvblI1UjZhVkZEb3pxVXJnUVlvamRDaTRUcVh5S05ubGhydDhkU1hNR2hOLVZldzhfbktjM0VJU3V4TTBKaS1ycUtvX2pQem4ycUNuN1NmUHU5cTlwLTctT3RQR0ZmZlVaSTNKcW9veHUyQVh2Nmx1dlFPRWc?oc=5", "source": "Kalkine India", "published": "2026-10-30 12:34", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Stock markets rise for 2nd session; Sensex gains 300 points on buying in IT stocks", "link": "https://news.google.com/rss/articles/CBMiwwFBVV95cUxNNHNJTGVrRmdOU1FVSGlwTFhRazBPeXZpUW1pc0MxOWxtc0FHT1pLZ2NiUF9XdTRnOV9vQlE1bGttMll3cndvLUVVTU5keHBhd09TNDJRSTRFNnBOUXVmaHFMYlhKZDUxYVpyanlsRDJWM2Jnc1EybzhJUU4xOV9LbWRPRHF4M2N0clRqeTY3dVQzMXdtcFQydkVyYjR5RkJYUEN6Z3lGLVNKSURzSmkxXzNrSjRXLThsSTNWQjE2aVY1R0HSAccBQVVfeXFMUEhJTURkQzA5dm1saFZIZjBlOTFFRUQ3dXZuaFd5MndSSUhNUGc2R2VBXzJHRWVObnBJdDVlY3FKVmRnbGlla25hSFhjb09fYktLRWY1Vm83TExtQkJlLVNvTkRzM0xfR1NxdTZUMUpMNHdCakZoX29GZ2hiUk1VNE9vMEdtTzZNXzU5ZWltdDZnSFFVY0R1aHRFeDRxR3Q1bEJhcEFTX2VSOFE1TzZiOVNpRjZyODdQMUN3aV9NSkxocDlWbU1zQQ?oc=5", "source": "The Tribune", "published": "2026-10-30 12:12", "score": 0.382, "label": "Positive"}, {"symbol": "MARKET", "title": "Rupee gains 33 paise as dollar weakens, Sensex and Nifty end higher", "link": "https://news.google.com/rss/articles/CBMi5wFBVV95cUxPbU9TVlhwU0RfZ2RaSWlHVzZ6aGIwa2RlSjR3OWpJOV9hNUdpQzh2R05ueGxaVVBMR1RtTlVqMU1Cd0Vwd0FJOVpDRGVZOWRlQzRtWEM5NUVOX2J6MjdlNTNfSUtzSnlQek1VQjRQZm1ocVVZVzdpTmJTb2tKajBzeWlSbjF1dzBwN0xMT2swckJfUlAwM3NqM21uN2ZSTU01bUl4S0M1YjZ6RFNTY0xPZDB5ZmxhRzVVTURZV1dmLWg1S1d4ZGRCQVF6RWV3MUh1a0lFd1VaMjdBMlk1aFdva1NnWHFLNE3SAewBQVVfeXFMUFpQa1Boc2xFMXp6VExQenhIdVBMb2poRHpCTk0xbWRuSmJxQWJIb0VGcFd4cHJuUDRUY0pTZTk0ZnBSOG1uNEhHRWM1a0lQek5RQ0RYVzR1WURocFg0eHJRQTdXOGpEWjJaSWczYnNVTlljUDZTYzVPakppc1g5azNhVmtRaGRrT29hcHFmczBVVE1BSzZiaVpocUppYmgyenJ5UnEyclBMN045ajFDQ1lkZ0dyNlRlLUo1UklSVHJIdEF6Qzg5Z21uS05DdVRIUmtFSFB1ajJkMHVaeWxMdUVCakdQTEFSU0toeUg?oc=5", "source": "The Times of India", "published": "2026-10-30 12:05", "score": 0.459, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty End Higher as IT and Pharma Stocks Lead Gains; Broader Markets Remain Weak", "link": "https://news.google.com/rss/articles/CBMiyAFBVV95cUxQOXFXLU9kY2FWQXc3dUJDdmZmZk9MYm9LNzFrclM5QWZNdklOSW42ZmwxMl9CVkdWYmJSZ3liYktscXZWeE8tc2NGNVVVSjNKdTVZRXkzSWlRWXpkcGhSQnlsRTYtZnI1Q2tvZkk5a1dxV0J2WmdwLVIybDg3MndlOFlwcmpXQzF1YjlCTHdWRnRBTktCbzVNMUFVODk4VFRRWmZYUGNOWE1QZmRGakZYUVFMaUJ4Zmxjc2pMM3JONDJKeDIyVHNUVg?oc=5", "source": "Business News This Week", "published": "2026-10-30 11:43", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Share Market Today: Nifty 50, Bank Nifty | Oct 30, 2026", "link": "https://news.google.com/rss/articles/CBMivgFBVV95cUxPY25ELUgtdk81RlJKeUYxeUE5TGpwQnVBcFJzVHZydWE4UmN2cmhTMDVONnhUeEg5ejBNd21IcU5nTWxtRmstMjl6Yks2TE1ZcHhMQVo0NVMwUGZrbkd0UFltSkE0bWdxMzlnV3NCZkhrelhfbTlVT0NadjJOZjYxejFobXhuT0dnNHlFYTduRXZNSlRJRFRrRVR3N0pBRFRaMlIxYVRZUmdIZDJHUmhFbjBScGdwMG5GNEdaS093?oc=5", "source": "Liquide Blog", "published": "2026-10-30 11:26", "score": 0.66, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock market today: Sensex, Nifty extend gains for second day as IT, pharma stocks lead rally", "link": "https://news.google.com/rss/articles/CBMitwFBVV95cUxNR3JxNnMzYkh6T2dLQjV3cEN0VzV3NGxfS3F6a0FWOTlFd0RYOS1Da200aWNibW1hbnFWTG0yOVBjMEZfSWU0bDZlUldYZEl5YW5pZFdoVi03U1Z0VUdQajh1eHhQcTlMV0FzVzBzNjg5Z3BvOUhKcG1nZ2FkeXVKbEZWVk5oa2U2bmhSUjZsOHVacGJxejlYdmtEOGhNbi1fT2pKeWZtaEttVkltR0lfYVZjeDc1N0E?oc=5", "source": "IBTimes India", "published": "2026-10-30 11:25", "score": 0.84, "label": "Positive"}, {"symbol": "MARKET", "title": "Green Energy Stocks Decline Despite Sensex Gaining 0.4% On October 30", "link": "https://news.google.com/rss/articles/CBMiqAFBVV95cUxQRmduc0NPQlNZdUdVRXMzR1R0WV91RjJCTzZvSTRWMHRxcW1MdXc2UF9nZnlSbnhkOTg4NXljdkNrYXE3UDV2WldYQ3lkS1pzV1duNVBkMm80SE5BRVh1MkdabzhfQ1lDZlROc3EzRHdEeV9GdG1UWkFEUGdTOXFsTklGLXFOTmlwSExzMnZSM3NxUVdydzg5Q2w3U29DUHNjRHNCRVRBNTc?oc=5", "source": "SolarQuarter", "published": "2026-10-30 11:24", "score": -0.428, "label": "Negative"}, {"symbol": "MARKET", "title": "Markets rally for 2nd day amid buying in IT firms, earnings-driven demand in Trent", "link": "https://news.google.com/rss/articles/CBMirgFBVV95cUxQMXVXZngtY2JfMzFTOVlMdVdLMmIyckJEZ28xbGI3djF0cXE3YVItSDk3WFRFRWx1QnJCRjR2NGdWLTAwNlJYZ0kyaFZ1VGd6STA2bVFRRVRWRjRla0VTZk1uR21XdlVLYUltMW1tSEV3TUdiR0dheXh4clR1a0Rhd25UbFlrNV9DVVdIc1QyRVJIVlR0OXdOaW0wUHNVOEFyOG1Vd1BNVUdVZ1NBM0HSAa4BQVVfeXFMUDF1V2Z4LWNiXzMxUzlZTHVXSzJiMnJCRGdvMWxiN3YxdHFxN2FSLUg5N1hURUVsdUJyQkY0djRnVi0wMDZSWGdJMmhWdVRnekkwNm1RUUVUVkY0ZWtFU2ZNbkdtV3ZVS2FJbTFtbUhFd01HYkdHYXl4eHJUdWtEYXduVGxZazVfQ1VXSHNUMkVSSFZUdDl3TmltMFBzVThBcjhtVXdQTVVHVWdTQTNB?oc=5", "source": "OrissaPOST", "published": "2026-10-30 11:17", "score": 0.361, "label": "Positive"}, {"symbol": "SYRMA", "title": "Diwali 2026 Top Stocks To Buy: Apollo Hospitals, GE Vernova, TARIL, TD Power, Jindal Steel, others; top 10 picks, target", "link": "https://news.google.com/rss/articles/CBMikwJBVV95cUxOejZuNVZHYUg3QlloRzQzYXBzbjR3OFdESEFXaU1ZaGg4ZU1YMkExbUpVNHZ0S1JCUEZQNmRKVXVraTVxNjAxcnc2MWhPamFkclpDVGNEZDlILWhBdmtzQy16RHVJaW1wQjdtbmN1TUVUZDBudlMtNnNfcXdWMEV1ZWphaElvTUdTeTBsNDFYbEs3UEFHMVMySzZCVEIzeUYwR3Y3bWdPQmVfcHBlOG84Zkg0aGxLMmtLVDhzQms1MUNnWDRXYmFjbnZWQzU0SC1Oci1JXzBjbnQ0UTBJU1l1MWJ4MTd4TV9NM0FVSC1LRV80c1Q4QllyS01NOWFHVUZpMXdkdEpSNmt0aEg4WVl4V2Fwc9IBmAJBVV95cUxPQjJxY1ZBR21RVFNpWE1vR0pkOVA5Z0RUUmFZRDZ4dS16TWpjdzFzcjM0QmQ3bVkxWV9fWmdIdXIzdzA3MFZHUXNIZm9sdjUtd3cyUl82V1RKRTlZVHBMQjVNeFdXWmp6U293TS1WYnpiVzJhZlV0UVZGbTJ6WldTVC03bmhmYlhobTJJNlRUd2VucW1vRlpPRElMelZneGJGdzZLWmRVMWxSd3MwbXpKVXBEQkdMVEdsNWR5c0NXT3dGRVlUSEFGZ3licnVTbllGbnZ6VFBCNGxmZk01cWJjcVpqQW1TZGlmNkE4RUlwdDVyRDhoZUJmaTNLNVpBQ3JRTklFX2dkM2lIcnUxNXlxZnBCemtMMThQ?oc=5", "source": "Livemint", "published": "2026-10-30 11:14", "score": 0.66, "label": "Positive"}, {"symbol": "MARKET", "title": "Indian Equities Rally on IT Sector Strength, Trent Earnings", "link": "https://news.google.com/rss/articles/CBMivgFBVV95cUxNUjdNY3FGSXVhZWNuMFI2cTU0Tk1HbjdRNHZ0NEJoOFBQTWNCNFU5S3ZfZzlKYlJYOHpid0twc3ZkUzRyMmE4VnJjUGJybldSTWlYRUl0QkNJRVVGSFdNNWRYWWtjYVVyNG94cVc0bGJhVGo0bmhqbFd3MklsSEh1b3h3YzhQY05QLWhzUTlzaUpsSUZyRFZiUG1KNVBIVEI0SUhneTZDRTJ2Nm5pUGJGR2J1cC1VRWhmVlEtQUx30gHAAUFVX3lxTFB3aVc1Wlo2ZUlnQkk5akNVSHU4ZmNjTlFEdEtOekpRYzFTZnFKZVlNRHAxSm5WUGlWMmhySGs4bzRnbGRpempPWU9WdG1FbXpKUlpzajNIVV9xYlZSYURwcFEtYS1yVWMzRkxOdmZnRTJjNU43ZnJNZFZpR0hMenJTU3hPZDVCa19FbGxaWUU5Z01kbklXaGZDSHVyYjVKQzRyamxydExyM1RkN0kwR2NRVnFIdFJOSkZ3ek1pZElYcA?oc=5", "source": "Rediff", "published": "2026-10-30 11:07", "score": 0.735, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex Rises Over 300 Points, Nifty Closes Above 23,050; IT, Pharma Stocks Lead Market Gains", "link": "https://news.google.com/rss/articles/CBMi8wFBVV95cUxNMFMwbG5wbEljemRIR3lwN192YnVpZm5OZkdZSV9ORzV1S014VXNwZ05lV2hEY0tlUXhfUW9mbmVxeWpsNU9ia2UyMlJRaGJkM2NrQ0pxYzVSbjQwLThkME5jRG5rb1FHTXQ5ZVNKUTB3Tnk4eTdYVXFiS2J3NENxM0lDTEhTZXNPSnlHVzBrLWhXUnh1MVROWkpXMFpSLUpBNkx4djUtck1RYk5PSER3cGR3UTd0d0lhWmNxRk40c1l0TGs1ckVsSGZTRHdjRVFCa0FIM1hlaVVuV1FzV1lhRHJHYVB4N3BQRmZ3T1JTbndoRjjSAfgBQVVfeXFMT0R4SzdXUXU1WldnR2dzSVpmTGdKdG9aNkhhemNHRTA1MVVfMmM0SVJoU3V0VWFIamw5ZDFibG5UR01RNlFjMHVvVXdjNUxwOGlGOUNXXy1tUmhSUjl5aFc1VmN5Mm8wRUlhNnBVTzhHbjZWUFA1QkJKX2xPV0pwV0NYRmVuNVM2Um1tSW9sSl8tVHZBZTI3WXNvNFlzT2M3dzRUTjE4d2F3RmhLUlZlZV9PenZFYW9kOW9xbjFJa0N5UkgzQ1pLRUk0bkR6dXA2UEFVS21mcFRWeWpVVGtwT01xYjVRd1duOGhHbW0ycm0yVXB4R0hHVWk?oc=5", "source": "Times Now", "published": "2026-10-30 11:00", "score": 0.649, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex and Nifty Gain Amid Mixed Sector Performance; Large Caps Lead Market Rally", "link": "https://news.google.com/rss/articles/CBMi1gFBVV95cUxNN0pVM1RiS0dxNkFVVTdVaUQxbTFOaHp2Z2x0N014TTRPcFpjZWs4YzhLb0RENWZ0RkcySVFza3JZU2hlWDRSNzhlajBLUlQzZVJQUWxpUy03RzkxSGFCZHZqMU0zaG1vOWVTYTdfNlNDaGpQR0VHemlDd2EzbFNQclNneTZUTjhpcC1JQXJJN0tNYzl0WjNHUC1SeHN3Vk4yOHJXSWVRaFdYVDZRWGRrU3hkX05LQUlha0p0RnlrblpfRjZ4Z0ZlMjR4VHB3ZmY4U1QwUnJR?oc=5", "source": "MarketsMojo", "published": "2026-10-30 10:59", "score": 0.796, "label": "Positive"}, {"symbol": "MARKET", "title": "Market wrap: Shriram Finance, Nestle India, Trent, InterGlobe top gainers and losers on Nifty and Sensex", "link": "https://news.google.com/rss/articles/CBMikgJBVV95cUxPOWtiUzAzVWw5Mk40VlV4WkZoSUJoOW5NNmZndTFSOEVMdHFkaGk3WHNRTFFlSzl1OHJ0VmVyalI5YkxsTGRWRVNoc0JPSXZ6RnpSMGxWcFhFNHFPdG9RWUJYYk1ULWlTV282cE5ES0YxWmVqNmUyaXE0d3RjQVA4UVFySzNreEZ3WWNmS0Nldi1RUDFSNDBMNWhYWE8zbW9uUEFaYTZlZTVUTHpwSVBWeTRpQjRBUmRmdjVSMXFCbE9kVy1tU3FtazFJaE0wUVJYVlNVYVJHSDEzTGpqU2FxZFdOQjY5ZFlxOHNEUnFKNnd5SC03ZDE2ZmR3YjdkS2U2cEFMSEw0dVkteHo2N29PMHZB0gGXAkFVX3lxTE96bkJGNFNzdEVsbWxGQzJDYjkwbkRtNjVjZnR5MV9TQlB5cHR4a2o2eVBhVW83T09YTUZ3dkdYTnVRVmlPaG9aNXVCbE9tZ0hFalhVamZoN2VGc3VNU01FZGVxSWtELWZhaXEwYTRjdUlhQzR5OGw5WW9ZWjhzNXVRYzViYV9oZ3NuUVlGbFNfQ3lHQkE1ci10OTBjRkNqR1hhZXk0WVAxZUVYSGhwUFpIcDhiQmZxYWZuODM2eEhFUXQ3ZEFsME8wdVZ0OVB3NVJoWU1iV25tVWdJT1FINklXT2JhTXM2NDFsT1JFVXphUUZLOTZ2OHVLejdOTzRsdkc0TkxVeGctbkwtVVlxUDRhb1pJVDJWMA?oc=5", "source": "The Economic Times", "published": "2026-10-30 10:56", "score": 0.026, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex, Nifty Rise; IT &amp; Pharma Lift Markets as Midcaps Slide", "link": "https://news.google.com/rss/articles/CBMisgFBVV95cUxOajFHdFZlZGo5cUk0dWJ3V1E4c2dCUFlBVFVMZV8wYklSQzVtUEJKRDZVSFhIdHRIUDUyZGlHc1ZWVC12bGwzMTFtSEpqdWdpYmowZmRqQ2ttVWVuaDRVOTh4b05lUVBQR2JYeUNjWDRjcjRMWExJSEFhV2lKRFRoUUVmaWFtSDBYdjBldjI2NWdYUlBHZXpUX1FRVXpwaXZucGpuQWlRLWxrdkJoWmRRblNR?oc=5", "source": "HDFC Sky", "published": "2026-10-30 10:53", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Closing Bell: Sensex Gains 300 Points, Nifty Reclaims 23,000 Mark as IT Stocks a Lead Rally", "link": "https://news.google.com/rss/articles/CBMi0wFBVV95cUxNWmRkUkxrWFBGcW9fcUVPUnhZSWpZNUhEUXI2ZXljYkVWSTM3ZWJmdl9EeTZwOEktUlF1a0tod0VsR1pLOUlrODNydzdCTXhxU3ZsNzBXTUkydlkteG9uQVp5dmxNM2lfcG04ZUREZV9GQTg3NWxKd0F5cUFxX0Vzd2hZV2RqSnA2VndFWnV2NUEzSGxwdVZVVS00YjVGQmlVVzRnZDgtRTVUTXBNRG9zano2dTFvWkpSRVY3OFRkVVplbjRmTXQtZ01SeXZhWHh6ZW5B?oc=5", "source": "Dalal Street Investment Journal", "published": "2026-10-30 10:36", "score": 0.807, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex rises 308 points, Nifty above 23,000 even as broader markets crash. Will D-Street bulls extend reco", "link": "https://news.google.com/rss/articles/CBMipwJBVV95cUxPTXhsRWN1cm45ckpDbWUxY21qclNKLTVCeDlaUlJweGFFUS1qSG40b09sNVlzTFBKQVNPZzU4R3VSSGZuNF96dHFPVVFDQmFOTy1YZU43YjJaRWpCczlrZkViZ0tTSS1lN1VzSUdrbHFoS01uMW9vRjl3MWRzSnZiSkd2T3REMjBBUTYwY29vOS1xSDNndVhFT0RNdjVtN1lFUkljSlE0cjR3ZjJqRDZodXBuMlpmSGJhYklpRnAxYktzS0hhYWJoRUJUWWUyeWlScXlTVk05VkMtazRESVQ1STE0TU1Cd0Q5Z2NHcXdZWm5XeFpaMHFJUm9CalNmMGdYZEpTS2ttUnFvaDFjVEc1YzhEb3NLSWlMRHYxUXVwaUFWQTZXZ0lR0gGgAkFVX3lxTE55RHpQVXVLRUxDYkNVYmFlZ2FlbU9vdnZVNTBvUXhZSFJBaHpKOXJ6dnE1aVpGSXlZeGdGaUtmMGN5TVdHX21JYkhuVXgyWmE5eW9UcEhMdmg0cGlJaGFRdEttaktQTlphMEs3Vml4cW1MMXY1eTU5S1dtbDRfRXREd2hmM3FRMGdBMVFjUmpqSlJZMUtOVjUzbTdaVTVUT3I1NDE5cWljc0NGaHFnZ1RVM0RWQUxBU0swOE1Ydk1HVDlvRU9GM0htOVdxeWZRRXRNWjVRbF96MVVZQzBsX2JfNlNLTDlaYk5HWm9fS2xQeExiWFNBMmh5UHlBdGUwYlozX0ZCU2ZxUzBjcmNQUG5PSzdkQW91cEppOWNsM1ZIWQ?oc=5", "source": "The Economic Times", "published": "2026-10-30 10:35", "score": -0.103, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex, Nifty extend gains for 2nd day: IT stocks lead rally, broader market underperforms", "link": "https://news.google.com/rss/articles/CBMiwAFBVV95cUxNUzFDYmRlTTRKR1BhNDQxb3lJc1ZER3FjUXB6ZFVQV1o5MHZVVk12ZS01ME1iVHZ1NkNWOGNHS2N2YTBWZzFRS0luNkRwUllwcDNYNktWWXNwaTFQdWk0aDlsQmUyQzNhMXowZnFkbzg1UGI2NHlkc2tldzhPYy0zc2tIVmw3VUhXMVRtbUxnd2pTdEdsME12eDM5VlBGWEZXNzFHY08zTl81am9jQkJTZFVzSVdMX0IzaTVZcUNGb1Q?oc=5", "source": "IndiaIPO", "published": "2026-10-30 10:31", "score": 0.84, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty extend recovery; what's driving this upmove? -", "link": "https://news.google.com/rss/articles/CBMilAFBVV95cUxORUxpb0U0WlRwTF81LXhEQklDb1lULTAyRHhKbzE2MDkyblBpNzg3QVJ3YlVTTG5zZ1RMSjlpaG1TUk1JUXhhZUVKTTE5bHJqMm1KRmpLUm91SGtibV81VURxNXZnd3c5YmRNcnpVWDFqNGJvaXBYXzdKd0NWSVlzMTMzVnV2Q1lIQWFPRTM0OEgxTDFl?oc=5", "source": "IndiaIPO", "published": "2026-10-30 10:31", "score": 0.527, "label": "Positive"}, {"symbol": "MARKET", "title": "Markets reverse last week's losses; Nifty crosses 23,000, pharma jumps 7% weekly", "link": "https://news.google.com/rss/articles/CBMiuAFBVV95cUxNdW5ud3NiVkJObS1vS3V4YWtacEFfYjNtX05KeWhyb2VacUlHZFc0UmF1Z0pBalhfRVNwampJb0VodkJ1czJJaV9INE8xUWVVRlkydGdDYS1zUU1lRWFmRjFUUktwa0U0a2d3VVU4VmJTaDBFRnVhUFZBSG9vVnpYV2NaSGRJZUFva1B6U296UzREYmlqcDF3RjhTU0lzLWh0cXFSazdFX3hHY040aXNjd2E5cTJZSWVk0gG4AUFVX3lxTE11bm53c2JWQk5tLW9LdXhha1pwQV9iM21fTkp5aHJvZVpxSUdkVzRSYXVnSkFqWF9FU3BqaklvRWh2QnVzMklpX0g0TzFRZVVGWTJ0Z0NhLXNRTWVFYWZGMVRSS3BrRTRrZ3dVVThWYlNoMEVGdWFQVkFIb29WelhXY1pIZEllQW9rUHpTb3pTNERiaWpwMXdGOFNTSXMtaHRxcVJrN0VfeEdjTjRpc2N3YTlxMllJZWQ?oc=5", "source": "NewsDrum", "published": "2026-10-30 10:30", "score": 0.44, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex Today Ends 308 Points Higher | Nifty Above 22,300 | Vedanta Oil and Gas Up 8%", "link": "https://news.google.com/rss/articles/CBMi2AFBVV95cUxOaVVsSnlXUHFmTWxXVlZSNnRHcy1zRW1wbUdOZmZRWG1DQmlBbVVSWmJIdF83V0VObkV0NVh0T3kwQ0Z3U2VuV01NSUxTU1drMldDTnpjVXF5a0d1ZldaU2liWHNaRlMzazdiOHpiaDdFeVBrbGJORWN5MmtUTk44UVVGZVFmaDJZNXdmekEwS05XQzNDbGxPeDZsWFd1amQ1YUxQd2w3VGVZUGtaTHdGUGdoemFLVUlqcU1aZkhJMUFKQmlqU1pmcXdfMEc4ZHM5U25iX3NjOVY?oc=5", "source": "Equitymaster", "published": "2026-10-30 10:28", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty close with gain of 0.5% as IT, pharma stocks rally; weak broader market limits gains", "link": "https://news.google.com/rss/articles/CBMivwFBVV95cUxPZW9rV0NJRXU2T002TkpGY3BBMWpjYWJMLXNYOUZ4bUQwZkw4UU1ZMmJLblFRZWhpdmZUc0VPYVp5WHVDMTRFZnRsNkZzQjFlMUdlMGgyQy05bVpVa0lhaU9PSTlXU2ZTYWdIUVF3ZEV2MFB1SGVtbk9LUWhPWWRQbVlCbHNTbVRZZW40QW45R1hVVkcwc3VWemxkRUdieTA1YmhHZVMybTBWNW5OTnJzcTgzOHVkbVlGbzBxSlpxUQ?oc=5", "source": "ChiniMandi", "published": "2026-10-30 10:26", "score": 0.796, "label": "Positive"}, {"symbol": "MARKET", "title": "Taking Stock: Nifty reclaims 23,000, Sensex gains 308 points led by IT, pharma stocks", "link": "https://news.google.com/rss/articles/CBMi4AFBVV95cUxOOVBXVDRvbFRPVGZUMlYxdWZuVVJKMUxjOWw1blFmUW5JQWFvYzFmd1pGVldOaWhSd2NySVF0NUs3V25BNlFKMnhrM0dRVmtRMU1IYmhtbVlPamRBejdHYXZ5XzFnd1JJdkk0Z0dGV2NYZ1JmNkhBVTNvV2xnc3BSb2FFaFdNUXdCWkJQU2V4V2JDMG8weXVyYmJBUHZZdndmVE5lNXNGdmtxeTlGVXl3ek1BN1k1bzJ0WGV2VmFYQ2h6SjVLUEQyT2JUeV9PZWRaUGFBTFNmSnUwSEZCOWFIV9IB5gFBVV95cUxPSU5LVTJRUC1YUEVNeHNUemEyUmRkd0JaT1hqbFlvZVBCWk8yMWtZY19sR3dnekgxT2FCT3pKaUZfWkMwZjdKYWtCUUlSZm1GaUcxbzdUSmN2M0RudFF1dHJHVFQ4UlVldnc3UE5JWFJ6T19OU0E0X2JvZXF5NTM3RGFmYWlTam1xTnE1bTYtMlFtcmdTYVBlOWtFbGxvQ2xNUThNTzZMei1obURvZ0s4VGFnazd5WUVHRXZFR0pERExITkhhc0VFM0VVbG9sWEtPb0xrd1F4TlUtYkc5bTY2M2M5ZVZ4Zw?oc=5", "source": "Moneycontrol.com", "published": "2026-10-30 10:21", "score": 0.649, "label": "Positive"}, {"symbol": "MARKET", "title": "Closing Bell: Sensex rises 308 points, Nifty tops 23,000; IT, pharma stocks lead recovery", "link": "https://news.google.com/rss/articles/CBMi9wFBVV95cUxQc3JkY25Iamc5akJlYWgxSHNJMGJqQm9iSWtwWThPZWhnczU4YnJJOC1sdGZMOERMeWluV0FkVmV0QlNxQy1mVG5xMkRWSUVEdE0xYk81QjcxdXdra1kyTk1lZlc5MFV2RnQ5d0hOUGdXQWNBSUIxUWRTc1pMcmNfakNUOG5HcTVaNlBFblI3R1FUX21PbDNJY3I2Q2o3Rnc1OTZDVzI1TG10VUpUS0pLdWJMS2dLY1ZSSzVTdU80MTZlUFFPSEdKN3V1VklZZm93RmtzcF9nNTBsM0FFdVhfY01UamRYRkpWVlYxcDJmVkxMUEpJdmkw?oc=5", "source": "Zee Business", "published": "2026-10-30 10:05", "score": 0.718, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex ends 308 points higher, Nifty above 23,000; Trent up 5%", "link": "https://news.google.com/rss/articles/CBMi1wFBVV95cUxQMlVJODZONnhDZU1vT2d0Wl9ZMEFmZkN6RGFrVU95R2RqanBoZEpCSTRZckxNcjVOTDFoY1FyaGE0RF9hS3UwVlptODRfMHFoY0Rvd0l0R3JJTUUzTExBeVc0RVFNUElyaGkybHdwZHByWjF6Nld4VWVCRHFEQ3l1UkQtSHB0M1VrZXB4MTBEWENzUnowS1I2c1BOeGIycEJWSmRScUlFQnc2N1VwVmlGd3BSX19iNEp4SWxNMWJiV0hXZHZ3NDIyQlg2NnQ0N09XWWZTdHU1UdIB3AFBVV95cUxQSTJkN2R1WXNmVVFmNE5GX1M4RHhod3daU2k0emQ5N0lWdmZxcXI1VDFCWDBkcDg2eGZ0TWV4R2ZCOVdtTC1leTBaOGRnaFd6UHRhbWhUNVBpRzhib0F4RWNybFlUTlBMamtLUXN4VXlOcUZTT0FBZ21Wa1hUZ2FYZUgwSDVPVGFjQ2R5ZXh6OGtMWGlzMUI1SjJQR2NaelFXTm5nZU9jVnBSLUtjTzhqZVlMWHNTc3FjSm1pekpVRFd2TTdLci03cGozMjhoczAtQ3pENXNoZ056d3dM?oc=5", "source": "India Today", "published": "2026-10-30 10:03", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Market Wrap: Sensex Gains 308 Points, Nifty 50 Ends Above 23,000; Trent, IndiGo, Infosys Lead", "link": "https://news.google.com/rss/articles/CBMiiAJBVV95cUxQZTFyMk9sdFl3QmJnUDd2OGhhdDNIZ3FwcDQwclFmNE1Ba3ZsakV0RzN0RHlKUkRYZnJST19SVDlqZmp5UGV0OGdOYzlLTkNNMTFqaEhNZGQ5cmctT2JzTEtZNzk4N1lfb2lyc2NuVU1ETHNWU0ZBZWpxX29hVWxxNUp4VE5pNndCVFVDeWtmZWNPQkh4U2xFeFp6NEd0am1jV2FBSWZIb215bUxTVnc2LTdhQ0lmM21KSHUtQjVSVlVpajhPdkZYdHQwTEgyc01tMFdxLXZBZkUwSUdGdXNkUjl4NGVMeHNWNzVROXhhSDUxT1BJSXo1enlzR3VVNXpyeWRaeTc4YmLSAZACQVVfeXFMTUltcFpOMzllTWlGSzAweENGY0Nob0tmTk96eV9wOVB1cGlDeTRuN1hRRFI4RS1KTVoyUW5xdWxpU24ySVIzWk9JV2F6bks2bVJ4TlZidVFqQk1LU3pOYlNEV2Qyc1JVSGlhVDhyb19xQlpQbWFmUmdXakhsUDZtSUEzSXlnQVA1SEhXV1BzZURDVnJablhfSk1FUzVCSmEwQmpZczltQVRON3otMzV4MnUzVGxsTlNJMGt3ZU5fWlhrcU53YzdHTE92UGx0QjdBTkdfOUVobGVib3VCcDR2MGZ4Ulk4R1haZkJZdEQxalExRDZqT01DMjlQbEE4RVJ4b0Z0UGh1c05kX1A3bnNOWFQ?oc=5", "source": "NDTV Profit", "published": "2026-10-30 09:52", "score": 0.649, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex Rises 298 Points, Nifty 50 Crosses 23,000 as IT Stocks Lead Gains", "link": "https://news.google.com/rss/articles/CBMiuwFBVV95cUxNTkdfNHBGVl9UeTFzNGUtdzRHMk5xb3Y4N0VvTGkxWUZ1WGJuNm9FLUtBRWxuZUE4QUVQT2VYOFpSTXpDOHJ6b1VrUXZia3E5TzdCdTlOUnhXVkNVMW5GVEJmQmZuWDlieDl2VndJTWYzRF9rZ3I5LVVfb0ZpbDBya2JrdHBIdFQzZUROemVYUU5LSjAwMFVaellUbWVnMkYyMUFTam9WY25YUWd3NFNRUHE5MkRGTW82TTJN?oc=5", "source": "Dalal Street Investment Journal", "published": "2026-10-30 08:59", "score": 0.649, "label": "Positive"}, {"symbol": "CPPLUS", "title": "Aditya Infotech CPPLUS ESOP Allotment 48,100 Shares Oct 2026", "link": "https://news.google.com/rss/articles/CBMiwAFBVV95cUxOUHlaMl84Z2E4T0RVUE5PMW5FZjVuQW1RcjFVTXd2ZUdMdmE3dXpNTURraTVmWHJYd2lQbG5fQVh2ZE1WVDlob2NDR2I2YWRQMVRLR0t2YVRaSVlYWXBsVXJoS2YwUENlLXducG1jaUtKbXNlUEVHQy1RT0JXdXhLZV81UklYZzFuMmFMUFFuRS1sMkRaZGgzRHNyMk9Yek5sdi1oNVZXbmdxTDhyZzlhODVKX1pmS1pYODc3MHBBT3Y?oc=5", "source": "Kalkine India", "published": "2026-10-30 08:44", "score": 0.0, "label": "Neutral"}, {"symbol": "AETHER", "title": "Aether Industries reports robust Q2 FY27 financial performance with \u20b93,472M in operating revenue", "link": "https://news.google.com/rss/articles/CBMizwFBVV95cUxQaXBiV3ZRODczRjJseWRyYjk2WlFLdHd1ek5tSHNjR0NGRGVIV09hM29yRHZLUjRxaTMxeU9fMmN0bFE4d3k5a0hMWk42TXVVR0NZMV90Zmcyc1p2NHJNRzRnT2NMN0szWFRTcm80TU96MTlGdXZ4UEs2U2VYaGZmUUdGdGdtNE5YVVRTdVNOSXpsYUpQTEdVMXU2NVNBbHR4RUNNQ09WaHIwSVdtRjM2Qm5RNjV0cGk0ZThLblZOLW1UbGwxYjg4RFN3QW1kOE0?oc=5", "source": "Business Upturn", "published": "2026-10-30 08:35", "score": 0.421, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex zooms 1,200 pts in 2 days, Nifty tops 23K: Why are bulls in charge?", "link": "https://news.google.com/rss/articles/CBMi1AFBVV95cUxOTDJ1dFlKVkRQMEhPdHhUbGlyTHk4ams1Y0EySG9zRlhkcWpORm1FUzdwWDdtVmZRT2s1YWJJYUpDU3h6UUt6Y29DaFJsMFpmZkwxMnk1dnNGQ3kzSlNfNlZoOTVURThySncwaUZ1cDJzeGU5NlN2NV9aeWROd3RuWTItcmtlNUE5WkZVbi1wUUtobnJzRGp4SE1PcUtPaTQxbnVDRUdTWFpQTGZjMzh6dTJ0TzJtRVNMbUJMVmlBTlFPTXQxX19QWktWUEhWM3ZkNm51VtIB2gFBVV95cUxQcjQ4VkQzSUZjUnlJeGk3b3ZFQk5QYVM1ejM2X3dZanFHNFhOWTFJME0teEVXZFRQZDgzMzktem9uMWc3ZXphVVJJUGwzUG1KVnpKVi1Xamd4cy1qM0hTYUR6OTVSa2ZUQ1E2S3dwWHV3MTByUGtFQS1seXl0SWNUXzhxeFZ3UEZIQVd2V0w5NlNNeHgzeUVHYTV4ak1iYW5IY0IycU4xYnJ5dGxxMm1QSFdQTGpQYWE3Y2dUekVadEVSeHZYc3c1UDdmMDVJd3hXbjlMRjItUlhBUQ?oc=5", "source": "Business Standard", "published": "2026-10-30 08:02", "score": 0.718, "label": "Positive"}, {"symbol": "MARKET", "title": "IndiGo, Trent, Vedanta Power among buzzing stocks as SENSEX gains over 500 pts; NIFTY trades above 23K", "link": "https://news.google.com/rss/articles/CBMi8gFBVV95cUxQVWhkWWtVc0VYNGNZNEZwLWxOVklBeHdGYnpsM3NiVnRtUlYtNGlwWHVzNWpZUkdnRjJmUVhiT2g2MFEwN2o4SXNwM1ZSOGV4cnEzb3lOUHJDbVdYcnJiMDBVbFB4cHo4Und1XzdMRF9uWEo4ZDRpSks0SE1GUTlFX251ZGNfWVZ2dEw0QklyVmZZR3g4X2dSNWRNOFcxXzJUbnY4WXFqeXVSRUdfVFBNUm9ZVVp5UGRCNG1PaHFsUW5BOVJsTHFPSHJvTlBxd0VIZW9NWkhfUkJGbEFKOXRER0ZBdkE1VDdoNWhyVlloQWlOZw?oc=5", "source": "Upstox", "published": "2026-10-30 07:52", "score": 0.721, "label": "Positive"}, {"symbol": "MARKET", "title": "Why Stock Market Is Rallying? Nifty Reclaims 23,100, Sensex Surges 500 Points; Three Reasons Why", "link": "https://news.google.com/rss/articles/CBMi1gFBVV95cUxNT3ppT2hyUUlUTExXYmkwSWM5TTRRSGd3d1ZzTk5rU1kxU2pRQkZQX2RybGhkWE80aUFRc2gwZ3MyczV4Mzh1emRfd0h5QjlOOWN3S21ZbFkwODVqOUs0b0tnbzNNd2Y2ZENQXzM0WFNxUTZLS3VMUFFidXR1SjdFb19hLVZIY2JxVHZPVW9CMVc1S0cyb0FCOW5ydENoQ1ZSYUVuaGJBY1l6U1RjQXF0c3FYU0VXbGpnLVhkTEtyc01yM1hZTjRvbnpPMEpVNE9JMkRqaVRn0gHeAUFVX3lxTE1JUmRUNjZycl9ZN1RHazZuU2VHLUxzRzMtZWF6Mzg0X2dvOHNhMXYzeUpzc212SU5wdEN6SGhLd1g5ZTNER3pCalNkWnp1NnN4MnNYNi00cVdwZUdyUFRrZnFDdHllaUxYVGFnZy12WEJtMHNGSUxrbkJ2YTZ4djlYWFZ5czdKUW80aFV0YXVjTThZc0tFNmJ1MENSRzZkV1FyMTZQMTc4LXZSWHYyNC1UeFhHWTJaUFM3U2RuZ29HUWVLa3JudW9rb1EyQU9iS3dKN0dxSnNTR1ZHNVRqdw?oc=5", "source": "NDTV Profit", "published": "2026-10-30 07:31", "score": 0.71, "label": "Positive"}, {"symbol": "MARKET", "title": "Passive funds could buy up to Rs 36,500 crore upon Jio Platforms' entry into Nifty, Sensex", "link": "https://news.google.com/rss/articles/CBMi6AFBVV95cUxPQml6RHdZS2FTeE1nN05IMHpUTVYwR3BxdXhNRVViWjlzSExMb2ZsRFBGZmc3bXZRbDR0Z2ZZVkNhclFpRS1tYWtfN3RpM18waHFDdkRzR3FWeDllUFhvb2JlaVQ0RkozVWt6b0dwS1VWRk5zcjVaM09RUjE4ME1rNmZ1WkxqVl9FVm40ZmVoeEp0X25uTWN0Vm5PLVV2OGpLaTF6X1VuNW5kNUVwU1FtclNGdU94LXQxdUozUTNwQnVDQzR1OEhCcVhpNWpOakxseUIySzRrdWMycFR2TWRRSUtjQWdCZUxh0gHuAUFVX3lxTFBvVWFETnc5Y1BDWk1YWmhPdFNTbTZESnpWaHNVSTRoTWJHVlBONW1yVldTVThqckJyTURkTXotaVRCX3lOZ3o0QlRINTZJcnY2SmI0R0JuMkdjV21jVVJrcG55Y1lrM0F5N0NUS1pnODZNTmRIbVRLYU5nbXE3UmZyb0hERFNBdTJ1SEdTLUluV3FldFF2VVd1d2lucXpUcUlxNVlnODdqdkN2UjE1WmNfWlU2NWJLelpwSXptX3hKMGpjQ2xaOVFDdW5hd21UMktsODRIaVdmY0ZoZkdhQnZvaC1Ha01SN1JlVV9TR2c?oc=5", "source": "Moneycontrol.com", "published": "2026-10-30 06:40", "score": 0.691, "label": "Positive"}, {"symbol": "AETHER", "title": "AETHER Share Price Today - Aether Industries on NSE/BSE", "link": "https://news.google.com/rss/articles/CBMiXkFVX3lxTE5YVWFUSmNPUGtKRF9jY2EtNTNkS1lUVHJYOFgzZWJkY3NrY1lucDJqajdnSjhJTFZuSkZMSjhwSUp3UEs2cDZtNTYzd0YzbEs5NE9IRy1VQzgyWm5YTVE?oc=5", "source": "scanx.trade", "published": "2026-10-30 06:37", "score": 0.0, "label": "Neutral"}, {"symbol": "AETHER", "title": "Aether Industries Q2 FY27: Net profit rises 26% to \u20b968 crore as revenue climbs 24% to \u20b9347 crore", "link": "https://news.google.com/rss/articles/CBMi2wFBVV95cUxNbVVVa0lsV1JvNU1BWnlRVFJSNDQ2Y3l5Z0xwZWdFS2JSTkJPbkxlN2ZfNE1ZZ2hVa0EwMVZ3enhwOGNTQ2VFRC0waFdOckhEaGJ5RDctUGg4UUEyNE9La1BweFVkeWNya2h0SFZ4WVZhZlVLTjl2cXhLaURoTkxSMXd6MHVVTmtYZk90SUx1NmsycU1KMHZKZVItNWRuR29pYy1KWTVEMWdPdGVQcHRQMXFadHJ2TFc0UEFjVGpKM2s1WTJER1RJV3Y4eU1GMmItSDNpR2hBZlRNdkk?oc=5", "source": "Business Upturn", "published": "2026-10-30 06:35", "score": 0.612, "label": "Positive"}, {"symbol": "AETHER", "title": "Aether Industries Q2 FY27 Results: Revenue, EBITDA and PAT", "link": "https://news.google.com/rss/articles/CBMiwwFBVV95cUxNLTdIWDMtbG5YaEVpMVZSemJTMzFndWU5OVVkcDJXdHpCeU9ON2JtcGRmNmJESXByQ3ZWYlh0bDZuWExfOXhtQXVhc2U2eThtZ2psXzFKS2NKS1VXU3lPNG1uNmlfWUE0aUlWVERSdS1RTXpGZkVzZlRfWXhhcDN3dGktb2JwdjJHQUM5YTdTZU43RkZGM3Q4RTZKc09HTzFHTlNmNlZpcWtKSi1Ia0hyMWNUZEUtUy1GWXdFMlVPRWNVQ1E?oc=5", "source": "Kalkine India", "published": "2026-10-30 06:31", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex Today Live: Sensex, Nifty Trade Higher; Trent, IndiGo Gain, Coal India Shares Fall", "link": "https://news.google.com/rss/articles/CBMizAFBVV95cUxOcXdkRkl0dlpWcXlSb1U1T3BxdXhIb0x3Mi1PUUE4QXh6WWNkREVUTWV0djV4MFBUSVlLZk54SDlsbnFsNGg2b0dnZjh4b193bXpzRndMZHZpUjAxb3VTam5mc0J2dEdWOVNNLUt</t>
+          <t>"src": "bhavcopy"}}, "CPPLUS": {"2026-10-29": {"open": 3985.0, "close": 3951.7, "src": "yahoo"}, "2026-10-30": {"open": 3932.1, "close": 3811.5, "src": "bhavcopy"}}, "THANGAMAYL": {"2026-10-29": {"open": 4681.0, "close": 4630.5, "src": "yahoo"}, "2026-10-30": {"open": 4620.0, "close": 4455.0, "src": "bhavcopy"}}, "KIRLOSENG": {"2026-10-29": {"open": 1907.3, "close": 1890.3, "src": "yahoo"}, "2026-10-30": {"open": 1884.0, "close": 1796.1, "src": "bhavcopy"}}, "SMLMAH": {"2026-10-29": {"open": 4770.5, "close": 4848.0, "src": "yahoo"}, "2026-10-30": {"open": 4918.0, "close": 4724.5, "src": "bhavcopy"}}, "AETHER": {"2026-10-29": {"open": 1590.0, "close": 1581.0, "src": "yahoo"}, "2026-10-30": {"open": 1597.4, "close": 1616.2, "src": "bhavcopy"}}, "SBC": {"2026-10-29": {"open": 65.39, "close": 66.52, "src": "yahoo"}, "2026-10-30": {"open": 67.05, "close": 66.15, "src": "bhavcopy"}}, "SYRMA": {"2026-10-29": {"open": 1563.0, "close": 1669.0, "src": "yahoo"}, "2026-10-30": {"open": 1675.0, "close": 1625.3, "src": "bhavcopy"}}, "TDPOWERSYS": {"2026-10-29": {"open": 719.8, "close": 719.45, "src": "yahoo"}, "2026-10-30": {"open": 705.0, "close": 713.9, "src": "bhavcopy"}}, "RATNAVEER": {"2026-10-29": {"open": 345.0, "close": 352.85, "src": "yahoo"}, "2026-10-30": {"open": 354.2, "close": 360.25, "src": "bhavcopy"}}, "NIFTY50": {"2026-10-29": {"open": 22690.65, "close": 22936.75, "src": "yahoo"}, "2026-10-30": {"open": 22964.5, "close": 23053.1, "src": "bhavcopy"}}}, "entry_override": {}, "news": {"fetched": "2026-10-30 19:42", "days": 7, "items": [{"symbol": "SYRMA", "title": "JSW Dulux Share Price, Stock Price - NSE/BSE Live", "link": "https://news.google.com/rss/articles/CBMid0FVX3lxTE9ZY2VvMlBJUE9CTHlXTmN1RXVwUENwel8ycEZCaF9DXzFLNjZqNDJteV94NklGRlNFbWwzS0ZKX1hsdW5SbHhNZkZZS3VUelJhVnMwUHp5ZHVXUGxjRGE5dTZjSkxhc3VxeENXMnV6MlVqcGcySGZJ?oc=5", "source": "NDTV Profit", "published": "2026-10-30 18:13", "score": 0.0, "label": "Neutral"}, {"symbol": "SYRMA", "title": "Syrma SGS reports best-ever quarter; Q2 revenue up 73% to Rs 1,999.5 crore", "link": "https://news.google.com/rss/articles/CBMi4wFBVV95cUxOX1lzeEswS005dk5yZEl6Z0pvX1VQbnp2RzBnR3JvdFVwanI5V2lFdHlTcE02Tm14Mzg5MFN0blpUcm54YnNjY3dsSVJSSEpLaXQ3ZHlocnpLYVpIVVo2NkNxRVVEZTFmT29UOHFIbmNxS1VlUnN0SW1oMXl3NzZyUGpBU29HVWd3c2dNVGFhNWtxNjMyeHlsTEc3NmxmY3Q5LUF3TE9GRkpoZFByd2ZEeG1fb2liWkJaRUMwUTFiZWptOWFXZXJIeUxKQzg1ckpoY0NIUzhtVXNqMHZvS1VJRWtnUdIB6AFBVV95cUxQNWpYOU5EY3MweXZaRE53azhMcEpJRG8wNzlVcm1DY0xiZjhNa2JQaGF5bFlad19ZNGpQcGZiR3RQSk1hNnZkdEllZWdKRVdJZnZhb3dwZzgtY1dfVklxc0k3NzVPQ1h1VElTQkxSbGNMZThoNDJaNG5DQV9kbGY2U0ctaTVBZXc1cTM2dkVzaWc1NzVLYXo5WWJVcWhVdUpXS2pzRS1LT3VDT3B5Ym5SNjNlbk5CcHJaaWdiOUNZWGxNOHExX0lLLWo4S2c0eF9DOGotTkZPdzR4R1lYN0otRURMdXBRRi1N?oc=5", "source": "The Economic Times", "published": "2026-10-30 16:35", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Indian Shares Snap Two-Month Losing Streak, Nifty And Sensex Gain In October", "link": "https://news.google.com/rss/articles/CBMizAFBVV95cUxOWWxJcWJZM0t1RFdIV0ZTRkVWZzVHZkluTlB1aFZmVC1KeUhaSS15eDN6QnFHb2hBYy1HdHRQV3Rjb0xOOUpPMlBZRUpEcGtUaFA4YjNISVpLN0NHZVVqNElaXzFvTV9KUTJWVHJiaFlkbXpLTEpiNDdLd2VkNEU5bWQxdnVZUThmVkNseGVEa1VpQnhhUEN4X1hYY2ZGcGNWb25LdzFOVzhNU0xvVWNITjNnRHJYekQxNm10ODVTTFVtRVhGSEFxdEluLWQ?oc=5", "source": "TradingView", "published": "2026-10-30 16:01", "score": 0.361, "label": "Positive"}, {"symbol": "SYRMA", "title": "Syrma SGS Q2 results: Profit nearly doubles to \u20b9117 crore, revenue jumps 74%", "link": "https://news.google.com/rss/articles/CBMirAFBVV95cUxQWWVNajdfcWthd1FGS3dENzdIeWltVzdfWTRueHBPYlFWSEs4MHNnOW9HQnVWODIxTENyb21PblA5Y3d2Ym4zeVkza29VZ0VQSENCb3dhUVQyN1N4WFlGWnNTaUt1czBRWl9NTy01UmU0bExnQXZKMUhpeW8yUU9GT0tPbDFpeHh6em5GZzNZNzZTYUFuSkR6RlFwS0Fwcy1SQjZLSHdDdTRFaTZm0gGsAUFVX3lxTFBZZU1qN19xa2F3UUZLd0Q3N0h5aW1XN19ZNG54cE9iUVZISzgwc2c5b0dCdVY4MjFMQ3JvbU9uUDljd3ZibjN5WTNrb1VnRVBIQ0Jvd2FRVDI3U3hYWUZac1NpS3VzMFFaX01PLTVSZTRsTGdBdkoxSGl5bzJRT0ZPS09sMWl4eHp6bkZnM1k3NlNhQW5KRHpGUXBLQXBzLVJCNktId0N1NEVpNmY?oc=5", "source": "CNBC TV18", "published": "2026-10-30 13:51", "score": 0.66, "label": "Positive"}, {"symbol": "AETHER", "title": "Aether Industries (NSE:AETHER): What Do Aether Industries\u2019 September-Quarter Results Show?", "link": "https://news.google.com/rss/articles/CBMixgFBVV95cUxNb3lGcXBYMGhGTkhHcVNBUFRETjZsYWl5eDRicWZEU0hTLVo1bHB1UDFFNHRPa3NsaGM1MzlmU0ptWnUtNzJwTWVCTDB2RXU3cWVvblI1UjZhVkZEb3pxVXJnUVlvamRDaTRUcVh5S05ubGhydDhkU1hNR2hOLVZldzhfbktjM0VJU3V4TTBKaS1ycUtvX2pQem4ycUNuN1NmUHU5cTlwLTctT3RQR0ZmZlVaSTNKcW9veHUyQVh2Nmx1dlFPRWc?oc=5", "source": "Kalkine India", "published": "2026-10-30 12:34", "score": 0.0, "label": "Neutral"}, {"symbol": "SYRMA", "title": "Diwali 2026 Top Stocks To Buy: Apollo Hospitals, GE Vernova, TARIL, TD Power, Jindal Steel, others; top 10 picks, target", "link": "https://news.google.com/rss/articles/CBMikwJBVV95cUxOejZuNVZHYUg3QlloRzQzYXBzbjR3OFdESEFXaU1ZaGg4ZU1YMkExbUpVNHZ0S1JCUEZQNmRKVXVraTVxNjAxcnc2MWhPamFkclpDVGNEZDlILWhBdmtzQy16RHVJaW1wQjdtbmN1TUVUZDBudlMtNnNfcXdWMEV1ZWphaElvTUdTeTBsNDFYbEs3UEFHMVMySzZCVEIzeUYwR3Y3bWdPQmVfcHBlOG84Zkg0aGxLMmtLVDhzQms1MUNnWDRXYmFjbnZWQzU0SC1Oci1JXzBjbnQ0UTBJU1l1MWJ4MTd4TV9NM0FVSC1LRV80c1Q4QllyS01NOWFHVUZpMXdkdEpSNmt0aEg4WVl4V2Fwc9IBmAJBVV95cUxPQjJxY1ZBR21RVFNpWE1vR0pkOVA5Z0RUUmFZRDZ4dS16TWpjdzFzcjM0QmQ3bVkxWV9fWmdIdXIzdzA3MFZHUXNIZm9sdjUtd3cyUl82V1RKRTlZVHBMQjVNeFdXWmp6U293TS1WYnpiVzJhZlV0UVZGbTJ6WldTVC03bmhmYlhobTJJNlRUd2VucW1vRlpPRElMelZneGJGdzZLWmRVMWxSd3MwbXpKVXBEQkdMVEdsNWR5c0NXT3dGRVlUSEFGZ3licnVTbllGbnZ6VFBCNGxmZk01cWJjcVpqQW1TZGlmNkE4RUlwdDVyRDhoZUJmaTNLNVpBQ3JRTklFX2dkM2lIcnUxNXlxZnBCemtMMThQ?oc=5", "source": "Livemint", "published": "2026-10-30 11:14", "score": 0.66, "label": "Positive"}, {"symbol": "MARKET", "title": "Market wrap: Shriram Finance, Nestle India, Trent, InterGlobe top gainers and losers on Nifty and Sensex", "link": "https://news.google.com/rss/articles/CBMingJBVV95cUxQNWQ5WS1pSUV0c0k1UDRCeWxBMjNfVDZWWXg2UUJXLWJIUjUxQ2pwb0NBUk1sRDh3MkJRSVZpZnBzOWJ5c3k1Vlh4RW9DUmpROUdjQUpGMm1oSDMycTlMOU1RU1ZjSTA4REhOb0o3c0FqYTFuc29VaTRBMkd1Mms1aVF4NW95dHVaME8ydXp6VDVVU1BTeWFFanRSR2dhOE9PdWU1MWY3dW1QSi1aN21UemxxdXptbHE3Q0FNWVZqN1JXTnBEVzJXTV9jdXFId04ta0ZvTGdCOFRZcnU0WjlGYkdQQlpISlNxQi1XY09zYTBaNVZLcEVfVVpWdUJaYzNBd3l1alEtYjFXZzVETzFodUk3Wk93a3lVX0I2R1ZB0gGXAkFVX3lxTE96bkJGNFNzdEVsbWxGQzJDYjkwbkRtNjVjZnR5MV9TQlB5cHR4a2o2eVBhVW83T09YTUZ3dkdYTnVRVmlPaG9aNXVCbE9tZ0hFalhVamZoN2VGc3VNU01FZGVxSWtELWZhaXEwYTRjdUlhQzR5OGw5WW9ZWjhzNXVRYzViYV9oZ3NuUVlGbFNfQ3lHQkE1ci10OTBjRkNqR1hhZXk0WVAxZUVYSGhwUFpIcDhiQmZxYWZuODM2eEhFUXQ3ZEFsME8wdVZ0OVB3NVJoWU1iV25tVWdJT1FINklXT2JhTXM2NDFsT1JFVXphUUZLOTZ2OHVLejdOTzRsdkc0TkxVeGctbkwtVVlxUDRhb1pJVDJWMA?oc=5", "source": "The Economic Times", "published": "2026-10-30 10:56", "score": 0.026, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex, Nifty Rise; IT &amp; Pharma Lift Markets as Midcaps Slide", "link": "https://news.google.com/rss/articles/CBMisgFBVV95cUxOajFHdFZlZGo5cUk0dWJ3V1E4c2dCUFlBVFVMZV8wYklSQzVtUEJKRDZVSFhIdHRIUDUyZGlHc1ZWVC12bGwzMTFtSEpqdWdpYmowZmRqQ2ttVWVuaDRVOTh4b05lUVBQR2JYeUNjWDRjcjRMWExJSEFhV2lKRFRoUUVmaWFtSDBYdjBldjI2NWdYUlBHZXpUX1FRVXpwaXZucGpuQWlRLWxrdkJoWmRRblNR?oc=5", "source": "HDFC Sky", "published": "2026-10-30 10:53", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex rises 308 points, Nifty above 23,000 even as broader markets crash. Will D-Street bulls extend reco", "link": "https://news.google.com/rss/articles/CBMipwJBVV95cUxPTXhsRWN1cm45ckpDbWUxY21qclNKLTVCeDlaUlJweGFFUS1qSG40b09sNVlzTFBKQVNPZzU4R3VSSGZuNF96dHFPVVFDQmFOTy1YZU43YjJaRWpCczlrZkViZ0tTSS1lN1VzSUdrbHFoS01uMW9vRjl3MWRzSnZiSkd2T3REMjBBUTYwY29vOS1xSDNndVhFT0RNdjVtN1lFUkljSlE0cjR3ZjJqRDZodXBuMlpmSGJhYklpRnAxYktzS0hhYWJoRUJUWWUyeWlScXlTVk05VkMtazRESVQ1STE0TU1Cd0Q5Z2NHcXdZWm5XeFpaMHFJUm9CalNmMGdYZEpTS2ttUnFvaDFjVEc1YzhEb3NLSWlMRHYxUXVwaUFWQTZXZ0lR0gGgAkFVX3lxTE55RHpQVXVLRUxDYkNVYmFlZ2FlbU9vdnZVNTBvUXhZSFJBaHpKOXJ6dnE1aVpGSXlZeGdGaUtmMGN5TVdHX21JYkhuVXgyWmE5eW9UcEhMdmg0cGlJaGFRdEttaktQTlphMEs3Vml4cW1MMXY1eTU5S1dtbDRfRXREd2hmM3FRMGdBMVFjUmpqSlJZMUtOVjUzbTdaVTVUT3I1NDE5cWljc0NGaHFnZ1RVM0RWQUxBU0swOE1Ydk1HVDlvRU9GM0htOVdxeWZRRXRNWjVRbF96MVVZQzBsX2JfNlNLTDlaYk5HWm9fS2xQeExiWFNBMmh5UHlBdGUwYlozX0ZCU2ZxUzBjcmNQUG5PSzdkQW91cEppOWNsM1ZIWQ?oc=5", "source": "The Economic Times", "published": "2026-10-30 10:35", "score": -0.103, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex, Nifty extend gains for 2nd day: IT stocks lead rally, broader market underperforms", "link": "https://news.google.com/rss/articles/CBMiwAFBVV95cUxNUzFDYmRlTTRKR1BhNDQxb3lJc1ZER3FjUXB6ZFVQV1o5MHZVVk12ZS01ME1iVHZ1NkNWOGNHS2N2YTBWZzFRS0luNkRwUllwcDNYNktWWXNwaTFQdWk0aDlsQmUyQzNhMXowZnFkbzg1UGI2NHlkc2tldzhPYy0zc2tIVmw3VUhXMVRtbUxnd2pTdEdsME12eDM5VlBGWEZXNzFHY08zTl81am9jQkJTZFVzSVdMX0IzaTVZcUNGb1Q?oc=5", "source": "IndiaIPO", "published": "2026-10-30 10:31", "score": 0.84, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex Today Ends 308 Points Higher | Nifty Above 22,300 | Vedanta Oil and Gas Up 8%", "link": "https://news.google.com/rss/articles/CBMi2AFBVV95cUxOaVVsSnlXUHFmTWxXVlZSNnRHcy1zRW1wbUdOZmZRWG1DQmlBbVVSWmJIdF83V0VObkV0NVh0T3kwQ0Z3U2VuV01NSUxTU1drMldDTnpjVXF5a0d1ZldaU2liWHNaRlMzazdiOHpiaDdFeVBrbGJORWN5MmtUTk44UVVGZVFmaDJZNXdmekEwS05XQzNDbGxPeDZsWFd1amQ1YUxQd2w3VGVZUGtaTHdGUGdoemFLVUlqcU1aZkhJMUFKQmlqU1pmcXdfMEc4ZHM5U25iX3NjOVY?oc=5", "source": "Equitymaster", "published": "2026-10-30 10:28", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty close with gain of 0.5% as IT, pharma stocks rally; weak broader market limits gains", "link": "https://news.google.com/rss/articles/CBMivwFBVV95cUxPZW9rV0NJRXU2T002TkpGY3BBMWpjYWJMLXNYOUZ4bUQwZkw4UU1ZMmJLblFRZWhpdmZUc0VPYVp5WHVDMTRFZnRsNkZzQjFlMUdlMGgyQy05bVpVa0lhaU9PSTlXU2ZTYWdIUVF3ZEV2MFB1SGVtbk9LUWhPWWRQbVlCbHNTbVRZZW40QW45R1hVVkcwc3VWemxkRUdieTA1YmhHZVMybTBWNW5OTnJzcTgzOHVkbVlGbzBxSlpxUQ?oc=5", "source": "ChiniMandi", "published": "2026-10-30 10:26", "score": 0.796, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex ends 308 points higher, Nifty above 23,000; Trent up 5%", "link": "https://news.google.com/rss/articles/CBMi1wFBVV95cUxQMlVJODZONnhDZU1vT2d0Wl9ZMEFmZkN6RGFrVU95R2RqanBoZEpCSTRZckxNcjVOTDFoY1FyaGE0RF9hS3UwVlptODRfMHFoY0Rvd0l0R3JJTUUzTExBeVc0RVFNUElyaGkybHdwZHByWjF6Nld4VWVCRHFEQ3l1UkQtSHB0M1VrZXB4MTBEWENzUnowS1I2c1BOeGIycEJWSmRScUlFQnc2N1VwVmlGd3BSX19iNEp4SWxNMWJiV0hXZHZ3NDIyQlg2NnQ0N09XWWZTdHU1UdIB3AFBVV95cUxQSTJkN2R1WXNmVVFmNE5GX1M4RHhod3daU2k0emQ5N0lWdmZxcXI1VDFCWDBkcDg2eGZ0TWV4R2ZCOVdtTC1leTBaOGRnaFd6UHRhbWhUNVBpRzhib0F4RWNybFlUTlBMamtLUXN4VXlOcUZTT0FBZ21Wa1hUZ2FYZUgwSDVPVGFjQ2R5ZXh6OGtMWGlzMUI1SjJQR2NaelFXTm5nZU9jVnBSLUtjTzhqZVlMWHNTc3FjSm1pekpVRFd2TTdLci03cGozMjhoczAtQ3pENXNoZ056d3dM?oc=5", "source": "India Today", "published": "2026-10-30 10:03", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Market Wrap: Sensex Gains 308 Points, Nifty 50 Ends Above 23,000; Trent, IndiGo, Infosys Lead", "link": "https://news.google.com/rss/articles/CBMiiAJBVV95cUxQZTFyMk9sdFl3QmJnUDd2OGhhdDNIZ3FwcDQwclFmNE1Ba3ZsakV0RzN0RHlKUkRYZnJST19SVDlqZmp5UGV0OGdOYzlLTkNNMTFqaEhNZGQ5cmctT2JzTEtZNzk4N1lfb2lyc2NuVU1ETHNWU0ZBZWpxX29hVWxxNUp4VE5pNndCVFVDeWtmZWNPQkh4U2xFeFp6NEd0am1jV2FBSWZIb215bUxTVnc2LTdhQ0lmM21KSHUtQjVSVlVpajhPdkZYdHQwTEgyc01tMFdxLXZBZkUwSUdGdXNkUjl4NGVMeHNWNzVROXhhSDUxT1BJSXo1enlzR3VVNXpyeWRaeTc4YmLSAZACQVVfeXFMTUltcFpOMzllTWlGSzAweENGY0Nob0tmTk96eV9wOVB1cGlDeTRuN1hRRFI4RS1KTVoyUW5xdWxpU24ySVIzWk9JV2F6bks2bVJ4TlZidVFqQk1LU3pOYlNEV2Qyc1JVSGlhVDhyb19xQlpQbWFmUmdXakhsUDZtSUEzSXlnQVA1SEhXV1BzZURDVnJablhfSk1FUzVCSmEwQmpZczltQVRON3otMzV4MnUzVGxsTlNJMGt3ZU5fWlhrcU53YzdHTE92UGx0QjdBTkdfOUVobGVib3VCcDR2MGZ4Ulk4R1haZkJZdEQxalExRDZqT01DMjlQbEE4RVJ4b0Z0UGh1c05kX1A3bnNOWFQ?oc=5", "source": "NDTV Profit", "published": "2026-10-30 09:52", "score": 0.649, "label": "Positive"}, {"symbol": "CPPLUS", "title": "Aditya Infotech CPPLUS ESOP Allotment 48,100 Shares Oct 2026", "link": "https://news.google.com/rss/articles/CBMiwAFBVV95cUxOUHlaMl84Z2E4T0RVUE5PMW5FZjVuQW1RcjFVTXd2ZUdMdmE3dXpNTURraTVmWHJYd2lQbG5fQVh2ZE1WVDlob2NDR2I2YWRQMVRLR0t2YVRaSVlYWXBsVXJoS2YwUENlLXducG1jaUtKbXNlUEVHQy1RT0JXdXhLZV81UklYZzFuMmFMUFFuRS1sMkRaZGgzRHNyMk9Yek5sdi1oNVZXbmdxTDhyZzlhODVKX1pmS1pYODc3MHBBT3Y?oc=5", "source": "Kalkine India", "published": "2026-10-30 08:44", "score": 0.0, "label": "Neutral"}, {"symbol": "AETHER", "title": "Aether Industries reports robust Q2 FY27 financial performance with \u20b93,472M in operating revenue", "link": "https://news.google.com/rss/articles/CBMi1AFBVV95cUxOLUhIalRub2FoUnJULWtJalpwX0JyTzdscWdJc1VieWdfd2xONUlQSFMtRVBfMHZSVUoxbHBna3lDRk9TMlFRSnZlTVpMZWwzV2h4UFh4dlloblJIbGhqVVVnY3JQVmRKVkJNV3BDQzRQTVdhYWVwRTFvd01yVGh5WFFUUnBvQTRnTTZsQkR1SzVOUjBiZWUwR3g4Nl9ELTNaay1vSFVoVnhBXzhlamJkRGQxX1dxa1ZOSVBUY19kZHZYcHRybElETi14akh6MjgxTnpKUw?oc=5", "source": "Business Upturn", "published": "2026-10-30 08:35", "score": 0.421, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex zooms 1,200 pts in 2 days, Nifty tops 23K: Why are bulls in charge?", "link": "https://news.google.com/rss/articles/CBMi1AFBVV95cUxOTDJ1dFlKVkRQMEhPdHhUbGlyTHk4ams1Y0EySG9zRlhkcWpORm1FUzdwWDdtVmZRT2s1YWJJYUpDU3h6UUt6Y29DaFJsMFpmZkwxMnk1dnNGQ3kzSlNfNlZoOTVURThySncwaUZ1cDJzeGU5NlN2NV9aeWROd3RuWTItcmtlNUE5WkZVbi1wUUtobnJzRGp4SE1PcUtPaTQxbnVDRUdTWFpQTGZjMzh6dTJ0TzJtRVNMbUJMVmlBTlFPTXQxX19QWktWUEhWM3ZkNm51VtIB2gFBVV95cUxQcjQ4VkQzSUZjUnlJeGk3b3ZFQk5QYVM1ejM2X3dZanFHNFhOWTFJME0teEVXZFRQZDgzMzktem9uMWc3ZXphVVJJUGwzUG1KVnpKVi1Xamd4cy1qM0hTYUR6OTVSa2ZUQ1E2S3dwWHV3MTByUGtFQS1seXl0SWNUXzhxeFZ3UEZIQVd2V0w5NlNNeHgzeUVHYTV4ak1iYW5IY0IycU4xYnJ5dGxxMm1QSFdQTGpQYWE3Y2dUekVadEVSeHZYc3c1UDdmMDVJd3hXbjlMRjItUlhBUQ?oc=5", "source": "Business Standard", "published": "2026-10-30 08:02", "score": 0.718, "label": "Positive"}, {"symbol": "MARKET", "title": "Passive funds could buy up to Rs 36,500 crore upon Jio Platforms' entry into Nifty, Sensex", "link": "https://news.google.com/rss/articles/CBMi6AFBVV95cUxPQml6RHdZS2FTeE1nN05IMHpUTVYwR3BxdXhNRVViWjlzSExMb2ZsRFBGZmc3bXZRbDR0Z2ZZVkNhclFpRS1tYWtfN3RpM18waHFDdkRzR3FWeDllUFhvb2JlaVQ0RkozVWt6b0dwS1VWRk5zcjVaM09RUjE4ME1rNmZ1WkxqVl9FVm40ZmVoeEp0X25uTWN0Vm5PLVV2OGpLaTF6X1VuNW5kNUVwU1FtclNGdU94LXQxdUozUTNwQnVDQzR1OEhCcVhpNWpOakxseUIySzRrdWMycFR2TWRRSUtjQWdCZUxh0gHuAUFVX3lxTFBvVWFETnc5Y1BDWk1YWmhPdFNTbTZESnpWaHNVSTRoTWJHVlBONW1yVldTVThqckJyTURkTXotaVRCX3lOZ3o0QlRINTZJcnY2SmI0R0JuMkdjV21jVVJrcG55Y1lrM0F5N0NUS1pnODZNTmRIbVRLYU5nbXE3UmZyb0hERFNBdTJ1SEdTLUluV3FldFF2VVd1d2lucXpUcUlxNVlnODdqdkN2UjE1WmNfWlU2NWJLelpwSXptX3hKMGpjQ2xaOVFDdW5hd21UMktsODRIaVdmY0ZoZkdhQnZvaC1Ha01SN1JlVV9TR2c?oc=5", "source": "Moneycontrol.com", "published": "2026-10-30 06:40", "score": 0.691, "label": "Positive"}, {"symbol": "AETHER", "title": "AETHER Share Price Today - Aether Industries on NSE/BSE", "link": "https://news.google.com/rss/articles/CBMiXkFVX3lxTE5YVWFUSmNPUGtKRF9jY2EtNTNkS1lUVHJYOFgzZWJkY3NrY1lucDJqajdnSjhJTFZuSkZMSjhwSUp3UEs2cDZtNTYzd0YzbEs5NE9IRy1VQzgyWm5YTVE?oc=5", "source": "scanx.trade", "published": "2026-10-30 06:37", "score": 0.0, "label": "Neutral"}, {"symbol": "AETHER", "title": "Aether Industries Q2 FY27 Results: Revenue, EBITDA and PAT", "link": "https://news.google.com/rss/articles/CBMiwwFBVV95cUxNLTdIWDMtbG5YaEVpMVZSemJTMzFndWU5OVVkcDJXdHpCeU9ON2JtcGRmNmJESXByQ3ZWYlh0bDZuWExfOXhtQXVhc2U2eThtZ2psXzFKS2NKS1VXU3lPNG1uNmlfWUE0aUlWVERSdS1RTXpGZkVzZlRfWXhhcDN3dGktb2JwdjJHQUM5YTdTZU43RkZGM3Q4RTZKc09HTzFHTlNmNlZpcWtKSi1Ia0hyMWNUZEUtUy1GWXdFMlVPRWNVQ1E?oc=5", "source": "Kalkine India", "published": "2026-10-30 06:31", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex, Nifty turn lower; broader markets crash as oil tops $116/barrel. What lies ahead?", "link": "https://news.google.com/rss/articles/CBMi2AJBVV95cUxOZEZkOUo3elRXQW41eS1KOUQ0S3NvWFE1OTNHVy04WW1BeHhDV3djcGFrem5PMS10dEVmamxsYjEwYnNJZ1BVbTNwVnQySHpKZ2RPd1NzempiTGp3UTMySEc5d011SkdOYzFXUzlPd0hRLTREMGRmQVZLS0FyNWUwaDNnUm1nSjhISzYtNGNsZEF6VWZVOEc0bjJ5azRJODFKWVZyZldCeUJtbUg4Z19GWEUtWFNQLVA4azNtVkZ6UWNMcDk0ZWdEYmdVS05WQ0RLZElsQ2I1RjVXbUZZaHBaSF9lay1BQzNuMlc5b2o5Uk1oWmNMLU84dmQzRnZub2RXbjVYVlZ4bjVKTVpkaHZLeDRZcjZVNnpocnRTMU00eGQxZHZUbGNGemN3SFl1T1NzbXBCTmdMU3BuYWZMc0pJbmVnOTFCb0dUeXFhRXU3bGNqUjNzamVGQ9IB9AFBVV95cUxOamxtQkl4aWpPQXZ3RXdZblRPa085YklxbVh2ZXczb1BhNGdoLWpOSWF6OEdHTjcydlA4eXlUOHpZMUdNMk45VDNGNXJacFBra25ycnNGQlFJT090el9yc3ZjZ3NYRmhZa0VHX1JEOER2RHQyV3RXRURtUnZrQk5Xci04Wk41X1RTSXhJN0haNmtVNUFpbmVMR0F6VzFPZHliV0dHMU9iR05WTWFPb29QazVvRXk0eVNLb1hfNXlIclJ6YWhfa0ZUc25Xdm5fLWZhWEhHUGk3SHZHNkxKUUpqRm9KdjdyREFhdV8xeXpkMll4aEZk?oc=5", "source": "The Economic Times", "published": "2026-10-30 05:36", "score": -0.34, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex, Nifty Open Volatile; India VIX Rises, Crude Above $116", "link": "https://news.google.com/rss/articles/CBMixgFBVV95cUxQY2daQnV3TThDSXViZGppTlJha2tMZVU4ZEV6Smw5ai13RUxwa3ZoODdGYTYwLS16eW1UdlY3SHVyQjVSLVAxUlVXNmhiTVNSdTFHVXNNYk94VXY2a1Q4V2c0cjluWDNBbkxwZDVfLXdxUTk3aV9xM0hnVElQcERGaDAwaVBRU2JZam8wTVM5WlhsSXJGMXBkWWlIdUZXWEZITzlJRk9LM1pEOE8yYVdETHp4WjRzWklrV0dvak5Pc0ZiaFdlMVE?oc=5", "source": "HDFC Sky", "published": "2026-10-30 05:13", "score": -0.25, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex, Nifty trade flat as IT gains counter crude oil concerns", "link": "https://news.google.com/rss/articles/CBMi1gFBVV95cUxOMUFDOGdnZDc3VlZTRnBlVi1TNmpxRmRKTUtJaVVaYXFIOWJYRklfam54WG1OWkU2MEphUEhmbjlEVHBWUEp4TVhNSFZQN256ZGxjcjdaRUxsd1ZsNjYyc192SnlCNnVBdjJXU3gwdEVBX3AxMllFTXlLbFJOUGlkWnNRRjE2RXJRUUhUMVFraGpnZEFRQlFLUTVnY3lDREJkWXdsZ2l4MVhxNXZxSlUzMllBQy1IRm9ja1lYTUdzRXBqdHhvTkFOVlRJTVR1VFRFMjFEUzVR0gHbAUFVX3lxTFAwZDI2NmhfbDE1RmRhTlk3a0NVMGpWakRNLXpfMVdYQmJGcDRjYWpOTkVNTS0xaWc3MVRCRXVrV0g4YlNIY080RmtqN1QwUEdwRzlXOGdESzFXOUZxalN2RmJRZGh5MGdOUUFEQlQ1XzZOSFUtb2dEemREUFJXTUZYSTJ0eWwtRUpMWTBBa2ZBanpkV19PYkpUNFJFVDk0OWN4cnJTeUw1MjdVTjBDNF9Mamdzc3BrTHM3dXFWZWs3Ujh4ZWREQTZQVlRWYU1raXJpMmpOVDFpUC1vbw?oc=5", "source": "India Today", "published": "2026-10-30 05:07", "score": 0.153, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex Today Trades Flat | Nifty Below 22,950 | BSE Telecommunication Down 1.7%", "link": "https://news.google.com/rss/articles/CBMi0AFBVV95cUxOcUo1LU9Dd3BjaFU1bVBLSXhidmJfcFJmeDBUWFBaRUFJRF9FVlk0ckhLWTR2ZzJWQ0NIRkhXZUZOQzVHR0VDQjI2NE5IUl9PS0I3UmFSbVVnRVI2V2NoeDdOVGdPYXM2UDdkQTVIa2RMOTAzUzRKRExNTERWbk84eDVsN0RPM3gtcmhENlBhNEcyZEo5UFdoQWZKSkFiUTR1eDltLXpoTFF4VTM4UXUzLVFBSGIwMlVzV0lyTDRrSEFZaGNjTTlLRkp0N1ltbXln?oc=5", "source": "Equitymaster", "published": "2026-10-30 05:01", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty Rally 2nd Day on IT Buying, Trent Earnings", "link": "https://news.google.com/rss/articles/CBMipAFBVV95cUxPSHQwT25wUDBQTGJydm9RS2lOZkl5b1Bod190aV94bE5lRVZsNUVYX1ppMHQxRWc3bGZCNTRyeThwbE01bG11OUdmYUtnMEE1VkduNVZUTTBMRkZST2JDM05qaDVnUnY0LWlHV0cya1d6SEh5MnNhUjB1VUtIc2pPVmk5N245MDJ5VVNuR0I3b1VKRlFYcE1YM002b0RRb3IzY0ZMMdIBqgFBVV95cUxPQ2N4c1RBUjFWOGVlVUE2NzFITzlDOVJ3Rm83dXJhX2F4UmF0cE9RLXhOTTFIQzdmYVoyM1ZCamdabGlUTU9tVklfUm4xTVlPZTgyaUNTM1FnRnlUTzdiOVBFeURwTUhWd05qdUxiNjktVmlyQTZyeWZBa1VaWS1UanR2d0dLbEJyQm9YN2hBeXJ6d3hJdlVDR2Q4dmloMG5tbC1YOFR5TUdBUQ?oc=5", "source": "Rediff MoneyWiz", "published": "2026-10-30 04:58", "score": 0.691, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock Markets Today: Sensex, Nifty Up on Gains in IT Stocks", "link": "https://news.google.com/rss/articles/CBMiwgFBVV95cUxNRm9wczhmdDJsYW0tSUc3Q3VzRGVzTzZSMzdpR2o2MmJHX21lYTJHQmNUU2w3dElpcEpyUXFBbHZaZHlqRXNidXdpWVZEaWhXWlNaZlM2TTM1RXpWb1BwTUFNOWU4YjNsSnZzazJWbkdwNE5XTDdueHgzWWdwdWlCZkdUekVNdEhDaDhKRzZuUnFiWlNtaDIxd3RwNHFkWXB2andGM0ZwMUJLUHpOSDExLXZndGtjSmdCYzl1UXNLRWZWUdIBxAFBVV95cUxPTmdzMG1GRF93RmdyMFR4SUYzWFFxSUhLei1zLXZSZXZIaXdFY29CWU5zcVFLNHAxMzBJUGhfUWhEMW9STlRBME9aUUstYzZvMV9TaXFUOF9DWk1mM1BOOUVuUXVPMjJTUTI0Y1BRMkN4MDE0cENsV05mbEEteHAtMmR1WWM2TjVGbHNnWmdoTFVNR1Q3OER3WDFjUU1oMkt1VXJfRmt3bTEwWGM5ZmE0bDZRbDVUUUYzYmVEdl9QS04xNUxY?oc=5", "source": "Rediff", "published": "2026-10-30 04:57", "score": 0.649, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty open marginally higher amid rising crude prices, weak global cues", "link": "https://news.google.com/rss/articles/CBMi6AFBVV95cUxQVVdQbFd1TGh2Y1ZldUp4b21nR3VzUFZHSHZUQUw4NlY0M1hBZ2g2NGZDa2RZcmFYNktpeWpMWVpkaExBZVloVUgxaFFXOS1mTkJZcmxsNHVjNGgxWTR6dDNvR0c2UzlnaTM3VGVmakt6OTlzZndtSG5HV2pkc0R4azlLOWVjVm5xLWtFblFSZU44RFEzajdNT2JDbjNvdFFvYlNSV2ppVGQ1Y0VyYmtNNlg1U2IxdlR0Z1ROZmh0OTNmNkVnUlpmSzNDMEp1YmRzRlV4LV8xb3d5anFyRHNVSXoyOFhBNVBE0gHuAUFVX3lxTE9CSG94UGNLcE8yWWR0RzBacVdib2ZORzVDZlhRUkg2V1dkTGROQzFuTTlFRlM0SmRfcjVZRklIRHZ4NDlyNTh3d2NGZEQwSG83RUl6c3pmX2FvdWx4S0RLbWRpT05iN0JFTW5xUnh0Yk1UWUhfMnRBOTBGODJOelRlTUZBU0hJaHlfYUJId1lvSkE0UktENUVjXzY3cnNsbUU0WXoyTzktSHh6REhHZHJwS2NqalVoTGlDZElCSXlSR0tLaDhURXFORE5RRGhMOEIxbFhDaXJBWFNxWWc5dDRWY01VT205MzA0QV9wbVE?oc=5", "source": "bfsi.economictimes.indiatimes.com", "published": "2026-10-30 04:25", "score": -0.557, "label": "Negative"}, {"symbol": "SYRMA", "title": "SYRMA Stock Price and Chart \u2014 NSE:SYRMA", "link": "https://news.google.com/rss/articles/CBMiWkFVX3lxTE1ud0tHczZETmVYWGR6VkdGWkdsc1M4N2pKRFM1UXdpNGlyWTVHbGVHS25tOUdlZjBPRExoWlZLcVQ3ckFPU21KdFQ5dHBqc09VdjJZeV9JMjVzUQ?oc=5", "source": "TradingView", "published": "2026-10-30 04:16", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Coal India falls 3% post Q2 results but brokerages upbeat on PSU stock", "link": "https://news.google.com/rss/articles/CBMi0gFBVV95cUxNRWNKZDdGNHlETVRZR2VZMEZOdWJVUXZLbzd1RVRqazNuN0NrV2NUMWJDREZxanNlWElPSHRyRUFsY1lMZVRCTWtIMEZNSDBnd0xxREJtVG9FSFU1NUd4WDd4aGN1X2phV2lIY1pjTDRNMlNHYWxYNUZ5NjdnTVp2YndLa3ZDRjFiaGNvTkdQbm5fVTRvX09IakEzMm1CU0VFSjh6UmI1TjdybFJwc19mNjlwM09wU2RrSmRuTDBjOGhlalItM28wa2trQU5fZFpvOEHSAdcBQVVfeXFMTkVnMXZSY1FaMDlfNURXUTctY2NnMml1SExJZHV6SFNSYlhTVTBmckc5YVhrRTJHYndWMlg2YWo5OXRUUV9yNzgyWk9VVnVpU252WENCLXFQNnlTMEdVeHoxb293N1czYnE4WmwwV1lCZE9zS2VOYm9YSEZ2ZDE3RFlDeFMwRTJMZFFSNFh1X3B5RjZ6ek5fbVdqSHd4S3JOMEkwLUdBRkRMSEJ6SFE2eHFmZFJKejdGZ3Y1aGZHdnBHUjN3UUoyY0RYbmJoZnladHV6RS1xQTQ?oc=5", "source": "Business Standard", "published": "2026-10-30 03:59", "score": -0.202, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock Market Today: Sensex edges higher, Nifty opens above 22,950", "link": "https://news.google.com/rss/articles/CBMirgFBVV95cUxQNHhZR2hsX1hjcDRiWWxSc1V4QVNpNDFad3g3STVkMGdrTG9vaU5ObV9ZYUNIN3dpUlFUUmhsTHVHWmpHRVRMVVlfUHVFSURqZHJQaksycmc5Y2NVZEt1OVlyWFJOWEVsWDB6Tm1nOVFLOWJ0YjZ1UnJKMXJwcEJGdXljWlJUcmdhWTdkS1A4NFlpeXRDekdoN3l6SEQxSEhSQnhjcURURkkyajlGVHc?oc=5", "source": "Zee Business", "published": "2026-10-30 03:50", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty may gain 5-8% if external headwinds recede: Baldev Prakash", "link": "https://news.google.com/rss/articles/CBMi2gFBVV95cUxPcTJTc3Vndll3czhydnJSQk8xRzVicWRTQXIxdWVxb1diVGt1R2IxMEEzWkF6d2stU2F0U2o4SlZQSkVUMUJlSEdzMVdCQ05Da2pNaC1TaUJaYW9Za1Jfd2hFNmJpdTNXQ2NXbXR4SXJ2RU1na183RnUtSk5IYmJ2V0lfVWhTMkx5VXFULUNqY2dUVUVqY1BVbXZvRHpmeS01d0lQbWgyUFBqUURPV2tFTG00eWZQNmFxckRYUkxZVF81TGNEaDRMdkRNZ2txWDBYS2taNnJvTEJ5Z9IB3wFBVV95cUxNeVpabmdOVGR1X3M1R21QQlZJbGZ1MzJmdU81a3lGTTdlaVhGLVNwUUUtMF9QRlFJdXlkNG9UMVdiNjhhUmE4bGV6b2tGREdROGV4MXFGVk43NS1faWNZT3dpcUUwR1FXU19uZW5rUHhZUUFzcjdTVzkzTWlWTWZ0eGxYclR0S2t0VWlHcVpacFVjYlFPazNpYVY4TWxkeGQ4U2JTZTFNd0dDTXBiMS1kY0otbXZjbUpONDBhcnFwMFhqdEhfZW1oWDFvdkZRNkxfUktFaW85RjRXQWhSR2ZZ?oc=5", "source": "Business Standard", "published": "2026-10-30 03:34", "score": 0.625, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock market outlook: Crude oil prices to FPI inflows - 8 triggers that could reverse trend in Sensex, Nifty 50", "link": "https://news.google.com/rss/articles/CBMihgJBVV95cUxNOEZaNmc4dnEtRC16Vm5IVHhCd1Y2S19zcjRpVDdSWVZZajg4NjNGMGtyWnE0U2tPbjJUMXVkOFFlT1RERHZWQlBEOHJxWmdITmJPREVXZ1JIaUd3aWNQUTcyMUlqZnpFQWRiZHJLcE5YWmlZOUdlamlzX1NtYUdqczBmamh5Q044dnNPVHZsdEdfTWRmR2pxLUlXeXduUU1laHVpVHhfVmE3OThMWmdwMHdBa2RmbDdVZW82VUc3TGV4TVM1cG85anM5TUpROGVZZlR6MkYzczB4d2YwcU42YWlPeEtmUUw3Tk4wbFBZTDMwUGlSUWtDeHFmRjQyejJLaXhiVmxn0gGLAkFVX3lxTFBIdUVWNXVfYV8zN0tXeE1oZmNpZS1LTk1GNGxzUXRINHQxcWQ3Zy1SOTN1NWRta2tjeG1uQ2NJaE5nTGpzVUlHeXBtaHlaNTM5NWVGUmM4cm10M25WTGplanFSd0F5OUtYWXFGWklQYkpudlIzakczNDNjQi1HNmJYUnRxSTlsVi1xelhNd2h3MU9wSmpyNjcyMTRoLXNpcXBLc1VreklSaS1DNktabHpISXdSSmhpWXRGRm1wQlgzSUk2RVJOZDJTY21vMFdwS0FNZ2psM1NZT0FpbmZsZGQ5VnRlQmx0Q0RWM0FudEk4SEFqRldYOGpsNktPdGxPdU1DZ2hldlRMaEZFOA?oc=5", "source": "Livemint", "published": "2026-10-30 03:00", "score": -0.25, "label": "Negative"}, {"symbol": "MARKET", "title": "GIFT Nifty down, signals muted start for Sensex, Nifty; Asian markets plunge on AI spending worries, oil...", "link": "https://news.google.com/rss/articles/CBMigAJBVV95cUxOQkZmUHBNNXpGaGxiR2gxMnp3Ry1tVjBlTWlHMUZHUWc0SnJLbk5vU3kteU1zMVFkZDd6RGUwQ0RmZV9OUUtITUgtSU8tMURBT0ExV3dWaDF4MzFKZDhGcTJoeXVzUkg0QzRKcHJiSUZjV29XeGJhVDNIMXE5YzEyNEFiSTJ0cnYyUndHbXY1UTFtUzhZT1l0Q21YYi1Ycy0xekxBR0cxdkxFUmZuMEN1eklZd1c5ekNWV2JtbXEzV1F1emd2eXlhOWtXR3k5VTBaNGd4Z3M0U0ZTdUZ6a0tHakV1WktJd1YwMHh2M3pQUjkwSHRwcE93c0R1bzBhVTdD0gGGAkFVX3lxTE1SNmF2clJMZV9kSHRkZUpwZ0FjcUhOS0NEQVZ1S0NzYzBXaE5jMXQ0Y3NuYUR0VEVFZE94OFpRbGtiYUgxbVc3TzRad3JGb2t6ZDJZQVVzMnd6QXpMeGFMd3RHWTF2QmNGUjlMT0NnTDQ4SURVZ2UtcnJLUjRncVptM1BGMnhtdWRCM1N2STRsUnpSWDhYbnlwcTF1UHhNOUpadWpzaDJTOFZJUzVoN0w2Q3dRNG0tdFpUbDdrVm9XWk5lRUF5bUk3X3BmVTVBZ0E5dzIxMzJDeHdhbWVxVFRtcFNfWkVyV0QtN1BzbFFkRkJiLVVlMVAzMENGMlVYUU43ZGdvUnc?oc=5", "source": "Moneycontrol.com", "published": "2026-10-30 02:41", "score": 0.408, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock Market Today LIVE: GIFT Nifty signals quiet start; Brent crude at $111", "link": "https://news.google.com/rss/articles/CBMirgFBVV95cUxQVkZ2QnRqNU0xM0Y0anVKUjZmQzR4VHE5enhQc0N6WjgxMmhya3pGSzJmUEY5cHgyV09BRm5xUU9vMlU0RW9oM1BxeHBoalg3ZzhldWFJZUgyRlhkWXE5WjZnQzJfU05lSnhRU21jVEhMZ0dhcDNPZk5GWDd6aDNLVFhzNDVXSWJjQWpxTTA0YlZMdU5QcFpfNDVTUWVPVlR3YVB0Ti1pTW5MX19GWlE?oc=5", "source": "IndiaIPO", "published": "2026-10-30 02:31", "score": 0.389, "label": "Positive"}, {"symbol": "MARKET", "title": "Can Sensex, Nifty extend rally on Friday? Here's what market analysts say", "link": "https://news.google.com/rss/articles/CBMi1AFBVV95cUxPWGxjWEFLUmtMVFF2bVBLY0d2a0dvWV95My1ZU25MbTFtS0tIb2czMm5CdV9IV0o0WGMxalUtWGM1RUJkNlBybVcwa2hIZ0pydGJKN3Uxc1BzUDExNklVR1lsTk5jVnVDZ2VZR0pVbElVcFpmRVJfa09nVWhUMXVWWEtDaTFjeE9OQ2lnYTcwQnlLcnVZSlA0MHZud3VQNUthYmlDZzFtNFd6RldnRnhMTVlZREZCWlJuOGtNVE9OYTV6WllHcXBiUTFsVzJPazM5c2ZjWtIB2gFBVV95cUxOM3BKenNkenFoUnlraTJ0WHpzeTdKbWhQako4dWNmMjVva05Qd0tzc2Zyc3J1YTZEN1JSRjA0dS1Yb0p0bXJlVTU1N0tCN3dNTFVXVFFwcFNnOVdGUUZCQ3NoTFk5ODZ6UkJTRHdkOFppdWtiUU9YSmlMMTZpVmdULUYxRnVXdkxmeXNmTFN4d2EyR0JnVGVVNnFvbmJRZ1pmVWhiYTlaYXRnZk1FM0Q5ZXVyWTgtWGozSUpsQmJWZkJCY0JxODV5WXRaZGNDZ2I4X2s2MjU1Nmk3dw?oc=5", "source": "Business Standard", "published": "2026-10-30 02:26", "score": 0.751, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock Market Today: Gift Nifty, Tech Stocks Selloff To Binance Hack; Five Key Factors For Sensex, Nifty 50 On Oct 30", "link": "https://news.google.com/rss/articles/CBMigAJBVV95cUxNdkc2UTMzMXp6a3dsbm55eXlZMzFHdzJ2S2UtYWkzcVdJekZDOHh1RVJaOXFMMlFwdXdWd0lMajR2TUItTTl3cF84b2R2R1NXVmd1dVlta0VpcTFhYWkxUlhnZDYxTHhoeEtYM0JGeDAzQkRlc0FNR1dCNWV1RUw1VUdYa1FkQ09FMWZmM21mN2pwQTVfUVU5ejlScGhzY3F0MjVHY1lTNmZkdHNJRTk5dG0zODcwOTVHRzRqYi1OVE1BUVQwbWdQWkQzWE13ZWZlTmJYUGlHRnhGTWJhWGtQTkJmMExFa0ZURmJzcGtOeWVwWHg4SlNfUnc5TC15eUxT0gGIAkFVX3lxTE5kMVJROUdWQWIwcWlxNGduSHdncXluWWduV1l3a3MtMzRMcXdsUmdzekdkVkVPR1JRNUp3bVVhb19WREFhTzUyYU5BVzRpUDNEZTduODNsb1ZyMDR1OGRybGRhWlRGbzB1Q25iTTRLZGtYMlpBT050bTM0TXBDX1BfN1JOLUttSkd2N0dYT2RGX1dUOTE5Tk1aOVVSRXlmd2tmaUVTUTczcTlrVTU0QnEtSHhJdjhDa1Y5R2R0aHlJQVhpNkg5bC1FcWtOU09KN0FuY3pmZW1RcWplZ0toNUZWYXdMZGx4aGJBZXpidlF6MXhnWGpmaHEwUTZVYVVlUE1VM3FBanFvZg?oc=5", "source": "NDTV Profit", "published": "2026-10-30 01:44", "score": 0.807, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock market outlook today, 30 Oct: Sensex, Nifty prediction - DJIA, S&amp;P, NASDAQ, GIFT Nifty, Kospi, Nikkei, Taiwan cues", "link": "https://news.google.com/rss/articles/CBMihAJBVV95cUxNU0lLTXdXRXlnWnktM1lpdVdQMEZ1Q0ltbHlFQlZOa1pRM09LcGlnYTRubzNDcks4N21ZaGdEV3ZpRFV0N1FhT3htZkM5djl3WngtREVSVkdhbWkzWFQzNjJQN2MwZDVYaXQ3Q3pPOUxLaDlVUFF5aEFzWkY2TU1jRjloa19jNTBBMHZMYkZGVExUMlV5aXlXaVV6M3Z4QV9WaDF2ekFRMlg4dXV1aE1TMWR5bHlUUi1XODB1MHFraXVKLXZGOXJvNTdmRnJNNmY5WU1JSXJ1dXpVTjdXR2NyVUpVSUdYbFFqS0gybXp5MG5tSDdhWEpTb1RVMkJlZ29ZN09WNdIBigJBVV95cUxQQ3pIRzJQZmY1VXpnc0Nra014TklOZ0lvNkhtZUJ0UFJiQmtZQ090aUpZTlFfTWdMMW9HT1U1UVJEU2NUcVFUUmtyb0E2emhPa1hmMGd6eDYyMWk4R3JURTFVYThqZzNBS3lyNC1zcTRyajNKcWF0d213aWd2Y1J3aGRNMVlqRDhOaUZpNktDcmNSRFlpMnVVU1NOTlV3TTMtX2tLSkNyMWNrVWtwd29sQkxxTkUxYll2X1FoOWJVY2ZTcUVBUXRMVGVTNnY5UGZlNVZpRTQ1bnhUdzBkM1BPTjl4dUxfS2FRd3NzZUpJMF9CWW44QXRWaVFuaW02M29sZlBCMThPRWlfUQ?oc=5", "source": "Livemint", "published": "2026-10-30 01:14", "score": 0.842, "label": "Positive"}, {"symbol": "AETHER", "title": "Ather Energy Share Price Today, Ather Energy Stock Price Live NSE/BSE Updates | The Economic Times", "link": "https://news.google.com/rss/articles/CBMiigFBVV95cUxNMmpPVXcxeVFIRHF1aHV6dFRLVnhXV3djOWRQN2tuMmxVTnhDeVNJSnFoV2ZscmFoaEtaWXhCT0tabGNHdVhlOV8zcG45eTJrYS04ek9hSlNlMEZPYlpyeS1pbXNqbjlVVklKeEFrX1R6OUEzXzhRdjNneFZzbEFFMjc4MmZ4T3dSMnc?oc=5", "source": "The Economic Times", "published": "2026-10-30 00:10", "score": 0.494, "label": "Positive"}, {"symbol": "AETHER", "title": "NAVINFLUOR Share Price Today - Navin Fluorine International on NSE/BSE", "link": "https://news.google.com/rss/articles/CBMibEFVX3lxTE5KVkRzcU5uaGJqRnktQVNCenZKQ1NlZERDM2duMTh3ZVBRWGRheFQxdkdZdzJoZHozc2dpcFhmUUl3Mmg1M1IwY3diN3hNMjBnVTVyRG1VOVdzOEdlVzlaY2taamYyRnYtNTJoQQ?oc=5", "source": "scanx.trade", "published": "2026-10-29 18:01", "score": 0.0, "label": "Neutral"}, {"symbol": "SYRMA", "title": "ZF Commercial Vehicle Control Systems India Share Price, Stock Price - NSE/BSE Live", "link": "https://news.google.com/rss/articles/CBMipAFBVV95cUxQaGJ5UUduMmFWUzQxODJRNUFmT0hGMWE5Ykx6RXRJRFRRMGowSGJ2eE5INlhVYVU2OENDblNfcUFlRUlHNzZBRlFyQlZ6dmxtX1N</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CR2VuX2lDWlF4NDhWSTFNVVVyVE9VbHJrSUwzZnJPdG9FVE1NNHVIcWlnMEpiWWZfVjJrZ1hmbE5zTXJXdVptRS05V1ZqM0VpVENxV1gyaDZCT2t4c1Y3d1lQTk5zUEHSAdIBQVVfeXFMTVNfZHAtb3RQNmU4T09SV0dBZFdLSkZJUUdRV2VZSjRUaUtVR05CRVNpR2EwVy1GR3NtdHlrYndwZmZ0T2d5NkNCeDAyS0M2Y1ZkX0oyUks1LXpkTkFqUnNvWHYwYWw1MTJDQno1NWZxT3pDS3F4Z1B2a3ZKTTlkNFM4ZGZicWlSYVV3WTFqbHBWNW05ZmpZZXk1akFpQTl0YWJ3V1FIdGFKOHB4VXVNdkgyanNmdTFYRUczZ2NleW5xaVNiRkNmXzh4dXQ1b2YtM3hB?oc=5", "source": "The Sunday Guardian", "published": "2026-10-30 06:14", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty open flat as crude oil prices remain elevated; IT stocks gain", "link": "https://news.google.com/rss/articles/CBMiogFBVV95cUxNMzlJdG1RZmREVmFLalpRMGpfR2k0a010SjVMTk0za3NnazZxdlE1MlZ6TTczdW9aM2s0ZGZsVmlBcTJvSnJ4ZlhTZ0JubW5kTDR6aE9FR0p3ekxHeU9fOHptZVRBNVdHd3lNSVJVZ1F1NzNFcURBRTQ4WjRBNEFqZE1Gamx2VFY2NHJaZkxYRHdiNUhzcDdCck5lZk1WTlhnQWc?oc=5", "source": "Telangana Today", "published": "2026-10-30 05:55", "score": 0.103, "label": "Neutral"}, {"symbol": "MARKET", "title": "BSE IT index set to report 2nd sharpest monthly rally in over two decades", "link": "https://news.google.com/rss/articles/CBMi1wFBVV95cUxNNlZWX3NYV0RDNkQxcXNfZ3Z3VEZwVDY3ejdUOElORUN2YXd3eFNBODctaDV5a3ZrT29fNnY3VzRtTjJOSVdwVVNCRW9LZU5kOWhJZFE1UHlLaGk2VHcyVGZMWGhJUE1KNlR0SkdRN1hpVkhvOG16Y1dSZm5oWEpNYU9oeW11QjEzV3FzbVVDcldGTXJWNng1bHdNbHQtaFlRUGpqWHpUbTVESzVBQnBrT3NoYWVpdS0tYlQzaVRveWhLZG8tN2NQSy00V29SWWdJUEJBTTBHY9IB3AFBVV95cUxQNzFWYUNDdTRJdVR5ZEw4N0RDYXdwaEFTM21GTTZoQ3hLbjNQOGZHTTFjSWk1VXpuY0lmMGZJZlk5ZFdCZkhoX3U2ek5wZU5LbDBnczctRmJxaWFxNVl2TjZWaktwTDBSWjVMTEhBZGh0ZGNoSXN5TEdvYzVqaUtHQ2pCQmZYTXppVmJrdzN0N0hCVTZSRzc2cGdtVTJpREFoUGxQclFpWmdIWUZQVkViaFNwd293dEp3a3BpbW5nZVRCdkZvd2czWXFhLWFlbGlMN3ZYQjJ6b2t3cWlf?oc=5", "source": "Business Standard", "published": "2026-10-30 05:50", "score": 0.459, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty turn lower; broader markets crash as oil tops $116/barrel. What lies ahead?", "link": "https://news.google.com/rss/articles/CBMi2AJBVV95cUxOZEZkOUo3elRXQW41eS1KOUQ0S3NvWFE1OTNHVy04WW1BeHhDV3djcGFrem5PMS10dEVmamxsYjEwYnNJZ1BVbTNwVnQySHpKZ2RPd1NzempiTGp3UTMySEc5d011SkdOYzFXUzlPd0hRLTREMGRmQVZLS0FyNWUwaDNnUm1nSjhISzYtNGNsZEF6VWZVOEc0bjJ5azRJODFKWVZyZldCeUJtbUg4Z19GWEUtWFNQLVA4azNtVkZ6UWNMcDk0ZWdEYmdVS05WQ0RLZElsQ2I1RjVXbUZZaHBaSF9lay1BQzNuMlc5b2o5Uk1oWmNMLU84dmQzRnZub2RXbjVYVlZ4bjVKTVpkaHZLeDRZcjZVNnpocnRTMU00eGQxZHZUbGNGemN3SFl1T1NzbXBCTmdMU3BuYWZMc0pJbmVnOTFCb0dUeXFhRXU3bGNqUjNzamVGQ9IB9AFBVV95cUxOamxtQkl4aWpPQXZ3RXdZblRPa085YklxbVh2ZXczb1BhNGdoLWpOSWF6OEdHTjcydlA4eXlUOHpZMUdNMk45VDNGNXJacFBra25ycnNGQlFJT090el9yc3ZjZ3NYRmhZa0VHX1JEOER2RHQyV3RXRURtUnZrQk5Xci04Wk41X1RTSXhJN0haNmtVNUFpbmVMR0F6VzFPZHliV0dHMU9iR05WTWFPb29QazVvRXk0eVNLb1hfNXlIclJ6YWhfa0ZUc25Xdm5fLWZhWEhHUGk3SHZHNkxKUUpqRm9KdjdyREFhdV8xeXpkMll4aEZk?oc=5", "source": "The Economic Times", "published": "2026-10-30 05:36", "score": -0.34, "label": "Negative"}, {"symbol": "MARKET", "title": "Breakout stocks: Adani Ports, Nykaa, Saregama on radar; analyst tells why", "link": "https://news.google.com/rss/articles/CBMi0gFBVV95cUxOTW50Tkl2NDNWMDEzblZlNmpXRTdHSDNFVkpwNGZIQjJDVTJ0OGJWeVFPWjIwclB4TU9meUs5d25nZUYxU0VYWlRZQjRGSV9PdERaTVRWY1VOcWxXX1pJY0p6WDJ2LWN5N0ZqYXBRSnE0Vzd6Y2MtTWduaTBURU04SXJCVVRBN0RNOVRqcmJDb1hRWW1hdFkzZ2NNM0hGU2RNLVMzVG9taU5XNFBFdkpzNlQ5WDJVckRFTmNKMDFTckRsblJoX2Y0S1czWlc2dDhBMmfSAdcBQVVfeXFMTmQ5Rm4yV2dIQS1VOFR0clFWLUdUTlZUR1A5VVYzV2NhVzdhZXJCMGhKMlNxMElXT3F1UFdTbWl2bWs2N0Iya0U0WHhxZld1U29mRWlwYU1RWnlNOEZmQ3QzQnlIQkFsRjRnMFl3QlZ0c3lfT1NFQk5GVWV0cmQtT093RWE4UTNXMGx5dWZBenZCMmYxak41TkFYNXJEUWFTSlkxWEpsNGFsTl80SE85NVVWYTBiSk9wcG9BVF9jLWpiaVltQWpVVEsyTk9KX2luU1ZsUTA3aHc?oc=5", "source": "Business Standard", "published": "2026-10-30 05:14", "score": 0.421, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty Open Volatile; India VIX Rises, Crude Above $116", "link": "https://news.google.com/rss/articles/CBMixgFBVV95cUxQY2daQnV3TThDSXViZGppTlJha2tMZVU4ZEV6Smw5ai13RUxwa3ZoODdGYTYwLS16eW1UdlY3SHVyQjVSLVAxUlVXNmhiTVNSdTFHVXNNYk94VXY2a1Q4V2c0cjluWDNBbkxwZDVfLXdxUTk3aV9xM0hnVElQcERGaDAwaVBRU2JZam8wTVM5WlhsSXJGMXBkWWlIdUZXWEZITzlJRk9LM1pEOE8yYVdETHp4WjRzWklrV0dvak5Pc0ZiaFdlMVE?oc=5", "source": "HDFC Sky", "published": "2026-10-30 05:13", "score": -0.25, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex, Nifty trade flat as IT gains counter crude oil concerns", "link": "https://news.google.com/rss/articles/CBMi1gFBVV95cUxOMUFDOGdnZDc3VlZTRnBlVi1TNmpxRmRKTUtJaVVaYXFIOWJYRklfam54WG1OWkU2MEphUEhmbjlEVHBWUEp4TVhNSFZQN256ZGxjcjdaRUxsd1ZsNjYyc192SnlCNnVBdjJXU3gwdEVBX3AxMllFTXlLbFJOUGlkWnNRRjE2RXJRUUhUMVFraGpnZEFRQlFLUTVnY3lDREJkWXdsZ2l4MVhxNXZxSlUzMllBQy1IRm9ja1lYTUdzRXBqdHhvTkFOVlRJTVR1VFRFMjFEUzVR0gHbAUFVX3lxTFAwZDI2NmhfbDE1RmRhTlk3a0NVMGpWakRNLXpfMVdYQmJGcDRjYWpOTkVNTS0xaWc3MVRCRXVrV0g4YlNIY080RmtqN1QwUEdwRzlXOGdESzFXOUZxalN2RmJRZGh5MGdOUUFEQlQ1XzZOSFUtb2dEemREUFJXTUZYSTJ0eWwtRUpMWTBBa2ZBanpkV19PYkpUNFJFVDk0OWN4cnJTeUw1MjdVTjBDNF9Mamdzc3BrTHM3dXFWZWs3Ujh4ZWREQTZQVlRWYU1raXJpMmpOVDFpUC1vbw?oc=5", "source": "India Today", "published": "2026-10-30 05:07", "score": 0.153, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex Today Trades Flat | Nifty Below 22,950 | BSE Telecommunication Down 1.7%", "link": "https://news.google.com/rss/articles/CBMi0AFBVV95cUxOcUo1LU9Dd3BjaFU1bVBLSXhidmJfcFJmeDBUWFBaRUFJRF9FVlk0ckhLWTR2ZzJWQ0NIRkhXZUZOQzVHR0VDQjI2NE5IUl9PS0I3UmFSbVVnRVI2V2NoeDdOVGdPYXM2UDdkQTVIa2RMOTAzUzRKRExNTERWbk84eDVsN0RPM3gtcmhENlBhNEcyZEo5UFdoQWZKSkFiUTR1eDltLXpoTFF4VTM4UXUzLVFBSGIwMlVzV0lyTDRrSEFZaGNjTTlLRkp0N1ltbXln?oc=5", "source": "Equitymaster", "published": "2026-10-30 05:01", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty Rally 2nd Day on IT Buying, Trent Earnings", "link": "https://news.google.com/rss/articles/CBMipAFBVV95cUxPSHQwT25wUDBQTGJydm9RS2lOZkl5b1Bod190aV94bE5lRVZsNUVYX1ppMHQxRWc3bGZCNTRyeThwbE01bG11OUdmYUtnMEE1VkduNVZUTTBMRkZST2JDM05qaDVnUnY0LWlHV0cya1d6SEh5MnNhUjB1VUtIc2pPVmk5N245MDJ5VVNuR0I3b1VKRlFYcE1YM002b0RRb3IzY0ZMMdIBqgFBVV95cUxPQ2N4c1RBUjFWOGVlVUE2NzFITzlDOVJ3Rm83dXJhX2F4UmF0cE9RLXhOTTFIQzdmYVoyM1ZCamdabGlUTU9tVklfUm4xTVlPZTgyaUNTM1FnRnlUTzdiOVBFeURwTUhWd05qdUxiNjktVmlyQTZyeWZBa1VaWS1UanR2d0dLbEJyQm9YN2hBeXJ6d3hJdlVDR2Q4dmloMG5tbC1YOFR5TUdBUQ?oc=5", "source": "Rediff MoneyWiz", "published": "2026-10-30 04:58", "score": 0.691, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock Markets Today: Sensex, Nifty Up on Gains in IT Stocks", "link": "https://news.google.com/rss/articles/CBMiwgFBVV95cUxNRm9wczhmdDJsYW0tSUc3Q3VzRGVzTzZSMzdpR2o2MmJHX21lYTJHQmNUU2w3dElpcEpyUXFBbHZaZHlqRXNidXdpWVZEaWhXWlNaZlM2TTM1RXpWb1BwTUFNOWU4YjNsSnZzazJWbkdwNE5XTDdueHgzWWdwdWlCZkdUekVNdEhDaDhKRzZuUnFiWlNtaDIxd3RwNHFkWXB2andGM0ZwMUJLUHpOSDExLXZndGtjSmdCYzl1UXNLRWZWUdIBxAFBVV95cUxPTmdzMG1GRF93RmdyMFR4SUYzWFFxSUhLei1zLXZSZXZIaXdFY29CWU5zcVFLNHAxMzBJUGhfUWhEMW9STlRBME9aUUstYzZvMV9TaXFUOF9DWk1mM1BOOUVuUXVPMjJTUTI0Y1BRMkN4MDE0cENsV05mbEEteHAtMmR1WWM2TjVGbHNnWmdoTFVNR1Q3OER3WDFjUU1oMkt1VXJfRmt3bTEwWGM5ZmE0bDZRbDVUUUYzYmVEdl9QS04xNUxY?oc=5", "source": "Rediff", "published": "2026-10-30 04:57", "score": 0.649, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock market today: Sensex opens higher, Trent rallies; Suzlon tumbles 8%", "link": "https://news.google.com/rss/articles/CBMisAFBVV95cUxQd0tQR0Y5aWc2NjdaVlF0a0RFLTFKM0kwclM2WXFsQmJrTGtEbkFSYmRKSk95b3F5LVVYcXVTVTBJNWxBM2xqSzVKOGJGVllrMURVZmhRcmYxa0QyRVRqZW8xYS1kQjdneVktNHRLaUx6ZHlrY3F4ekk0RkktSkVWRl9rME9PNUFsbC1fcDQ5VTR2UDBwVUJGV1AwcXJQQk1pQlBleXF2WVVTWVhuNjZ1SNIBsAFBVV95cUxQd0tQR0Y5aWc2NjdaVlF0a0RFLTFKM0kwclM2WXFsQmJrTGtEbkFSYmRKSk95b3F5LVVYcXVTVTBJNWxBM2xqSzVKOGJGVllrMURVZmhRcmYxa0QyRVRqZW8xYS1kQjdneVktNHRLaUx6ZHlrY3F4ekk0RkktSkVWRl9rME9PNUFsbC1fcDQ5VTR2UDBwVUJGV1AwcXJQQk1pQlBleXF2WVVTWVhuNjZ1SA?oc=5", "source": "NewsDrum", "published": "2026-10-30 04:50", "score": -0.052, "label": "Neutral"}, {"symbol": "MARKET", "title": "Stock Market Today: Sensex Gains in Early Trade as Investors Focus on Earnings and Global Cues", "link": "https://news.google.com/rss/articles/CBMi0gFBVV95cUxPYjRWVkJta0FLZGc0VW1vVWVpMnZxckxFNll3RkVpdGZsbGJrWVJKZk85Y1ZWODY2ZUs3V3pBRnFYSHpCR0VrdXpEX09DTHJwTkgybTdvLTFzZnNCQ1NocmNyMXpyQjBfX29GeWZMdHY3M0g3T0NVeERRT3g0UUN2Vlg3eTNzRlhRaklnalQ2VlF5aWZDcGxZb1puYXNaX1NvUk9yLUZhUklaV0N0ZmhyeW9ROERDbGRtOF92V1pvU2l6NGJwMHNPZk5xWkdWcDhXX0E?oc=5", "source": "Business News This Week", "published": "2026-10-30 04:47", "score": 0.382, "label": "Positive"}, {"symbol": "MARKET", "title": "BLS Polymers IPO allotment today; GMP at 45% \u2014 check status on BSE, NSE and registrar", "link": "https://news.google.com/rss/articles/CBMi4AFBVV95cUxNYWZNdk04SlliSDd0WXdTVm9EYVFNc2lFcXJfbTdXN3BMLTVoeEM1UUh2eVl0WWJTSGpHNnY4aUEySTMxblYtblFzNHplTS1qRE14VXFkQ0lJcHpBa3FZMlphZk5LSEkxTGtFMWlSVm9HMnVieXRJbWc2bmlHdWJxZ1JkNF9IYnpOazNpWjVvcWttbThpdHFJNkJzT3Rrd3I2Q2hPUmduaExHZFA2WWZiaG1BOHVVdGdWRVUxenAtWjJxbU1Ga1lVT1VCcXY4RmlaUjFWWWQwUEg3UFJtcGVVdNIB5gFBVV95cUxNS1JhWVlMbVdvTTVwdFFuaTNRNnZDemVETm8wdjRKRk1LTWRJb3hpWUNWOVY0WUdDRU1iNThsMzFQbnZGQnVRWnBsYnFXVkNTLUh4M1BDZERhdVRXY056NGRuemN3NTZKTFNYUFp5TFlvSWJIdFhFX3RfeEdvcHlVQTA3TnFZNURBclJrR0d5YjN5V2xrbHlkaDM5a1NRVzI1WHUtT3ZoNm0wS3BqQ1BlZEtrSnR4SzNCbjducnpFRHZEMGxlX0sxMEE5NHdPMkM1bGJWN2Jnei1Za3dhMENZbGN0SmhSZw?oc=5", "source": "Moneycontrol.com", "published": "2026-10-30 04:26", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex, Nifty open marginally higher amid rising crude prices, weak global cues", "link": "https://news.google.com/rss/articles/CBMizwFBVV95cUxQZEVUOGVMeklfRE9LWkxXTEw2eHBrUG9qTkZjSkt1ZFpvZ0laVlpMS2FhN0ZTWnh5RnJjNFZsb1BTcjJreS0xS1pUT29lQVl0UXNUT1dlemdUZEFLVlhjQUQ2QXVCdnZYazJ4bnhnZERxWU9FMGg1WG9vM2pBZEFNV1ZycE55QTdvLXJscl9faTZfSGNWc2VYUTF3R3NUMXZfVWtDak5UNjFjQVJvZVpqTEFWRmhKQnozcjFQdjVKVWV3Z3lxVTA3QkNUU2F3Zjg?oc=5", "source": "TradingView", "published": "2026-10-30 04:19", "score": -0.557, "label": "Negative"}, {"symbol": "SYRMA", "title": "SYRMA Stock Price and Chart \u2014 NSE:SYRMA", "link": "https://news.google.com/rss/articles/CBMiWkFVX3lxTE1ud0tHczZETmVYWGR6VkdGWkdsc1M4N2pKRFM1UXdpNGlyWTVHbGVHS25tOUdlZjBPRExoWlZLcVQ3ckFPU21KdFQ5dHBqc09VdjJZeV9JMjVzUQ?oc=5", "source": "TradingView", "published": "2026-10-30 04:16", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "SFC Environmental Technologies IPO allotment: How to check status online on NSE, BSE, MUFG Intime India; listing date, time here", "link": "https://news.google.com/rss/articles/CBMiiwJBVV95cUxPQnU3M05KNTNXQ1M1NEp0YkxucF9JdkpfYjdVU242WjVTcmI1eFlCWk5odktUV1k2MDJlcUwwTEZzTEFtLU1YMnUtaFdwSk4zZFZScnJ5Uk1IbHpySnYzWmxwYlVBaTdxZ1p0M0NmSGpBMl82blNZSEw0RnNzVHBMbzFJZkV4VDNhUVQ5MWJzT21yelpGMlZ6RHp0Qk1lZzBkSl9GTDJRQk5ZR1FzeTE5OVF1a3VjWlc5eWlkT0M5R2ZsaDFuVWdWRzdEcTREVnVRVnBNUE0tN3JNUGtoY1g2bkVpWmd1OWV3Umc2T2JhekhDOXlRSVMtNDNXRjdBbXg4Qm5rZW8ycVAyRUk?oc=5", "source": "Upstox", "published": "2026-10-30 04:14", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex, Nifty open flat amid high crude oil prices, jump in IT stocks | Business News", "link": "https://news.google.com/rss/articles/CBMiiwJBVV95cUxQZzBDN3QzQVZXQWpWLTRSUV9kckdKZThxT2F4amxOS2JlZjRYc0puWVUzX3NoTVVxa0V0djNvd2ZNUjhZNEFjTU1DdGxIaGpacXVwb2o5bG9HNnIyRmNTSDZpLU5xSU9vR0RZYU10QUlBQnZPaTlQNDVvZGtaY0h2RnJvN1RXbGhDdG5Mek5UeUNjNXBNd201ekJBSksxTVY2YkhiUzRjaWlQYk9mV2s4Q1Y4RjBSSnd2d2hDcm15TEk2dm5UcHd2UG1IV0lSVVJnR2lYUVk0UHZCZFV2ZnVWZVR0dG5UcVhPSG5nQ2lZT3FpZi1VSjM5SkVrd1Q3R2FGYmhHY1ZERUptajTSAZACQVVfeXFMTVgza0lkcW9ucm1sWEE1YkQteVVCQXpfbE9SWU1FUWxpUHhtcG5pWlpkaVBKNmlka3JaN1N5MW02QTlZUmYwTFdYMUtObGhIQi11dkM0NG9zOHhVZVMzSVYwQU9KQ0l1bGFucktxZ21UcjV3TFd5Q2Q2dzJfUnYwZndLZlUwYkVVRTdhUUNTYkJvZm45Vm5MVUxQT3VyMWxDNDUySi0yNzVKN3hIRG9PZjJEMXpiSE40UWZqem5BU09fVjNSNWZxYzZzZTd1THFCSXRDS2NUV2RmY2RMa1R2bV9mN0pOUzJZaTFGSVlsMG83WTlFNjdSdkswa3NES2lLUW15SENIWWR5blNHWEJaa1Y?oc=5", "source": "Hindustan Times", "published": "2026-10-30 04:11", "score": 0.382, "label": "Positive"}, {"symbol": "MARKET", "title": "Coal India falls 3% post Q2 results but brokerages upbeat on PSU stock", "link": "https://news.google.com/rss/articles/CBMi0gFBVV95cUxNRWNKZDdGNHlETVRZR2VZMEZOdWJVUXZLbzd1RVRqazNuN0NrV2NUMWJDREZxanNlWElPSHRyRUFsY1lMZVRCTWtIMEZNSDBnd0xxREJtVG9FSFU1NUd4WDd4aGN1X2phV2lIY1pjTDRNMlNHYWxYNUZ5NjdnTVp2YndLa3ZDRjFiaGNvTkdQbm5fVTRvX09IakEzMm1CU0VFSjh6UmI1TjdybFJwc19mNjlwM09wU2RrSmRuTDBjOGhlalItM28wa2trQU5fZFpvOEHSAdcBQVVfeXFMTkVnMXZSY1FaMDlfNURXUTctY2NnMml1SExJZHV6SFNSYlhTVTBmckc5YVhrRTJHYndWMlg2YWo5OXRUUV9yNzgyWk9VVnVpU252WENCLXFQNnlTMEdVeHoxb293N1czYnE4WmwwV1lCZE9zS2VOYm9YSEZ2ZDE3RFlDeFMwRTJMZFFSNFh1X3B5RjZ6ek5fbVdqSHd4S3JOMEkwLUdBRkRMSEJ6SFE2eHFmZFJKejdGZ3Y1aGZHdnBHUjN3UUoyY0RYbmJoZnladHV6RS1xQTQ?oc=5", "source": "Business Standard", "published": "2026-10-30 03:59", "score": -0.202, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock Market Today (October 30): Sensex, Nifty Open Flat; Rising Oil Prices, Geopolitical Tensions In Focus", "link": "https://news.google.com/rss/articles/CBMigwJBVV95cUxPSkcyQktHdUYwRC1IRHJsakZFTVhZUHRvX2FiZDRnZmdVdy1jWkd3bkFRQWhkLWlQZHp2aE42MTYxU3ZvOURHQUFUdV9YTGdWb292M0xDWV9TekpLU0pNaEp5MnJDMXRDRFdnZHJDdi13VVM2Tzk0d3FyZmpfVHEtVEpaV29SN25RYS10SjV2SzRTV25uNmZRMjRvR2tXV0w5M1FqcUZVNEVXbFo1aHpyNm42VWQzbnVFY1Q3ZkhpRzF5YkIyWnBqM1JoNkZ2Q2tfc00wNnNKOEJlSW54LXFjSmVZNGlnTkRWS2Q0d2s2RlBQMUJwMnRSazdlaVhRak81d3NR0gGIAkFVX3lxTFBrc1lJc1k2dWYtM3dmcTRSNGZyS0htWEg4akV0MjhNU2dvRkMwTlg2a1poMk5sR0NCLURBNDBBMUwzZEJqa0ZPR1N5dWI1OHBWT3FYV2Itczh6Z2w1SEN0QjFHYTdNUlVEVmZza3F6aGtvSEhPZ19tZkNrQVVtcEFHdGFVNXhiQlJZR0RoTDBkdHBPTXE0WktPT21CQnFPWGQzUmM2b3I4bXBwbWQwX29QWEI2aVpyWk5fSmpYNHVtSWtRSkhmbU9ONHVrNThqQXVNT2dCUXY1R2NxaGQ1dkNTaHVqN1RmcHRTLXdOOEhTbkVncHVpYzNiSVVNY0dtUnhHOGthZF9YVQ?oc=5", "source": "Times Now", "published": "2026-10-30 03:51", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Stock Market Today: Sensex edges higher, Nifty opens above 22,950", "link": "https://news.google.com/rss/articles/CBMirgFBVV95cUxQNHhZR2hsX1hjcDRiWWxSc1V4QVNpNDFad3g3STVkMGdrTG9vaU5ObV9ZYUNIN3dpUlFUUmhsTHVHWmpHRVRMVVlfUHVFSURqZHJQaksycmc5Y2NVZEt1OVlyWFJOWEVsWDB6Tm1nOVFLOWJ0YjZ1UnJKMXJwcEJGdXljWlJUcmdhWTdkS1A4NFlpeXRDekdoN3l6SEQxSEhSQnhjcURURkkyajlGVHc?oc=5", "source": "Zee Business", "published": "2026-10-30 03:50", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty may gain 5-8% if external headwinds recede: Baldev Prakash", "link": "https://news.google.com/rss/articles/CBMi2gFBVV95cUxPcTJTc3Vndll3czhydnJSQk8xRzVicWRTQXIxdWVxb1diVGt1R2IxMEEzWkF6d2stU2F0U2o4SlZQSkVUMUJlSEdzMVdCQ05Da2pNaC1TaUJaYW9Za1Jfd2hFNmJpdTNXQ2NXbXR4SXJ2RU1na183RnUtSk5IYmJ2V0lfVWhTMkx5VXFULUNqY2dUVUVqY1BVbXZvRHpmeS01d0lQbWgyUFBqUURPV2tFTG00eWZQNmFxckRYUkxZVF81TGNEaDRMdkRNZ2txWDBYS2taNnJvTEJ5Z9IB3wFBVV95cUxNeVpabmdOVGR1X3M1R21QQlZJbGZ1MzJmdU81a3lGTTdlaVhGLVNwUUUtMF9QRlFJdXlkNG9UMVdiNjhhUmE4bGV6b2tGREdROGV4MXFGVk43NS1faWNZT3dpcUUwR1FXU19uZW5rUHhZUUFzcjdTVzkzTWlWTWZ0eGxYclR0S2t0VWlHcVpacFVjYlFPazNpYVY4TWxkeGQ4U2JTZTFNd0dDTXBiMS1kY0otbXZjbUpONDBhcnFwMFhqdEhfZW1oWDFvdkZRNkxfUktFaW85RjRXQWhSR2ZZ?oc=5", "source": "Business Standard", "published": "2026-10-30 03:34", "score": 0.625, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock market outlook: Crude oil prices to FPI inflows - 8 triggers that could reverse trend in Sensex, Nifty 50", "link": "https://news.google.com/rss/articles/CBMihgJBVV95cUxNOEZaNmc4dnEtRC16Vm5IVHhCd1Y2S19zcjRpVDdSWVZZajg4NjNGMGtyWnE0U2tPbjJUMXVkOFFlT1RERHZWQlBEOHJxWmdITmJPREVXZ1JIaUd3aWNQUTcyMUlqZnpFQWRiZHJLcE5YWmlZOUdlamlzX1NtYUdqczBmamh5Q044dnNPVHZsdEdfTWRmR2pxLUlXeXduUU1laHVpVHhfVmE3OThMWmdwMHdBa2RmbDdVZW82VUc3TGV4TVM1cG85anM5TUpROGVZZlR6MkYzczB4d2YwcU42YWlPeEtmUUw3Tk4wbFBZTDMwUGlSUWtDeHFmRjQyejJLaXhiVmxn0gGLAkFVX3lxTFBIdUVWNXVfYV8zN0tXeE1oZmNpZS1LTk1GNGxzUXRINHQxcWQ3Zy1SOTN1NWRta2tjeG1uQ2NJaE5nTGpzVUlHeXBtaHlaNTM5NWVGUmM4cm10M25WTGplanFSd0F5OUtYWXFGWklQYkpudlIzakczNDNjQi1HNmJYUnRxSTlsVi1xelhNd2h3MU9wSmpyNjcyMTRoLXNpcXBLc1VreklSaS1DNktabHpISXdSSmhpWXRGRm1wQlgzSUk2RVJOZDJTY21vMFdwS0FNZ2psM1NZT0FpbmZsZGQ5VnRlQmx0Q0RWM0FudEk4SEFqRldYOGpsNktPdGxPdU1DZ2hldlRMaEZFOA?oc=5", "source": "Livemint", "published": "2026-10-30 03:00", "score": -0.25, "label": "Negative"}, {"symbol": "MARKET", "title": "GIFT Nifty down, signals muted start for Sensex, Nifty; Asian markets plunge on AI spending worries, oil...", "link": "https://news.google.com/rss/articles/CBMigAJBVV95cUxOQkZmUHBNNXpGaGxiR2gxMnp3Ry1tVjBlTWlHMUZHUWc0SnJLbk5vU3kteU1zMVFkZDd6RGUwQ0RmZV9OUUtITUgtSU8tMURBT0ExV3dWaDF4MzFKZDhGcTJoeXVzUkg0QzRKcHJiSUZjV29XeGJhVDNIMXE5YzEyNEFiSTJ0cnYyUndHbXY1UTFtUzhZT1l0Q21YYi1Ycy0xekxBR0cxdkxFUmZuMEN1eklZd1c5ekNWV2JtbXEzV1F1emd2eXlhOWtXR3k5VTBaNGd4Z3M0U0ZTdUZ6a0tHakV1WktJd1YwMHh2M3pQUjkwSHRwcE93c0R1bzBhVTdD0gGGAkFVX3lxTE1SNmF2clJMZV9kSHRkZUpwZ0FjcUhOS0NEQVZ1S0NzYzBXaE5jMXQ0Y3NuYUR0VEVFZE94OFpRbGtiYUgxbVc3TzRad3JGb2t6ZDJZQVVzMnd6QXpMeGFMd3RHWTF2QmNGUjlMT0NnTDQ4SURVZ2UtcnJLUjRncVptM1BGMnhtdWRCM1N2STRsUnpSWDhYbnlwcTF1UHhNOUpadWpzaDJTOFZJUzVoN0w2Q3dRNG0tdFpUbDdrVm9XWk5lRUF5bUk3X3BmVTVBZ0E5dzIxMzJDeHdhbWVxVFRtcFNfWkVyV0QtN1BzbFFkRkJiLVVlMVAzMENGMlVYUU43ZGdvUnc?oc=5", "source": "Moneycontrol.com", "published": "2026-10-30 02:41", "score": 0.408, "label": "Positive"}, {"symbol": "MARKET", "title": "Indian shares seen opening higher after earnings-led rebound; higher oil to cap gains", "link": "https://news.google.com/rss/articles/CBMi6gFBVV95cUxORkRQbWxVNzVaYjNjN2d0aXNjQURWdFEyOXVPY2hENENXdU42M2t6M3dWM1Z4M1A1dVBPQ1RoTW8zZF85eXhQZE9Yb1ZORE1sdTcyWmlHem04YXBxWHFPYlFnenYyY0FDMENWdGh2OWd4VERuMERHOFVDTHFPU0FuM2FYOWZ6a0dKUUdJZnh2SlJZUC1aZkNCU0JFSFFqNTROYzRIcEVPek9QejlIZTBlUXVhbHJheTl5YnZXX09MYVpUSmZaV3VaYWE0WkZhYzdwUUo4bU1pS0hKSWNTblg5MnBFX1ZpbW9SZ1HSAe8BQVVfeXFMTlV4SnU3cWpJSUQ0U0ZPdEg3Q016RmVCSmUtb09pY1hsZjBweEZvSDM3d3dlQUwzRy1WX0RISm5naDZCQ1VIWFNTYzdiMm84cW5UZjgzQ2ljOVJFVEctUnFzR0pKZ3R2RE5qVFZvdURFNldfT183VktEcUd2bjgtWGxoSjVsdTFvMjhiXzAyMVBjb0czNjNQRkJmN1Fjb19rUzlFVDNmT3F0MnBCNFAzUnVaTHdXdDBGTl9IQ3RIM3Z3VTR2VHVrTDg4cWR1a25GY1BaUVVaN2RtYVRULTVCN1UtaGJQTlJXcUtTRXBoUk0?oc=5", "source": "Livemint", "published": "2026-10-30 02:35", "score": 0.382, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock Market Today, October 30: RIL, Jio Q2 results, Japan rate decision, forex reserves - 10 key triggers for Sensex, Nifty", "link": "https://news.google.com/rss/articles/CBMi_AFBVV95cUxNamZ1UG1fNEpHV0dYVE1zb1lmLWJxUk5rSEx0M2hsV0NGRXdSaElkZTBNUjZXbU5pZW5STUpUbEkzTFg2OEhGWlk4Q2hkeXZxdHAzMG1vZFZVT2VoTkdweEt4Z0ppU3BscGlFMjN5ell5NE5wNHJ4NWpkV05PMkVENUVHVHR1bjAzQWtNTW8yelVwWjN3SldlUkxpaEIwdHlQdXFRVXh3dUZYR1JMZUVwY3Y3S09GdXBpTVFVVGFxaWdYcXRzR0NYVlBFMVR2NmJYVUNJcmZmVlhXQnJiRG9pZzBiUlJuMnpJVlBpWjBzTjh3bkhEeHpRRWJRdU7SAYICQVVfeXFMTVlBRG51UDZtVlB0OENLRUZvdlJTOXUzNU44SndaYUoxVXplVS1GZFpTMXF4WVUwTUp5bHotM0N6SXJtZlJmdzE3ZjFUaDcwUlBpWmR2c2ZpTUJNSUREOTV5cUN3eUFsTWZ0dmt3UVhEYzFaYTJaaWRFV284OGlZeGVoLUJfTElLZVVqUTVudUR4aGR4aHVEb3lYXzg2WUpIbjR5OVJ0NVdUUE1HWGdfSHoxckxvM09YdVBGRnNLV3laOXNNckVRWXEyd1pvelRCelluV1RNT1Zxb25reU42ODN6SlhBVWdLV0lXd2tXMGx0QVBXM2Y4WVNzZ3Y3c2lTV2Rn?oc=5", "source": "ET Now", "published": "2026-10-30 02:21", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock Market Today: Gift Nifty, Tech Stocks Selloff To Binance Hack; Five Key Factors For Sensex, Nifty 50 On Oct 30", "link": "https://news.google.com/rss/articles/CBMigAJBVV95cUxNdkc2UTMzMXp6a3dsbm55eXlZMzFHdzJ2S2UtYWkzcVdJekZDOHh1RVJaOXFMMlFwdXdWd0lMajR2TUItTTl3cF84b2R2R1NXVmd1dVlta0VpcTFhYWkxUlhnZDYxTHhoeEtYM0JGeDAzQkRlc0FNR1dCNWV1RUw1VUdYa1FkQ09FMWZmM21mN2pwQTVfUVU5ejlScGhzY3F0MjVHY1lTNmZkdHNJRTk5dG0zODcwOTVHRzRqYi1OVE1BUVQwbWdQWkQzWE13ZWZlTmJYUGlHRnhGTWJhWGtQTkJmMExFa0ZURmJzcGtOeWVwWHg4SlNfUnc5TC15eUxT0gGIAkFVX3lxTE5kMVJROUdWQWIwcWlxNGduSHdncXluWWduV1l3a3MtMzRMcXdsUmdzekdkVkVPR1JRNUp3bVVhb19WREFhTzUyYU5BVzRpUDNEZTduODNsb1ZyMDR1OGRybGRhWlRGbzB1Q25iTTRLZGtYMlpBT050bTM0TXBDX1BfN1JOLUttSkd2N0dYT2RGX1dUOTE5Tk1aOVVSRXlmd2tmaUVTUTczcTlrVTU0QnEtSHhJdjhDa1Y5R2R0aHlJQVhpNkg5bC1FcWtOU09KN0FuY3pmZW1RcWplZ0toNUZWYXdMZGx4aGJBZXpidlF6MXhnWGpmaHEwUTZVYVVlUE1VM3FBanFvZg?oc=5", "source": "NDTV Profit", "published": "2026-10-30 01:44", "score": 0.807, "label": "Positive"}, {"symbol": "THANGAMAYL", "title": "Thangamayil FY26 Net Profit Jumps 196% to \u20b935,165 Lakhs", "link": "https://news.google.com/rss/articles/CBMi8AFBVV95cUxNZWQxVFZva3o0cms1Y2N2ZmRJMnk0TmZzTTdLUWVuZE8taXVteEgyeDhHQi1wYUIyU0RGb3J5QWFxd2pLSTJILUVSOEZVZTBDbExkVkMtT0tiNjhGOGpubU1KQ25LQ1ZFUXkyUDZmY0FIdWZBSm96cm1vZ3R3VEtQUHFKLTBZM18tZmx4NDhNRWM2OURvX2xQQXJncWtod1ZoR3ZoV3A4bldUSkxXMU8xNlEzU2tMeWYxeHMwYk5LeVlYQ3hJeGVqMkdNYlRIQTZnUXpxTk5xZzA0aGZqNGVId0pnbTRLd3RJNWZZcWQ3azQ?oc=5", "source": "scanx.trade", "published": "2026-10-30 01:17", "score": 0.66, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock market outlook today, 30 Oct: Sensex, Nifty prediction - DJIA, S&amp;P, NASDAQ, GIFT Nifty, Kospi, Nikkei, Taiwan cues", "link": "https://news.google.com/rss/articles/CBMihAJBVV95cUxNU0lLTXdXRXlnWnktM1lpdVdQMEZ1Q0ltbHlFQlZOa1pRM09LcGlnYTRubzNDcks4N21ZaGdEV3ZpRFV0N1FhT3htZkM5djl3WngtREVSVkdhbWkzWFQzNjJQN2MwZDVYaXQ3Q3pPOUxLaDlVUFF5aEFzWkY2TU1jRjloa19jNTBBMHZMYkZGVExUMlV5aXlXaVV6M3Z4QV9WaDF2ekFRMlg4dXV1aE1TMWR5bHlUUi1XODB1MHFraXVKLXZGOXJvNTdmRnJNNmY5WU1JSXJ1dXpVTjdXR2NyVUpVSUdYbFFqS0gybXp5MG5tSDdhWEpTb1RVMkJlZ29ZN09WNdIBigJBVV95cUxQQ3pIRzJQZmY1VXpnc0Nra014TklOZ0lvNkhtZUJ0UFJiQmtZQ090aUpZTlFfTWdMMW9HT1U1UVJEU2NUcVFUUmtyb0E2emhPa1hmMGd6eDYyMWk4R3JURTFVYThqZzNBS3lyNC1zcTRyajNKcWF0d213aWd2Y1J3aGRNMVlqRDhOaUZpNktDcmNSRFlpMnVVU1NOTlV3TTMtX2tLSkNyMWNrVWtwd29sQkxxTkUxYll2X1FoOWJVY2ZTcUVBUXRMVGVTNnY5UGZlNVZpRTQ1bnhUdzBkM1BPTjl4dUxfS2FRd3NzZUpJMF9CWW44QXRWaVFuaW02M29sZlBCMThPRWlfUQ?oc=5", "source": "Livemint", "published": "2026-10-30 01:14", "score": 0.842, "label": "Positive"}, {"symbol": "MARKET", "title": "eClerx Services Q2 FY27 Results | Birlasoft Q2 FY27 Results | Top Buzzing Stocks Today", "link": "https://news.google.com/rss/articles/CBMi3gFBVV95cUxOS0Fuc0x6cVdyNW5qTUFaU2FrZU8wRzZaeXA3ZV9rZ3FtTE9jeml2NzVaOWhaV2stVzl0VnJDRERDNXlnX1dnSUI5M3dROEpacDFlTDF3QldiVTBaVGhvVmR5ZnoySE9zUlVIN0RyeVItTGpiVkFXSjV3TW9hdXF6X1AyWFdyeVNNaGQ3VEh0cWphT3dnTmlBWHBYZmwtazZ4REVpSHJtWC05cUpRc3VCZmVKYkpCbnRvLVl5VXBYVTk5ZTZWZ1FNZVY4V1JNVFV4U2FwNDhuNkZHRjJ6NGc?oc=5", "source": "Equitymaster", "published": "2026-10-30 00:30", "score": 0.202, "label": "Positive"}, {"symbol": "MARKET", "title": "Advance-decline ratio hits 7-month low as market breadth weakens", "link": "https://news.google.com/rss/articles/CBMi0gFBVV95cUxNSXRYTnJUbnhsTDFmcG5lMlVpT3lvVjNCUDR5NmJQTHU2UmdnZ21RZ25XOWRFdmF5X2prVU5nYVMyb0pZMXBZRkZ0SmZmaTczMVVEUlRXblVOUS1aMlg5V2lrMzlHQVJmU285blJNM0Y4T3UtNVlQd184cmlNcTZRUkVJNmc5Qjdva1VVUlJ2RU1taWlqNk1lWVpVOEtFZkNaMTdwRF9rUEZNQVdCUGQyTFBwWFJOVkl5RGx0a0RYVWtQS2pNYWhUY20xWHRJV2pkeFHSAdcBQVVfeXFMTUVCeWwyaTY1Um55NjExa2t4WXR1b09RSHlvRDlPYlA4M3Z4aTVCX05lQ1FpNTlsM3I2dUVRR0FSWk9hNmdYSFdkeWxCM3hDaUZMMVlockdfSnV2bUEtSlBEaHVCdW5NRGw1YjdTaGRjWDlMaDMzMy14Q1RyaHA5UVVxVE1RYXNBTnFQNU9aeVE4amd1UmNFWG5PdlVMMzhvQTlQZGxNeTJVb0ptUUZyNlFjY0tHX0EzQU5PYzVCSXZjdWVpaWRBRnlDRE1oQWNFOWJFRHZQdWM?oc=5", "source": "The Economic Times", "published": "2026-10-30 00:23", "score": -0.612, "label": "Negative"}, {"symbol": "AETHER", "title": "Ather Energy Share Price Today, Ather Energy Stock Price Live NSE/BSE Updates | The Economic Times", "link": "https://news.google.com/rss/articles/CBMiigFBVV95cUxNMmpPVXcxeVFIRHF1aHV6dFRLVnhXV3djOWRQN2tuMmxVTnhDeVNJSnFoV2ZscmFoaEtaWXhCT0tabGNHdVhlOV8zcG45eTJrYS04ek9hSlNlMEZPYlpyeS1pbXNqbjlVVklKeEFrX1R6OUEzXzhRdjNneFZzbEFFMjc4MmZ4T3dSMnc?oc=5", "source": "The Economic Times", "published": "2026-10-30 00:10", "score": 0.494, "label": "Positive"}, {"symbol": "SYRMA", "title": "ZF Commercial Vehicle Control Systems India Share Price, Stock Price - NSE/BSE Live", "link": "https://news.google.com/rss/articles/CBMipAFBVV95cUxQaGJ5UUduMmFWUzQxODJRNUFmT0hGMWE5Ykx6RXRJRFRRMGowSGJ2eE5INlhVYVU2OENDblNfcUFlRUlHNzZBRlFyQlZ6dmxtX1NXUjE4dUxEOHpkM1U2NXM3dl9jdzZsU2FUTnQ3SFRqWUNxOXl4cUV1NzllM296YVBMQlktaHQ3V21QQktRWEp4Vm9xbkhjZ0Y2TEY1SzVDVTVkZw?oc=5", "source": "NDTV Profit", "published": "2026-10-29 17:53", "score": 0.0, "label": "Neutral"}, {"symbol": "AEROFLEX", "title": "Aeroflex Industries (NSE:AEROFLEX) Q2 FY27 Results and Hyd-Air Amalgamation", "link": "https://news.google.com/rss/articles/CBMi8AFBVV95cUxNVzBvb2wxcTMxV1h4Y0l6T01NR1p3blBHcUxEN1pKQVNxVTZXQWFmWmdyMDFMaHRxRERqNkJLMjQ4WGJzNENnUklwaUJBMHVLMmFodmdmWXlPLTdhOEpZSGJwLU9ON1NmUks1VUE5cnNYUHYzQ0hrb1pveURwTU9yd0J3WUMwSmJkWmEyMEZrMUhNcVBCZWRpMV9HSFpPdVFKV0xXOU9BTFB5cWVVbTlFdGU3YmY3cHQtX3M1UTVFYVMwZHg5a3djc09lY09PTWt5UzdRMnJEUF94U0N6ZlZ3X2doc3hmSXFMRGxiZjA5SDQ?oc=5", "source": "Kalkine India", "published": "2026-10-29 15:28", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Benchmarks rise over 1% on positive Q2 earnings, easing crude prices", "link": "https://news.google.com/rss/articles/CBMi0AFBVV95cUxQN2x1Nk5sek1aeDluWGNMSnEwREx2SGR5ZjRTd0tzT1NiQ3hoY3htWkJtSW1nYWlrOWRNeS1LVlNMYU5sRVF3eWRzQTVzallfc1JEMVhkSWc3TV9IM21vWG1vTmZRUmVEUmllVVhNdU13YUVVS01LUFNzTHVRRE80bDdaVW5XWXFUTm1oVjZNN2dQaExRMmpMNEdiSzdGMlhuTVBvZ2ZVTTZ1aUdYSTRhek9HbXFMZDNyTEdFSF9GLUZkRGZPOVlTU2JsNTF4WWtw0gHWAUFVX3lxTFB2LU9UckFtY0YwdFAtQ080T2I5a0NJZFowOEJ5bGJsRUR0M1E4WU5jR1d1X2ViencxOWR1dUVlYlVBdS1XRDhBWmpHVUhDNWhxbTdIWkdtdDBLY1hSN2hOclNhcG9HYlRITk81azlSZzFIY0lWZ0RrREg3THYxQWw0ZzIwUnFfUVFpbDQtQ3JESmpTMTZ2U1NFRHk5YjJRekdGWmlUaUhPR0I1UnYxc2dMSmRTdV9yc3hVM1VFc3lXWjZPRTB2UzZzT2kwVE9zMlhkZUQ0NFE?oc=5", "source": "Business Standard", "published": "2026-10-29 14:36", "score": 0.226, "label": "Positive"}, {"symbol": "MARKET", "title": "Indian Equities Rally: Sensex Jumps 905 Pts, Nifty Tops 22,900", "link": "https://news.google.com/rss/articles/CBMixgFBVV95cUxNYUVZT0t1WTRFOVoyX2FhRnJvNFl6cWcwVFhIS3llaUlxMzVHQmpoUXhYVHdQM002TFNvdXA2VktDUk5DczlZQ2ZOUkM4X2lyQXhOMkNqcDk3M1BnUkZYLVpPdVNjeGlaaDNrWGZEdXBncTUyMl9lZDVpTTZrclU5eXpaLWdELV8ybmo4cVgxZTRQRkZneC1nSDVESGNzZUhPRnkxMHNaUC1JRlRaQUx0d180VHN2bmZXX1pGM0FzMm0ydmJoZlHSAcgBQVVfeXFMUGFhZ2k5dzdoSnBTZGxVNlpZdVNMYzBwdnJlUmh0NU1Xa2FGOTBSMFV6STJFdzRSQUFWOE1udE1abXdWUklOdVJlN2lFSk1DVlVRbTdNRDlsZFZ6STd2ZE5UYU8zZElhRGR5U1M5NDZFaDROZjNXRS1leXdtNDJsT3JjUDQ3Z1dkd1B3Zjl0Y0RVRWhVRS04b2RxWkZvRUJPY0pBM21IZUY1TDdPNXNwUmlTdEk3WGViTWtQYjltQ3pOb2NvVV9SVHU?oc=5", "source": "Rediff", "published": "2026-10-29 12:44", "score": 0.9, "label": "Positive"}, {"symbol": "SYRMA", "title": "Syrma SGS Tech - Technical picks for Diwali! 10 stocks PL Capital is bullish on this festive season. See full list", "link": "https://news.google.com/rss/articles/CBMijwJBVV95cUxPY0dYWGhsUHRsOC1HMHVFeFR6YlBhcENObTZlV3lXZkJyUVFLMU50T2pfT3k1Qk5aWkJBUWJOZDE4TTNrSDlUd1dCbTJ0NjlYal9SUmFjSTg0LWt5RldXS3YwRzVOZjBGbk96OF9IQnRETU9VcXFXM2tVMHJWb2R4Szk5MU5YNlpsa05xMldaajYxaUtXc3JmWnJZREZpdHlkM2dsS2Z5VDE2bjRZdmZidE1fR3NXTXRGdFdMVTh4czJOVDBxZFB0MDk4bEN4RmZpN2dJT2JyeFMyYVlYbXdxVE13dmxSWEtTa0NnWDM3eGJIaDA2ejJpdkZHcVFLUTJGZEhJVFduNEh0aGNGY3Q0?oc=5", "source": "The Economic Times", "published": "2026-10-29 11:52", "score": 0.771, "label": "Positive"}, {"symbol": "MARKET", "title": "Share Market Today: Nifty 50, Bank Nifty | Oct 29, 2026", "link": "https://news.google.com/rss/articles/CBMizAFBVV95cUxOTzVHQkVNVVJvd3ItZVNfcUVReFBxSXIzdVNXdnpxUF9iYUg5eURJTmlFbHN4M2hqd014d1BKOV9RdUxtTm5XQjd2TmNGU1piWU9uZUZ2S0c3WWFTcnpoRTFQYmN4T2ZLNWNadndEY0h2OFMzXzdoUDU3dXB6cEhhcG45dEdVLVdvanplODBFTnJod2JiWi0zaml0S1Q5MEF1LVFfajRXS1hoakRDZk5jZ3N3akYteTB1RUloODg4UU9aRDZvRUg4bW9TMDA?oc=5", "source": "Liquide Blog", "published": "2026-10-29 11:41", "score": 0.66, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex jumps 905 points, Nifty gains 238 points as markets stage strong rebound", "link": "https://news.google.com/rss/articles/CBMiygFBVV95cUxNQkR0eEdvajJ2ZVB6SjltUGY0ODdUZ1BYZGxjb3Nfdjd4Y3hYMVZ3MlNqU1BBSmsyQ05fWDVFZ0s1SEd5dmg3ay1OdnNrT0ZINnVfVnU0dzJodXg5ZzBvejZRY2pMb3RBREYwMGNIaTdwXzZsZXJkOEIxUFJxVFRvdjgzVnhfMGdOTVNUVDFmOE4tVDVvM1lZNHlHNlZ6cTNYa000YTVTM19qV1VFek40RVUxVUU4WXhWZjQtV3Y5REdrN1V0VllxMU930gHPAUFVX3lxTE5pbk1LaDNBZDF1WGstdlROOUVfSXBQX2FuaE5FTzVQOEhCNHh1UTdEdmtua3JzLUY2RDRBYkJ5Z0xLRVdRMFkxZEZlcTl3cFZLSXZuM0VBOUw3SDYyazBGcVVyZWFOTVhqRDhteTBnTVc4UzBENXk1YXZwcVY1V19LZ0JVSWV0aGpfbDY0YWwxN1ZOVUlQeVlaTUNhY0NuZVVkTmNvZ2Z3VG1QUk5yd2p5VzdyRTRYUFN0Q2lYejd6cVF1YVBGQko1TzhuOGJxbw?oc=5", "source": "Telegraph India", "published": "2026-10-29 10:56", "score": 0.872, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty see sharp recovery; is the worst finally over?", "link": "https://news.google.com/rss/articles/CBMiwwFBVV95cUxOOEJuMmFvQ1BDSEJEeUIzWTZSdDJ1cGtQZW0ySm4tM2xhM2xIQlhIUHVJUXNFM1pyMGpUMlhQeXIyZXhDT2VLcVRFc3ZfOGVIUTVQMEwwenIxLVF5eDZfRk01VkdBYWN6cmh6Z0dJYmtxNV8wRDdOM0FBOV9QbHluRWFhUkRwalVsM3ZyX19fajBId2tiUmFRUEY0VUkxaVpyOE00cXhXTS1ueFRCRlpacUZYWnNJcFRSMmtQX2ptTXVfT1HSAcgBQVVfeXFMTkhyMVUwVHBnRTl3RUY4U1RJSHNacGtrVEhNbnR5bjFVak9yeTBfWHlqMXZjaTFLUFlFNUtQM1FjY2ZJdW13WFdYR2M2WmppQnBiOTZ2WTRJUG9mNGExOFVxVXJ2OEg3aHpBRmM5eUJoUHBxT2VrUGcyekRPVm9VZFlfX0JuWTFydFlPYnR6OEpscUdPNHcydU9KejNORW5Jd1N5UGh6TGxidWgwb2R2Q01ydWVJVF9Dckd1X2FETVdtVmUxdVd2Tks?oc=5", "source": "Business Today", "published": "2026-10-29 10:50", "score": -0.34, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex Soars 905 Points; Nifty Near 22,940 as Markets Rebound", "link": "https://news.google.com/rss/articles/CBMiyAFBVV95cUxNTEctOW5hZk9uc1ItTjBmOVl2NmRMZlViRF9VWG5fZEdSMnQ1YU5OSEhTcXZ4RU0yMF9XSDZZeDJQbHprOS0zYkxOSW9scjBCeDlJTTF3Wmo0TDJNWXFTMzNWVUJhZFIxQmFMSmo3Tjk2Sk95RFNzVS0tbDdQWnM0RjlhdnliUldJWGh3c29mTUk3Y04zbExYVno2TDBVdTdka3VvcktuTXlYeWFBNDhDbGlWT1VqVTJuUVQ3YWVoZmRBa3dZb2V2Sg?oc=5", "source": "HDFC Sky", "published": "2026-10-29 10:46", "score": 0.727, "label": "Positive"}, {"symbol": "MARKET", "title": "Indian markets stage a strong rebound, recouping yesterday\u2019s losses as Sensex surges over 1%", "link": "https://news.google.com/rss/articles/CBMi2wFBVV95cUxPNjhqLWVyaGVfUDI5aXNGT3VhMUNQc2wwQVQtVnA3S29YWVc3ZlpRVmQ4WG9JUHBZVjhpOVpIYi04YVBlMmVuMF9ZOXdHM3pfUGNSS1Fzcm05dnQ4Z1ZPN3l4WUVTMlRZdlVRcUQxUDVVdmE2RXg4aF9wcGpYZmlnQTNOVG5zUmJ2OVh6a0dOTjFKY3h1WC0xOU1qd0dZUndxc2NjRUxGNE13cVd5dUJGTTZhUUh4Vnlrc29vRHZmTW4xQmhwM1FpWVJTQVlNYldZRENhTDZWcW5oYm_SAeg</t>
+          <t>XUjE4dUxEOHpkM1U2NXM3dl9jdzZsU2FUTnQ3SFRqWUNxOXl4cUV1NzllM296YVBMQlktaHQ3V21QQktRWEp4Vm9xbkhjZ0Y2TEY1SzVDVTVkZw?oc=5", "source": "NDTV Profit", "published": "2026-10-29 17:53", "score": 0.0, "label": "Neutral"}, {"symbol": "AEROFLEX", "title": "Aeroflex Industries (NSE:AEROFLEX) Q2 FY27 Results and Hyd-Air Amalgamation", "link": "https://news.google.com/rss/articles/CBMi8AFBVV95cUxNVzBvb2wxcTMxV1h4Y0l6T01NR1p3blBHcUxEN1pKQVNxVTZXQWFmWmdyMDFMaHRxRERqNkJLMjQ4WGJzNENnUklwaUJBMHVLMmFodmdmWXlPLTdhOEpZSGJwLU9ON1NmUks1VUE5cnNYUHYzQ0hrb1pveURwTU9yd0J3WUMwSmJkWmEyMEZrMUhNcVBCZWRpMV9HSFpPdVFKV0xXOU9BTFB5cWVVbTlFdGU3YmY3cHQtX3M1UTVFYVMwZHg5a3djc09lY09PTWt5UzdRMnJEUF94U0N6ZlZ3X2doc3hmSXFMRGxiZjA5SDQ?oc=5", "source": "Kalkine India", "published": "2026-10-29 15:28", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Benchmarks rise over 1% on positive Q2 earnings, easing crude prices", "link": "https://news.google.com/rss/articles/CBMi0AFBVV95cUxQN2x1Nk5sek1aeDluWGNMSnEwREx2SGR5ZjRTd0tzT1NiQ3hoY3htWkJtSW1nYWlrOWRNeS1LVlNMYU5sRVF3eWRzQTVzallfc1JEMVhkSWc3TV9IM21vWG1vTmZRUmVEUmllVVhNdU13YUVVS01LUFNzTHVRRE80bDdaVW5XWXFUTm1oVjZNN2dQaExRMmpMNEdiSzdGMlhuTVBvZ2ZVTTZ1aUdYSTRhek9HbXFMZDNyTEdFSF9GLUZkRGZPOVlTU2JsNTF4WWtw0gHWAUFVX3lxTFB2LU9UckFtY0YwdFAtQ080T2I5a0NJZFowOEJ5bGJsRUR0M1E4WU5jR1d1X2ViencxOWR1dUVlYlVBdS1XRDhBWmpHVUhDNWhxbTdIWkdtdDBLY1hSN2hOclNhcG9HYlRITk81azlSZzFIY0lWZ0RrREg3THYxQWw0ZzIwUnFfUVFpbDQtQ3JESmpTMTZ2U1NFRHk5YjJRekdGWmlUaUhPR0I1UnYxc2dMSmRTdV9yc3hVM1VFc3lXWjZPRTB2UzZzT2kwVE9zMlhkZUQ0NFE?oc=5", "source": "Business Standard", "published": "2026-10-29 14:36", "score": 0.226, "label": "Positive"}, {"symbol": "AETHER", "title": "GUJALKALI Share Price Today - Gujarat Alkalies &amp; Chemicals on NSE/BSE", "link": "https://news.google.com/rss/articles/CBMiakFVX3lxTE1jSVBOQjUwbHMxcUhlTUlVcWJmVjlNbWhoMEZXTWZvRUVVMnJZdWlDV0xWcVZKaURzT1o1UG1xaENWRkNkX1BDVzNZUHBLa0dJNWlsaWRUSi0wNGZqRExjZTU5T3dNTmViSXc?oc=5", "source": "scanx.trade", "published": "2026-10-29 14:27", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Why markets rallied: Sensex jumps over 900 points, Nifty gains 1 per cent; 5 key reasons", "link": "https://news.google.com/rss/articles/CBMi9AFBVV95cUxOV2JFLS1oXzVnM3R0aFVjdkpzTDM0cVh6cWRtUnBmOVpqbGpGU19iWjAyS2NTdEhpMHZITGZwNm1kbFg5YVVpWUkzOEpaWHNvVGRCYTRyOUM0RWtsTkJIWFpYSjYwTXdfTjFVTXNEVmpROHBfblVxdTVTRlI5NmVpYlUwX3JXT2J6M0dWVmNRWjZwSDZSMlpaTHhxdUFRRGVNZDh1VV9mS2I3Wkp1UUx2SnVOaVMtTEtGZFhDcW53V0ZWWUFMdWJqU3dzeE1DV1dVMkR3THhJeHg2blJmVXU0SEtQbHdFSDN2Q0cyU0RMMGVPM0xM0gH6AUFVX3lxTE1CQWRvOTFHOU9DMTAtMjUyTWEyem5lQVRyYzNQMzd1OWxPRHEyVUx3OEtsUUc0Uy16Q0lkTTE2X0FBQ1VyaTFwUnFNMnc2b0pIM1N1SUdKcnhuWG1YbDNGZUE0RE5uSzBqdDcyRWEwN3lLR3htVTBfLTNSclZTeW84ajcwQ05tWS1pczQtN0dJdEtKdXA4d0N3UTlrdDFOWXVVdG8xMDVpQ2JkaGI3Nnlic1RHaUtEMWlQS0VrajR3RGc5SWo0aWNrSEloNzczZ3lMQ01LZ2hkWXIxSFBCanJHSUpwUWxsVGt3S2J5MVNvTFI2aFZYWXFPbmc?oc=5", "source": "The Times of India", "published": "2026-10-29 13:03", "score": 0.807, "label": "Positive"}, {"symbol": "MARKET", "title": "Indian Equities Rally: Sensex Jumps 905 Pts, Nifty Tops 22,900", "link": "https://news.google.com/rss/articles/CBMixgFBVV95cUxNYUVZT0t1WTRFOVoyX2FhRnJvNFl6cWcwVFhIS3llaUlxMzVHQmpoUXhYVHdQM002TFNvdXA2VktDUk5DczlZQ2ZOUkM4X2lyQXhOMkNqcDk3M1BnUkZYLVpPdVNjeGlaaDNrWGZEdXBncTUyMl9lZDVpTTZrclU5eXpaLWdELV8ybmo4cVgxZTRQRkZneC1nSDVESGNzZUhPRnkxMHNaUC1JRlRaQUx0d180VHN2bmZXX1pGM0FzMm0ydmJoZlHSAcgBQVVfeXFMUGFhZ2k5dzdoSnBTZGxVNlpZdVNMYzBwdnJlUmh0NU1Xa2FGOTBSMFV6STJFdzRSQUFWOE1udE1abXdWUklOdVJlN2lFSk1DVlVRbTdNRDlsZFZ6STd2ZE5UYU8zZElhRGR5U1M5NDZFaDROZjNXRS1leXdtNDJsT3JjUDQ3Z1dkd1B3Zjl0Y0RVRWhVRS04b2RxWkZvRUJPY0pBM21IZUY1TDdPNXNwUmlTdEk3WGViTWtQYjltQ3pOb2NvVV9SVHU?oc=5", "source": "Rediff", "published": "2026-10-29 12:44", "score": 0.9, "label": "Positive"}, {"symbol": "SYRMA", "title": "Syrma SGS Tech - Technical picks for Diwali! 10 stocks PL Capital is bullish on this festive season. See full list", "link": "https://news.google.com/rss/articles/CBMijwJBVV95cUxPY0dYWGhsUHRsOC1HMHVFeFR6YlBhcENObTZlV3lXZkJyUVFLMU50T2pfT3k1Qk5aWkJBUWJOZDE4TTNrSDlUd1dCbTJ0NjlYal9SUmFjSTg0LWt5RldXS3YwRzVOZjBGbk96OF9IQnRETU9VcXFXM2tVMHJWb2R4Szk5MU5YNlpsa05xMldaajYxaUtXc3JmWnJZREZpdHlkM2dsS2Z5VDE2bjRZdmZidE1fR3NXTXRGdFdMVTh4czJOVDBxZFB0MDk4bEN4RmZpN2dJT2JyeFMyYVlYbXdxVE13dmxSWEtTa0NnWDM3eGJIaDA2ejJpdkZHcVFLUTJGZEhJVFduNEh0aGNGY3Q0?oc=5", "source": "The Economic Times", "published": "2026-10-29 11:52", "score": 0.771, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex Surges 905 Pts, Nifty Tops 22,900 on Banking, FMCG Boost", "link": "https://news.google.com/rss/articles/CBMiqwFBVV95cUxQYldTSk5iZ1RLbnd3cU05cDdfbVVwaFJnZVNSTjlPX3B4MW9uZlNlUkhyN05LQVJlTGVYQjN5eXM0aGR6MFZ5U2FPcjE1U2Zoa2tzbm15X1VrVm9JTnFiUjBvOWRybElwcldLbGlCNk5ackFCQnFNeWo3ejdRcFktdHprRGRha3FmN2tzVm83VDVyX21TZkFSdTE0WnlMQjBRSWtMN3BzcGlOdlXSAbABQVVfeXFMTnZxRzZteVlmN3gzSEpRUEJ6ZXJZM0VDMjV5LVA2b3FicTBLYUpmNG5DdXdkbDJIdllXU0llTjREQXN3YmJIZU1OcEVJVkczSk54TzZod0d5azRlM19GbDhoZ1U5UkNtTktoTzhmLXRaQjhFYkEtbzNEZkw0eURSbWRVNy1lV1JZSUNLaGlhX08yQzJTYzJjYkwzbUVZdVVUYXN6eGRxZnNmS1pBZno0Z1o?oc=5", "source": "Rediff MoneyWiz", "published": "2026-10-29 10:59", "score": 0.898, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex jumps 905 points, Nifty gains 238 points as markets stage strong rebound", "link": "https://news.google.com/rss/articles/CBMiygFBVV95cUxNQkR0eEdvajJ2ZVB6SjltUGY0ODdUZ1BYZGxjb3Nfdjd4Y3hYMVZ3MlNqU1BBSmsyQ05fWDVFZ0s1SEd5dmg3ay1OdnNrT0ZINnVfVnU0dzJodXg5ZzBvejZRY2pMb3RBREYwMGNIaTdwXzZsZXJkOEIxUFJxVFRvdjgzVnhfMGdOTVNUVDFmOE4tVDVvM1lZNHlHNlZ6cTNYa000YTVTM19qV1VFek40RVUxVUU4WXhWZjQtV3Y5REdrN1V0VllxMU930gHPAUFVX3lxTE5pbk1LaDNBZDF1WGstdlROOUVfSXBQX2FuaE5FTzVQOEhCNHh1UTdEdmtua3JzLUY2RDRBYkJ5Z0xLRVdRMFkxZEZlcTl3cFZLSXZuM0VBOUw3SDYyazBGcVVyZWFOTVhqRDhteTBnTVc4UzBENXk1YXZwcVY1V19LZ0JVSWV0aGpfbDY0YWwxN1ZOVUlQeVlaTUNhY0NuZVVkTmNvZ2Z3VG1QUk5yd2p5VzdyRTRYUFN0Q2lYejd6cVF1YVBGQko1TzhuOGJxbw?oc=5", "source": "Telegraph India", "published": "2026-10-29 10:56", "score": 0.872, "label": "Positive"}, {"symbol": "MARKET", "title": "Indian markets stage a strong rebound, recouping yesterday\u2019s losses as Sensex surges over 1%", "link": "https://news.google.com/rss/articles/CBMi2wFBVV95cUxPNjhqLWVyaGVfUDI5aXNGT3VhMUNQc2wwQVQtVnA3S29YWVc3ZlpRVmQ4WG9JUHBZVjhpOVpIYi04YVBlMmVuMF9ZOXdHM3pfUGNSS1Fzcm05dnQ4Z1ZPN3l4WUVTMlRZdlVRcUQxUDVVdmE2RXg4aF9wcGpYZmlnQTNOVG5zUmJ2OVh6a0dOTjFKY3h1WC0xOU1qd0dZUndxc2NjRUxGNE13cVd5dUJGTTZhUUh4Vnlrc29vRHZmTW4xQmhwM1FpWVJTQVlNYldZRENhTDZWcW5oYm_SAegBQVVfeXFMTUlaeTNneHFjNHF0a2Y0cWpyeXF4QzNSdDBRWFlKTmptOTN6VVJ5MDR3X0pjajQydzZRQWcwNmhKRmhuUXA3T3U1TUo5WDQwT2l0OVV5ZVZ4UGJlVVNtT1luR0plcTBaU1p6dDdqYm1oSS11NEJ1bWR2eGFlcno3eF94U0xOV2Z3WjFVTk9jMmJOUUhlNkZzUjlYekp0VkVaWW12M2pDUlZKbGJUaWtiZFdYVmxPV0x2ekZoX2ZpbU5RMFhZXzNzbnZlcjVLOGFrMTVjMU92VzNZQTFUNDhzSGRpWlQ5cnMybQ?oc=5", "source": "The New Indian Express", "published": "2026-10-29 10:42", "score": 0.459, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex Today Rallies 905 Points | Nifty Above 22,900 | 5 Reasons Why Indian Stock Markets Are Rising", "link": "https://news.google.com/rss/articles/CBMi7wFBVV95cUxPdmVRUFJReXJwV3FPNWs0U21MRjBvOHE4eGxuMGpOWHpFWlVSSU90WHFITUwtQUM5VjJXQzRGY1RLb3A1UFEzS1l2blhJTUlnaEhxS2ROOVQtNDNNUUl2TGZSajc3ZHh5MG9VdERpbWF4LTRfSFdvS1JxVU1BYmZFdHo0WW5hZkdkam1sbzNDUE51Nmp5NnU2QWlZUFFzYWt3SUR2SW5xTGtFRDdkSklUaHVNSFh5bG9STDd2Q0lRamxfMDlEc2ktX295clRDZVRvN3kwdTBmMVgxV1FKSTh3bW1MLUNVanV3ZXBYQWd1QQ?oc=5", "source": "Equitymaster", "published": "2026-10-29 10:39", "score": 0.691, "label": "Positive"}, {"symbol": "AEROFLEX", "title": "OnEMI Technology rises 5% after Q2FY27 profit doubles to \u20b9125 crore", "link": "https://news.google.com/rss/articles/CBMi3AFBVV95cUxNbGlvX0FHQ1JfUEFBa3FfTlJHN01rRC1VSUpYYlN4TFpGVGZMb1d0akNDNFBWNWVQVFBCOXpqQ0FoUm9uNExvd1UtMkxiRVNGNnc3Z0N4Ymk2a3FkR1N3bTNtYkxxVlkwNHdRbEFfTTQ3NXA4VWlCcE01RTZFZTBTbGVsd0dfRmllMDdnbHh1RXpIY0cwSDFVaXVKX0R3dG5kRzdxbVFtZlgwZ3NfMWdpS3RBa3gzREJwTWdyNEIycXFBbzk1YjQ1VS15SE5zemRNYjBjZE5kTXlNWVM50gHiAUFVX3lxTFBrdXI4MnRhaDVEVV9JaW5ibHQtN0Nnc3M0RHd5OFQ4RVp5VGJ1QjRIZXBnejB1ODZFZndtNU1RM1lqUW1FYVhXVGJsc09pT3JpZjhOaDBoX3VMU19LYXdaS1J2TjNVN1FvczdDNUdTaFVjTDZCVDUwNEp5RVoyeElWRWJFdFdLN0RrRFR3ODlXUm91TVYyR3ZWaGRKWTVraWFacDFOOTZaa0xndEtZM1lsaXVTSG9GUkg5SWwyVjB6eXBvdnh3ZmpzUTJ2ZzdQVUlNbnFhTGVhOU5aczdqU1l0QkE?oc=5", "source": "Business Standard", "published": "2026-10-29 08:32", "score": 0.34, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock Market Today: Why are Sensex, Nifty rising? 3 key factors", "link": "https://news.google.com/rss/articles/CBMiqwFBVV95cUxQd2ZpdWNMN2xVa3NjdUc0WDFvUGNhdDZkVUhOZGQ0dm04T0s5R1Q1cHJyVE9CVDF5RXk0V3UzT1lTSFRCYTJfTXNEd3NyRVRrVU5UNUEtbnpPaE1Ycm45MjVmWERFMnR5X05pQldUUlIwVlA3QjQ1Qmh6ZG1Ua3JQVUxRSDBKbjhIYlc4cjVJNmxsS3ZsQV8xZ1VoOF9Ed2NlR01LWU0zcDhtaWc?oc=5", "source": "Zee Business", "published": "2026-10-29 08:03", "score": 0.402, "label": "Positive"}, {"symbol": "AEROFLEX", "title": "Aeroflex Industries shares rally over 17% on strong Q2 earnings show; material costs jump 120% YoY", "link": "https://news.google.com/rss/articles/CBMi7AFBVV95cUxQQWlWYm1LaHBiMlF4V1d2VEg1UW1NY1FUWHlOWDFRTjBlMVVZNFlNSzBsWjB0MC1TeVRnbS1OZ2tvUjJUWkY1ejlnQXd6Nm44U21MZ0JmOXdsb3hhc19felBvbVJBZW1XMkFNeU1QSU50ZFZPUGs5N0Y5MlR0cVJDNjd3S2wyaF84MG4wQ3g1ajFSOWxTc2pqeGZOWmRoQmE2cHhOeFVodGdGOHBkLXRfNmhkNE1hdFNjcVlkVlJxX19JeGo1V1FJMjFZZUFJOENNMDh0U0pnaW1uQnNoLWJ1SnF4c1FiWENYQldTRg?oc=5", "source": "Upstox", "published": "2026-10-29 07:48", "score": 0.813, "label": "Positive"}, {"symbol": "MARKET", "title": "Three Reasons Why Markets Are Rising: Sensex Jumps Over 800 Points, Nifty Crosses 22,900", "link": "https://news.google.com/rss/articles/CBMiywFBVV95cUxOc1l6QlN6SUJqM0FLV0M4MnlVWU9IYndGOG03emVPN0ZJXzRMTnI0SGg4Ymh4UHhpcnRyWmpDanp5VUIwSzhwSnhrYUtvYnlVYjk1czBqeFkzT2hEMVBZMllqcGxMWlUtQmFpQ3p4SGRMaW5WejN3MWNqRC1GaEpidUFKc3FiVU5TMXlhYlFqR3ZBaXBMYXRFVUNZMUdweUh0ZjNpcGV4N2ZoYVNMcU93LXdoQkVTOXdZLWpaWW5QSi1aMFQzRF84S2RWSdIB0wFBVV95cUxPcElqNUotVFRQdmJJMk9VeW1SaWVBaUU0UjVSeldWTS1RVjZISjF0NmFiVTR2a28zbmFSb1U5NDYzaDdaX3ducV90NkNRaFJHVmZ5dWlzU0dJNUx4WHdaeVN2Nk5TU3V5aDViNDIxYXVSQlhyOGk4b3F0OUhrSEp2V2lKNEJ1eHlCY3V6RFY3bUpQQnlOYXFrSUdyTEJzM1c0UlJIbjl6azFYREU4MHdyTWtwLVM1dVlweG50enNCVDJxQjJLcm1fcGtoV21RbFhVbG9z?oc=5", "source": "NDTV Profit", "published": "2026-10-29 07:09", "score": 0.691, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty Rise as Reliance Industries and IT Stocks Gain; Crude Oil Limits Upside", "link": "https://news.google.com/rss/articles/CBMixAFBVV95cUxNRXNQN3ZYVmxrczhYNV9wVHBZTVJ6bjFaY29LT1kyS08yQmd2MXlweEVaQUduNmhhWDBqTVlhZVpKb3dZdHdkdHlvOVRhY2toLTFRajBQMW1lMS1rZGpUaEp5WDJuaTJ1X2M5UW5LM3k0bFp5SkM0TkVwWTViYS1RMlFNcWk5SkVHbnVLbGtxYVNuNl9OanU4Mk5Ja2tUNTVBUDFSVVZ5cFBsQ3pncVZneVBQS3hTV3N3TEhzVm1hYldRLXc3?oc=5", "source": "India Infoline", "published": "2026-10-29 07:05", "score": 0.494, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex Today | Stock Market Live: Sensex jumps 600 pts, Nifty at 22,850; Adani Ports surges 4%, FMCG", "link": "https://news.google.com/rss/articles/CBMixwFBVV95cUxPcmJpVmFjbm1zTFhWOGJoLUdodXU4UHYwU1RQZ1VIeTBlbF92UlFaNDNMTkpwUDJ4N3JpQTBrSnFNQTk2dE1xN3l6RjVDbHlJbEtLaEhoZlBPZkdTRXEyanhNeW9OcjdXejVRRzY0RFdqUk9rNmR5dVV0NFZpYzZYRTZMX0o4TEhVckRYTDlZZnAzYWdvR1B1RDc3TjNuX3ZMUG1wYWJOMHZna3REemFaSVNKRTdVT1NCWHAzV1FyRmhPUXFmZjE4?oc=5", "source": "IndiaIPO", "published": "2026-10-29 07:00", "score": 0.836, "label": "Positive"}, {"symbol": "SBC", "title": "20 Best Stocks Under 50 Rs In India October 2026 For High Returns", "link": "https://news.google.com/rss/articles/CBMidEFVX3lxTE92U3Fjd2lHOGFGOGZCWE1YTDJpVmo0TktIVk5LUkx5NkE2R3B5M0Y5VjBmZWRYS25aNjB3SlhWMVFVUVNrRVZQX3YzM2FiOHg4b0FhN3kwY1dkejdFWWtFd0dNNlEtRVh4TjNLQnVzRFJWa1ZO?oc=5", "source": "Samco", "published": "2026-10-29 06:51", "score": 0.718, "label": "Positive"}, {"symbol": "AEROFLEX", "title": "NSE: Growth levers, easing regulatory pressure underpin Jefferies' buy call", "link": "https://news.google.com/rss/articles/CBMi1gFBVV95cUxOWDh2RDkydGlLckd3VlBaTWo1NzZfQ1UwRUZzaDlleFQwQTR3MmdmQTlxWkIwTnpFblRKSnVLaHpxSUNVcnpkTmVxZFhuTWdQc1pKTEJJUGZqYnBOWjNVcVNzT2VTa1NLY3VmYXhpQU55Qkd5eTJjMmFWZ2JXM1dmTk1LeEZPQndQdjZadnRmS2pkbV81V3htOXVwUXFXcnVDNkM2VU9PNzR3VzhLUUpyWmw1dUtmWlVPN09BYzlJSEIzZ0RGc2hEemJNcUlPa1hnZFRMaG9B0gHbAUFVX3lxTE53SVEzdlA1N2syc1RkZHBqMW9qcng5UmpVZ1lMczg5VkI3VmFTTzFZckxIVzhScTZZUDRGc1Q3UnlwYkUzcmQ5ZmlaSGJ3NmJBanZxUExPSzdLVlJ2UUJtYUhZNGVOZ0x3c0cxcFhkcVBuOVRjSnJkTS1feGRqN2ZQMU1MaGtJUy15dlRwdnhmT0lSalh2YVN0WDFXWkhIMlJQZVh4RUFja0pDNzVxRHV0eWhTeXFWMTBBcGhTbnZUMG55aEpST2dhZFlocWUxdGl2RVJjMHVEYzJHUQ?oc=5", "source": "Business Standard", "published": "2026-10-29 06:44", "score": 0.542, "label": "Positive"}, {"symbol": "AEROFLEX", "title": "Aeroflex Industries (NSE:AEROFLEX): Did It Publish Q2 FY27 Financial Results?", "link": "https://news.google.com/rss/articles/CBMivAFBVV95cUxOUDdIXzZMbXllYVcydHVDazlNYnJkSm05eGt5eFBtTzEzWDBsOWpiUG1IdjFPaHVwQjNRZm11Zl93S211VmhlaWUxaDNMTmVhaGV3RkhkRnFFYU9rb0pCcWlFRDJHVmtLNXhmVGV0R0ZXbUNLajlVZlZsZGhMZkZqWjA5NEFlbVplSjF0cGwxTE1ob2FzQjFkem9nNkRhdEtzX2tqOUY2SXU2dEhaWVViTDB0QjVwWWw5UmRBdg?oc=5", "source": "Kalkine India", "published": "2026-10-29 06:42", "score": 0.0, "label": "Neutral"}, {"symbol": "AEROFLEX", "title": "Aeroflex zooms 18% on huge volume, over 31 mn shares change hands", "link": "https://news.google.com/rss/articles/CBMiygFBVV95cUxPM0hjTzhyVzdyUnJfQnc5eFZFNlRQbVREa2s0S1VnRFc0UlUtVzRrT1NCa3hHaC0wVXM3RjVRNE5wczd1Tk9idzk2OTY2MGQwUDJCNHFlVDQ1el9RWGl4Zm9sd1pJOU00T2t1RU1ZMzRHeXZ3YzNEWFlFV1RmTUFsakMxY1ZINVFONGxJb091cFhtbjV5QVJfSDVjODZHeWhxT0piOW9EaE9SZlVIcXNMS1JRcFNLbkxxOURKUUxKRmo1N0hPek1TNGNn0gHPAUFVX3lxTE50REw5VnZCd1NnOE1DMUVBeXJuQnpKOWlsNkZnMVNhTmlkZjY0OTY3bEhMaDBnNmdNRkNHdDVEdzhua0NCRW9sdGhoVnE2LUpuYVpJY2Ywbk1vTnlBY3REVHJoT2hIOU1yWTVrdVlDZ0pLZnVTNldwcDZ6dUNYRW5yblpqS3o5NWpDVlByeW5xS3o4ME02NTBZb1Y5VzdTZEloOXR1T3VzaTZxU2cwYVlGMGJIcEhsdVNrUmREYXdDQjRkOUJRV0hPTnMydVF5cw?oc=5", "source": "Business Standard", "published": "2026-10-29 06:38", "score": 0.318, "label": "Positive"}, {"symbol": "MARKET", "title": "Why is market rallying today? Sensex jumps 900 points, Nifty above 22,900. 6 key factors behind Rs 5 lakh", "link": "https://news.google.com/rss/articles/CBMikwJBVV95cUxPdk9rN2FKLVE5VTg4S2phUUhUUjlCTjhVTjEtZVJqbmhiUkx6aVlfc2o2ZzNOVDVOVEltQm14TlRFYU5tTVZja0pnRC0xbC13aEZzeVYtUGRCTGEwVDA3ZEI4SzZybkpmNW9QNFBJTmkzZ2FEN25CQk5yT3h5ZXZHdUlLUGo3blE1TlAyQVJBTllJdl8tQkF6TGlEYkJ6YURwd05EMFlWUXNIT1NZRnE4WmZQTXBKX1h2LXJHT0dSZ1V0S1RKbFNDZkZXQTNmY2xObEoyTGpaSmNPaG9zR19zLUlld3pBR0dYajN4NW45Ui14TlV2dGNwX2FSXzNHNlh4Vy1CZmpaUkJpQ244ODJUY1d5MNIBmAJBVV95cUxPYWJWLV9VVHRFQjZwWFhwRnFQRlBJTjRGSzA2R0ZWUnhsMUlDSjBMMlZpaTVNZVA5Z0h0Z0dmdzZsVHpvRkJlalNpMTBUeWxJWXV4VWJ6Y0pyTVE5WHlfczZ1RkdEaWlzcDlKWjdoS3d6aWF5S2hGeThzTkd0dHdLTDQxMkVQZ25feFhxUFlub3NueHJJVHQ0TEttTzRhOWpKSWkwcWZWbmJhTW16RUFWa2V4bmc5SjE0eHlVVVVvbDRlMWtXV3d6MG43UmlBMnkxTlJCWDJQUGY0YUpSRGFmd01EenBnZ0VQREE5ZGliZTZiaDBnNEhlcUFSN0IzV3Izdlk5NGdqb2VkSnVUNDlZQ3ZROTA5QUc4?oc=5", "source": "The Economic Times", "published": "2026-10-29 05:31", "score": 0.691, "label": "Positive"}, {"symbol": "AEROFLEX", "title": "Aeroflex Industries Share Price Surges 14% After Q2: Profit Jumps 157%, Why the Depreciation Change Matters", "link": "https://news.google.com/rss/articles/CBMi3AFBVV95cUxNanpjQUFtMlRJTE9VYkRiZHVsdDd4bzhuRTd4MlpDd2RvRzZYTDN0UzdQaDJwcEQwaWc4cktjUzRPVUFBN2RRY2czNlhDRVJ5WnlDMHdyTmpUb2J1ekgtZ3RwcHVJYnptZVV2dWJxX0xuRWU1UkVVVjBmOU5Pd2FBMWl2ZkV6TFlodUt1MUNwb2dRNG9aaTRrenRrU3g3ZnE2TXFWU2NHUjYxUVJVOWpYRG5RdUNRMUdvSC16ZGtQb25uZnVNd1BPZHBpOE80MFNMYy04SS1TaGVSNWtl?oc=5", "source": "Univest", "published": "2026-10-29 05:29", "score": 0.827, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock Markets Today: Sensex, Nifty rise in early trade on buying in RIL FII inflows", "link": "https://news.google.com/rss/articles/CBMiwAFBVV95cUxPbTVraU16TkYwWTUwVXpUbzRPV2FHUzNLQk5KVk4zS2RWdzhZLXdTTFVnaV9EcnZwR0ozcHQ2VzFYTDZTeUJ3MzFKM3ZNbEhPM2c4UmZySndFcHFKeG1oQnhwZ3Rpb0lJQk5obzhrWHNreTUwbGUwY3IydU5EMGNPTHppNy1XM1ZiWUFJY2ZKSkRGZjdzN2ZUaHMwbVdtbXo4WnhBVVA5NW1BYnVFMVF1eWhDZnBVYTRpZ1NaOGdNQjLSAcMBQVVfeXFMUE14LWs0aDE1M29hdE1ZemNOTkdVbXNoS1ZKQzc4N29zdkx1MGtYY29TZXRWSWdxdzAyX1ZtMHYyeVhZRG1hbFZlWGduaXhJRWgyUnl6QUljNUZMUmU2X0xLUWZpTnpNMFZuRW1zU3FjeF82eDVTZDRpYzJuTzZhMHlQTW5YNC1HX1BBXzRyWkxwVkNCYXpQeldNR1puMDdIaWtKeURJdXNWTHVENWxPRnBuVEkwdDI5ZDB1OTBnTEstUDNF?oc=5", "source": "Rediff", "published": "2026-10-29 05:18", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty rise in early trade on Reliance buying, foreign inflows", "link": "https://news.google.com/rss/articles/CBMiyAFBVV95cUxNbm9FWDJhbHFCMEpNTC1uZ1dtTWhHd09pYzd6N0s5aTJfclVMU3hmTmVoQVQ4UUxiWXQ2THJ6SkxJSDFIVGRfT3VHZFktS0d1M09BQzIxc1Y3OHE4Vjg5TjYwYjJ6UWpSRk9heE0xdWtSTThObUczdk51dEJmMUlZeXI5eExPQnF6OHp5Z3lna2RhVG9LemNROEkyVFBYUGVwZS04MWxzZkZqbjlpRGd2ekFXZzJ3VHB1YkpOeTBpQ3dabmtjOUFXdtIBzwFBVV95cUxNUm83blpBb3pITXIyTnhpekdUM19lZkFHR3pwOVlxaGRZbHhZeVJ0akN1MW4zSk9EdjgzRl9sUnZUMy1aWkVDQTJJaVJYeVI5SHdnYUVwM3VseEdjNkU2aDU5MlZrdkw3alBCMFlROTRBWVlGMnBHeGFhZXhxSFFRdzU3MjZzSS13djBVcXNpSDVvSlNtSVNkT0JPTmg3SkZ4amFZMFhYTG5uVjN0ZlNmSy02VnUzWlBEaWhZUFlhQmJYakZJQVUxZFJMWnRDZDg?oc=5", "source": "The Hindu", "published": "2026-10-29 05:17", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty Open Higher as Fed Holds Rates; Oil Dips Slightly", "link": "https://news.google.com/rss/articles/CBMi2AFBVV95cUxOWmtQMEZ5NFEwOHMtVlFJWGFKY005a2RTMWF4NlNNcXFQN1RYMmNHeDVVbmx2YlA0Z0xSUGs3aWZlUUJqVmpDMjhOU1M4enFVbFhTOTZEWmZVUFFUZ2JHSzNmRU5GaDhlQjRNUEpuTUd3aFI4MjJYa0tXamJUU3RXQmlJYXFRc2ZVU2UwSkIyNXF4SU5HRjhlZ1UwUktObGJjU29FRlBTSDJva29XUlVudGd5NldOcmxaTU14OFhsTi05Q2V5NEtFQXY5T0MzQnF2Smo5SWdTV1o?oc=5", "source": "HDFC Sky", "published": "2026-10-29 04:44", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex Today Trades Higher | Nifty Above 22,700 | Jio Platforms Up 4%", "link": "https://news.google.com/rss/articles/CBMixAFBVV95cUxPdHRLMXRySU0yU0lBdUJDU1RzcEpvM01WZjNEOXlaTlJGd2FnZk1fNUxTY2p0Q2lrNUpNOFN6UkNpc2xKNVBTYVJmRkJXaEJyX0Z0eUoxOG9kZmlic1hQaE84eWR4TU9JNDhVa243amFRMC11bjRzN3pwZHpiV2N6VlVMTEJqR2gtYmk5WExRek40TWtvOGtvcHRhTU14MGhaYWtsZHBianlEajd0dnFGdElaR0FIbmQyTkxMSHhjZG1nUTBL?oc=5", "source": "Equitymaster", "published": "2026-10-29 04:35", "score": 0.402, "label": "Positive"}, {"symbol": "AEROFLEX", "title": "Why are Aeroflex Industries shares rallying over 12% today? Here's what's driving the stock", "link": "https://news.google.com/rss/articles/CBMi0gFBVV95cUxQY2xISHBTaDU1UWd6TWtwbHpNS3NmbFNCcHZYWU1VUWdjNVAyM2phUmZUVTJkZWowcjZ6VzhreGN0dFBWQkIxaTFyX19aeC0xTFgzSF90eldySGttWEdkQjRRLU02eEdZVk1wd0RsT2xhX2pBaDhIdWc2d3pKMl9XbDBTb1Q1LW1OWl9UYThkRThlYno2TjBhakJXSlZYemhHSFRVdUNBU1lLc0h5OFBRdFZRMXBPZTNWeGpyNUJRTEc3Vm9tVTRhR0dlOTBuQ2ZoWmc?oc=5", "source": "Business Upturn", "published": "2026-10-29 04:11", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Stock Market Highlights: Sensex Jumps 905 Points, Nifty 50 Ends Above 22,900; Adani Stocks, Kotak Bank Lead Rally", "link": "https://news.google.com/rss/articles/CBMi5gFBVV95cUxNd2cxcjN4THQ4TFZtR2FweWRJR1BWYmpUcDJTZlRBVWZEeGZYR3R5RFNsYmFzM1ppNlN0Ykw4ZDdZR3l1Y05qZWdjZGpHOEt0QWZHcWFEQmVEc2RkMzl2cFZGbzV6eWFsZU42Nm1YUWZ1QTM4QVZIWmttM056VDhidk1sNmQ0Z3FDU3V1T3c3THFrTGloTjVUU2FHN3pKRUlfXzk1NkhzWTBmTWxWdGk2OVRwTWlLNmpLb1ZDamdaYVFwNHBtdzJObklHbXVEYzhCZHowY0o0OGs4WC1OTDl4WnVtUS1ld9IB7gFBVV95cUxObXhwRThRVnFsTlU0c3E5ejlpZEV1TTJ1QzBWd1JraWdFVWdaMjgwV2p6UUZGSGx6U0Rrajd6cjRlQUdocWczWDUzcGhpSE9YQ2g0RlN2eGg4M01aUHM2TzdPMm1Id1BqVS1pTnQ5eEl5MEZIaGQ2YVBRYlZ2ZU9hdVVkeGJ3NVVVQUpuRlVKQy1MdDl5SHdQUzFhM1A1eFdOcWVKN0k0cmlJOHN2NlNoamZaNlZIWF9GQ1JMWHRFM2drU3FTVERXX2ZYYlFUOGo3dmpVN3N3YUFNV1pTbzJwQUJkUnRLSFV3SXBFZkFn?oc=5", "source": "NDTV Profit", "published": "2026-10-29 03:51", "score": 0.827, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty trade higher after US Fed holds rates; crude oil remains a concern", "link": "https://news.google.com/rss/articles/CBMiwgFBVV95cUxNQXViREYtTGFhN2E1dTNudm5xR0VHZU1kakd2WHZiNDZXV3VvWFRhVXVvUlAxU3FEVTlmeHdWbjc3VFRvVmNvczJwTkVPbldUejYza0FYcFBDVTFrWHVtS2xLYXhPNjNkLWRmbE5wMDNTbWY2Mm92UGNhZDhaNUdZSF9GODkyMjhselJ0eDVQbGpscENobHRpWkxBU1F3R2cwWVR4cDNDVkd4dWZ1dS1nRkhEQTA4WlBnZGZERndyM1M2UdIBxwFBVV95cUxQV2VVVC1qZXc5RGl2TGRPd0Y5YTFKQV9GWFVLV3o1WHpDVldxaDdWVEljWGxsTVViS2R6Q1BXNTNJYXVMX1g5NDZ5cUFiOUNjMnlUZ1NHYWlqUUhRUWl3S29FR3haNFl5OGZnakRVbmVNWjdnclA1anlWbDZ2aGFXZ29KQnJncXcyWGZjd3pCYVBmZjJDbDJ5UXFxanBlcm1kNXRBRlo0UmlQaVBxWkF6eEV5T3ZjamRZY0dpc2dHS04xWjI0NFhv?oc=5", "source": "India Today", "published": "2026-10-29 03:50", "score": -0.25, "label": "Negative"}, {"symbol": "MARKET", "title": "Share Market Today LIVE, 29th Oct: GIFT Nifty signals gains; Fed holds rates, Brent at $114", "link": "https://news.google.com/rss/articles/CBMivwFBVV95cUxQczk0c1RrQXRIanlFM3NjMVdkZFlqMU5vbWNmR19LSkU5ZE9hcVhFTmt4U2hVTzdRbHhxOTFpSFVTWTdiMFVvYWdFUVBQYUdpN1Y4ZlpxbEdhbm1PWUVHejdYZ1BoQmQ3QzAwcjBzbURCVHZOelNoTUxoYm1nRmlqYV9oMjVZX2taYkV5SGxlY2NVWElLb3NYUDlJM180eGJJQmNZREZUdWRtVmRVazVhTjJONGNWeTBXem1udi1pTQ?oc=5", "source": "IndiaIPO", "published": "2026-10-29 02:36", "score": 0.837, "label": "Positive"}, {"symbol": "MARKET", "title": "US Fed Holds Rates, But Another Hike Looms: What It Means For Indian Stock Market", "link": "https://news.google.com/rss/articles/CBMiiwJBVV95cUxOSmRrRU52T09kVW12NGFacmo3dF9mT3pGeVBaYmsySExkdjhKUnkxdDNTYUMyMWZCVnJOUnRGU1lGck9LYm54UTNFSWpaNnJjSVdnNnJLWEdxTW5JMU5SRnl1YkRMRGVRdWhFbVRHdU1SMDRCd2FKclJZcVVqWnJmcWxWZ0xqaHJCaTFEOXdyUVYzbVRyNDA0YWZMMDF1QWtuaVBQSGtmTXhqekJ0dGJTTTgtMnAzZzEzd0tLWFkzNG5ZSzhCaEw1ZlFsMHpyTEZ1aDBBWHJPQVNxcnlHVS1ycm4yOVVpeUR1QTRyemZvN2pIN29zUVVKa0dYV1h4Zkd3aDRHQURTMU1tMnfSAZMCQVVfeXFMTUJoVG5GdV95TEhndUJvUk50T0ZMOERWbU5FbmtGX2RibnRxczhISW1BbnRCVUpRSjlLLW1BOXlndmJvSC10cmlmY052bFNhVFFHREZYcW5lVnBYbEpicEZ3bXZpMENvc2ZyNGdHd19qbkRKM1RtT2U0ZGlzVnAzT3daS0Jsdl9qU0lWTFJpY1V5S3daeGNaT3J1eFRNTnVzcy1mR0FHc1BLR2EwMmR5d05HWnNva0hQdGV4dl9Dby04eUtRMzlPVmo2X3FpVUJXVVc2T1lsS2lfTUVWTVk4U1U1Qm1rYnZfbDd3d3dWbHY1akRQd1NHNWRQSDVWVjdGTUdTUlZJTXZtYzJkSnFtdXd2aGM?oc=5", "source": "NDTV Profit", "published": "2026-10-29 01:50", "score": -0.226, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock Market Today: Gift Nifty, US Fed Policy To Oil Prices; Five Key Factors For Sensex, Nifty 50 On October 29", "link": "https://news.google.com/rss/articles/CBMi9gFBVV95cUxQTkdjeEhGQ0k3SHlKU0xzYmpBYVV2MWlyVl9laFRPY2N3WXRFWFEtdDQ3ZUU2YWdhaGpab1FKRXZMTlVHYmRHODQtZEUyVk5aVVc2c0hnV2FsYndnQ0FsaGMtTnhzcWhTMGZNeHBNbWxITEN3Y1ZjSTZMZ1Q1UjZjX1E5elRJdXZFd1dPeEx0ZzBfai1qQjA4TDZyRUZHY3V2Uk9mMW9qYWtrXzg4ZVEzU0IxSUlkTlZzM2VVcUpyU2lDN1lRSThQZFExVTNBVVdHOTUzem5qTXBreHJYV0g4c1ktRG0wYVpLSGJDcnA1ODZNbWtRa0HSAf4BQVVfeXFMT1NWT0FQYUNvd1FuaW1kcGpueVB0TmQ0THlZckR5aUlqaVViM0xYY2NTb0szRzVpa1hPRUk4MVo2WmNzc0gtTFF6Y2paZUs3VzZRRW5YZHJaanNDenJObUpxSW1BVHhkNWhBNV9teHVUTm5ERkx0V0tRQnVYNW1GUGY0VFp2RnFUc1BaRHlyeVpYYUMtbkpmanpoVk9aQ21wMzQwbnhqT2FiM1o2ZF9xemRBbzZiYWJwOWFZcTNtVHRMUDZvYkZKbk1EVXFRQ1ZSLWJYMXVJMUtzVVVyRDB5Q0ViNV9wTFdxdnFxWlFmN1RMZ2FDbHJlSFB3UVNDNEE?oc=5", "source": "NDTV Profit", "published": "2026-10-29 01:39", "score": 0.807, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock market outlook today, 29 Oct: Sensex, Nifty prediction - DJIA, S&amp;P, NASDAQ, GIFT Nifty, Kospi, Nikkei, Taiwan cues", "link": "https://news.google.com/rss/articles/CBMihAJBVV95cUxPbGZqMHp2VC02aEFPMWpFUDdkcGlUbGVqSHFVUTdtem9scXhMSTdwRHlQNWxyeGFjd19oVUJBLWtEWXA4bGVSVFlHY3BMTzdhc2RlekgyWmpWVFBYdThfNGJqT05SREFmb2NVT3hsZ0IxSWlVSXVWXzhyeUVQYWlWQWV5OUlmdDA1dldGM1JQdjBSZEtackdibmVLVEFwdWo3M0lha3hvdTNaNEZYTzhXQ01ic3lPMlFjSWFIRHJDeGlTTVR5dUc5S0RvaW85aG82T2xwdnFoSy1yTDRWNnloQ2UxaUpWbW9xYTFHNGw4dDJZMWoxVEUtZER0NlFQa2p2NHZQddIBigJBVV95cUxOYWFiZ291M3RVdE1Oc3JKM05Nd0d0LTM3dWFHS2laLXF6M1ltczBYWlh0SUFtejJZVU9lZlM1R0FWcldBZGRvT2hyWjlBZkl0QV8wUTFqN2J3THNzUGtYekI3MU5oRUVTbklKMXp4Q3NZQUJUaE4zaUJvVXFCRDZiXzN2NTZUWlRQdkRpNWFFdDdpTi0wSTR6ejhNMXBVQWNoMFI0MzVCckFaeklBMUZINEZ6czM0YjdpRjBId1lfVXFqYWszN0tvRy1leWhDZEJZSDBQa2lzdUtIZjNqVHpFcTBJZFZRbzJTMVZkS3BKVUVERWdhWUhlQkdUWGlKOHhuWXpqRDFTbnFHUQ?oc=5", "source": "Livemint", "published": "2026-10-29 01:15", "score": 0.842, "label": "Positive"}, {"symbol": "AEROFLEX", "title": "Stocks to Watch Today: Dr Reddys Labs, Fortis Healthcare, Titagarh Rail, Hero MotoCorp, RR Kabel, Meesho,...", "link": "https://news.google.com/rss/articles/CBMivwJBVV95cUxOckZvTEdLSXpNR2ZfZFZRSlBSb251aFdLSERNTF9tTEVuOWt2a3JoVG9GWEZZa1B5VTVCZDc3Sm40VWlpZGJ0TWQzcWJNbmJjenNTcVpBUW83Mm1ySWpaYUVabmpaUHhGTmxWMjNqWWdmcHJtWWJvS3haYzEzY1J5MHg1YmVlV2FiTkZRTGNyQ1Yxb05WUFNiaDJNVjRjRHBjZHR6SmYyakpkNXFRWm1rcnpxaDlUVktBTWUtaTVoNjRjejJJUUVDeEl0ak5qWjBBb291eERuUHp2dkNNTXJCczFSaE9ycUpic0hZY2llYTFSdmNUMS1pQ3ZwRDczNkZ2UU9xMFNTLV9XMVF5Y1dCcTRfeE1aR2FqMW85ekJCMGhUWTY5ejhEd0NLT0tDTTdKR3pOVklydkxjX0pSb0R30gHEAkFVX3lxTE4zbTVMdTBDbDhuSFZpOUNZQWlQc000SVprR1hFRHIzajZFVkhEUGFRRjhXaDVwai15X2VfQUxVYnVnRW00QmxzZktoRms4UjB5N3Q0U2ZSNElMWktubjhxcVdBY0tlSldIMkI5czlWZU1QNkF5dlRINHBOa2VKakp0RnFMbUhiMzFNSHEtOHN6QnZxUEM3aHhHSF94cC1kMEtFck5QM3A4RzBydk83dHFETWxkOWFhYzltM0RPTkdMMTl2NXp0RUtsTFJrRjU4dlNWcjFTXzBYTEdQSFB3STBXY2YyR2tGNnFTTlBTRGhJODdpbDdPRVJBUlFzN0FxWnpQN05vVzVWSDN4R2ZzWlJ0bFN5dlloOVh5QWlWZWJHTGtWRmtXOG85djNCdlhNM3V4bTNSSl91QlZoOFVKSzBENVVEaw?oc=5", "source": "Moneycontrol.com", "published": "2026-10-29 01:01", "score": 0.557, "label": "Positive"}, {"symbol": "MARKET", "title": "How can US Fed FOMC meeting outcome impact Indian stock market? Sensex, Nifty to rise? Experts decode", "link": "https://news.google.com/rss/articles/CBMi_AFBVV95cUxOZFZvM3NMeWFaZWdDOXJWX3Y3dnA3RjJmMUlZNjZUU3I4RlRwemFzWjNLc2VGSXIxOThvYXJmekVZMkJDNjkxbkV0SVNRWjI2ZGdsOFctY2Z3TExhbFFKUXlfUHZXUG5RNmVtVktMLUtLVjN1WmdmM2RvQUs5b0gwVlBhbkEwdlFkN1duNURLcGJ2Ni1fSVpCdXpORXlFR1JudmYyZHM4U3RsRFpuMUxtakh2MjFMLUJKMkRoSmZmU3lSRmxhWHpNLUlDS2E2c2VGbU5fV0d1dW5jc2tpb1VQWjQzYV9sRmh4Ykk5Vk5rLWR4UkZZZFdJNW1yNzDSAYICQVVfeXFMTXhyQlhLeEtxLW9oR0lQcHoxNTBaaTdqaDgyMWVYVXhJZXlteDZGUEcwUjlZd05rUXdSRC1yMmFZWkl6ZEZZRmFiZ0dBSFBMcTVzU3ZORG82VzZ6VGVseW0yZGZxR1M4V1VLTjI0aDJfU29EZ0NqT1VsaktXNTVoeXdPNlNxYlNpSWZpOXpTQzB4c1lrb2Y3T1F1MVp2T08xaW4zNTVobVpQTmlfdlRITThka2hhc1U5WTF5cXgtXzBZdXlYbGVPT0t5OTd1MXZnTUtMWUxVRUFwbWlPWmxTeFRKV0VvNkh6U3pEUVdBZ04wSzJaN0dEWUFsWnMteWpuZzB3?oc=5", "source": "Livemint", "published": "2026-10-28 18:46", "score": 0.47, "label": "Positive"}, {"symbol": "RATNAVEER", "title": "Ratnaveer Precision Engineering Q2 FY27 Earnings Call on 3 Nov", "link": "https://news.google.com/rss/articles/CBMi1gFBVV95cUxOT0FlR3g5MTluX3phZ0tWLW1iVHAzbUh0dGFBRjcyLTBFQTl5bXkweTNIYlAtYjFSYlhBUFJYQ05VOVUzUFRLaDhwcmg0b2xZSE1JMV9rNlpuMFFDYTljQnpjdE5rMDJ2YWxGaDJZMFpCWFd5RDBuYjFvbE8xS085dmc0aktudXE5MDc5UlhCUVlQSVBtRnFwbUtwNG1lNkFVM2tWYzNLeDdHTGlhUjBXNEVMZ011Q0RJVkVoM24tWTNHWERXbHZ5U1hhOTRDQ0RmSlBFWDdn?oc=5", "source": "Kalkine India", "published": "2026-10-28 13:42", "score": 0.0, "label": "Neutral"}, {"symbol": "AETHER", "title": "SRF Share Price Today - SRF on NSE/BSE", "link": "https://news.google.com/rss/articles/CBMiS0FVX3lxTE92aVdVcHo2Sk5FU3FpVjJraHRrdzkzcHk3cWNySWN5NTF4T3dqOTRLMXNoOU1XVnRaNzZpY0FYTHpPcXZreE1VTWZFSQ?oc=5", "source": "scanx.trade", "published": "2026-10-28 12:26", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Indian markets end lower as IT weakness and crude oil concerns weigh on sentiment", "link": "https://news.google.com/rss/articles/CBMi0AFBVV95cUxQOWZoUXlONnJ6X2V1bFJOclpWWVlXcGVzWmtNYzdlbHJoZThoMEJ3RnZoUlJsOTkzal9jZWtyY3hPTnU4R3dwZ0JpdDcwT0RvNXlhZ2M5TUJ1QzljYktmNmpYbkxfREVHVklXbkpFc2dfb3cyRTdYX1VvYnFRbkczSEZuY0cweG0yRVdsVUluVHRBbE1IZGZjMXAxU1FBRUhPaXZvNkhmdHFKLU0tVTlvc3JMSldjTGRsY1JSTzVtMk1vNTRzR2NZbjZObG5jUG8z0gHeAUFVX3lxTE5zYWI2anl3OExsVTF0RFVuM0FnbzdYQXNQaDNoME8tQ1c4ejE2NWFpVG5aa1BaeXpIc2drSUFIcjB4NkFzUkpydmFxODJnaEp2VnNsMEthLTN3TS1PaXM5b05LQUxIWkdLdVVQMXBmcF9LUTlkUThjVzFoMG1URjhHemxxX090TDBSS3lqOXNWT0lGVmdxQy0welU4RDZySjV6TGhrcXFDSVBJNW1xTmg4RUlCY05EcnY0cTBpVU5vYURybm1hM2l5V0ZZWm00cTNZdEZtQkUzaUVNdXJKUQ?oc=5", "source": "The New Indian Express", "published": "2026-10-28 12:18", "score": -0.807, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex, Nifty Slip as Crude Near $115; IT, O&amp;G Drag Markets", "link": "https://news.google.com/rss/articles/CBMiywFBVV95cUxPWW9WemFsdTYxd0YtRXFGNGktZFJxM2lCV0ozWnFvRElEdWExdDdDSmRGVU5Gb3RBanh0Qld6OUNyVnJjR2JGSnFEMUttV3Bjazc0eWM3V0FEcm5feE5aV0t2Z2FlT0NiMUkyX1c5UlAtZmxRQkNwX1IzMmRib2NWaWs2V1ZsSUVsRUR4S29FdmV1dkdzaGJaRWdtelhacGRjcmFITlU5RndRMWxUcy1wTkxReDNCci1TeDhvenZhZXhsUG4tVjhFQTF0dw?oc=5", "source": "HDFC Sky", "published": "2026-10-28 12:04", "score": -0.649, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex ends in red on selling in IT stocks, rising crude oil prices", "link": "https://news.google.com/rss/articles/CBMingFBVV95cUxPWHdjeTlxY29wcTBTRVJKZlg0eklLVDZXX005c3AxOG1ueDdXV0NmcWJHNVFIaXBlX2FUaVI3SUhqaUY2RG9rc2JqWmppVnhPQzlPdjY5ODFFajZ2X0xLMnNwYWNIZXlXX205aTBRTm40WnJncDNOeFRPdWU4ZzhjNlVQSUNoWkxaSEZNU0E0aXAzZzlNalhkRWc1M1NXUQ?oc=5", "source": "DD India", "published": "2026-10-28 11:30", "score": -0.572, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex Today Ends 353 Points Lower | Nifty Below 22,700 | AWL Agri Business Down 6%", "link": "https://news.google.com/rss/articles/CBMi1wFBVV95cUxQMzRmeU5idFdCSUtXRDhnSndONWszVVlrLWVlbUxpSERVY3pFLVdZSjdBZmoxY2o2bGdnQU1rNDhXcGk0WTlUeHRoT0syaG4tdzJ6d0E1TTZUWlVJX2g3YzcweXNYZnZzNmR1TkdQazRvQk1Md2VDd1hnT3VKQnZHSnZQWlprVUY0N0dxUXVFck5ETXRZN2w0TjRqSEYwMkNPSjZWa29MaGpyOHNMRFBBLUI1Y2Qzc2NYU1RvaE9FQVROTzFwNEdJWkx5NXlTSDU2X2tLQWJaaw?oc=5", "source": "Equitymaster", "published": "2026-10-28 10:43", "score": 0.226, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex falls 353 points, Nifty below 22,700 as IT and oil stocks drag", "link": "https://news.google.com/rss/articles/CBMizAFBVV95cUxNZTliNHpyYmJJOEJwOHk5MWkyOHFFTnlnN2EzUXdBR2pHVl9ZZHlZM0pTLTZGb0lhSXdaOGhfakNheE9OLW93WHd2S2o5TEJRdHBDR2lSdkxJeTR6TGVzSk5uZy1zWVBCVWl1R2NDdmZiT0RpN295T3BDWGxNcy1GcDFTUWpSZXBQbVVOc0luTm1Za2dUYkNCYVRtLXVNeHdLTUhzWXhrbUxKTmJWbDI3QkN2UjljV1l4bUdoUjRiX1VUTHpKUHZvbmtXR03SAdIBQVVfeXFMUHFvV2hZS2dRVGRqRGtEMWVxQVhaalp6cVBGbVVUZzZTNWIz</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BQVVfeXFMTUlaeTNneHFjNHF0a2Y0cWpyeXF4QzNSdDBRWFlKTmptOTN6VVJ5MDR3X0pjajQydzZRQWcwNmhKRmhuUXA3T3U1TUo5WDQwT2l0OVV5ZVZ4UGJlVVNtT1luR0plcTBaU1p6dDdqYm1oSS11NEJ1bWR2eGFlcno3eF94U0xOV2Z3WjFVTk9jMmJOUUhlNkZzUjlYekp0VkVaWW12M2pDUlZKbGJUaWtiZFdYVmxPV0x2ekZoX2ZpbU5RMFhZXzNzbnZlcjVLOGFrMTVjMU92VzNZQTFUNDhzSGRpWlQ5cnMybQ?oc=5", "source": "The New Indian Express", "published": "2026-10-29 10:42", "score": 0.459, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex Today Rallies 905 Points | Nifty Above 22,900 | 5 Reasons Why Indian Stock Markets Are Rising", "link": "https://news.google.com/rss/articles/CBMi7wFBVV95cUxPdmVRUFJReXJwV3FPNWs0U21MRjBvOHE4eGxuMGpOWHpFWlVSSU90WHFITUwtQUM5VjJXQzRGY1RLb3A1UFEzS1l2blhJTUlnaEhxS2ROOVQtNDNNUUl2TGZSajc3ZHh5MG9VdERpbWF4LTRfSFdvS1JxVU1BYmZFdHo0WW5hZkdkam1sbzNDUE51Nmp5NnU2QWlZUFFzYWt3SUR2SW5xTGtFRDdkSklUaHVNSFh5bG9STDd2Q0lRamxfMDlEc2ktX295clRDZVRvN3kwdTBmMVgxV1FKSTh3bW1MLUNVanV3ZXBYQWd1QQ?oc=5", "source": "Equitymaster", "published": "2026-10-29 10:39", "score": 0.691, "label": "Positive"}, {"symbol": "MARKET", "title": "Taking Stock: Markets rebound sharply; Nifty above 22,900, Sensex jumps 905 pts as IT, FMCG, banking...", "link": "https://news.google.com/rss/articles/CBMigwJBVV95cUxOXzFMWXRnalBiNzZsclZWenNqSHowWVV6S2FERmkzNVNwLXBmNzF1c2d6ckVTbkktVlRjUks2VEJFdm5jLU1NXy04MUNaLVE3X0NzU3ZIc2hJOTUxekM2a1llTTZBd3BiNFFFRndOZ0NEZzg0dzcyam96LUpsUnB0dndBa3VndXFvajl1R2JrSl83TWdxVzJITkwwY2UyQjdib2stWUVwSF9FMmc5eG9vZGRtNFdwejNZUmVTeEdsb0lyVVlXOFVRYmZlLTFkLTVyTThFekVvcHgyZXFYOWZCNDdhdzJpVi1YVUFWMnNlMUM5UFV3SzlGMHZFbWVFZF9CQzNR0gGIAkFVX3lxTE1xMWNrVTUzbjlORGN3R2hOcU1qYjFIeW9UMGR3a0FSQUFLTFpnUzBWb0w0UHVxU0tVenQ5V1ZEMTNIb1Z6bGhSenNLblBleUpQckp0SXBuTFpIX1FSNWZhelZxNWtZRVZrMVJ6MTcxbkZ3b3B4MThKdHZXY1M0bGVrcENTd0RrUkMzQWlPemQza0N4bENUZWtOaWl4U0g1Y0JZc0lWRHJJVkpXYmxYal9TRnkxU3FxYnFIdS1WTmlWdzZjWWlVNGJuVjJtOTgxY2x1RURxVXUwTWQ5d1VFXzF1VEhJMlg2NWZkVEl0d1pab3JmMDNxRjFXSlRFSkQwUmVEbGpvQ3d6VA?oc=5", "source": "Moneycontrol.com", "published": "2026-10-29 10:11", "score": 0.691, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex jumps over 900 points, Nifty inches above 22,950; Reliance, Jio, Adani stocks lead gains", "link": "https://news.google.com/rss/articles/CBMixgFBVV95cUxPQVZrakE3dkhQQVJoLWlTOFk3NUkzSkVhaUJQSkNIR0RVTkpyU1k0ekpCc21oSXhSc2J4MS1ZbHNBSWQtbVhuNGw4WGw0S1RHaTZsU2dqUDQ4ZzVzUHJFSVRpWFdRRzg4ZTFIOVV5VmxfVmY0cXBjV09JWlRLYXhBbEMtSEhQcGlGQzZvdFMzWEllQ0RGTXVlYXZVMml5cnVGbVVIdXNudHNTVlN3ZnVoMlljTXN0TVJ1N2VQa01xUHVRNkZCVlHSAdMBQVVfeXFMTk4xOG9rOGlGVEZVWjhhUEx4X1llNENQeEZHUy13eC1XWjlvY21zZGRWNTdmZTJHTFU1STlpUXZHTFJVOWt2R3FsbTk0cmM1MDFYV2tzdDUyUUVZUTZJVDdqeWNfbFZwZTI0V1RqT3lGT1RkaDFlUFhDd3NTNzdKaUtZVU5OZHpEWC1GU3hxckNJWWI3c3ZDWmM2b2g1cVpaWTBsRTJQVUE2NXlZQzh2QVRQdlZ1RmJKcG9SM3FhZ0hiVGxPbFYwT2tCczd6YVpUTUlqWQ?oc=5", "source": "Fortune India", "published": "2026-10-29 08:33", "score": 0.807, "label": "Positive"}, {"symbol": "AEROFLEX", "title": "OnEMI Technology rises 5% after Q2FY27 profit doubles to \u20b9125 crore", "link": "https://news.google.com/rss/articles/CBMi3AFBVV95cUxNbGlvX0FHQ1JfUEFBa3FfTlJHN01rRC1VSUpYYlN4TFpGVGZMb1d0akNDNFBWNWVQVFBCOXpqQ0FoUm9uNExvd1UtMkxiRVNGNnc3Z0N4Ymk2a3FkR1N3bTNtYkxxVlkwNHdRbEFfTTQ3NXA4VWlCcE01RTZFZTBTbGVsd0dfRmllMDdnbHh1RXpIY0cwSDFVaXVKX0R3dG5kRzdxbVFtZlgwZ3NfMWdpS3RBa3gzREJwTWdyNEIycXFBbzk1YjQ1VS15SE5zemRNYjBjZE5kTXlNWVM50gHiAUFVX3lxTFBrdXI4MnRhaDVEVV9JaW5ibHQtN0Nnc3M0RHd5OFQ4RVp5VGJ1QjRIZXBnejB1ODZFZndtNU1RM1lqUW1FYVhXVGJsc09pT3JpZjhOaDBoX3VMU19LYXdaS1J2TjNVN1FvczdDNUdTaFVjTDZCVDUwNEp5RVoyeElWRWJFdFdLN0RrRFR3ODlXUm91TVYyR3ZWaGRKWTVraWFacDFOOTZaa0xndEtZM1lsaXVTSG9GUkg5SWwyVjB6eXBvdnh3ZmpzUTJ2ZzdQVUlNbnFhTGVhOU5aczdqU1l0QkE?oc=5", "source": "Business Standard", "published": "2026-10-29 08:32", "score": 0.34, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock Market Today: Why are Sensex, Nifty rising? 3 key factors", "link": "https://news.google.com/rss/articles/CBMiqwFBVV95cUxQd2ZpdWNMN2xVa3NjdUc0WDFvUGNhdDZkVUhOZGQ0dm04T0s5R1Q1cHJyVE9CVDF5RXk0V3UzT1lTSFRCYTJfTXNEd3NyRVRrVU5UNUEtbnpPaE1Ycm45MjVmWERFMnR5X05pQldUUlIwVlA3QjQ1Qmh6ZG1Ua3JQVUxRSDBKbjhIYlc4cjVJNmxsS3ZsQV8xZ1VoOF9Ed2NlR01LWU0zcDhtaWc?oc=5", "source": "Zee Business", "published": "2026-10-29 08:03", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "SENSEX jumps over 500 pts, NIFTY above 22,800 in noon deals; Power Grid, Hyundai Motor, Jupiter Wagon among buzzing stocks", "link": "https://news.google.com/rss/articles/CBMiiAJBVV95cUxPdnJnbmdzc1NmZ0hiWGxTdWRUQWlaNmdGS0l1U2NrbktXbjBfMldGNmREeVlrakdOOTJQUHN5b0JLUmVYbzgxcWZZcGRmZER3OHkwVS05bGE2YTdkaHFjdDEtYVRaTFFaczBuZ2tPRjd2TlI3b0F6OEZFMDlqT0JDd041b0Z5SUlVOG5hYjVWVk5nd3EyZ1d2UWxORlZnSUtPdllmbU1TcDIxWWVsTnI5Mjlrd0RxRE0ydkNNTUVuZHRJZk9pWXNQSDIwUnlKQnhnNkxRbFhsRHM2TXZNcHk5U1h5UkpwaHZNZFlwWUg1SDhkcWJtR0JnNTkwSFFpRENHcko3VFduRHY?oc=5", "source": "Upstox", "published": "2026-10-29 07:59", "score": 0.753, "label": "Positive"}, {"symbol": "AEROFLEX", "title": "Aeroflex Industries shares rally over 17% on strong Q2 earnings show; material costs jump 120% YoY", "link": "https://news.google.com/rss/articles/CBMi7AFBVV95cUxQQWlWYm1LaHBiMlF4V1d2VEg1UW1NY1FUWHlOWDFRTjBlMVVZNFlNSzBsWjB0MC1TeVRnbS1OZ2tvUjJUWkY1ejlnQXd6Nm44U21MZ0JmOXdsb3hhc19felBvbVJBZW1XMkFNeU1QSU50ZFZPUGs5N0Y5MlR0cVJDNjd3S2wyaF84MG4wQ3g1ajFSOWxTc2pqeGZOWmRoQmE2cHhOeFVodGdGOHBkLXRfNmhkNE1hdFNjcVlkVlJxX19JeGo1V1FJMjFZZUFJOENNMDh0U0pnaW1uQnNoLWJ1SnF4c1FiWENYQldTRg?oc=5", "source": "Upstox", "published": "2026-10-29 07:48", "score": 0.813, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty Rise as Reliance Industries and IT Stocks Gain; Crude Oil Limits Upside", "link": "https://news.google.com/rss/articles/CBMixAFBVV95cUxNRXNQN3ZYVmxrczhYNV9wVHBZTVJ6bjFaY29LT1kyS08yQmd2MXlweEVaQUduNmhhWDBqTVlhZVpKb3dZdHdkdHlvOVRhY2toLTFRajBQMW1lMS1rZGpUaEp5WDJuaTJ1X2M5UW5LM3k0bFp5SkM0TkVwWTViYS1RMlFNcWk5SkVHbnVLbGtxYVNuNl9OanU4Mk5Ja2tUNTVBUDFSVVZ5cFBsQ3pncVZneVBQS3hTV3N3TEhzVm1hYldRLXc3?oc=5", "source": "India Infoline", "published": "2026-10-29 07:05", "score": 0.494, "label": "Positive"}, {"symbol": "SBC", "title": "20 Best Stocks Under 50 Rs In India October 2026 For High Returns", "link": "https://news.google.com/rss/articles/CBMidEFVX3lxTE92U3Fjd2lHOGFGOGZCWE1YTDJpVmo0TktIVk5LUkx5NkE2R3B5M0Y5VjBmZWRYS25aNjB3SlhWMVFVUVNrRVZQX3YzM2FiOHg4b0FhN3kwY1dkejdFWWtFd0dNNlEtRVh4TjNLQnVzRFJWa1ZO?oc=5", "source": "Samco", "published": "2026-10-29 06:51", "score": 0.718, "label": "Positive"}, {"symbol": "AEROFLEX", "title": "NSE: Growth levers, easing regulatory pressure underpin Jefferies' buy call", "link": "https://news.google.com/rss/articles/CBMi1gFBVV95cUxOWDh2RDkydGlLckd3VlBaTWo1NzZfQ1UwRUZzaDlleFQwQTR3MmdmQTlxWkIwTnpFblRKSnVLaHpxSUNVcnpkTmVxZFhuTWdQc1pKTEJJUGZqYnBOWjNVcVNzT2VTa1NLY3VmYXhpQU55Qkd5eTJjMmFWZ2JXM1dmTk1LeEZPQndQdjZadnRmS2pkbV81V3htOXVwUXFXcnVDNkM2VU9PNzR3VzhLUUpyWmw1dUtmWlVPN09BYzlJSEIzZ0RGc2hEemJNcUlPa1hnZFRMaG9B0gHbAUFVX3lxTE53SVEzdlA1N2syc1RkZHBqMW9qcng5UmpVZ1lMczg5VkI3VmFTTzFZckxIVzhScTZZUDRGc1Q3UnlwYkUzcmQ5ZmlaSGJ3NmJBanZxUExPSzdLVlJ2UUJtYUhZNGVOZ0x3c0cxcFhkcVBuOVRjSnJkTS1feGRqN2ZQMU1MaGtJUy15dlRwdnhmT0lSalh2YVN0WDFXWkhIMlJQZVh4RUFja0pDNzVxRHV0eWhTeXFWMTBBcGhTbnZUMG55aEpST2dhZFlocWUxdGl2RVJjMHVEYzJHUQ?oc=5", "source": "Business Standard", "published": "2026-10-29 06:44", "score": 0.542, "label": "Positive"}, {"symbol": "AEROFLEX", "title": "Aeroflex Industries (NSE:AEROFLEX): Did It Publish Q2 FY27 Financial Results?", "link": "https://news.google.com/rss/articles/CBMivAFBVV95cUxOUDdIXzZMbXllYVcydHVDazlNYnJkSm05eGt5eFBtTzEzWDBsOWpiUG1IdjFPaHVwQjNRZm11Zl93S211VmhlaWUxaDNMTmVhaGV3RkhkRnFFYU9rb0pCcWlFRDJHVmtLNXhmVGV0R0ZXbUNLajlVZlZsZGhMZkZqWjA5NEFlbVplSjF0cGwxTE1ob2FzQjFkem9nNkRhdEtzX2tqOUY2SXU2dEhaWVViTDB0QjVwWWw5UmRBdg?oc=5", "source": "Kalkine India", "published": "2026-10-29 06:42", "score": 0.0, "label": "Neutral"}, {"symbol": "AEROFLEX", "title": "Aeroflex zooms 18% on huge volume, over 31 mn shares change hands", "link": "https://news.google.com/rss/articles/CBMiygFBVV95cUxPM0hjTzhyVzdyUnJfQnc5eFZFNlRQbVREa2s0S1VnRFc0UlUtVzRrT1NCa3hHaC0wVXM3RjVRNE5wczd1Tk9idzk2OTY2MGQwUDJCNHFlVDQ1el9RWGl4Zm9sd1pJOU00T2t1RU1ZMzRHeXZ3YzNEWFlFV1RmTUFsakMxY1ZINVFONGxJb091cFhtbjV5QVJfSDVjODZHeWhxT0piOW9EaE9SZlVIcXNMS1JRcFNLbkxxOURKUUxKRmo1N0hPek1TNGNn0gHPAUFVX3lxTE50REw5VnZCd1NnOE1DMUVBeXJuQnpKOWlsNkZnMVNhTmlkZjY0OTY3bEhMaDBnNmdNRkNHdDVEdzhua0NCRW9sdGhoVnE2LUpuYVpJY2Ywbk1vTnlBY3REVHJoT2hIOU1yWTVrdVlDZ0pLZnVTNldwcDZ6dUNYRW5yblpqS3o5NWpDVlByeW5xS3o4ME02NTBZb1Y5VzdTZEloOXR1T3VzaTZxU2cwYVlGMGJIcEhsdVNrUmREYXdDQjRkOUJRV0hPTnMydVF5cw?oc=5", "source": "Business Standard", "published": "2026-10-29 06:38", "score": 0.318, "label": "Positive"}, {"symbol": "AEROFLEX", "title": "Aeroflex Industries Share Price Surges 14% After Q2: Profit Jumps 157%, Why the Depreciation Change Matters", "link": "https://news.google.com/rss/articles/CBMi3AFBVV95cUxNanpjQUFtMlRJTE9VYkRiZHVsdDd4bzhuRTd4MlpDd2RvRzZYTDN0UzdQaDJwcEQwaWc4cktjUzRPVUFBN2RRY2czNlhDRVJ5WnlDMHdyTmpUb2J1ekgtZ3RwcHVJYnptZVV2dWJxX0xuRWU1UkVVVjBmOU5Pd2FBMWl2ZkV6TFlodUt1MUNwb2dRNG9aaTRrenRrU3g3ZnE2TXFWU2NHUjYxUVJVOWpYRG5RdUNRMUdvSC16ZGtQb25uZnVNd1BPZHBpOE80MFNMYy04SS1TaGVSNWtl?oc=5", "source": "Univest", "published": "2026-10-29 05:29", "score": 0.827, "label": "Positive"}, {"symbol": "MARKET", "title": "Why Is Share Market Rising Today? Know Key Reasons Behind Sensex, Nifty Rally On October 29", "link": "https://news.google.com/rss/articles/CBMi2wFBVV95cUxOeE9MZkVEWTFFS1VsUjNNTFU5ZlRHVFdZaWpNSnYxd0Z3RVUxVU44d0VYai1fVWVjQUZOb1RaaTNfVHFSSTNvUFdUNzdwbXI3NWVIYk1SaDRkcGJTdjQxWEdvcVZnZTk2c2psZFRQUmhvVHlpM1ZmVHFvMUpRT2VSZHFnaF9BT2VSc1EtNUxNWVNNekg4ZUVqendFR3NwTDJVSENkaDhncHNmdlYtSGRtWXY3bUxCbDZMVG9yNmh3QlNMSVphWG5iOTF0N240Q0JiVGg3Nzh3eXZJeU3SAeABQVVfeXFMT0RuVlF2YUh6LUZlVTVLRUxEbGVrZHJNV2NLRGdEdVktSWx1UjdYSkpfU1doZFlrZnNCYmRrMmhyWmRlVlhOZ1N3YVdHZlBIelhzbFhuVEJOYkFsQ1g0cHhWOF9sWGlCUDVlY0g0Tm50eUxmWDdtTUpGbllCeUl1anJiWmI1UFJtcURLaXhiNWIwUTFwdFVDM1RMVk9CLXMxOUNIYnpMSi1QNEtzRHRnN1VzVHVzdG96VVktOWdNaGR4Yzl6UUVZdDBzeGVxVVd4dmwxV1I5Z2FvVThNQXJhb0I?oc=5", "source": "News18", "published": "2026-10-29 05:25", "score": 0.691, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty rise in early trade on Reliance buying, foreign inflows", "link": "https://news.google.com/rss/articles/CBMiyAFBVV95cUxNbm9FWDJhbHFCMEpNTC1uZ1dtTWhHd09pYzd6N0s5aTJfclVMU3hmTmVoQVQ4UUxiWXQ2THJ6SkxJSDFIVGRfT3VHZFktS0d1M09BQzIxc1Y3OHE4Vjg5TjYwYjJ6UWpSRk9heE0xdWtSTThObUczdk51dEJmMUlZeXI5eExPQnF6OHp5Z3lna2RhVG9LemNROEkyVFBYUGVwZS04MWxzZkZqbjlpRGd2ekFXZzJ3VHB1YkpOeTBpQ3dabmtjOUFXdtIBzwFBVV95cUxNUm83blpBb3pITXIyTnhpekdUM19lZkFHR3pwOVlxaGRZbHhZeVJ0akN1MW4zSk9EdjgzRl9sUnZUMy1aWkVDQTJJaVJYeVI5SHdnYUVwM3VseEdjNkU2aDU5MlZrdkw3alBCMFlROTRBWVlGMnBHeGFhZXhxSFFRdzU3MjZzSS13djBVcXNpSDVvSlNtSVNkT0JPTmg3SkZ4amFZMFhYTG5uVjN0ZlNmSy02VnUzWlBEaWhZUFlhQmJYakZJQVUxZFJMWnRDZDg?oc=5", "source": "The Hindu", "published": "2026-10-29 05:17", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty Rise on Reliance Buying, Foreign Inflows", "link": "https://news.google.com/rss/articles/CBMipwFBVV95cUxPRVNVU1ZRN1V1UUVLcGhjaHU0VFhyOWtyM3liZjJRMktZZ1dyVnk2cVphWFNPUnZLMDlBLW1kLUtid2RoMnpfTUdUZnNid002YVNDWkRqYWFPMHJDVkNzNHlZZGVPOFh6Tm4wRjI1UWtDMFV4cmI3b0l4WHVGRVliMkc2NUVGNHFqOUtKQV84UFgtVTlSa2gwanZxM2k2d0M3RkZQamhoWdIBrAFBVV95cUxOcFR0UC0yTjN5THRxNGk0cXRiaURuZXZhanBvUFNiMW5mOS1TSS1WbTc2TXcweE5IMFd3U01BeTg5R1FKelY0eUhIYVJibUxZNmE5WUtPeWlwQ2ZmUFVEMnNmUUZGT0luS0d5YkNydTcwMFNvOTBHdzctWkl5MzRuNElfU0M4QkVabGtEYlR0U294NFBxNFpRWGs5blc3elZFa3QySy1SdkN4VGNu?oc=5", "source": "Rediff MoneyWiz", "published": "2026-10-29 04:58", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty Open Higher as Fed Holds Rates; Oil Dips Slightly", "link": "https://news.google.com/rss/articles/CBMi2AFBVV95cUxOWmtQMEZ5NFEwOHMtVlFJWGFKY005a2RTMWF4NlNNcXFQN1RYMmNHeDVVbmx2YlA0Z0xSUGs3aWZlUUJqVmpDMjhOU1M4enFVbFhTOTZEWmZVUFFUZ2JHSzNmRU5GaDhlQjRNUEpuTUd3aFI4MjJYa0tXamJUU3RXQmlJYXFRc2ZVU2UwSkIyNXF4SU5HRjhlZ1UwUktObGJjU29FRlBTSDJva29XUlVudGd5NldOcmxaTU14OFhsTi05Q2V5NEtFQXY5T0MzQnF2Smo5SWdTV1o?oc=5", "source": "HDFC Sky", "published": "2026-10-29 04:44", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex Today Trades Higher | Nifty Above 22,700 | Jio Platforms Up 4%", "link": "https://news.google.com/rss/articles/CBMixAFBVV95cUxPdHRLMXRySU0yU0lBdUJDU1RzcEpvM01WZjNEOXlaTlJGd2FnZk1fNUxTY2p0Q2lrNUpNOFN6UkNpc2xKNVBTYVJmRkJXaEJyX0Z0eUoxOG9kZmlic1hQaE84eWR4TU9JNDhVa243amFRMC11bjRzN3pwZHpiV2N6VlVMTEJqR2gtYmk5WExRek40TWtvOGtvcHRhTU14MGhaYWtsZHBianlEajd0dnFGdElaR0FIbmQyTkxMSHhjZG1nUTBL?oc=5", "source": "Equitymaster", "published": "2026-10-29 04:35", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock Market Highlights: Sensex Jumps 905 Points, Nifty 50 Ends Above 22,900; Adani Stocks, Kotak Bank Lead Rally", "link": "https://news.google.com/rss/articles/CBMi5gFBVV95cUxNd2cxcjN4THQ4TFZtR2FweWRJR1BWYmpUcDJTZlRBVWZEeGZYR3R5RFNsYmFzM1ppNlN0Ykw4ZDdZR3l1Y05qZWdjZGpHOEt0QWZHcWFEQmVEc2RkMzl2cFZGbzV6eWFsZU42Nm1YUWZ1QTM4QVZIWmttM056VDhidk1sNmQ0Z3FDU3V1T3c3THFrTGloTjVUU2FHN3pKRUlfXzk1NkhzWTBmTWxWdGk2OVRwTWlLNmpLb1ZDamdaYVFwNHBtdzJObklHbXVEYzhCZHowY0o0OGs4WC1OTDl4WnVtUS1ld9IB7gFBVV95cUxObXhwRThRVnFsTlU0c3E5ejlpZEV1TTJ1QzBWd1JraWdFVWdaMjgwV2p6UUZGSGx6U0Rrajd6cjRlQUdocWczWDUzcGhpSE9YQ2g0RlN2eGg4M01aUHM2TzdPMm1Id1BqVS1pTnQ5eEl5MEZIaGQ2YVBRYlZ2ZU9hdVVkeGJ3NVVVQUpuRlVKQy1MdDl5SHdQUzFhM1A1eFdOcWVKN0k0cmlJOHN2NlNoamZaNlZIWF9GQ1JMWHRFM2drU3FTVERXX2ZYYlFUOGo3dmpVN3N3YUFNV1pTbzJwQUJkUnRLSFV3SXBFZkFn?oc=5", "source": "NDTV Profit", "published": "2026-10-29 03:51", "score": 0.827, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty trade higher after US Fed holds rates; crude oil remains a concern", "link": "https://news.google.com/rss/articles/CBMiwgFBVV95cUxNQXViREYtTGFhN2E1dTNudm5xR0VHZU1kakd2WHZiNDZXV3VvWFRhVXVvUlAxU3FEVTlmeHdWbjc3VFRvVmNvczJwTkVPbldUejYza0FYcFBDVTFrWHVtS2xLYXhPNjNkLWRmbE5wMDNTbWY2Mm92UGNhZDhaNUdZSF9GODkyMjhselJ0eDVQbGpscENobHRpWkxBU1F3R2cwWVR4cDNDVkd4dWZ1dS1nRkhEQTA4WlBnZGZERndyM1M2UdIBxwFBVV95cUxQV2VVVC1qZXc5RGl2TGRPd0Y5YTFKQV9GWFVLV3o1WHpDVldxaDdWVEljWGxsTVViS2R6Q1BXNTNJYXVMX1g5NDZ5cUFiOUNjMnlUZ1NHYWlqUUhRUWl3S29FR3haNFl5OGZnakRVbmVNWjdnclA1anlWbDZ2aGFXZ29KQnJncXcyWGZjd3pCYVBmZjJDbDJ5UXFxanBlcm1kNXRBRlo0UmlQaVBxWkF6eEV5T3ZjamRZY0dpc2dHS04xWjI0NFhv?oc=5", "source": "India Today", "published": "2026-10-29 03:50", "score": -0.25, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock market outlook today, 29 Oct: Sensex, Nifty prediction - DJIA, S&amp;P, NASDAQ, GIFT Nifty, Kospi, Nikkei, Taiwan cues", "link": "https://news.google.com/rss/articles/CBMihAJBVV95cUxPbGZqMHp2VC02aEFPMWpFUDdkcGlUbGVqSHFVUTdtem9scXhMSTdwRHlQNWxyeGFjd19oVUJBLWtEWXA4bGVSVFlHY3BMTzdhc2RlekgyWmpWVFBYdThfNGJqT05SREFmb2NVT3hsZ0IxSWlVSXVWXzhyeUVQYWlWQWV5OUlmdDA1dldGM1JQdjBSZEtackdibmVLVEFwdWo3M0lha3hvdTNaNEZYTzhXQ01ic3lPMlFjSWFIRHJDeGlTTVR5dUc5S0RvaW85aG82T2xwdnFoSy1yTDRWNnloQ2UxaUpWbW9xYTFHNGw4dDJZMWoxVEUtZER0NlFQa2p2NHZQddIBigJBVV95cUxOYWFiZ291M3RVdE1Oc3JKM05Nd0d0LTM3dWFHS2laLXF6M1ltczBYWlh0SUFtejJZVU9lZlM1R0FWcldBZGRvT2hyWjlBZkl0QV8wUTFqN2J3THNzUGtYekI3MU5oRUVTbklKMXp4Q3NZQUJUaE4zaUJvVXFCRDZiXzN2NTZUWlRQdkRpNWFFdDdpTi0wSTR6ejhNMXBVQWNoMFI0MzVCckFaeklBMUZINEZ6czM0YjdpRjBId1lfVXFqYWszN0tvRy1leWhDZEJZSDBQa2lzdUtIZjNqVHpFcTBJZFZRbzJTMVZkS3BKVUVERWdhWUhlQkdUWGlKOHhuWXpqRDFTbnFHUQ?oc=5", "source": "Livemint", "published": "2026-10-29 01:15", "score": 0.842, "label": "Positive"}, {"symbol": "AEROFLEX", "title": "Stocks to Watch Today: Dr Reddys Labs, Fortis Healthcare, Titagarh Rail, Hero MotoCorp, RR Kabel, Meesho,...", "link": "https://news.google.com/rss/articles/CBMivwJBVV95cUxOckZvTEdLSXpNR2ZfZFZRSlBSb251aFdLSERNTF9tTEVuOWt2a3JoVG9GWEZZa1B5VTVCZDc3Sm40VWlpZGJ0TWQzcWJNbmJjenNTcVpBUW83Mm1ySWpaYUVabmpaUHhGTmxWMjNqWWdmcHJtWWJvS3haYzEzY1J5MHg1YmVlV2FiTkZRTGNyQ1Yxb05WUFNiaDJNVjRjRHBjZHR6SmYyakpkNXFRWm1rcnpxaDlUVktBTWUtaTVoNjRjejJJUUVDeEl0ak5qWjBBb291eERuUHp2dkNNTXJCczFSaE9ycUpic0hZY2llYTFSdmNUMS1pQ3ZwRDczNkZ2UU9xMFNTLV9XMVF5Y1dCcTRfeE1aR2FqMW85ekJCMGhUWTY5ejhEd0NLT0tDTTdKR3pOVklydkxjX0pSb0R30gHEAkFVX3lxTE4zbTVMdTBDbDhuSFZpOUNZQWlQc000SVprR1hFRHIzajZFVkhEUGFRRjhXaDVwai15X2VfQUxVYnVnRW00QmxzZktoRms4UjB5N3Q0U2ZSNElMWktubjhxcVdBY0tlSldIMkI5czlWZU1QNkF5dlRINHBOa2VKakp0RnFMbUhiMzFNSHEtOHN6QnZxUEM3aHhHSF94cC1kMEtFck5QM3A4RzBydk83dHFETWxkOWFhYzltM0RPTkdMMTl2NXp0RUtsTFJrRjU4dlNWcjFTXzBYTEdQSFB3STBXY2YyR2tGNnFTTlBTRGhJODdpbDdPRVJBUlFzN0FxWnpQN05vVzVWSDN4R2ZzWlJ0bFN5dlloOVh5QWlWZWJHTGtWRmtXOG85djNCdlhNM3V4bTNSSl91QlZoOFVKSzBENVVEaw?oc=5", "source": "Moneycontrol.com", "published": "2026-10-29 01:01", "score": 0.557, "label": "Positive"}, {"symbol": "MARKET", "title": "How can US Fed FOMC meeting outcome impact Indian stock market? Sensex, Nifty to rise? Experts decode", "link": "https://news.google.com/rss/articles/CBMi_AFBVV95cUxOZFZvM3NMeWFaZWdDOXJWX3Y3dnA3RjJmMUlZNjZUU3I4RlRwemFzWjNLc2VGSXIxOThvYXJmekVZMkJDNjkxbkV0SVNRWjI2ZGdsOFctY2Z3TExhbFFKUXlfUHZXUG5RNmVtVktMLUtLVjN1WmdmM2RvQUs5b0gwVlBhbkEwdlFkN1duNURLcGJ2Ni1fSVpCdXpORXlFR1JudmYyZHM4U3RsRFpuMUxtakh2MjFMLUJKMkRoSmZmU3lSRmxhWHpNLUlDS2E2c2VGbU5fV0d1dW5jc2tpb1VQWjQzYV9sRmh4Ykk5Vk5rLWR4UkZZZFdJNW1yNzDSAYICQVVfeXFMTXhyQlhLeEtxLW9oR0lQcHoxNTBaaTdqaDgyMWVYVXhJZXlteDZGUEcwUjlZd05rUXdSRC1yMmFZWkl6ZEZZRmFiZ0dBSFBMcTVzU3ZORG82VzZ6VGVseW0yZGZxR1M4V1VLTjI0aDJfU29EZ0NqT1VsaktXNTVoeXdPNlNxYlNpSWZpOXpTQzB4c1lrb2Y3T1F1MVp2T08xaW4zNTVobVpQTmlfdlRITThka2hhc1U5WTF5cXgtXzBZdXlYbGVPT0t5OTd1MXZnTUtMWUxVRUFwbWlPWmxTeFRKV0VvNkh6U3pEUVdBZ04wSzJaN0dEWUFsWnMteWpuZzB3?oc=5", "source": "Livemint", "published": "2026-10-28 18:46", "score": 0.47, "label": "Positive"}, {"symbol": "RATNAVEER", "title": "Ratnaveer Precision Engineering Q2 FY27 Earnings Call on 3 Nov", "link": "https://news.google.com/rss/articles/CBMi1gFBVV95cUxOT0FlR3g5MTluX3phZ0tWLW1iVHAzbUh0dGFBRjcyLTBFQTl5bXkweTNIYlAtYjFSYlhBUFJYQ05VOVUzUFRLaDhwcmg0b2xZSE1JMV9rNlpuMFFDYTljQnpjdE5rMDJ2YWxGaDJZMFpCWFd5RDBuYjFvbE8xS085dmc0aktudXE5MDc5UlhCUVlQSVBtRnFwbUtwNG1lNkFVM2tWYzNLeDdHTGlhUjBXNEVMZ011Q0RJVkVoM24tWTNHWERXbHZ5U1hhOTRDQ0RmSlBFWDdn?oc=5", "source": "Kalkine India", "published": "2026-10-28 13:42", "score": 0.0, "label": "Neutral"}, {"symbol": "AEROFLEX", "title": "Aeroflex Industries Q2 FY27 Results and CFO Change Announced", "link": "https://news.google.com/rss/articles/CBMiwgFBVV95cUxNUnE1em5WY3o4a3A5REpCZ2hBWEVjVmh0SHZrdTlNcFpIaWs4cGZvWVBSeXZ5QU5vQkJHX25UMk9CVVQ0VVFfRXNuMnJWcDhrOWczYko2Q2FmYk90LWRadHFfbFRwM1hrQ2lBYmNaX3psWFp1MTg2dGdyTmtCTWt4OF9hQkdmaG1JVU13TFVaNVVrLURGOVVDckl5Z1pMenBsc3Axdmswam1ET0NLMk1MNzVubVFTTkVVR0dsbUhxMU1UZw?oc=5", "source": "Kalkine India", "published": "2026-10-28 12:25", "score": 0.0, "label": "Neutral"}, {"symbol": "SYRMA", "title": "Syrma SGS Technology (NSEI:SYRMA) Stock Forecast &amp; Analyst Predictions", "link": "https://news.google.com/rss/articles/CBMiiAFBVV95cUxOdkctWjFPZDVydlFqbGVBQmtXM184Ny1vUmw1dnFzSGNyTmNRRzd4dWVLTFZEeXNRbjRYdng5eXhaaGE4cDV3RHNBd21HeGJZYVhDbFU5anp4LURYeUFpeVV0bUk3ekF2NEtWN0NTTFRDekFwTUY5MEpoeGlobnNOWWxWMFVPVTdt?oc=5", "source": "Simply Wall St", "published": "2026-10-28 07:00", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Market News: Share Market Today, NIFTY, BSE/NSE LIVE, Sensex Today, Latest Share Market News Live Updates", "link": "https://news.google.com/rss/articles/CBMiRkFVX3lxTFA2eURra0RNN0hZR0ZxYmMxV00ycGZkVS14M1JaTGFnc2lGeVdLS3NUaDQ0Q0pKSkpLbDcwMUhQN1lwcHJNbmc?oc=5", "source": "Livemint", "published": "2026-10-28 07:00", "score": 0.532, "label": "Positive"}, {"symbol": "SYRMA", "title": "NSE adds six stocks to F&amp;O segment from today, October 28: Check full list", "link": "https://news.google.com/rss/articles/CBMiugFBVV95cUxQcXRqZ2VkU1BlRnY3clZsRkEweDlZOXdLYUFpMmM5QUc2eVhULTBmaXZNOTJaM1ltRkMwY1g5NUFSSUJibzdac2JSeV9pLWlzblJuMmdwTVlRSktfNlJ4YkxfYWpVd1VMd3JLel9hcGNrcmZJQUJsYlplNVMtQXNROC1CZTBvOE55eXpUSnhIaXNPeGt5V09rdjVEQlhJaTJDbmJlRTMxeGtONVhJbGNJb3FuSHRaWXFPMlE?oc=5", "source": "Zee Business", "published": "2026-10-28 06:20", "score": 0.0, "label": "Neutral"}, {"symbol": "SYRMA", "title": "Syrma SGS Technology (SYRMA.NS) Jumps 3.67% to \u20b91575.3, Approaches \u20b91654.07 Resistance Zone - Time Weighted Price", "link": "https://news.google.com/rss/articles/CBMiwgFBVV95cUxNeXpfQm9hem5Ed2xQdUZyMjYxaWUwd0pFME01Rmoza0E3VjctMWFyUHlBNEpNVWNaTkdyc1dBelRsbmZaWVRObEx2eXFsS2hxWVpsRGVDeEEtYmtjcG1rVHNzNllEbTVFVks2YklNTFJiUjU1Qld0bUZjVUhxN0NzYmp2dmFOc05wcmFHOFV5aVBhRHdBb2dmcERPZ2RhMEZ2UGpfeVpxZTJJV2hnZlZFOGdJcXJZN3N6X21uVDY4TngwZw?oc=5", "source": "https://www.siam.in/", "published": "2026-10-28 05:30", "score": 0.459, "label": "Positive"}, {"symbol": "MARKET", "title": "Why Is Stock Market Falling Today? 4 Key Reasons Behind Sensex, Nifty Crash", "link": "https://news.google.com/rss/articles/CBMiuAFBVV95cUxObWxhVDV4ZlIydzBlUDdmdzFaMGRMcWw5N3RjWHRSWnZKOU85V1BaM1pOVDJBU0NjcUcycEZ0a1lGdTFjT2JBU3hGRl8xV0tmRmN6Rk9pSmo2MTJXLW1sRTFEZXROZ2NyaWlOc25CajVNNlBBTWN1aTNrWk9rTDU0QlhJaUt4MHV0cDdwSUs4M1M0WEZGYUJxTWtUUDhJeUNRc1Z1NXhlZTRPZHFzZmgwQzlWQWNxeldN0gHAAUFVX3lxTE5jb2ZQVkFqMmdkV1pQR3ZUaFBnRnNEODlSbFdlOWpxNGUxVnlRTlZjX1JraXlkVlZhNjc0ektuZ0VpaVFfbkhwRFI2N3JaSEtKc0pkZ1RQRjFVS3hhQlFVSUJHdE0yODNqS1NJRXc5LU9mM19GMWc4ZjdfbXd5WnRZTWpqTDJ3eGs3NnUxNmdhOWg2S2YxS2FnUUdPOFZoQ1JBdElkQWZJaVBNVXNuRDB2c1dpSEpxaDVwWWdKOFo4LQ?oc=5", "source": "NDTV", "published": "2026-10-28 05:26", "score": -0.402, "label": "Negative"}, {"symbol": "MARKET", "title": "Jio Platforms becomes 12th Reliance Group company to list on NSE, says CEO Ashishkumar Chauhan", "link": "https://news.google.com/rss/articles/CBMi6gFBVV95cUxQVmpfeVpRbWpoMXJWS3BUZUQtMXRSUXgweXpYTEdsTERjUVNUdWNtbWJTZHFzeDBhNTdvUVpDUVA4b19UMXVjYVpNZ09HbVd1VmhqRlRfeTNrYVp4LXR1YXRGaTI0V1pOdnYyVk0wWmlrd01PazZzQzIxQndjcGdDZlBmYUdfQ3BXSEdzMF9sZExrcXRNV1NFRGFfMGo1MVZ3S0JpU1lXbmNadFc2S0RWV3JOSzVxc1Q3MzAzV25jMTc2WDY0SU5jRkthRy1JVGQwQUNDZWRSWXVMVFBKaVRINXdsUnRKdHVHX2fSAe8BQVVfeXFMT054SUVmc0J6eEdQOWs4NzBLcGRoOExnZkEzTWpwMVFYeDBHZjBnYkJkTDF4WTI1d1UwMWFheFgwQWRJTHJCb3A0dGF0b3l5R01USkMwUmtiUktQWE4wWlluU1dhRDBvbVBfTHpUNFhzZ0gzTEN4WmtXOGVzRlo5U0RBb3g3aGRwNzRQdkdqcEhyOXlYYTc1eWJKQ3d0MS1FbkJxT1FmbUc0NXlId1Q3ZmRKYWtORWRmUlQ4eEpTQjhlbkVhQ2lqRWNQdUhwaHo1UHU4UEd0c0p0bU13aEprR2ZqUEFLdE5takk0RU5fWTQ?oc=5", "source": "Moneycontrol.com", "published": "2026-10-28 04:15", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Stock Market Today Highlights , Oct 6: Sensex settles 685 pts higher; Nifty 50 rises 220 pts; IT, Realty, PSU Banks end in red", "link": "https://news.google.com/rss/articles/CBMixwFBVV95cUxPNjdLa1Q4STc5UFU5VzcxNWpmcHBDaXd3U1ktUkJhTUk0ZjlJRHZ6YWtzTkRhNDg0WFlELXdwLUlkMkVCYm1GUHhQNUlwazJHWlZIaVlhZmVBcGdOVHZsNFd2QUg5VXJkNjRKSzlvMnc3dWN0SjVFTnlidVVZMzctRjdEVzF4X3B0TEpUNURhcHFRV2ZMb3VDUGtnNDZhNXdIQWNlTTBHRGZPXzNkLUVXY1ZONFNHYjhqbFQwS0JqMGROVjE2bmZJ0gHOAUFVX3lxTE8wN3RPazNfT2JQaWdsVUpBb01Jd1FBTU9qYkZrNnZ2eENBY1UwSTBwOU1FWEcteXJ3RDNBME40TTRJTGdWOGxRVGl6TC1FTTkzenVWTFczZ2Q4c19jSXcyU3VfdFVwdzVZaktpa0hsRWIyZWtRbkVYcWdtWHpUTWd2MWFlTG4xVWhTY1o3czQ0RmF6NU5xTXNTRUdPZXhTNGVlT1Z6TXZHUHN0aVlmeTVBalhXdVBYdl96OGxaSksyQ19wMks2em5jNDZOdDFn?oc=5", "source": "BusinessLine", "published": "2026-10-28 01:13", "score": 0.402, "label": "Positive"}, {"symbol": "AETHER", "title": "Ather Energy shares: 125% YTD returns! Experts give 'portfolio stock' tag after Q2 results 2026 | Target, stop-loss", "link": "https://news.google.com/rss/articles/CBMi9wFBVV95cUxPYmlLLVpwT1RwQ2tYR1F6WlNVTWJ3N3h6R3MyX2ZvVlhHUjlDZVdHTHhGeVF1dnBQOEdjb21UQUFuclpzTVh6a283ZF9EWWJqb1lreEp1dzZFMEx0eVJLQmlUcXc2elo2SEE2c3ZiVEZLYk1sLVJkZ191cnZOb0QyT1pBSUxfR1o2UkRoMlN5dnlnWklGMC1OTVp0bmlNaFJwdW1JOUhFdkg1TWlIZl9xUUwweTlfUThhaE9oeGstZ1ZnaUZGckh0b2xsSldWb3B1Um9MUWtCUDJzTmQycFVUTExRUFdGSkx1a0hubHVjYmtLZEo1ZGRr?oc=5", "source": "TradingView", "published": "2026-10-27 12:08", "score": 0.457, "label": "Positive"}, {"symbol": "CPPLUS", "title": "Aditya Infotech partners with Ranveer Singh as brand ambassador for CP PLUS", "link": "https://news.google.com/rss/articles/CBMitwFBVV95cUxOYV92ZHBGUmxnOU0ydGQwSjdwUnBLNFBuMHdjbGhLSWpRYzI4ajM2dEFIVW9lQkV5NFZOdzNYeFJtS3pISkZXMVZET1p3aWZXQ1N1cU92OUNMa19wNGEycXF6Ykw5SlJ0eGVreTZZdW9UTktVbTFGeU5HRHpuVWpLOTQ5SWo1bTJKU0tJNUlVVzhqYnBoMEpuVGFWelJ1U09EclhrM19FeVNCbVFOUENnZ2xraFNiZVE?oc=5", "source": "Business Upturn", "published": "2026-10-27 10:46", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex Today | Stock Market Live: Sensex, Nifty trade flat; smallcaps jump 2.5%, IT slides 1.5%", "link": "https://news.google.com/rss/articles/CBMivgFBVV95cUxNeXFmTEJhQTB3U2FSNW5IN0lub2hFVk1aSGlmU1RUUE1ITjFDcmpDTVdFQ1VJOHFzYWpqZXpoNEVUbE9pVjh3ZWE2VEcybVI0VEdLNDV2WF9jbHdIX1llcklPcjFXMDM4QzZ0MXptcGtVTjdLTjlUN0pPeFhjOS1vel9YcERQWWFibVdYdzAwTkdtak9UNV9ObGlfdmVXU2RhZGNvaW9XV2o4VFlvOXFUQmd6OU9PaW5GbEhkdDBn?oc=5", "source": "IndiaIPO", "published": "2026-10-27 07:00", "score": 0.67, "label": "Positive"}, {"symbol": "CPPLUS", "title": "Do Aditya Infotech's (NSE:CPPLUS) Earnings Warrant Your Attention?", "link": "https://news.google.com/rss/articles/CBMi0gFBVV95cUxPWm03Y2s2TzZiU2ZxV1l5QTBwZTlLVXkzOFd2WlYyZ1ZiU2dEWUFneElwRG1HMUNaNTFCX1p2V3otUVhCZU5SOTlyRUNIdjZaTTh4cUVmWDRHMlg3ZDNCX0VQaEtITUpRNVBvbHRFMnJ0NjV4YjhOUHZNUFJhZ1IwRGt3UXJDeE16ck5zb3ZSN0ozNVVMc2xjM05NRGVrUjVfWlVEZGJpWGNicFNnb0NvSDYxMFZyS0FoRkFhZTU2T2lienVEZzV5WWxkeFF4bjFsMHfSAdcBQVVfeXFMTkpxQ2JGc2tYb1NXcGpqQzBib1gxRXpKNUpTcmZ0a3lkcm1oMVpBcTN5M3piTUludmVTZWN2ekRHUnpDTThqRVd5TFloZ0h2UkpScFBiWkJ1ZlhxMUtqaXdNaTU0bGhlZVFPX2wyOG9fRDhZYWRPVWxkUzRTTmZabnFpSnA4b0FnM0VDbTY1R3U0ZmJueThIU180bWtiSTV6NHhzbzd4blZsVDdSaHQwWlo3RTdDSk9iTFdqSkZKbEJhSHhzWFJhR3NkVnVzdUVXbTNUTXM5c00?oc=5", "source": "Simply Wall St", "published": "2026-10-27 02:09", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Indian Stock Market Crash: Sensex Falls 5,035 Pts, Nifty Drops 1,453 Pts From Peak; Can Budget Revive Bulls?", "link": "https://news.google.com/rss/articles/CBMi3gFBVV95cUxNaTRicEdpc2xjWnRrZGlDQmVHYUhyYlk5bE5VeU9FSWtwWEQ2MzFWMGtmeDJ3NFo2R0dEX3cwblVQemxEWFp0U3dwalVQTnFWOGlWb08zbGNVSlYyQzUtM244eWJPeGFXTHZMMm9RdVlHaTJqb0NJeFNiekM0TmxJbnhRSl82YWFUNlpyaWR0Q0NsMEVkb05jQXVOQTI1Vlpmb1FCZzVrcjcybUpJX1NON3dMRUVDbE9jV2FHQXd1OU1FRll5Rm40NVpkYmdlZTVpUFZ1b2dEb1VXU3FKaWc?oc=5", "source": "Goodreturns", "published": "2026-10-26 21:36", "score": -0.318, "label": "Negative"}, {"symbol": "SMLMAH", "title": "SML Mahindra Limited (SMLMAH.NS) Slips 2.83% to \u20b94,706.5 as Stock Tests Lower End of \u20b94,471\u2013\u20b94,942 Range - Hedge Fund Favorites", "link": "https://news.google.com/rss/articles/CBMizwFBVV95cUxNbV9TQktMZzVLS2k1YWJHSlJsamJtNXBFOHJwZHEtX2ZCZ2Y2azU5blNvbVpLQngxeF94SEVkb3phRXVpOUFVb2tBdFJCUkczMENNTU92Ry12WE5idExOVjFVOXZNdndUNEVIdVpFZlpvczFiT3ZtRlVDeE9ibkhleVc0dEJNWFF1ZmJpMTdMa3V2a1ZaNzBGenpNTXRxTEdERXNVb3dQbXBPMWdWMURzeXNkZHVfRnFnTkxvclhiVk1FcVBJQUlDUDNzcFNtTUU?oc=5", "source": "https://www.siam.in/", "published": "2026-10-26 05:47", "score": -0.318, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock market prediction for Monday Oct 26: Sensex, Nifty levels, top stocks to watch - Will bulls dance again?", "link": "https://news.google.com/rss/articles/CBMi1wFBVV95cUxQaHNMNE94WElpelJxRFNZMmFoS1p0a2lrZUFFa2Vla0JFb2psbEVOSW5HY2pCNjZ5VzBfa1lyem8zRktLVVduZ1hlc1E0aW0yQ0Fxb0ZSUFJZLWlMd3hKZjFqY1VaOTRSNGxpN3QzbVNvaFhoX2Zyc2JueHVtRWRyTkhkalBPZ2M1dWdwU2NFWURyTmFLUjFvV3NybkJiTVpQYy1Fd1dLMlRxRHFZWGNobWpUclFZQ184OGk2eFRqUFBaWF9sT1FiUlJ2SjdpWTZCT1ktVzhNdw?oc=5", "source": "IndiaIPO", "published": "2026-10-25 14:34", "score": 0.542, "label": "Positive"}], "errors": []}, "created": "2026-10-30T14:55:17", "last_updated": "2026-10-30T18:08:40", "corp_actions": [], "fundamentals": {"AEROFLEX": {"name": "AEROFLEX INDUSTRIES LTD", "pe": 78.65103, "fwd_pe": 54.181824, "sector": "Industrials", "industry": "Metal Fabrication", "mcap_cr": 7098.2230016, "pb": 14.2838125, "rev_growth": 0.873, "earn_growth": 1.509}, "CPPLUS": {"name": "ADITYA INFOTECH LIMITED", "pe": 93.28194, "fwd_pe": 50.383343, "sector": "Industrials", "industry": "Building Products &amp; Equipment", "mcap_cr": 46739.259392, "pb": 23.922348, "rev_growth": 0.895, "earn_growth": 3.037}, "THANGAMAYL": {"name": "THANGAMAYIL JEWELLERY LTD", "pe": 35.413353, "fwd_pe": 24.44221, "sector": "Consumer Cyclical", "industry": "Luxury Goods", "mcap_cr": 13847.0391808, "pb": 9.778979, "rev_growth": 0.712, "earn_growth": 0.861}, "KIRLOSENG": {"name": "KIRLOSKAR OIL ENG LTD", "pe": 47.92156, "fwd_pe": 31.48291, "sector": "Industrials", "industry": "Specialty Industrial Machinery", "mcap_cr": 26136.82176, "pb": 7.2113123, "rev_growth": 0.134, "earn_growth": -0.199}, "SMLMAH": {"name": "SML MAHINDRA LIMITED", "pe": 46.491833, "fwd_pe": null, "sector": "Consumer Cyclical", "industry": "Auto Manufacturers", "mcap_cr": 6837.129216, "pb": 12.203249, "rev_growth": 0.207, "earn_growth": -0.444}, "AETHER": {"name": "AETHER INDUSTRIES LIMITED", "pe": 91.00225, "fwd_pe": 54.33023, "sector": "Basic Materials", "industry": "Specialty Chemicals", "mcap_cr": 21451.4745344, "pb": 8.731544, "rev_growth": 0.275, "earn_growth": 0.341}, "SBC": {"name": "SBC EXPORTS LIMITED", "pe": 77.82353, "fwd_pe": null, "sector": "Consumer Cyclical", "industry": "Apparel Manufacturing", "mcap_cr": 3149.997056, "pb": 31.276596, "rev_growth": 0.855, "earn_growth": 0.0}, "SYRMA": {"name": "SYRMA SGS TECHNOLOGY LTD", "pe": 84.51898, "fwd_pe": 50.154373, "sector": "Technology", "industry": "Electronic Components", "mcap_cr": 31307.3369088, "pb": 10.862635, "rev_growth": 0.683, "earn_growth": 0.86}, "TDPOWERSYS": {"name": "TD POWER SYSTEMS LTD.", "pe": 81.125, "fwd_pe": 47.99328, "sector": "Industrials", "industry": "Specialty Industrial Machinery", "mcap_cr": 22948.2299392, "pb": 20.810984, "rev_growth": 0.721, "earn_growth": 0.72}, "RATNAVEER": {"name": "RATNAVEER PRECISION ENG L", "pe": 18.569588, "fwd_pe": 22.657234, "sector": "Basic Materials", "industry": "Steel", "mcap_cr": 3023.4468352, "pb": 3.659887, "rev_growth": 0.189, "earn_growth": -0.097}}, "research": {"method": "auto", "generated": "2026-10-30 18:08", "title": "Stock by stock (auto-generated)", "stocks": {"AEROFLEX": {"symbol": "AEROFLEX", "name": "AEROF</t>
+          <t>S19Zbkk2SVR1Z0syU1diTmlQRXNVYzEzUUNRdzdtelp4ZEpTazJTV2JFX2ZhMnNBQkFpQ1p2MFlBZlg4SkxBT0s4Q2R4UXBxTk9KdlpQd1g2ZUh0djZTRTdTQ1RnUXdNQnR0RWZIMG03dWd3Z1JmTEQ0TkNmamdFQTZGbTJCX1ZSUTZKRFZlZS1wRzU5VFZ0VEJiNnYxM25TNjNYY1VScTBBVnJMczdB?oc=5", "source": "India Today", "published": "2026-10-28 10:40", "score": -0.202, "label": "Negative"}, {"symbol": "SYRMA", "title": "Syrma SGS Technology (NSEI:SYRMA) Stock Forecast &amp; Analyst Predictions", "link": "https://news.google.com/rss/articles/CBMiiAFBVV95cUxOdkctWjFPZDVydlFqbGVBQmtXM184Ny1vUmw1dnFzSGNyTmNRRzd4dWVLTFZEeXNRbjRYdng5eXhaaGE4cDV3RHNBd21HeGJZYVhDbFU5anp4LURYeUFpeVV0bUk3ekF2NEtWN0NTTFRDekFwTUY5MEpoeGlobnNOWWxWMFVPVTdt?oc=5", "source": "Simply Wall St", "published": "2026-10-28 07:00", "score": 0.0, "label": "Neutral"}, {"symbol": "SYRMA", "title": "NSE adds six stocks to F&amp;O segment from today, October 28: Check full list", "link": "https://news.google.com/rss/articles/CBMiugFBVV95cUxQcXRqZ2VkU1BlRnY3clZsRkEweDlZOXdLYUFpMmM5QUc2eVhULTBmaXZNOTJaM1ltRkMwY1g5NUFSSUJibzdac2JSeV9pLWlzblJuMmdwTVlRSktfNlJ4YkxfYWpVd1VMd3JLel9hcGNrcmZJQUJsYlplNVMtQXNROC1CZTBvOE55eXpUSnhIaXNPeGt5V09rdjVEQlhJaTJDbmJlRTMxeGtONVhJbGNJb3FuSHRaWXFPMlE?oc=5", "source": "Zee Business", "published": "2026-10-28 06:20", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Stock market crash today: Sensex plunges 995 points, Nifty sheds 1% ahead of Fed decision: Here's what spooked D-Street", "link": "https://news.google.com/rss/articles/CBMikAJBVV95cUxOMFlUOGxPbER6VGFzUWlYX1hkbGdNNlpHb2lIU1VlNTNhQ3Jvdm9TZ2Z6NHdhUzVhV25aNXBpT2hrUmt0SW9SVjJPZUJPOEtlVnJaVWtfUWdMWE9QdkJQV0E1ZVlDSzV4alhSOTZtR05SWEd0TEZfbFdWZnV2VGp0VFcyMmZnQVh6ZlhCbmpDTmY5NXNxZWwxWnZhV0xMUXJxdFNQbHNwWHB2LXc4cnJiVnFXeXJNX2lYc0lQZUd6MHRuOTM1TXlCek4td1JveFNnZU8wYnQxZVFaRWIxWWtOdUNCUTRHLW5hLWNueEUzcGJ5Tzc4NXpseUw3TFViZHJwZ0k2OGFEWGt0RnJ6V0RjaNIBlgJBVV95cUxNQXlWaURfa2owSFdwNGtDa2JvalN2M3RKYmlaYVl2d1M2QVV2TURNemU1dmlOMnVqa29EX0tqYm44OTNDUnc3NVpoSlU5Z2YtYU16T3AzNHlaWGFyMWkwNUJ6SDFHM1o0b3hla25rQkNvZ2t2cGo4c21oM0txVUdzeDhPTFRYOUVUN1BHSEt1ajROcTU4UFpJc3I4WmxIMnVCbGZKeGpYZXFMYnRRSXZqUjNVUHNNaWRaN2U3THZqWEtHYVEtS3FMVnRiRmNNR3p4UkpSekF5ZnJtM2wtUDEtNER2eGhhdl8ta3dBeE1EbS0wMlktSnhjaFhRUHQxalFncHk3WThfeEZrWVNPN1lzbm50dHVTQQ?oc=5", "source": "Livemint", "published": "2026-10-28 05:37", "score": -0.802, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex falls 500 points: 3 reasons why the stock market is down today", "link": "https://news.google.com/rss/articles/CBMi6gFBVV95cUxOQUdsVkg4RjMtMFpldFBOTi1NSFVMZFZaR0dXeXFrT29uRUluZzlOUVJGaEh5aUZ5WmFBY050eUFHdTRDZ3pVOS1yZDVZMjRwa2tvX2h4OW1MejktVHFqZHk1VWxTMU1EV1VjcUhkSnBjS1k4elhQZkpzazNzUEJXLUpjcUsyVklKeEJ3N1oybTNqXzVvU3RhaVBPVE1peS1XR2JSVk8tT1l5YldGNV80S2dDd2l0VE9yXzNIUFVQbGNRSnByN0RZWE9XX25pam54ZFNBa3hqcHJubzJ6SHhGYl9lZFdMaGFpU3fSAe8BQVVfeXFMUEpDRGJmdmlHNkU3Um5xRDBRSWhFZWFIeUVwUWtGOXdZZ19jMzRhajNOdTdfRUhhU3NQTVJzdVQ3YWpNNWdSVC1DcmdaQ19fUzR2UmN4a2Z3NWV0TVVZN21jOWFNbkhwbUtjQnBsZlRQTnYyMDhKei1KNE1XZFFlTHJjM1Fmbl9wLWFHTzFTZXkxUzd4TUhYUnpRSy0tTWVyM1ltTW1pZ1Q0Rkt0eEItNVFiX3VwYnNuWTJNYXlINGl4UUZHeG1YVlZhc05QNG5rQzRmX2xnMTNCWkpKcTQtVFk4bGNqOFZEVXBKalJJUGc?oc=5", "source": "India Today", "published": "2026-10-28 05:36", "score": -0.382, "label": "Negative"}, {"symbol": "SYRMA", "title": "Syrma SGS Technology (SYRMA.NS) Jumps 3.67% to \u20b91575.3, Approaches \u20b91654.07 Resistance Zone - Time Weighted Price", "link": "https://news.google.com/rss/articles/CBMiwgFBVV95cUxNeXpfQm9hem5Ed2xQdUZyMjYxaWUwd0pFME01Rmoza0E3VjctMWFyUHlBNEpNVWNaTkdyc1dBelRsbmZaWVRObEx2eXFsS2hxWVpsRGVDeEEtYmtjcG1rVHNzNllEbTVFVks2YklNTFJiUjU1Qld0bUZjVUhxN0NzYmp2dmFOc05wcmFHOFV5aVBhRHdBb2dmcERPZ2RhMEZ2UGpfeVpxZTJJV2hnZlZFOGdJcXJZN3N6X21uVDY4TngwZw?oc=5", "source": "https://www.siam.in/", "published": "2026-10-28 05:30", "score": 0.459, "label": "Positive"}, {"symbol": "MARKET", "title": "Why Is Stock Market Falling Today? 4 Key Reasons Behind Sensex, Nifty Crash", "link": "https://news.google.com/rss/articles/CBMiuAFBVV95cUxObWxhVDV4ZlIydzBlUDdmdzFaMGRMcWw5N3RjWHRSWnZKOU85V1BaM1pOVDJBU0NjcUcycEZ0a1lGdTFjT2JBU3hGRl8xV0tmRmN6Rk9pSmo2MTJXLW1sRTFEZXROZ2NyaWlOc25CajVNNlBBTWN1aTNrWk9rTDU0QlhJaUt4MHV0cDdwSUs4M1M0WEZGYUJxTWtUUDhJeUNRc1Z1NXhlZTRPZHFzZmgwQzlWQWNxeldN0gHAAUFVX3lxTE5jb2ZQVkFqMmdkV1pQR3ZUaFBnRnNEODlSbFdlOWpxNGUxVnlRTlZjX1JraXlkVlZhNjc0ektuZ0VpaVFfbkhwRFI2N3JaSEtKc0pkZ1RQRjFVS3hhQlFVSUJHdE0yODNqS1NJRXc5LU9mM19GMWc4ZjdfbXd5WnRZTWpqTDJ3eGs3NnUxNmdhOWg2S2YxS2FnUUdPOFZoQ1JBdElkQWZJaVBNVXNuRDB2c1dpSEpxaDVwWWdKOFo4LQ?oc=5", "source": "NDTV", "published": "2026-10-28 05:26", "score": -0.402, "label": "Negative"}, {"symbol": "MARKET", "title": "Market fall explained: Sensex dives 995 points intraday, Nifty at 22,500", "link": "https://news.google.com/rss/articles/CBMi0wFBVV95cUxOajRZeW5FeTk4NGJnOHFzaHlmWjd0WDk4NU9fWTVlLXJqWjhpUjVSaUR0UHZpOW9jN010OWhpQU1TakwyMlhSWlM4dFdYZnlXbnRsUzlQeW5FZnN2MThOLUNacHZCQ2RzNlkzaFZONzZTVXNPNlk2QmVZcnFJOGdRM3hPMDFGd1JiSEViZE1KN3pZRF9MN2NXcWo4amV4R1VMVmxkMmFxSDJXNXhSTDZXWHRaakpIdkIxR2VUVmVqLVdVWGkxN1ZtRnRTUmlQS1E1T1800gHYAUFVX3lxTE5tUW5DWXVQQzNNazEyRy1Jci1SeUNrSkNCOEc4OXBJZVR2NTluNUxidGtDNFZBSEttQkhHNEhOSE51ZE5taEZaa1JyX1NEZlZTRDZHWUtOdm5KdVR5d09wMmdsWDVCMlY1SlZhdGxFd09oWXpmUkc1YmRIdUVTa3duUWpLbkF4R09WdURRSER3WC1BYndqYno3cV9Fd2RJNXB6cjk1eUxTMTFISFhHOGcyRmpuaGNJUHlMU2tINDE5UjRHOTNualZLMFlITjA3Tk03RmV3a1owVA?oc=5", "source": "Business Standard", "published": "2026-10-28 05:26", "score": 0.077, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex Today Tanks 793 Points | Nifty Below 22,550 | Nifty IT Index Down 3.1%", "link": "https://news.google.com/rss/articles/CBMisgJBVV95cUxNNTE5SXk2WlQ0bDBjSGZrYVBzRWtub2dySmF0Ym9rV1hFYTJ4aHdrUU02UFF5dzFQN3o0X2VhMDAxRTFJX1ptLXRsSGZOTTUxbzNIcGRISTN4X1JWSkZRa0RiS1Ytamh3Vmh6Q0huNnh6WnNQbFI2S0pKSWNQYXM0RG0xM3RvUVhIT0VRYjhQMHJrMFNTd1R3N0FHcmNfWnM2RDh5SndjdVVmQTBNdlUtdlplM1FsYnRoeVc3SHhDUE5nMmdLX3Z1Y29VLUpuN1JGS0hvMXh4ZlVKV3BycHNRU0NZMlFLY0ppcUpHNDQwVWtLRzRFRmVEam5CazVycGszeWlJTU1CRkxCY1A4VkUzTXpWWEZoN1FlRGR6MC03ZHdfbUdtdG5wZXJHdzVZUWpodmc?oc=5", "source": "Equitymaster", "published": "2026-10-28 04:56", "score": 0.296, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex falls nearly 700 points as rising crude prices, FPI outflows weigh on markets", "link": "https://news.google.com/rss/articles/CBMitAFBVV95cUxQN25aS1ZxTW1tUkNIMkpGYTRyUDdKWVA5aGF1ZnRDY3dpZkRrbjBjWUtjRjVXbXhLRndScEdobk4yUW1mSi1mN1hzQ2poVDBlYWJvanJDVFFNNEl6c2k0aHVIWFJ5bHMzNG93c1JTQ0YyczFtTlMtR3NKMGhBT2pRVk1xSXNkYjJCMFhaTnB5Rk8tMDNCdzlVcjViZkR6azItdWt3MTE3S2VKcWZTb0RrSkdiUXc?oc=5", "source": "DD India", "published": "2026-10-28 04:46", "score": -0.743, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex sheds 691 points, Nifty falls below 22,600 on rising crude prices, FPI concerns", "link": "https://news.google.com/rss/articles/CBMisAFBVV95cUxNTVhwVWxMZ0EteGF2NHZ5ekpSamxCN24wVklBaFljblVtcWhNY1FLN0tpcjRuWWFIQmlRcEIycmY0eUthaVZLOUVOcjBuU21XR3pXdVphanhwdnp2a2dtY0tQSTllbll6dUpOOG1PcEducmhrSzR6blhxTlNHTnFRT0hETUdZcWhWM0xXTEJuMzE4Y01UYTM2alpOVnBEdW5ZaGUtZV9LQTJEeV9mM3gyaw?oc=5", "source": "ChiniMandi", "published": "2026-10-28 04:35", "score": -0.735, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock Markets Today: Sensex, Nifty Tumble as IT Stocks, Crude Prices Weigh", "link": "https://news.google.com/rss/articles/CBMixwFBVV95cUxPUjYzTTdhbkI4NlczWmJKbWxMblNncjdaQnpoRzVQbTBjdEc2YW9hZk5rclZ6RXVIU2hJOGdpTkttMUE2cTFieVZ2ekg5QVJQbU1vWkg1cHFIMFRzYlVjM043SS02aUozQ2xQenQ3alZMZzJ6U1c5VmJJejk1NS1RdWhBcTNyeHBZaWhadi1UdlpJQ05rUWxBTkJaOEJtejBvNThXSXlnTVdSWWxhSXVVdG1vcGJpQkZFZmNSM1h3T2NuSDg1NEsw0gHKAUFVX3lxTE83QUF3N2RZejc1a2dBQVZQb1pmczFoWUpSeVYxNVhBRjFqRDlYMTdJTEZUdEhuQlpyUTJMUUI1T3JYaVlqQVlaN191YXRpNXRxb0FDNVROdnEyZlk5MWVFM0tvSUlLLVo4X3dJYzhsTjlUTkdWdDdUSncxdm1TQm5FbFgyWUwxSE9BSXRtb2ZtN04tNmJlQ01qWHNHWkF0TkNtZ3FhdkhyejRqVVhzSHBWQ2l1Y1d4cWlOQ3FYdm9IMC1iRWdqSVJGa1E?oc=5", "source": "Rediff", "published": "2026-10-28 04:32", "score": -0.25, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex, Nifty Slide as Crude Near $116 and IT Stocks Tumble", "link": "https://news.google.com/rss/articles/CBMi0AFBVV95cUxOUVVIU2hUd1lTbTJOQWNJeUdXeENUbC02SEJ3M1JPTU1acnU2d2NHWmxucTB3Nk9MNVZjc29BUGprR2VSZzhZN2UyX01KdEdBWDBFQ3h6UVhVQlRtYnJaTE1TX0FGSTFvMGo5SlQ2RnVfNnM0TDJLTV9lVXFRRzhGMUQ4OTN6bXh3M0tPaGdLNmgxUVNFZzlxVjg3Uzg0enFlUE8welpMT1E3Z2NnWUhkcmxhZkNXUFg2R3FnajhTaFlKV3I3bmVqWG8wMHFmSHZq?oc=5", "source": "HDFC Sky", "published": "2026-10-28 04:32", "score": -0.25, "label": "Negative"}, {"symbol": "MARKET", "title": "Why Is Stock Market Falling Today? Sensex Drops Over 800 Points, Nifty Slips Below 22,600; Key Reasons Explained", "link": "https://news.google.com/rss/articles/CBMiigJBVV95cUxPWWg0dDRpcmtjNklEc0lVSG5lZWxUR2JXMF9EaDR5YWozMk1rMjZhU0hOQjhaR0lLMDZFYWNuNUxPV1NmdkdLTGRwMnRMVDVDNFlaSmpONU5qellPa0lVTjRfZ2FxWERCbVptWWc3WFlZazJTUlp0bW53U3QySDBHMW9Ic2g3djNHbS1oWV82NHVmWTQwaDNOU3UtWDFqRmtjSi1jZUgwczZ3dW16SHFYbXhieUZQWlZRV3ZnbVY0bjFyZXdyS1N6eG81QnU2c2l0dFNSdlRCVXFhdTdnSmN5WEdkQ1dGTXZiblVMUVRpX2NCLXA1bWxadmMySVFaZDcwY25EQVRyY3BHd9IBkgJBVV95cUxONzVPaXVRSE1WNE8teUkxaWRiR3JXMklmNk55OUx4YnlTX3lDLXQyaUx3ZXRtekFFcm9XbDlNMmt6NEJYeVpzNlJPRF9DQUVzSS0wbDZSTHE4QjJ4UDhCRTJNLVMxY1hRV3FoZFhpeGVqQkpFWHdqYzVQZHpIb24tckxGWWpMTHVtN0pQbXBfXzczMG1kRFVnN0ctWXdCbmhKNzV6YlV0dnNyQlFrX1hjZzd2bHhfa0tIZ3l3TDhqMnExTFVlcnIzci10cG1YSURiWUpvMEs5S2JNV3hZdmYydmRETGlKMGE3WGVrTC1YLWtGbFVfcG82MmNtZjZ1X0tGZEN2U1pyUkFVQWpPVEJ5d013?oc=5", "source": "NDTV Profit", "published": "2026-10-28 04:25", "score": -0.077, "label": "Neutral"}, {"symbol": "MARKET", "title": "Why did market fall today? Sensex falls 353 points, Nifty closes below 22,700 despite Jio\u2019s solid debut; 4", "link": "https://news.google.com/rss/articles/CBMimgJBVV95cUxPN3hVTktXNUNKT25YaFFQM052YXZtRFJhT2x1cmVuUlZ0SmZqWEM5VHlmcjJrcG03cFRiZHlmZzdKMjRiT1VOLUdBWFc1Y3V1REpYdzd0N2NXTFBMM0hVRExkZ3JjS2NZX3hObU5PTERMZmJ6VGVKSERCeEl2bmp4aFFYcXZINEplX3FCNGwtMzZxamJ2bzAwcTF4ZmVHa19UeUJPS1NfUW5FWHp6cGM5c2tjRGFoT2NMNXJQQmpHWk1VaUNqZkY3S2R1dlZLbVhpQXgzZUJlc05zdHpHQU85Mm13a1ZQMzZtUHc3WDNBS0tReWtVQmFiVHdWemtzLVFuM1JUN05wbm5fYlNpVjNDNEV0WVdMMGFOV1HSAZ8CQVVfeXFMTlgyVjJwSnZEQURZMTMxWFdXdGdJUHdhVXdxaUR3Q2g0RjVBaG1PazdmQmlfNU13NUVNUEQ4UVoyaWcxX015ZGFiUGdyc29LQzRXanMtODBZbGlVQVFTTV9sRmEzdHA4NFdOUENlU1F2WjkyMloyTWxyNzJvMkZRZU5HZ0xxTVpsOHowaVVYT2RqdGNGeHBMb2xkWUpaM0g4Tm5YaW5qcmRQRHpta0FUVlRvVVJhaEJvcHc3Qnl1WWhxMlQyaEFUTzVFZ3d1cDRBUm02VFpvUzNuWXFQQ3RPdTRVTzVOME5TeFZiUHYtcGFUQ2RPTklPbG9iZXVfek1PcHk4bVNsWmdtXzNIWGtuREtWZF9OLXRpSE1Ra0RLU1k?oc=5", "source": "The Economic Times", "published": "2026-10-28 04:06", "score": -0.411, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex, Nifty open in red dragged by fall in IT stocks; Infosys down 5%", "link": "https://news.google.com/rss/articles/CBMi7AFBVV95cUxOZ0VWVnNwckNzWGp4dnIwU1kxY09iakhsLW5TMnBWRmkwQTlKc0JvZF9BZ3VmTFJKb010SGVSM1NMUmhwak5QUVNOQTZ1Vm1uZFA4Z25LSkNGaEVLcjZyRF9JeWwwbHBUa3U4Q0VoYks3b21GT1c4YW9SQ2FEQWM1QWNsSHVYMVIteDc2NHY1SElEVFpFTVRhOTFhVnR3NjhFZHhpWnVHRmpTbnVqaDdabWpsNEVVem5vVlprX09wbTgwZWRCVXEyNFgxTEJobXFzOTJsdU5sZk85NXRtLW4wMEVEUHVGNnFsZ0w3Z9IB8gFBVV95cUxNNXJvUWlJOHllZ0ZpbkZsNzJ2am1zR1J6MnVNOWV6RUZXbG1fSGxjODRvdGlsRnJMTkxVQVM4eXg5eE0tb29oTzNpLWUwTUpYdmJST0E4MVF3Vks2OU9kVU9LZzV1dG8tY2hiclVLTHUxS1FxR2ZxTGNQc2pQNVoxVHJuZnFhandSd0RqWmxacUloUEpaV3NuZDZoR2JiUGhPSjZPaHdMT3ZxX2pYcFRYQ0pjcnhOVUROdjFMNUxRNWpjdl81enNHY1JnN1lRaHFnYzdMcERoWUNOTkJjUVFZRGp2bE1fR0Fhd1R0c3EzY0JsZw?oc=5", "source": "India Today", "published": "2026-10-28 03:49", "score": 0.026, "label": "Neutral"}, {"symbol": "MARKET", "title": "GIFT Nifty crashes over 220 pts, signals weak start for Sensex and Nifty despite global rally; US Fed in...", "link": "https://news.google.com/rss/articles/CBMigwJBVV95cUxQODRoS2dkTW5ybk9WdnFlU216MXdvdFdkWXZ1YVlWbFRvcjYyZDFYZG9KanZueFFXazEzQ1ljRURydm9MbWlMNmM1dmY2dHpucnlXOEIzNXdWRVNBc3JCR2FnZkhZMEMwLXlpVS16UmtvNWlKR3BDRFIxb1pIY0NQN3EzNXRlNGc2Vk5yV3EtX01JOG5lUXFmM3doeS15Ml85WWMtZmtlTkFCRjdmU0licG9DUDIyZjFqMzNUUTBjRG9MQV9FVGhlYjZJV0lYQnE1elJCb1RJZFhCN2VUWEpmeURfYTYtdmM3YlVpckdORG13VHMwXzVvUWh5OURiRkFkZWh30gGIAkFVX3lxTE1yUWV2R29fUFY5TGFZWUZLRTRlX3RTQ3R3cHN5dFpxRUVqVFllUDVZMFlQZkd3cXN5MUlCWlpNMl9ZQXJEdFNuRFBfZ0E4OFBSVGtWdGE1VWo2LUNyYVg0ZEN1Y2xZRnBEQnZ4QTNFOGhjVXNCSWlhdUJfc3IwNjR3N1dDdENxbGFMelRSTEJnM1paN1RRY1dMTDBQUEg3XzhXWVU5aFQxemRXZ3ZvZUhjbWg1Q3ZzWkEzZzJkeG9NZTUzWkRVa0FNVlRQX0lIT1ZZQmZtdkItczRDME9tUnlCUU84cnU5QmNVQy1nRi1LeXI5YTVwVDFxZENUYlkzUnI1YmJKRWRXWg?oc=5", "source": "Moneycontrol.com", "published": "2026-10-28 02:47", "score": 0.606, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock Market Today: Gift Nifty, Jio IPO Listing To Nasdaq, Kospi Rally; Five Factors For Sensex, Nifty 50 On Oct 28", "link": "https://news.google.com/rss/articles/CBMigwJBVV95cUxOV0NNUHlXN193VWhlcWJONTl4M0taMm1wN0ZUcmRoOXZNZ1dhWkdjWjY5a3U3ZXJzNTlHRlM3NjZuY095QVZITERNU091VFVud1FYQmM1aXRVc1BnQ1NKSzlMNDJtMzFwdUpUenRjLThPZWJIRGxvWnRiYkdxSnlwYUIxS0NRWU9ERnJ4N1FhRGIxSUxWRm5USjRGdGtnWjRTOUtTUzJFVUoxNF9vS0ZtNVdSbm9icFZJRWM5UWp1MndBcmotY3FvNHlxeklhOElDaU5ZWUR0VG96MjVKZUpkSC1ZWW94NWU5d2czcW15OU1sXzljN0UxSTFIeUwxLVp4ZXVV0gGLAkFVX3lxTE1CaEZOVXM2WVpwS2RtSGNma1A2M1ExMklaUXR2eFZnU1RDVmZLV1hjTnFUQkJxNmJiamJPdU96a21udE13bm8xZ3g1LWdIRXhaekJITWJPMlJ4b0ZwM2hCSENsRV9QNjFWUTU5X1RDcjV1aXZHdkNBVkg4em1YalJPSV92SGJNUDdJWFNLWnZfSUNXTDhWSDBMX3FtbXd0aGlzVWVPMlpVbnV4VkJYY0U2RHRSU0doa3l2TktzZWRKdFBoMUtjUU9rWHl1UVlBZ1lyc2VCS2hGdkwxcXFFbERVQndQS2JTOHgtMmJuUEhVYlZSUXRTZGN0bW5NMzFmdVIwMlNzUlcyMkpjaw?oc=5", "source": "NDTV Profit", "published": "2026-10-28 01:54", "score": 0.883, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock market outlook for 28 Oct: Sensex, Nifty prediction - Jio Platforms IPO listing, GIFT Nifty, US and Asian markets", "link": "https://news.google.com/rss/articles/CBMikAJBVV95cUxQbGQxcFFLUDN1THJXOVNaMEsydnpFQWJjQVZRWW9jNGJXczJxZDNpdElrOGx3bFluNFFCWVgyM1RQR0RUWFgwTGFCc3FaLTlBcTVGQ2JDRUNCVll4cFJ0V2pxVGw1TkJaTjZqSjE2VGZHZXdqR19talF2N085OGJBYjF3M1lCaWNlZjFLRGtaNUVBVHpIWi1mNXJaTE9iZVREdTkyQ0djMWNGdGNaZkV0WGlqOS1HTUJUcWRpSDZYTkc0VUVya1JBSEVzLUlibDhZUjJfS0JrdVdWTGJTYWJpTXVWeWRNdU8tSXZHQ25ybmtZQzlhR21mNzl5TlBtbzhNRnJmTFcxN2VWLUdJNEp4Q9IBlgJBVV95cUxONVlXWWJCbVhCZDBjM0ZhUDlEcnBWNVJUdTNGNjJXeXV4NlRpY2lwQlNmVFM5dDlwdVVEejdRX2MyZWFvbG1LLUJ1VGc1Zy1KamlfWHk3SHRiMlAtM0VBUjY2MHIwVzZyR3Jyc3ZMNnkxSTlLTUNHQ3hRNHdJRi00UEZ5TDNrS2p4UGVxUFhyX19RLUZSOXd1c2NzSm5LczdpRkY1UnFzRks3cjdBX2NWVXhVSkZoaXNfOGxvMXQwX3p3VVN2M2tVZTZmRDIyZ1FvN0tfTWF4LUt1ZXI2RTZkTGY1Zndpdkw2Y3djeUdNT2pwOU44Q1JXWHM0UkV0bEdTVWpaVTZ3SXA0SzZSTnYtWjBLMUxldw?oc=5", "source": "Livemint", "published": "2026-10-28 01:45", "score": 0.842, "label": "Positive"}, {"symbol": "MARKET", "title": "Indian Stock Market News, Equity Market and Sensex Today in India", "link": "https://news.google.com/rss/articles/CBMihwJBVV95cUxPTmRhZ3Y3Rjc2RHNlaE5fd0VwSWlKR1dYd3VaZXFlcUNnM05XMnpwTlF1c3lNMXZVcGNtTzBvTW1kVVd0UmpPRFQtYjM5WWdXN1VQWnItbDNxQUhqeUhtNEc4eHVfRDlKekdlSjlxVk9aekxDd2o0QzZLU183TkRLQ0MwWXVnZ1NzQjJ1bUc0Vm5IZmJEV0RLZTk2S243d1EyX21iZVVkYVBYNmtNaHR3amlPbm5KYkl1Tkk4aUo2UFY2NC1iSV9FTTVHR25ybHZzZTdGU2pkbjlXRm9nT0QyUE9KVzc3Wk4xV1JFN3h0YUhKdUZreS1rM0UxTUtiTGFqUFc5ZWktVQ?oc=5", "source": "Equitymaster", "published": "2026-10-28 00:44", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Reading the Nifty 50 and Sensex: What the Two Headline Indices Tell You", "link": "https://news.google.com/rss/articles/CBMiqgFBVV95cUxPNnFuYVBDbWNVdXpPblY4eC05ZTlEWk51T3dWSEVPLUJaRzN4SUJLWkRfa3VfbGN4dFJqeVY4WV81V3VPb18tUmlqS20zM1lIZ0dwRmVzMGxPUE1oWmdFdnVtd3gyOC1OYkdsRXVjZGd2R3BVV2YyQVMxalFfd1ZZMDFtNENrWXNtM2hjMGdXbVFPclhXeUE2N2RRU3Jfc1Jrd2pGRXd6WE0tQQ?oc=5", "source": "www.tmgm.com", "published": "2026-10-28 00:40", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Markets end flat ahead of Fed decision; FPIs buy shares worth \u20b94,240 crore", "link": "https://news.google.com/rss/articles/CBMi8gFBVV95cUxOeGdEaVY2NjFmaFl5cU1MSmM2SmRFWEQycFhUMjNlbkRkY3I1SUpfOG10X2oyLW1jd0dCb2wzNkZ6dWZjcGV5ajJJWmMwVnNKRVJwcDJ3SlY5NU5rSEpCUVh3bFE4cDhkeHZFY01GS2pIYlU3ejVPY2VpRVUwS2dkQ1dXZzNVRWtsUkJxSXA4NTVobHFpcHFYU0lGMHdlc2hBSUI5eUQ5RldFUDRzMXZzTHJVVzBnMFBJM0xGc0l4Y1kyaTJCbnZMMnc5ampMbk1QOHF0a3oySjJJNG0ybXNOel9sdjVPZE41RVEtWkpKUU1OZ9IB9wFBVV95cUxNTHFKcFdlVGVRcWtEMWlTWUl3XzFDdGJ0RGJRWXBnLWFBdzQtZ1B4UW9mMWEzbEhoVkxRZXZXMWVoN2VXeUlWS2VfS1Z2WVpWZmhacDlZRjVDSFhUbFl2Qm5GeGRXNmRHaURwNjAydk9aSmJxSTFPclc4UTVydmN2X3dxdmNNVllMZmJReWlqUHFwSEZnckphOTRwUEpCRHFnV0lOM19MMUZKWGZqOUZ3YUlMTEw1OGhIUVlRTTFsSnZTWXUzYmZhVXRGZDRwN0liZHIxcTU4NG50X2NiRXBRdHdaelEzc05oaExtbFpYSnJuSnRrMDRR?oc=5", "source": "Business Standard", "published": "2026-10-27 18:08", "score": 0.477, "label": "Positive"}, {"symbol": "AETHER", "title": "Ather Energy shares: 125% YTD returns! Experts give 'portfolio stock' tag after Q2 results 2026 | Target, stop-loss", "link": "https://news.google.com/rss/articles/CBMi9wFBVV95cUxPYmlLLVpwT1RwQ2tYR1F6WlNVTWJ3N3h6R3MyX2ZvVlhHUjlDZVdHTHhGeVF1dnBQOEdjb21UQUFuclpzTVh6a283ZF9EWWJqb1lreEp1dzZFMEx0eVJLQmlUcXc2elo2SEE2c3ZiVEZLYk1sLVJkZ191cnZOb0QyT1pBSUxfR1o2UkRoMlN5dnlnWklGMC1OTVp0bmlNaFJwdW1JOUhFdkg1TWlIZl9xUUwweTlfUThhaE9oeGstZ1ZnaUZGckh0b2xsSldWb3B1Um9MUWtCUDJzTmQycFVUTExRUFdGSkx1a0hubHVjYmtLZEo1ZGRr?oc=5", "source": "TradingView", "published": "2026-10-27 12:08", "score": 0.457, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock market today: Sensex, Nifty flat as smallcaps rally and IT stocks fall", "link": "https://news.google.com/rss/articles/CBMi0AFBVV95cUxPWGZBRmlDeUJ2YWlaNjVHQXo2RnRkS2R3VlRrdEVNd0t2Ymg0Ri1qQi15dEI2NFdhYkRKSkVBejd6SzJZSS1FejBQcWNaNmY5UC1ZcUVqZ0U4djcxNk9BWHZmeEFQRjNrT2dmZEI5bkUxUlNMbk9HTk9Uam9zRGlDclI4bmNVOFNYMS0xQ2tQUm5SYjdvb2Vmb3NsaDFzcExOeWlRT3p0M05jbnk3VDlqQ0ZKaExWN09RdGp0ZVZUQVc2X0VxYVlKNjVZZDRlbWVv0gHXAUFVX3lxTE5GZHRLX2Y0cVZ4eUM3TUUtZ0dEMTd3Ml9senV2YWFkTmVXX3RndG5vZzRFN2xJNmZidi16ZHhVTllyLTJzcUExcWp5SDJJVXJnRUtpOF92WWNXMkNnN0ljVURlbVhwcENBZmFhYXBGNTRyazhwZ09FMURzd2dRSDI5dXZyTW1PYWlfa0FZV1RTRkRQQ3lfSFVFT3ZGSTZvMnVtS2VQck9yYTFxbmlfX2pOeUtEN0xybDBKeE9CU3A2T1RzVFNVNUM0dk8wanVnZHUwWGEwMTRV?oc=5", "source": "BusinessLine", "published": "2026-10-27 12:05", "score": 0.511, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock Market Highlights: Sensex, Nifty 50 End Flat On F&amp;O Expiry Day; Asian Paints, Coal India, Grasim Top Drags", "link": "https://news.google.com/rss/articles/CBMi0gFBVV95cUxOTkxWdW4yQXdPNm12MEU0dmYwN29LYl9tMjV3Zml3WmhvNXdpU3doc2h2bWEwcEE3cElFRkVIZUJjeTdTdXl3OWxZZ1luUG84LU9vbGRsVWNldnhPNWFWT2RTRUJMNUxaV3ZmWmxXQ2tHelJHMm5UdjFCSFpRNzlVYjcyR19ZZ3ZicVhrZVFITzAtQUZXaFRpZlBaOUpHOXhhelhURW1qUmhhbEJfREFOQ0hnSUJ4V3RHVHlTMHZwV1c0d2dHSm5UV0pseFJCMkJjaVHSAdoBQVVfeXFMTmx6S1hjeHJac2pGQjRHc0ZwMWw3c0R1Z3o0Sm5paS1VMG1ILW5ieWNnN3dXVUhwZFFVSm1YUmdTYURLdDdVUEpTSm1vaFJVSGQ3MEdqb3VOVUdVVHJGNGhSb3JRM2pwWm02aUEtd3oyN1ZUVG1XVC1iam1zTjlLY3VJa1BHeUNYc3V5NXFTOW5aVmRSOGI4WUNQdmxpT1hzcUFjMk5lQWlrd2lyZmZxLVNDMUtHbFVqNjEzR2Z0V3VRREJFcm9uRzl1WHB2cklZeXN1VU5FY29tUXc?oc=5", "source": "NDTV Profit", "published": "2026-10-27 11:36", "score": 0.273, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex, Nifty End Flat as Oil, Fed Jitters Cap Upside", "link": "https://news.google.com/rss/articles/CBMiuAFBVV95cUxQNmV5cmNlY2hydnc0SVZGcWdIVGZxWEhyUWU3QlE1M05YNUpMeWw3R0Q3Z2JWdUo3d2tSZHdjR1RRV1FQVlZOLURJTzBEOVJydkFXREtsUmpkeHFIemJOMW96Z3c1MElNVzlLdzVlcVEzX1N1OEhvTW10NFdOZkJUUm14RzU4Y2ZEOXAwWHZzY0lGbEpsY2FDWFZKZUZlZ0JDamZKRzJYcld5ejdHU0RDS2VnaS1iTmR2?oc=5", "source": "HDFC Sky", "published": "2026-10-27 11:30", "score": 0.67, "label": "Positive"}, {"symbol": "MARKET", "title": "Gift Nifty Signals Flat Start as Fed Decision Looms", "link": "https://news.google.com/rss/articles/CBMiiwFBVV95cUxNZ3FjZTljMEVjbVliUVRyeW16RzNKZkNYaHJtdkRWZFQ5ZUkwdUNwbGpEdGVYSl9HWXoyc1NHazVObXZEVUZBcFlxTnZkZmNnRFpZUk1JcFBhdGQxTTk1YXdneU92ZjFDcTVHWlYxTS02RWpDNnF4bk9IOFVXTk9KU2JFZDl0WE9DNmw4?oc=5", "source": "HDFC Sky", "published": "2026-10-27 11:27", "score": 0.612, "label": "Positive"}, {"symbol": "CPPLUS", "title": "Aditya Infotech partners with Ranveer Singh as brand ambassador for CP PLUS", "link": "https://news.google.com/rss/articles/CBMitwFBVV95cUxOYV92ZHBGUmxnOU0ydGQwSjdwUnBLNFBuMHdjbGhLSWpRYzI4ajM2dEFIVW9lQkV5NFZOdzNYeFJtS3pISkZXMVZET1p3aWZXQ1N1cU92OUNMa19wNGEycXF6Ykw5SlJ0eGVreTZZdW9UTktVbTFGeU5HRHpuVWpLOTQ5SWo1bTJKU0tJNUlVVzhqYnBoMEpuVGFWelJ1U09EclhrM19FeVNCbVFOUENnZ2xraFNiZVE?oc=5", "source": "Business Upturn", "published": "2026-10-27 10:46", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex Today Ends Flat | Nifty Below 22,750 | Axis Bank &amp; Asian Paints Top Losers", "link": "https://news.google.com/rss/articles/CBMi1AFBVV95cUxOZnZSRWJxOEQyWXg1YVB1VXlXeUFVbTVicHBxMkxUbnJxbnhhTlZKU3p4V0c0dk1vbjY3NVBpOFNmRVUwNWVCSC00ZkNkTDNHRHUyOVFpWVZzMXVRQzNzbWtLMGEwQ3ZRaEZCVnl4MVN1WXQtTmNVa1Z3ZVFDTTJxeHZYQzJwQlpmQU9FTjRtRldzUXhGSkJFQ2tpRURXVnJ0UTNXUmE4SE5lLUdXSmNlYkVpRGpnVzI4akcxcENlcG83QWJTNE1RZEdDOGVNVncxTnM2Nw?oc=5", "source": "Equitymaster", "published": "2026-10-27 10:44", "score": 0.026, "label": "Neutral"}, {"symbol": "MARKET", "title": "Sensex, Nifty Flat Amid Bank/IT Selling, Crude, US Fed Caution", "link": "https://news.google.com/rss/articles/CBMirwFBVV95cUxPaE94ZzJ5dnQxdWVKWG1pRDVyUGRja0JfdEdSdXBnMzNLTjl1Q0ZhRUNfMDNmTWhRamdJQTJUZzNBdWNSWG5TYVp4OUQ3Z0p2bEpTTk9kZUVJY0thSk9IM19qSy1DVkNxOFR6SFphTEkxWHRuLVl1T1hVd1BDUnB1MFpaZ056anFvZDZhSWFDMUJ1V2czT3dNbnp0eU56MkMyYUtBMnZFQkxyVVN5OTBj0gG0AUFVX3lxTE9sdGR4dWFjdV8xTHpMMTFyeERSZEVjNWNBOFpNWW9DNkN2M0pnYkc0T08tVlFIQ1V2cnlrbmF6OGZwSnp2TDdsZmY5dTVadTNHdFRHdEs2cUpBQlRieFFud1hRS0daLUNzMTRrRUFfLVhXT2tFV1JVQ2t0VDJXQm1QZmFsWWZZMko5eHpBODE1V3dZVENIb3ZYMWk5aHU1b1QyUkd1ek13VkNOSS0zbHRzcmpycQ?oc=5", "source": "Rediff MoneyWiz", "published": "2026-10-27 10:43", "score": -0.25, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex, Nifty end flat as high crude and Fed caution offset sectoral gains", "link": "https://news.google.com/rss/articles/CBMi0AFBVV95cUxNSE5fd2R2dlZMSHNPUEg2cnQ3WktSX1BzbUVuWnE5aVNkdlZjSzN5NkVXZzZHUE1MUldtRFdCRXYyX2l2WFo3allFekdTSW91VEl4RFVoWG1mZ2wxOHk0YmhNRXo0dmZfNkdUZUt0VGVGNmhsMkN1d0lCaGxDS2VSTFh0WGpmS2dHSVpfMWUycTZTVTZ4bjktU05VQ0FDOFZHVlBoNzhzUFYyNU9YSFZVUUM1WFg2VC1yMHFCZmJyMEZwWW9pNzNDWlZjSHNjQTRS0gHWAUFVX3lxTE44RkJWdG9HajgtbVZVSjlnQ1hPdF85akRSWF9BZTBpeGMzeXlNTDMwRXFpYk9QLVdfRlFMZ0xPYUI0MGpHZnVfWmZLdTJrNlVzeGpLOWdSOVNjV25EVVRBLTdqNTl4NXlGQzlucThWbWVyU1hxVGFNQ3M3bkthSnJYSTIwVW9TcEJsanhyV0lDNldtd3NmbE8wU0taeHpVUkM3RVBLQTZkYzkzMXB3dVdaSS1oMF9ndE1ZcUhXMHBiT2JjbkhyckJwQzdjZnIzLTJSelB4cUE?oc=5", "source": "India Today", "published": "2026-10-27 10:37", "score": 0.34, "label": "Positive"}, {"symbol": "MARKET", "title": "Why stock market ended mixed today: Sensex, Nifty flat as Midcap Index gains 565 points", "link": "https://news.google.com/rss/articles/CBMivgFBVV95cUxPWXUzSV8xY1IwQmZCLVJRSWl5b29heE8zSWE0dUExaUFsR1pBaGNacFVaZVc5OXUzbFdwajRYMVBFZ2tad0IwWDVrMnEzeExrWktpMHRvWFlENnFybERmSlhLVzZsa1laa3k1Yll2aUVXbC13THhFOUhIV0NIX2pwcTVOSml5ckZJRjhIY3JlTVgxenlXR1owRmdGdDZkSnZSM0w1SDY0dGVGTHRzUDRjYTRfbjhqT2Zrek1HOEdB?oc=5", "source": "IndiaIPO", "published": "2026-10-27 10:35", "score": 0.649, "label": "Positive"}, {"symbol": "MARKET", "title": "Nifty, Sensex close flat amid pressure from high crude prices and caution ahead of US Fed policy", "link": "https://news.google.com/rss/articles/CBMi4wFBVV95cUxPSFBtUFJmM3hPblNvT1VQemlJRFl5WDV1Y0NuREtvVk1abHQxWkROczktb09iMXAzd2xMRi1yUGxyNHVxdkdVbnlBbkRLaXAzS1VMRWVMSm4tckVTUUF1aEpvb2tWem55TUd4Smx5S2IzMUl1RTZlR3lhYjJQM0xfTU9Ya2FRRmxRWWRWSnpzYVlNaWxTbk9MYlFPRm5sT1FRTTBWWVhSa0h6MlNzSVM5WFhrN29JUTRkeGdRX01UeksxWlk2cllkek9GSEtCZ1NkZ0E3MHVVMndTczVRUFBkamtVOA?oc=5", "source": "ANI News", "published": "2026-10-27 10:22", "score": -0.34, "label": "Negative"}, {"symbol": "MARKET", "title": "Is India's Stock Market Heading For Its Worst Year Since 2008 Crisis?", "link": "https://news.google.com/rss/articles/CBMivwFBVV95cUxQaUVuSEo2MFlJdEl2TzJpb0FDR3QxUzQ2TnJaWVk3V09oMW8zV0w0S0NtZDRzUnZiN2RIRGQ3aElmeG5YelB5MVF3MElkYmFJQV9RX0ZMR2FsSUJzdDcydkVZeS1zZUJTSDZtYTdfTGI4cm1ES0JRTjFkd080YS1JbHNzOUFYQ2pwYjE1SEE5MkY3TXBLSE04d1BnOFZ0S3dnR1I0cjI3Yi0wUWxzSWxfZ19ydnNESlJIS0s1NFpVUdIBxwFBVV95cUxNOHRRcjNnTjFKcHlkWFI0eXBXZ2R3QmhQcGZzRXQ2OTVqdE1ZWlZrdGNBTEFlMzJtdlpJMTVPdFJpZ3pDaVRYd0Myd1FraUwtV1d5X29zM1pGNGJ1dVZ5OF82US1rRGRyMGR0UEFrb0RBQVFRRHNUR054UVdKYUJBTHhmYjhjWkVXZ1l3LWRtaWRPNTRDNXJacHpoNTYxN0Fxb3NnNHR0MzkxMmpibGdKY0hkeWh1UHNRUmZNUXdtWFdMT2hJVGhr?oc=5", "source": "NDTV", "published": "2026-10-27 08:56", "score": -0.848, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex Today | Stock Market Live: Sensex, Nifty trade flat; smallcaps jump 2.5%, IT slides 1.5%", "link": "https://news.google.com/rss/articles/CBMivgFBVV95cUxNeXFmTEJhQTB3U2FSNW5IN0lub2hFVk1aSGlmU1RUUE1ITjFDcmpDTVdFQ1VJOHFzYWpqZXpoNEVUbE9pVjh3ZWE2VEcybVI0VEdLNDV2WF9jbHdIX1llcklPcjFXMDM4QzZ0MXptcGtVTjdLTjlUN0pPeFhjOS1vel9YcERQWWFibVdYdzAwTkdtak9UNV9ObGlfdmVXU2RhZGNvaW9XV2o4VFlvOXFUQmd6OU9PaW5GbEhkdDBn?oc=5", "source": "IndiaIPO", "published": "2026-10-27 07:00", "score": 0.67, "label": "Positive"}, {"symbol": "MARKET", "title": "Indian Stock Market: Sensex and Nifty Trade Flat Amid IT Sell-Off, Broader Markets Outperform", "link": "https://news.google.com/rss/articles/CBMitwFBVV95cUxPd2pWd3Q1X1Ywa1lMdUZQcm9ibFNSUkJmc2U5VGVYbkQzWGkzX213ZFRwa3JTVGp4Ui16VEMxVDhLNUE5SVBCb0VnaG9CazdWYTZDajBVTmhmc2tpbjJtR3F4b1FBem9LSUdjejRLRkdrcjFrR3h0akpLRU44SXdoZWc0bXdaMXJHdnRUcGkyV1F6aGFsMEtMT2phNVZVQ0xPb0lELTZIaU1GaTYxVk5oNDdHdjdNMzQ?oc=5", "source": "Pragativadi", "published": "2026-10-27 06:58", "score": 0.691, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex Jumps 483 Points, Nifty Recovers After 4-Day Slump", "link": "https://news.google.com/rss/articles/CBMirgFBVV95cUxQZnNvcWk2MGZvU2hxU2lOaVh0ZjJtdTQ2ZEIxeU5ZVmNfTHotQ1FPQUk2RzE4SlY3Wm12UUhGdHlGOFlPSEh4dVQzX1VBOW14NE5IVnRLdzJtUDZQY05uN1V3aGtUcUJsTndEMVFPcmZOUFVKZlgxTXFucGdKX2E3a2h1UmlWMEVmdmZWQmRvcXVzTDdCalk0MWtSVnRqVTN3Y2cxWVBVYXNGek1PR0HSAbMBQVVfeXFMT1F0SHhMdjdDNXJOWFFKek9TX0FwV2lkTS1Gal9RMkV5eXZmSUlhbmNJZllTZVFaYnRWVTBYcXBlWno2U1ZDXzBYRHpMdXNLZEhBU3NvcUVxaExhNGRHNmZVLUJKTi1vcTI2REl0dnpJVnZ4VXRES2l3MkpmRExaYlZ3d09MNWVoN1JuclpsTmV1VXVGdmRnSjB0ZEllT2RCUDgtdmh0X1JQSU8tbktsV2trTmM?oc=5", "source": "Rediff MoneyWiz", "published": "2026-10-27 06:02", "score": 0.361, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock Markets Today: Sensex, Nifty Dip on High Crude Prices, IT Sector Woes", "link": "https://news.google.com/rss/articles/CBMi2wFBVV95cUxNeHFLVTdjZ2hPazYwSXhYRjQzaFZhV3VGeWx5QzQ4cEw3VHBnN3FGRGNYUnAtckZseEI3SDNrRnlZRHZPcVdoZmdKemtVTnBKX2Zza3VuYUpIZWxiS043OUcwWEhmaTVRcHJkb3FfQTB1QUZrXy1CSml3MkFfVUE3VmpOMmlvaEJJVTlsaUpjMjJFeFBLZ2pPbUN6YlAtX2JfVEtHMnY1VUdmYVRPSnZyQU5mUlNVVzVjOHFsbGRVMHdGUnk5Z0Z2SkNoUkpNSXIzbkVCS2U3R2J6dmvSAd4BQVVfeXFMTVhJay1WR0kwZzBCZzRreEl3Q3I2VXFiTE5sVjcySno3MC0tRVBPVUNsQWpJaFp1VUp0SlJJUG1oQnNDRWZ0YnFSMEZGQXdFUUMxOG42dTdGM2ZwYlYwcnlmLVFIbERLVlkydGx4RGp6THEwakstdnhObVB3Ymxta0dfYVlsNlFwVHJLWENoSXpzeFFZSkxWZnR5TFpER1Vsc1NPS2dndW04c040NGlmeElJRjU0TVZ0eVdjazZ3N1FSSkdkUEJnVFlWOW1ITWFIY0xWUU1PUi1tYlQxVlp3?oc=5", "source": "Rediff", "published": "2026-10-27 05:17", "score": -0.477, "label": "Negative"}, {"symbol": "MARKET", "title": "Stock markets fall in early trade amid persistently elevated crude oil prices, IT selling", "link": "https://news.google.com/rss/articles/CBMi9wFBVV95cUxQX1hLOFBnck1zNGxNSl9SQVlEb3B5QnE4YW9veWRZdmdFd3MxelJFRDRKVXVBVERQX3c1SHdDeDZPZFlpMGZ6NW9lLVAyMWJRRTlSREJMRm9QVUIyZkRVNFA4OThZOGJiQ1F4ZC1LYnRRMHRTNEFMejZabElmbmQ0ZDI1aWU0R2pCUjdRX0F3ejByeWJMQXc3S05uYV9GNWRYM1BFd2ViUWpsOU5oRlhkOVdxUEx6NVdlZUx0elQwdHVXUjVkd2VtSWlkcnl0QzRpVi13VlpXM1NwdzhIR3dPTlY5YmwxUUNtZXhjcXIteExzbE03TUhZ0gH8AUFVX3lxTE5Ba0ZTXy1wcDBKSm1fUFFtRTVFT010TG50Q29IcUJhRnZCc1VpMjItdkQ5LTBsd2ZEaEJPR05LUVlHeDM1MWotdVdSNUpYRVFhYjJidHU0QXhjNkV0akt6V0xkZlNPZ0ZkMGRBd241cERHLV83N1pvc0UzclRYazlBcWpTR3JzVjRDbElMX0dhRnMtSG9MYTloSkloVTlKTkhYanVfV3htNEwwUjlXeEh5OWZ4WEUtLVVIZS1RZTRJMUh2Z29sZ1g5UlI5TzVHeUk2a1M0ZlBldUhNSnlOWDlfS2VuY2NzOGo2SkNJUXlJM0RqdUNFYjlTVWYxNA?oc=5", "source": "bfsi.economictimes.indiatimes.com", "published": "2026-10-27 05:10", "score": -0.727, "label": "Negative"}, {"symbol": "CPPLUS", "title": "Do Aditya Infotech's (NSE:CPPLUS) Earnings Warrant Your Attention?", "link": "https://news.google.com/rss/articles/CBMi0gFBVV95cUxPWm03Y2s2TzZiU2ZxV1l5QTBwZTlLVXkzOFd2WlYyZ1ZiU2dEWUFneElwRG1HMUNaNTFCX1p2V3otUVhCZU5SOTlyRUNIdjZaTTh4cUVmWDRHMlg3ZDNCX0VQaEtITUpRNVBvbHRFMnJ0NjV4YjhOUHZNUFJhZ1IwRGt3UXJDeE16ck5zb3ZSN0ozNVVMc2xjM05NRGVrUjVfWlVEZGJpWGNicFNnb0NvSDYxMFZyS0FoRkFhZTU2T2lienVEZzV5WWxkeFF4bjFsMHfSAdcBQVVfeXFMTkpxQ2JGc2tYb1NXcGpqQzBib1gxRXpKNUpTcmZ0a3lkcm1oMVpBcTN5M3piTUludmVTZWN2ekRHUnpDTThqRVd5TFloZ0h2UkpScFBiWkJ1ZlhxMUtqaXdNaTU0bGhlZVFPX2wyOG9fRDhZYWRPVWxkUzRTTmZabnFpSnA4b0FnM0VDbTY1R3U0ZmJueThIU180bWtiSTV6NHhzbzd4blZsVDdSaHQwWlo3RTdDSk9iTFdqSkZKbEJhSHhzWFJhR3NkVnVzdUVXbTNUTXM5c00?oc=5", "source": "Simply Wall St", "published": "2026-10-27 02:09", "score": 0.0, "label": "Neutral"}, {"symbol": "MARKET", "title": "Stock market outlook today, 27 Oct: Sensex, Nifty prediction - DJIA, S&amp;P, NASDAQ, GIFT Nifty, Kospi, Nikkei, Taiwan cues", "link": "https://news.google.com/rss/articles/CBMiggJBVV95cUxQUVVnVFprN1pwVWtldGFwam9RN2lqcVZPdDRPb3R0Tk84UmlicnBGWHlqanhVZ3JRRTFPcTliOE8xTkg0SkVqRFplanRfTHdDUXdpa3o3NGt3TmRIRHZ2NzZlU20zWHpTY1gtdGVuU1JEeXNvSU91M2QxUTJNMXNUVTczZWdKN0ZkSDBvUG9nOUE0X01GV3FjYU1ocDJuS1FzVW5lZ29DTG5wWEZPUS0yTWJyZGt4UVBLckowTTdtMXd5OGZFN2YwMGotelU3X0ZFRXNkalpydUtzN3lMamN2eWxoN2JYelhLY0V5dG1GeWppeFRNWjVzaTlMUlFsOGNqY1HSAYcCQVVfeXFMTnQ1TGxaT2xKNGpmMUw4dVpEeV84S19hclJFOGpRT1Q5V3BFSXFYZXR5YWZjYTdZSndVbFFZRUdSVldRekxQcVIwV3MyN1pxb24wTnFPZXQ1UmltTF8xSm9NeVhuc3JfTXZQeEpCVy1GbUNRbWI3M2NHTkhqYk03bXVLOGpVZ3g1Y3pMeE9oUkREWEhlZzNVZ3pNOVNlcGtfeG85UUk5M3A2SEVpR0Y1VWdlX2hreTlRV1p6VnVXSjNMUnZWYVhmSnh6T20tdDNKbUUyaHNhWS1tQVU2YXpBOGlTN3Y1QkVhRVQzWFJ4VU0tUHdfaWI5ekE1UnBZU09HdEs0bW1CTFE?oc=5", "source": "Livemint", "published": "2026-10-27 01:30", "score": 0.842, "label": "Positive"}, {"symbol": "MARKET", "title": "Sensex Today Ends 483 Points Higher | Nifty Above 22,750 | Apollo Micro Systems Up 10%", "link": "https://news.google.com/rss/articles/CBMi2wFBVV95cUxPNVY4djR0M0xNQWI4dUltb0hiY0pBV0RER</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LEX INDUSTRIES LTD", "view": "Moderately bullish", "view_score": 0.85, "tone": "mod-bull", "summary": "6.1% below its 12-month high: a shallow pullback inside the uptrend.", "why": "Shallow pullback, strong earnings growth, highest volatility", "points": [{"text": "6.1% below its 12-month high: a shallow pullback inside the uptrend.", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "Highest volatility of the batch (70%) \u2014 expect big swings.", "kind": "risk", "source": "SwingScope data", "url": ""}, {"text": "Premium valuation (P/E \u2248 79).", "kind": "context", "source": "SwingScope data", "url": ""}, {"text": "Earnings growth \u2248 151% YoY (latest quarter).", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "[Results] Aeroflex Industries Share Price Surges 14% After Q2: Profit Jumps 157%, Why the Depreciation Change Matters", "kind": "catalyst", "source": "Univest", "url": "https://news.google.com/rss/articles/CBMi3AFBVV95cUxNanpjQUFtMlRJTE9VYkRiZHVsdDd4bzhuRTd4MlpDd2RvRzZYTDN0UzdQaDJwcEQwaWc4cktjUzRPVUFBN2RRY2czNlhDRVJ5WnlDMHdyTmpUb2J1ekgtZ3RwcHVJYnptZVV2dWJxX0xuRWU1UkVVVjBmOU5Pd2FBMWl2ZkV6TFlodUt1MUNwb2dRNG9aaTRrenRrU3g3ZnE2TXFWU2NHUjYxUVJVOWpYRG5RdUNRMUdvSC16ZGtQb25uZnVNd1BPZHBpOE80MFNMYy04SS1TaGVSNWtl?oc=5"}, {"text": "Since entry: -0.36% (Day 1).", "kind": "risk", "source": "SwingScope data", "url": ""}]}, "CPPLUS": {"symbol": "CPPLUS", "name": "ADITYA INFOTECH LIMITED", "view": "Neutral to bullish", "view_score": 0.4, "tone": "spec", "summary": "11.0% below its 12-month high: a shallow pullback inside the uptrend.", "why": "Shallow pullback, strong earnings growth, stretched valuation", "points": [{"text": "11.0% below its 12-month high: a shallow pullback inside the uptrend.", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "Valuation is stretched (P/E \u2248 93).", "kind": "risk", "source": "SwingScope data", "url": ""}, {"text": "Earnings growth \u2248 304% YoY (latest quarter).", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "[Results] Do Aditya Infotech's (NSE:CPPLUS) Earnings Warrant Your Attention?", "kind": "context", "source": "Simply Wall St", "url": "https://news.google.com/rss/articles/CBMi0gFBVV95cUxPWm03Y2s2TzZiU2ZxV1l5QTBwZTlLVXkzOFd2WlYyZ1ZiU2dEWUFneElwRG1HMUNaNTFCX1p2V3otUVhCZU5SOTlyRUNIdjZaTTh4cUVmWDRHMlg3ZDNCX0VQaEtITUpRNVBvbHRFMnJ0NjV4YjhOUHZNUFJhZ1IwRGt3UXJDeE16ck5zb3ZSN0ozNVVMc2xjM05NRGVrUjVfWlVEZGJpWGNicFNnb0NvSDYxMFZyS0FoRkFhZTU2T2lienVEZzV5WWxkeFF4bjFsMHfSAdcBQVVfeXFMTkpxQ2JGc2tYb1NXcGpqQzBib1gxRXpKNUpTcmZ0a3lkcm1oMVpBcTN5M3piTUludmVTZWN2ekRHUnpDTThqRVd5TFloZ0h2UkpScFBiWkJ1ZlhxMUtqaXdNaTU0bGhlZVFPX2wyOG9fRDhZYWRPVWxkUzRTTmZabnFpSnA4b0FnM0VDbTY1R3U0ZmJueThIU180bWtiSTV6NHhzbzd4blZsVDdSaHQwWlo3RTdDSk9iTFdqSkZKbEJhSHhzWFJhR3NkVnVzdUVXbTNUTXM5c00?oc=5"}, {"text": "Since entry: -3.07% (Day 1).", "kind": "risk", "source": "SwingScope data", "url": ""}]}, "THANGAMAYL": {"symbol": "THANGAMAYL", "name": "THANGAMAYIL JEWELLERY LTD", "view": "Neutral to bearish", "view_score": -0.91, "tone": "mod-bear", "summary": "36.7% below its 12-month high \u2014 a deep drawdown; the trend is weakening.", "why": "Strong earnings growth, results, deep drawdown, negative recent leg", "points": [{"text": "36.7% below its 12-month high \u2014 a deep drawdown; the trend is weakening.", "kind": "risk", "source": "SwingScope data", "url": ""}, {"text": "3-1 month return -22.3% \u2014 the recent leg is negative.", "kind": "risk", "source": "SwingScope data", "url": ""}, {"text": "High volatility (58%).", "kind": "risk", "source": "SwingScope data", "url": ""}, {"text": "Thin liquidity (\u20b937 cr/day) \u2014 gap risk in a falling market.", "kind": "risk", "source": "SwingScope data", "url": ""}, {"text": "Earnings growth \u2248 86% YoY (latest quarter).", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "[Results] Thangamayil FY26 Net Profit Jumps 196% to \u20b935,165 Lakhs", "kind": "catalyst", "source": "scanx.trade", "url": "https://news.google.com/rss/articles/CBMi8AFBVV95cUxNZWQxVFZva3o0cms1Y2N2ZmRJMnk0TmZzTTdLUWVuZE8taXVteEgyeDhHQi1wYUIyU0RGb3J5QWFxd2pLSTJILUVSOEZVZTBDbExkVkMtT0tiNjhGOGpubU1KQ25LQ1ZFUXkyUDZmY0FIdWZBSm96cm1vZ3R3VEtQUHFKLTBZM18tZmx4NDhNRWM2OURvX2xQQXJncWtod1ZoR3ZoV3A4bldUSkxXMU8xNlEzU2tMeWYxeHMwYk5LeVlYQ3hJeGVqMkdNYlRIQTZnUXpxTk5xZzA0aGZqNGVId0pnbTRLd3RJNWZZcWQ3azQ?oc=5"}, {"text": "Since entry: -3.79% (Day 1).", "kind": "risk", "source": "SwingScope data", "url": ""}]}, "KIRLOSENG": {"symbol": "KIRLOSENG", "name": "KIRLOSKAR OIL ENG LTD", "view": "Neutral to bearish", "view_score": -1.2, "tone": "mod-bear", "summary": "26.3% below its 12-month high \u2014 a deep drawdown; the trend is weakening.", "why": "Deep drawdown", "points": [{"text": "26.3% below its 12-month high \u2014 a deep drawdown; the trend is weakening.", "kind": "risk", "source": "SwingScope data", "url": ""}, {"text": "Since entry: -4.98% (Day 1).", "kind": "risk", "source": "SwingScope data", "url": ""}]}, "SMLMAH": {"symbol": "SMLMAH", "name": "SML MAHINDRA LIMITED", "view": "Bearish", "view_score": -1.78, "tone": "bear", "summary": "29.0% below its 12-month high \u2014 a deep drawdown; the trend is weakening.", "why": "Accelerating momentum, deep drawdown, high volatility", "points": [{"text": "29.0% below its 12-month high \u2014 a deep drawdown; the trend is weakening.", "kind": "risk", "source": "SwingScope data", "url": ""}, {"text": "3-1 month return +42.7% \u2014 recent momentum is accelerating.", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "High volatility (62%).", "kind": "risk", "source": "SwingScope data", "url": ""}, {"text": "Thin liquidity (\u20b938 cr/day) \u2014 gap risk in a falling market.", "kind": "risk", "source": "SwingScope data", "url": ""}, {"text": "Since entry: -3.93% (Day 1).", "kind": "risk", "source": "SwingScope data", "url": ""}]}, "AETHER": {"symbol": "AETHER", "name": "AETHER INDUSTRIES LIMITED", "view": "Neutral", "view_score": -0.46, "tone": "neutral", "summary": "12.2% below its 12-month high \u2014 consolidating after a big run.", "why": "Results, thin liquidity, stretched valuation", "points": [{"text": "12.2% below its 12-month high \u2014 consolidating after a big run.", "kind": "context", "source": "SwingScope data", "url": ""}, {"text": "Thin liquidity (\u20b939 cr/day) \u2014 gap risk in a falling market.", "kind": "risk", "source": "SwingScope data", "url": ""}, {"text": "Valuation is stretched (P/E \u2248 91).", "kind": "risk", "source": "SwingScope data", "url": ""}, {"text": "[Results] Aether Industries Q2 FY27: Net profit rises 26% to \u20b968 crore as revenue climbs 24% to \u20b9347 crore", "kind": "catalyst", "source": "Business Upturn", "url": "https://news.google.com/rss/articles/CBMi2wFBVV95cUxNbVVVa0lsV1JvNU1BWnlRVFJSNDQ2Y3l5Z0xwZWdFS2JSTkJPbkxlN2ZfNE1ZZ2hVa0EwMVZ3enhwOGNTQ2VFRC0waFdOckhEaGJ5RDctUGg4UUEyNE9La1BweFVkeWNya2h0SFZ4WVZhZlVLTjl2cXhLaURoTkxSMXd6MHVVTmtYZk90SUx1NmsycU1KMHZKZVItNWRuR29pYy1KWTVEMWdPdGVQcHRQMXFadHJ2TFc0UEFjVGpKM2s1WTJER1RJV3Y4eU1GMmItSDNpR2hBZlRNdkk?oc=5"}, {"text": "Since entry: +1.18% (Day 1).", "kind": "catalyst", "source": "SwingScope data", "url": ""}]}, "SBC": {"symbol": "SBC", "name": "SBC EXPORTS LIMITED", "view": "Strongest, bullish", "view_score": 2.0, "tone": "strong-bull", "summary": "Close is only -0.0% below its 12-month high \u2014 relative strength near highs.", "why": "Near highs, accelerating momentum, thin liquidity", "points": [{"text": "Close is only -0.0% below its 12-month high \u2014 relative strength near highs.", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "3-1 month return +27.2% \u2014 recent momentum is accelerating.", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "Lowest volatility of the batch (36%).", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "Thin liquidity (\u20b948 cr/day) \u2014 gap risk in a falling market.", "kind": "risk", "source": "SwingScope data", "url": ""}, {"text": "Premium valuation (P/E \u2248 78).", "kind": "context", "source": "SwingScope data", "url": ""}, {"text": "Since entry: -1.34% (Day 1).", "kind": "risk", "source": "SwingScope data", "url": ""}]}, "SYRMA": {"symbol": "SYRMA", "name": "SYRMA SGS TECHNOLOGY LTD", "view": "Bullish", "view_score": 1.54, "tone": "bull", "summary": "6.4% below its 12-month high: a shallow pullback inside the uptrend.", "why": "Shallow pullback, accelerating momentum", "points": [{"text": "6.4% below its 12-month high: a shallow pullback inside the uptrend.", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "3-1 month return +30.0% \u2014 recent momentum is accelerating.", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "Premium valuation (P/E \u2248 85).", "kind": "context", "source": "SwingScope data", "url": ""}, {"text": "Earnings growth \u2248 86% YoY (latest quarter).", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "[Results] Syrma SGS Q2 results: Profit nearly doubles to \u20b9117 crore, revenue jumps 74%", "kind": "catalyst", "source": "CNBC TV18", "url": "https://news.google.com/rss/articles/CBMirAFBVV95cUxQWWVNajdfcWthd1FGS3dENzdIeWltVzdfWTRueHBPYlFWSEs4MHNnOW9HQnVWODIxTENyb21PblA5Y3d2Ym4zeVkza29VZ0VQSENCb3dhUVQyN1N4WFlGWnNTaUt1czBRWl9NTy01UmU0bExnQXZKMUhpeW8yUU9GT0tPbDFpeHh6em5GZzNZNzZTYUFuSkR6RlFwS0Fwcy1SQjZLSHdDdTRFaTZm0gGsAUFVX3lxTFBZZU1qN19xa2F3UUZLd0Q3N0h5aW1XN19ZNG54cE9iUVZISzgwc2c5b0dCdVY4MjFMQ3JvbU9uUDljd3ZibjN5WTNrb1VnRVBIQ0Jvd2FRVDI3U3hYWUZac1NpS3VzMFFaX01PLTVSZTRsTGdBdkoxSGl5bzJRT0ZPS09sMWl4eHp6bkZnM1k3NlNhQW5KRHpGUXBLQXBzLVJCNktId0N1NEVpNmY?oc=5"}, {"text": "Since entry: -2.97% (Day 1).", "kind": "risk", "source": "SwingScope data", "url": ""}]}, "TDPOWERSYS": {"symbol": "TDPOWERSYS", "name": "TD POWER SYSTEMS LTD.", "view": "Neutral to bullish", "view_score": 0.5, "tone": "spec", "summary": "12.9% below its 12-month high \u2014 consolidating after a big run.", "why": "Accelerating momentum, strong earnings growth, high volatility", "points": [{"text": "12.9% below its 12-month high \u2014 consolidating after a big run.", "kind": "context", "source": "SwingScope data", "url": ""}, {"text": "3-1 month return +39.4% \u2014 recent momentum is accelerating.", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "High volatility (63%).", "kind": "risk", "source": "SwingScope data", "url": ""}, {"text": "Premium valuation (P/E \u2248 81).", "kind": "context", "source": "SwingScope data", "url": ""}, {"text": "Earnings growth \u2248 72% YoY (latest quarter).", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "Since entry: -0.77% (Day 1).", "kind": "risk", "source": "SwingScope data", "url": ""}]}, "RATNAVEER": {"symbol": "RATNAVEER", "name": "RATNAVEER PRECISION ENG L", "view": "Strongest, bullish", "view_score": 1.8, "tone": "strong-bull", "summary": "Close is only -0.0% below its 12-month high \u2014 relative strength near highs.", "why": "Near highs, very strong 6-1", "points": [{"text": "Close is only -0.0% below its 12-month high \u2014 relative strength near highs.", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "6-1 month return +106% \u2014 very strong medium-term momentum.", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "3-1 month return +77.9% \u2014 recent momentum is accelerating.", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "Most liquid name in the batch (\u20b9178 cr/day).", "kind": "context", "source": "SwingScope data", "url": ""}, {"text": "[Results] Ratnaveer Precision Engineering Q2 FY27 Earnings Call on 3 Nov", "kind": "context", "source": "Kalkine India", "url": "https://news.google.com/rss/articles/CBMi1gFBVV95cUxOT0FlR3g5MTluX3phZ0tWLW1iVHAzbUh0dGFBRjcyLTBFQTl5bXkweTNIYlAtYjFSYlhBUFJYQ05VOVUzUFRLaDhwcmg0b2xZSE1JMV9rNlpuMFFDYTljQnpjdE5rMDJ2YWxGaDJZMFpCWFd5RDBuYjFvbE8xS085dmc0aktudXE5MDc5UlhCUVlQSVBtRnFwbUtwNG1lNkFVM2tWYzNLeDdHTGlhUjBXNEVMZ011Q0RJVkVoM24tWTNHWERXbHZ5U1hhOTRDQ0RmSlBFWDdn?oc=5"}, {"text": "Since entry: +1.71% (Day 1).", "kind": "catalyst", "source": "SwingScope data", "url": ""}]}}, "shortlist": ["SBC", "RATNAVEER", "SYRMA", "AEROFLEX", "TDPOWERSYS", "CPPLUS", "AETHER", "THANGAMAYL", "KIRLOSENG", "SMLMAH"], "missing": []}, "telegram_sent": "2026-10-30", "pending_alerts": []}</t>
+          <t>mduWkxPd05zT0xvWDR6TkI4UnFlWEpXQ2RoeUdzTmVCYTltSlBNWU1uelg5ZmhDLW9YaGNPLTJxeWNOUUk2QWhrd3VOZ2tkZWRtZTI1c3lHUW1qQXlRWUI5QzJ4bDg5a29rSnJ5R2tlbnJvQ3NRR2JNMzVEeG5ERmtNSmcwclc5TmdKVFZsVDlKQnM3QzN2c054Q1M2V2U3MmRKTmFOS2oySGh0dXJQRXpZQXoyaGJfdTVURHFDSW55QlE?oc=5", "source": "Equitymaster", "published": "2026-10-26 10:28", "score": 0.402, "label": "Positive"}, {"symbol": "MARKET", "title": "Taking Stock: Market snaps 4-day losing streak; Nifty reclaims 22,700, Sensex gains 483 pts", "link": "https://news.google.com/rss/articles/CBMi6AFBVV95cUxOVWJueUF1ZWF1TG4wWWNaNDZuZTBmVExLdzJIbm5IMEtxZ2xSRXFZSll3ZGJRTnNHTU9yVUZJa24xR0NJUUMySENtQU9pRTlGaWNRMXluNl9La1M0U1VnanlmN09OQmV2N3hRbE1uTWhJamNUMldPVF9HWUV3SC12MmxqS002SFF0X2JHTUl3ZkMtUldyTWlXX092YjZJdUt6OHVVMXZIR1NUamZ5RGVJM3BqVnFFQ0JIbmhHNjlFLUhreVVKRk9DVG1vR3JtSWN4V1V5X3JvUDhPMERoeERIUjBsM2kzWExz0gHuAUFVX3lxTE9SUjdSaUNmT294eG1rSTRKdWhFSEtzMDlHQ29odFVmckFhMzI2UUFSZDVicHdoMDdNZ3QwTHlkMV9oYU41Mk1pMERicWcxdk9OX1hkLUdpN3VCa1ZfV1NVWHo3Ukc0QXJLMWxnR2xmaGQxQWtMOGZIcFpBXzMxSF9PTzBkS2pVOU1zZTFLNGpEMFpxQ24zNWZlZ0QwSWdaanpqZHNUa2x4V3BVWm9xa3phdFlkQnE2TWVndWZRWkw2OFBpemV4ZUJPV2JYbEItYVRqZFl1TDF4ZlVZU3RoNGNqVzVaUnJPMGNMMllyR0E?oc=5", "source": "Moneycontrol.com", "published": "2026-10-26 10:18", "score": 0.402, "label": "Positive"}, {"symbol": "SMLMAH", "title": "SML Mahindra Limited (SMLMAH.NS) Slips 2.83% to \u20b94,706.5 as Stock Tests Lower End of \u20b94,471\u2013\u20b94,942 Range - Hedge Fund Favorites", "link": "https://news.google.com/rss/articles/CBMizwFBVV95cUxNbV9TQktMZzVLS2k1YWJHSlJsamJtNXBFOHJwZHEtX2ZCZ2Y2azU5blNvbVpLQngxeF94SEVkb3phRXVpOUFVb2tBdFJCUkczMENNTU92Ry12WE5idExOVjFVOXZNdndUNEVIdVpFZlpvczFiT3ZtRlVDeE9ibkhleVc0dEJNWFF1ZmJpMTdMa3V2a1ZaNzBGenpNTXRxTEdERXNVb3dQbXBPMWdWMURzeXNkZHVfRnFnTkxvclhiVk1FcVBJQUlDUDNzcFNtTUU?oc=5", "source": "https://www.siam.in/", "published": "2026-10-26 05:47", "score": -0.318, "label": "Negative"}, {"symbol": "MARKET", "title": "Sensex settles 500 pts higher, Nifty ends above 22,750: Key factors behind markets snapping 4-day fall", "link": "https://news.google.com/rss/articles/CBMi8gFBVV95cUxObWtEb2xmNG1MT1gtZGl5QmxBd0FnOUsyTG9KRC1fZGp4TVB2bXU5dy1DbXVFT0lpMHJsdjhJUG8xUGNOUTRCazQ0eGdNNm1aRmp5STQ5WVVfVk11QmlNaW5sRVFzMGFneGd0WFR1TV9SMzRYWlR6M2JxR3FPMmFXVjctVlRQS0Fkb0dLUGN0QzdHUlV3YjBJWUhLYnppS0xrY3ljU1pScG1ZYlhYOUQ4bGJCQXRkRDNMS0h6cExQOWRkWkJhbm5UMEt6clUxbjhNamRwNnBMUF9GZXlhc29ZOEhwN0ZFdEc0OHdNM21pOXcwQdIB9wFBVV95cUxPYm5CY2tLWFh0dHNHTDhZVU5ZUU9jTzZqUmZkMUxHX09CT1JXVW9yNDJralc1a0I3MkY5ajNSVlNlZEtOOVJhajV2SERSbDRveW5CZVRyaWl1QmxmMF9zR0M1a2hwUEtibHRnYzhrc2xreUpKNVJLbkdCdnBnelpMejYxeDFhVmc0czFLQXd2dmd1cFBHTmVES1VabGxha25OTnFIZ2RTUlU4b3BXWmxuVVZidVJpcEhxdU5VaHBGT0JYd2JUaUlKa2lJdl9TV29tTHQ0NWJJZUpZM2l6eUZIT1lVTGQxQ3d6SF9SMloxMUZTODFYR01v?oc=5", "source": "Moneycontrol.com", "published": "2026-10-26 04:32", "score": 0.077, "label": "Neutral"}, {"symbol": "MARKET", "title": "Why is the stock market down today? Sensex drops over 600 points, Nifty drops below 22,400 - Top 3 reasons explained", "link": "https://news.google.com/rss/articles/CBMijwJBVV95cUxOb1ltRTY1OWNHNTZkX01xdG94Sno3YzJaVXpTRGVHRm5oeHVsbmtxX2lLN1VYbDhkaV91TUdPRG1vYk5ISlp6Y2xzVkZXdkNtQ1FCY2h0WFRSck9fZG5idm9STGFzWjQ2RXN0THlLcWZITV9QRy1yVGFyTnRvNTFHQ2sxRkloT190WWlFRTlJWUJCV3Vhcmg2YUZtVEJOaVRTR3FyclhwSlF0OGhHM3AyZVhPbmhQa2lpalR1QTRabi1pRDdYWHVSSUNINzRIWUd5TDJtUm9ieklsb3hzZ2tqdWp6ZHdGWVZFLTFDVVJWem1XVHJtRFhQd2J6Vy1DWjFyV0JOMGxtaUw2QzhTX2Iw0gGUAkFVX3lxTE43aTVQOGpOSnN6Q1RIY0hHMUZoa1lWQ3VWYjBCVzdxSmZJM2VxRlkzdngteEhxTzRWOFY5UVE3Rk1NX0J0a281VDdaTTVCakxnX0pWTTJNT09QNzRLcjRmdGhNNlBJczlFUzNIOEY0Qm1UNUpPVzhqbFduWmg2azBPTlY2WW5KZ1BPYmZBQ0t0a3NYem0zc3h4cXBjVXhRWkdxZXFqR3pyS2JjX2pycmVGc0ZtblJRa0F5WVU0bDlFMlNlV2hUeFo2c0c3X2JydnBRNjlGMEkxb3RUcVdNMThtRVNiVG05RlBhX3FkRXdGc2NZN1V4cW9MQTZ4MkRkNU9YNkc1Njg1QklKVXM2SGx2dVZmQQ?oc=5", "source": "Livemint", "published": "2026-10-26 04:05", "score": 0.542, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock Market Today: Gift Nifty, FPI Outflows To Oil Prices; Five Key Factors For Sensex, Nifty 50 On October 26", "link": "https://news.google.com/rss/articles/CBMi9AFBVV95cUxPSHRyNnRKa2l4REEydXQ2Q2k3TGFibXlGTHYxMXZYNWVfT0wwREEwV1JCbDMtZjZPa2c3SGMtcVVXdTVONDFuQ19MRmdxNkYxNVRMOHRJTEVyX2Jwd3h4UVVZcGhSZExmLXNUc0ZpS3dPX0V5eEVVTmtWMVlaNXNwTkFxaVFZTnVxNjNuaWkwbWZGb0toQkVkcUZvVG1oWi1VdzFPZHVQSzFFdFVfcHRIMVAtV1lycE9OaVJzdDRGWE5uamNsdEhCWmt2TEZpZ1plUE1uS3V5ZlViQWVmMzljSURGeTZBWkdJM1R4NWlnQWpTX3BO0gH8AUFVX3lxTE9JSmRUODFyV0xUUE16TFZoTkxKOXFjOTVRSUxzenEwRmt6LUUtWXlUZlNBekdRWFhUM3kwUjV2d2JWMExZWEUxNkt2d0JET2RMdkw0WGNpakMyMm9yX3NhLW5PVVdNTlVaNVdSUDRELUZOUXJsZndCTXU4TE9wcFVySTk3LW5qQzRJMUR1aWhsLW15VUJDbVhHNlg4QWpkTFdaODItQzVEMUs2Ukd3ci1LaHV4Y1lqS1VadWRVcmxYM1JRRl9qZTNQRUZSM0NsRDVFOWUxT1ZiVUU4eWVaT3hQUWJjMnFwb0JlcG1BMmc1TldxdVJNRzhHN3BDMQ?oc=5", "source": "NDTV Profit", "published": "2026-10-26 01:27", "score": 0.807, "label": "Positive"}, {"symbol": "MARKET", "title": "Stock market outlook today, 26 Oct: Sensex, Nifty prediction - DJIA, S&amp;P, NASDAQ, GIFT Nifty, Kospi, Nikkei cues", "link": "https://news.google.com/rss/articles/CBMiggJBVV95cUxPQ1VteDhIb2FLNjlYTDNFYnpHMkZnUUhzdWp1OXhZVmFEakEwUkRhaFRQWkw1NTFmT3pNWjdtWV9sRG44T2t3ZWJKY2hfZ2JnTVBHMkZaVDFFdWpseUQ2Q1BrMG9UTzUtWmJjaDlEQkJzWkczZ096NWNyekZwODNmTi1vaFRaRHJ5WHVoRnJ0anZ3RnRYVTB0UVJtaWU3VHotWHkyN253b1N2U3FBakhfcFBMcVotUXJEZVB3bV9VN0NpWnJIT2dQQ1lhNm9TNTJ0TnhSOHctb3FKeldmVmtzN0Y1UXBNWXkwckpSdU5LM2FpSDNrNGdkQmhOY3RzVThScmfSAYcCQVVfeXFMTVhYNU56cEdVekczaDV0QXFhMWhxYk1ScXYxVGpyZURHTDQyYmJYdTAtdEt3S0NPaDVxaXpodmMwNko5bzJtcnZjSlV5Xy1WS3ViVDFDWk9TUUdjclpRMnpGMWsweklyTk5SenllRUR4QnF0N1pMU0NaTXNHTWw1NmljUE1FX2FSOUtaZGc3SldjMVBjNzZsV2EyUEVTdlZ4STlGY0JTRlNOUGFxUVN3bC1kVWlTSHNUb0NlQUhSZmw1UlZxWkJHQjNMYlI2V01JZ2ZCcldqemg2Qk81NFZESE1yVjZORUxBSnlYY1FYaGtSeXowOEUwYVVSXzRuRWs2UjFhNmkzdlU?oc=5", "source": "Livemint", "published": "2026-10-26 01:22", "score": 0.842, "label": "Positive"}, {"symbol": "MARKET", "title": "Trump hints at an Iran attack or deal! Impact on India stock market, Sensex, Nifty, gold decoded; top 10 stocks to watch", "link": "https://news.google.com/rss/articles/CBMikwJBVV95cUxNa3ozTnRCMGwyY1N4ZU44amNGNmtOQU95T0dPWG1JV0lLOHI3TEdzU0pJYXR1S3VPODFBZktza2RBYTRnQmdiSFROTE9fNkkwNTJsNnVMZDBwR3NQMTlxUEVudmRpMjM2Wmh1bjBsdjBfZmtHM3RwWUc2Tk5sc2JhVjQ1dElaS3hJdl9HOHNucGhHZ1lNQTMycHVSTmxZZFY2RHpobzZjNmNSNTBrb1lTeE14WkdYcWNnU29PWU1BRW5RVTY4QkJNbUM2dlhZRU9aYnRJUDNvaHI0TDg5N0ZEakVndlh4Z1k0cV90ZTRGeW9RNW9tWjhUakR0cGtzanJ1OHVFR0lzRFdaOTdMUmRybUdlONIBmAJBVV95cUxQaUpwaTBtTU0wdTdWbUllRWhlMmR4eGRwY055bVE5VVUxNGEyY3h2Y09XaXN5SjJ2a2FGc3ZrT2VTNFRtTEZJTjdlQkR4eGFqSDgzMzlSZFJJYUxjYmNmZTdoMUhneS1CZm0wZ3RnS3JNcnJkSUJPMS1pRW81aDA5UHNBbXZVYThRY19BSFNRZno2Sm5GeXpSMDFPUG1sRjZxMTFTWGZOMU4yakNFNmRaeW03NEJGLVA3aElDWThicGZNb2ZzdzE2eHN3bk1WUWxyQ0x6dDBULTg4T1hFNGFjTDFQOWF3Y1VRdWtqdEFJS2dDYW54LWZtaERRNGZKMHdIOUZCbWMxQWpiTV9VV2w3ekNRQnF0Q1Nx?oc=5", "source": "Livemint", "published": "2026-10-25 07:03", "score": 0.176, "label": "Neutral"}], "errors": []}, "created": "2026-10-30T14:55:17", "last_updated": "2026-10-30T19:42:20", "corp_actions": [], "fundamentals": {"AEROFLEX": {"name": "AEROFLEX INDUSTRIES LTD", "pe": 78.65103, "fwd_pe": 54.181824, "sector": "Industrials", "industry": "Metal Fabrication", "mcap_cr": 7098.2230016, "pb": 14.2838125, "rev_growth": 0.873, "earn_growth": 1.509}, "CPPLUS": {"name": "ADITYA INFOTECH LIMITED", "pe": 93.28194, "fwd_pe": 50.383343, "sector": "Industrials", "industry": "Building Products &amp; Equipment", "mcap_cr": 46739.259392, "pb": 23.922348, "rev_growth": 0.895, "earn_growth": 3.037}, "THANGAMAYL": {"name": "THANGAMAYIL JEWELLERY LTD", "pe": 35.413353, "fwd_pe": 24.44221, "sector": "Consumer Cyclical", "industry": "Luxury Goods", "mcap_cr": 13847.0391808, "pb": 9.778979, "rev_growth": 0.712, "earn_growth": 0.861}, "KIRLOSENG": {"name": "KIRLOSKAR OIL ENG LTD", "pe": 47.92156, "fwd_pe": 31.48291, "sector": "Industrials", "industry": "Specialty Industrial Machinery", "mcap_cr": 26136.82176, "pb": 7.2113123, "rev_growth": 0.134, "earn_growth": -0.199}, "SMLMAH": {"name": "SML MAHINDRA LIMITED", "pe": 46.491833, "fwd_pe": null, "sector": "Consumer Cyclical", "industry": "Auto Manufacturers", "mcap_cr": 6837.129216, "pb": 12.203249, "rev_growth": 0.207, "earn_growth": -0.444}, "AETHER": {"name": "AETHER INDUSTRIES LIMITED", "pe": 91.00225, "fwd_pe": 54.33023, "sector": "Basic Materials", "industry": "Specialty Chemicals", "mcap_cr": 21451.4745344, "pb": 8.731544, "rev_growth": 0.275, "earn_growth": 0.341}, "SBC": {"name": "SBC EXPORTS LIMITED", "pe": 77.82353, "fwd_pe": null, "sector": "Consumer Cyclical", "industry": "Apparel Manufacturing", "mcap_cr": 3149.997056, "pb": 31.276596, "rev_growth": 0.855, "earn_growth": 0.0}, "SYRMA": {"name": "SYRMA SGS TECHNOLOGY LTD", "pe": 84.51898, "fwd_pe": 50.154373, "sector": "Technology", "industry": "Electronic Components", "mcap_cr": 31307.3369088, "pb": 10.862635, "rev_growth": 0.683, "earn_growth": 0.86}, "TDPOWERSYS": {"name": "TD POWER SYSTEMS LTD.", "pe": 81.125, "fwd_pe": 47.99328, "sector": "Industrials", "industry": "Specialty Industrial Machinery", "mcap_cr": 22948.2299392, "pb": 20.810984, "rev_growth": 0.721, "earn_growth": 0.72}, "RATNAVEER": {"name": "RATNAVEER PRECISION ENG L", "pe": 18.569588, "fwd_pe": 22.657234, "sector": "Basic Materials", "industry": "Steel", "mcap_cr": 3023.4468352, "pb": 3.659887, "rev_growth": 0.189, "earn_growth": -0.097}}, "research": {"method": "auto", "generated": "2026-10-30 19:42", "title": "Stock by stock (auto-generated)", "stocks": {"AEROFLEX": {"symbol": "AEROFLEX", "name": "AEROFLEX INDUSTRIES LTD", "view": "Moderately bullish", "view_score": 0.85, "tone": "mod-bull", "summary": "6.1% below its 12-month high: a shallow pullback inside the uptrend.", "why": "Shallow pullback, strong earnings growth, highest volatility", "points": [{"text": "6.1% below its 12-month high: a shallow pullback inside the uptrend.", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "Highest volatility of the batch (70%) \u2014 expect big swings.", "kind": "risk", "source": "SwingScope data", "url": ""}, {"text": "Premium valuation (P/E \u2248 79).", "kind": "context", "source": "SwingScope data", "url": ""}, {"text": "Earnings growth \u2248 151% YoY (latest quarter).", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "[Results] Aeroflex Industries Share Price Surges 14% After Q2: Profit Jumps 157%, Why the Depreciation Change Matters", "kind": "catalyst", "source": "Univest", "url": "https://news.google.com/rss/articles/CBMi3AFBVV95cUxNanpjQUFtMlRJTE9VYkRiZHVsdDd4bzhuRTd4MlpDd2RvRzZYTDN0UzdQaDJwcEQwaWc4cktjUzRPVUFBN2RRY2czNlhDRVJ5WnlDMHdyTmpUb2J1ekgtZ3RwcHVJYnptZVV2dWJxX0xuRWU1UkVVVjBmOU5Pd2FBMWl2ZkV6TFlodUt1MUNwb2dRNG9aaTRrenRrU3g3ZnE2TXFWU2NHUjYxUVJVOWpYRG5RdUNRMUdvSC16ZGtQb25uZnVNd1BPZHBpOE80MFNMYy04SS1TaGVSNWtl?oc=5"}, {"text": "Since entry: -0.36% (Day 1).", "kind": "risk", "source": "SwingScope data", "url": ""}]}, "CPPLUS": {"symbol": "CPPLUS", "name": "ADITYA INFOTECH LIMITED", "view": "Neutral to bullish", "view_score": 0.4, "tone": "spec", "summary": "11.0% below its 12-month high: a shallow pullback inside the uptrend.", "why": "Shallow pullback, strong earnings growth, stretched valuation", "points": [{"text": "11.0% below its 12-month high: a shallow pullback inside the uptrend.", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "Valuation is stretched (P/E \u2248 93).", "kind": "risk", "source": "SwingScope data", "url": ""}, {"text": "Earnings growth \u2248 304% YoY (latest quarter).", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "[Results] Do Aditya Infotech's (NSE:CPPLUS) Earnings Warrant Your Attention?", "kind": "context", "source": "Simply Wall St", "url": "https://news.google.com/rss/articles/CBMi0gFBVV95cUxPWm03Y2s2TzZiU2ZxV1l5QTBwZTlLVXkzOFd2WlYyZ1ZiU2dEWUFneElwRG1HMUNaNTFCX1p2V3otUVhCZU5SOTlyRUNIdjZaTTh4cUVmWDRHMlg3ZDNCX0VQaEtITUpRNVBvbHRFMnJ0NjV4YjhOUHZNUFJhZ1IwRGt3UXJDeE16ck5zb3ZSN0ozNVVMc2xjM05NRGVrUjVfWlVEZGJpWGNicFNnb0NvSDYxMFZyS0FoRkFhZTU2T2lienVEZzV5WWxkeFF4bjFsMHfSAdcBQVVfeXFMTkpxQ2JGc2tYb1NXcGpqQzBib1gxRXpKNUpTcmZ0a3lkcm1oMVpBcTN5M3piTUludmVTZWN2ekRHUnpDTThqRVd5TFloZ0h2UkpScFBiWkJ1ZlhxMUtqaXdNaTU0bGhlZVFPX2wyOG9fRDhZYWRPVWxkUzRTTmZabnFpSnA4b0FnM0VDbTY1R3U0ZmJueThIU180bWtiSTV6NHhzbzd4blZsVDdSaHQwWlo3RTdDSk9iTFdqSkZKbEJhSHhzWFJhR3NkVnVzdUVXbTNUTXM5c00?oc=5"}, {"text": "Since entry: -3.07% (Day 1).", "kind": "risk", "source": "SwingScope data", "url": ""}]}, "THANGAMAYL": {"symbol": "THANGAMAYL", "name": "THANGAMAYIL JEWELLERY LTD", "view": "Bearish", "view_score": -1.7, "tone": "bear", "summary": "36.7% below its 12-month high \u2014 a deep drawdown; the trend is weakening.", "why": "Strong earnings growth, deep drawdown, negative recent leg", "points": [{"text": "36.7% below its 12-month high \u2014 a deep drawdown; the trend is weakening.", "kind": "risk", "source": "SwingScope data", "url": ""}, {"text": "3-1 month return -22.3% \u2014 the recent leg is negative.", "kind": "risk", "source": "SwingScope data", "url": ""}, {"text": "High volatility (58%).", "kind": "risk", "source": "SwingScope data", "url": ""}, {"text": "Thin liquidity (\u20b937 cr/day) \u2014 gap risk in a falling market.", "kind": "risk", "source": "SwingScope data", "url": ""}, {"text": "Earnings growth \u2248 86% YoY (latest quarter).", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "Since entry: -3.79% (Day 1).", "kind": "risk", "source": "SwingScope data", "url": ""}]}, "KIRLOSENG": {"symbol": "KIRLOSENG", "name": "KIRLOSKAR OIL ENG LTD", "view": "Neutral to bearish", "view_score": -1.2, "tone": "mod-bear", "summary": "26.3% below its 12-month high \u2014 a deep drawdown; the trend is weakening.", "why": "Deep drawdown", "points": [{"text": "26.3% below its 12-month high \u2014 a deep drawdown; the trend is weakening.", "kind": "risk", "source": "SwingScope data", "url": ""}, {"text": "Since entry: -4.98% (Day 1).", "kind": "risk", "source": "SwingScope data", "url": ""}]}, "SMLMAH": {"symbol": "SMLMAH", "name": "SML MAHINDRA LIMITED", "view": "Bearish", "view_score": -1.78, "tone": "bear", "summary": "29.0% below its 12-month high \u2014 a deep drawdown; the trend is weakening.", "why": "Accelerating momentum, deep drawdown, high volatility", "points": [{"text": "29.0% below its 12-month high \u2014 a deep drawdown; the trend is weakening.", "kind": "risk", "source": "SwingScope data", "url": ""}, {"text": "3-1 month return +42.7% \u2014 recent momentum is accelerating.", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "High volatility (62%).", "kind": "risk", "source": "SwingScope data", "url": ""}, {"text": "Thin liquidity (\u20b938 cr/day) \u2014 gap risk in a falling market.", "kind": "risk", "source": "SwingScope data", "url": ""}, {"text": "Since entry: -3.93% (Day 1).", "kind": "risk", "source": "SwingScope data", "url": ""}]}, "AETHER": {"symbol": "AETHER", "name": "AETHER INDUSTRIES LIMITED", "view": "Neutral to bearish", "view_score": -0.62, "tone": "mod-bear", "summary": "12.2% below its 12-month high \u2014 consolidating after a big run.", "why": "Results, thin liquidity, stretched valuation", "points": [{"text": "12.2% below its 12-month high \u2014 consolidating after a big run.", "kind": "context", "source": "SwingScope data", "url": ""}, {"text": "Thin liquidity (\u20b939 cr/day) \u2014 gap risk in a falling market.", "kind": "risk", "source": "SwingScope data", "url": ""}, {"text": "Valuation is stretched (P/E \u2248 91).", "kind": "risk", "source": "SwingScope data", "url": ""}, {"text": "[Results] Ather Energy shares: 125% YTD returns! Experts give 'portfolio stock' tag after Q2 results 2026 | Target, stop-loss", "kind": "catalyst", "source": "TradingView", "url": "https://news.google.com/rss/articles/CBMi9wFBVV95cUxPYmlLLVpwT1RwQ2tYR1F6WlNVTWJ3N3h6R3MyX2ZvVlhHUjlDZVdHTHhGeVF1dnBQOEdjb21UQUFuclpzTVh6a283ZF9EWWJqb1lreEp1dzZFMEx0eVJLQmlUcXc2elo2SEE2c3ZiVEZLYk1sLVJkZ191cnZOb0QyT1pBSUxfR1o2UkRoMlN5dnlnWklGMC1OTVp0bmlNaFJwdW1JOUhFdkg1TWlIZl9xUUwweTlfUThhaE9oeGstZ1ZnaUZGckh0b2xsSldWb3B1Um9MUWtCUDJzTmQycFVUTExRUFdGSkx1a0hubHVjYmtLZEo1ZGRr?oc=5"}, {"text": "Since entry: +1.18% (Day 1).", "kind": "catalyst", "source": "SwingScope data", "url": ""}]}, "SBC": {"symbol": "SBC", "name": "SBC EXPORTS LIMITED", "view": "Strongest, bullish", "view_score": 2.0, "tone": "strong-bull", "summary": "Close is only -0.0% below its 12-month high \u2014 relative strength near highs.", "why": "Near highs, accelerating momentum, thin liquidity", "points": [{"text": "Close is only -0.0% below its 12-month high \u2014 relative strength near highs.", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "3-1 month return +27.2% \u2014 recent momentum is accelerating.", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "Lowest volatility of the batch (36%).", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "Thin liquidity (\u20b948 cr/day) \u2014 gap risk in a falling market.", "kind": "risk", "source": "SwingScope data", "url": ""}, {"text": "Premium valuation (P/E \u2248 78).", "kind": "context", "source": "SwingScope data", "url": ""}, {"text": "Since entry: -1.34% (Day 1).", "kind": "risk", "source": "SwingScope data", "url": ""}]}, "SYRMA": {"symbol": "SYRMA", "name": "SYRMA SGS TECHNOLOGY LTD", "view": "Bullish", "view_score": 1.51, "tone": "bull", "summary": "6.4% below its 12-month high: a shallow pullback inside the uptrend.", "why": "Shallow pullback, accelerating momentum", "points": [{"text": "6.4% below its 12-month high: a shallow pullback inside the uptrend.", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "3-1 month return +30.0% \u2014 recent momentum is accelerating.", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "Premium valuation (P/E \u2248 85).", "kind": "context", "source": "SwingScope data", "url": ""}, {"text": "Earnings growth \u2248 86% YoY (latest quarter).", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "[Results] Syrma SGS Q2 results: Profit nearly doubles to \u20b9117 crore, revenue jumps 74%", "kind": "catalyst", "source": "CNBC TV18", "url": "https://news.google.com/rss/articles/CBMirAFBVV95cUxQWWVNajdfcWthd1FGS3dENzdIeWltVzdfWTRueHBPYlFWSEs4MHNnOW9HQnVWODIxTENyb21PblA5Y3d2Ym4zeVkza29VZ0VQSENCb3dhUVQyN1N4WFlGWnNTaUt1czBRWl9NTy01UmU0bExnQXZKMUhpeW8yUU9GT0tPbDFpeHh6em5GZzNZNzZTYUFuSkR6RlFwS0Fwcy1SQjZLSHdDdTRFaTZm0gGsAUFVX3lxTFBZZU1qN19xa2F3UUZLd0Q3N0h5aW1XN19ZNG54cE9iUVZISzgwc2c5b0dCdVY4MjFMQ3JvbU9uUDljd3ZibjN5WTNrb1VnRVBIQ0Jvd2FRVDI3U3hYWUZac1NpS3VzMFFaX01PLTVSZTRsTGdBdkoxSGl5bzJRT0ZPS09sMWl4eHp6bkZnM1k3NlNhQW5KRHpGUXBLQXBzLVJCNktId0N1NEVpNmY?oc=5"}, {"text": "Since entry: -2.97% (Day 1).", "kind": "risk", "source": "SwingScope data", "url": ""}]}, "TDPOWERSYS": {"symbol": "TDPOWERSYS", "name": "TD POWER SYSTEMS LTD.", "view": "Neutral to bullish", "view_score": 0.5, "tone": "spec", "summary": "12.9% below its 12-month high \u2014 consolidating after a big run.", "why": "Accelerating momentum, strong earnings growth, high volatility", "points": [{"text": "12.9% below its 12-month high \u2014 consolidating after a big run.", "kind": "context", "source": "SwingScope data", "url": ""}, {"text": "3-1 month return +39.4% \u2014 recent momentum is accelerating.", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "High volatility (63%).", "kind": "risk", "source": "SwingScope data", "url": ""}, {"text": "Premium valuation (P/E \u2248 81).", "kind": "context", "source": "SwingScope data", "url": ""}, {"text": "Earnings growth \u2248 72% YoY (latest quarter).", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "Since entry: -0.77% (Day 1).", "kind": "risk", "source": "SwingScope data", "url": ""}]}, "RATNAVEER": {"symbol": "RATNAVEER", "name": "RATNAVEER PRECISION ENG L", "view": "Strongest, bullish", "view_score": 1.8, "tone": "strong-bull", "summary": "Close is only -0.0% below its 12-month high \u2014 relative strength near highs.", "why": "Near highs, very strong 6-1", "points": [{"text": "Close is only -0.0% below its 12-month high \u2014 relative strength near highs.", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "6-1 month return +106% \u2014 very strong medium-term momentum.", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "3-1 month return +77.9% \u2014 recent momentum is accelerating.", "kind": "catalyst", "source": "SwingScope data", "url": ""}, {"text": "Most liquid name in the batch (\u20b9178 cr/day).", "kind": "context", "source": "SwingScope data", "url": ""}, {"text": "[Results] Ratnaveer Precision Engineering Q2 FY27 Earnings Call on 3 Nov", "kind": "context", "source": "Kalkine India", "url": "https://news.google.com/rss/articles/CBMi1gFBVV95cUxOT0FlR3g5MTluX3phZ0tWLW1iVHAzbUh0dGFBRjcyLTBFQTl5bXkweTNIYlAtYjFSYlhBUFJYQ05VOVUzUFRLaDhwcmg0b2xZSE1JMV9rNlpuMFFDYTljQnpjdE5rMDJ2YWxGaDJZMFpCWFd5RDBuYjFvbE8xS085dmc0aktudXE5MDc5UlhCUVlQSVBtRnFwbUtwNG1lNkFVM2tWYzNLeDdHTGlhUjBXNEVMZ011Q0RJVkVoM24tWTNHWERXbHZ5U1hhOTRDQ0RmSlBFWDdn?oc=5"}, {"text": "Since entry: +1.71% (Day 1).", "kind": "catalyst", "source": "SwingScope data", "url": ""}]}}, "shortlist": ["SBC", "RATNAVEER", "SYRMA", "AEROFLEX", "TDPOWERSYS", "CPPLUS", "AETHER", "KIRLOSENG", "THANGAMAYL", "SMLMAH"], "missing": []}, "telegram_sent": "2026-10-30", "pending_alerts": []}</t>
         </is>
       </c>
     </row>
